--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hages\Music\polish-library-proptotype\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mirko Vladjic\Music\bookstore-main\bookstore-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C77B1CC-5691-4133-A728-B1B392E49F53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C849AB37-EE31-41F6-9099-6300FD8FC1DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="305" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="194">
   <si>
     <t>cover</t>
   </si>
@@ -110,9 +110,6 @@
     <t>publisher</t>
   </si>
   <si>
-    <t>format</t>
-  </si>
-  <si>
     <t>currency</t>
   </si>
   <si>
@@ -185,9 +182,6 @@
     <t>active</t>
   </si>
   <si>
-    <t>paperback</t>
-  </si>
-  <si>
     <t>ingram</t>
   </si>
   <si>
@@ -200,9 +194,6 @@
     <t>price_gbp</t>
   </si>
   <si>
-    <t>hardcover</t>
-  </si>
-  <si>
     <t>izabela-the-valiant</t>
   </si>
   <si>
@@ -347,9 +338,6 @@
     <t>Another Day of Life</t>
   </si>
   <si>
-    <t>another-day</t>
-  </si>
-  <si>
     <t>light-and-flame</t>
   </si>
   <si>
@@ -374,9 +362,6 @@
     <t>The Last Olympiad</t>
   </si>
   <si>
-    <t>seven-against</t>
-  </si>
-  <si>
     <t>emperor-julian</t>
   </si>
   <si>
@@ -434,9 +419,6 @@
     <t>The Invincible</t>
   </si>
   <si>
-    <t>the-invicible</t>
-  </si>
-  <si>
     <t>Chahary</t>
   </si>
   <si>
@@ -501,13 +483,159 @@
   </si>
   <si>
     <t>chahary</t>
+  </si>
+  <si>
+    <t>format_1</t>
+  </si>
+  <si>
+    <t>format_2</t>
+  </si>
+  <si>
+    <t>format_3</t>
+  </si>
+  <si>
+    <t>sku</t>
+  </si>
+  <si>
+    <t>buy link</t>
+  </si>
+  <si>
+    <t>Hardcover</t>
+  </si>
+  <si>
+    <t>Paperback</t>
+  </si>
+  <si>
+    <t>Ebook</t>
+  </si>
+  <si>
+    <t>Jacek Bocheński</t>
+  </si>
+  <si>
+    <t>Divine Julius</t>
+  </si>
+  <si>
+    <t>Naso the Poet</t>
+  </si>
+  <si>
+    <t>Tiberius Caesar</t>
+  </si>
+  <si>
+    <t>divine-julius</t>
+  </si>
+  <si>
+    <t>naso-the-poet</t>
+  </si>
+  <si>
+    <t>tiberius-caesar</t>
+  </si>
+  <si>
+    <t>covers/divine-julius.jpg</t>
+  </si>
+  <si>
+    <t>covers/naso-the-poet-1.jpg</t>
+  </si>
+  <si>
+    <t>covers/tiberius-caesar.jpg</t>
+  </si>
+  <si>
+    <t>The Roman Trilogy</t>
+  </si>
+  <si>
+    <t>The Wonderful World of Maria Ro</t>
+  </si>
+  <si>
+    <t>the-invincible</t>
+  </si>
+  <si>
+    <t>seven-against-thebes</t>
+  </si>
+  <si>
+    <t>another-day-of-life</t>
+  </si>
+  <si>
+    <r>
+      <t>‎ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0F1111"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>9782919820467</t>
+    </r>
+  </si>
+  <si>
+    <t>978-1607720041</t>
+  </si>
+  <si>
+    <t>Poetry</t>
+  </si>
+  <si>
+    <t>Czesław Miłosz</t>
+  </si>
+  <si>
+    <t>Collected Poems</t>
+  </si>
+  <si>
+    <t>Ecco</t>
+  </si>
+  <si>
+    <t>milosz-collected-poems</t>
+  </si>
+  <si>
+    <t>Wisława Szymborska</t>
+  </si>
+  <si>
+    <t>View with a Grain of Sand</t>
+  </si>
+  <si>
+    <t>Mariner Books</t>
+  </si>
+  <si>
+    <t>Mondrala Press</t>
+  </si>
+  <si>
+    <t>Zbigniew Herbert</t>
+  </si>
+  <si>
+    <t>Selected Poems</t>
+  </si>
+  <si>
+    <t>Adam Zagajewski</t>
+  </si>
+  <si>
+    <t>Without End: New and Selected Poems</t>
+  </si>
+  <si>
+    <t>Farrar, Straus and Giroux</t>
+  </si>
+  <si>
+    <t>Jerzy Ficowski</t>
+  </si>
+  <si>
+    <t>Everything I Don’t Know</t>
+  </si>
+  <si>
+    <t>Seagull Books</t>
+  </si>
+  <si>
+    <t>Tadeusz Różewicz</t>
+  </si>
+  <si>
+    <t>W. W. Norton</t>
+  </si>
+  <si>
+    <t>Map: Collected and Last Poems</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -522,30 +650,77 @@
       <family val="2"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF0F1111"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FFC00000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF0F1111"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="3" tint="0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="3" tint="0.249977111117893"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="3" tint="0.249977111117893"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FF0F1111"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -568,15 +743,25 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -911,104 +1096,168 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01CE5F32-AD1D-47CB-A8F1-52ACBFFA0BE8}">
-  <dimension ref="A1:AA29"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:AU39"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="13.6640625" customWidth="1"/>
-    <col min="4" max="4" width="26.86328125" customWidth="1"/>
-    <col min="7" max="7" width="14.265625" style="4" customWidth="1"/>
-    <col min="9" max="10" width="9.06640625" style="5"/>
+    <col min="1" max="1" width="29.140625" customWidth="1"/>
+    <col min="2" max="3" width="13.7109375" customWidth="1"/>
+    <col min="4" max="4" width="26.85546875" customWidth="1"/>
+    <col min="8" max="9" width="9.140625" style="9"/>
+    <col min="10" max="11" width="9" style="9"/>
+    <col min="12" max="14" width="9.140625" style="9"/>
+    <col min="15" max="15" width="16" style="11" customWidth="1"/>
+    <col min="16" max="22" width="9.140625" style="4"/>
+    <col min="23" max="23" width="17" style="15" customWidth="1"/>
+    <col min="24" max="30" width="9.140625" style="6"/>
+    <col min="31" max="31" width="22" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>18</v>
       </c>
       <c r="B1" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" t="s">
+        <v>41</v>
+      </c>
+      <c r="G1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="K1" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="L1" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="N1" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="Q1" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="R1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="W1" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="X1" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="Y1" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="Z1" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA1" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB1" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="AC1" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="AD1" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="AE1" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AP1" t="s">
         <v>47</v>
       </c>
-      <c r="D1" t="s">
-        <v>32</v>
-      </c>
-      <c r="E1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G1" s="4" t="s">
+      <c r="AQ1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:47" ht="36" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>34</v>
       </c>
-      <c r="H1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="K1" t="s">
-        <v>0</v>
-      </c>
-      <c r="L1" t="s">
-        <v>36</v>
-      </c>
-      <c r="M1" t="s">
-        <v>23</v>
-      </c>
-      <c r="N1" t="s">
-        <v>24</v>
-      </c>
-      <c r="O1" t="s">
-        <v>25</v>
-      </c>
-      <c r="P1" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>27</v>
-      </c>
-      <c r="R1" t="s">
-        <v>28</v>
-      </c>
-      <c r="S1" t="s">
-        <v>29</v>
-      </c>
-      <c r="T1" t="s">
-        <v>37</v>
-      </c>
-      <c r="U1" t="s">
-        <v>30</v>
-      </c>
-      <c r="V1" t="s">
-        <v>48</v>
-      </c>
-      <c r="W1" t="s">
-        <v>38</v>
-      </c>
-      <c r="X1" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" ht="23.25" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>35</v>
-      </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -1019,43 +1268,61 @@
       <c r="E2" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="2">
+      <c r="H2" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="O2" s="11">
+        <v>9780684812199</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>15</v>
+      </c>
+      <c r="R2" s="4">
+        <v>18</v>
+      </c>
+      <c r="S2" s="4">
+        <v>15</v>
+      </c>
+      <c r="W2" s="7">
         <v>9780306809330</v>
       </c>
-      <c r="H2">
+      <c r="X2" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y2" s="6">
         <v>15</v>
       </c>
-      <c r="I2" s="5">
+      <c r="Z2" s="6">
         <v>18</v>
       </c>
-      <c r="J2" s="5">
+      <c r="AA2" s="6">
         <v>15</v>
       </c>
-      <c r="K2" t="s">
+      <c r="AF2" t="s">
         <v>13</v>
       </c>
-      <c r="L2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N2" t="s">
-        <v>49</v>
-      </c>
-      <c r="U2" t="s">
-        <v>31</v>
-      </c>
-      <c r="V2" t="s">
-        <v>31</v>
-      </c>
-      <c r="X2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="34.9" x14ac:dyDescent="0.45">
+      <c r="AG2" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:47" ht="36" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C3">
         <v>200</v>
@@ -1066,43 +1333,64 @@
       <c r="E3" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="2">
+      <c r="H3" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="O3" s="11">
+        <v>9780312625924</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>18</v>
+      </c>
+      <c r="R3" s="4">
+        <v>18</v>
+      </c>
+      <c r="S3" s="4">
+        <v>15</v>
+      </c>
+      <c r="W3" s="7">
         <v>9780312625948</v>
       </c>
-      <c r="H3">
+      <c r="X3" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y3" s="6">
         <v>18</v>
       </c>
-      <c r="I3" s="5">
+      <c r="Z3" s="6">
         <v>18</v>
       </c>
-      <c r="J3" s="5">
+      <c r="AA3" s="6">
         <v>15</v>
       </c>
-      <c r="K3" t="s">
+      <c r="AE3" s="14">
+        <v>9781429964395</v>
+      </c>
+      <c r="AF3" t="s">
         <v>14</v>
       </c>
-      <c r="L3" t="s">
-        <v>50</v>
-      </c>
-      <c r="N3" t="s">
-        <v>49</v>
-      </c>
-      <c r="U3" t="s">
-        <v>31</v>
-      </c>
-      <c r="V3" t="s">
-        <v>31</v>
-      </c>
-      <c r="X3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="23.25" x14ac:dyDescent="0.45">
+      <c r="AG3" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:47" ht="24" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B4" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C4">
         <v>300</v>
@@ -1113,43 +1401,64 @@
       <c r="E4" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="O4" s="11">
+        <v>9780008411251</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>20</v>
+      </c>
+      <c r="R4" s="4">
+        <v>20</v>
+      </c>
+      <c r="S4" s="4">
+        <v>16</v>
+      </c>
+      <c r="W4" s="7">
         <v>9780008521684</v>
       </c>
-      <c r="H4">
+      <c r="X4" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y4" s="6">
         <v>20</v>
       </c>
-      <c r="I4" s="5">
+      <c r="Z4" s="6">
         <v>20</v>
       </c>
-      <c r="J4" s="5">
+      <c r="AA4" s="6">
         <v>16</v>
       </c>
-      <c r="K4" t="s">
+      <c r="AE4" s="14">
+        <v>9780008411275</v>
+      </c>
+      <c r="AF4" t="s">
         <v>20</v>
       </c>
-      <c r="L4" t="s">
-        <v>50</v>
-      </c>
-      <c r="N4" t="s">
-        <v>49</v>
-      </c>
-      <c r="U4" t="s">
-        <v>31</v>
-      </c>
-      <c r="V4" t="s">
-        <v>31</v>
-      </c>
-      <c r="X4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="34.9" x14ac:dyDescent="0.45">
+      <c r="AG4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:47" ht="36" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C5">
         <v>400</v>
@@ -1160,43 +1469,62 @@
       <c r="E5" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H5" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I5" s="9">
+        <v>44</v>
+      </c>
+      <c r="J5" s="9">
+        <v>45</v>
+      </c>
+      <c r="K5" s="9">
+        <v>38</v>
+      </c>
+      <c r="O5" s="10">
         <v>9780300252200</v>
       </c>
-      <c r="H5">
+      <c r="P5" s="3"/>
+      <c r="W5" s="15">
+        <v>9780300252217</v>
+      </c>
+      <c r="X5" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y5" s="6">
         <v>44</v>
       </c>
-      <c r="I5" s="5">
+      <c r="Z5" s="6">
         <v>45</v>
       </c>
-      <c r="J5" s="5">
+      <c r="AA5" s="6">
         <v>38</v>
       </c>
-      <c r="K5" t="s">
+      <c r="AE5" s="14">
+        <v>9780300252224</v>
+      </c>
+      <c r="AF5" t="s">
         <v>15</v>
       </c>
-      <c r="L5" t="s">
-        <v>50</v>
-      </c>
-      <c r="N5" t="s">
-        <v>54</v>
-      </c>
-      <c r="U5" t="s">
-        <v>31</v>
-      </c>
-      <c r="V5" t="s">
-        <v>31</v>
-      </c>
-      <c r="X5" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="23.25" x14ac:dyDescent="0.45">
+      <c r="AG5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:47" ht="36" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C6">
         <v>500</v>
@@ -1207,43 +1535,59 @@
       <c r="E6" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="2">
+      <c r="H6" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I6" s="9">
+        <v>58</v>
+      </c>
+      <c r="J6" s="9">
+        <v>52</v>
+      </c>
+      <c r="K6" s="9">
+        <v>44</v>
+      </c>
+      <c r="O6" s="10">
         <v>9781472816030</v>
       </c>
-      <c r="H6">
+      <c r="P6" s="3"/>
+      <c r="W6" s="15">
+        <v>9781472816047</v>
+      </c>
+      <c r="X6" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y6" s="6">
         <v>58</v>
       </c>
-      <c r="I6" s="5">
+      <c r="Z6" s="6">
         <v>52</v>
       </c>
-      <c r="J6" s="5">
+      <c r="AA6" s="6">
         <v>44</v>
       </c>
-      <c r="K6" t="s">
+      <c r="AF6" t="s">
         <v>17</v>
       </c>
-      <c r="L6" t="s">
-        <v>50</v>
-      </c>
-      <c r="N6" t="s">
-        <v>54</v>
-      </c>
-      <c r="U6" t="s">
-        <v>31</v>
-      </c>
-      <c r="V6" t="s">
-        <v>31</v>
-      </c>
-      <c r="X6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="23.25" x14ac:dyDescent="0.45">
+      <c r="AG6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO6" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP6" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:47" ht="36" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C7">
         <v>600</v>
@@ -1255,1064 +1599,1852 @@
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="2">
+        <v>42</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="O7" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q7" s="4">
+        <v>23</v>
+      </c>
+      <c r="R7" s="4">
+        <v>20</v>
+      </c>
+      <c r="S7" s="4">
+        <v>18</v>
+      </c>
+      <c r="W7" s="7">
         <v>9781607720058</v>
       </c>
-      <c r="H7">
+      <c r="X7" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y7" s="6">
         <v>23</v>
       </c>
-      <c r="I7" s="5">
+      <c r="Z7" s="6">
         <v>20</v>
       </c>
-      <c r="J7" s="5">
+      <c r="AA7" s="6">
         <v>18</v>
       </c>
-      <c r="K7" t="s">
+      <c r="AF7" t="s">
         <v>16</v>
       </c>
-      <c r="L7" t="s">
-        <v>50</v>
-      </c>
-      <c r="N7" t="s">
-        <v>49</v>
-      </c>
-      <c r="U7" t="s">
-        <v>31</v>
-      </c>
-      <c r="V7" t="s">
-        <v>31</v>
-      </c>
-      <c r="X7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AG7" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO7" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP7" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR7" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C8">
         <v>150</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F8" t="s">
         <v>57</v>
       </c>
-      <c r="E8" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8" s="2">
+      <c r="H8" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q8" s="4">
+        <v>18</v>
+      </c>
+      <c r="R8" s="4">
+        <v>16</v>
+      </c>
+      <c r="S8" s="4">
+        <v>14</v>
+      </c>
+      <c r="W8" s="7">
         <v>9781590173831</v>
       </c>
-      <c r="H8">
+      <c r="X8" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y8" s="6">
         <v>18</v>
       </c>
-      <c r="I8" s="5">
+      <c r="Z8" s="6">
         <v>16</v>
       </c>
-      <c r="J8" s="5">
+      <c r="AA8" s="6">
         <v>14</v>
       </c>
-      <c r="K8" t="s">
-        <v>69</v>
-      </c>
-      <c r="N8" t="s">
-        <v>49</v>
-      </c>
-      <c r="U8" t="s">
-        <v>31</v>
-      </c>
-      <c r="V8" t="s">
-        <v>31</v>
-      </c>
-      <c r="X8" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AE8" s="14">
+        <v>9781590173848</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>66</v>
+      </c>
+      <c r="AO8" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP8" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR8" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="9" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C9">
         <v>250</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E9" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" t="s">
+        <v>58</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q9" s="4">
+        <v>19.5</v>
+      </c>
+      <c r="R9" s="4">
+        <v>18</v>
+      </c>
+      <c r="S9" s="4">
+        <v>17</v>
+      </c>
+      <c r="W9" s="7">
+        <v>9780241524244</v>
+      </c>
+      <c r="X9" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y9" s="6">
+        <v>19.5</v>
+      </c>
+      <c r="Z9" s="6">
+        <v>18</v>
+      </c>
+      <c r="AA9" s="6">
+        <v>17</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>67</v>
+      </c>
+      <c r="AO9" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP9" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="1:47" ht="24" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>63</v>
       </c>
-      <c r="E9" t="s">
-        <v>62</v>
-      </c>
-      <c r="F9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" s="2">
-        <v>9780241524244</v>
-      </c>
-      <c r="H9">
-        <v>19.5</v>
-      </c>
-      <c r="I9" s="5">
-        <v>18</v>
-      </c>
-      <c r="J9" s="5">
-        <v>17</v>
-      </c>
-      <c r="K9" t="s">
-        <v>70</v>
-      </c>
-      <c r="N9" t="s">
-        <v>49</v>
-      </c>
-      <c r="U9" t="s">
-        <v>31</v>
-      </c>
-      <c r="V9" t="s">
-        <v>31</v>
-      </c>
-      <c r="X9" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="23.25" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>66</v>
-      </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C10">
         <v>350</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" t="s">
+        <v>64</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E10" t="s">
-        <v>67</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="2"/>
+      <c r="H10" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q10" s="4">
+        <v>16.96</v>
+      </c>
+      <c r="R10" s="4">
+        <v>15</v>
+      </c>
+      <c r="S10" s="4">
+        <v>13</v>
+      </c>
+      <c r="W10" s="7">
+        <v>9781939810007</v>
+      </c>
+      <c r="X10" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y10" s="6">
+        <v>16.96</v>
+      </c>
+      <c r="Z10" s="6">
+        <v>15</v>
+      </c>
+      <c r="AA10" s="6">
+        <v>13</v>
+      </c>
+      <c r="AF10" t="s">
         <v>68</v>
       </c>
-      <c r="G10" s="2">
-        <v>9781939810007</v>
-      </c>
-      <c r="H10">
-        <v>16.96</v>
-      </c>
-      <c r="I10" s="5">
-        <v>15</v>
-      </c>
-      <c r="J10" s="5">
-        <v>13</v>
-      </c>
-      <c r="K10" t="s">
-        <v>71</v>
-      </c>
-      <c r="N10" t="s">
-        <v>49</v>
-      </c>
-      <c r="U10" t="s">
-        <v>31</v>
-      </c>
-      <c r="V10" t="s">
-        <v>31</v>
-      </c>
-      <c r="X10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AO10" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="B11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C11">
         <v>450</v>
       </c>
       <c r="D11" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" t="s">
+        <v>70</v>
+      </c>
+      <c r="F11" t="s">
+        <v>71</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q11" s="4">
+        <v>20</v>
+      </c>
+      <c r="R11" s="4">
+        <v>19</v>
+      </c>
+      <c r="S11" s="4">
+        <v>17</v>
+      </c>
+      <c r="W11" s="7">
+        <v>9780875807072</v>
+      </c>
+      <c r="X11" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y11" s="6">
+        <v>20</v>
+      </c>
+      <c r="Z11" s="6">
+        <v>19</v>
+      </c>
+      <c r="AA11" s="6">
+        <v>17</v>
+      </c>
+      <c r="AF11" t="s">
         <v>72</v>
       </c>
-      <c r="E11" t="s">
-        <v>73</v>
-      </c>
-      <c r="F11" t="s">
-        <v>74</v>
-      </c>
-      <c r="G11" s="2">
-        <v>9780875807072</v>
-      </c>
-      <c r="H11">
-        <v>20</v>
-      </c>
-      <c r="I11" s="5">
-        <v>19</v>
-      </c>
-      <c r="J11" s="5">
-        <v>17</v>
-      </c>
-      <c r="K11" t="s">
-        <v>75</v>
-      </c>
-      <c r="N11" t="s">
-        <v>49</v>
-      </c>
-      <c r="U11" t="s">
-        <v>31</v>
-      </c>
-      <c r="V11" t="s">
-        <v>31</v>
-      </c>
-      <c r="X11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AO11" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP11" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="B12" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C12">
         <v>550</v>
       </c>
       <c r="D12" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="E12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F12" t="s">
-        <v>84</v>
-      </c>
-      <c r="G12" s="2">
+        <v>81</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I12" s="9">
+        <v>17.989999999999998</v>
+      </c>
+      <c r="J12" s="9">
+        <v>15</v>
+      </c>
+      <c r="K12" s="9">
+        <v>13</v>
+      </c>
+      <c r="O12" s="10">
         <v>9798325216770</v>
       </c>
-      <c r="H12">
+      <c r="P12" s="3"/>
+      <c r="X12" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y12" s="6">
         <v>17.989999999999998</v>
       </c>
-      <c r="I12" s="5">
+      <c r="Z12" s="6">
         <v>15</v>
       </c>
-      <c r="J12" s="5">
+      <c r="AA12" s="6">
         <v>13</v>
       </c>
-      <c r="K12" t="s">
-        <v>86</v>
-      </c>
-      <c r="N12" t="s">
-        <v>54</v>
-      </c>
-      <c r="U12" t="s">
-        <v>31</v>
-      </c>
-      <c r="V12" t="s">
-        <v>31</v>
-      </c>
-      <c r="X12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AF12" t="s">
+        <v>83</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B13" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C13">
         <v>650</v>
       </c>
       <c r="D13" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E13" t="s">
+        <v>76</v>
+      </c>
+      <c r="F13" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" t="s">
+        <v>182</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I13" s="9">
+        <v>24</v>
+      </c>
+      <c r="O13" s="10">
+        <v>9789998791732</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="X13" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y13" s="6">
+        <v>24</v>
+      </c>
+      <c r="AF13" t="s">
         <v>78</v>
       </c>
-      <c r="E13" t="s">
-        <v>79</v>
-      </c>
-      <c r="F13" t="s">
-        <v>80</v>
-      </c>
-      <c r="G13" s="2">
-        <v>9789998791732</v>
-      </c>
-      <c r="H13">
-        <v>24</v>
-      </c>
-      <c r="K13" t="s">
-        <v>81</v>
-      </c>
-      <c r="N13" t="s">
-        <v>54</v>
-      </c>
-      <c r="U13" t="s">
-        <v>31</v>
-      </c>
-      <c r="V13" t="s">
-        <v>31</v>
-      </c>
-      <c r="X13" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AO13" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP13" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR13" t="s">
+        <v>40</v>
+      </c>
+      <c r="AT13" t="s">
+        <v>168</v>
+      </c>
+      <c r="AU13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B14" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C14">
         <v>100</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E14" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F14" t="s">
-        <v>91</v>
-      </c>
-      <c r="G14" s="2">
+        <v>88</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I14" s="9">
+        <v>15</v>
+      </c>
+      <c r="J14" s="9">
+        <v>12</v>
+      </c>
+      <c r="K14" s="9">
+        <v>10</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>15</v>
+      </c>
+      <c r="R14" s="4">
+        <v>12</v>
+      </c>
+      <c r="S14" s="4">
+        <v>10</v>
+      </c>
+      <c r="W14" s="7">
         <v>9781852429454</v>
       </c>
-      <c r="H14">
+      <c r="X14" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y14" s="6">
         <v>15</v>
       </c>
-      <c r="I14" s="5">
+      <c r="Z14" s="6">
         <v>12</v>
       </c>
-      <c r="J14" s="5">
+      <c r="AA14" s="6">
         <v>10</v>
       </c>
-      <c r="K14" t="s">
-        <v>101</v>
-      </c>
-      <c r="N14" t="s">
-        <v>49</v>
-      </c>
-      <c r="U14" t="s">
-        <v>31</v>
-      </c>
-      <c r="V14" t="s">
-        <v>31</v>
-      </c>
-      <c r="X14" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.45">
+      <c r="AF14" t="s">
+        <v>98</v>
+      </c>
+      <c r="AO14" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP14" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR14" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B15" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C15">
         <v>100</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
+        <v>91</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I15" s="9">
+        <v>14</v>
+      </c>
+      <c r="J15" s="9">
+        <v>14</v>
+      </c>
+      <c r="K15" s="9">
+        <v>12</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q15" s="4">
+        <v>14</v>
+      </c>
+      <c r="R15" s="4">
+        <v>14</v>
+      </c>
+      <c r="S15" s="4">
+        <v>12</v>
+      </c>
+      <c r="W15" s="7">
+        <v>9780679738015</v>
+      </c>
+      <c r="X15" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y15" s="6">
+        <v>14</v>
+      </c>
+      <c r="Z15" s="6">
+        <v>14</v>
+      </c>
+      <c r="AA15" s="6">
+        <v>12</v>
+      </c>
+      <c r="AF15" t="s">
+        <v>95</v>
+      </c>
+      <c r="AO15" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP15" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:47" ht="24" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>94</v>
       </c>
-      <c r="G15" s="2">
-        <v>9780679738015</v>
-      </c>
-      <c r="H15">
-        <v>14</v>
-      </c>
-      <c r="I15" s="5">
-        <v>14</v>
-      </c>
-      <c r="J15" s="5">
-        <v>12</v>
-      </c>
-      <c r="K15" t="s">
-        <v>98</v>
-      </c>
-      <c r="N15" t="s">
-        <v>49</v>
-      </c>
-      <c r="U15" t="s">
-        <v>31</v>
-      </c>
-      <c r="V15" t="s">
-        <v>31</v>
-      </c>
-      <c r="X15" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="23.25" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
+      <c r="B16" t="s">
         <v>97</v>
-      </c>
-      <c r="B16" t="s">
-        <v>100</v>
       </c>
       <c r="C16">
         <v>400</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="E16" t="s">
-        <v>94</v>
-      </c>
-      <c r="G16" s="2">
+        <v>91</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I16" s="9">
+        <v>14</v>
+      </c>
+      <c r="J16" s="9">
+        <v>14</v>
+      </c>
+      <c r="K16" s="9">
+        <v>12</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q16" s="4">
+        <v>14</v>
+      </c>
+      <c r="R16" s="4">
+        <v>14</v>
+      </c>
+      <c r="S16" s="4">
+        <v>12</v>
+      </c>
+      <c r="W16" s="7">
         <v>9780141188034</v>
       </c>
-      <c r="H16">
+      <c r="X16" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y16" s="6">
         <v>14</v>
       </c>
-      <c r="I16" s="5">
+      <c r="Z16" s="6">
         <v>14</v>
       </c>
-      <c r="J16" s="5">
+      <c r="AA16" s="6">
         <v>12</v>
       </c>
-      <c r="K16" t="s">
-        <v>99</v>
-      </c>
-      <c r="N16" t="s">
-        <v>49</v>
-      </c>
-      <c r="U16" t="s">
-        <v>31</v>
-      </c>
-      <c r="V16" t="s">
-        <v>31</v>
-      </c>
-      <c r="X16" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="AF16" t="s">
+        <v>96</v>
+      </c>
+      <c r="AO16" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP16" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>103</v>
+        <v>171</v>
       </c>
       <c r="B17" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="C17">
         <v>400</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="E17" t="s">
-        <v>94</v>
-      </c>
-      <c r="G17" s="2">
+        <v>91</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I17" s="9">
+        <v>13</v>
+      </c>
+      <c r="J17" s="9">
+        <v>12</v>
+      </c>
+      <c r="K17" s="9">
+        <v>11</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>13</v>
+      </c>
+      <c r="R17" s="4">
+        <v>12</v>
+      </c>
+      <c r="S17" s="4">
+        <v>11</v>
+      </c>
+      <c r="W17" s="7">
         <v>9780375726293</v>
       </c>
-      <c r="H17">
+      <c r="X17" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y17" s="6">
         <v>13</v>
       </c>
-      <c r="I17" s="5">
+      <c r="Z17" s="6">
         <v>12</v>
       </c>
-      <c r="J17" s="5">
+      <c r="AA17" s="6">
         <v>11</v>
       </c>
-      <c r="K17" t="s">
-        <v>137</v>
-      </c>
-      <c r="N17" t="s">
-        <v>49</v>
-      </c>
-      <c r="U17" t="s">
-        <v>31</v>
-      </c>
-      <c r="V17" t="s">
-        <v>31</v>
-      </c>
-      <c r="X17" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="AF17" t="s">
+        <v>131</v>
+      </c>
+      <c r="AO17" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP17" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B18" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C18">
         <v>600</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E18" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F18" t="s">
-        <v>80</v>
-      </c>
-      <c r="G18" s="2">
+        <v>77</v>
+      </c>
+      <c r="G18" t="s">
+        <v>182</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I18" s="9">
+        <v>25</v>
+      </c>
+      <c r="J18" s="9">
+        <v>24</v>
+      </c>
+      <c r="K18" s="9">
+        <v>22</v>
+      </c>
+      <c r="O18" s="10">
         <v>9782919820382</v>
       </c>
-      <c r="H18">
+      <c r="P18" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q18" s="4">
         <v>25</v>
       </c>
-      <c r="I18" s="5">
+      <c r="R18" s="4">
         <v>24</v>
       </c>
-      <c r="J18" s="5">
+      <c r="S18" s="4">
         <v>22</v>
       </c>
-      <c r="K18" t="s">
-        <v>116</v>
-      </c>
-      <c r="N18" t="s">
-        <v>54</v>
-      </c>
-      <c r="U18" t="s">
-        <v>31</v>
-      </c>
-      <c r="V18" t="s">
-        <v>31</v>
-      </c>
-      <c r="X18" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="X18" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y18" s="6">
+        <v>25</v>
+      </c>
+      <c r="Z18" s="6">
+        <v>24</v>
+      </c>
+      <c r="AA18" s="6">
+        <v>22</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>111</v>
+      </c>
+      <c r="AO18" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP18" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR18" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>112</v>
+        <v>170</v>
       </c>
       <c r="B19" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C19">
         <v>800</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E19" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F19" t="s">
-        <v>80</v>
-      </c>
-      <c r="G19" s="2">
+        <v>77</v>
+      </c>
+      <c r="G19" t="s">
+        <v>182</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I19" s="9">
+        <v>25</v>
+      </c>
+      <c r="J19" s="9">
+        <v>24</v>
+      </c>
+      <c r="K19" s="9">
+        <v>20</v>
+      </c>
+      <c r="O19" s="10">
         <v>9789998793729</v>
       </c>
-      <c r="H19">
+      <c r="P19" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q19" s="4">
         <v>25</v>
       </c>
-      <c r="I19" s="5">
+      <c r="R19" s="4">
         <v>24</v>
       </c>
-      <c r="J19" s="5">
+      <c r="S19" s="4">
         <v>20</v>
       </c>
-      <c r="K19" t="s">
-        <v>115</v>
-      </c>
-      <c r="N19" t="s">
-        <v>54</v>
-      </c>
-      <c r="U19" t="s">
-        <v>31</v>
-      </c>
-      <c r="V19" t="s">
-        <v>31</v>
-      </c>
-      <c r="X19" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="X19" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y19" s="6">
+        <v>25</v>
+      </c>
+      <c r="Z19" s="6">
+        <v>24</v>
+      </c>
+      <c r="AA19" s="6">
+        <v>20</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>110</v>
+      </c>
+      <c r="AO19" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP19" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B20" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C20">
         <v>900</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E20" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F20" t="s">
-        <v>80</v>
-      </c>
-      <c r="G20" s="4">
+        <v>77</v>
+      </c>
+      <c r="G20" t="s">
+        <v>182</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I20" s="9">
+        <v>27</v>
+      </c>
+      <c r="J20" s="9">
+        <v>25</v>
+      </c>
+      <c r="K20" s="9">
+        <v>22</v>
+      </c>
+      <c r="O20" s="8">
         <v>9782919840052</v>
       </c>
-      <c r="H20">
+      <c r="P20" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q20" s="4">
         <v>27</v>
       </c>
-      <c r="I20" s="5">
+      <c r="R20" s="4">
         <v>25</v>
       </c>
-      <c r="J20" s="5">
+      <c r="S20" s="4">
         <v>22</v>
       </c>
-      <c r="K20" t="s">
-        <v>117</v>
-      </c>
-      <c r="N20" t="s">
-        <v>54</v>
-      </c>
-      <c r="U20" t="s">
-        <v>31</v>
-      </c>
-      <c r="V20" t="s">
-        <v>31</v>
-      </c>
-      <c r="X20" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="X20" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y20" s="6">
+        <v>27</v>
+      </c>
+      <c r="Z20" s="6">
+        <v>25</v>
+      </c>
+      <c r="AA20" s="6">
+        <v>22</v>
+      </c>
+      <c r="AF20" t="s">
+        <v>112</v>
+      </c>
+      <c r="AO20" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP20" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B21" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C21">
         <v>1000</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E21" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F21" t="s">
-        <v>80</v>
-      </c>
-      <c r="G21" s="4">
+        <v>77</v>
+      </c>
+      <c r="G21" t="s">
+        <v>182</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I21" s="9">
+        <v>25</v>
+      </c>
+      <c r="J21" s="9">
+        <v>24</v>
+      </c>
+      <c r="K21" s="9">
+        <v>20</v>
+      </c>
+      <c r="O21" s="8">
         <v>9782919820290</v>
       </c>
-      <c r="H21">
+      <c r="P21" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q21" s="4">
         <v>25</v>
       </c>
-      <c r="I21" s="5">
+      <c r="R21" s="4">
         <v>24</v>
       </c>
-      <c r="J21" s="5">
+      <c r="S21" s="4">
         <v>20</v>
       </c>
-      <c r="K21" t="s">
-        <v>118</v>
-      </c>
-      <c r="N21" t="s">
-        <v>54</v>
-      </c>
-      <c r="U21" t="s">
-        <v>31</v>
-      </c>
-      <c r="V21" t="s">
-        <v>31</v>
-      </c>
-      <c r="X21" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="X21" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y21" s="6">
+        <v>25</v>
+      </c>
+      <c r="Z21" s="6">
+        <v>24</v>
+      </c>
+      <c r="AA21" s="6">
+        <v>20</v>
+      </c>
+      <c r="AF21" t="s">
+        <v>113</v>
+      </c>
+      <c r="AO21" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP21" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B22" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C22">
         <v>600</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="E22" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F22" t="s">
-        <v>125</v>
-      </c>
-      <c r="G22" s="4">
+        <v>120</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I22" s="9">
+        <v>10</v>
+      </c>
+      <c r="J22" s="9">
+        <v>9</v>
+      </c>
+      <c r="K22" s="9">
+        <v>8</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q22" s="4">
+        <v>10</v>
+      </c>
+      <c r="R22" s="4">
+        <v>9</v>
+      </c>
+      <c r="S22" s="4">
+        <v>8</v>
+      </c>
+      <c r="W22" s="3">
         <v>9780156027601</v>
       </c>
-      <c r="H22">
+      <c r="X22" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y22" s="6">
         <v>10</v>
       </c>
-      <c r="I22" s="5">
+      <c r="Z22" s="6">
         <v>9</v>
       </c>
-      <c r="J22" s="5">
+      <c r="AA22" s="6">
         <v>8</v>
       </c>
-      <c r="K22" t="s">
-        <v>126</v>
-      </c>
-      <c r="N22" t="s">
-        <v>49</v>
-      </c>
-      <c r="U22" t="s">
-        <v>31</v>
-      </c>
-      <c r="V22" t="s">
-        <v>31</v>
-      </c>
-      <c r="X22" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="AF22" t="s">
+        <v>121</v>
+      </c>
+      <c r="AO22" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP22" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR22" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="23" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="B23" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C23">
         <v>200</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="E23" t="s">
+        <v>119</v>
+      </c>
+      <c r="F23" t="s">
         <v>124</v>
       </c>
-      <c r="F23" t="s">
-        <v>129</v>
-      </c>
-      <c r="G23" s="4">
+      <c r="H23" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I23" s="9">
+        <v>17</v>
+      </c>
+      <c r="J23" s="9">
+        <v>15</v>
+      </c>
+      <c r="K23" s="9">
+        <v>12</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q23" s="4">
+        <v>17</v>
+      </c>
+      <c r="R23" s="4">
+        <v>15</v>
+      </c>
+      <c r="S23" s="4">
+        <v>12</v>
+      </c>
+      <c r="W23" s="3">
         <v>9780156306300</v>
       </c>
-      <c r="H23">
+      <c r="X23" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y23" s="6">
         <v>17</v>
       </c>
-      <c r="I23" s="5">
+      <c r="Z23" s="6">
         <v>15</v>
       </c>
-      <c r="J23" s="5">
+      <c r="AA23" s="6">
         <v>12</v>
       </c>
-      <c r="K23" t="s">
-        <v>130</v>
-      </c>
-      <c r="N23" t="s">
-        <v>49</v>
-      </c>
-      <c r="U23" t="s">
-        <v>31</v>
-      </c>
-      <c r="V23" t="s">
-        <v>31</v>
-      </c>
-      <c r="X23" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="AF23" t="s">
+        <v>125</v>
+      </c>
+      <c r="AO23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR23" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>132</v>
+        <v>169</v>
       </c>
       <c r="B24" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C24">
         <v>600</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E24" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="F24" t="s">
-        <v>68</v>
-      </c>
-      <c r="G24" s="4">
+        <v>65</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I24" s="9">
+        <v>17</v>
+      </c>
+      <c r="J24" s="9">
+        <v>16</v>
+      </c>
+      <c r="K24" s="9">
+        <v>13</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q24" s="4">
+        <v>17</v>
+      </c>
+      <c r="R24" s="4">
+        <v>16</v>
+      </c>
+      <c r="S24" s="4">
+        <v>13</v>
+      </c>
+      <c r="W24" s="3">
         <v>9780262357685</v>
       </c>
-      <c r="H24">
+      <c r="X24" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y24" s="6">
         <v>17</v>
       </c>
-      <c r="I24" s="5">
+      <c r="Z24" s="6">
         <v>16</v>
       </c>
-      <c r="J24" s="5">
+      <c r="AA24" s="6">
         <v>13</v>
       </c>
-      <c r="K24" t="s">
-        <v>136</v>
-      </c>
-      <c r="N24" t="s">
-        <v>49</v>
-      </c>
-      <c r="U24" t="s">
-        <v>31</v>
-      </c>
-      <c r="V24" t="s">
-        <v>31</v>
-      </c>
-      <c r="X24" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="AF24" t="s">
+        <v>130</v>
+      </c>
+      <c r="AO24" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP24" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR24" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="25" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="B25" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="C25">
         <v>100</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E25" t="s">
+        <v>76</v>
+      </c>
+      <c r="F25" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" t="s">
+        <v>182</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I25" s="9">
+        <v>17</v>
+      </c>
+      <c r="J25" s="9">
+        <v>16</v>
+      </c>
+      <c r="K25" s="9">
+        <v>15</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q25" s="4">
+        <v>17</v>
+      </c>
+      <c r="R25" s="4">
+        <v>16</v>
+      </c>
+      <c r="S25" s="4">
+        <v>15</v>
+      </c>
+      <c r="W25" s="3">
+        <v>9782919840106</v>
+      </c>
+      <c r="X25" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y25" s="6">
+        <v>17</v>
+      </c>
+      <c r="Z25" s="6">
+        <v>16</v>
+      </c>
+      <c r="AA25" s="6">
+        <v>15</v>
+      </c>
+      <c r="AF25" t="s">
+        <v>128</v>
+      </c>
+      <c r="AO25" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP25" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR25" t="s">
+        <v>40</v>
+      </c>
+      <c r="AT25" t="s">
+        <v>168</v>
+      </c>
+      <c r="AU25">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>133</v>
       </c>
-      <c r="E25" t="s">
-        <v>79</v>
-      </c>
-      <c r="F25" t="s">
-        <v>80</v>
-      </c>
-      <c r="H25">
-        <v>17</v>
-      </c>
-      <c r="I25" s="5">
-        <v>16</v>
-      </c>
-      <c r="J25" s="5">
-        <v>15</v>
-      </c>
-      <c r="K25" t="s">
-        <v>134</v>
-      </c>
-      <c r="N25" t="s">
-        <v>49</v>
-      </c>
-      <c r="U25" t="s">
-        <v>31</v>
-      </c>
-      <c r="V25" t="s">
-        <v>31</v>
-      </c>
-      <c r="X25" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>139</v>
-      </c>
       <c r="B26" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C26">
         <v>100</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="E26" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="F26" t="s">
-        <v>80</v>
-      </c>
-      <c r="G26" s="4">
+        <v>77</v>
+      </c>
+      <c r="G26" t="s">
+        <v>182</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I26" s="9">
+        <v>24</v>
+      </c>
+      <c r="J26" s="9">
+        <v>24</v>
+      </c>
+      <c r="K26" s="9">
+        <v>20</v>
+      </c>
+      <c r="O26" s="8">
         <v>9789998791671</v>
       </c>
-      <c r="H26">
+      <c r="P26" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q26" s="4">
         <v>24</v>
       </c>
-      <c r="I26" s="5">
+      <c r="R26" s="4">
         <v>24</v>
       </c>
-      <c r="J26" s="5">
+      <c r="S26" s="4">
         <v>20</v>
       </c>
-      <c r="K26" t="s">
-        <v>146</v>
-      </c>
-      <c r="N26" t="s">
-        <v>54</v>
-      </c>
-      <c r="U26" t="s">
-        <v>31</v>
-      </c>
-      <c r="V26" t="s">
-        <v>31</v>
-      </c>
-      <c r="X26" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="X26" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y26" s="6">
+        <v>24</v>
+      </c>
+      <c r="Z26" s="6">
+        <v>24</v>
+      </c>
+      <c r="AA26" s="6">
+        <v>20</v>
+      </c>
+      <c r="AF26" t="s">
+        <v>140</v>
+      </c>
+      <c r="AO26" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP26" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR26" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B27" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C27">
         <v>600</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E27" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="F27" t="s">
-        <v>80</v>
-      </c>
-      <c r="G27" s="4">
+        <v>77</v>
+      </c>
+      <c r="G27" t="s">
+        <v>182</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I27" s="9">
+        <v>24</v>
+      </c>
+      <c r="J27" s="9">
+        <v>24</v>
+      </c>
+      <c r="K27" s="9">
+        <v>20</v>
+      </c>
+      <c r="O27" s="8">
         <v>9789998791794</v>
       </c>
-      <c r="H27">
+      <c r="P27" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q27" s="4">
         <v>24</v>
       </c>
-      <c r="I27" s="5">
+      <c r="R27" s="4">
         <v>24</v>
       </c>
-      <c r="J27" s="5">
+      <c r="S27" s="4">
         <v>20</v>
       </c>
-      <c r="K27" t="s">
-        <v>147</v>
-      </c>
-      <c r="N27" t="s">
-        <v>54</v>
-      </c>
-      <c r="U27" t="s">
-        <v>31</v>
-      </c>
-      <c r="V27" t="s">
-        <v>31</v>
-      </c>
-      <c r="X27" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="X27" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y27" s="6">
+        <v>24</v>
+      </c>
+      <c r="Z27" s="6">
+        <v>24</v>
+      </c>
+      <c r="AA27" s="6">
+        <v>20</v>
+      </c>
+      <c r="AF27" t="s">
+        <v>141</v>
+      </c>
+      <c r="AO27" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP27" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR27" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="28" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="B28" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C28">
         <v>100</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="E28" t="s">
         <v>12</v>
       </c>
       <c r="F28" t="s">
-        <v>80</v>
-      </c>
-      <c r="G28" s="4">
+        <v>77</v>
+      </c>
+      <c r="G28" t="s">
+        <v>182</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I28" s="9">
+        <v>21</v>
+      </c>
+      <c r="J28" s="9">
+        <v>20</v>
+      </c>
+      <c r="K28" s="9">
+        <v>18</v>
+      </c>
+      <c r="O28" s="8">
         <v>9782919820481</v>
       </c>
-      <c r="H28">
+      <c r="P28" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q28" s="4">
         <v>21</v>
       </c>
-      <c r="I28" s="5">
+      <c r="R28" s="4">
         <v>20</v>
       </c>
-      <c r="J28" s="5">
+      <c r="S28" s="4">
         <v>18</v>
       </c>
-      <c r="K28" t="s">
-        <v>153</v>
-      </c>
-      <c r="N28" t="s">
-        <v>54</v>
-      </c>
-      <c r="U28" t="s">
-        <v>31</v>
-      </c>
-      <c r="V28" t="s">
-        <v>31</v>
-      </c>
-      <c r="X28" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.45">
+      <c r="X28" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y28" s="6">
+        <v>21</v>
+      </c>
+      <c r="Z28" s="6">
+        <v>20</v>
+      </c>
+      <c r="AA28" s="6">
+        <v>18</v>
+      </c>
+      <c r="AF28" t="s">
+        <v>147</v>
+      </c>
+      <c r="AO28" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP28" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR28" t="s">
+        <v>40</v>
+      </c>
+      <c r="AT28" t="s">
+        <v>143</v>
+      </c>
+      <c r="AU28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="B29" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="C29">
         <v>200</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E29" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="F29" t="s">
-        <v>80</v>
-      </c>
-      <c r="G29" s="4">
+        <v>77</v>
+      </c>
+      <c r="G29" t="s">
+        <v>182</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I29" s="9">
+        <v>21</v>
+      </c>
+      <c r="J29" s="9">
+        <v>20</v>
+      </c>
+      <c r="K29" s="9">
+        <v>18</v>
+      </c>
+      <c r="O29" s="8">
         <v>9782919820153</v>
       </c>
-      <c r="H29">
+      <c r="P29" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q29" s="4">
         <v>21</v>
       </c>
-      <c r="I29" s="5">
+      <c r="R29" s="4">
         <v>20</v>
       </c>
-      <c r="J29" s="5">
+      <c r="S29" s="4">
         <v>18</v>
       </c>
-      <c r="K29" t="s">
-        <v>151</v>
-      </c>
-      <c r="N29" t="s">
-        <v>54</v>
-      </c>
-      <c r="U29" t="s">
-        <v>31</v>
-      </c>
-      <c r="V29" t="s">
-        <v>31</v>
-      </c>
-      <c r="X29" t="s">
-        <v>41</v>
+      <c r="X29" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="Y29" s="6">
+        <v>21</v>
+      </c>
+      <c r="Z29" s="6">
+        <v>20</v>
+      </c>
+      <c r="AA29" s="6">
+        <v>18</v>
+      </c>
+      <c r="AF29" t="s">
+        <v>145</v>
+      </c>
+      <c r="AO29" t="s">
+        <v>30</v>
+      </c>
+      <c r="AP29" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR29" t="s">
+        <v>40</v>
+      </c>
+      <c r="AT29" t="s">
+        <v>142</v>
+      </c>
+      <c r="AU29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>161</v>
+      </c>
+      <c r="B30" t="s">
+        <v>53</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="E30" t="s">
+        <v>157</v>
+      </c>
+      <c r="F30" t="s">
+        <v>77</v>
+      </c>
+      <c r="G30" t="s">
+        <v>182</v>
+      </c>
+      <c r="H30" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I30" s="9">
+        <v>24</v>
+      </c>
+      <c r="O30" s="12">
+        <v>9789998793781</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF30" t="s">
+        <v>164</v>
+      </c>
+      <c r="AR30" t="s">
+        <v>40</v>
+      </c>
+      <c r="AT30" t="s">
+        <v>167</v>
+      </c>
+      <c r="AU30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>162</v>
+      </c>
+      <c r="B31" t="s">
+        <v>53</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="E31" t="s">
+        <v>157</v>
+      </c>
+      <c r="F31" t="s">
+        <v>77</v>
+      </c>
+      <c r="G31" t="s">
+        <v>182</v>
+      </c>
+      <c r="H31" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I31" s="9">
+        <v>25</v>
+      </c>
+      <c r="O31" s="12">
+        <v>9782919820047</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF31" t="s">
+        <v>165</v>
+      </c>
+      <c r="AR31" t="s">
+        <v>40</v>
+      </c>
+      <c r="AT31" t="s">
+        <v>167</v>
+      </c>
+      <c r="AU31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:47" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>163</v>
+      </c>
+      <c r="B32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="E32" t="s">
+        <v>157</v>
+      </c>
+      <c r="F32" t="s">
+        <v>77</v>
+      </c>
+      <c r="G32" t="s">
+        <v>182</v>
+      </c>
+      <c r="H32" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="I32" s="9">
+        <v>32</v>
+      </c>
+      <c r="O32" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="AF32" t="s">
+        <v>166</v>
+      </c>
+      <c r="AT32" t="s">
+        <v>167</v>
+      </c>
+      <c r="AU32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>178</v>
+      </c>
+      <c r="B33" t="s">
+        <v>174</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="E33" t="s">
+        <v>175</v>
+      </c>
+      <c r="G33" t="s">
+        <v>177</v>
+      </c>
+      <c r="W33" s="15">
+        <v>9780060934941</v>
+      </c>
+    </row>
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
+        <v>174</v>
+      </c>
+      <c r="D34" t="s">
+        <v>180</v>
+      </c>
+      <c r="E34" t="s">
+        <v>179</v>
+      </c>
+      <c r="G34" t="s">
+        <v>181</v>
+      </c>
+      <c r="W34" s="15">
+        <v>9780156005166</v>
+      </c>
+    </row>
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>174</v>
+      </c>
+      <c r="D35" t="s">
+        <v>184</v>
+      </c>
+      <c r="E35" t="s">
+        <v>183</v>
+      </c>
+      <c r="G35" t="s">
+        <v>177</v>
+      </c>
+      <c r="W35" s="15">
+        <v>9780060931544</v>
+      </c>
+    </row>
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>174</v>
+      </c>
+      <c r="D36" t="s">
+        <v>186</v>
+      </c>
+      <c r="E36" t="s">
+        <v>185</v>
+      </c>
+      <c r="G36" t="s">
+        <v>187</v>
+      </c>
+      <c r="W36" s="15">
+        <v>9780374533311</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>174</v>
+      </c>
+      <c r="D37" t="s">
+        <v>189</v>
+      </c>
+      <c r="E37" t="s">
+        <v>188</v>
+      </c>
+      <c r="G37" t="s">
+        <v>190</v>
+      </c>
+      <c r="W37" s="15">
+        <v>9780857425935</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B38" t="s">
+        <v>174</v>
+      </c>
+      <c r="D38" t="s">
+        <v>193</v>
+      </c>
+      <c r="E38" t="s">
+        <v>191</v>
+      </c>
+      <c r="G38" t="s">
+        <v>192</v>
+      </c>
+      <c r="W38" s="15">
+        <v>9780393323856</v>
+      </c>
+    </row>
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B39" t="s">
+        <v>174</v>
+      </c>
+      <c r="E39" t="s">
+        <v>179</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U1:V1048576" xr:uid="{F1FB7CD6-B38A-4A39-862C-8A1111411C8C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO1:AP1048576" xr:uid="{F1FB7CD6-B38A-4A39-862C-8A1111411C8C}">
       <formula1>"yes, no"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N1:N1048576" xr:uid="{D2C177B6-092A-4420-B1E2-D1681CD512E9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33:H1048576 X30:X1048576 P33:P1048576" xr:uid="{D2C177B6-092A-4420-B1E2-D1681CD512E9}">
       <formula1>"hardcover, paperback, eBook, audiobook1"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L1:L1048576" xr:uid="{E592C05B-F748-4394-B2BA-C13419076CB7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG1:AG1048576" xr:uid="{E592C05B-F748-4394-B2BA-C13419076CB7}">
       <formula1>"ingram, gardners, libri, bookvault"</formula1>
     </dataValidation>
   </dataValidations>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mirko Vladjic\Music\bookstore-main\bookstore-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/bookstore-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C849AB37-EE31-41F6-9099-6300FD8FC1DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
+    <workbookView xWindow="3060" yWindow="570" windowWidth="23220" windowHeight="14940" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="218">
   <si>
     <t>cover</t>
   </si>
@@ -554,20 +554,6 @@
     <t>another-day-of-life</t>
   </si>
   <si>
-    <r>
-      <t>‎ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF0F1111"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>9782919820467</t>
-    </r>
-  </si>
-  <si>
     <t>978-1607720041</t>
   </si>
   <si>
@@ -577,21 +563,12 @@
     <t>Czesław Miłosz</t>
   </si>
   <si>
-    <t>Collected Poems</t>
-  </si>
-  <si>
     <t>Ecco</t>
   </si>
   <si>
-    <t>milosz-collected-poems</t>
-  </si>
-  <si>
     <t>Wisława Szymborska</t>
   </si>
   <si>
-    <t>View with a Grain of Sand</t>
-  </si>
-  <si>
     <t>Mariner Books</t>
   </si>
   <si>
@@ -601,9 +578,6 @@
     <t>Zbigniew Herbert</t>
   </si>
   <si>
-    <t>Selected Poems</t>
-  </si>
-  <si>
     <t>Adam Zagajewski</t>
   </si>
   <si>
@@ -613,15 +587,6 @@
     <t>Farrar, Straus and Giroux</t>
   </si>
   <si>
-    <t>Jerzy Ficowski</t>
-  </si>
-  <si>
-    <t>Everything I Don’t Know</t>
-  </si>
-  <si>
-    <t>Seagull Books</t>
-  </si>
-  <si>
     <t>Tadeusz Różewicz</t>
   </si>
   <si>
@@ -629,6 +594,102 @@
   </si>
   <si>
     <t>Map: Collected and Last Poems</t>
+  </si>
+  <si>
+    <t>Sobbing Superpower</t>
+  </si>
+  <si>
+    <t>From the Tree of Knowledge</t>
+  </si>
+  <si>
+    <t>Józef Wittlin</t>
+  </si>
+  <si>
+    <t>Patrick John Corness</t>
+  </si>
+  <si>
+    <t>Krzysztof Kamil Baczyński Poet of the Warsaw Uprising 1944: Saved poetry, manuscripts, and drawings</t>
+  </si>
+  <si>
+    <t>Anna Mickiewicz, Tomasz Mickiewicz, Steve Rushton</t>
+  </si>
+  <si>
+    <t>Krzysztof Kamil Baczynski</t>
+  </si>
+  <si>
+    <t>White Magic and Other Poems</t>
+  </si>
+  <si>
+    <t>without-end</t>
+  </si>
+  <si>
+    <t>sobbing-superpower</t>
+  </si>
+  <si>
+    <t>map-collected-and-last</t>
+  </si>
+  <si>
+    <t>from-tree-of-knowledge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">krzysztof-kamil-baczynski </t>
+  </si>
+  <si>
+    <t>white-magic-baczynski</t>
+  </si>
+  <si>
+    <t>milosz-selected-and-last-poems</t>
+  </si>
+  <si>
+    <t>Selected and Last Poems: 1931-2004</t>
+  </si>
+  <si>
+    <t>covers/milosz-selected-and-last-poems.jpg</t>
+  </si>
+  <si>
+    <t>Poems New And Collected: 1957-1997</t>
+  </si>
+  <si>
+    <t>Harcourt</t>
+  </si>
+  <si>
+    <t>poems-new-and-szymborska</t>
+  </si>
+  <si>
+    <t>covers/poems-new-and-szymborska.jpg</t>
+  </si>
+  <si>
+    <t>Poems</t>
+  </si>
+  <si>
+    <t>Everyman's Library</t>
+  </si>
+  <si>
+    <t>poems-herbert</t>
+  </si>
+  <si>
+    <t>covers/poems-herbert.jpg</t>
+  </si>
+  <si>
+    <t>covers/without-end.jpg</t>
+  </si>
+  <si>
+    <t>covers/sobbing-superpower.jpg</t>
+  </si>
+  <si>
+    <t>Joanna Trzeciak</t>
+  </si>
+  <si>
+    <t>covers/from-the-tree-of-knowledge.jpg</t>
+  </si>
+  <si>
+    <t>covers/white-magic-baczynski.jpg</t>
+  </si>
+  <si>
+    <t>covers/map-collected-and-last.jpg</t>
+  </si>
+  <si>
+    <t>covers/krzysztof-kamil-baczynski.jpg</t>
   </si>
 </sst>
 </file>
@@ -716,8 +777,7 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color rgb="FF0F1111"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -743,11 +803,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -757,11 +814,15 @@
     <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1096,23 +1157,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01CE5F32-AD1D-47CB-A8F1-52ACBFFA0BE8}">
-  <dimension ref="A1:AU39"/>
+  <dimension ref="A1:AW41"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.140625" customWidth="1"/>
     <col min="2" max="3" width="13.7109375" customWidth="1"/>
-    <col min="4" max="4" width="26.85546875" customWidth="1"/>
-    <col min="8" max="9" width="9.140625" style="9"/>
-    <col min="10" max="11" width="9" style="9"/>
-    <col min="12" max="14" width="9.140625" style="9"/>
-    <col min="15" max="15" width="16" style="11" customWidth="1"/>
-    <col min="16" max="22" width="9.140625" style="4"/>
-    <col min="23" max="23" width="17" style="15" customWidth="1"/>
-    <col min="24" max="30" width="9.140625" style="6"/>
-    <col min="31" max="31" width="22" style="14" customWidth="1"/>
+    <col min="4" max="6" width="46" customWidth="1"/>
+    <col min="8" max="10" width="9.140625" style="8"/>
+    <col min="11" max="12" width="9" style="8"/>
+    <col min="13" max="15" width="9.140625" style="8"/>
+    <col min="16" max="16" width="16" style="7" customWidth="1"/>
+    <col min="17" max="24" width="9.140625" style="3"/>
+    <col min="25" max="25" width="17" style="11" customWidth="1"/>
+    <col min="26" max="32" width="9.140625" style="5"/>
+    <col min="33" max="33" width="22" style="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>18</v>
       </c>
@@ -1134,125 +1195,126 @@
       <c r="G1" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="M1" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="P1" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="R1" s="2"/>
+      <c r="S1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="T1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="U1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="V1" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="W1" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="X1" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="O1" s="11" t="s">
+      <c r="Y1" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="P1" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="Q1" s="4" t="s">
+      <c r="Z1" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="AA1" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="AB1" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="AC1" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="AD1" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="AE1" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="V1" s="4" t="s">
+      <c r="AF1" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="W1" s="15" t="s">
+      <c r="AG1" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="X1" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="Y1" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="Z1" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="AA1" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AH1" t="s">
+        <v>0</v>
+      </c>
+      <c r="AI1" t="s">
         <v>35</v>
       </c>
-      <c r="AC1" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="AD1" s="6" t="s">
-        <v>153</v>
-      </c>
-      <c r="AE1" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="AF1" t="s">
-        <v>0</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>24</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>25</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>26</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AN1" t="s">
         <v>27</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AO1" t="s">
         <v>28</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AP1" t="s">
         <v>36</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AQ1" t="s">
         <v>29</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>47</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AS1" t="s">
         <v>37</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AT1" t="s">
         <v>38</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AU1" t="s">
         <v>43</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AV1" t="s">
         <v>44</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AW1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:47" ht="36" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -1262,62 +1324,64 @@
       <c r="C2">
         <v>100</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="14" t="s">
         <v>1</v>
       </c>
       <c r="E2" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="O2" s="11">
+      <c r="I2"/>
+      <c r="P2" s="7">
         <v>9780684812199</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="Q2" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q2" s="4">
+      <c r="R2" s="2"/>
+      <c r="S2" s="3">
         <v>15</v>
       </c>
-      <c r="R2" s="4">
+      <c r="T2" s="3">
         <v>18</v>
       </c>
-      <c r="S2" s="4">
+      <c r="U2" s="3">
         <v>15</v>
       </c>
-      <c r="W2" s="7">
+      <c r="Y2" s="6">
         <v>9780306809330</v>
       </c>
-      <c r="X2" s="5" t="s">
+      <c r="Z2" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y2" s="6">
+      <c r="AA2" s="5">
         <v>15</v>
       </c>
-      <c r="Z2" s="6">
+      <c r="AB2" s="5">
         <v>18</v>
       </c>
-      <c r="AA2" s="6">
+      <c r="AC2" s="5">
         <v>15</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AH2" t="s">
         <v>13</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AI2" t="s">
         <v>48</v>
       </c>
-      <c r="AO2" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP2" t="s">
+      <c r="AQ2" t="s">
         <v>30</v>
       </c>
       <c r="AR2" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT2" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:47" ht="36" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -1327,65 +1391,67 @@
       <c r="C3">
         <v>200</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="14" t="s">
         <v>3</v>
       </c>
       <c r="E3" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="O3" s="11">
+      <c r="I3"/>
+      <c r="P3" s="7">
         <v>9780312625924</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="Q3" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q3" s="4">
+      <c r="R3" s="2"/>
+      <c r="S3" s="3">
         <v>18</v>
       </c>
-      <c r="R3" s="4">
+      <c r="T3" s="3">
         <v>18</v>
       </c>
-      <c r="S3" s="4">
+      <c r="U3" s="3">
         <v>15</v>
       </c>
-      <c r="W3" s="7">
+      <c r="Y3" s="6">
         <v>9780312625948</v>
       </c>
-      <c r="X3" s="5" t="s">
+      <c r="Z3" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y3" s="6">
+      <c r="AA3" s="5">
         <v>18</v>
       </c>
-      <c r="Z3" s="6">
+      <c r="AB3" s="5">
         <v>18</v>
       </c>
-      <c r="AA3" s="6">
+      <c r="AC3" s="5">
         <v>15</v>
       </c>
-      <c r="AE3" s="14">
+      <c r="AG3" s="10">
         <v>9781429964395</v>
       </c>
-      <c r="AF3" t="s">
+      <c r="AH3" t="s">
         <v>14</v>
       </c>
-      <c r="AG3" t="s">
+      <c r="AI3" t="s">
         <v>48</v>
       </c>
-      <c r="AO3" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP3" t="s">
+      <c r="AQ3" t="s">
         <v>30</v>
       </c>
       <c r="AR3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT3" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:47" ht="24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>52</v>
       </c>
@@ -1395,65 +1461,67 @@
       <c r="C4">
         <v>300</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="14" t="s">
         <v>5</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="O4" s="11">
+      <c r="I4"/>
+      <c r="P4" s="7">
         <v>9780008411251</v>
       </c>
-      <c r="P4" s="3" t="s">
+      <c r="Q4" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q4" s="4">
+      <c r="R4" s="2"/>
+      <c r="S4" s="3">
         <v>20</v>
       </c>
-      <c r="R4" s="4">
+      <c r="T4" s="3">
         <v>20</v>
       </c>
-      <c r="S4" s="4">
+      <c r="U4" s="3">
         <v>16</v>
       </c>
-      <c r="W4" s="7">
+      <c r="Y4" s="6">
         <v>9780008521684</v>
       </c>
-      <c r="X4" s="5" t="s">
+      <c r="Z4" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y4" s="6">
+      <c r="AA4" s="5">
         <v>20</v>
       </c>
-      <c r="Z4" s="6">
+      <c r="AB4" s="5">
         <v>20</v>
       </c>
-      <c r="AA4" s="6">
+      <c r="AC4" s="5">
         <v>16</v>
       </c>
-      <c r="AE4" s="14">
+      <c r="AG4" s="10">
         <v>9780008411275</v>
       </c>
-      <c r="AF4" t="s">
+      <c r="AH4" t="s">
         <v>20</v>
       </c>
-      <c r="AG4" t="s">
+      <c r="AI4" t="s">
         <v>48</v>
       </c>
-      <c r="AO4" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP4" t="s">
+      <c r="AQ4" t="s">
         <v>30</v>
       </c>
       <c r="AR4" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:47" ht="36" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>100</v>
       </c>
@@ -1463,63 +1531,65 @@
       <c r="C5">
         <v>400</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="14" t="s">
         <v>7</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5"/>
+      <c r="J5" s="8">
         <v>44</v>
       </c>
-      <c r="J5" s="9">
+      <c r="K5" s="8">
         <v>45</v>
       </c>
-      <c r="K5" s="9">
+      <c r="L5" s="8">
         <v>38</v>
       </c>
-      <c r="O5" s="10">
+      <c r="P5" s="9">
         <v>9780300252200</v>
       </c>
-      <c r="P5" s="3"/>
-      <c r="W5" s="15">
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="Y5" s="11">
         <v>9780300252217</v>
       </c>
-      <c r="X5" s="5" t="s">
+      <c r="Z5" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y5" s="6">
+      <c r="AA5" s="5">
         <v>44</v>
       </c>
-      <c r="Z5" s="6">
+      <c r="AB5" s="5">
         <v>45</v>
       </c>
-      <c r="AA5" s="6">
+      <c r="AC5" s="5">
         <v>38</v>
       </c>
-      <c r="AE5" s="14">
+      <c r="AG5" s="10">
         <v>9780300252224</v>
       </c>
-      <c r="AF5" t="s">
+      <c r="AH5" t="s">
         <v>15</v>
       </c>
-      <c r="AG5" t="s">
+      <c r="AI5" t="s">
         <v>48</v>
       </c>
-      <c r="AO5" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP5" t="s">
+      <c r="AQ5" t="s">
         <v>30</v>
       </c>
       <c r="AR5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:47" ht="36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -1529,60 +1599,62 @@
       <c r="C6">
         <v>500</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="14" t="s">
         <v>9</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6"/>
+      <c r="J6" s="8">
         <v>58</v>
       </c>
-      <c r="J6" s="9">
+      <c r="K6" s="8">
         <v>52</v>
       </c>
-      <c r="K6" s="9">
+      <c r="L6" s="8">
         <v>44</v>
       </c>
-      <c r="O6" s="10">
+      <c r="P6" s="9">
         <v>9781472816030</v>
       </c>
-      <c r="P6" s="3"/>
-      <c r="W6" s="15">
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="Y6" s="11">
         <v>9781472816047</v>
       </c>
-      <c r="X6" s="5" t="s">
+      <c r="Z6" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y6" s="6">
+      <c r="AA6" s="5">
         <v>58</v>
       </c>
-      <c r="Z6" s="6">
+      <c r="AB6" s="5">
         <v>52</v>
       </c>
-      <c r="AA6" s="6">
+      <c r="AC6" s="5">
         <v>44</v>
       </c>
-      <c r="AF6" t="s">
+      <c r="AH6" t="s">
         <v>17</v>
       </c>
-      <c r="AG6" t="s">
+      <c r="AI6" t="s">
         <v>48</v>
       </c>
-      <c r="AO6" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP6" t="s">
+      <c r="AQ6" t="s">
         <v>30</v>
       </c>
       <c r="AR6" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT6" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:47" ht="36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -1592,7 +1664,7 @@
       <c r="C7">
         <v>600</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="14" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
@@ -1601,56 +1673,58 @@
       <c r="F7" t="s">
         <v>42</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="O7" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="P7" s="3" t="s">
+      <c r="I7"/>
+      <c r="P7" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="Q7" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q7" s="4">
+      <c r="R7" s="2"/>
+      <c r="S7" s="3">
         <v>23</v>
       </c>
-      <c r="R7" s="4">
+      <c r="T7" s="3">
         <v>20</v>
       </c>
-      <c r="S7" s="4">
+      <c r="U7" s="3">
         <v>18</v>
       </c>
-      <c r="W7" s="7">
+      <c r="Y7" s="6">
         <v>9781607720058</v>
       </c>
-      <c r="X7" s="5" t="s">
+      <c r="Z7" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y7" s="6">
+      <c r="AA7" s="5">
         <v>23</v>
       </c>
-      <c r="Z7" s="6">
+      <c r="AB7" s="5">
         <v>20</v>
       </c>
-      <c r="AA7" s="6">
+      <c r="AC7" s="5">
         <v>18</v>
       </c>
-      <c r="AF7" t="s">
+      <c r="AH7" t="s">
         <v>16</v>
       </c>
-      <c r="AG7" t="s">
+      <c r="AI7" t="s">
         <v>48</v>
       </c>
-      <c r="AO7" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP7" t="s">
+      <c r="AQ7" t="s">
         <v>30</v>
       </c>
       <c r="AR7" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT7" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>55</v>
       </c>
@@ -1660,7 +1734,7 @@
       <c r="C8">
         <v>150</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="14" t="s">
         <v>54</v>
       </c>
       <c r="E8" t="s">
@@ -1669,53 +1743,55 @@
       <c r="F8" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="I8"/>
+      <c r="Q8" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q8" s="4">
+      <c r="R8" s="2"/>
+      <c r="S8" s="3">
         <v>18</v>
       </c>
-      <c r="R8" s="4">
+      <c r="T8" s="3">
         <v>16</v>
       </c>
-      <c r="S8" s="4">
+      <c r="U8" s="3">
         <v>14</v>
       </c>
-      <c r="W8" s="7">
+      <c r="Y8" s="6">
         <v>9781590173831</v>
       </c>
-      <c r="X8" s="5" t="s">
+      <c r="Z8" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y8" s="6">
+      <c r="AA8" s="5">
         <v>18</v>
       </c>
-      <c r="Z8" s="6">
+      <c r="AB8" s="5">
         <v>16</v>
       </c>
-      <c r="AA8" s="6">
+      <c r="AC8" s="5">
         <v>14</v>
       </c>
-      <c r="AE8" s="14">
+      <c r="AG8" s="10">
         <v>9781590173848</v>
       </c>
-      <c r="AF8" t="s">
+      <c r="AH8" t="s">
         <v>66</v>
       </c>
-      <c r="AO8" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP8" t="s">
+      <c r="AQ8" t="s">
         <v>30</v>
       </c>
       <c r="AR8" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT8" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="9" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>61</v>
       </c>
@@ -1725,7 +1801,7 @@
       <c r="C9">
         <v>250</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="14" t="s">
         <v>60</v>
       </c>
       <c r="E9" t="s">
@@ -1734,50 +1810,52 @@
       <c r="F9" t="s">
         <v>58</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="P9" s="3" t="s">
+      <c r="I9"/>
+      <c r="Q9" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q9" s="4">
+      <c r="R9" s="2"/>
+      <c r="S9" s="3">
         <v>19.5</v>
       </c>
-      <c r="R9" s="4">
+      <c r="T9" s="3">
         <v>18</v>
       </c>
-      <c r="S9" s="4">
+      <c r="U9" s="3">
         <v>17</v>
       </c>
-      <c r="W9" s="7">
+      <c r="Y9" s="6">
         <v>9780241524244</v>
       </c>
-      <c r="X9" s="5" t="s">
+      <c r="Z9" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y9" s="6">
+      <c r="AA9" s="5">
         <v>19.5</v>
       </c>
-      <c r="Z9" s="6">
+      <c r="AB9" s="5">
         <v>18</v>
       </c>
-      <c r="AA9" s="6">
+      <c r="AC9" s="5">
         <v>17</v>
       </c>
-      <c r="AF9" t="s">
+      <c r="AH9" t="s">
         <v>67</v>
       </c>
-      <c r="AO9" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP9" t="s">
+      <c r="AQ9" t="s">
         <v>30</v>
       </c>
       <c r="AR9" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT9" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:47" ht="24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>63</v>
       </c>
@@ -1787,60 +1865,62 @@
       <c r="C10">
         <v>350</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="14" t="s">
         <v>62</v>
       </c>
       <c r="E10" t="s">
         <v>64</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="8" t="s">
+      <c r="G10" s="1"/>
+      <c r="H10" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="P10" s="3" t="s">
+      <c r="I10" s="1"/>
+      <c r="Q10" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q10" s="4">
+      <c r="R10" s="2"/>
+      <c r="S10" s="3">
         <v>16.96</v>
       </c>
-      <c r="R10" s="4">
+      <c r="T10" s="3">
         <v>15</v>
       </c>
-      <c r="S10" s="4">
+      <c r="U10" s="3">
         <v>13</v>
       </c>
-      <c r="W10" s="7">
+      <c r="Y10" s="6">
         <v>9781939810007</v>
       </c>
-      <c r="X10" s="5" t="s">
+      <c r="Z10" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y10" s="6">
+      <c r="AA10" s="5">
         <v>16.96</v>
       </c>
-      <c r="Z10" s="6">
+      <c r="AB10" s="5">
         <v>15</v>
       </c>
-      <c r="AA10" s="6">
+      <c r="AC10" s="5">
         <v>13</v>
       </c>
-      <c r="AF10" t="s">
+      <c r="AH10" t="s">
         <v>68</v>
       </c>
-      <c r="AO10" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP10" t="s">
+      <c r="AQ10" t="s">
         <v>30</v>
       </c>
       <c r="AR10" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="11" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>74</v>
       </c>
@@ -1850,7 +1930,7 @@
       <c r="C11">
         <v>450</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="14" t="s">
         <v>69</v>
       </c>
       <c r="E11" t="s">
@@ -1859,50 +1939,52 @@
       <c r="F11" t="s">
         <v>71</v>
       </c>
-      <c r="H11" s="8" t="s">
+      <c r="H11" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="P11" s="3" t="s">
+      <c r="I11"/>
+      <c r="Q11" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q11" s="4">
+      <c r="R11" s="2"/>
+      <c r="S11" s="3">
         <v>20</v>
       </c>
-      <c r="R11" s="4">
+      <c r="T11" s="3">
         <v>19</v>
       </c>
-      <c r="S11" s="4">
+      <c r="U11" s="3">
         <v>17</v>
       </c>
-      <c r="W11" s="7">
+      <c r="Y11" s="6">
         <v>9780875807072</v>
       </c>
-      <c r="X11" s="5" t="s">
+      <c r="Z11" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y11" s="6">
+      <c r="AA11" s="5">
         <v>20</v>
       </c>
-      <c r="Z11" s="6">
+      <c r="AB11" s="5">
         <v>19</v>
       </c>
-      <c r="AA11" s="6">
+      <c r="AC11" s="5">
         <v>17</v>
       </c>
-      <c r="AF11" t="s">
+      <c r="AH11" t="s">
         <v>72</v>
       </c>
-      <c r="AO11" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP11" t="s">
+      <c r="AQ11" t="s">
         <v>30</v>
       </c>
       <c r="AR11" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT11" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>80</v>
       </c>
@@ -1921,48 +2003,50 @@
       <c r="F12" t="s">
         <v>81</v>
       </c>
-      <c r="H12" s="8" t="s">
+      <c r="H12" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12"/>
+      <c r="J12" s="8">
         <v>17.989999999999998</v>
       </c>
-      <c r="J12" s="9">
+      <c r="K12" s="8">
         <v>15</v>
       </c>
-      <c r="K12" s="9">
+      <c r="L12" s="8">
         <v>13</v>
       </c>
-      <c r="O12" s="10">
+      <c r="P12" s="9">
         <v>9798325216770</v>
       </c>
-      <c r="P12" s="3"/>
-      <c r="X12" s="5" t="s">
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="Z12" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y12" s="6">
+      <c r="AA12" s="5">
         <v>17.989999999999998</v>
       </c>
-      <c r="Z12" s="6">
+      <c r="AB12" s="5">
         <v>15</v>
       </c>
-      <c r="AA12" s="6">
+      <c r="AC12" s="5">
         <v>13</v>
       </c>
-      <c r="AF12" t="s">
+      <c r="AH12" t="s">
         <v>83</v>
       </c>
-      <c r="AO12" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP12" t="s">
+      <c r="AQ12" t="s">
         <v>30</v>
       </c>
       <c r="AR12" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT12" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>79</v>
       </c>
@@ -1972,7 +2056,7 @@
       <c r="C13">
         <v>650</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="14" t="s">
         <v>75</v>
       </c>
       <c r="E13" t="s">
@@ -1982,46 +2066,50 @@
         <v>77</v>
       </c>
       <c r="G13" t="s">
-        <v>182</v>
-      </c>
-      <c r="H13" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="H13" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" t="s">
+        <v>178</v>
+      </c>
+      <c r="J13" s="8">
         <v>24</v>
       </c>
-      <c r="O13" s="10">
+      <c r="P13" s="9">
         <v>9789998791732</v>
       </c>
-      <c r="P13" s="3" t="s">
+      <c r="Q13" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="X13" s="5" t="s">
+      <c r="R13" s="2"/>
+      <c r="Z13" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y13" s="6">
+      <c r="AA13" s="5">
         <v>24</v>
       </c>
-      <c r="AF13" t="s">
+      <c r="AH13" t="s">
         <v>78</v>
       </c>
-      <c r="AO13" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP13" t="s">
+      <c r="AQ13" t="s">
         <v>30</v>
       </c>
       <c r="AR13" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT13" t="s">
         <v>40</v>
       </c>
-      <c r="AT13" t="s">
+      <c r="AV13" t="s">
         <v>168</v>
       </c>
-      <c r="AU13">
+      <c r="AW13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>89</v>
       </c>
@@ -2031,7 +2119,7 @@
       <c r="C14">
         <v>100</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="14" t="s">
         <v>86</v>
       </c>
       <c r="E14" t="s">
@@ -2040,59 +2128,61 @@
       <c r="F14" t="s">
         <v>88</v>
       </c>
-      <c r="H14" s="8" t="s">
+      <c r="H14" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14"/>
+      <c r="J14" s="8">
         <v>15</v>
       </c>
-      <c r="J14" s="9">
+      <c r="K14" s="8">
         <v>12</v>
       </c>
-      <c r="K14" s="9">
+      <c r="L14" s="8">
         <v>10</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="Q14" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q14" s="4">
+      <c r="R14" s="2"/>
+      <c r="S14" s="3">
         <v>15</v>
       </c>
-      <c r="R14" s="4">
+      <c r="T14" s="3">
         <v>12</v>
       </c>
-      <c r="S14" s="4">
+      <c r="U14" s="3">
         <v>10</v>
       </c>
-      <c r="W14" s="7">
+      <c r="Y14" s="6">
         <v>9781852429454</v>
       </c>
-      <c r="X14" s="5" t="s">
+      <c r="Z14" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y14" s="6">
+      <c r="AA14" s="5">
         <v>15</v>
       </c>
-      <c r="Z14" s="6">
+      <c r="AB14" s="5">
         <v>12</v>
       </c>
-      <c r="AA14" s="6">
+      <c r="AC14" s="5">
         <v>10</v>
       </c>
-      <c r="AF14" t="s">
+      <c r="AH14" t="s">
         <v>98</v>
       </c>
-      <c r="AO14" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP14" t="s">
+      <c r="AQ14" t="s">
         <v>30</v>
       </c>
       <c r="AR14" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT14" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>93</v>
       </c>
@@ -2102,65 +2192,67 @@
       <c r="C15">
         <v>100</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="14" t="s">
         <v>90</v>
       </c>
       <c r="E15" t="s">
         <v>91</v>
       </c>
-      <c r="H15" s="8" t="s">
+      <c r="H15" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15"/>
+      <c r="J15" s="8">
         <v>14</v>
       </c>
-      <c r="J15" s="9">
+      <c r="K15" s="8">
         <v>14</v>
       </c>
-      <c r="K15" s="9">
+      <c r="L15" s="8">
         <v>12</v>
       </c>
-      <c r="P15" s="3" t="s">
+      <c r="Q15" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q15" s="4">
+      <c r="R15" s="2"/>
+      <c r="S15" s="3">
         <v>14</v>
       </c>
-      <c r="R15" s="4">
+      <c r="T15" s="3">
         <v>14</v>
       </c>
-      <c r="S15" s="4">
+      <c r="U15" s="3">
         <v>12</v>
       </c>
-      <c r="W15" s="7">
+      <c r="Y15" s="6">
         <v>9780679738015</v>
       </c>
-      <c r="X15" s="5" t="s">
+      <c r="Z15" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y15" s="6">
+      <c r="AA15" s="5">
         <v>14</v>
       </c>
-      <c r="Z15" s="6">
+      <c r="AB15" s="5">
         <v>14</v>
       </c>
-      <c r="AA15" s="6">
+      <c r="AC15" s="5">
         <v>12</v>
       </c>
-      <c r="AF15" t="s">
+      <c r="AH15" t="s">
         <v>95</v>
       </c>
-      <c r="AO15" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP15" t="s">
+      <c r="AQ15" t="s">
         <v>30</v>
       </c>
       <c r="AR15" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT15" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:47" ht="24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>94</v>
       </c>
@@ -2170,65 +2262,67 @@
       <c r="C16">
         <v>400</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="14" t="s">
         <v>92</v>
       </c>
       <c r="E16" t="s">
         <v>91</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16"/>
+      <c r="J16" s="8">
         <v>14</v>
       </c>
-      <c r="J16" s="9">
+      <c r="K16" s="8">
         <v>14</v>
       </c>
-      <c r="K16" s="9">
+      <c r="L16" s="8">
         <v>12</v>
       </c>
-      <c r="P16" s="3" t="s">
+      <c r="Q16" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q16" s="4">
+      <c r="R16" s="2"/>
+      <c r="S16" s="3">
         <v>14</v>
       </c>
-      <c r="R16" s="4">
+      <c r="T16" s="3">
         <v>14</v>
       </c>
-      <c r="S16" s="4">
+      <c r="U16" s="3">
         <v>12</v>
       </c>
-      <c r="W16" s="7">
+      <c r="Y16" s="6">
         <v>9780141188034</v>
       </c>
-      <c r="X16" s="5" t="s">
+      <c r="Z16" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y16" s="6">
+      <c r="AA16" s="5">
         <v>14</v>
       </c>
-      <c r="Z16" s="6">
+      <c r="AB16" s="5">
         <v>14</v>
       </c>
-      <c r="AA16" s="6">
+      <c r="AC16" s="5">
         <v>12</v>
       </c>
-      <c r="AF16" t="s">
+      <c r="AH16" t="s">
         <v>96</v>
       </c>
-      <c r="AO16" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP16" t="s">
+      <c r="AQ16" t="s">
         <v>30</v>
       </c>
       <c r="AR16" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT16" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>171</v>
       </c>
@@ -2238,65 +2332,67 @@
       <c r="C17">
         <v>400</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="14" t="s">
         <v>99</v>
       </c>
       <c r="E17" t="s">
         <v>91</v>
       </c>
-      <c r="H17" s="8" t="s">
+      <c r="H17" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17"/>
+      <c r="J17" s="8">
         <v>13</v>
       </c>
-      <c r="J17" s="9">
+      <c r="K17" s="8">
         <v>12</v>
       </c>
-      <c r="K17" s="9">
+      <c r="L17" s="8">
         <v>11</v>
       </c>
-      <c r="P17" s="3" t="s">
+      <c r="Q17" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q17" s="4">
+      <c r="R17" s="2"/>
+      <c r="S17" s="3">
         <v>13</v>
       </c>
-      <c r="R17" s="4">
+      <c r="T17" s="3">
         <v>12</v>
       </c>
-      <c r="S17" s="4">
+      <c r="U17" s="3">
         <v>11</v>
       </c>
-      <c r="W17" s="7">
+      <c r="Y17" s="6">
         <v>9780375726293</v>
       </c>
-      <c r="X17" s="5" t="s">
+      <c r="Z17" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y17" s="6">
+      <c r="AA17" s="5">
         <v>13</v>
       </c>
-      <c r="Z17" s="6">
+      <c r="AB17" s="5">
         <v>12</v>
       </c>
-      <c r="AA17" s="6">
+      <c r="AC17" s="5">
         <v>11</v>
       </c>
-      <c r="AF17" t="s">
+      <c r="AH17" t="s">
         <v>131</v>
       </c>
-      <c r="AO17" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP17" t="s">
+      <c r="AQ17" t="s">
         <v>30</v>
       </c>
       <c r="AR17" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT17" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>104</v>
       </c>
@@ -2306,7 +2402,7 @@
       <c r="C18">
         <v>600</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="14" t="s">
         <v>103</v>
       </c>
       <c r="E18" t="s">
@@ -2316,61 +2412,65 @@
         <v>77</v>
       </c>
       <c r="G18" t="s">
-        <v>182</v>
-      </c>
-      <c r="H18" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="H18" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" t="s">
+        <v>178</v>
+      </c>
+      <c r="J18" s="8">
         <v>25</v>
       </c>
-      <c r="J18" s="9">
+      <c r="K18" s="8">
         <v>24</v>
       </c>
-      <c r="K18" s="9">
+      <c r="L18" s="8">
         <v>22</v>
       </c>
-      <c r="O18" s="10">
+      <c r="P18" s="9">
         <v>9782919820382</v>
       </c>
-      <c r="P18" s="3" t="s">
+      <c r="Q18" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q18" s="4">
+      <c r="R18" s="2"/>
+      <c r="S18" s="3">
         <v>25</v>
       </c>
-      <c r="R18" s="4">
+      <c r="T18" s="3">
         <v>24</v>
       </c>
-      <c r="S18" s="4">
+      <c r="U18" s="3">
         <v>22</v>
       </c>
-      <c r="X18" s="5" t="s">
+      <c r="Z18" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y18" s="6">
+      <c r="AA18" s="5">
         <v>25</v>
       </c>
-      <c r="Z18" s="6">
+      <c r="AB18" s="5">
         <v>24</v>
       </c>
-      <c r="AA18" s="6">
+      <c r="AC18" s="5">
         <v>22</v>
       </c>
-      <c r="AF18" t="s">
+      <c r="AH18" t="s">
         <v>111</v>
       </c>
-      <c r="AO18" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP18" t="s">
+      <c r="AQ18" t="s">
         <v>30</v>
       </c>
       <c r="AR18" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT18" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>170</v>
       </c>
@@ -2380,7 +2480,7 @@
       <c r="C19">
         <v>800</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="14" t="s">
         <v>105</v>
       </c>
       <c r="E19" t="s">
@@ -2390,61 +2490,65 @@
         <v>77</v>
       </c>
       <c r="G19" t="s">
-        <v>182</v>
-      </c>
-      <c r="H19" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="H19" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" t="s">
+        <v>178</v>
+      </c>
+      <c r="J19" s="8">
         <v>25</v>
       </c>
-      <c r="J19" s="9">
+      <c r="K19" s="8">
         <v>24</v>
       </c>
-      <c r="K19" s="9">
+      <c r="L19" s="8">
         <v>20</v>
       </c>
-      <c r="O19" s="10">
+      <c r="P19" s="9">
         <v>9789998793729</v>
       </c>
-      <c r="P19" s="3" t="s">
+      <c r="Q19" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q19" s="4">
+      <c r="R19" s="2"/>
+      <c r="S19" s="3">
         <v>25</v>
       </c>
-      <c r="R19" s="4">
+      <c r="T19" s="3">
         <v>24</v>
       </c>
-      <c r="S19" s="4">
+      <c r="U19" s="3">
         <v>20</v>
       </c>
-      <c r="X19" s="5" t="s">
+      <c r="Z19" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y19" s="6">
+      <c r="AA19" s="5">
         <v>25</v>
       </c>
-      <c r="Z19" s="6">
+      <c r="AB19" s="5">
         <v>24</v>
       </c>
-      <c r="AA19" s="6">
+      <c r="AC19" s="5">
         <v>20</v>
       </c>
-      <c r="AF19" t="s">
+      <c r="AH19" t="s">
         <v>110</v>
       </c>
-      <c r="AO19" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP19" t="s">
+      <c r="AQ19" t="s">
         <v>30</v>
       </c>
       <c r="AR19" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT19" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="20" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>108</v>
       </c>
@@ -2454,7 +2558,7 @@
       <c r="C20">
         <v>900</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="14" t="s">
         <v>106</v>
       </c>
       <c r="E20" t="s">
@@ -2464,61 +2568,65 @@
         <v>77</v>
       </c>
       <c r="G20" t="s">
-        <v>182</v>
-      </c>
-      <c r="H20" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="H20" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" t="s">
+        <v>178</v>
+      </c>
+      <c r="J20" s="8">
         <v>27</v>
       </c>
-      <c r="J20" s="9">
+      <c r="K20" s="8">
         <v>25</v>
       </c>
-      <c r="K20" s="9">
+      <c r="L20" s="8">
         <v>22</v>
       </c>
-      <c r="O20" s="8">
+      <c r="P20" s="7">
         <v>9782919840052</v>
       </c>
-      <c r="P20" s="3" t="s">
+      <c r="Q20" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q20" s="4">
+      <c r="R20" s="2"/>
+      <c r="S20" s="3">
         <v>27</v>
       </c>
-      <c r="R20" s="4">
+      <c r="T20" s="3">
         <v>25</v>
       </c>
-      <c r="S20" s="4">
+      <c r="U20" s="3">
         <v>22</v>
       </c>
-      <c r="X20" s="5" t="s">
+      <c r="Z20" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y20" s="6">
+      <c r="AA20" s="5">
         <v>27</v>
       </c>
-      <c r="Z20" s="6">
+      <c r="AB20" s="5">
         <v>25</v>
       </c>
-      <c r="AA20" s="6">
+      <c r="AC20" s="5">
         <v>22</v>
       </c>
-      <c r="AF20" t="s">
+      <c r="AH20" t="s">
         <v>112</v>
       </c>
-      <c r="AO20" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP20" t="s">
+      <c r="AQ20" t="s">
         <v>30</v>
       </c>
       <c r="AR20" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT20" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>109</v>
       </c>
@@ -2528,7 +2636,7 @@
       <c r="C21">
         <v>1000</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="14" t="s">
         <v>107</v>
       </c>
       <c r="E21" t="s">
@@ -2538,61 +2646,65 @@
         <v>77</v>
       </c>
       <c r="G21" t="s">
-        <v>182</v>
-      </c>
-      <c r="H21" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="H21" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" t="s">
+        <v>178</v>
+      </c>
+      <c r="J21" s="8">
         <v>25</v>
       </c>
-      <c r="J21" s="9">
+      <c r="K21" s="8">
         <v>24</v>
       </c>
-      <c r="K21" s="9">
+      <c r="L21" s="8">
         <v>20</v>
       </c>
-      <c r="O21" s="8">
+      <c r="P21" s="7">
         <v>9782919820290</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="Q21" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q21" s="4">
+      <c r="R21" s="2"/>
+      <c r="S21" s="3">
         <v>25</v>
       </c>
-      <c r="R21" s="4">
+      <c r="T21" s="3">
         <v>24</v>
       </c>
-      <c r="S21" s="4">
+      <c r="U21" s="3">
         <v>20</v>
       </c>
-      <c r="X21" s="5" t="s">
+      <c r="Z21" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y21" s="6">
+      <c r="AA21" s="5">
         <v>25</v>
       </c>
-      <c r="Z21" s="6">
+      <c r="AB21" s="5">
         <v>24</v>
       </c>
-      <c r="AA21" s="6">
+      <c r="AC21" s="5">
         <v>20</v>
       </c>
-      <c r="AF21" t="s">
+      <c r="AH21" t="s">
         <v>113</v>
       </c>
-      <c r="AO21" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP21" t="s">
+      <c r="AQ21" t="s">
         <v>30</v>
       </c>
       <c r="AR21" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT21" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="22" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>117</v>
       </c>
@@ -2602,7 +2714,7 @@
       <c r="C22">
         <v>600</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="14" t="s">
         <v>118</v>
       </c>
       <c r="E22" t="s">
@@ -2611,59 +2723,61 @@
       <c r="F22" t="s">
         <v>120</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H22" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I22" s="9">
+      <c r="I22"/>
+      <c r="J22" s="8">
         <v>10</v>
       </c>
-      <c r="J22" s="9">
+      <c r="K22" s="8">
         <v>9</v>
       </c>
-      <c r="K22" s="9">
+      <c r="L22" s="8">
         <v>8</v>
       </c>
-      <c r="P22" s="3" t="s">
+      <c r="Q22" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q22" s="4">
+      <c r="R22" s="2"/>
+      <c r="S22" s="3">
         <v>10</v>
       </c>
-      <c r="R22" s="4">
+      <c r="T22" s="3">
         <v>9</v>
       </c>
-      <c r="S22" s="4">
+      <c r="U22" s="3">
         <v>8</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="2">
         <v>9780156027601</v>
       </c>
-      <c r="X22" s="5" t="s">
+      <c r="Z22" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y22" s="6">
+      <c r="AA22" s="5">
         <v>10</v>
       </c>
-      <c r="Z22" s="6">
+      <c r="AB22" s="5">
         <v>9</v>
       </c>
-      <c r="AA22" s="6">
+      <c r="AC22" s="5">
         <v>8</v>
       </c>
-      <c r="AF22" t="s">
+      <c r="AH22" t="s">
         <v>121</v>
       </c>
-      <c r="AO22" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP22" t="s">
+      <c r="AQ22" t="s">
         <v>30</v>
       </c>
       <c r="AR22" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT22" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="23" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>122</v>
       </c>
@@ -2673,7 +2787,7 @@
       <c r="C23">
         <v>200</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="14" t="s">
         <v>123</v>
       </c>
       <c r="E23" t="s">
@@ -2682,59 +2796,61 @@
       <c r="F23" t="s">
         <v>124</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I23"/>
+      <c r="J23" s="8">
         <v>17</v>
       </c>
-      <c r="J23" s="9">
+      <c r="K23" s="8">
         <v>15</v>
       </c>
-      <c r="K23" s="9">
+      <c r="L23" s="8">
         <v>12</v>
       </c>
-      <c r="P23" s="3" t="s">
+      <c r="Q23" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q23" s="4">
+      <c r="R23" s="2"/>
+      <c r="S23" s="3">
         <v>17</v>
       </c>
-      <c r="R23" s="4">
+      <c r="T23" s="3">
         <v>15</v>
       </c>
-      <c r="S23" s="4">
+      <c r="U23" s="3">
         <v>12</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="2">
         <v>9780156306300</v>
       </c>
-      <c r="X23" s="5" t="s">
+      <c r="Z23" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y23" s="6">
+      <c r="AA23" s="5">
         <v>17</v>
       </c>
-      <c r="Z23" s="6">
+      <c r="AB23" s="5">
         <v>15</v>
       </c>
-      <c r="AA23" s="6">
+      <c r="AC23" s="5">
         <v>12</v>
       </c>
-      <c r="AF23" t="s">
+      <c r="AH23" t="s">
         <v>125</v>
       </c>
-      <c r="AO23" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP23" t="s">
+      <c r="AQ23" t="s">
         <v>30</v>
       </c>
       <c r="AR23" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT23" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>169</v>
       </c>
@@ -2744,7 +2860,7 @@
       <c r="C24">
         <v>600</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="14" t="s">
         <v>126</v>
       </c>
       <c r="E24" t="s">
@@ -2753,59 +2869,61 @@
       <c r="F24" t="s">
         <v>65</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I24" s="9">
+      <c r="I24"/>
+      <c r="J24" s="8">
         <v>17</v>
       </c>
-      <c r="J24" s="9">
+      <c r="K24" s="8">
         <v>16</v>
       </c>
-      <c r="K24" s="9">
+      <c r="L24" s="8">
         <v>13</v>
       </c>
-      <c r="P24" s="3" t="s">
+      <c r="Q24" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q24" s="4">
+      <c r="R24" s="2"/>
+      <c r="S24" s="3">
         <v>17</v>
       </c>
-      <c r="R24" s="4">
+      <c r="T24" s="3">
         <v>16</v>
       </c>
-      <c r="S24" s="4">
+      <c r="U24" s="3">
         <v>13</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="2">
         <v>9780262357685</v>
       </c>
-      <c r="X24" s="5" t="s">
+      <c r="Z24" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y24" s="6">
+      <c r="AA24" s="5">
         <v>17</v>
       </c>
-      <c r="Z24" s="6">
+      <c r="AB24" s="5">
         <v>16</v>
       </c>
-      <c r="AA24" s="6">
+      <c r="AC24" s="5">
         <v>13</v>
       </c>
-      <c r="AF24" t="s">
+      <c r="AH24" t="s">
         <v>130</v>
       </c>
-      <c r="AO24" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP24" t="s">
+      <c r="AQ24" t="s">
         <v>30</v>
       </c>
       <c r="AR24" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT24" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>148</v>
       </c>
@@ -2815,7 +2933,7 @@
       <c r="C25">
         <v>100</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="14" t="s">
         <v>127</v>
       </c>
       <c r="E25" t="s">
@@ -2825,67 +2943,71 @@
         <v>77</v>
       </c>
       <c r="G25" t="s">
-        <v>182</v>
-      </c>
-      <c r="H25" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="H25" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" t="s">
+        <v>178</v>
+      </c>
+      <c r="J25" s="8">
         <v>17</v>
       </c>
-      <c r="J25" s="9">
+      <c r="K25" s="8">
         <v>16</v>
       </c>
-      <c r="K25" s="9">
+      <c r="L25" s="8">
         <v>15</v>
       </c>
-      <c r="P25" s="3" t="s">
+      <c r="Q25" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q25" s="4">
+      <c r="R25" s="2"/>
+      <c r="S25" s="3">
         <v>17</v>
       </c>
-      <c r="R25" s="4">
+      <c r="T25" s="3">
         <v>16</v>
       </c>
-      <c r="S25" s="4">
+      <c r="U25" s="3">
         <v>15</v>
       </c>
-      <c r="W25" s="3">
+      <c r="Y25" s="2">
         <v>9782919840106</v>
       </c>
-      <c r="X25" s="5" t="s">
+      <c r="Z25" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y25" s="6">
+      <c r="AA25" s="5">
         <v>17</v>
       </c>
-      <c r="Z25" s="6">
+      <c r="AB25" s="5">
         <v>16</v>
       </c>
-      <c r="AA25" s="6">
+      <c r="AC25" s="5">
         <v>15</v>
       </c>
-      <c r="AF25" t="s">
+      <c r="AH25" t="s">
         <v>128</v>
       </c>
-      <c r="AO25" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP25" t="s">
+      <c r="AQ25" t="s">
         <v>30</v>
       </c>
       <c r="AR25" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT25" t="s">
         <v>40</v>
       </c>
-      <c r="AT25" t="s">
+      <c r="AV25" t="s">
         <v>168</v>
       </c>
-      <c r="AU25">
+      <c r="AW25">
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>133</v>
       </c>
@@ -2895,7 +3017,7 @@
       <c r="C26">
         <v>100</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="14" t="s">
         <v>137</v>
       </c>
       <c r="E26" t="s">
@@ -2905,61 +3027,65 @@
         <v>77</v>
       </c>
       <c r="G26" t="s">
-        <v>182</v>
-      </c>
-      <c r="H26" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="H26" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" t="s">
+        <v>178</v>
+      </c>
+      <c r="J26" s="8">
         <v>24</v>
       </c>
-      <c r="J26" s="9">
+      <c r="K26" s="8">
         <v>24</v>
       </c>
-      <c r="K26" s="9">
+      <c r="L26" s="8">
         <v>20</v>
       </c>
-      <c r="O26" s="8">
+      <c r="P26" s="7">
         <v>9789998791671</v>
       </c>
-      <c r="P26" s="3" t="s">
+      <c r="Q26" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q26" s="4">
+      <c r="R26" s="2"/>
+      <c r="S26" s="3">
         <v>24</v>
       </c>
-      <c r="R26" s="4">
+      <c r="T26" s="3">
         <v>24</v>
       </c>
-      <c r="S26" s="4">
+      <c r="U26" s="3">
         <v>20</v>
       </c>
-      <c r="X26" s="5" t="s">
+      <c r="Z26" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y26" s="6">
+      <c r="AA26" s="5">
         <v>24</v>
       </c>
-      <c r="Z26" s="6">
+      <c r="AB26" s="5">
         <v>24</v>
       </c>
-      <c r="AA26" s="6">
+      <c r="AC26" s="5">
         <v>20</v>
       </c>
-      <c r="AF26" t="s">
+      <c r="AH26" t="s">
         <v>140</v>
       </c>
-      <c r="AO26" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP26" t="s">
+      <c r="AQ26" t="s">
         <v>30</v>
       </c>
       <c r="AR26" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT26" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>134</v>
       </c>
@@ -2969,7 +3095,7 @@
       <c r="C27">
         <v>600</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="14" t="s">
         <v>138</v>
       </c>
       <c r="E27" t="s">
@@ -2979,61 +3105,65 @@
         <v>77</v>
       </c>
       <c r="G27" t="s">
-        <v>182</v>
-      </c>
-      <c r="H27" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="H27" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I27" s="9">
+      <c r="I27" t="s">
+        <v>178</v>
+      </c>
+      <c r="J27" s="8">
         <v>24</v>
       </c>
-      <c r="J27" s="9">
+      <c r="K27" s="8">
         <v>24</v>
       </c>
-      <c r="K27" s="9">
+      <c r="L27" s="8">
         <v>20</v>
       </c>
-      <c r="O27" s="8">
+      <c r="P27" s="7">
         <v>9789998791794</v>
       </c>
-      <c r="P27" s="3" t="s">
+      <c r="Q27" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q27" s="4">
+      <c r="R27" s="2"/>
+      <c r="S27" s="3">
         <v>24</v>
       </c>
-      <c r="R27" s="4">
+      <c r="T27" s="3">
         <v>24</v>
       </c>
-      <c r="S27" s="4">
+      <c r="U27" s="3">
         <v>20</v>
       </c>
-      <c r="X27" s="5" t="s">
+      <c r="Z27" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y27" s="6">
+      <c r="AA27" s="5">
         <v>24</v>
       </c>
-      <c r="Z27" s="6">
+      <c r="AB27" s="5">
         <v>24</v>
       </c>
-      <c r="AA27" s="6">
+      <c r="AC27" s="5">
         <v>20</v>
       </c>
-      <c r="AF27" t="s">
+      <c r="AH27" t="s">
         <v>141</v>
       </c>
-      <c r="AO27" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP27" t="s">
+      <c r="AQ27" t="s">
         <v>30</v>
       </c>
       <c r="AR27" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT27" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>146</v>
       </c>
@@ -3043,7 +3173,7 @@
       <c r="C28">
         <v>100</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="14" t="s">
         <v>143</v>
       </c>
       <c r="E28" t="s">
@@ -3053,67 +3183,71 @@
         <v>77</v>
       </c>
       <c r="G28" t="s">
-        <v>182</v>
-      </c>
-      <c r="H28" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="H28" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I28" s="9">
+      <c r="I28" t="s">
+        <v>178</v>
+      </c>
+      <c r="J28" s="8">
         <v>21</v>
       </c>
-      <c r="J28" s="9">
+      <c r="K28" s="8">
         <v>20</v>
       </c>
-      <c r="K28" s="9">
+      <c r="L28" s="8">
         <v>18</v>
       </c>
-      <c r="O28" s="8">
+      <c r="P28" s="7">
         <v>9782919820481</v>
       </c>
-      <c r="P28" s="3" t="s">
+      <c r="Q28" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q28" s="4">
+      <c r="R28" s="2"/>
+      <c r="S28" s="3">
         <v>21</v>
       </c>
-      <c r="R28" s="4">
+      <c r="T28" s="3">
         <v>20</v>
       </c>
-      <c r="S28" s="4">
+      <c r="U28" s="3">
         <v>18</v>
       </c>
-      <c r="X28" s="5" t="s">
+      <c r="Z28" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y28" s="6">
+      <c r="AA28" s="5">
         <v>21</v>
       </c>
-      <c r="Z28" s="6">
+      <c r="AB28" s="5">
         <v>20</v>
       </c>
-      <c r="AA28" s="6">
+      <c r="AC28" s="5">
         <v>18</v>
       </c>
-      <c r="AF28" t="s">
+      <c r="AH28" t="s">
         <v>147</v>
       </c>
-      <c r="AO28" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP28" t="s">
+      <c r="AQ28" t="s">
         <v>30</v>
       </c>
       <c r="AR28" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT28" t="s">
         <v>40</v>
       </c>
-      <c r="AT28" t="s">
+      <c r="AV28" t="s">
         <v>143</v>
       </c>
-      <c r="AU28">
+      <c r="AW28">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>144</v>
       </c>
@@ -3123,7 +3257,7 @@
       <c r="C29">
         <v>200</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="14" t="s">
         <v>142</v>
       </c>
       <c r="E29" t="s">
@@ -3133,74 +3267,81 @@
         <v>77</v>
       </c>
       <c r="G29" t="s">
-        <v>182</v>
-      </c>
-      <c r="H29" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="H29" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" t="s">
+        <v>178</v>
+      </c>
+      <c r="J29" s="8">
         <v>21</v>
       </c>
-      <c r="J29" s="9">
+      <c r="K29" s="8">
         <v>20</v>
       </c>
-      <c r="K29" s="9">
+      <c r="L29" s="8">
         <v>18</v>
       </c>
-      <c r="O29" s="8">
+      <c r="P29" s="7">
         <v>9782919820153</v>
       </c>
-      <c r="P29" s="3" t="s">
+      <c r="Q29" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Q29" s="4">
+      <c r="R29" s="2"/>
+      <c r="S29" s="3">
         <v>21</v>
       </c>
-      <c r="R29" s="4">
+      <c r="T29" s="3">
         <v>20</v>
       </c>
-      <c r="S29" s="4">
+      <c r="U29" s="3">
         <v>18</v>
       </c>
-      <c r="X29" s="5" t="s">
+      <c r="Z29" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="Y29" s="6">
+      <c r="AA29" s="5">
         <v>21</v>
       </c>
-      <c r="Z29" s="6">
+      <c r="AB29" s="5">
         <v>20</v>
       </c>
-      <c r="AA29" s="6">
+      <c r="AC29" s="5">
         <v>18</v>
       </c>
-      <c r="AF29" t="s">
+      <c r="AH29" t="s">
         <v>145</v>
       </c>
-      <c r="AO29" t="s">
-        <v>30</v>
-      </c>
-      <c r="AP29" t="s">
+      <c r="AQ29" t="s">
         <v>30</v>
       </c>
       <c r="AR29" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT29" t="s">
         <v>40</v>
       </c>
-      <c r="AT29" t="s">
+      <c r="AV29" t="s">
         <v>142</v>
       </c>
-      <c r="AU29">
+      <c r="AW29">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>161</v>
       </c>
       <c r="B30" t="s">
         <v>53</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="C30">
+        <v>250</v>
+      </c>
+      <c r="D30" s="14" t="s">
         <v>158</v>
       </c>
       <c r="E30" t="s">
@@ -3210,41 +3351,57 @@
         <v>77</v>
       </c>
       <c r="G30" t="s">
-        <v>182</v>
-      </c>
-      <c r="H30" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="H30" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I30" s="9">
+      <c r="I30" t="s">
+        <v>178</v>
+      </c>
+      <c r="J30" s="8">
         <v>24</v>
       </c>
-      <c r="O30" s="12">
+      <c r="P30" s="12">
         <v>9789998793781</v>
       </c>
-      <c r="P30" s="3" t="s">
+      <c r="Q30" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="AF30" t="s">
+      <c r="R30" s="2"/>
+      <c r="Z30" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH30" t="s">
         <v>164</v>
       </c>
+      <c r="AQ30" t="s">
+        <v>30</v>
+      </c>
       <c r="AR30" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT30" t="s">
         <v>40</v>
       </c>
-      <c r="AT30" t="s">
+      <c r="AV30" t="s">
         <v>167</v>
       </c>
-      <c r="AU30">
+      <c r="AW30">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>162</v>
       </c>
       <c r="B31" t="s">
         <v>53</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="C31">
+        <v>450</v>
+      </c>
+      <c r="D31" s="14" t="s">
         <v>159</v>
       </c>
       <c r="E31" t="s">
@@ -3254,41 +3411,57 @@
         <v>77</v>
       </c>
       <c r="G31" t="s">
-        <v>182</v>
-      </c>
-      <c r="H31" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="H31" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I31" s="9">
+      <c r="I31" t="s">
+        <v>178</v>
+      </c>
+      <c r="J31" s="8">
         <v>25</v>
       </c>
-      <c r="O31" s="12">
+      <c r="P31" s="12">
         <v>9782919820047</v>
       </c>
-      <c r="P31" s="3" t="s">
+      <c r="Q31" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="AF31" t="s">
+      <c r="R31" s="2"/>
+      <c r="Z31" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH31" t="s">
         <v>165</v>
       </c>
+      <c r="AQ31" t="s">
+        <v>30</v>
+      </c>
       <c r="AR31" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT31" t="s">
         <v>40</v>
       </c>
-      <c r="AT31" t="s">
+      <c r="AV31" t="s">
         <v>167</v>
       </c>
-      <c r="AU31">
+      <c r="AW31">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:47" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>163</v>
       </c>
       <c r="B32" t="s">
         <v>53</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="C32">
+        <v>650</v>
+      </c>
+      <c r="D32" s="14" t="s">
         <v>160</v>
       </c>
       <c r="E32" t="s">
@@ -3298,153 +3471,537 @@
         <v>77</v>
       </c>
       <c r="G32" t="s">
+        <v>178</v>
+      </c>
+      <c r="H32" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="I32" t="s">
+        <v>178</v>
+      </c>
+      <c r="J32" s="8">
+        <v>32</v>
+      </c>
+      <c r="P32" s="12">
+        <v>9782919820467</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="R32" s="2"/>
+      <c r="Z32" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH32" t="s">
+        <v>166</v>
+      </c>
+      <c r="AQ32" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR32" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT32" t="s">
+        <v>40</v>
+      </c>
+      <c r="AV32" t="s">
+        <v>167</v>
+      </c>
+      <c r="AW32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>200</v>
+      </c>
+      <c r="B33" t="s">
+        <v>173</v>
+      </c>
+      <c r="C33">
+        <v>100</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="E33" t="s">
+        <v>174</v>
+      </c>
+      <c r="G33" t="s">
+        <v>175</v>
+      </c>
+      <c r="H33" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="I33" t="s">
+        <v>175</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="R33" s="2"/>
+      <c r="S33" s="3">
+        <v>14</v>
+      </c>
+      <c r="Y33" s="11">
+        <v>9780062095886</v>
+      </c>
+      <c r="Z33" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH33" t="s">
+        <v>202</v>
+      </c>
+      <c r="AQ33" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR33" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT33" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>205</v>
+      </c>
+      <c r="B34" t="s">
+        <v>173</v>
+      </c>
+      <c r="C34">
+        <v>200</v>
+      </c>
+      <c r="D34" t="s">
+        <v>203</v>
+      </c>
+      <c r="E34" t="s">
+        <v>176</v>
+      </c>
+      <c r="G34" t="s">
+        <v>175</v>
+      </c>
+      <c r="H34" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="I34" t="s">
+        <v>204</v>
+      </c>
+      <c r="J34" s="8">
+        <v>38</v>
+      </c>
+      <c r="P34" s="7">
+        <v>9780151003532</v>
+      </c>
+      <c r="Q34" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="R34" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="S34" s="3">
+        <v>11</v>
+      </c>
+      <c r="Y34" s="11">
+        <v>9780156011464</v>
+      </c>
+      <c r="Z34" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH34" t="s">
+        <v>206</v>
+      </c>
+      <c r="AQ34" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR34" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT34" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>209</v>
+      </c>
+      <c r="B35" t="s">
+        <v>173</v>
+      </c>
+      <c r="C35">
+        <v>300</v>
+      </c>
+      <c r="D35" t="s">
+        <v>207</v>
+      </c>
+      <c r="E35" t="s">
+        <v>179</v>
+      </c>
+      <c r="H35" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="I35"/>
+      <c r="Q35" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="R35" t="s">
+        <v>208</v>
+      </c>
+      <c r="S35" s="3">
+        <v>18</v>
+      </c>
+      <c r="Y35" s="11">
+        <v>9781400043293</v>
+      </c>
+      <c r="Z35" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH35" t="s">
+        <v>210</v>
+      </c>
+      <c r="AQ35" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR35" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT35" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="36" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>194</v>
+      </c>
+      <c r="B36" t="s">
+        <v>173</v>
+      </c>
+      <c r="C36">
+        <v>400</v>
+      </c>
+      <c r="D36" t="s">
+        <v>181</v>
+      </c>
+      <c r="E36" t="s">
+        <v>180</v>
+      </c>
+      <c r="G36" t="s">
         <v>182</v>
       </c>
-      <c r="H32" s="8" t="s">
+      <c r="H36" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="I32" s="9">
-        <v>32</v>
-      </c>
-      <c r="O32" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="P32" s="3" t="s">
+      <c r="I36" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q36" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="AF32" t="s">
-        <v>166</v>
-      </c>
-      <c r="AT32" t="s">
-        <v>167</v>
-      </c>
-      <c r="AU32">
-        <v>3</v>
+      <c r="R36" t="s">
+        <v>182</v>
+      </c>
+      <c r="S36" s="3">
+        <v>15</v>
+      </c>
+      <c r="Y36" s="11">
+        <v>9780374528614</v>
+      </c>
+      <c r="Z36" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH36" t="s">
+        <v>211</v>
+      </c>
+      <c r="AQ36" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR36" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT36" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+    <row r="37" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>195</v>
+      </c>
+      <c r="B37" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37">
+        <v>600</v>
+      </c>
+      <c r="D37" t="s">
+        <v>186</v>
+      </c>
+      <c r="E37" t="s">
+        <v>183</v>
+      </c>
+      <c r="F37" t="s">
+        <v>213</v>
+      </c>
+      <c r="G37" t="s">
+        <v>184</v>
+      </c>
+      <c r="H37" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="I37" t="s">
+        <v>184</v>
+      </c>
+      <c r="J37" s="8">
+        <v>16</v>
+      </c>
+      <c r="P37" s="7">
+        <v>9780393067798</v>
+      </c>
+      <c r="Q37" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="R37" s="2"/>
+      <c r="S37" s="3">
+        <v>19</v>
+      </c>
+      <c r="Y37" s="11">
+        <v>9780393345551</v>
+      </c>
+      <c r="Z37" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH37" t="s">
+        <v>212</v>
+      </c>
+      <c r="AQ37" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR37" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT37" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="38" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>196</v>
+      </c>
+      <c r="B38" t="s">
+        <v>173</v>
+      </c>
+      <c r="C38">
+        <v>700</v>
+      </c>
+      <c r="D38" t="s">
+        <v>185</v>
+      </c>
+      <c r="E38" t="s">
+        <v>176</v>
+      </c>
+      <c r="G38" t="s">
+        <v>177</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="I38" t="s">
+        <v>177</v>
+      </c>
+      <c r="J38" s="8">
+        <v>30</v>
+      </c>
+      <c r="P38" s="7">
+        <v>9780544126022</v>
+      </c>
+      <c r="Q38" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="R38" s="2"/>
+      <c r="S38" s="3">
+        <v>11</v>
+      </c>
+      <c r="Y38" s="11">
+        <v>9780544705159</v>
+      </c>
+      <c r="Z38" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH38" t="s">
+        <v>216</v>
+      </c>
+      <c r="AQ38" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR38" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT38" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="39" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>197</v>
+      </c>
+      <c r="B39" t="s">
+        <v>173</v>
+      </c>
+      <c r="C39">
+        <v>800</v>
+      </c>
+      <c r="D39" t="s">
+        <v>187</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="F39" t="s">
+        <v>189</v>
+      </c>
+      <c r="G39" t="s">
         <v>178</v>
       </c>
-      <c r="B33" t="s">
-        <v>174</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="E33" t="s">
-        <v>175</v>
-      </c>
-      <c r="G33" t="s">
-        <v>177</v>
-      </c>
-      <c r="W33" s="15">
-        <v>9780060934941</v>
+      <c r="H39" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="I39"/>
+      <c r="J39" s="8">
+        <v>25</v>
+      </c>
+      <c r="P39" s="7">
+        <v>9788367602488</v>
+      </c>
+      <c r="Q39" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="R39" s="2"/>
+      <c r="S39" s="3">
+        <v>11</v>
+      </c>
+      <c r="Y39" s="11">
+        <v>9788367602471</v>
+      </c>
+      <c r="Z39" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH39" t="s">
+        <v>214</v>
+      </c>
+      <c r="AQ39" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR39" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT39" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B34" t="s">
-        <v>174</v>
-      </c>
-      <c r="D34" t="s">
-        <v>180</v>
-      </c>
-      <c r="E34" t="s">
-        <v>179</v>
-      </c>
-      <c r="G34" t="s">
-        <v>181</v>
-      </c>
-      <c r="W34" s="15">
-        <v>9780156005166</v>
+    <row r="40" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>198</v>
+      </c>
+      <c r="B40" t="s">
+        <v>173</v>
+      </c>
+      <c r="C40">
+        <v>900</v>
+      </c>
+      <c r="D40" t="s">
+        <v>190</v>
+      </c>
+      <c r="E40" t="s">
+        <v>191</v>
+      </c>
+      <c r="H40" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="I40"/>
+      <c r="Q40" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="R40" s="2"/>
+      <c r="S40" s="3">
+        <v>7</v>
+      </c>
+      <c r="Y40" s="11">
+        <v>9798802065853</v>
+      </c>
+      <c r="Z40" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH40" t="s">
+        <v>217</v>
+      </c>
+      <c r="AQ40" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR40" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT40" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B35" t="s">
-        <v>174</v>
-      </c>
-      <c r="D35" t="s">
-        <v>184</v>
-      </c>
-      <c r="E35" t="s">
-        <v>183</v>
-      </c>
-      <c r="G35" t="s">
-        <v>177</v>
-      </c>
-      <c r="W35" s="15">
-        <v>9780060931544</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B36" t="s">
-        <v>174</v>
-      </c>
-      <c r="D36" t="s">
-        <v>186</v>
-      </c>
-      <c r="E36" t="s">
-        <v>185</v>
-      </c>
-      <c r="G36" t="s">
-        <v>187</v>
-      </c>
-      <c r="W36" s="15">
-        <v>9780374533311</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B37" t="s">
-        <v>174</v>
-      </c>
-      <c r="D37" t="s">
-        <v>189</v>
-      </c>
-      <c r="E37" t="s">
-        <v>188</v>
-      </c>
-      <c r="G37" t="s">
-        <v>190</v>
-      </c>
-      <c r="W37" s="15">
-        <v>9780857425935</v>
-      </c>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B38" t="s">
-        <v>174</v>
-      </c>
-      <c r="D38" t="s">
+    <row r="41" spans="1:46" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>199</v>
+      </c>
+      <c r="B41" t="s">
+        <v>173</v>
+      </c>
+      <c r="C41">
+        <v>1000</v>
+      </c>
+      <c r="D41" t="s">
         <v>193</v>
       </c>
-      <c r="E38" t="s">
-        <v>191</v>
-      </c>
-      <c r="G38" t="s">
+      <c r="E41" t="s">
         <v>192</v>
       </c>
-      <c r="W38" s="15">
-        <v>9780393323856</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B39" t="s">
-        <v>174</v>
-      </c>
-      <c r="E39" t="s">
-        <v>179</v>
+      <c r="F41" t="s">
+        <v>65</v>
+      </c>
+      <c r="H41" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="I41"/>
+      <c r="Q41" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="R41" s="2"/>
+      <c r="S41" s="3">
+        <v>14</v>
+      </c>
+      <c r="Y41" s="11">
+        <v>9781931243810</v>
+      </c>
+      <c r="Z41" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="AH41" t="s">
+        <v>215</v>
+      </c>
+      <c r="AQ41" t="s">
+        <v>30</v>
+      </c>
+      <c r="AR41" t="s">
+        <v>30</v>
+      </c>
+      <c r="AT41" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AO1:AP1048576" xr:uid="{F1FB7CD6-B38A-4A39-862C-8A1111411C8C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Z42:Z1048576 Q42:R1048576 H42:I1048576" xr:uid="{D2C177B6-092A-4420-B1E2-D1681CD512E9}">
+      <formula1>"hardcover, paperback, eBook, audiobook1"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AQ1:AR1048576" xr:uid="{F1FB7CD6-B38A-4A39-862C-8A1111411C8C}">
       <formula1>"yes, no"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H33:H1048576 X30:X1048576 P33:P1048576" xr:uid="{D2C177B6-092A-4420-B1E2-D1681CD512E9}">
-      <formula1>"hardcover, paperback, eBook, audiobook1"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AG1:AG1048576" xr:uid="{E592C05B-F748-4394-B2BA-C13419076CB7}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI1:AI1048576" xr:uid="{E592C05B-F748-4394-B2BA-C13419076CB7}">
       <formula1>"ingram, gardners, libri, bookvault"</formula1>
     </dataValidation>
   </dataValidations>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/bookstore-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DC03F12-F7B5-4D22-AF7F-466D28735146}"/>
   <bookViews>
     <workbookView xWindow="3060" yWindow="570" windowWidth="23220" windowHeight="14940" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
@@ -533,9 +533,6 @@
     <t>covers/divine-julius.jpg</t>
   </si>
   <si>
-    <t>covers/naso-the-poet-1.jpg</t>
-  </si>
-  <si>
     <t>covers/tiberius-caesar.jpg</t>
   </si>
   <si>
@@ -690,6 +687,9 @@
   </si>
   <si>
     <t>covers/krzysztof-kamil-baczynski.jpg</t>
+  </si>
+  <si>
+    <t>covers/naso-the-poet.jpg</t>
   </si>
 </sst>
 </file>
@@ -1678,7 +1678,7 @@
       </c>
       <c r="I7"/>
       <c r="P7" s="7" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="Q7" s="2" t="s">
         <v>155</v>
@@ -2066,13 +2066,13 @@
         <v>77</v>
       </c>
       <c r="G13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H13" s="7" t="s">
         <v>154</v>
       </c>
       <c r="I13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J13" s="8">
         <v>24</v>
@@ -2103,7 +2103,7 @@
         <v>40</v>
       </c>
       <c r="AV13" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AW13">
         <v>1</v>
@@ -2324,7 +2324,7 @@
     </row>
     <row r="17" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B17" t="s">
         <v>129</v>
@@ -2412,13 +2412,13 @@
         <v>77</v>
       </c>
       <c r="G18" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H18" s="7" t="s">
         <v>154</v>
       </c>
       <c r="I18" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J18" s="8">
         <v>25</v>
@@ -2472,7 +2472,7 @@
     </row>
     <row r="19" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B19" t="s">
         <v>97</v>
@@ -2490,13 +2490,13 @@
         <v>77</v>
       </c>
       <c r="G19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H19" s="7" t="s">
         <v>154</v>
       </c>
       <c r="I19" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J19" s="8">
         <v>25</v>
@@ -2568,13 +2568,13 @@
         <v>77</v>
       </c>
       <c r="G20" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H20" s="7" t="s">
         <v>154</v>
       </c>
       <c r="I20" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J20" s="8">
         <v>27</v>
@@ -2646,13 +2646,13 @@
         <v>77</v>
       </c>
       <c r="G21" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H21" s="7" t="s">
         <v>154</v>
       </c>
       <c r="I21" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J21" s="8">
         <v>25</v>
@@ -2852,7 +2852,7 @@
     </row>
     <row r="24" spans="1:49" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B24" t="s">
         <v>102</v>
@@ -2943,13 +2943,13 @@
         <v>77</v>
       </c>
       <c r="G25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H25" s="7" t="s">
         <v>154</v>
       </c>
       <c r="I25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J25" s="8">
         <v>17</v>
@@ -3001,7 +3001,7 @@
         <v>40</v>
       </c>
       <c r="AV25" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AW25">
         <v>4</v>
@@ -3027,13 +3027,13 @@
         <v>77</v>
       </c>
       <c r="G26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H26" s="7" t="s">
         <v>154</v>
       </c>
       <c r="I26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J26" s="8">
         <v>24</v>
@@ -3105,13 +3105,13 @@
         <v>77</v>
       </c>
       <c r="G27" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H27" s="7" t="s">
         <v>154</v>
       </c>
       <c r="I27" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J27" s="8">
         <v>24</v>
@@ -3183,13 +3183,13 @@
         <v>77</v>
       </c>
       <c r="G28" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H28" s="7" t="s">
         <v>154</v>
       </c>
       <c r="I28" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J28" s="8">
         <v>21</v>
@@ -3267,13 +3267,13 @@
         <v>77</v>
       </c>
       <c r="G29" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H29" s="7" t="s">
         <v>154</v>
       </c>
       <c r="I29" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J29" s="8">
         <v>21</v>
@@ -3351,13 +3351,13 @@
         <v>77</v>
       </c>
       <c r="G30" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H30" s="7" t="s">
         <v>154</v>
       </c>
       <c r="I30" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J30" s="8">
         <v>24</v>
@@ -3385,7 +3385,7 @@
         <v>40</v>
       </c>
       <c r="AV30" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AW30">
         <v>1</v>
@@ -3411,13 +3411,13 @@
         <v>77</v>
       </c>
       <c r="G31" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H31" s="7" t="s">
         <v>154</v>
       </c>
       <c r="I31" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J31" s="8">
         <v>25</v>
@@ -3433,7 +3433,7 @@
         <v>156</v>
       </c>
       <c r="AH31" t="s">
-        <v>165</v>
+        <v>217</v>
       </c>
       <c r="AQ31" t="s">
         <v>30</v>
@@ -3445,7 +3445,7 @@
         <v>40</v>
       </c>
       <c r="AV31" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AW31">
         <v>2</v>
@@ -3471,13 +3471,13 @@
         <v>77</v>
       </c>
       <c r="G32" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H32" s="7" t="s">
         <v>154</v>
       </c>
       <c r="I32" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J32" s="8">
         <v>32</v>
@@ -3493,7 +3493,7 @@
         <v>156</v>
       </c>
       <c r="AH32" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AQ32" t="s">
         <v>30</v>
@@ -3505,7 +3505,7 @@
         <v>40</v>
       </c>
       <c r="AV32" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AW32">
         <v>3</v>
@@ -3513,28 +3513,28 @@
     </row>
     <row r="33" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B33" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C33">
         <v>100</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E33" t="s">
+        <v>173</v>
+      </c>
+      <c r="G33" t="s">
         <v>174</v>
-      </c>
-      <c r="G33" t="s">
-        <v>175</v>
       </c>
       <c r="H33" s="7" t="s">
         <v>154</v>
       </c>
       <c r="I33" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Q33" s="2" t="s">
         <v>155</v>
@@ -3550,7 +3550,7 @@
         <v>156</v>
       </c>
       <c r="AH33" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AQ33" t="s">
         <v>30</v>
@@ -3564,28 +3564,28 @@
     </row>
     <row r="34" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B34" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C34">
         <v>200</v>
       </c>
       <c r="D34" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E34" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G34" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H34" s="7" t="s">
         <v>154</v>
       </c>
       <c r="I34" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="J34" s="8">
         <v>38</v>
@@ -3597,7 +3597,7 @@
         <v>155</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="S34" s="3">
         <v>11</v>
@@ -3609,7 +3609,7 @@
         <v>156</v>
       </c>
       <c r="AH34" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AQ34" t="s">
         <v>30</v>
@@ -3623,19 +3623,19 @@
     </row>
     <row r="35" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B35" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C35">
         <v>300</v>
       </c>
       <c r="D35" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E35" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H35" s="7" t="s">
         <v>154</v>
@@ -3645,7 +3645,7 @@
         <v>155</v>
       </c>
       <c r="R35" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="S35" s="3">
         <v>18</v>
@@ -3657,7 +3657,7 @@
         <v>156</v>
       </c>
       <c r="AH35" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AQ35" t="s">
         <v>30</v>
@@ -3671,34 +3671,34 @@
     </row>
     <row r="36" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B36" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C36">
         <v>400</v>
       </c>
       <c r="D36" t="s">
+        <v>180</v>
+      </c>
+      <c r="E36" t="s">
+        <v>179</v>
+      </c>
+      <c r="G36" t="s">
         <v>181</v>
-      </c>
-      <c r="E36" t="s">
-        <v>180</v>
-      </c>
-      <c r="G36" t="s">
-        <v>182</v>
       </c>
       <c r="H36" s="7" t="s">
         <v>154</v>
       </c>
       <c r="I36" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Q36" s="2" t="s">
         <v>155</v>
       </c>
       <c r="R36" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="S36" s="3">
         <v>15</v>
@@ -3710,7 +3710,7 @@
         <v>156</v>
       </c>
       <c r="AH36" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AQ36" t="s">
         <v>30</v>
@@ -3724,31 +3724,31 @@
     </row>
     <row r="37" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B37" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C37">
         <v>600</v>
       </c>
       <c r="D37" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E37" t="s">
+        <v>182</v>
+      </c>
+      <c r="F37" t="s">
+        <v>212</v>
+      </c>
+      <c r="G37" t="s">
         <v>183</v>
-      </c>
-      <c r="F37" t="s">
-        <v>213</v>
-      </c>
-      <c r="G37" t="s">
-        <v>184</v>
       </c>
       <c r="H37" s="7" t="s">
         <v>154</v>
       </c>
       <c r="I37" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="J37" s="8">
         <v>16</v>
@@ -3770,7 +3770,7 @@
         <v>156</v>
       </c>
       <c r="AH37" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AQ37" t="s">
         <v>30</v>
@@ -3784,28 +3784,28 @@
     </row>
     <row r="38" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B38" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C38">
         <v>700</v>
       </c>
       <c r="D38" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E38" t="s">
+        <v>175</v>
+      </c>
+      <c r="G38" t="s">
         <v>176</v>
-      </c>
-      <c r="G38" t="s">
-        <v>177</v>
       </c>
       <c r="H38" s="7" t="s">
         <v>154</v>
       </c>
       <c r="I38" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J38" s="8">
         <v>30</v>
@@ -3827,7 +3827,7 @@
         <v>156</v>
       </c>
       <c r="AH38" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AQ38" t="s">
         <v>30</v>
@@ -3841,25 +3841,25 @@
     </row>
     <row r="39" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B39" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C39">
         <v>800</v>
       </c>
       <c r="D39" t="s">
+        <v>186</v>
+      </c>
+      <c r="E39" s="13" t="s">
         <v>187</v>
       </c>
-      <c r="E39" s="13" t="s">
+      <c r="F39" t="s">
         <v>188</v>
       </c>
-      <c r="F39" t="s">
-        <v>189</v>
-      </c>
       <c r="G39" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H39" s="7" t="s">
         <v>154</v>
@@ -3885,7 +3885,7 @@
         <v>156</v>
       </c>
       <c r="AH39" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AQ39" t="s">
         <v>30</v>
@@ -3899,19 +3899,19 @@
     </row>
     <row r="40" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B40" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C40">
         <v>900</v>
       </c>
       <c r="D40" t="s">
+        <v>189</v>
+      </c>
+      <c r="E40" t="s">
         <v>190</v>
-      </c>
-      <c r="E40" t="s">
-        <v>191</v>
       </c>
       <c r="H40" s="7" t="s">
         <v>154</v>
@@ -3931,7 +3931,7 @@
         <v>156</v>
       </c>
       <c r="AH40" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AQ40" t="s">
         <v>30</v>
@@ -3945,19 +3945,19 @@
     </row>
     <row r="41" spans="1:46" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B41" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C41">
         <v>1000</v>
       </c>
       <c r="D41" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E41" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F41" t="s">
         <v>65</v>
@@ -3980,7 +3980,7 @@
         <v>156</v>
       </c>
       <c r="AH41" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AQ41" t="s">
         <v>30</v>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="1" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DC03F12-F7B5-4D22-AF7F-466D28735146}"/>
   <bookViews>
-    <workbookView xWindow="3060" yWindow="570" windowWidth="23220" windowHeight="14940" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/bookstore-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="255" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A6A1B34-A3F3-435E-8B40-A52AF56B91F5}"/>
+  <xr:revisionPtr revIDLastSave="258" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{932F48F3-90D3-474A-9A59-99570B0BC66F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="258">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="219">
   <si>
     <t>cover</t>
   </si>
@@ -77,30 +77,12 @@
     <t>Arkady Fiedler</t>
   </si>
   <si>
-    <t>covers/ChopinInParis.jpg</t>
-  </si>
-  <si>
-    <t>covers/PeasantPrince.jpg</t>
-  </si>
-  <si>
-    <t>covers/LightAndFlame.jpg</t>
-  </si>
-  <si>
-    <t>covers/303squadron.jpg</t>
-  </si>
-  <si>
-    <t>covers/TrailOfHope.jpg</t>
-  </si>
-  <si>
     <t>id</t>
   </si>
   <si>
     <t>peasant-prince</t>
   </si>
   <si>
-    <t>covers/IzabelaTheValiant.jpg</t>
-  </si>
-  <si>
     <t>trail-of-hope</t>
   </si>
   <si>
@@ -215,15 +197,6 @@
     <t>Bill Johnston</t>
   </si>
   <si>
-    <t>covers/the-doll.jpg</t>
-  </si>
-  <si>
-    <t>covers/the-peasants.jpg</t>
-  </si>
-  <si>
-    <t>covers/pan-tadeusz.jpg</t>
-  </si>
-  <si>
     <t>Choucas</t>
   </si>
   <si>
@@ -233,9 +206,6 @@
     <t>Ursula Philips</t>
   </si>
   <si>
-    <t>covers/choucas.jpg</t>
-  </si>
-  <si>
     <t>Henryk Sienkiewicz</t>
   </si>
   <si>
@@ -251,9 +221,6 @@
     <t>Tom Pinch</t>
   </si>
   <si>
-    <t>covers/forest-folk.jpg</t>
-  </si>
-  <si>
     <t>forest-folk</t>
   </si>
   <si>
@@ -266,9 +233,6 @@
     <t>In desert and wilderness</t>
   </si>
   <si>
-    <t>covers/desert-wilderness.jpg</t>
-  </si>
-  <si>
     <t>Classics; Books in Focus</t>
   </si>
   <si>
@@ -299,18 +263,9 @@
     <t>the-emperor</t>
   </si>
   <si>
-    <t>covers/shah-of-shahs.jpg</t>
-  </si>
-  <si>
-    <t>covers/the-emperor.jpg</t>
-  </si>
-  <si>
     <t>Non-fiction</t>
   </si>
   <si>
-    <t>covers/castorp.jpg</t>
-  </si>
-  <si>
     <t>Another Day of Life</t>
   </si>
   <si>
@@ -344,18 +299,6 @@
     <t>last-olympiad</t>
   </si>
   <si>
-    <t>covers/seven-against.jpg</t>
-  </si>
-  <si>
-    <t>meeting-in-oea.jpg</t>
-  </si>
-  <si>
-    <t>covers/emperor-julian.jpg</t>
-  </si>
-  <si>
-    <t>covers/last-olympiad.jpg</t>
-  </si>
-  <si>
     <t>Polish History; Books in Focus</t>
   </si>
   <si>
@@ -377,9 +320,6 @@
     <t>Joanna Kilmartin</t>
   </si>
   <si>
-    <t>covers/solaris.jpg</t>
-  </si>
-  <si>
     <t>fiasco</t>
   </si>
   <si>
@@ -389,27 +329,15 @@
     <t>Michael Kandel</t>
   </si>
   <si>
-    <t>covers/fiasco.jpg</t>
-  </si>
-  <si>
     <t>The Invincible</t>
   </si>
   <si>
     <t>Chahary</t>
   </si>
   <si>
-    <t>covers/chahary.jpg</t>
-  </si>
-  <si>
     <t>Books in Focus</t>
   </si>
   <si>
-    <t>covers/the-invincible.jpg</t>
-  </si>
-  <si>
-    <t>covers/another-day.jpg</t>
-  </si>
-  <si>
     <t>Fiction; Books in Focus</t>
   </si>
   <si>
@@ -434,12 +362,6 @@
     <t>Witold Makowiecki</t>
   </si>
   <si>
-    <t>covers/melicles.jpg</t>
-  </si>
-  <si>
-    <t>covers/diossos.jpg</t>
-  </si>
-  <si>
     <t>The Ships of Minos</t>
   </si>
   <si>
@@ -449,15 +371,9 @@
     <t>ships-minos-1</t>
   </si>
   <si>
-    <t>covers/ships-minos-1.jpg</t>
-  </si>
-  <si>
     <t>white-jaguar-1</t>
   </si>
   <si>
-    <t>covers/white-jaguar-1.jpg</t>
-  </si>
-  <si>
     <t>chahary</t>
   </si>
   <si>
@@ -500,12 +416,6 @@
     <t>tiberius-caesar</t>
   </si>
   <si>
-    <t>covers/divine-julius.jpg</t>
-  </si>
-  <si>
-    <t>covers/tiberius-caesar.jpg</t>
-  </si>
-  <si>
     <t>The Roman Trilogy</t>
   </si>
   <si>
@@ -608,9 +518,6 @@
     <t>Selected and Last Poems: 1931-2004</t>
   </si>
   <si>
-    <t>covers/milosz-selected-and-last-poems.jpg</t>
-  </si>
-  <si>
     <t>Poems New And Collected: 1957-1997</t>
   </si>
   <si>
@@ -620,9 +527,6 @@
     <t>poems-new-and-szymborska</t>
   </si>
   <si>
-    <t>covers/poems-new-and-szymborska.jpg</t>
-  </si>
-  <si>
     <t>Poems</t>
   </si>
   <si>
@@ -632,31 +536,7 @@
     <t>poems-herbert</t>
   </si>
   <si>
-    <t>covers/poems-herbert.jpg</t>
-  </si>
-  <si>
-    <t>covers/without-end.jpg</t>
-  </si>
-  <si>
-    <t>covers/sobbing-superpower.jpg</t>
-  </si>
-  <si>
     <t>Joanna Trzeciak</t>
-  </si>
-  <si>
-    <t>covers/from-the-tree-of-knowledge.jpg</t>
-  </si>
-  <si>
-    <t>covers/white-magic-baczynski.jpg</t>
-  </si>
-  <si>
-    <t>covers/map-collected-and-last.jpg</t>
-  </si>
-  <si>
-    <t>covers/krzysztof-kamil-baczynski.jpg</t>
-  </si>
-  <si>
-    <t>covers/naso-the-poet.jpg</t>
   </si>
   <si>
     <t>hc_publisher</t>
@@ -871,6 +751,9 @@
 -Yuliya Musakovska
 -Les Wicks
 While all have seen their work translated into foreign languages, all poems included in this collection appear in English for the first time.</t>
+  </si>
+  <si>
+    <t>Fiction; Books in Focus; Young Adult</t>
   </si>
 </sst>
 </file>
@@ -1004,7 +887,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1021,14 +904,12 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -1391,165 +1272,165 @@
   <sheetData>
     <row r="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B1" t="s">
-        <v>231</v>
+        <v>191</v>
       </c>
       <c r="C1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D1" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="E1" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="F1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>207</v>
+        <v>167</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>208</v>
+        <v>168</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>209</v>
+        <v>169</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>211</v>
+        <v>171</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>212</v>
+        <v>172</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>213</v>
+        <v>173</v>
       </c>
       <c r="O1" s="13" t="s">
-        <v>214</v>
+        <v>174</v>
       </c>
       <c r="P1" s="2" t="s">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>215</v>
+        <v>175</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>216</v>
+        <v>176</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>217</v>
+        <v>177</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>218</v>
+        <v>178</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>219</v>
+        <v>179</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>220</v>
+        <v>180</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>221</v>
+        <v>181</v>
       </c>
       <c r="X1" s="9" t="s">
-        <v>222</v>
+        <v>182</v>
       </c>
       <c r="Y1" s="4" t="s">
-        <v>143</v>
+        <v>115</v>
       </c>
       <c r="Z1" s="4" t="s">
-        <v>223</v>
+        <v>183</v>
       </c>
       <c r="AA1" s="5" t="s">
-        <v>224</v>
+        <v>184</v>
       </c>
       <c r="AB1" s="5" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="AC1" s="5" t="s">
-        <v>226</v>
+        <v>186</v>
       </c>
       <c r="AD1" s="5" t="s">
-        <v>227</v>
+        <v>187</v>
       </c>
       <c r="AE1" s="5" t="s">
-        <v>228</v>
+        <v>188</v>
       </c>
       <c r="AF1" s="5" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="AG1" s="8" t="s">
-        <v>230</v>
+        <v>190</v>
       </c>
       <c r="AH1" t="s">
         <v>0</v>
       </c>
       <c r="AI1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="AJ1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AK1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="AL1" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AM1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AN1" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="AN1" s="12" t="s">
-        <v>33</v>
-      </c>
       <c r="AO1" t="s">
-        <v>232</v>
+        <v>192</v>
       </c>
       <c r="AP1" t="s">
-        <v>234</v>
+        <v>194</v>
       </c>
       <c r="AQ1" t="s">
-        <v>233</v>
+        <v>193</v>
       </c>
       <c r="AR1" t="s">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="AS1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AU1" t="s">
         <v>28</v>
       </c>
-      <c r="AT1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AW1" t="s">
         <v>34</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AX1" t="s">
         <v>35</v>
       </c>
-      <c r="AW1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>41</v>
-      </c>
       <c r="AY1" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="C2">
         <v>100</v>
@@ -1561,13 +1442,13 @@
         <v>2</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="O2" s="13">
         <v>9780684812199</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" s="3">
@@ -1583,7 +1464,7 @@
         <v>9780306809330</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="Z2" s="4"/>
       <c r="AA2" s="5">
@@ -1595,25 +1476,26 @@
       <c r="AC2" s="5">
         <v>15</v>
       </c>
-      <c r="AH2" t="s">
-        <v>13</v>
+      <c r="AH2" t="str">
+        <f>"covers/" &amp; A2 &amp; ".jpg"</f>
+        <v>covers/chopin-in-paris.jpg</v>
       </c>
       <c r="AS2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT2" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV2" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="C3">
         <v>200</v>
@@ -1625,13 +1507,13 @@
         <v>4</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="O3" s="13">
         <v>9780312625924</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" s="3">
@@ -1647,7 +1529,7 @@
         <v>9780312625948</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="Z3" s="4"/>
       <c r="AA3" s="5">
@@ -1662,25 +1544,26 @@
       <c r="AG3" s="8">
         <v>9781429964395</v>
       </c>
-      <c r="AH3" t="s">
-        <v>14</v>
+      <c r="AH3" t="str">
+        <f t="shared" ref="AH3:AH46" si="0">"covers/" &amp; A3 &amp; ".jpg"</f>
+        <v>covers/peasant-prince.jpg</v>
       </c>
       <c r="AS3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="C4">
         <v>300</v>
@@ -1692,13 +1575,13 @@
         <v>6</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="O4" s="13">
         <v>9780008411251</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" s="3">
@@ -1714,7 +1597,7 @@
         <v>9780008521684</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="Z4" s="4"/>
       <c r="AA4" s="5">
@@ -1729,25 +1612,26 @@
       <c r="AG4" s="8">
         <v>9780008411275</v>
       </c>
-      <c r="AH4" t="s">
-        <v>20</v>
+      <c r="AH4" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/izabela-the-valiant.jpg</v>
       </c>
       <c r="AS4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="C5">
         <v>400</v>
@@ -1759,7 +1643,7 @@
         <v>8</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="I5" s="7">
         <v>44</v>
@@ -1777,7 +1661,7 @@
       <c r="Q5" s="2"/>
       <c r="X5" s="14"/>
       <c r="Y5" s="4" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="Z5" s="4"/>
       <c r="AA5" s="5">
@@ -1792,25 +1676,26 @@
       <c r="AG5" s="8">
         <v>9780300252224</v>
       </c>
-      <c r="AH5" t="s">
-        <v>15</v>
+      <c r="AH5" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/light-and-flame.jpg</v>
       </c>
       <c r="AS5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT5" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV5" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="C6">
         <v>500</v>
@@ -1822,7 +1707,7 @@
         <v>10</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="I6" s="7">
         <v>93</v>
@@ -1840,7 +1725,7 @@
       <c r="Q6" s="2"/>
       <c r="X6" s="14"/>
       <c r="Y6" s="4" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="Z6" s="4"/>
       <c r="AA6" s="5">
@@ -1855,25 +1740,26 @@
       <c r="AG6" s="8">
         <v>9781472816054</v>
       </c>
-      <c r="AH6" t="s">
-        <v>17</v>
+      <c r="AH6" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/trail-of-hope.jpg</v>
       </c>
       <c r="AS6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT6" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV6" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="C7">
         <v>600</v>
@@ -1885,16 +1771,16 @@
         <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="O7" s="15">
         <v>9781607720041</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="3">
@@ -1911,42 +1797,43 @@
       </c>
       <c r="Y7" s="4"/>
       <c r="Z7" s="4"/>
-      <c r="AH7" t="s">
-        <v>16</v>
+      <c r="AH7" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/303-squadron.jpg</v>
       </c>
       <c r="AS7" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT7" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV7" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C8">
         <v>150</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G8" s="6"/>
       <c r="O8" s="15"/>
       <c r="P8" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" s="3">
@@ -1962,7 +1849,7 @@
         <v>9781590173831</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="Z8" s="4"/>
       <c r="AA8" s="5">
@@ -1977,42 +1864,43 @@
       <c r="AG8" s="8">
         <v>9781590173848</v>
       </c>
-      <c r="AH8" t="s">
-        <v>59</v>
+      <c r="AH8" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/the-doll.jpg</v>
       </c>
       <c r="AS8" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT8" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV8" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C9">
         <v>250</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="E9" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="F9" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="G9" s="6"/>
       <c r="O9" s="15"/>
       <c r="P9" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" s="3">
@@ -2029,43 +1917,44 @@
       </c>
       <c r="Y9" s="4"/>
       <c r="Z9" s="4"/>
-      <c r="AH9" t="s">
-        <v>60</v>
+      <c r="AH9" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/the-peasants.jpg</v>
       </c>
       <c r="AS9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT9" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV9" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C10">
         <v>350</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G10" s="6"/>
-      <c r="H10" s="20"/>
+      <c r="H10" s="18"/>
       <c r="O10" s="15"/>
       <c r="P10" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="3">
@@ -2082,42 +1971,43 @@
       </c>
       <c r="Y10" s="4"/>
       <c r="Z10" s="4"/>
-      <c r="AH10" t="s">
-        <v>61</v>
+      <c r="AH10" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/pan-tadeusz.jpg</v>
       </c>
       <c r="AS10" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT10" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV10" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="C11">
         <v>450</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E11" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
       <c r="G11" s="6"/>
       <c r="O11" s="15"/>
       <c r="P11" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" s="3">
@@ -2134,40 +2024,41 @@
       </c>
       <c r="Y11" s="4"/>
       <c r="Z11" s="4"/>
-      <c r="AH11" t="s">
-        <v>65</v>
+      <c r="AH11" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/choucas.jpg</v>
       </c>
       <c r="AS11" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT11" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV11" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C12">
         <v>550</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E12" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F12" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="I12" s="7">
         <v>17.989999999999998</v>
@@ -2186,43 +2077,44 @@
       <c r="X12" s="14"/>
       <c r="Y12" s="4"/>
       <c r="Z12" s="4"/>
-      <c r="AH12" t="s">
-        <v>76</v>
+      <c r="AH12" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/desert-wilderness.jpg</v>
       </c>
       <c r="AS12" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT12" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV12" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B13" t="s">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="C13">
         <v>650</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E13" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F13" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="I13" s="7">
         <v>24</v>
@@ -2235,20 +2127,21 @@
       <c r="X13" s="14"/>
       <c r="Y13" s="4"/>
       <c r="Z13" s="4"/>
-      <c r="AH13" t="s">
-        <v>71</v>
+      <c r="AH13" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/forest-folk.jpg</v>
       </c>
       <c r="AS13" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT13" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV13" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="AX13" t="s">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="AY13">
         <v>1</v>
@@ -2256,27 +2149,27 @@
     </row>
     <row r="14" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="B14" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="C14">
         <v>100</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="E14" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="F14" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="G14" s="6"/>
       <c r="O14" s="15"/>
       <c r="P14" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" s="3">
@@ -2293,39 +2186,40 @@
       </c>
       <c r="Y14" s="4"/>
       <c r="Z14" s="4"/>
-      <c r="AH14" t="s">
-        <v>90</v>
+      <c r="AH14" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/castorp.jpg</v>
       </c>
       <c r="AS14" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT14" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV14" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="B15" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C15">
         <v>100</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="G15" s="6"/>
       <c r="O15" s="15"/>
       <c r="P15" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" s="3">
@@ -2342,39 +2236,40 @@
       </c>
       <c r="Y15" s="4"/>
       <c r="Z15" s="4"/>
-      <c r="AH15" t="s">
-        <v>87</v>
+      <c r="AH15" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/shah-of-shahs.jpg</v>
       </c>
       <c r="AS15" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT15" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV15" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="B16" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C16">
         <v>400</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="E16" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="G16" s="6"/>
       <c r="O16" s="15"/>
       <c r="P16" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="3">
@@ -2391,39 +2286,40 @@
       </c>
       <c r="Y16" s="4"/>
       <c r="Z16" s="4"/>
-      <c r="AH16" t="s">
-        <v>88</v>
+      <c r="AH16" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/the-emperor.jpg</v>
       </c>
       <c r="AS16" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT16" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV16" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="C17">
         <v>400</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="E17" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="G17" s="6"/>
       <c r="O17" s="15"/>
       <c r="P17" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" s="3">
@@ -2440,43 +2336,44 @@
       </c>
       <c r="Y17" s="4"/>
       <c r="Z17" s="4"/>
-      <c r="AH17" t="s">
-        <v>123</v>
+      <c r="AH17" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/another-day-of-life.jpg</v>
       </c>
       <c r="AS17" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT17" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV17" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="B18" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C18">
         <v>600</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="E18" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="F18" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="I18" s="7">
         <v>25</v>
@@ -2494,43 +2391,44 @@
       <c r="Q18" s="2"/>
       <c r="Y18" s="4"/>
       <c r="Z18" s="4"/>
-      <c r="AH18" t="s">
-        <v>103</v>
+      <c r="AH18" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/meeting-in-oea.jpg</v>
       </c>
       <c r="AS18" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT18" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV18" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C19">
         <v>800</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="F19" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="I19" s="7">
         <v>25</v>
@@ -2548,43 +2446,44 @@
       <c r="Q19" s="2"/>
       <c r="Y19" s="4"/>
       <c r="Z19" s="4"/>
-      <c r="AH19" t="s">
-        <v>102</v>
+      <c r="AH19" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/seven-against-thebes.jpg</v>
       </c>
       <c r="AS19" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT19" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV19" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="B20" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C20">
         <v>900</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="F20" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="I20" s="7">
         <v>27</v>
@@ -2602,43 +2501,44 @@
       <c r="Q20" s="2"/>
       <c r="Y20" s="4"/>
       <c r="Z20" s="4"/>
-      <c r="AH20" t="s">
-        <v>104</v>
+      <c r="AH20" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/emperor-julian.jpg</v>
       </c>
       <c r="AS20" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT20" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV20" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="C21">
         <v>1000</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>99</v>
+        <v>84</v>
       </c>
       <c r="E21" t="s">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="F21" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="I21" s="7">
         <v>25</v>
@@ -2656,42 +2556,43 @@
       <c r="Q21" s="2"/>
       <c r="Y21" s="4"/>
       <c r="Z21" s="4"/>
-      <c r="AH21" t="s">
-        <v>105</v>
+      <c r="AH21" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/last-olympiad.jpg</v>
       </c>
       <c r="AS21" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT21" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV21" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="B22" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="C22">
         <v>600</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="E22" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="F22" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="G22" s="6"/>
       <c r="O22" s="15"/>
       <c r="P22" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" s="3">
@@ -2708,42 +2609,43 @@
       </c>
       <c r="Y22" s="4"/>
       <c r="Z22" s="4"/>
-      <c r="AH22" t="s">
-        <v>113</v>
+      <c r="AH22" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/solaris.jpg</v>
       </c>
       <c r="AS22" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT22" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV22" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="C23">
         <v>200</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="E23" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="F23" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="G23" s="6"/>
       <c r="O23" s="15"/>
       <c r="P23" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" s="3">
@@ -2760,42 +2662,43 @@
       </c>
       <c r="Y23" s="4"/>
       <c r="Z23" s="4"/>
-      <c r="AH23" t="s">
-        <v>117</v>
+      <c r="AH23" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/fiasco.jpg</v>
       </c>
       <c r="AS23" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT23" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV23" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="24" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="B24" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="C24">
         <v>600</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="E24" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="F24" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G24" s="6"/>
       <c r="O24" s="15"/>
       <c r="P24" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" s="3">
@@ -2812,42 +2715,43 @@
       </c>
       <c r="Y24" s="4"/>
       <c r="Z24" s="4"/>
-      <c r="AH24" t="s">
-        <v>122</v>
+      <c r="AH24" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/the-invincible.jpg</v>
       </c>
       <c r="AS24" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT24" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV24" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>140</v>
+        <v>112</v>
       </c>
       <c r="B25" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="C25">
         <v>100</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="E25" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F25" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G25" s="6"/>
       <c r="O25" s="15"/>
       <c r="P25" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" s="3">
@@ -2864,20 +2768,21 @@
       </c>
       <c r="Y25" s="4"/>
       <c r="Z25" s="4"/>
-      <c r="AH25" t="s">
-        <v>120</v>
+      <c r="AH25" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/chahary.jpg</v>
       </c>
       <c r="AS25" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT25" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV25" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="AX25" t="s">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="AY25">
         <v>4</v>
@@ -2885,28 +2790,28 @@
     </row>
     <row r="26" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="B26" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="C26">
         <v>100</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>129</v>
+        <v>105</v>
       </c>
       <c r="E26" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="F26" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="I26" s="7">
         <v>24</v>
@@ -2924,58 +2829,59 @@
       <c r="Q26" s="2"/>
       <c r="Y26" s="4"/>
       <c r="Z26" s="4"/>
-      <c r="AH26" t="s">
-        <v>132</v>
+      <c r="AH26" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/melicles.jpg</v>
       </c>
       <c r="AN26" s="12" t="s">
-        <v>236</v>
+        <v>196</v>
       </c>
       <c r="AO26" t="s">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="AP26" t="s">
-        <v>239</v>
+        <v>199</v>
       </c>
       <c r="AQ26" t="s">
-        <v>238</v>
+        <v>198</v>
       </c>
       <c r="AR26" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="AS26" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT26" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV26" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="27" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="B27" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="C27">
         <v>600</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>130</v>
+        <v>106</v>
       </c>
       <c r="E27" t="s">
-        <v>131</v>
+        <v>107</v>
       </c>
       <c r="F27" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="I27" s="7">
         <v>24</v>
@@ -2993,43 +2899,44 @@
       <c r="Q27" s="2"/>
       <c r="Y27" s="4"/>
       <c r="Z27" s="4"/>
-      <c r="AH27" t="s">
-        <v>133</v>
+      <c r="AH27" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/diossos.jpg</v>
       </c>
       <c r="AS27" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT27" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV27" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="28" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>138</v>
+        <v>111</v>
       </c>
       <c r="B28" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="C28">
         <v>100</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="E28" t="s">
         <v>12</v>
       </c>
       <c r="F28" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="I28" s="7">
         <v>21</v>
@@ -3047,20 +2954,21 @@
       <c r="Q28" s="2"/>
       <c r="Y28" s="4"/>
       <c r="Z28" s="4"/>
-      <c r="AH28" t="s">
-        <v>139</v>
+      <c r="AH28" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/white-jaguar-1.jpg</v>
       </c>
       <c r="AS28" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT28" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV28" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="AX28" t="s">
-        <v>135</v>
+        <v>109</v>
       </c>
       <c r="AY28">
         <v>1</v>
@@ -3068,28 +2976,28 @@
     </row>
     <row r="29" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>136</v>
+        <v>110</v>
       </c>
       <c r="B29" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="C29">
         <v>200</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="E29" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="F29" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="I29" s="7">
         <v>21</v>
@@ -3107,20 +3015,21 @@
       <c r="Q29" s="2"/>
       <c r="Y29" s="4"/>
       <c r="Z29" s="4"/>
-      <c r="AH29" t="s">
-        <v>137</v>
+      <c r="AH29" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/ships-minos-1.jpg</v>
       </c>
       <c r="AS29" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT29" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV29" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="AX29" t="s">
-        <v>134</v>
+        <v>108</v>
       </c>
       <c r="AY29">
         <v>1</v>
@@ -3128,28 +3037,28 @@
     </row>
     <row r="30" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>151</v>
+        <v>123</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C30">
         <v>250</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>148</v>
+        <v>120</v>
       </c>
       <c r="E30" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="F30" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="I30" s="7">
         <v>24</v>
@@ -3158,10 +3067,10 @@
         <v>9789998793781</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="R30" s="3">
         <v>16</v>
@@ -3170,10 +3079,10 @@
         <v>9789998793774</v>
       </c>
       <c r="Y30" s="4" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="Z30" s="4" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="AA30" s="5">
         <v>10</v>
@@ -3181,20 +3090,21 @@
       <c r="AG30" s="8">
         <v>9789998793750</v>
       </c>
-      <c r="AH30" t="s">
-        <v>154</v>
+      <c r="AH30" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/divine-julius.jpg</v>
       </c>
       <c r="AS30" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT30" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV30" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="AX30" t="s">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="AY30">
         <v>1</v>
@@ -3202,28 +3112,28 @@
     </row>
     <row r="31" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>152</v>
+        <v>124</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C31">
         <v>450</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="E31" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="F31" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="I31" s="7">
         <v>25</v>
@@ -3232,10 +3142,10 @@
         <v>9782919820047</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="R31" s="3">
         <v>17</v>
@@ -3244,10 +3154,10 @@
         <v>9782919820054</v>
       </c>
       <c r="Y31" s="4" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="Z31" s="4" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="AA31" s="5">
         <v>10</v>
@@ -3255,20 +3165,21 @@
       <c r="AG31" s="8">
         <v>9782919820016</v>
       </c>
-      <c r="AH31" t="s">
-        <v>206</v>
+      <c r="AH31" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/naso-the-poet.jpg</v>
       </c>
       <c r="AS31" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT31" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV31" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="AX31" t="s">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="AY31">
         <v>2</v>
@@ -3276,28 +3187,28 @@
     </row>
     <row r="32" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C32">
         <v>650</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="E32" t="s">
-        <v>147</v>
+        <v>119</v>
       </c>
       <c r="F32" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="I32" s="7">
         <v>32</v>
@@ -3306,10 +3217,10 @@
         <v>9782919820467</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="R32" s="3">
         <v>18</v>
@@ -3319,20 +3230,21 @@
       </c>
       <c r="Y32" s="4"/>
       <c r="Z32" s="4"/>
-      <c r="AH32" t="s">
-        <v>155</v>
+      <c r="AH32" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/tiberius-caesar.jpg</v>
       </c>
       <c r="AS32" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT32" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV32" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="AX32" t="s">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="AY32">
         <v>3</v>
@@ -3340,26 +3252,26 @@
     </row>
     <row r="33" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>188</v>
+        <v>158</v>
       </c>
       <c r="B33" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="C33">
         <v>100</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="E33" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="G33" s="6"/>
       <c r="P33" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="R33" s="3">
         <v>14</v>
@@ -3369,40 +3281,41 @@
       </c>
       <c r="Y33" s="4"/>
       <c r="Z33" s="4"/>
-      <c r="AH33" t="s">
-        <v>190</v>
+      <c r="AH33" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/milosz-selected-and-last-poems.jpg</v>
       </c>
       <c r="AS33" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT33" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV33" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>193</v>
+        <v>162</v>
       </c>
       <c r="B34" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="C34">
         <v>200</v>
       </c>
       <c r="D34" t="s">
-        <v>191</v>
+        <v>160</v>
       </c>
       <c r="E34" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>192</v>
+        <v>161</v>
       </c>
       <c r="I34" s="7">
         <v>38</v>
@@ -3411,10 +3324,10 @@
         <v>9780151003532</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="R34" s="3">
         <v>11</v>
@@ -3424,41 +3337,42 @@
       </c>
       <c r="Y34" s="4"/>
       <c r="Z34" s="4"/>
-      <c r="AH34" t="s">
-        <v>194</v>
+      <c r="AH34" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/poems-new-and-szymborska.jpg</v>
       </c>
       <c r="AS34" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT34" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV34" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="35" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>197</v>
+        <v>165</v>
       </c>
       <c r="B35" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="C35">
         <v>300</v>
       </c>
       <c r="D35" t="s">
-        <v>195</v>
+        <v>163</v>
       </c>
       <c r="E35" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="G35" s="6"/>
       <c r="P35" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>196</v>
+        <v>164</v>
       </c>
       <c r="R35" s="3">
         <v>18</v>
@@ -3468,41 +3382,42 @@
       </c>
       <c r="Y35" s="4"/>
       <c r="Z35" s="4"/>
-      <c r="AH35" t="s">
-        <v>198</v>
+      <c r="AH35" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/poems-herbert.jpg</v>
       </c>
       <c r="AS35" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT35" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV35" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>182</v>
+        <v>152</v>
       </c>
       <c r="B36" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="C36">
         <v>400</v>
       </c>
       <c r="D36" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="E36" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="G36" s="6"/>
       <c r="P36" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="R36" s="3">
         <v>15</v>
@@ -3512,43 +3427,44 @@
       </c>
       <c r="Y36" s="4"/>
       <c r="Z36" s="4"/>
-      <c r="AH36" t="s">
-        <v>199</v>
+      <c r="AH36" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/without-end.jpg</v>
       </c>
       <c r="AS36" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT36" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV36" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="37" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>183</v>
+        <v>153</v>
       </c>
       <c r="B37" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="C37">
         <v>600</v>
       </c>
       <c r="D37" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="E37" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="F37" t="s">
-        <v>201</v>
+        <v>166</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="I37" s="7">
         <v>16</v>
@@ -3557,7 +3473,7 @@
         <v>9780393067798</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" s="3">
@@ -3568,40 +3484,41 @@
       </c>
       <c r="Y37" s="4"/>
       <c r="Z37" s="4"/>
-      <c r="AH37" t="s">
-        <v>200</v>
+      <c r="AH37" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/sobbing-superpower.jpg</v>
       </c>
       <c r="AS37" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT37" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV37" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>184</v>
+        <v>154</v>
       </c>
       <c r="B38" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="C38">
         <v>700</v>
       </c>
       <c r="D38" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="E38" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="I38" s="7">
         <v>30</v>
@@ -3610,7 +3527,7 @@
         <v>9780544126022</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" s="3">
@@ -3621,43 +3538,44 @@
       </c>
       <c r="Y38" s="4"/>
       <c r="Z38" s="4"/>
-      <c r="AH38" t="s">
-        <v>204</v>
+      <c r="AH38" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/map-collected-and-last.jpg</v>
       </c>
       <c r="AS38" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT38" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV38" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="39" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="B39" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="C39">
         <v>800</v>
       </c>
       <c r="D39" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="F39" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="I39" s="7">
         <v>25</v>
@@ -3666,7 +3584,7 @@
         <v>9788367602488</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" s="3">
@@ -3677,38 +3595,39 @@
       </c>
       <c r="Y39" s="4"/>
       <c r="Z39" s="4"/>
-      <c r="AH39" t="s">
-        <v>202</v>
+      <c r="AH39" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/from-tree-of-knowledge.jpg</v>
       </c>
       <c r="AS39" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT39" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV39" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="40" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>186</v>
+        <v>156</v>
       </c>
       <c r="B40" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="C40">
         <v>900</v>
       </c>
       <c r="D40" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="E40" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="G40" s="6"/>
       <c r="P40" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" s="3">
@@ -3719,41 +3638,42 @@
       </c>
       <c r="Y40" s="4"/>
       <c r="Z40" s="4"/>
-      <c r="AH40" t="s">
-        <v>205</v>
+      <c r="AH40" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/krzysztof-kamil-baczynski .jpg</v>
       </c>
       <c r="AS40" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT40" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV40" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="41" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>187</v>
+        <v>157</v>
       </c>
       <c r="B41" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="C41">
         <v>1000</v>
       </c>
       <c r="D41" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="E41" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="F41" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="G41" s="6"/>
       <c r="P41" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" s="3">
@@ -3764,43 +3684,44 @@
       </c>
       <c r="Y41" s="4"/>
       <c r="Z41" s="4"/>
-      <c r="AH41" t="s">
-        <v>203</v>
+      <c r="AH41" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/white-magic-baczynski.jpg</v>
       </c>
       <c r="AS41" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT41" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV41" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="42" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>254</v>
+        <v>214</v>
       </c>
       <c r="B42" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="C42">
         <v>1100</v>
       </c>
       <c r="D42" t="s">
-        <v>255</v>
+        <v>215</v>
       </c>
       <c r="E42" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="F42" t="s">
-        <v>256</v>
+        <v>216</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="I42" s="7">
         <v>19</v>
@@ -3809,7 +3730,7 @@
         <v>9788367602426</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" s="3">
@@ -3821,43 +3742,43 @@
       <c r="Y42" s="4"/>
       <c r="Z42" s="4"/>
       <c r="AH42" t="str">
-        <f>"covers/" &amp; A42</f>
-        <v>covers/new-poems-ukr-po</v>
+        <f t="shared" si="0"/>
+        <v>covers/new-poems-ukr-po.jpg</v>
       </c>
       <c r="AN42" s="12" t="s">
-        <v>257</v>
+        <v>217</v>
       </c>
       <c r="AS42" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT42" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV42" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>246</v>
+        <v>206</v>
       </c>
       <c r="B43" t="s">
-        <v>124</v>
+        <v>218</v>
       </c>
       <c r="D43" t="s">
-        <v>242</v>
+        <v>202</v>
       </c>
       <c r="E43" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="F43" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="I43" s="7">
         <v>26</v>
@@ -3866,7 +3787,7 @@
         <v>9782919820863</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="R43" s="3">
         <v>13</v>
@@ -3875,10 +3796,10 @@
         <v>9782919820856</v>
       </c>
       <c r="Y43" s="4" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="Z43" s="4" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="AA43" s="5">
         <v>2.99</v>
@@ -3887,43 +3808,43 @@
         <v>9782919820849</v>
       </c>
       <c r="AH43" t="str">
-        <f>"covers/" &amp; A43</f>
-        <v>covers/wheels-templars</v>
+        <f t="shared" si="0"/>
+        <v>covers/wheels-templars.jpg</v>
       </c>
       <c r="AN43" s="12" t="s">
-        <v>251</v>
+        <v>211</v>
       </c>
       <c r="AS43" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT43" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV43" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="44" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>249</v>
+        <v>209</v>
       </c>
       <c r="B44" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="D44" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="E44" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="F44" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="I44" s="7">
         <v>25</v>
@@ -3932,7 +3853,7 @@
         <v>9782919840014</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="R44" s="3">
         <v>17</v>
@@ -3941,10 +3862,10 @@
         <v>9782919840021</v>
       </c>
       <c r="Y44" s="4" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="Z44" s="4" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="AA44" s="5">
         <v>9.99</v>
@@ -3953,43 +3874,43 @@
         <v>9782919840038</v>
       </c>
       <c r="AH44" t="str">
-        <f t="shared" ref="AH44:AH46" si="0">"covers/" &amp; A44</f>
-        <v>covers/wheels-mysteries</v>
+        <f t="shared" si="0"/>
+        <v>covers/wheels-mysteries.jpg</v>
       </c>
       <c r="AN44" s="12" t="s">
-        <v>253</v>
+        <v>213</v>
       </c>
       <c r="AS44" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT44" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV44" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>248</v>
+        <v>208</v>
       </c>
       <c r="B45" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="D45" t="s">
-        <v>245</v>
+        <v>205</v>
       </c>
       <c r="E45" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="F45" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="I45" s="7">
         <v>25</v>
@@ -3998,7 +3919,7 @@
         <v>9782919820955</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="R45" s="3">
         <v>15</v>
@@ -4007,10 +3928,10 @@
         <v>9782919820948</v>
       </c>
       <c r="Y45" s="4" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="Z45" s="4" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="AA45" s="5">
         <v>9.99</v>
@@ -4020,42 +3941,42 @@
       </c>
       <c r="AH45" t="str">
         <f t="shared" si="0"/>
-        <v>covers/wheels-bandits</v>
+        <v>covers/wheels-bandits.jpg</v>
       </c>
       <c r="AN45" s="12" t="s">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="AS45" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT45" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV45" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="46" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>247</v>
+        <v>207</v>
       </c>
       <c r="B46" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="D46" t="s">
-        <v>244</v>
+        <v>204</v>
       </c>
       <c r="E46" t="s">
-        <v>241</v>
+        <v>201</v>
       </c>
       <c r="F46" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="I46" s="7">
         <v>25</v>
@@ -4064,7 +3985,7 @@
         <v>9782919820917</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>145</v>
+        <v>117</v>
       </c>
       <c r="R46" s="3">
         <v>13</v>
@@ -4073,10 +3994,10 @@
         <v>9782919820900</v>
       </c>
       <c r="Y46" s="4" t="s">
-        <v>146</v>
+        <v>118</v>
       </c>
       <c r="Z46" s="4" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="AA46" s="5">
         <v>9.99</v>
@@ -4086,125 +4007,125 @@
       </c>
       <c r="AH46" t="str">
         <f t="shared" si="0"/>
-        <v>covers/wheels-copernicus</v>
-      </c>
-      <c r="AN46" s="19" t="s">
-        <v>252</v>
+        <v>covers/wheels-copernicus.jpg</v>
+      </c>
+      <c r="AN46" s="1" t="s">
+        <v>212</v>
       </c>
       <c r="AS46" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AT46" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="AV46" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="47" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="AN47" s="16"/>
+      <c r="AN47"/>
     </row>
     <row r="48" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="AN48" s="18"/>
+      <c r="AN48" s="17"/>
     </row>
     <row r="49" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN49" s="16"/>
+      <c r="AN49"/>
     </row>
     <row r="50" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN50" s="17"/>
+      <c r="AN50" s="16"/>
     </row>
     <row r="51" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN51" s="16"/>
+      <c r="AN51"/>
     </row>
     <row r="52" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN52" s="19"/>
+      <c r="AN52" s="1"/>
     </row>
     <row r="53" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN53" s="16"/>
+      <c r="AN53"/>
     </row>
     <row r="54" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN54" s="19"/>
+      <c r="AN54" s="1"/>
     </row>
     <row r="55" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN55" s="16"/>
+      <c r="AN55"/>
     </row>
     <row r="56" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN56" s="19"/>
+      <c r="AN56" s="1"/>
     </row>
     <row r="57" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN57" s="16"/>
+      <c r="AN57"/>
     </row>
     <row r="58" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN58" s="19"/>
+      <c r="AN58" s="1"/>
     </row>
     <row r="59" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN59" s="17"/>
+      <c r="AN59" s="16"/>
     </row>
     <row r="60" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN60" s="17"/>
+      <c r="AN60" s="16"/>
     </row>
     <row r="76" spans="23:40" x14ac:dyDescent="0.25">
       <c r="W76" s="9"/>
       <c r="AF76" s="8"/>
       <c r="AG76" s="5"/>
       <c r="AM76" s="12"/>
-      <c r="AN76" s="16"/>
+      <c r="AN76"/>
     </row>
     <row r="77" spans="23:40" x14ac:dyDescent="0.25">
       <c r="W77" s="9"/>
       <c r="AF77" s="8"/>
       <c r="AG77" s="5"/>
       <c r="AM77" s="12"/>
-      <c r="AN77" s="16"/>
+      <c r="AN77"/>
     </row>
     <row r="78" spans="23:40" x14ac:dyDescent="0.25">
       <c r="W78" s="9"/>
       <c r="AF78" s="8"/>
       <c r="AG78" s="5"/>
       <c r="AM78" s="12"/>
-      <c r="AN78" s="16"/>
+      <c r="AN78"/>
     </row>
     <row r="79" spans="23:40" x14ac:dyDescent="0.25">
       <c r="W79" s="9"/>
       <c r="AF79" s="8"/>
       <c r="AG79" s="5"/>
       <c r="AM79" s="12"/>
-      <c r="AN79" s="16"/>
+      <c r="AN79"/>
     </row>
     <row r="80" spans="23:40" x14ac:dyDescent="0.25">
       <c r="W80" s="9"/>
       <c r="AF80" s="8"/>
       <c r="AG80" s="5"/>
       <c r="AM80" s="12"/>
-      <c r="AN80" s="16"/>
+      <c r="AN80"/>
     </row>
     <row r="81" spans="23:40" x14ac:dyDescent="0.25">
       <c r="W81" s="9"/>
       <c r="AF81" s="8"/>
       <c r="AG81" s="5"/>
       <c r="AM81" s="12"/>
-      <c r="AN81" s="16"/>
+      <c r="AN81"/>
     </row>
     <row r="82" spans="23:40" x14ac:dyDescent="0.25">
       <c r="W82" s="9"/>
       <c r="AF82" s="8"/>
       <c r="AG82" s="5"/>
       <c r="AM82" s="12"/>
-      <c r="AN82" s="16"/>
+      <c r="AN82"/>
     </row>
     <row r="83" spans="23:40" x14ac:dyDescent="0.25">
       <c r="W83" s="9"/>
       <c r="AF83" s="8"/>
       <c r="AG83" s="5"/>
       <c r="AM83" s="12"/>
-      <c r="AN83" s="16"/>
+      <c r="AN83"/>
     </row>
     <row r="84" spans="23:40" x14ac:dyDescent="0.25">
       <c r="W84" s="9"/>
       <c r="AF84" s="8"/>
       <c r="AG84" s="5"/>
       <c r="AM84" s="12"/>
-      <c r="AN84" s="16"/>
+      <c r="AN84"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/bookstore-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="258" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{932F48F3-90D3-474A-9A59-99570B0BC66F}"/>
+  <xr:revisionPtr revIDLastSave="263" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D079A16E-A63C-44EB-8643-9BF9690127A5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
@@ -506,9 +506,6 @@
     <t>from-tree-of-knowledge</t>
   </si>
   <si>
-    <t xml:space="preserve">krzysztof-kamil-baczynski </t>
-  </si>
-  <si>
     <t>white-magic-baczynski</t>
   </si>
   <si>
@@ -754,6 +751,9 @@
   </si>
   <si>
     <t>Fiction; Books in Focus; Young Adult</t>
+  </si>
+  <si>
+    <t>krzysztof-kamil-baczynski</t>
   </si>
 </sst>
 </file>
@@ -1275,7 +1275,7 @@
         <v>13</v>
       </c>
       <c r="B1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C1" t="s">
         <v>37</v>
@@ -1293,82 +1293,82 @@
         <v>113</v>
       </c>
       <c r="H1" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="O1" s="13" t="s">
         <v>173</v>
-      </c>
-      <c r="O1" s="13" t="s">
-        <v>174</v>
       </c>
       <c r="P1" s="2" t="s">
         <v>114</v>
       </c>
       <c r="Q1" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="R1" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="9" t="s">
         <v>181</v>
-      </c>
-      <c r="X1" s="9" t="s">
-        <v>182</v>
       </c>
       <c r="Y1" s="4" t="s">
         <v>115</v>
       </c>
       <c r="Z1" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="AA1" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AB1" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AC1" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AD1" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="AD1" s="5" t="s">
+      <c r="AE1" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="AE1" s="5" t="s">
+      <c r="AF1" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AG1" s="8" t="s">
         <v>189</v>
-      </c>
-      <c r="AG1" s="8" t="s">
-        <v>190</v>
       </c>
       <c r="AH1" t="s">
         <v>0</v>
@@ -1392,16 +1392,16 @@
         <v>27</v>
       </c>
       <c r="AO1" t="s">
+        <v>191</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>193</v>
+      </c>
+      <c r="AQ1" t="s">
         <v>192</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>194</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>193</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>195</v>
       </c>
       <c r="AS1" t="s">
         <v>22</v>
@@ -2834,19 +2834,19 @@
         <v>covers/melicles.jpg</v>
       </c>
       <c r="AN26" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="AO26" t="s">
         <v>196</v>
       </c>
-      <c r="AO26" t="s">
+      <c r="AP26" t="s">
+        <v>198</v>
+      </c>
+      <c r="AQ26" t="s">
         <v>197</v>
       </c>
-      <c r="AP26" t="s">
+      <c r="AR26" t="s">
         <v>199</v>
-      </c>
-      <c r="AQ26" t="s">
-        <v>198</v>
-      </c>
-      <c r="AR26" t="s">
-        <v>200</v>
       </c>
       <c r="AS26" t="s">
         <v>23</v>
@@ -3252,7 +3252,7 @@
     </row>
     <row r="33" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B33" t="s">
         <v>131</v>
@@ -3261,7 +3261,7 @@
         <v>100</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="E33" t="s">
         <v>132</v>
@@ -3297,7 +3297,7 @@
     </row>
     <row r="34" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B34" t="s">
         <v>131</v>
@@ -3306,7 +3306,7 @@
         <v>200</v>
       </c>
       <c r="D34" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E34" t="s">
         <v>134</v>
@@ -3315,7 +3315,7 @@
         <v>116</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I34" s="7">
         <v>38</v>
@@ -3353,7 +3353,7 @@
     </row>
     <row r="35" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B35" t="s">
         <v>131</v>
@@ -3362,7 +3362,7 @@
         <v>300</v>
       </c>
       <c r="D35" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E35" t="s">
         <v>137</v>
@@ -3372,7 +3372,7 @@
         <v>117</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="R35" s="3">
         <v>18</v>
@@ -3458,7 +3458,7 @@
         <v>141</v>
       </c>
       <c r="F37" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="G37" s="6" t="s">
         <v>116</v>
@@ -3611,7 +3611,7 @@
     </row>
     <row r="40" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>156</v>
+        <v>218</v>
       </c>
       <c r="B40" t="s">
         <v>131</v>
@@ -3640,7 +3640,7 @@
       <c r="Z40" s="4"/>
       <c r="AH40" t="str">
         <f t="shared" si="0"/>
-        <v>covers/krzysztof-kamil-baczynski .jpg</v>
+        <v>covers/krzysztof-kamil-baczynski.jpg</v>
       </c>
       <c r="AS40" t="s">
         <v>23</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="41" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B41" t="s">
         <v>131</v>
@@ -3700,7 +3700,7 @@
     </row>
     <row r="42" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B42" t="s">
         <v>131</v>
@@ -3709,13 +3709,13 @@
         <v>1100</v>
       </c>
       <c r="D42" t="s">
+        <v>214</v>
+      </c>
+      <c r="E42" t="s">
         <v>215</v>
       </c>
-      <c r="E42" t="s">
-        <v>216</v>
-      </c>
       <c r="F42" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>116</v>
@@ -3746,7 +3746,7 @@
         <v>covers/new-poems-ukr-po.jpg</v>
       </c>
       <c r="AN42" s="12" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AS42" t="s">
         <v>23</v>
@@ -3760,16 +3760,19 @@
     </row>
     <row r="43" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B43" t="s">
-        <v>218</v>
+        <v>217</v>
+      </c>
+      <c r="C43">
+        <v>1000</v>
       </c>
       <c r="D43" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E43" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F43" t="s">
         <v>60</v>
@@ -3812,7 +3815,7 @@
         <v>covers/wheels-templars.jpg</v>
       </c>
       <c r="AN43" s="12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AS43" t="s">
         <v>23</v>
@@ -3826,16 +3829,19 @@
     </row>
     <row r="44" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B44" t="s">
         <v>103</v>
       </c>
+      <c r="C44">
+        <v>1100</v>
+      </c>
       <c r="D44" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E44" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F44" t="s">
         <v>60</v>
@@ -3878,7 +3884,7 @@
         <v>covers/wheels-mysteries.jpg</v>
       </c>
       <c r="AN44" s="12" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AS44" t="s">
         <v>23</v>
@@ -3892,16 +3898,19 @@
     </row>
     <row r="45" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B45" t="s">
         <v>103</v>
       </c>
+      <c r="C45">
+        <v>1200</v>
+      </c>
       <c r="D45" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E45" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F45" t="s">
         <v>60</v>
@@ -3944,7 +3953,7 @@
         <v>covers/wheels-bandits.jpg</v>
       </c>
       <c r="AN45" s="12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AS45" t="s">
         <v>23</v>
@@ -3958,16 +3967,19 @@
     </row>
     <row r="46" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B46" t="s">
         <v>103</v>
       </c>
+      <c r="C46">
+        <v>1300</v>
+      </c>
       <c r="D46" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="E46" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F46" t="s">
         <v>60</v>
@@ -4010,7 +4022,7 @@
         <v>covers/wheels-copernicus.jpg</v>
       </c>
       <c r="AN46" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AS46" t="s">
         <v>23</v>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/bookstore-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="289" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49DF3B1E-268B-47F8-9C42-D5DE3562E33E}"/>
+  <xr:revisionPtr revIDLastSave="296" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D93F0656-A899-4977-A3E0-928BBD6E0FE6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
+    <workbookView xWindow="3060" yWindow="570" windowWidth="23220" windowHeight="14940" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="219">
   <si>
     <t>cover</t>
   </si>
@@ -743,6 +743,12 @@
 &lt;p&gt; They slip their jailors in Carthage and rush across the Mediterranean pursued by enemy agents and assassins: a mysterious oriental priest and his Greek apprentice. Their mission: to prevent the outbreak of a civil war in Egypt. Their opponents: the Great Phoenician Council and the entire state apparatus of Eternal Egypt. Their resources: the old man's wit and the young man's courage.&lt;/p&gt;
 &lt;p&gt;A classic tale of high adventure, full of white-knuckle twists and turns, engaging characters, and sparkling humor. A European best-seller since 1946 now beautifully translated into English. If you liked &lt;em&gt;The Treasure Island&lt;/em&gt; and &lt;em&gt;The Three Musketeers&lt;/em&gt;, you will love this.&lt;/p&gt;
 &lt;p&gt;&lt;strong&gt;Get whisked off into the exotic, exciting world of classical antiquity! Pick up your copy today!&lt;/strong&gt;&lt;/P&gt;</t>
+  </si>
+  <si>
+    <t>praise_1_source</t>
+  </si>
+  <si>
+    <t>praise_2_source</t>
   </si>
 </sst>
 </file>
@@ -1395,13 +1401,13 @@
         <v>214</v>
       </c>
       <c r="AP1" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="AQ1" t="s">
         <v>215</v>
       </c>
       <c r="AR1" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AS1" t="s">
         <v>22</v>
@@ -2845,8 +2851,22 @@
       <c r="O26" s="14">
         <v>9789998791671</v>
       </c>
-      <c r="P26" s="2"/>
+      <c r="P26" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="Q26" s="2"/>
+      <c r="R26" s="3">
+        <v>17</v>
+      </c>
+      <c r="S26" s="3">
+        <v>16</v>
+      </c>
+      <c r="T26" s="3">
+        <v>15</v>
+      </c>
+      <c r="X26" s="18">
+        <v>9789998791664</v>
+      </c>
       <c r="Y26" s="4"/>
       <c r="Z26" s="4"/>
       <c r="AH26" t="str">

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/bookstore-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="296" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D93F0656-A899-4977-A3E0-928BBD6E0FE6}"/>
+  <xr:revisionPtr revIDLastSave="299" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55E36C77-DA34-4B59-A176-A6300FAD9504}"/>
   <bookViews>
     <workbookView xWindow="3060" yWindow="570" windowWidth="23220" windowHeight="14940" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="219">
   <si>
     <t>cover</t>
   </si>
@@ -611,16 +611,7 @@
     <t>shelves</t>
   </si>
   <si>
-    <t>The best historical adventure series of the interwar period</t>
-  </si>
-  <si>
-    <t>This is literature how it should be written regardless of genre! I absolutely love it!</t>
-  </si>
-  <si>
     <t>Czesław Miłosz, Literature Nobel Prize 1980</t>
-  </si>
-  <si>
-    <t>Michelle Jacqueline Miller, author of Fire in Erebus</t>
   </si>
   <si>
     <t>Zbigniew Nienacki</t>
@@ -749,6 +740,15 @@
   </si>
   <si>
     <t>praise_2_source</t>
+  </si>
+  <si>
+    <t>"The best historical adventure series of the interwar period."</t>
+  </si>
+  <si>
+    <t>"This is literature how it should be written regardless of genre! I absolutely loved it!"</t>
+  </si>
+  <si>
+    <t>Michelle Jacqueline Miller, author of "Fire in Erebus"</t>
   </si>
 </sst>
 </file>
@@ -1398,16 +1398,16 @@
         <v>27</v>
       </c>
       <c r="AO1" t="s">
+        <v>211</v>
+      </c>
+      <c r="AP1" t="s">
         <v>214</v>
       </c>
-      <c r="AP1" t="s">
-        <v>217</v>
-      </c>
       <c r="AQ1" t="s">
+        <v>212</v>
+      </c>
+      <c r="AR1" t="s">
         <v>215</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>218</v>
       </c>
       <c r="AS1" t="s">
         <v>22</v>
@@ -2874,19 +2874,19 @@
         <v>covers/melicles.jpg</v>
       </c>
       <c r="AN26" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="AO26" t="s">
         <v>216</v>
       </c>
-      <c r="AO26" t="s">
+      <c r="AP26" t="s">
         <v>191</v>
       </c>
-      <c r="AP26" t="s">
-        <v>193</v>
-      </c>
       <c r="AQ26" t="s">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="AR26" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="AS26" t="s">
         <v>23</v>
@@ -3651,7 +3651,7 @@
     </row>
     <row r="40" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B40" t="s">
         <v>131</v>
@@ -3740,7 +3740,7 @@
     </row>
     <row r="42" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B42" t="s">
         <v>131</v>
@@ -3749,13 +3749,13 @@
         <v>1100</v>
       </c>
       <c r="D42" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="E42" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="F42" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="G42" s="6" t="s">
         <v>116</v>
@@ -3786,7 +3786,7 @@
         <v>covers/new-poems-ukr-po.jpg</v>
       </c>
       <c r="AN42" s="12" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AS42" t="s">
         <v>23</v>
@@ -3800,19 +3800,19 @@
     </row>
     <row r="43" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B43" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C43">
         <v>1000</v>
       </c>
       <c r="D43" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="E43" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F43" t="s">
         <v>60</v>
@@ -3855,7 +3855,7 @@
         <v>covers/wheels-templars.jpg</v>
       </c>
       <c r="AN43" s="12" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="AS43" t="s">
         <v>23</v>
@@ -3869,7 +3869,7 @@
     </row>
     <row r="44" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="B44" t="s">
         <v>103</v>
@@ -3878,10 +3878,10 @@
         <v>1100</v>
       </c>
       <c r="D44" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E44" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F44" t="s">
         <v>60</v>
@@ -3924,7 +3924,7 @@
         <v>covers/wheels-mysteries.jpg</v>
       </c>
       <c r="AN44" s="12" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="AS44" t="s">
         <v>23</v>
@@ -3938,7 +3938,7 @@
     </row>
     <row r="45" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="B45" t="s">
         <v>103</v>
@@ -3947,10 +3947,10 @@
         <v>1200</v>
       </c>
       <c r="D45" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E45" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F45" t="s">
         <v>60</v>
@@ -3993,7 +3993,7 @@
         <v>covers/wheels-bandits.jpg</v>
       </c>
       <c r="AN45" s="12" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="AS45" t="s">
         <v>23</v>
@@ -4007,7 +4007,7 @@
     </row>
     <row r="46" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="B46" t="s">
         <v>103</v>
@@ -4016,10 +4016,10 @@
         <v>1300</v>
       </c>
       <c r="D46" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="E46" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F46" t="s">
         <v>60</v>
@@ -4062,7 +4062,7 @@
         <v>covers/wheels-copernicus.jpg</v>
       </c>
       <c r="AN46" s="1" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="AS46" t="s">
         <v>23</v>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/bookstore-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="299" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{55E36C77-DA34-4B59-A176-A6300FAD9504}"/>
+  <xr:revisionPtr revIDLastSave="317" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B84445C0-FF2B-46EF-A641-88349A937EC2}"/>
   <bookViews>
-    <workbookView xWindow="3060" yWindow="570" windowWidth="23220" windowHeight="14940" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1044" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="225">
   <si>
     <t>cover</t>
   </si>
@@ -749,6 +749,29 @@
   </si>
   <si>
     <t>Michelle Jacqueline Miller, author of "Fire in Erebus"</t>
+  </si>
+  <si>
+    <t>cold-sea</t>
+  </si>
+  <si>
+    <t>Cold Sea Stories</t>
+  </si>
+  <si>
+    <t>Paweł Huelle</t>
+  </si>
+  <si>
+    <t>eBook</t>
+  </si>
+  <si>
+    <t>Comma Press</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;A student pedals an old Ukraina bicycle between striking factories, delivering bulletins, in the tumultuous first days of the Solidarity movement...&lt;/p&gt;
+&lt;p&gt;A shepherd watches, unseen, as a strange figure disembarks from a pirate ship anchored in the cove below, to bury a chest on the beach that later proves empty…&lt;/p&gt;
+&lt;p&gt;A prisoner in a Berber dungeon recounts his life’s story – the failed pursuit of the world’s very first language – by scrawling in the sand on his cell floor…&lt;/p&gt;
+&lt;p&gt;The characters in Pawel Huelle’s mesmerising stories find themselves, willingly or not, at the heart of epic narratives; legends and histories that stretch far beyond the limits of their own lives. Against the backdrop of the Baltic coast, mythology and meteorology mix with the inexorable tide of political change: Kashubian folklore, Chinese mysticism and mediaeval scholarship butt up against the war in Chechnya, 9-11, and the struggle for Polish independence.&lt;/p&gt;
+&lt;p&gt;Central to Huelle’s imagery is the vision of the refugee – be it the Chechen woman carrying her newborn child across the Polish border (her face emblazoned on every TV screen), the survivor of the Gulag re-appearing on his friends’ doorstep, years after being presumed dead, or the stranger who befriends the sole resident of a ghostly Mennonite village in the final days of the Second World War. Each refugee carries a clue, it seems, or is in possession or pursuit of some mysterious text or book, knowing that only it – like the Chinese ‘Book of Changes’ – can decode their story.
+What we do with this text, this clue, Huelle seems to say, is up to us.&lt;/p&gt;</t>
   </si>
 </sst>
 </file>
@@ -889,7 +912,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -915,6 +938,9 @@
     <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1557,7 +1583,7 @@
         <v>9781429964395</v>
       </c>
       <c r="AH3" t="str">
-        <f t="shared" ref="AH3:AH46" si="0">"covers/" &amp; A3 &amp; ".jpg"</f>
+        <f t="shared" ref="AH3:AH47" si="0">"covers/" &amp; A3 &amp; ".jpg"</f>
         <v>covers/peasant-prince.jpg</v>
       </c>
       <c r="AS3" t="s">
@@ -4074,8 +4100,62 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="AN47"/>
+    <row r="47" spans="1:48" ht="375" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>219</v>
+      </c>
+      <c r="B47" t="s">
+        <v>79</v>
+      </c>
+      <c r="C47">
+        <v>525</v>
+      </c>
+      <c r="D47" t="s">
+        <v>220</v>
+      </c>
+      <c r="E47" t="s">
+        <v>221</v>
+      </c>
+      <c r="F47" t="s">
+        <v>68</v>
+      </c>
+      <c r="P47" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="R47" s="3">
+        <v>19</v>
+      </c>
+      <c r="X47" s="18">
+        <v>9781905583393</v>
+      </c>
+      <c r="Y47" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="Z47" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="AA47" s="5">
+        <v>5.99</v>
+      </c>
+      <c r="AG47" s="8">
+        <v>9781905583829</v>
+      </c>
+      <c r="AH47" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/cold-sea.jpg</v>
+      </c>
+      <c r="AN47" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="AS47" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT47" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV47" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="48" spans="1:48" x14ac:dyDescent="0.25">
       <c r="AN48" s="16"/>
@@ -4182,7 +4262,7 @@
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G47:H1048576 Y85:Z1048576 P85:Q1048576 X76:Y84 O76:P84 O44 AG44 X44 P47:P75 Q43:Q75 Y47:Z75" xr:uid="{D2C177B6-092A-4420-B1E2-D1681CD512E9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G47:H1048576 Y85:Z1048576 P85:Q1048576 X76:Y84 O76:P84 O44 AG44 X44 P48:P75 Q43:Q75 Y47:Y75 Z48:Z75" xr:uid="{D2C177B6-092A-4420-B1E2-D1681CD512E9}">
       <formula1>"hardcover, paperback, eBook, audiobook1"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR76:AS84 AS85:AT1048576 AS1:AT75" xr:uid="{F1FB7CD6-B38A-4A39-862C-8A1111411C8C}">

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/bookstore-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="317" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B84445C0-FF2B-46EF-A641-88349A937EC2}"/>
+  <xr:revisionPtr revIDLastSave="319" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74B0E2F0-19EB-482B-B0CD-3EBD427CDFC8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
@@ -2082,10 +2082,10 @@
         <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>104</v>
       </c>
       <c r="C12">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="D12" t="s">
         <v>64</v>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/bookstore-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="319" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{74B0E2F0-19EB-482B-B0CD-3EBD427CDFC8}"/>
+  <xr:revisionPtr revIDLastSave="326" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4642FF68-1DDC-4ED3-8400-B7ABB41A8F0A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="226">
   <si>
     <t>cover</t>
   </si>
@@ -717,9 +717,6 @@
 While all have seen their work translated into foreign languages, all poems included in this collection appear in English for the first time.</t>
   </si>
   <si>
-    <t>Fiction; Books in Focus; Young Adult</t>
-  </si>
-  <si>
     <t>krzysztof-kamil-baczynski</t>
   </si>
   <si>
@@ -772,6 +769,12 @@
 &lt;p&gt;The characters in Pawel Huelle’s mesmerising stories find themselves, willingly or not, at the heart of epic narratives; legends and histories that stretch far beyond the limits of their own lives. Against the backdrop of the Baltic coast, mythology and meteorology mix with the inexorable tide of political change: Kashubian folklore, Chinese mysticism and mediaeval scholarship butt up against the war in Chechnya, 9-11, and the struggle for Polish independence.&lt;/p&gt;
 &lt;p&gt;Central to Huelle’s imagery is the vision of the refugee – be it the Chechen woman carrying her newborn child across the Polish border (her face emblazoned on every TV screen), the survivor of the Gulag re-appearing on his friends’ doorstep, years after being presumed dead, or the stranger who befriends the sole resident of a ghostly Mennonite village in the final days of the Second World War. Each refugee carries a clue, it seems, or is in possession or pursuit of some mysterious text or book, knowing that only it – like the Chinese ‘Book of Changes’ – can decode their story.
 What we do with this text, this clue, Huelle seems to say, is up to us.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Books in Focus; Young Adult</t>
+  </si>
+  <si>
+    <t>Young Adult</t>
   </si>
 </sst>
 </file>
@@ -1424,16 +1427,16 @@
         <v>27</v>
       </c>
       <c r="AO1" t="s">
+        <v>210</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>213</v>
+      </c>
+      <c r="AQ1" t="s">
         <v>211</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AR1" t="s">
         <v>214</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>212</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>215</v>
       </c>
       <c r="AS1" t="s">
         <v>22</v>
@@ -1858,7 +1861,7 @@
         <v>40</v>
       </c>
       <c r="C8">
-        <v>150</v>
+        <v>650</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>41</v>
@@ -2082,10 +2085,10 @@
         <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>104</v>
+        <v>225</v>
       </c>
       <c r="C12">
-        <v>565</v>
+        <v>1050</v>
       </c>
       <c r="D12" t="s">
         <v>64</v>
@@ -2900,19 +2903,19 @@
         <v>covers/melicles.jpg</v>
       </c>
       <c r="AN26" s="20" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="AO26" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AP26" t="s">
         <v>191</v>
       </c>
       <c r="AQ26" t="s">
+        <v>216</v>
+      </c>
+      <c r="AR26" t="s">
         <v>217</v>
-      </c>
-      <c r="AR26" t="s">
-        <v>218</v>
       </c>
       <c r="AS26" t="s">
         <v>23</v>
@@ -3677,7 +3680,7 @@
     </row>
     <row r="40" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B40" t="s">
         <v>131</v>
@@ -3829,7 +3832,7 @@
         <v>197</v>
       </c>
       <c r="B43" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="C43">
         <v>1000</v>
@@ -3898,7 +3901,7 @@
         <v>200</v>
       </c>
       <c r="B44" t="s">
-        <v>103</v>
+        <v>225</v>
       </c>
       <c r="C44">
         <v>1100</v>
@@ -3967,7 +3970,7 @@
         <v>199</v>
       </c>
       <c r="B45" t="s">
-        <v>103</v>
+        <v>225</v>
       </c>
       <c r="C45">
         <v>1200</v>
@@ -4036,7 +4039,7 @@
         <v>198</v>
       </c>
       <c r="B46" t="s">
-        <v>103</v>
+        <v>225</v>
       </c>
       <c r="C46">
         <v>1300</v>
@@ -4102,7 +4105,7 @@
     </row>
     <row r="47" spans="1:48" ht="375" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B47" t="s">
         <v>79</v>
@@ -4111,10 +4114,10 @@
         <v>525</v>
       </c>
       <c r="D47" t="s">
+        <v>219</v>
+      </c>
+      <c r="E47" t="s">
         <v>220</v>
-      </c>
-      <c r="E47" t="s">
-        <v>221</v>
       </c>
       <c r="F47" t="s">
         <v>68</v>
@@ -4129,10 +4132,10 @@
         <v>9781905583393</v>
       </c>
       <c r="Y47" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="Z47" s="4" t="s">
         <v>222</v>
-      </c>
-      <c r="Z47" s="4" t="s">
-        <v>223</v>
       </c>
       <c r="AA47" s="5">
         <v>5.99</v>
@@ -4145,7 +4148,7 @@
         <v>covers/cold-sea.jpg</v>
       </c>
       <c r="AN47" s="21" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AS47" t="s">
         <v>23</v>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/bookstore-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="326" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4642FF68-1DDC-4ED3-8400-B7ABB41A8F0A}"/>
+  <xr:revisionPtr revIDLastSave="330" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79A884FF-61EE-4F1A-8AA3-5C815436B93A}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
@@ -1861,7 +1861,7 @@
         <v>40</v>
       </c>
       <c r="C8">
-        <v>650</v>
+        <v>750</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>41</v>
@@ -2848,7 +2848,7 @@
         <v>101</v>
       </c>
       <c r="B26" t="s">
-        <v>103</v>
+        <v>225</v>
       </c>
       <c r="C26">
         <v>100</v>
@@ -2932,7 +2932,7 @@
         <v>102</v>
       </c>
       <c r="B27" t="s">
-        <v>103</v>
+        <v>225</v>
       </c>
       <c r="C27">
         <v>600</v>
@@ -2990,7 +2990,7 @@
         <v>103</v>
       </c>
       <c r="C28">
-        <v>100</v>
+        <v>220</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>109</v>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/bookstore-main/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="330" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79A884FF-61EE-4F1A-8AA3-5C815436B93A}"/>
+  <xr:revisionPtr revIDLastSave="534" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45562432-AB08-494D-8F34-24FDFCAF8E00}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="272">
   <si>
     <t>cover</t>
   </si>
@@ -757,12 +757,6 @@
     <t>Paweł Huelle</t>
   </si>
   <si>
-    <t>eBook</t>
-  </si>
-  <si>
-    <t>Comma Press</t>
-  </si>
-  <si>
     <t>&lt;p&gt;A student pedals an old Ukraina bicycle between striking factories, delivering bulletins, in the tumultuous first days of the Solidarity movement...&lt;/p&gt;
 &lt;p&gt;A shepherd watches, unseen, as a strange figure disembarks from a pirate ship anchored in the cove below, to bury a chest on the beach that later proves empty…&lt;/p&gt;
 &lt;p&gt;A prisoner in a Berber dungeon recounts his life’s story – the failed pursuit of the world’s very first language – by scrawling in the sand on his cell floor…&lt;/p&gt;
@@ -776,24 +770,200 @@
   <si>
     <t>Young Adult</t>
   </si>
+  <si>
+    <t>saragossa</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;It is 1739 and Alphonse van Worden, a Walloon officer serving the King of Spain, spends the night in a haunted inn in the Sierra Morena where he is plunged into a series of adventures, by turns mysterious, erotic and nightmarish. Convinced that he is being hunted by the Inquisition, he joins a band of wanderers - including a gypsy chief, a geometer, a cabbalist and the Wandering Jew himself - who travel aimlessly while regaling their companions with a hundred and more stories, and stories within stories, told over the course of sixty-six 'days', each day as disorienting as a thousand and one nights.&lt;/p&gt;
+&lt;p&gt;And this nest of stories frames yet more stories driving the reader ever deeper into a labyrinth of sadism, satanism, the cabbala and other phantoms brought forth by the sleep of eighteenth-century Reason. For as well as being one of the great masterpieces of subversion, The Manuscript Found in Saragossa is also an encyclopedia of the dark side of the European Enlightenment.&lt;/p&gt;
+&lt;p&gt;&lt;em&gt;The Manuscript Found in Saragossa&lt;/em&gt; was written in French, probably between 1797 and 1815; this new translation makes the full text available in English for the first time.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>The Manuscript Found in Saragossa</t>
+  </si>
+  <si>
+    <t>Jan Potocki</t>
+  </si>
+  <si>
+    <t>Viking Adult</t>
+  </si>
+  <si>
+    <t>birch-grove</t>
+  </si>
+  <si>
+    <t>Jarosław Iwaszkiewicz</t>
+  </si>
+  <si>
+    <t>Central European University Press</t>
+  </si>
+  <si>
+    <t>Jaroslaw Iwaszkiewicz's work is familiar to every Polish reader, yet remains unknown to the outside world. The stories in this selection were all written in the 1930s, and provide an extraordinary evocation of Poland's first brief era of independence between the wars. They are also timeless sonatas of love and loss. In 'A New Love', Iwaszkiewicz uses masterful brevity to take a wry, comical look at the illusion of romance from the viewpoint of a jaded, cynical lover. One of his best-known works, 'The Wilko Girls', tells of a middle-aged man's quest to recover his lost youth in the aftermath of the First World War, which has left him psychologically scarred. He travels to the scene of his pre-war summer holidays in the eastern borderlands, where he renews his friendship with the fascinating sisters whom he knew when they were girls. But no one is the same and nothing can be as it was. 'The Birch Grove' is the moving story of a woodsman who, spiritually destroyed by the death of his wife, has buried himself away in an isolated forest. When his lively younger brother unexpectedly comes to stay, his self-centred peace is disrupted. But his brother has come home to die. The lives of two young men, one a deeply religious poet, the other a sceptical, worldly estate owner, are touchingly contrasted in 'The Mill on the River Utrata'. Confirming these stories' central place in Polish cultural history, 'The Wilko Girls' and 'The Birch Grove' were made into classic films by Andrzej Wajda, Poland's leading director.</t>
+  </si>
+  <si>
+    <t>The Danton Case and Thermidor: Two Plays</t>
+  </si>
+  <si>
+    <t>danton-thermidor</t>
+  </si>
+  <si>
+    <t>Stanislawa Przybyszewska</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Boleslaw Taborski</t>
+  </si>
+  <si>
+    <t>Northwestern University Press</t>
+  </si>
+  <si>
+    <t>Stanislawa Przybyszewska is recognized as a major twentieth-century playwright on the basis of her trilogy about the French Revolution, of which The Danton Case and Thermidor are the principal parts. The Danton Case depicts the battle for power between two exceptional individuals: the corrupt sentimental idealist, Danton, and the incorruptible genius of the Revolution, Robespierre. Thermidor shows the final playing out of this drama, as Robespierre, left alone with the heroic absolutist Saint-Just, foresees the ruin of himself and his cause, and in his despair predicts that hatred, war, and capitalism will steal the Revolution and corrupt nineteenth-century man.</t>
+  </si>
+  <si>
+    <t>coming-spring</t>
+  </si>
+  <si>
+    <t>Coming Spring</t>
+  </si>
+  <si>
+    <t>The Coming Spring (Przedwiosnie), Zeromski's last novel, tells the story of Cezary Baryka, a young Pole who finds himself in Baku, Azerbaijan, then a predominantly Armenian city, as the Russian Revolution breaks out. He becomes embroiled in the chaos caused by the revolution, and barely escapes with his life. Then, he and his father set off on a horrendous journey west to reach Poland. His father dies en route, but Cezary makes it to the newly independent Poland. Cezary sees the suffering of the poor, yet his experiences in the newly formed Soviet Union make him suspicious of socialist and communist solutions. He is an outsider among both the gentry and the working classes, and he cannot find where he belongs. Furthermore, he has unsuccessful and tragic love relations. The novel ends when, despite his profound misgivings, he takes up political action on behalf of the poor. Zeromski, whose vivid, assured style is instantly recognizable, was a writer with a strong social conscience, taking up the concerns of the poor and downtrodden.</t>
+  </si>
+  <si>
+    <t>Stefan Żeromski</t>
+  </si>
+  <si>
+    <t>Ian Maclean</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;&lt;strong&gt;“Although he was nominated for the Nobel Prize in literature four times, Stefan Żeromski’s work is not as widely known outside Poland as it should be. Thus this elegant translation is most welcome . . . A beautiful, prescient story.”
+—Celia Jeffries, author of Blue Desert&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;The first contemporary English edition of a Polish masterpiece&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;&lt;strong&gt;Beautifully translated by Stephanie Kraft, this new edition includes an Introduction by Jennifer Croft and Boris Dralyuk.&lt;/strong&gt;&lt;/p&gt;
+&lt;p&gt;Tomasz Judym was born in a slum in Warsaw. Against all odds, he has become a doctor, and he finds that his driving motivation to treat disadvantaged people like those he grew up with is at odds with the expectations of his peers. He sees the unhealthy working and living conditions of the working class in twentieth-century Poland wearing on those around him, even as he strives to help them. As he battles alone to do the kind of work that boards of health and other agencies do today, Dr. Judym wrestles inwardly with feelings of inferiority and revulsion caused by his difficult childhood. His mission takes him out of the city and into the countryside, bringing him into conflict with his other desires, and the love that he feels for a sympathetic woman whose background differs fundamentally from his own.&lt;/p&gt;
+&lt;p&gt;The Homeless combines concrete detail about social issues—the urgent need for public hygiene and access to medical treatment, the effects of industrialization on health and the landscape, and the disinterest that people in power have in the disadvantaged—with beautiful, artistic passages of prose that sensitively probe the characters’ inner lives. The title comes not from the obvious reference to the impoverished people Dr. Judym concerns himself with, but from the unmoored status of the protagonist, the woman he loves, a mysterious engineer friend of his, his brother, and many others who find themselves rootless—emotionally and physically alienated by class divides and the social upheaval of industrialization. The Homeless is a portrait of the time and place it was written—Poland on the precipice of the twentieth century—that speaks to our current time and place.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>the-homless</t>
+  </si>
+  <si>
+    <t>The Homeless</t>
+  </si>
+  <si>
+    <t>Stefanie Kraft</t>
+  </si>
+  <si>
+    <t>Paul Dry Books</t>
+  </si>
+  <si>
+    <t>The Birch Grove and Other Stories</t>
+  </si>
+  <si>
+    <t>The Intriguing Life and Ignominious Death of Maurice Benyovszky</t>
+  </si>
+  <si>
+    <t>Andrew Drummond</t>
+  </si>
+  <si>
+    <t>Routledge</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;Published in 1790, Maurice Benyovszky’s posthumous memoir was an instant sensation. A tale of exploration and adventure beginning with his daring escape from a Siberian prison and ending with his coronation as King of Madagascar, it was translated into several languages and adapted for the theatre and opera. This book explores the veracity of this memoir and, more broadly, the challenges faced by the explorers of the age and the brutality of colonisation.&lt;/p&gt;
+&lt;p&gt;The self-styled Hungarian Baron Maurice Auguste Aladar Benyovszky, Counsellor to the Duke of Saxony and Colonel in the service of the Queen of Hungary, was in fact only confirmed to have been an officer in a regiment of the Polish Confederation of Bar. While he did escape from Russian captors and subsequently travel to Japan, Formosa, China and Madagascar, many of his exploits were wildly exaggerated or simply invented. Andrew Drummond reveals an alternative picture of events by looking at statements from Benyovszky’s travelling companions and sceptical officials as well as contemporary documents from the places he claimed to have visited, untangling the truth behind his stories and examining what these stories can nonetheless tell us about the era in which Benyovszky lived.&lt;/p&gt;
+&lt;p&gt;Witty and engagingly written, this book is fascinating reading for anyone interested in eighteenth-century colonial history and the story of early European and Russian explorers.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>beniowski</t>
+  </si>
+  <si>
+    <t>witcher-set</t>
+  </si>
+  <si>
+    <t>The Witcher Boxed Set: Blood of Elves, The Time of Contempt, Baptism of Fire, The Tower of Swallows, The Lady of the Lake</t>
+  </si>
+  <si>
+    <t>Andrzej Sapkowski</t>
+  </si>
+  <si>
+    <t>Danusia Stok, David French</t>
+  </si>
+  <si>
+    <t>Orbit</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;Andrzej Sapkowski created an international phenomenon with his New York Times bestselling epic fantasy series about Geralt of Rivia, which has gone on to inspire the hit Netflix show and the blockbuster video games. Now, for the first time in a single boxed set, and featuring stunning new cover designs, the five novels that comprise the Witcher Saga: Blood of Elves, The Time of Contempt, Baptism of Fire,The Tower of Swallows, and Lady of the Lake.&lt;/p&gt;
+&lt;p&gt;★ The New York Times bestselling series&lt;/p&gt;
+&lt;p&gt;★ Over Fifteen Million Copies Sold Worldwide&lt;/p&gt;
+&lt;p&gt;★ World Fantasy Award Winning Author&lt;/p&gt;
+&lt;p&gt;★ David Gemmell Legend Award Winning Author&lt;/p&gt;
+&lt;p&gt;★ Named One of the Greatest Book Series of All Time by Forbes&lt;/p&gt;
+&lt;p&gt;For over a century, humans, dwarves, gnomes, and elves have lived together in relative peace. But times have changed, the uneasy peace is over, and now the races are fighting once again. &lt;/p&gt;
+&lt;p&gt;Geralt of Rivia, the hunter known as the Witcher, has been waiting for the birth of a prophesied child. This child has the power to change the world—for good, or for evil.&lt;/p&gt;
+&lt;p&gt;As the threat of war hangs over the land the child, Ciri, is hunted for her extraordinary powers. Geralt and his allies, including the powerful sorceress Yennefer, must find a way to protect her, and to protect the world. And the Witcher never accepts defeat.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>tower-fools</t>
+  </si>
+  <si>
+    <t>The Tower of Fools</t>
+  </si>
+  <si>
+    <t>David French</t>
+  </si>
+  <si>
+    <t>"A fantastic novel that any fan of The Witcher will instantly appreciate." —The Gamer&lt;/p&gt;
+&lt;p&gt;Andrzej Sapkowski's Witcher series has become a fantasy phenomenon, finding millions of fans worldwide and inspiring the hit Netflix show and video games. Now the bestselling author introduces readers to a new hero on an epic journey in The Tower of Fools, the first book of the Hussite Trilogy.&lt;/p&gt;
+&lt;p&gt;Reinmar of Bielawa, sometimes known as Reynevan, is a healer, a magician, and according to some, a charlatan. When a thoughtless indiscretion forces him to flee his home, he finds himself pursuednot only by brothers bent on vengeance but by the Holy  Inquisition.&lt;/p&gt;
+&lt;p&gt;In a time when tensions between Hussite and Catholic countries are threatening to turn into war and mystical forces are gathering in the shadows, Reynevan's journey will lead him to the Narrenturm—the Tower of Fools.&lt;/p&gt;
+&lt;p&gt;The Tower is an asylum for the mad...or for those who dare to think differently and challenge the prevailing order. And escaping it, avoiding the conflict around him, and keeping his own sanity will prove more difficult than he ever imagined&lt;/p&gt;
+&lt;p&gt;"A ripping yarn delivered with world-weary wit, bursting at the seams with sex, death, magic and madness." —Joe Abercrombie&lt;/p&gt;
+&lt;p&gt;"This is historical fantasy done right." —Publishers Weekly (starred review)&lt;/p&gt;
+&lt;p&gt;"A highly enjoyable historical fantasy." —Booklist&lt;/p&gt;
+&lt;p&gt;The Tower of Fools is an historical novel set during the Hussite Wars in Bohemia during the 1400s, a period of religious conflict and persecution. Characters in the novel may express views that some readers might find offensive.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>The Hussite Trilogy</t>
+  </si>
+  <si>
+    <t>warrior-god</t>
+  </si>
+  <si>
+    <t>Warriors of God</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;From the New York Times bestselling author of The Witcher: Reynevan—scoundrel, magician, possibly a fool—travels into the depths of war as he attempts to navigate the religious fervors of the fifteenth century.&lt;/p&gt;
+&lt;p&gt;When the Hussite leaders entrust Reynevan with a dangerous secret mission, he is forced to come out of hiding in Bohemia and depart for Silesia. At the same time, he strives to avenge the death of his brother and discover the whereabouts of his beloved. Once again pursued by multiple enemies, he must contend with danger on every front. &lt;/p&gt;
+&lt;p&gt;Full of gripping action replete with twists and mysteries, seasoned with magic and Sapkowski's ever-present wit, fans of the Witcher will appreciate this rich historical epic set during the Hussite Wars. &lt;/p&gt;
+&lt;p&gt;Praise for the The Tower of Fools, book one of the Hussite Trilogy:&lt;/p&gt;
+"This is historical fantasy done right." —Publishers Weekly (starred review)&lt;/p&gt;
+&lt;p&gt;“A fantastic novel that any fan of The Witcher will instantly appreciate.” —The Gamer&lt;/p&gt;
+&lt;p&gt;“A ripping yarn delivered with world-weary wit, bursting at the seams with sex, death, magic and madness.” —Joe Abercrombie &lt;/p&gt;
+&lt;p&gt;“Sapkowski's energetic and satirical prose as well as the unconventional setting makes this a highly enjoyable historical fantasy.” —Booklist&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>light-perpetua</t>
+  </si>
+  <si>
+    <t>Light Perpetua</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;From the globally bestselling author of The Witcher comes the final book in the rich historical epic, the Hussite trilogy. Join Reynevan—scoundrel, magician, possibly a fool—as he embarks on a last great adventure across the war-riddled landscape of 15th century Bohemia.&lt;/p&gt;
+&lt;p&gt;After his adventures in The Tower of Fools and Warriors of God, Reynevan is on the run again, harried by enemies—some human, and some mystical—at every turn. These are cruel and dangerous times for a man such as Reynevan, and to survive, he must set aside his history as a peaceful healer and idealist and play the brutal role of Hussite spy as crusades sweep through Silesia and the Czech Republic, and the world around him is forever changed.&lt;/p&gt;
+&lt;p&gt;Praise for the Hussite Trilogy:&lt;/p&gt;
+&lt;p&gt;“A ripping yarn delivered with world-weary wit, bursting at the seams with sex, death, magic and madness.” —Joe Abercrombie &lt;/p&gt;
+&lt;p&gt;"This is historical fantasy done right." —Publishers Weekly (starred review)&lt;/p&gt;
+&lt;p&gt;“A fantastic novel that any fan of The Witcher will instantly appreciate.” —The Gamer&lt;/p&gt;
+&lt;p&gt;“Sapkowski's energetic and satirical prose as well as the unconventional setting makes this a highly enjoyable historical fantasy.” —Booklist&lt;/p&gt;</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF0F1111"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
@@ -868,20 +1038,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF0F1111"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF0F1111"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
@@ -891,6 +1047,37 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0F1111"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0F1111"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF0F1111"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
@@ -915,34 +1102,45 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1285,27 +1483,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01CE5F32-AD1D-47CB-A8F1-52ACBFFA0BE8}">
   <dimension ref="A1:AY84"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="29.140625" customWidth="1"/>
-    <col min="2" max="3" width="13.7109375" customWidth="1"/>
-    <col min="4" max="6" width="46" customWidth="1"/>
-    <col min="7" max="9" width="9.140625" style="7"/>
+    <col min="1" max="1" width="29.1328125" customWidth="1"/>
+    <col min="2" max="3" width="13.73046875" customWidth="1"/>
+    <col min="4" max="4" width="46" style="27" customWidth="1"/>
+    <col min="5" max="6" width="46" customWidth="1"/>
+    <col min="7" max="9" width="9.1328125" style="7"/>
     <col min="10" max="11" width="9" style="7"/>
-    <col min="12" max="14" width="9.140625" style="7"/>
-    <col min="15" max="15" width="16" style="13" customWidth="1"/>
-    <col min="16" max="23" width="9.140625" style="3"/>
-    <col min="24" max="24" width="17" style="18" customWidth="1"/>
-    <col min="25" max="32" width="9.140625" style="5"/>
+    <col min="12" max="14" width="9.1328125" style="7"/>
+    <col min="15" max="15" width="16" style="12" customWidth="1"/>
+    <col min="16" max="23" width="9.1328125" style="3"/>
+    <col min="24" max="24" width="17" style="15" customWidth="1"/>
+    <col min="25" max="32" width="9.1328125" style="5"/>
     <col min="33" max="33" width="22" style="8" customWidth="1"/>
-    <col min="34" max="34" width="26.28515625" customWidth="1"/>
+    <col min="34" max="34" width="26.265625" customWidth="1"/>
     <col min="37" max="37" width="16" customWidth="1"/>
-    <col min="39" max="39" width="21.140625" customWidth="1"/>
-    <col min="40" max="40" width="95.85546875" style="12" customWidth="1"/>
-    <col min="41" max="44" width="19.7109375" customWidth="1"/>
+    <col min="39" max="39" width="21.1328125" customWidth="1"/>
+    <col min="40" max="40" width="95.86328125" style="19" customWidth="1"/>
+    <col min="41" max="44" width="19.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -1315,7 +1514,7 @@
       <c r="C1" t="s">
         <v>37</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="27" t="s">
         <v>24</v>
       </c>
       <c r="E1" t="s">
@@ -1348,7 +1547,7 @@
       <c r="N1" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="O1" s="13" t="s">
+      <c r="O1" s="12" t="s">
         <v>173</v>
       </c>
       <c r="P1" s="2" t="s">
@@ -1375,7 +1574,7 @@
       <c r="W1" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="X1" s="18" t="s">
+      <c r="X1" s="15" t="s">
         <v>181</v>
       </c>
       <c r="Y1" s="4" t="s">
@@ -1423,7 +1622,7 @@
       <c r="AM1" t="s">
         <v>21</v>
       </c>
-      <c r="AN1" s="12" t="s">
+      <c r="AN1" s="19" t="s">
         <v>27</v>
       </c>
       <c r="AO1" t="s">
@@ -1460,7 +1659,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -1470,7 +1669,7 @@
       <c r="C2">
         <v>100</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="26" t="s">
         <v>1</v>
       </c>
       <c r="E2" t="s">
@@ -1482,7 +1681,7 @@
       <c r="I2" s="7">
         <v>25</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="12">
         <v>9780684812199</v>
       </c>
       <c r="P2" s="2" t="s">
@@ -1498,7 +1697,7 @@
       <c r="T2" s="3">
         <v>15</v>
       </c>
-      <c r="X2" s="19">
+      <c r="X2" s="16">
         <v>9780306809330</v>
       </c>
       <c r="Y2" s="4" t="s">
@@ -1528,7 +1727,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1538,7 +1737,7 @@
       <c r="C3">
         <v>200</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="26" t="s">
         <v>3</v>
       </c>
       <c r="E3" t="s">
@@ -1550,7 +1749,7 @@
       <c r="I3" s="7">
         <v>36</v>
       </c>
-      <c r="O3" s="13">
+      <c r="O3" s="12">
         <v>9780312625924</v>
       </c>
       <c r="P3" s="2" t="s">
@@ -1566,7 +1765,7 @@
       <c r="T3" s="3">
         <v>15</v>
       </c>
-      <c r="X3" s="19">
+      <c r="X3" s="16">
         <v>9780312625948</v>
       </c>
       <c r="Y3" s="4" t="s">
@@ -1586,7 +1785,7 @@
         <v>9781429964395</v>
       </c>
       <c r="AH3" t="str">
-        <f t="shared" ref="AH3:AH47" si="0">"covers/" &amp; A3 &amp; ".jpg"</f>
+        <f t="shared" ref="AH3:AH57" si="0">"covers/" &amp; A3 &amp; ".jpg"</f>
         <v>covers/peasant-prince.jpg</v>
       </c>
       <c r="AS3" t="s">
@@ -1599,7 +1798,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -1609,14 +1808,14 @@
       <c r="C4">
         <v>300</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="26" t="s">
         <v>5</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="6"/>
-      <c r="O4" s="13">
+      <c r="O4" s="12">
         <v>9780008411251</v>
       </c>
       <c r="P4" s="2" t="s">
@@ -1632,7 +1831,7 @@
       <c r="T4" s="3">
         <v>16</v>
       </c>
-      <c r="X4" s="19">
+      <c r="X4" s="16">
         <v>9780008521684</v>
       </c>
       <c r="Y4" s="4" t="s">
@@ -1665,7 +1864,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>77</v>
       </c>
@@ -1675,7 +1874,7 @@
       <c r="C5">
         <v>400</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="D5" s="26" t="s">
         <v>7</v>
       </c>
       <c r="E5" t="s">
@@ -1693,12 +1892,12 @@
       <c r="K5" s="7">
         <v>38</v>
       </c>
-      <c r="O5" s="14">
+      <c r="O5" s="13">
         <v>9780300252200</v>
       </c>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
-      <c r="X5" s="19"/>
+      <c r="X5" s="16"/>
       <c r="Y5" s="4" t="s">
         <v>118</v>
       </c>
@@ -1729,7 +1928,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1739,7 +1938,7 @@
       <c r="C6">
         <v>500</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="26" t="s">
         <v>9</v>
       </c>
       <c r="E6" t="s">
@@ -1757,12 +1956,12 @@
       <c r="K6" s="7">
         <v>44</v>
       </c>
-      <c r="O6" s="14">
+      <c r="O6" s="13">
         <v>9781472816030</v>
       </c>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
-      <c r="X6" s="19"/>
+      <c r="X6" s="16"/>
       <c r="Y6" s="4" t="s">
         <v>118</v>
       </c>
@@ -1793,7 +1992,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -1803,7 +2002,7 @@
       <c r="C7">
         <v>600</v>
       </c>
-      <c r="D7" s="11" t="s">
+      <c r="D7" s="26" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
@@ -1818,7 +2017,7 @@
       <c r="I7" s="7">
         <v>27</v>
       </c>
-      <c r="O7" s="14">
+      <c r="O7" s="13">
         <v>9781607720041</v>
       </c>
       <c r="P7" s="2" t="s">
@@ -1834,7 +2033,7 @@
       <c r="T7" s="3">
         <v>18</v>
       </c>
-      <c r="X7" s="19">
+      <c r="X7" s="16">
         <v>9781607720058</v>
       </c>
       <c r="Y7" s="4"/>
@@ -1853,7 +2052,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -1863,7 +2062,7 @@
       <c r="C8">
         <v>750</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="26" t="s">
         <v>41</v>
       </c>
       <c r="E8" t="s">
@@ -1873,7 +2072,7 @@
         <v>44</v>
       </c>
       <c r="G8" s="6"/>
-      <c r="O8" s="14"/>
+      <c r="O8" s="13"/>
       <c r="P8" s="2" t="s">
         <v>117</v>
       </c>
@@ -1887,7 +2086,7 @@
       <c r="T8" s="3">
         <v>14</v>
       </c>
-      <c r="X8" s="19">
+      <c r="X8" s="16">
         <v>9781590173831</v>
       </c>
       <c r="Y8" s="4" t="s">
@@ -1920,7 +2119,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -1930,7 +2129,7 @@
       <c r="C9">
         <v>250</v>
       </c>
-      <c r="D9" s="11" t="s">
+      <c r="D9" s="26" t="s">
         <v>47</v>
       </c>
       <c r="E9" t="s">
@@ -1940,7 +2139,7 @@
         <v>45</v>
       </c>
       <c r="G9" s="6"/>
-      <c r="O9" s="14"/>
+      <c r="O9" s="13"/>
       <c r="P9" s="2" t="s">
         <v>117</v>
       </c>
@@ -1954,7 +2153,7 @@
       <c r="T9" s="3">
         <v>17</v>
       </c>
-      <c r="X9" s="19">
+      <c r="X9" s="16">
         <v>9780241524244</v>
       </c>
       <c r="Y9" s="4"/>
@@ -1973,7 +2172,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -1983,7 +2182,7 @@
       <c r="C10">
         <v>350</v>
       </c>
-      <c r="D10" s="11" t="s">
+      <c r="D10" s="26" t="s">
         <v>49</v>
       </c>
       <c r="E10" t="s">
@@ -1993,8 +2192,8 @@
         <v>52</v>
       </c>
       <c r="G10" s="6"/>
-      <c r="H10" s="17"/>
-      <c r="O10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="O10" s="13"/>
       <c r="P10" s="2" t="s">
         <v>117</v>
       </c>
@@ -2008,7 +2207,7 @@
       <c r="T10" s="3">
         <v>13</v>
       </c>
-      <c r="X10" s="19">
+      <c r="X10" s="16">
         <v>9781939810007</v>
       </c>
       <c r="Y10" s="4"/>
@@ -2027,7 +2226,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -2037,7 +2236,7 @@
       <c r="C11">
         <v>450</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="D11" s="26" t="s">
         <v>53</v>
       </c>
       <c r="E11" t="s">
@@ -2047,7 +2246,7 @@
         <v>55</v>
       </c>
       <c r="G11" s="6"/>
-      <c r="O11" s="14"/>
+      <c r="O11" s="13"/>
       <c r="P11" s="2" t="s">
         <v>117</v>
       </c>
@@ -2061,7 +2260,7 @@
       <c r="T11" s="3">
         <v>17</v>
       </c>
-      <c r="X11" s="19">
+      <c r="X11" s="16">
         <v>9780875807072</v>
       </c>
       <c r="Y11" s="4"/>
@@ -2080,17 +2279,17 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C12">
         <v>1050</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="27" t="s">
         <v>64</v>
       </c>
       <c r="E12" t="s">
@@ -2111,7 +2310,7 @@
       <c r="K12" s="7">
         <v>15</v>
       </c>
-      <c r="O12" s="14">
+      <c r="O12" s="13">
         <v>9798872593621</v>
       </c>
       <c r="P12" s="2" t="s">
@@ -2127,7 +2326,7 @@
       <c r="T12" s="3">
         <v>14</v>
       </c>
-      <c r="X12" s="19">
+      <c r="X12" s="16">
         <v>9798245149318</v>
       </c>
       <c r="Y12" s="4"/>
@@ -2146,7 +2345,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -2156,7 +2355,7 @@
       <c r="C13">
         <v>650</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="D13" s="26" t="s">
         <v>58</v>
       </c>
       <c r="E13" t="s">
@@ -2174,12 +2373,12 @@
       <c r="I13" s="7">
         <v>24</v>
       </c>
-      <c r="O13" s="14">
+      <c r="O13" s="13">
         <v>9789998791732</v>
       </c>
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
-      <c r="X13" s="19"/>
+      <c r="X13" s="16"/>
       <c r="Y13" s="4"/>
       <c r="Z13" s="4"/>
       <c r="AH13" t="str">
@@ -2202,7 +2401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>69</v>
       </c>
@@ -2212,7 +2411,7 @@
       <c r="C14">
         <v>100</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="26" t="s">
         <v>66</v>
       </c>
       <c r="E14" t="s">
@@ -2222,7 +2421,7 @@
         <v>68</v>
       </c>
       <c r="G14" s="6"/>
-      <c r="O14" s="14"/>
+      <c r="O14" s="13"/>
       <c r="P14" s="2" t="s">
         <v>117</v>
       </c>
@@ -2236,7 +2435,7 @@
       <c r="T14" s="3">
         <v>10</v>
       </c>
-      <c r="X14" s="19">
+      <c r="X14" s="16">
         <v>9781852429454</v>
       </c>
       <c r="Y14" s="4"/>
@@ -2255,7 +2454,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>73</v>
       </c>
@@ -2265,14 +2464,14 @@
       <c r="C15">
         <v>100</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="26" t="s">
         <v>70</v>
       </c>
       <c r="E15" t="s">
         <v>71</v>
       </c>
       <c r="G15" s="6"/>
-      <c r="O15" s="14"/>
+      <c r="O15" s="13"/>
       <c r="P15" s="2" t="s">
         <v>117</v>
       </c>
@@ -2286,7 +2485,7 @@
       <c r="T15" s="3">
         <v>12</v>
       </c>
-      <c r="X15" s="19">
+      <c r="X15" s="16">
         <v>9780679738015</v>
       </c>
       <c r="Y15" s="4"/>
@@ -2305,7 +2504,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>74</v>
       </c>
@@ -2315,14 +2514,14 @@
       <c r="C16">
         <v>400</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="26" t="s">
         <v>72</v>
       </c>
       <c r="E16" t="s">
         <v>71</v>
       </c>
       <c r="G16" s="6"/>
-      <c r="O16" s="14"/>
+      <c r="O16" s="13"/>
       <c r="P16" s="2" t="s">
         <v>117</v>
       </c>
@@ -2336,7 +2535,7 @@
       <c r="T16" s="3">
         <v>12</v>
       </c>
-      <c r="X16" s="19">
+      <c r="X16" s="16">
         <v>9780141188034</v>
       </c>
       <c r="Y16" s="4"/>
@@ -2355,7 +2554,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>130</v>
       </c>
@@ -2365,14 +2564,14 @@
       <c r="C17">
         <v>400</v>
       </c>
-      <c r="D17" s="11" t="s">
+      <c r="D17" s="26" t="s">
         <v>76</v>
       </c>
       <c r="E17" t="s">
         <v>71</v>
       </c>
       <c r="G17" s="6"/>
-      <c r="O17" s="14"/>
+      <c r="O17" s="13"/>
       <c r="P17" s="2" t="s">
         <v>117</v>
       </c>
@@ -2386,7 +2585,7 @@
       <c r="T17" s="3">
         <v>11</v>
       </c>
-      <c r="X17" s="19">
+      <c r="X17" s="16">
         <v>9780375726293</v>
       </c>
       <c r="Y17" s="4"/>
@@ -2405,7 +2604,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>81</v>
       </c>
@@ -2415,7 +2614,7 @@
       <c r="C18">
         <v>600</v>
       </c>
-      <c r="D18" s="11" t="s">
+      <c r="D18" s="26" t="s">
         <v>80</v>
       </c>
       <c r="E18" t="s">
@@ -2439,7 +2638,7 @@
       <c r="K18" s="7">
         <v>22</v>
       </c>
-      <c r="O18" s="14">
+      <c r="O18" s="13">
         <v>9782919820382</v>
       </c>
       <c r="P18" s="2"/>
@@ -2460,7 +2659,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>129</v>
       </c>
@@ -2470,7 +2669,7 @@
       <c r="C19">
         <v>800</v>
       </c>
-      <c r="D19" s="11" t="s">
+      <c r="D19" s="26" t="s">
         <v>82</v>
       </c>
       <c r="E19" t="s">
@@ -2494,7 +2693,7 @@
       <c r="K19" s="7">
         <v>20</v>
       </c>
-      <c r="O19" s="14">
+      <c r="O19" s="13">
         <v>9789998793729</v>
       </c>
       <c r="P19" s="2"/>
@@ -2515,7 +2714,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>85</v>
       </c>
@@ -2525,7 +2724,7 @@
       <c r="C20">
         <v>900</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" s="26" t="s">
         <v>83</v>
       </c>
       <c r="E20" t="s">
@@ -2549,7 +2748,7 @@
       <c r="K20" s="7">
         <v>22</v>
       </c>
-      <c r="O20" s="14">
+      <c r="O20" s="13">
         <v>9782919840052</v>
       </c>
       <c r="P20" s="2"/>
@@ -2570,7 +2769,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>86</v>
       </c>
@@ -2580,7 +2779,7 @@
       <c r="C21">
         <v>1000</v>
       </c>
-      <c r="D21" s="11" t="s">
+      <c r="D21" s="26" t="s">
         <v>84</v>
       </c>
       <c r="E21" t="s">
@@ -2604,7 +2803,7 @@
       <c r="K21" s="7">
         <v>20</v>
       </c>
-      <c r="O21" s="14">
+      <c r="O21" s="13">
         <v>9782919820290</v>
       </c>
       <c r="P21" s="2"/>
@@ -2625,7 +2824,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>90</v>
       </c>
@@ -2635,7 +2834,7 @@
       <c r="C22">
         <v>600</v>
       </c>
-      <c r="D22" s="11" t="s">
+      <c r="D22" s="26" t="s">
         <v>91</v>
       </c>
       <c r="E22" t="s">
@@ -2645,7 +2844,7 @@
         <v>93</v>
       </c>
       <c r="G22" s="6"/>
-      <c r="O22" s="14"/>
+      <c r="O22" s="13"/>
       <c r="P22" s="2" t="s">
         <v>117</v>
       </c>
@@ -2659,7 +2858,7 @@
       <c r="T22" s="3">
         <v>8</v>
       </c>
-      <c r="X22" s="18">
+      <c r="X22" s="15">
         <v>9780156027601</v>
       </c>
       <c r="Y22" s="4"/>
@@ -2678,7 +2877,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>94</v>
       </c>
@@ -2688,7 +2887,7 @@
       <c r="C23">
         <v>200</v>
       </c>
-      <c r="D23" s="11" t="s">
+      <c r="D23" s="26" t="s">
         <v>95</v>
       </c>
       <c r="E23" t="s">
@@ -2698,7 +2897,7 @@
         <v>96</v>
       </c>
       <c r="G23" s="6"/>
-      <c r="O23" s="14"/>
+      <c r="O23" s="13"/>
       <c r="P23" s="2" t="s">
         <v>117</v>
       </c>
@@ -2712,7 +2911,7 @@
       <c r="T23" s="3">
         <v>12</v>
       </c>
-      <c r="X23" s="18">
+      <c r="X23" s="15">
         <v>9780156306300</v>
       </c>
       <c r="Y23" s="4"/>
@@ -2731,7 +2930,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>128</v>
       </c>
@@ -2741,7 +2940,7 @@
       <c r="C24">
         <v>600</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" s="26" t="s">
         <v>97</v>
       </c>
       <c r="E24" t="s">
@@ -2751,7 +2950,7 @@
         <v>52</v>
       </c>
       <c r="G24" s="6"/>
-      <c r="O24" s="14"/>
+      <c r="O24" s="13"/>
       <c r="P24" s="2" t="s">
         <v>117</v>
       </c>
@@ -2765,7 +2964,7 @@
       <c r="T24" s="3">
         <v>13</v>
       </c>
-      <c r="X24" s="18">
+      <c r="X24" s="15">
         <v>9780262357685</v>
       </c>
       <c r="Y24" s="4"/>
@@ -2784,7 +2983,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>112</v>
       </c>
@@ -2794,7 +2993,7 @@
       <c r="C25">
         <v>100</v>
       </c>
-      <c r="D25" s="11" t="s">
+      <c r="D25" s="26" t="s">
         <v>98</v>
       </c>
       <c r="E25" t="s">
@@ -2804,7 +3003,7 @@
         <v>60</v>
       </c>
       <c r="G25" s="6"/>
-      <c r="O25" s="14"/>
+      <c r="O25" s="13"/>
       <c r="P25" s="2" t="s">
         <v>117</v>
       </c>
@@ -2818,7 +3017,7 @@
       <c r="T25" s="3">
         <v>15</v>
       </c>
-      <c r="X25" s="18">
+      <c r="X25" s="15">
         <v>9782919840106</v>
       </c>
       <c r="Y25" s="4"/>
@@ -2843,17 +3042,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:51" ht="165" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:51" ht="142.5" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>101</v>
       </c>
       <c r="B26" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C26">
         <v>100</v>
       </c>
-      <c r="D26" s="11" t="s">
+      <c r="D26" s="26" t="s">
         <v>105</v>
       </c>
       <c r="E26" t="s">
@@ -2877,7 +3076,7 @@
       <c r="K26" s="7">
         <v>20</v>
       </c>
-      <c r="O26" s="14">
+      <c r="O26" s="13">
         <v>9789998791671</v>
       </c>
       <c r="P26" s="2" t="s">
@@ -2893,7 +3092,7 @@
       <c r="T26" s="3">
         <v>15</v>
       </c>
-      <c r="X26" s="18">
+      <c r="X26" s="15">
         <v>9789998791664</v>
       </c>
       <c r="Y26" s="4"/>
@@ -2927,17 +3126,17 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>102</v>
       </c>
       <c r="B27" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C27">
         <v>600</v>
       </c>
-      <c r="D27" s="11" t="s">
+      <c r="D27" s="26" t="s">
         <v>106</v>
       </c>
       <c r="E27" t="s">
@@ -2961,7 +3160,7 @@
       <c r="K27" s="7">
         <v>20</v>
       </c>
-      <c r="O27" s="14">
+      <c r="O27" s="13">
         <v>9789998791794</v>
       </c>
       <c r="P27" s="2"/>
@@ -2982,7 +3181,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>111</v>
       </c>
@@ -2992,7 +3191,7 @@
       <c r="C28">
         <v>220</v>
       </c>
-      <c r="D28" s="11" t="s">
+      <c r="D28" s="26" t="s">
         <v>109</v>
       </c>
       <c r="E28" t="s">
@@ -3016,7 +3215,7 @@
       <c r="K28" s="7">
         <v>18</v>
       </c>
-      <c r="O28" s="13">
+      <c r="O28" s="12">
         <v>9782919820481</v>
       </c>
       <c r="P28" s="2"/>
@@ -3043,7 +3242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>110</v>
       </c>
@@ -3053,7 +3252,7 @@
       <c r="C29">
         <v>200</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D29" s="26" t="s">
         <v>108</v>
       </c>
       <c r="E29" t="s">
@@ -3077,7 +3276,7 @@
       <c r="K29" s="7">
         <v>18</v>
       </c>
-      <c r="O29" s="13">
+      <c r="O29" s="12">
         <v>9782919820153</v>
       </c>
       <c r="P29" s="2"/>
@@ -3104,7 +3303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>123</v>
       </c>
@@ -3114,7 +3313,7 @@
       <c r="C30">
         <v>250</v>
       </c>
-      <c r="D30" s="11" t="s">
+      <c r="D30" s="26" t="s">
         <v>120</v>
       </c>
       <c r="E30" t="s">
@@ -3132,7 +3331,7 @@
       <c r="I30" s="7">
         <v>24</v>
       </c>
-      <c r="O30" s="14">
+      <c r="O30" s="13">
         <v>9789998793781</v>
       </c>
       <c r="P30" s="2" t="s">
@@ -3144,7 +3343,7 @@
       <c r="R30" s="3">
         <v>16</v>
       </c>
-      <c r="X30" s="18">
+      <c r="X30" s="15">
         <v>9789998793774</v>
       </c>
       <c r="Y30" s="4" t="s">
@@ -3179,7 +3378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>124</v>
       </c>
@@ -3189,7 +3388,7 @@
       <c r="C31">
         <v>450</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="D31" s="26" t="s">
         <v>121</v>
       </c>
       <c r="E31" t="s">
@@ -3207,7 +3406,7 @@
       <c r="I31" s="7">
         <v>25</v>
       </c>
-      <c r="O31" s="14">
+      <c r="O31" s="13">
         <v>9782919820047</v>
       </c>
       <c r="P31" s="2" t="s">
@@ -3219,7 +3418,7 @@
       <c r="R31" s="3">
         <v>17</v>
       </c>
-      <c r="X31" s="18">
+      <c r="X31" s="15">
         <v>9782919820054</v>
       </c>
       <c r="Y31" s="4" t="s">
@@ -3254,7 +3453,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>125</v>
       </c>
@@ -3264,7 +3463,7 @@
       <c r="C32">
         <v>650</v>
       </c>
-      <c r="D32" s="11" t="s">
+      <c r="D32" s="26" t="s">
         <v>122</v>
       </c>
       <c r="E32" t="s">
@@ -3282,7 +3481,7 @@
       <c r="I32" s="7">
         <v>32</v>
       </c>
-      <c r="O32" s="14">
+      <c r="O32" s="13">
         <v>9782919820467</v>
       </c>
       <c r="P32" s="2" t="s">
@@ -3294,7 +3493,7 @@
       <c r="R32" s="3">
         <v>18</v>
       </c>
-      <c r="X32" s="18">
+      <c r="X32" s="15">
         <v>9782919820450</v>
       </c>
       <c r="Y32" s="4"/>
@@ -3319,7 +3518,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>157</v>
       </c>
@@ -3329,7 +3528,7 @@
       <c r="C33">
         <v>100</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" s="26" t="s">
         <v>158</v>
       </c>
       <c r="E33" t="s">
@@ -3345,7 +3544,7 @@
       <c r="R33" s="3">
         <v>14</v>
       </c>
-      <c r="X33" s="18">
+      <c r="X33" s="15">
         <v>9780062095886</v>
       </c>
       <c r="Y33" s="4"/>
@@ -3364,7 +3563,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>161</v>
       </c>
@@ -3374,7 +3573,7 @@
       <c r="C34">
         <v>200</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D34" s="27" t="s">
         <v>159</v>
       </c>
       <c r="E34" t="s">
@@ -3389,7 +3588,7 @@
       <c r="I34" s="7">
         <v>38</v>
       </c>
-      <c r="O34" s="13">
+      <c r="O34" s="12">
         <v>9780151003532</v>
       </c>
       <c r="P34" s="2" t="s">
@@ -3401,7 +3600,7 @@
       <c r="R34" s="3">
         <v>11</v>
       </c>
-      <c r="X34" s="19">
+      <c r="X34" s="16">
         <v>9780156011464</v>
       </c>
       <c r="Y34" s="4"/>
@@ -3420,7 +3619,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>164</v>
       </c>
@@ -3430,7 +3629,7 @@
       <c r="C35">
         <v>300</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D35" s="27" t="s">
         <v>162</v>
       </c>
       <c r="E35" t="s">
@@ -3446,7 +3645,7 @@
       <c r="R35" s="3">
         <v>18</v>
       </c>
-      <c r="X35" s="18">
+      <c r="X35" s="15">
         <v>9781400043293</v>
       </c>
       <c r="Y35" s="4"/>
@@ -3465,7 +3664,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>152</v>
       </c>
@@ -3475,7 +3674,7 @@
       <c r="C36">
         <v>400</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D36" s="27" t="s">
         <v>139</v>
       </c>
       <c r="E36" t="s">
@@ -3491,7 +3690,7 @@
       <c r="R36" s="3">
         <v>15</v>
       </c>
-      <c r="X36" s="18">
+      <c r="X36" s="15">
         <v>9780374528614</v>
       </c>
       <c r="Y36" s="4"/>
@@ -3510,7 +3709,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>153</v>
       </c>
@@ -3520,7 +3719,7 @@
       <c r="C37">
         <v>600</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D37" s="27" t="s">
         <v>144</v>
       </c>
       <c r="E37" t="s">
@@ -3538,7 +3737,7 @@
       <c r="I37" s="7">
         <v>16</v>
       </c>
-      <c r="O37" s="13">
+      <c r="O37" s="12">
         <v>9780393067798</v>
       </c>
       <c r="P37" s="2" t="s">
@@ -3548,7 +3747,7 @@
       <c r="R37" s="3">
         <v>19</v>
       </c>
-      <c r="X37" s="18">
+      <c r="X37" s="15">
         <v>9780393345551</v>
       </c>
       <c r="Y37" s="4"/>
@@ -3567,7 +3766,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>154</v>
       </c>
@@ -3577,7 +3776,7 @@
       <c r="C38">
         <v>700</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D38" s="27" t="s">
         <v>143</v>
       </c>
       <c r="E38" t="s">
@@ -3592,7 +3791,7 @@
       <c r="I38" s="7">
         <v>30</v>
       </c>
-      <c r="O38" s="13">
+      <c r="O38" s="12">
         <v>9780544126022</v>
       </c>
       <c r="P38" s="2" t="s">
@@ -3602,7 +3801,7 @@
       <c r="R38" s="3">
         <v>11</v>
       </c>
-      <c r="X38" s="18">
+      <c r="X38" s="15">
         <v>9780544705159</v>
       </c>
       <c r="Y38" s="4"/>
@@ -3621,7 +3820,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>155</v>
       </c>
@@ -3631,7 +3830,7 @@
       <c r="C39">
         <v>800</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D39" s="27" t="s">
         <v>145</v>
       </c>
       <c r="E39" s="10" t="s">
@@ -3649,7 +3848,7 @@
       <c r="I39" s="7">
         <v>25</v>
       </c>
-      <c r="O39" s="13">
+      <c r="O39" s="12">
         <v>9788367602488</v>
       </c>
       <c r="P39" s="2" t="s">
@@ -3659,7 +3858,7 @@
       <c r="R39" s="3">
         <v>11</v>
       </c>
-      <c r="X39" s="18">
+      <c r="X39" s="15">
         <v>9788367602471</v>
       </c>
       <c r="Y39" s="4"/>
@@ -3678,7 +3877,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>209</v>
       </c>
@@ -3688,7 +3887,7 @@
       <c r="C40">
         <v>900</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D40" s="27" t="s">
         <v>148</v>
       </c>
       <c r="E40" t="s">
@@ -3702,7 +3901,7 @@
       <c r="R40" s="3">
         <v>7</v>
       </c>
-      <c r="X40" s="18">
+      <c r="X40" s="15">
         <v>9798802065853</v>
       </c>
       <c r="Y40" s="4"/>
@@ -3721,7 +3920,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>156</v>
       </c>
@@ -3731,7 +3930,7 @@
       <c r="C41">
         <v>1000</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D41" s="27" t="s">
         <v>151</v>
       </c>
       <c r="E41" t="s">
@@ -3748,7 +3947,7 @@
       <c r="R41" s="3">
         <v>14</v>
       </c>
-      <c r="X41" s="18">
+      <c r="X41" s="15">
         <v>9781931243810</v>
       </c>
       <c r="Y41" s="4"/>
@@ -3767,7 +3966,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>205</v>
       </c>
@@ -3777,7 +3976,7 @@
       <c r="C42">
         <v>1100</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D42" s="27" t="s">
         <v>206</v>
       </c>
       <c r="E42" t="s">
@@ -3795,7 +3994,7 @@
       <c r="I42" s="7">
         <v>19</v>
       </c>
-      <c r="O42" s="13">
+      <c r="O42" s="12">
         <v>9788367602426</v>
       </c>
       <c r="P42" s="2" t="s">
@@ -3805,7 +4004,7 @@
       <c r="R42" s="3">
         <v>9.99</v>
       </c>
-      <c r="X42" s="18">
+      <c r="X42" s="15">
         <v>9788367602419</v>
       </c>
       <c r="Y42" s="4"/>
@@ -3814,7 +4013,7 @@
         <f t="shared" si="0"/>
         <v>covers/new-poems-ukr-po.jpg</v>
       </c>
-      <c r="AN42" s="12" t="s">
+      <c r="AN42" s="19" t="s">
         <v>208</v>
       </c>
       <c r="AS42" t="s">
@@ -3827,17 +4026,17 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>197</v>
       </c>
       <c r="B43" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="C43">
         <v>1000</v>
       </c>
-      <c r="D43" t="s">
+      <c r="D43" s="27" t="s">
         <v>193</v>
       </c>
       <c r="E43" t="s">
@@ -3855,7 +4054,7 @@
       <c r="I43" s="7">
         <v>26</v>
       </c>
-      <c r="O43" s="13">
+      <c r="O43" s="12">
         <v>9782919820863</v>
       </c>
       <c r="P43" s="2" t="s">
@@ -3864,7 +4063,7 @@
       <c r="R43" s="3">
         <v>13</v>
       </c>
-      <c r="X43" s="18">
+      <c r="X43" s="15">
         <v>9782919820856</v>
       </c>
       <c r="Y43" s="4" t="s">
@@ -3883,7 +4082,7 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-templars.jpg</v>
       </c>
-      <c r="AN43" s="12" t="s">
+      <c r="AN43" s="19" t="s">
         <v>202</v>
       </c>
       <c r="AS43" t="s">
@@ -3896,17 +4095,17 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>200</v>
       </c>
       <c r="B44" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C44">
         <v>1100</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D44" s="27" t="s">
         <v>194</v>
       </c>
       <c r="E44" t="s">
@@ -3924,7 +4123,7 @@
       <c r="I44" s="7">
         <v>25</v>
       </c>
-      <c r="O44" s="13">
+      <c r="O44" s="12">
         <v>9782919840014</v>
       </c>
       <c r="P44" s="2" t="s">
@@ -3933,7 +4132,7 @@
       <c r="R44" s="3">
         <v>17</v>
       </c>
-      <c r="X44" s="18">
+      <c r="X44" s="15">
         <v>9782919840021</v>
       </c>
       <c r="Y44" s="4" t="s">
@@ -3952,7 +4151,7 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-mysteries.jpg</v>
       </c>
-      <c r="AN44" s="12" t="s">
+      <c r="AN44" s="19" t="s">
         <v>204</v>
       </c>
       <c r="AS44" t="s">
@@ -3965,17 +4164,17 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>199</v>
       </c>
       <c r="B45" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C45">
         <v>1200</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D45" s="27" t="s">
         <v>196</v>
       </c>
       <c r="E45" t="s">
@@ -3993,7 +4192,7 @@
       <c r="I45" s="7">
         <v>25</v>
       </c>
-      <c r="O45" s="13">
+      <c r="O45" s="12">
         <v>9782919820955</v>
       </c>
       <c r="P45" s="2" t="s">
@@ -4002,7 +4201,7 @@
       <c r="R45" s="3">
         <v>15</v>
       </c>
-      <c r="X45" s="19">
+      <c r="X45" s="16">
         <v>9782919820948</v>
       </c>
       <c r="Y45" s="4" t="s">
@@ -4021,7 +4220,7 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-bandits.jpg</v>
       </c>
-      <c r="AN45" s="12" t="s">
+      <c r="AN45" s="19" t="s">
         <v>201</v>
       </c>
       <c r="AS45" t="s">
@@ -4034,17 +4233,17 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>198</v>
       </c>
       <c r="B46" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C46">
         <v>1300</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D46" s="27" t="s">
         <v>195</v>
       </c>
       <c r="E46" t="s">
@@ -4062,7 +4261,7 @@
       <c r="I46" s="7">
         <v>25</v>
       </c>
-      <c r="O46" s="13">
+      <c r="O46" s="12">
         <v>9782919820917</v>
       </c>
       <c r="P46" s="2" t="s">
@@ -4071,7 +4270,7 @@
       <c r="R46" s="3">
         <v>13</v>
       </c>
-      <c r="X46" s="18">
+      <c r="X46" s="15">
         <v>9782919820900</v>
       </c>
       <c r="Y46" s="4" t="s">
@@ -4090,7 +4289,7 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-copernicus.jpg</v>
       </c>
-      <c r="AN46" s="1" t="s">
+      <c r="AN46" s="21" t="s">
         <v>203</v>
       </c>
       <c r="AS46" t="s">
@@ -4103,7 +4302,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:48" ht="375" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:48" ht="327.75" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>218</v>
       </c>
@@ -4113,7 +4312,7 @@
       <c r="C47">
         <v>525</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D47" s="27" t="s">
         <v>219</v>
       </c>
       <c r="E47" t="s">
@@ -4128,14 +4327,14 @@
       <c r="R47" s="3">
         <v>19</v>
       </c>
-      <c r="X47" s="18">
+      <c r="X47" s="15">
         <v>9781905583393</v>
       </c>
-      <c r="Y47" s="5" t="s">
-        <v>221</v>
+      <c r="Y47" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="Z47" s="4" t="s">
-        <v>222</v>
+        <v>136</v>
       </c>
       <c r="AA47" s="5">
         <v>5.99</v>
@@ -4147,8 +4346,8 @@
         <f t="shared" si="0"/>
         <v>covers/cold-sea.jpg</v>
       </c>
-      <c r="AN47" s="21" t="s">
-        <v>223</v>
+      <c r="AN47" s="22" t="s">
+        <v>221</v>
       </c>
       <c r="AS47" t="s">
         <v>23</v>
@@ -4160,112 +4359,744 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="AN48" s="16"/>
-    </row>
-    <row r="49" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN49"/>
-    </row>
-    <row r="50" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN50" s="15"/>
-    </row>
-    <row r="51" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN51"/>
-    </row>
-    <row r="52" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN52" s="1"/>
-    </row>
-    <row r="53" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN53"/>
-    </row>
-    <row r="54" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN54" s="1"/>
-    </row>
-    <row r="55" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN55"/>
-    </row>
-    <row r="56" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN56" s="1"/>
-    </row>
-    <row r="57" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN57"/>
-    </row>
-    <row r="58" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN58" s="1"/>
-    </row>
-    <row r="59" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN59" s="15"/>
-    </row>
-    <row r="60" spans="40:40" x14ac:dyDescent="0.25">
-      <c r="AN60" s="15"/>
-    </row>
-    <row r="76" spans="23:40" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:48" ht="171" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>224</v>
+      </c>
+      <c r="B48" t="s">
+        <v>40</v>
+      </c>
+      <c r="C48">
+        <v>235</v>
+      </c>
+      <c r="D48" s="27" t="s">
+        <v>226</v>
+      </c>
+      <c r="E48" t="s">
+        <v>227</v>
+      </c>
+      <c r="F48" t="s">
+        <v>243</v>
+      </c>
+      <c r="G48" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H48" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="I48" s="7">
+        <v>47</v>
+      </c>
+      <c r="O48" s="17">
+        <v>9780670834280</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q48" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="R48" s="3">
+        <v>22</v>
+      </c>
+      <c r="X48" s="18">
+        <v>9780140445800</v>
+      </c>
+      <c r="Y48" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z48" s="4" t="str">
+        <f>Q48</f>
+        <v>Viking Adult</v>
+      </c>
+      <c r="AA48" s="5">
+        <v>13</v>
+      </c>
+      <c r="AG48" s="8">
+        <v>9780141914138</v>
+      </c>
+      <c r="AH48" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/saragossa.jpg</v>
+      </c>
+      <c r="AN48" s="23" t="s">
+        <v>225</v>
+      </c>
+      <c r="AS48" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT48" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV48" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="49" spans="1:51" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>229</v>
+      </c>
+      <c r="B49" t="s">
+        <v>40</v>
+      </c>
+      <c r="C49">
+        <v>450</v>
+      </c>
+      <c r="D49" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="E49" t="s">
+        <v>230</v>
+      </c>
+      <c r="F49" t="s">
+        <v>68</v>
+      </c>
+      <c r="P49" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q49" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="R49" s="3">
+        <v>28</v>
+      </c>
+      <c r="X49" s="15">
+        <v>9789639241459</v>
+      </c>
+      <c r="Y49" s="4"/>
+      <c r="Z49" s="4"/>
+      <c r="AH49" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/birch-grove.jpg</v>
+      </c>
+      <c r="AN49" s="24" t="s">
+        <v>232</v>
+      </c>
+      <c r="AS49" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT49" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV49" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:51" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>234</v>
+      </c>
+      <c r="B50" t="s">
+        <v>40</v>
+      </c>
+      <c r="C50">
+        <v>750</v>
+      </c>
+      <c r="D50" s="27" t="s">
+        <v>233</v>
+      </c>
+      <c r="E50" t="s">
+        <v>235</v>
+      </c>
+      <c r="F50" t="s">
+        <v>236</v>
+      </c>
+      <c r="O50" s="6"/>
+      <c r="P50" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q50" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="R50" s="3">
+        <v>22</v>
+      </c>
+      <c r="X50" s="15">
+        <v>9780810108066</v>
+      </c>
+      <c r="Y50" s="4"/>
+      <c r="Z50" s="4"/>
+      <c r="AH50" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/danton-thermidor.jpg</v>
+      </c>
+      <c r="AN50" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="AS50" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT50" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV50" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:51" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>239</v>
+      </c>
+      <c r="B51" t="s">
+        <v>40</v>
+      </c>
+      <c r="C51">
+        <v>800</v>
+      </c>
+      <c r="D51" s="27" t="s">
+        <v>240</v>
+      </c>
+      <c r="E51" t="s">
+        <v>242</v>
+      </c>
+      <c r="F51" t="s">
+        <v>52</v>
+      </c>
+      <c r="P51" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q51" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="R51" s="3">
+        <v>39</v>
+      </c>
+      <c r="X51" s="15">
+        <v>9789637326899</v>
+      </c>
+      <c r="Y51" s="4"/>
+      <c r="Z51" s="4"/>
+      <c r="AH51" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/coming-spring.jpg</v>
+      </c>
+      <c r="AN51" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="AS51" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT51" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV51" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="52" spans="1:51" ht="399.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>245</v>
+      </c>
+      <c r="B52" t="s">
+        <v>40</v>
+      </c>
+      <c r="C52">
+        <v>900</v>
+      </c>
+      <c r="D52" s="27" t="s">
+        <v>246</v>
+      </c>
+      <c r="E52" t="s">
+        <v>242</v>
+      </c>
+      <c r="F52" t="s">
+        <v>247</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q52" s="7" t="s">
+        <v>248</v>
+      </c>
+      <c r="R52" s="3">
+        <v>24.99</v>
+      </c>
+      <c r="X52" s="15">
+        <v>9781589881846</v>
+      </c>
+      <c r="Y52" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z52" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="AA52" s="5">
+        <v>9.99</v>
+      </c>
+      <c r="AG52" s="8">
+        <v>9781589883802</v>
+      </c>
+      <c r="AH52" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/the-homless.jpg</v>
+      </c>
+      <c r="AN52" s="20" t="s">
+        <v>244</v>
+      </c>
+      <c r="AS52" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT52" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV52" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="53" spans="1:51" ht="242.25" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>254</v>
+      </c>
+      <c r="B53" t="s">
+        <v>88</v>
+      </c>
+      <c r="C53">
+        <v>900</v>
+      </c>
+      <c r="D53" s="27" t="s">
+        <v>250</v>
+      </c>
+      <c r="E53" t="s">
+        <v>251</v>
+      </c>
+      <c r="P53" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q53" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="R53" s="3">
+        <v>57.99</v>
+      </c>
+      <c r="X53" s="15">
+        <v>9781412865432</v>
+      </c>
+      <c r="Y53" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z53" s="5" t="str">
+        <f>Q53</f>
+        <v>Routledge</v>
+      </c>
+      <c r="AA53" s="5">
+        <v>44</v>
+      </c>
+      <c r="AG53" s="8">
+        <v>9781351623674</v>
+      </c>
+      <c r="AH53" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/beniowski.jpg</v>
+      </c>
+      <c r="AN53" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="AS53" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT53" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV53" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="54" spans="1:51" ht="285" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>255</v>
+      </c>
+      <c r="B54" t="s">
+        <v>79</v>
+      </c>
+      <c r="C54">
+        <v>600</v>
+      </c>
+      <c r="D54" s="27" t="s">
+        <v>256</v>
+      </c>
+      <c r="E54" t="s">
+        <v>257</v>
+      </c>
+      <c r="F54" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="P54" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q54" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="R54" s="3">
+        <v>50</v>
+      </c>
+      <c r="X54" s="15">
+        <v>9780316498845</v>
+      </c>
+      <c r="Y54" s="4"/>
+      <c r="Z54" s="4"/>
+      <c r="AH54" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/witcher-set.jpg</v>
+      </c>
+      <c r="AN54" s="23" t="s">
+        <v>260</v>
+      </c>
+      <c r="AS54" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT54" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV54" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="55" spans="1:51" ht="370.5" x14ac:dyDescent="0.45">
+      <c r="A55" t="s">
+        <v>261</v>
+      </c>
+      <c r="B55" t="s">
+        <v>79</v>
+      </c>
+      <c r="C55">
+        <v>850</v>
+      </c>
+      <c r="D55" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="E55" t="s">
+        <v>257</v>
+      </c>
+      <c r="F55" t="s">
+        <v>263</v>
+      </c>
+      <c r="P55" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q55" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="R55" s="3">
+        <v>18</v>
+      </c>
+      <c r="X55" s="15">
+        <v>9780316423694</v>
+      </c>
+      <c r="Y55" s="4"/>
+      <c r="Z55" s="4"/>
+      <c r="AH55" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/tower-fools.jpg</v>
+      </c>
+      <c r="AN55" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="AS55" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT55" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV55" t="s">
+        <v>31</v>
+      </c>
+      <c r="AX55" t="s">
+        <v>265</v>
+      </c>
+      <c r="AY55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:51" ht="285" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>266</v>
+      </c>
+      <c r="B56" t="s">
+        <v>79</v>
+      </c>
+      <c r="C56">
+        <v>860</v>
+      </c>
+      <c r="D56" s="27" t="s">
+        <v>267</v>
+      </c>
+      <c r="E56" t="s">
+        <v>257</v>
+      </c>
+      <c r="F56" t="s">
+        <v>263</v>
+      </c>
+      <c r="P56" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q56" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="R56" s="3">
+        <v>9.99</v>
+      </c>
+      <c r="X56" s="15">
+        <v>9780316423717</v>
+      </c>
+      <c r="Y56" s="4"/>
+      <c r="Z56" s="4"/>
+      <c r="AH56" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/warrior-god.jpg</v>
+      </c>
+      <c r="AN56" s="23" t="s">
+        <v>268</v>
+      </c>
+      <c r="AS56" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT56" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV56" t="s">
+        <v>31</v>
+      </c>
+      <c r="AX56" t="s">
+        <v>265</v>
+      </c>
+      <c r="AY56">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:51" ht="356.25" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>269</v>
+      </c>
+      <c r="B57" t="s">
+        <v>79</v>
+      </c>
+      <c r="C57">
+        <v>870</v>
+      </c>
+      <c r="D57" s="27" t="s">
+        <v>270</v>
+      </c>
+      <c r="E57" t="s">
+        <v>257</v>
+      </c>
+      <c r="F57" t="s">
+        <v>263</v>
+      </c>
+      <c r="P57" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q57" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="R57" s="3">
+        <v>16</v>
+      </c>
+      <c r="X57" s="15">
+        <v>9780316423755</v>
+      </c>
+      <c r="Y57" s="4"/>
+      <c r="Z57" s="4"/>
+      <c r="AH57" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/light-perpetua.jpg</v>
+      </c>
+      <c r="AN57" s="22" t="s">
+        <v>271</v>
+      </c>
+      <c r="AS57" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT57" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV57" t="s">
+        <v>31</v>
+      </c>
+      <c r="AX57" t="s">
+        <v>265</v>
+      </c>
+      <c r="AY57">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:51" x14ac:dyDescent="0.45">
+      <c r="P58" s="2"/>
+      <c r="Q58" s="7"/>
+      <c r="Y58" s="4"/>
+      <c r="Z58" s="4"/>
+      <c r="AN58" s="21"/>
+    </row>
+    <row r="59" spans="1:51" x14ac:dyDescent="0.45">
+      <c r="P59" s="2"/>
+      <c r="Q59" s="7"/>
+      <c r="Y59" s="4"/>
+      <c r="Z59" s="4"/>
+      <c r="AN59" s="25"/>
+    </row>
+    <row r="60" spans="1:51" x14ac:dyDescent="0.45">
+      <c r="P60" s="2"/>
+      <c r="Q60" s="7"/>
+      <c r="Y60" s="4"/>
+      <c r="Z60" s="4"/>
+      <c r="AN60" s="25"/>
+    </row>
+    <row r="61" spans="1:51" x14ac:dyDescent="0.45">
+      <c r="Q61" s="7"/>
+      <c r="Y61" s="4"/>
+      <c r="Z61" s="4"/>
+    </row>
+    <row r="62" spans="1:51" x14ac:dyDescent="0.45">
+      <c r="Q62" s="7"/>
+      <c r="Y62" s="4"/>
+      <c r="Z62" s="4"/>
+    </row>
+    <row r="63" spans="1:51" x14ac:dyDescent="0.45">
+      <c r="Q63" s="7"/>
+      <c r="Y63" s="4"/>
+      <c r="Z63" s="4"/>
+    </row>
+    <row r="64" spans="1:51" x14ac:dyDescent="0.45">
+      <c r="Q64" s="7"/>
+      <c r="Y64" s="4"/>
+      <c r="Z64" s="4"/>
+    </row>
+    <row r="65" spans="17:40" x14ac:dyDescent="0.45">
+      <c r="Q65" s="7"/>
+      <c r="Y65" s="4"/>
+      <c r="Z65" s="4"/>
+    </row>
+    <row r="66" spans="17:40" x14ac:dyDescent="0.45">
+      <c r="Q66" s="7"/>
+      <c r="Y66" s="4"/>
+      <c r="Z66" s="4"/>
+    </row>
+    <row r="67" spans="17:40" x14ac:dyDescent="0.45">
+      <c r="Q67" s="7"/>
+      <c r="Y67" s="4"/>
+      <c r="Z67" s="4"/>
+    </row>
+    <row r="68" spans="17:40" x14ac:dyDescent="0.45">
+      <c r="Q68" s="7"/>
+      <c r="Y68" s="4"/>
+      <c r="Z68" s="4"/>
+    </row>
+    <row r="69" spans="17:40" x14ac:dyDescent="0.45">
+      <c r="Q69" s="7"/>
+      <c r="Y69" s="4"/>
+      <c r="Z69" s="4"/>
+    </row>
+    <row r="70" spans="17:40" x14ac:dyDescent="0.45">
+      <c r="Q70" s="7"/>
+      <c r="Y70" s="4"/>
+      <c r="Z70" s="4"/>
+    </row>
+    <row r="71" spans="17:40" x14ac:dyDescent="0.45">
+      <c r="Q71" s="7"/>
+      <c r="Y71" s="4"/>
+      <c r="Z71" s="4"/>
+      <c r="AA71" s="4"/>
+    </row>
+    <row r="72" spans="17:40" x14ac:dyDescent="0.45">
+      <c r="Q72" s="7"/>
+      <c r="Y72" s="4"/>
+      <c r="Z72" s="4"/>
+    </row>
+    <row r="73" spans="17:40" x14ac:dyDescent="0.45">
+      <c r="Q73" s="7"/>
+      <c r="Y73" s="4"/>
+      <c r="Z73" s="4"/>
+    </row>
+    <row r="74" spans="17:40" x14ac:dyDescent="0.45">
+      <c r="Q74" s="7"/>
+      <c r="Y74" s="4"/>
+      <c r="Z74" s="4"/>
+    </row>
+    <row r="75" spans="17:40" x14ac:dyDescent="0.45">
+      <c r="Q75" s="7"/>
+      <c r="Y75" s="4"/>
+      <c r="Z75" s="4"/>
+      <c r="AG75" s="5"/>
+    </row>
+    <row r="76" spans="17:40" x14ac:dyDescent="0.45">
+      <c r="Q76" s="7"/>
       <c r="W76" s="9"/>
+      <c r="Y76" s="4"/>
+      <c r="Z76" s="4"/>
       <c r="AF76" s="8"/>
       <c r="AG76" s="5"/>
-      <c r="AM76" s="12"/>
-      <c r="AN76"/>
-    </row>
-    <row r="77" spans="23:40" x14ac:dyDescent="0.25">
+      <c r="AM76" s="11"/>
+      <c r="AN76" s="24"/>
+    </row>
+    <row r="77" spans="17:40" x14ac:dyDescent="0.45">
+      <c r="Q77" s="7"/>
       <c r="W77" s="9"/>
+      <c r="Y77" s="4"/>
+      <c r="Z77" s="4"/>
       <c r="AF77" s="8"/>
       <c r="AG77" s="5"/>
-      <c r="AM77" s="12"/>
-      <c r="AN77"/>
-    </row>
-    <row r="78" spans="23:40" x14ac:dyDescent="0.25">
+      <c r="AM77" s="11"/>
+      <c r="AN77" s="24"/>
+    </row>
+    <row r="78" spans="17:40" x14ac:dyDescent="0.45">
+      <c r="Q78" s="7"/>
       <c r="W78" s="9"/>
+      <c r="Y78" s="4"/>
+      <c r="Z78" s="4"/>
       <c r="AF78" s="8"/>
       <c r="AG78" s="5"/>
-      <c r="AM78" s="12"/>
-      <c r="AN78"/>
-    </row>
-    <row r="79" spans="23:40" x14ac:dyDescent="0.25">
+      <c r="AM78" s="11"/>
+      <c r="AN78" s="24"/>
+    </row>
+    <row r="79" spans="17:40" x14ac:dyDescent="0.45">
+      <c r="Q79" s="7"/>
       <c r="W79" s="9"/>
+      <c r="Y79" s="4"/>
       <c r="AF79" s="8"/>
       <c r="AG79" s="5"/>
-      <c r="AM79" s="12"/>
-      <c r="AN79"/>
-    </row>
-    <row r="80" spans="23:40" x14ac:dyDescent="0.25">
+      <c r="AM79" s="11"/>
+      <c r="AN79" s="24"/>
+    </row>
+    <row r="80" spans="17:40" x14ac:dyDescent="0.45">
+      <c r="Q80" s="7"/>
       <c r="W80" s="9"/>
       <c r="AF80" s="8"/>
       <c r="AG80" s="5"/>
-      <c r="AM80" s="12"/>
-      <c r="AN80"/>
-    </row>
-    <row r="81" spans="23:40" x14ac:dyDescent="0.25">
+      <c r="AM80" s="11"/>
+      <c r="AN80" s="24"/>
+    </row>
+    <row r="81" spans="17:40" x14ac:dyDescent="0.45">
+      <c r="Q81" s="7"/>
       <c r="W81" s="9"/>
       <c r="AF81" s="8"/>
       <c r="AG81" s="5"/>
-      <c r="AM81" s="12"/>
-      <c r="AN81"/>
-    </row>
-    <row r="82" spans="23:40" x14ac:dyDescent="0.25">
+      <c r="AM81" s="11"/>
+      <c r="AN81" s="24"/>
+    </row>
+    <row r="82" spans="17:40" x14ac:dyDescent="0.45">
+      <c r="Q82" s="7"/>
       <c r="W82" s="9"/>
       <c r="AF82" s="8"/>
       <c r="AG82" s="5"/>
-      <c r="AM82" s="12"/>
-      <c r="AN82"/>
-    </row>
-    <row r="83" spans="23:40" x14ac:dyDescent="0.25">
+      <c r="AM82" s="11"/>
+      <c r="AN82" s="24"/>
+    </row>
+    <row r="83" spans="17:40" x14ac:dyDescent="0.45">
       <c r="W83" s="9"/>
       <c r="AF83" s="8"/>
       <c r="AG83" s="5"/>
-      <c r="AM83" s="12"/>
-      <c r="AN83"/>
-    </row>
-    <row r="84" spans="23:40" x14ac:dyDescent="0.25">
+      <c r="AM83" s="11"/>
+      <c r="AN83" s="24"/>
+    </row>
+    <row r="84" spans="17:40" x14ac:dyDescent="0.45">
       <c r="W84" s="9"/>
       <c r="AF84" s="8"/>
-      <c r="AG84" s="5"/>
-      <c r="AM84" s="12"/>
-      <c r="AN84"/>
+      <c r="AM84" s="11"/>
+      <c r="AN84" s="24"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G47:H1048576 Y85:Z1048576 P85:Q1048576 X76:Y84 O76:P84 O44 AG44 X44 P48:P75 Q43:Q75 Y47:Y75 Z48:Z75" xr:uid="{D2C177B6-092A-4420-B1E2-D1681CD512E9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y85:Z1048576 P85:Q1048576 Q43:Q47 O76:P84 O44 AG44 X44 Y80:Y84 H72:H1048576 P61:P75 G49:G1048576 G47 X75:X83" xr:uid="{D2C177B6-092A-4420-B1E2-D1681CD512E9}">
       <formula1>"hardcover, paperback, eBook, audiobook1"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR76:AS84 AS85:AT1048576 AS1:AT75" xr:uid="{F1FB7CD6-B38A-4A39-862C-8A1111411C8C}">

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/bookstore-main/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/the-polish-atheneum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="534" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45562432-AB08-494D-8F34-24FDFCAF8E00}"/>
+  <xr:revisionPtr revIDLastSave="562" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D79AA3AD-F446-4B99-B75E-EA18798A32E2}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
+    <workbookView xWindow="3060" yWindow="570" windowWidth="23220" windowHeight="14940" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="277">
   <si>
     <t>cover</t>
   </si>
@@ -951,6 +951,21 @@
 &lt;p&gt;"This is historical fantasy done right." —Publishers Weekly (starred review)&lt;/p&gt;
 &lt;p&gt;“A fantastic novel that any fan of The Witcher will instantly appreciate.” —The Gamer&lt;/p&gt;
 &lt;p&gt;“Sapkowski's energetic and satirical prose as well as the unconventional setting makes this a highly enjoyable historical fantasy.” —Booklist&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>red-prince</t>
+  </si>
+  <si>
+    <t>The Red Prince: The Fall of a Dynasty and the Rise of Modern Europe</t>
+  </si>
+  <si>
+    <t>Timothy Snyder</t>
+  </si>
+  <si>
+    <t>Vintage</t>
+  </si>
+  <si>
+    <t>Wilhelm Von Habsburg wore the uniform of the Austrian officer, the court regalia of a Habsburg archduke, the simple suit of a Parisian exile, the collar of the Order of the Golden Fleece, and, every so often, a dress. He could handle a saber, a pistol, a rudder, or a golf club; he handled women by necessity and men for pleasure. He spoke the Italian of his archduchess mother, the German of his archduke father, the English of his British royal friends, the Polish of the country his father wished to rule, and the Ukrainian of the land Wilhelm wished to rule himself. In this exhilarating narrative history, prize-winning historian Timothy D. Snyder offers an indelible portrait of an aristocrat whose life personifies the wrenching upheavals of the first half of the twentieth century, as the rule of empire gave way to the new politics of nationalism. Coming of age during the First World War, Wilhelm repudiated his family to fight alongside Ukrainian peasants in hopes that he would become their king. When this dream collapsed he became, by turns, an ally of German imperialists, a notorious French lover, an angry Austrian monarchist, a calm opponent of Hitler, and a British spy against Stalin. Played out in Europe's glittering capitals and bloody battlefields, in extravagant ski resorts and dank prison cells, The Red Prince captures an extraordinary moment in the history of Europe, in which the old order of the past was giving way to an undefined future-and in which everything, including identity itself, seemed up for grabs.</t>
   </si>
 </sst>
 </file>
@@ -1483,28 +1498,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01CE5F32-AD1D-47CB-A8F1-52ACBFFA0BE8}">
   <dimension ref="A1:AY84"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.1328125" customWidth="1"/>
-    <col min="2" max="3" width="13.73046875" customWidth="1"/>
+    <col min="1" max="1" width="29.140625" customWidth="1"/>
+    <col min="2" max="3" width="13.7109375" customWidth="1"/>
     <col min="4" max="4" width="46" style="27" customWidth="1"/>
     <col min="5" max="6" width="46" customWidth="1"/>
-    <col min="7" max="9" width="9.1328125" style="7"/>
+    <col min="7" max="9" width="9.140625" style="7"/>
     <col min="10" max="11" width="9" style="7"/>
-    <col min="12" max="14" width="9.1328125" style="7"/>
+    <col min="12" max="14" width="9.140625" style="7"/>
     <col min="15" max="15" width="16" style="12" customWidth="1"/>
-    <col min="16" max="23" width="9.1328125" style="3"/>
+    <col min="16" max="23" width="9.140625" style="3"/>
     <col min="24" max="24" width="17" style="15" customWidth="1"/>
-    <col min="25" max="32" width="9.1328125" style="5"/>
+    <col min="25" max="32" width="9.140625" style="5"/>
     <col min="33" max="33" width="22" style="8" customWidth="1"/>
-    <col min="34" max="34" width="26.265625" customWidth="1"/>
+    <col min="34" max="34" width="26.28515625" customWidth="1"/>
     <col min="37" max="37" width="16" customWidth="1"/>
-    <col min="39" max="39" width="21.1328125" customWidth="1"/>
-    <col min="40" max="40" width="95.86328125" style="19" customWidth="1"/>
-    <col min="41" max="44" width="19.73046875" customWidth="1"/>
+    <col min="39" max="39" width="21.140625" customWidth="1"/>
+    <col min="40" max="40" width="95.85546875" style="19" customWidth="1"/>
+    <col min="41" max="44" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -1659,7 +1674,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -1727,7 +1742,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1785,7 +1800,7 @@
         <v>9781429964395</v>
       </c>
       <c r="AH3" t="str">
-        <f t="shared" ref="AH3:AH57" si="0">"covers/" &amp; A3 &amp; ".jpg"</f>
+        <f t="shared" ref="AH3:AH58" si="0">"covers/" &amp; A3 &amp; ".jpg"</f>
         <v>covers/peasant-prince.jpg</v>
       </c>
       <c r="AS3" t="s">
@@ -1798,7 +1813,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -1864,7 +1879,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>77</v>
       </c>
@@ -1928,7 +1943,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1992,7 +2007,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -2052,7 +2067,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -2119,7 +2134,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -2172,7 +2187,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -2226,7 +2241,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -2279,7 +2294,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>62</v>
       </c>
@@ -2345,7 +2360,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -2401,7 +2416,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>69</v>
       </c>
@@ -2454,7 +2469,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>73</v>
       </c>
@@ -2504,7 +2519,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>74</v>
       </c>
@@ -2554,7 +2569,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>130</v>
       </c>
@@ -2604,7 +2619,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>81</v>
       </c>
@@ -2659,7 +2674,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>129</v>
       </c>
@@ -2714,7 +2729,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>85</v>
       </c>
@@ -2769,7 +2784,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>86</v>
       </c>
@@ -2824,7 +2839,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>90</v>
       </c>
@@ -2877,7 +2892,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>94</v>
       </c>
@@ -2930,7 +2945,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>128</v>
       </c>
@@ -2983,7 +2998,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>112</v>
       </c>
@@ -3042,7 +3057,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:51" ht="142.5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:51" ht="165" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>101</v>
       </c>
@@ -3126,7 +3141,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>102</v>
       </c>
@@ -3181,7 +3196,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>111</v>
       </c>
@@ -3242,7 +3257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>110</v>
       </c>
@@ -3303,7 +3318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>123</v>
       </c>
@@ -3378,7 +3393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>124</v>
       </c>
@@ -3453,7 +3468,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>125</v>
       </c>
@@ -3518,7 +3533,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>157</v>
       </c>
@@ -3563,7 +3578,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>161</v>
       </c>
@@ -3619,7 +3634,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>164</v>
       </c>
@@ -3664,7 +3679,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>152</v>
       </c>
@@ -3709,7 +3724,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>153</v>
       </c>
@@ -3766,7 +3781,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>154</v>
       </c>
@@ -3820,7 +3835,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>155</v>
       </c>
@@ -3877,7 +3892,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>209</v>
       </c>
@@ -3920,7 +3935,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>156</v>
       </c>
@@ -3966,7 +3981,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>205</v>
       </c>
@@ -4026,7 +4041,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>197</v>
       </c>
@@ -4095,7 +4110,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>200</v>
       </c>
@@ -4164,7 +4179,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>199</v>
       </c>
@@ -4233,7 +4248,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>198</v>
       </c>
@@ -4302,7 +4317,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:48" ht="327.75" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:48" ht="375" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>218</v>
       </c>
@@ -4359,7 +4374,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:48" ht="171" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:48" ht="180" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>224</v>
       </c>
@@ -4432,7 +4447,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>229</v>
       </c>
@@ -4482,7 +4497,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>234</v>
       </c>
@@ -4533,7 +4548,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>239</v>
       </c>
@@ -4583,7 +4598,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:51" ht="399.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:51" ht="399.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>245</v>
       </c>
@@ -4643,7 +4658,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="1:51" ht="242.25" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:51" ht="285" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>254</v>
       </c>
@@ -4701,7 +4716,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:51" ht="285" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:51" ht="315" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>255</v>
       </c>
@@ -4751,7 +4766,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:51" ht="370.5" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:51" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>261</v>
       </c>
@@ -4807,7 +4822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:51" ht="285" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:51" ht="330" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>266</v>
       </c>
@@ -4863,7 +4878,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:51" ht="356.25" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:51" ht="390" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>269</v>
       </c>
@@ -4919,105 +4934,168 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:51" x14ac:dyDescent="0.45">
-      <c r="P58" s="2"/>
-      <c r="Q58" s="7"/>
-      <c r="Y58" s="4"/>
+    <row r="58" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>272</v>
+      </c>
+      <c r="B58" t="s">
+        <v>88</v>
+      </c>
+      <c r="C58">
+        <v>553</v>
+      </c>
+      <c r="D58" s="27" t="s">
+        <v>273</v>
+      </c>
+      <c r="E58" t="s">
+        <v>274</v>
+      </c>
+      <c r="G58" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H58" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="I58" s="7">
+        <v>28</v>
+      </c>
+      <c r="O58" s="12">
+        <v>9780465002375</v>
+      </c>
+      <c r="P58" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q58" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="R58" s="3">
+        <v>22</v>
+      </c>
+      <c r="X58" s="15">
+        <v>9781845951207</v>
+      </c>
+      <c r="Y58" s="4" t="s">
+        <v>118</v>
+      </c>
       <c r="Z58" s="4"/>
-      <c r="AN58" s="21"/>
-    </row>
-    <row r="59" spans="1:51" x14ac:dyDescent="0.45">
+      <c r="AA58" s="5">
+        <v>8.99</v>
+      </c>
+      <c r="AG58" s="8">
+        <v>9780465012473</v>
+      </c>
+      <c r="AH58" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/red-prince.jpg</v>
+      </c>
+      <c r="AN58" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="AS58" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT58" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV58" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="59" spans="1:51" x14ac:dyDescent="0.25">
       <c r="P59" s="2"/>
       <c r="Q59" s="7"/>
       <c r="Y59" s="4"/>
       <c r="Z59" s="4"/>
       <c r="AN59" s="25"/>
     </row>
-    <row r="60" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:51" x14ac:dyDescent="0.25">
       <c r="P60" s="2"/>
       <c r="Q60" s="7"/>
       <c r="Y60" s="4"/>
       <c r="Z60" s="4"/>
       <c r="AN60" s="25"/>
     </row>
-    <row r="61" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="P61" s="2"/>
       <c r="Q61" s="7"/>
       <c r="Y61" s="4"/>
       <c r="Z61" s="4"/>
     </row>
-    <row r="62" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="P62" s="2"/>
       <c r="Q62" s="7"/>
       <c r="Y62" s="4"/>
       <c r="Z62" s="4"/>
     </row>
-    <row r="63" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="P63" s="2"/>
       <c r="Q63" s="7"/>
       <c r="Y63" s="4"/>
       <c r="Z63" s="4"/>
     </row>
-    <row r="64" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:51" x14ac:dyDescent="0.25">
       <c r="Q64" s="7"/>
       <c r="Y64" s="4"/>
       <c r="Z64" s="4"/>
     </row>
-    <row r="65" spans="17:40" x14ac:dyDescent="0.45">
+    <row r="65" spans="17:40" x14ac:dyDescent="0.25">
       <c r="Q65" s="7"/>
       <c r="Y65" s="4"/>
       <c r="Z65" s="4"/>
     </row>
-    <row r="66" spans="17:40" x14ac:dyDescent="0.45">
+    <row r="66" spans="17:40" x14ac:dyDescent="0.25">
       <c r="Q66" s="7"/>
       <c r="Y66" s="4"/>
       <c r="Z66" s="4"/>
     </row>
-    <row r="67" spans="17:40" x14ac:dyDescent="0.45">
+    <row r="67" spans="17:40" x14ac:dyDescent="0.25">
       <c r="Q67" s="7"/>
       <c r="Y67" s="4"/>
       <c r="Z67" s="4"/>
     </row>
-    <row r="68" spans="17:40" x14ac:dyDescent="0.45">
+    <row r="68" spans="17:40" x14ac:dyDescent="0.25">
       <c r="Q68" s="7"/>
       <c r="Y68" s="4"/>
       <c r="Z68" s="4"/>
     </row>
-    <row r="69" spans="17:40" x14ac:dyDescent="0.45">
+    <row r="69" spans="17:40" x14ac:dyDescent="0.25">
       <c r="Q69" s="7"/>
       <c r="Y69" s="4"/>
       <c r="Z69" s="4"/>
     </row>
-    <row r="70" spans="17:40" x14ac:dyDescent="0.45">
+    <row r="70" spans="17:40" x14ac:dyDescent="0.25">
       <c r="Q70" s="7"/>
       <c r="Y70" s="4"/>
       <c r="Z70" s="4"/>
     </row>
-    <row r="71" spans="17:40" x14ac:dyDescent="0.45">
+    <row r="71" spans="17:40" x14ac:dyDescent="0.25">
       <c r="Q71" s="7"/>
       <c r="Y71" s="4"/>
       <c r="Z71" s="4"/>
       <c r="AA71" s="4"/>
     </row>
-    <row r="72" spans="17:40" x14ac:dyDescent="0.45">
+    <row r="72" spans="17:40" x14ac:dyDescent="0.25">
       <c r="Q72" s="7"/>
       <c r="Y72" s="4"/>
       <c r="Z72" s="4"/>
     </row>
-    <row r="73" spans="17:40" x14ac:dyDescent="0.45">
+    <row r="73" spans="17:40" x14ac:dyDescent="0.25">
       <c r="Q73" s="7"/>
       <c r="Y73" s="4"/>
       <c r="Z73" s="4"/>
     </row>
-    <row r="74" spans="17:40" x14ac:dyDescent="0.45">
+    <row r="74" spans="17:40" x14ac:dyDescent="0.25">
       <c r="Q74" s="7"/>
       <c r="Y74" s="4"/>
       <c r="Z74" s="4"/>
     </row>
-    <row r="75" spans="17:40" x14ac:dyDescent="0.45">
+    <row r="75" spans="17:40" x14ac:dyDescent="0.25">
       <c r="Q75" s="7"/>
       <c r="Y75" s="4"/>
       <c r="Z75" s="4"/>
       <c r="AG75" s="5"/>
     </row>
-    <row r="76" spans="17:40" x14ac:dyDescent="0.45">
+    <row r="76" spans="17:40" x14ac:dyDescent="0.25">
       <c r="Q76" s="7"/>
       <c r="W76" s="9"/>
       <c r="Y76" s="4"/>
@@ -5027,7 +5105,7 @@
       <c r="AM76" s="11"/>
       <c r="AN76" s="24"/>
     </row>
-    <row r="77" spans="17:40" x14ac:dyDescent="0.45">
+    <row r="77" spans="17:40" x14ac:dyDescent="0.25">
       <c r="Q77" s="7"/>
       <c r="W77" s="9"/>
       <c r="Y77" s="4"/>
@@ -5037,7 +5115,7 @@
       <c r="AM77" s="11"/>
       <c r="AN77" s="24"/>
     </row>
-    <row r="78" spans="17:40" x14ac:dyDescent="0.45">
+    <row r="78" spans="17:40" x14ac:dyDescent="0.25">
       <c r="Q78" s="7"/>
       <c r="W78" s="9"/>
       <c r="Y78" s="4"/>
@@ -5047,7 +5125,7 @@
       <c r="AM78" s="11"/>
       <c r="AN78" s="24"/>
     </row>
-    <row r="79" spans="17:40" x14ac:dyDescent="0.45">
+    <row r="79" spans="17:40" x14ac:dyDescent="0.25">
       <c r="Q79" s="7"/>
       <c r="W79" s="9"/>
       <c r="Y79" s="4"/>
@@ -5056,7 +5134,7 @@
       <c r="AM79" s="11"/>
       <c r="AN79" s="24"/>
     </row>
-    <row r="80" spans="17:40" x14ac:dyDescent="0.45">
+    <row r="80" spans="17:40" x14ac:dyDescent="0.25">
       <c r="Q80" s="7"/>
       <c r="W80" s="9"/>
       <c r="AF80" s="8"/>
@@ -5064,7 +5142,7 @@
       <c r="AM80" s="11"/>
       <c r="AN80" s="24"/>
     </row>
-    <row r="81" spans="17:40" x14ac:dyDescent="0.45">
+    <row r="81" spans="17:40" x14ac:dyDescent="0.25">
       <c r="Q81" s="7"/>
       <c r="W81" s="9"/>
       <c r="AF81" s="8"/>
@@ -5072,7 +5150,7 @@
       <c r="AM81" s="11"/>
       <c r="AN81" s="24"/>
     </row>
-    <row r="82" spans="17:40" x14ac:dyDescent="0.45">
+    <row r="82" spans="17:40" x14ac:dyDescent="0.25">
       <c r="Q82" s="7"/>
       <c r="W82" s="9"/>
       <c r="AF82" s="8"/>
@@ -5080,14 +5158,14 @@
       <c r="AM82" s="11"/>
       <c r="AN82" s="24"/>
     </row>
-    <row r="83" spans="17:40" x14ac:dyDescent="0.45">
+    <row r="83" spans="17:40" x14ac:dyDescent="0.25">
       <c r="W83" s="9"/>
       <c r="AF83" s="8"/>
       <c r="AG83" s="5"/>
       <c r="AM83" s="11"/>
       <c r="AN83" s="24"/>
     </row>
-    <row r="84" spans="17:40" x14ac:dyDescent="0.45">
+    <row r="84" spans="17:40" x14ac:dyDescent="0.25">
       <c r="W84" s="9"/>
       <c r="AF84" s="8"/>
       <c r="AM84" s="11"/>
@@ -5096,7 +5174,7 @@
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y85:Z1048576 P85:Q1048576 Q43:Q47 O76:P84 O44 AG44 X44 Y80:Y84 H72:H1048576 P61:P75 G49:G1048576 G47 X75:X83" xr:uid="{D2C177B6-092A-4420-B1E2-D1681CD512E9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y85:Z1048576 P85:Q1048576 Q43:Q47 O76:P84 O44 AG44 X44 Y80:Y84 H72:H1048576 G59:G1048576 X75:X83 G47 G49:G57 P64:P75" xr:uid="{D2C177B6-092A-4420-B1E2-D1681CD512E9}">
       <formula1>"hardcover, paperback, eBook, audiobook1"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR76:AS84 AS85:AT1048576 AS1:AT75" xr:uid="{F1FB7CD6-B38A-4A39-862C-8A1111411C8C}">

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/the-polish-atheneum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="562" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D79AA3AD-F446-4B99-B75E-EA18798A32E2}"/>
+  <xr:revisionPtr revIDLastSave="563" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97FDDD71-CA26-4567-BEEA-CB445325E313}"/>
   <bookViews>
     <workbookView xWindow="3060" yWindow="570" windowWidth="23220" windowHeight="14940" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
@@ -841,9 +841,6 @@
 &lt;p&gt;The Homeless combines concrete detail about social issues—the urgent need for public hygiene and access to medical treatment, the effects of industrialization on health and the landscape, and the disinterest that people in power have in the disadvantaged—with beautiful, artistic passages of prose that sensitively probe the characters’ inner lives. The title comes not from the obvious reference to the impoverished people Dr. Judym concerns himself with, but from the unmoored status of the protagonist, the woman he loves, a mysterious engineer friend of his, his brother, and many others who find themselves rootless—emotionally and physically alienated by class divides and the social upheaval of industrialization. The Homeless is a portrait of the time and place it was written—Poland on the precipice of the twentieth century—that speaks to our current time and place.&lt;/p&gt;</t>
   </si>
   <si>
-    <t>the-homless</t>
-  </si>
-  <si>
     <t>The Homeless</t>
   </si>
   <si>
@@ -966,6 +963,9 @@
   </si>
   <si>
     <t>Wilhelm Von Habsburg wore the uniform of the Austrian officer, the court regalia of a Habsburg archduke, the simple suit of a Parisian exile, the collar of the Order of the Golden Fleece, and, every so often, a dress. He could handle a saber, a pistol, a rudder, or a golf club; he handled women by necessity and men for pleasure. He spoke the Italian of his archduchess mother, the German of his archduke father, the English of his British royal friends, the Polish of the country his father wished to rule, and the Ukrainian of the land Wilhelm wished to rule himself. In this exhilarating narrative history, prize-winning historian Timothy D. Snyder offers an indelible portrait of an aristocrat whose life personifies the wrenching upheavals of the first half of the twentieth century, as the rule of empire gave way to the new politics of nationalism. Coming of age during the First World War, Wilhelm repudiated his family to fight alongside Ukrainian peasants in hopes that he would become their king. When this dream collapsed he became, by turns, an ally of German imperialists, a notorious French lover, an angry Austrian monarchist, a calm opponent of Hitler, and a British spy against Stalin. Played out in Europe's glittering capitals and bloody battlefields, in extravagant ski resorts and dank prison cells, The Red Prince captures an extraordinary moment in the history of Europe, in which the old order of the past was giving way to an undefined future-and in which everything, including identity itself, seemed up for grabs.</t>
+  </si>
+  <si>
+    <t>the-homeless</t>
   </si>
 </sst>
 </file>
@@ -4458,7 +4458,7 @@
         <v>450</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="E49" t="s">
         <v>230</v>
@@ -4600,7 +4600,7 @@
     </row>
     <row r="52" spans="1:51" ht="399.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="B52" t="s">
         <v>40</v>
@@ -4609,19 +4609,19 @@
         <v>900</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E52" t="s">
         <v>242</v>
       </c>
       <c r="F52" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="P52" s="2" t="s">
         <v>117</v>
       </c>
       <c r="Q52" s="7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="R52" s="3">
         <v>24.99</v>
@@ -4633,7 +4633,7 @@
         <v>118</v>
       </c>
       <c r="Z52" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AA52" s="5">
         <v>9.99</v>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="AH52" t="str">
         <f t="shared" si="0"/>
-        <v>covers/the-homless.jpg</v>
+        <v>covers/the-homeless.jpg</v>
       </c>
       <c r="AN52" s="20" t="s">
         <v>244</v>
@@ -4660,7 +4660,7 @@
     </row>
     <row r="53" spans="1:51" ht="285" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B53" t="s">
         <v>88</v>
@@ -4669,16 +4669,16 @@
         <v>900</v>
       </c>
       <c r="D53" s="27" t="s">
+        <v>249</v>
+      </c>
+      <c r="E53" t="s">
         <v>250</v>
-      </c>
-      <c r="E53" t="s">
-        <v>251</v>
       </c>
       <c r="P53" s="2" t="s">
         <v>117</v>
       </c>
       <c r="Q53" s="7" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="R53" s="3">
         <v>57.99</v>
@@ -4704,7 +4704,7 @@
         <v>covers/beniowski.jpg</v>
       </c>
       <c r="AN53" s="22" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="AS53" t="s">
         <v>23</v>
@@ -4718,7 +4718,7 @@
     </row>
     <row r="54" spans="1:51" ht="315" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B54" t="s">
         <v>79</v>
@@ -4727,19 +4727,19 @@
         <v>600</v>
       </c>
       <c r="D54" s="27" t="s">
+        <v>255</v>
+      </c>
+      <c r="E54" t="s">
         <v>256</v>
       </c>
-      <c r="E54" t="s">
+      <c r="F54" s="28" t="s">
         <v>257</v>
-      </c>
-      <c r="F54" s="28" t="s">
-        <v>258</v>
       </c>
       <c r="P54" s="2" t="s">
         <v>117</v>
       </c>
       <c r="Q54" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="R54" s="3">
         <v>50</v>
@@ -4754,7 +4754,7 @@
         <v>covers/witcher-set.jpg</v>
       </c>
       <c r="AN54" s="23" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AS54" t="s">
         <v>23</v>
@@ -4768,7 +4768,7 @@
     </row>
     <row r="55" spans="1:51" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B55" t="s">
         <v>79</v>
@@ -4777,19 +4777,19 @@
         <v>850</v>
       </c>
       <c r="D55" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="E55" t="s">
+        <v>256</v>
+      </c>
+      <c r="F55" t="s">
         <v>262</v>
-      </c>
-      <c r="E55" t="s">
-        <v>257</v>
-      </c>
-      <c r="F55" t="s">
-        <v>263</v>
       </c>
       <c r="P55" s="2" t="s">
         <v>117</v>
       </c>
       <c r="Q55" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="R55" s="3">
         <v>18</v>
@@ -4804,7 +4804,7 @@
         <v>covers/tower-fools.jpg</v>
       </c>
       <c r="AN55" s="22" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AS55" t="s">
         <v>23</v>
@@ -4816,7 +4816,7 @@
         <v>31</v>
       </c>
       <c r="AX55" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AY55">
         <v>1</v>
@@ -4824,7 +4824,7 @@
     </row>
     <row r="56" spans="1:51" ht="330" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B56" t="s">
         <v>79</v>
@@ -4833,19 +4833,19 @@
         <v>860</v>
       </c>
       <c r="D56" s="27" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="E56" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F56" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P56" s="2" t="s">
         <v>117</v>
       </c>
       <c r="Q56" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="R56" s="3">
         <v>9.99</v>
@@ -4860,7 +4860,7 @@
         <v>covers/warrior-god.jpg</v>
       </c>
       <c r="AN56" s="23" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AS56" t="s">
         <v>23</v>
@@ -4872,7 +4872,7 @@
         <v>31</v>
       </c>
       <c r="AX56" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AY56">
         <v>2</v>
@@ -4880,7 +4880,7 @@
     </row>
     <row r="57" spans="1:51" ht="390" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B57" t="s">
         <v>79</v>
@@ -4889,19 +4889,19 @@
         <v>870</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E57" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="F57" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="P57" s="2" t="s">
         <v>117</v>
       </c>
       <c r="Q57" s="7" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="R57" s="3">
         <v>16</v>
@@ -4916,7 +4916,7 @@
         <v>covers/light-perpetua.jpg</v>
       </c>
       <c r="AN57" s="22" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AS57" t="s">
         <v>23</v>
@@ -4928,7 +4928,7 @@
         <v>31</v>
       </c>
       <c r="AX57" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AY57">
         <v>3</v>
@@ -4936,7 +4936,7 @@
     </row>
     <row r="58" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B58" t="s">
         <v>88</v>
@@ -4945,16 +4945,16 @@
         <v>553</v>
       </c>
       <c r="D58" s="27" t="s">
+        <v>272</v>
+      </c>
+      <c r="E58" t="s">
         <v>273</v>
-      </c>
-      <c r="E58" t="s">
-        <v>274</v>
       </c>
       <c r="G58" s="6" t="s">
         <v>116</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I58" s="7">
         <v>28</v>
@@ -4966,7 +4966,7 @@
         <v>117</v>
       </c>
       <c r="Q58" s="7" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="R58" s="3">
         <v>22</v>
@@ -4989,7 +4989,7 @@
         <v>covers/red-prince.jpg</v>
       </c>
       <c r="AN58" s="21" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="AS58" t="s">
         <v>23</v>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/the-polish-atheneum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="563" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97FDDD71-CA26-4567-BEEA-CB445325E313}"/>
+  <xr:revisionPtr revIDLastSave="667" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF2A58CC-873C-4C51-ABDA-78089D885BDA}"/>
   <bookViews>
-    <workbookView xWindow="3060" yWindow="570" windowWidth="23220" windowHeight="14940" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="310">
   <si>
     <t>cover</t>
   </si>
@@ -967,12 +967,120 @@
   <si>
     <t>the-homeless</t>
   </si>
+  <si>
+    <t>adam-mickiewicz</t>
+  </si>
+  <si>
+    <t>Adam Mickiewicz: The Life of a Romantic</t>
+  </si>
+  <si>
+    <t>Roman Koropeckyj</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;Adam Mickiewicz (1798–1855), Poland's national poet, was one of the extraordinary personalities of the age. In chronicling the events of his life-his travels, numerous loves, a troubled marriage, years spent as a member of a heterodox religious sect, and friendships with such luminaries of the time as Aleksandr Pushkin, James Fenimore Cooper, George Sand, Giuseppe Mazzini, Margaret Fuller, and Aleksandr Herzen-Roman Koropeckyj draws a portrait of the Polish poet as a quintessential European Romantic.&lt;/p&gt;
+&lt;p&gt;Spanning five decades of one of the most turbulent periods in modern European history, Mickiewicz's life and works at once reflected and articulated the cultural and political upheavals marking post-Napoleonic Europe. After a poetic debut in his native Lithuania that transformed the face of Polish literature, he spent five years of exile in Russia for engaging in Polish "patriotic" activity. Subsequently, his grand tour of Europe was interrupted by his country's 1830 uprising against Russia; his failure to take part in it would haunt him for the rest of his life. For the next twenty years Mickiewicz shared the fate of other Polish émigrés in the West. It was here that he wrote Forefathers' Eve, part 3 (1832) and Pan Tadeusz (1834), arguably the two most influential works of modern Polish literature. His reputation as his country's most prominent poet secured him a position teaching Latin literature at the Academy of Lausanne and then the first chair of Slavic Literature at the Collége de France. In 1848 he organized a Polish legion in Italy and upon his return to Paris founded a radical French-language newspaper. His final days were devoted to forming a Polish legion in Istanbul.&lt;/p&gt;
+&lt;p&gt;This richly illustrated biography-the first scholarly biography of the poet to be published in English since 1911-draws extensively on diaries, memoirs, correspondence, and the poet's literary texts to make sense of a life as sublime as it was tragic. It concludes with a description of the solemn transfer of Mickiewicz's remains in 1890 from Paris to Cracow, where he was interred in the Royal Cathedral alongside Poland's kings and military heroes.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Cornell University Press</t>
+  </si>
+  <si>
+    <t>Forefathers' Eve</t>
+  </si>
+  <si>
+    <t>forefathers-eve</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;Forefathers' Eve [Dziady] is a four-part dramatic work begun circa 1820 and completed in 1832 - with Part I published only after the poet's death, in 1860. The drama's title refers to Dziady, an ancient Slavic and Lithuanian feast commemorating the dead. This is the grand work of Polish literature, and it is one that elevates Mickiewicz to a position among the "great Europeans" such as Dante and Goethe.&lt;/p&gt;
+&lt;p&gt;With its Christian background of the Communion of the Saints, revenant spirits, and the interpenetration of the worlds of time and eternity, Forefathers' Eve speaks to men and women of all times and places. While it is a truly Polish work - Polish actors covet the role of Gustaw/Konrad in the same way that Anglophone actors covet that of Hamlet - it is one of the most universal works of literature written during the nineteenth century. It has been compared to Goethe's Faust - and rightfully so. Forefathers' Eve initiated the great contribution of Poland to world theatre: Monumental Drama, which stretches from him through Stanislaw Wyspiański to Tadeusz Kantor in our own day and age.&lt;/p&gt;
+&lt;p&gt;The present translation of Adam Mickiewicz's Forefathers' Eve is the first complete verse translation of the cycle published in English. It has been put to use in its entirety by the Teatr Polski in Wroclaw, and partially set to music by Arturas Bumsteinas in his contemporary orchestral work Different Trains (2014).&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Glagoslav Publications B.V.</t>
+  </si>
+  <si>
+    <t>Charles S. Kraszewski</t>
+  </si>
+  <si>
+    <t>Ballads and Romances</t>
+  </si>
+  <si>
+    <t>ballads-romances</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;An even two hundred years have passed since the first publication of Adam Mickiewicz's Ballads and Romances - a collection of lyrics which has the same significance for Polish literature as Wordsworth and Coleridge's Lyrical Ballads has for the English.&lt;/p&gt;
+&lt;p&gt;Poems of love, the supernatural, and the exotic, Mickiewicz's first volume of poetry achieved a level of sublimity that immediately set him at the head of all Polish writers - a position he sustained throughout his life with his lyrical, narrative, dramatic, and epic poetry, and which he continues to hold today. In cooperation with the Polish Cultural Institute of London, Glagoslav brings out an anniversary edition of Mickiewicz's Ballads and Romances in the English translation of Charles S. Kraszewski.&lt;/p&gt;
+&lt;p&gt;The collection includes all the poems of the 1822 edition, plus the ballads added shortly before the poet's death to the 1852, Leipzig edition.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>native-realm</t>
+  </si>
+  <si>
+    <t>Native Realm: A Search for Self-Definition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catherine S. Leach </t>
+  </si>
+  <si>
+    <t>&lt;p&gt;The autobiography of the Nobel laureate&lt;/p&gt;
+&lt;p&gt;Before he emigrated to the United States, Czeslaw Milosz lived through many of the social upheavals that defined the first half of the twentieth century. Here, in this compelling account of his early life, the author sketches his moral and intellectual history from childhood to the early fifties, providing the reader with a glimpse into a way of life that was radically different from anything an American or even a Western European could know.&lt;/p&gt;
+&lt;p&gt;Using the events of his life as a starting point, Native Realm sets out to explore the consciousness of a writer and a man, examining the possibility of finding glimmers of meaning in the midst of chaos while remaining true to oneself.&lt;/p&gt;
+&lt;p&gt;In this beautifully written and elegantly translated work, Milosz is at his very best.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>history-lit-milosz</t>
+  </si>
+  <si>
+    <t>The History of Polish Literature</t>
+  </si>
+  <si>
+    <t>University of California Press</t>
+  </si>
+  <si>
+    <t>Postwar Polish Poetry</t>
+  </si>
+  <si>
+    <t>postwar-polish-poetry</t>
+  </si>
+  <si>
+    <t>Poery</t>
+  </si>
+  <si>
+    <t>Czesław Miłosz (ed.)</t>
+  </si>
+  <si>
+    <t>A survey of Polish letters and culture from its beginnings to modern times. Czeslaw Milosz updated this edition in 1983 and added an epilogue to bring the discussion up to date.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The 1980 edition of Postwar Polish Poetry (which was originally published in 1965) presents 125 poems by 25 poets, including Czeslaw Milosz and other Polish poets living outside Poland. </t>
+  </si>
+  <si>
+    <t>captive-mind</t>
+  </si>
+  <si>
+    <t>The Captive Mind</t>
+  </si>
+  <si>
+    <t>The best known prose work by the winner of the 1980 Nobel Prize for Literature examines the moral and intellectual conflicts faced by men and women living under totalitarianism of the left or right.</t>
+  </si>
+  <si>
+    <t>Selected Masterpieces of Polish Poetry</t>
+  </si>
+  <si>
+    <t>selected-masterpieces</t>
+  </si>
+  <si>
+    <t>Jarek Zawadzki</t>
+  </si>
+  <si>
+    <t>The selection of poems in this anthology may seem a bit unorthodox for Polish literature experts. I have no degree or expertise in any sort of literary research, which may well be the reason for my bizarre taste as presented here. I have tried my very best to include mainly those poems that are obligatory readings in Polish high schools, so that the English Reader can have the chance to get to know a portion of the choicest Polish poetry that an average Pole has willy-nilly come across in his life (one of the poems happens to be a well-known Christmas carol, even).</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1084,13 +1192,6 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF0F1111"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -1117,7 +1218,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1139,26 +1240,15 @@
     <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1174,10 +1264,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1498,28 +1584,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01CE5F32-AD1D-47CB-A8F1-52ACBFFA0BE8}">
   <dimension ref="A1:AY84"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="29.140625" customWidth="1"/>
-    <col min="2" max="3" width="13.7109375" customWidth="1"/>
-    <col min="4" max="4" width="46" style="27" customWidth="1"/>
+    <col min="1" max="1" width="29.1328125" customWidth="1"/>
+    <col min="2" max="3" width="13.73046875" customWidth="1"/>
+    <col min="4" max="4" width="46" style="20" customWidth="1"/>
     <col min="5" max="6" width="46" customWidth="1"/>
-    <col min="7" max="9" width="9.140625" style="7"/>
+    <col min="7" max="9" width="9.1328125" style="7"/>
     <col min="10" max="11" width="9" style="7"/>
-    <col min="12" max="14" width="9.140625" style="7"/>
+    <col min="12" max="14" width="9.1328125" style="7"/>
     <col min="15" max="15" width="16" style="12" customWidth="1"/>
-    <col min="16" max="23" width="9.140625" style="3"/>
+    <col min="16" max="23" width="9.1328125" style="3"/>
     <col min="24" max="24" width="17" style="15" customWidth="1"/>
-    <col min="25" max="32" width="9.140625" style="5"/>
+    <col min="25" max="32" width="9.1328125" style="5"/>
     <col min="33" max="33" width="22" style="8" customWidth="1"/>
-    <col min="34" max="34" width="26.28515625" customWidth="1"/>
+    <col min="34" max="34" width="26.265625" customWidth="1"/>
     <col min="37" max="37" width="16" customWidth="1"/>
-    <col min="39" max="39" width="21.140625" customWidth="1"/>
-    <col min="40" max="40" width="95.85546875" style="19" customWidth="1"/>
-    <col min="41" max="44" width="19.7109375" customWidth="1"/>
+    <col min="39" max="39" width="21.1328125" customWidth="1"/>
+    <col min="40" max="40" width="95.86328125" style="22" customWidth="1"/>
+    <col min="41" max="44" width="19.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -1529,7 +1615,7 @@
       <c r="C1" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="20" t="s">
         <v>24</v>
       </c>
       <c r="E1" t="s">
@@ -1637,7 +1723,7 @@
       <c r="AM1" t="s">
         <v>21</v>
       </c>
-      <c r="AN1" s="19" t="s">
+      <c r="AN1" s="22" t="s">
         <v>27</v>
       </c>
       <c r="AO1" t="s">
@@ -1674,7 +1760,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -1684,7 +1770,7 @@
       <c r="C2">
         <v>100</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="19" t="s">
         <v>1</v>
       </c>
       <c r="E2" t="s">
@@ -1742,7 +1828,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1752,7 +1838,7 @@
       <c r="C3">
         <v>200</v>
       </c>
-      <c r="D3" s="26" t="s">
+      <c r="D3" s="19" t="s">
         <v>3</v>
       </c>
       <c r="E3" t="s">
@@ -1800,7 +1886,7 @@
         <v>9781429964395</v>
       </c>
       <c r="AH3" t="str">
-        <f t="shared" ref="AH3:AH58" si="0">"covers/" &amp; A3 &amp; ".jpg"</f>
+        <f t="shared" ref="AH3:AH66" si="0">"covers/" &amp; A3 &amp; ".jpg"</f>
         <v>covers/peasant-prince.jpg</v>
       </c>
       <c r="AS3" t="s">
@@ -1813,7 +1899,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -1823,7 +1909,7 @@
       <c r="C4">
         <v>300</v>
       </c>
-      <c r="D4" s="26" t="s">
+      <c r="D4" s="19" t="s">
         <v>5</v>
       </c>
       <c r="E4" t="s">
@@ -1879,7 +1965,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>77</v>
       </c>
@@ -1889,7 +1975,7 @@
       <c r="C5">
         <v>400</v>
       </c>
-      <c r="D5" s="26" t="s">
+      <c r="D5" s="19" t="s">
         <v>7</v>
       </c>
       <c r="E5" t="s">
@@ -1943,7 +2029,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -1953,7 +2039,7 @@
       <c r="C6">
         <v>500</v>
       </c>
-      <c r="D6" s="26" t="s">
+      <c r="D6" s="19" t="s">
         <v>9</v>
       </c>
       <c r="E6" t="s">
@@ -2007,7 +2093,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -2017,7 +2103,7 @@
       <c r="C7">
         <v>600</v>
       </c>
-      <c r="D7" s="26" t="s">
+      <c r="D7" s="19" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
@@ -2067,7 +2153,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -2077,7 +2163,7 @@
       <c r="C8">
         <v>750</v>
       </c>
-      <c r="D8" s="26" t="s">
+      <c r="D8" s="19" t="s">
         <v>41</v>
       </c>
       <c r="E8" t="s">
@@ -2134,7 +2220,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -2144,7 +2230,7 @@
       <c r="C9">
         <v>250</v>
       </c>
-      <c r="D9" s="26" t="s">
+      <c r="D9" s="19" t="s">
         <v>47</v>
       </c>
       <c r="E9" t="s">
@@ -2187,7 +2273,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -2197,7 +2283,7 @@
       <c r="C10">
         <v>350</v>
       </c>
-      <c r="D10" s="26" t="s">
+      <c r="D10" s="19" t="s">
         <v>49</v>
       </c>
       <c r="E10" t="s">
@@ -2241,7 +2327,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -2251,7 +2337,7 @@
       <c r="C11">
         <v>450</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="19" t="s">
         <v>53</v>
       </c>
       <c r="E11" t="s">
@@ -2294,7 +2380,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>62</v>
       </c>
@@ -2304,7 +2390,7 @@
       <c r="C12">
         <v>1050</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="20" t="s">
         <v>64</v>
       </c>
       <c r="E12" t="s">
@@ -2360,7 +2446,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -2370,7 +2456,7 @@
       <c r="C13">
         <v>650</v>
       </c>
-      <c r="D13" s="26" t="s">
+      <c r="D13" s="19" t="s">
         <v>58</v>
       </c>
       <c r="E13" t="s">
@@ -2416,7 +2502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>69</v>
       </c>
@@ -2426,7 +2512,7 @@
       <c r="C14">
         <v>100</v>
       </c>
-      <c r="D14" s="26" t="s">
+      <c r="D14" s="19" t="s">
         <v>66</v>
       </c>
       <c r="E14" t="s">
@@ -2469,7 +2555,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>73</v>
       </c>
@@ -2479,7 +2565,7 @@
       <c r="C15">
         <v>100</v>
       </c>
-      <c r="D15" s="26" t="s">
+      <c r="D15" s="19" t="s">
         <v>70</v>
       </c>
       <c r="E15" t="s">
@@ -2519,7 +2605,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>74</v>
       </c>
@@ -2529,7 +2615,7 @@
       <c r="C16">
         <v>400</v>
       </c>
-      <c r="D16" s="26" t="s">
+      <c r="D16" s="19" t="s">
         <v>72</v>
       </c>
       <c r="E16" t="s">
@@ -2569,7 +2655,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>130</v>
       </c>
@@ -2579,7 +2665,7 @@
       <c r="C17">
         <v>400</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="D17" s="19" t="s">
         <v>76</v>
       </c>
       <c r="E17" t="s">
@@ -2619,7 +2705,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>81</v>
       </c>
@@ -2629,7 +2715,7 @@
       <c r="C18">
         <v>600</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="D18" s="19" t="s">
         <v>80</v>
       </c>
       <c r="E18" t="s">
@@ -2674,7 +2760,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>129</v>
       </c>
@@ -2684,7 +2770,7 @@
       <c r="C19">
         <v>800</v>
       </c>
-      <c r="D19" s="26" t="s">
+      <c r="D19" s="19" t="s">
         <v>82</v>
       </c>
       <c r="E19" t="s">
@@ -2729,7 +2815,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>85</v>
       </c>
@@ -2739,7 +2825,7 @@
       <c r="C20">
         <v>900</v>
       </c>
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="19" t="s">
         <v>83</v>
       </c>
       <c r="E20" t="s">
@@ -2784,7 +2870,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>86</v>
       </c>
@@ -2794,7 +2880,7 @@
       <c r="C21">
         <v>1000</v>
       </c>
-      <c r="D21" s="26" t="s">
+      <c r="D21" s="19" t="s">
         <v>84</v>
       </c>
       <c r="E21" t="s">
@@ -2839,7 +2925,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>90</v>
       </c>
@@ -2849,7 +2935,7 @@
       <c r="C22">
         <v>600</v>
       </c>
-      <c r="D22" s="26" t="s">
+      <c r="D22" s="19" t="s">
         <v>91</v>
       </c>
       <c r="E22" t="s">
@@ -2892,7 +2978,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>94</v>
       </c>
@@ -2902,7 +2988,7 @@
       <c r="C23">
         <v>200</v>
       </c>
-      <c r="D23" s="26" t="s">
+      <c r="D23" s="19" t="s">
         <v>95</v>
       </c>
       <c r="E23" t="s">
@@ -2945,7 +3031,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>128</v>
       </c>
@@ -2955,7 +3041,7 @@
       <c r="C24">
         <v>600</v>
       </c>
-      <c r="D24" s="26" t="s">
+      <c r="D24" s="19" t="s">
         <v>97</v>
       </c>
       <c r="E24" t="s">
@@ -2998,7 +3084,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>112</v>
       </c>
@@ -3008,7 +3094,7 @@
       <c r="C25">
         <v>100</v>
       </c>
-      <c r="D25" s="26" t="s">
+      <c r="D25" s="19" t="s">
         <v>98</v>
       </c>
       <c r="E25" t="s">
@@ -3057,7 +3143,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:51" ht="165" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>101</v>
       </c>
@@ -3067,7 +3153,7 @@
       <c r="C26">
         <v>100</v>
       </c>
-      <c r="D26" s="26" t="s">
+      <c r="D26" s="19" t="s">
         <v>105</v>
       </c>
       <c r="E26" t="s">
@@ -3116,7 +3202,7 @@
         <f t="shared" si="0"/>
         <v>covers/melicles.jpg</v>
       </c>
-      <c r="AN26" s="20" t="s">
+      <c r="AN26" s="22" t="s">
         <v>212</v>
       </c>
       <c r="AO26" t="s">
@@ -3141,7 +3227,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>102</v>
       </c>
@@ -3151,7 +3237,7 @@
       <c r="C27">
         <v>600</v>
       </c>
-      <c r="D27" s="26" t="s">
+      <c r="D27" s="19" t="s">
         <v>106</v>
       </c>
       <c r="E27" t="s">
@@ -3196,7 +3282,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>111</v>
       </c>
@@ -3206,7 +3292,7 @@
       <c r="C28">
         <v>220</v>
       </c>
-      <c r="D28" s="26" t="s">
+      <c r="D28" s="19" t="s">
         <v>109</v>
       </c>
       <c r="E28" t="s">
@@ -3257,7 +3343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>110</v>
       </c>
@@ -3267,7 +3353,7 @@
       <c r="C29">
         <v>200</v>
       </c>
-      <c r="D29" s="26" t="s">
+      <c r="D29" s="19" t="s">
         <v>108</v>
       </c>
       <c r="E29" t="s">
@@ -3318,7 +3404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>123</v>
       </c>
@@ -3328,7 +3414,7 @@
       <c r="C30">
         <v>250</v>
       </c>
-      <c r="D30" s="26" t="s">
+      <c r="D30" s="19" t="s">
         <v>120</v>
       </c>
       <c r="E30" t="s">
@@ -3393,7 +3479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>124</v>
       </c>
@@ -3403,7 +3489,7 @@
       <c r="C31">
         <v>450</v>
       </c>
-      <c r="D31" s="26" t="s">
+      <c r="D31" s="19" t="s">
         <v>121</v>
       </c>
       <c r="E31" t="s">
@@ -3468,7 +3554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>125</v>
       </c>
@@ -3478,7 +3564,7 @@
       <c r="C32">
         <v>650</v>
       </c>
-      <c r="D32" s="26" t="s">
+      <c r="D32" s="19" t="s">
         <v>122</v>
       </c>
       <c r="E32" t="s">
@@ -3533,7 +3619,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>157</v>
       </c>
@@ -3543,7 +3629,7 @@
       <c r="C33">
         <v>100</v>
       </c>
-      <c r="D33" s="26" t="s">
+      <c r="D33" s="19" t="s">
         <v>158</v>
       </c>
       <c r="E33" t="s">
@@ -3578,7 +3664,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>161</v>
       </c>
@@ -3588,7 +3674,7 @@
       <c r="C34">
         <v>200</v>
       </c>
-      <c r="D34" s="27" t="s">
+      <c r="D34" s="20" t="s">
         <v>159</v>
       </c>
       <c r="E34" t="s">
@@ -3634,7 +3720,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>164</v>
       </c>
@@ -3644,7 +3730,7 @@
       <c r="C35">
         <v>300</v>
       </c>
-      <c r="D35" s="27" t="s">
+      <c r="D35" s="20" t="s">
         <v>162</v>
       </c>
       <c r="E35" t="s">
@@ -3679,7 +3765,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>152</v>
       </c>
@@ -3689,7 +3775,7 @@
       <c r="C36">
         <v>400</v>
       </c>
-      <c r="D36" s="27" t="s">
+      <c r="D36" s="20" t="s">
         <v>139</v>
       </c>
       <c r="E36" t="s">
@@ -3724,7 +3810,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>153</v>
       </c>
@@ -3734,7 +3820,7 @@
       <c r="C37">
         <v>600</v>
       </c>
-      <c r="D37" s="27" t="s">
+      <c r="D37" s="20" t="s">
         <v>144</v>
       </c>
       <c r="E37" t="s">
@@ -3781,7 +3867,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>154</v>
       </c>
@@ -3791,7 +3877,7 @@
       <c r="C38">
         <v>700</v>
       </c>
-      <c r="D38" s="27" t="s">
+      <c r="D38" s="20" t="s">
         <v>143</v>
       </c>
       <c r="E38" t="s">
@@ -3835,7 +3921,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>155</v>
       </c>
@@ -3845,7 +3931,7 @@
       <c r="C39">
         <v>800</v>
       </c>
-      <c r="D39" s="27" t="s">
+      <c r="D39" s="20" t="s">
         <v>145</v>
       </c>
       <c r="E39" s="10" t="s">
@@ -3892,7 +3978,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>209</v>
       </c>
@@ -3902,7 +3988,7 @@
       <c r="C40">
         <v>900</v>
       </c>
-      <c r="D40" s="27" t="s">
+      <c r="D40" s="20" t="s">
         <v>148</v>
       </c>
       <c r="E40" t="s">
@@ -3935,7 +4021,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>156</v>
       </c>
@@ -3945,7 +4031,7 @@
       <c r="C41">
         <v>1000</v>
       </c>
-      <c r="D41" s="27" t="s">
+      <c r="D41" s="20" t="s">
         <v>151</v>
       </c>
       <c r="E41" t="s">
@@ -3981,7 +4067,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>205</v>
       </c>
@@ -3991,7 +4077,7 @@
       <c r="C42">
         <v>1100</v>
       </c>
-      <c r="D42" s="27" t="s">
+      <c r="D42" s="20" t="s">
         <v>206</v>
       </c>
       <c r="E42" t="s">
@@ -4028,7 +4114,7 @@
         <f t="shared" si="0"/>
         <v>covers/new-poems-ukr-po.jpg</v>
       </c>
-      <c r="AN42" s="19" t="s">
+      <c r="AN42" s="22" t="s">
         <v>208</v>
       </c>
       <c r="AS42" t="s">
@@ -4041,7 +4127,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>197</v>
       </c>
@@ -4051,7 +4137,7 @@
       <c r="C43">
         <v>1000</v>
       </c>
-      <c r="D43" s="27" t="s">
+      <c r="D43" s="20" t="s">
         <v>193</v>
       </c>
       <c r="E43" t="s">
@@ -4097,7 +4183,7 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-templars.jpg</v>
       </c>
-      <c r="AN43" s="19" t="s">
+      <c r="AN43" s="22" t="s">
         <v>202</v>
       </c>
       <c r="AS43" t="s">
@@ -4110,7 +4196,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>200</v>
       </c>
@@ -4120,7 +4206,7 @@
       <c r="C44">
         <v>1100</v>
       </c>
-      <c r="D44" s="27" t="s">
+      <c r="D44" s="20" t="s">
         <v>194</v>
       </c>
       <c r="E44" t="s">
@@ -4166,7 +4252,7 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-mysteries.jpg</v>
       </c>
-      <c r="AN44" s="19" t="s">
+      <c r="AN44" s="22" t="s">
         <v>204</v>
       </c>
       <c r="AS44" t="s">
@@ -4179,7 +4265,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>199</v>
       </c>
@@ -4189,7 +4275,7 @@
       <c r="C45">
         <v>1200</v>
       </c>
-      <c r="D45" s="27" t="s">
+      <c r="D45" s="20" t="s">
         <v>196</v>
       </c>
       <c r="E45" t="s">
@@ -4235,7 +4321,7 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-bandits.jpg</v>
       </c>
-      <c r="AN45" s="19" t="s">
+      <c r="AN45" s="22" t="s">
         <v>201</v>
       </c>
       <c r="AS45" t="s">
@@ -4248,7 +4334,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>198</v>
       </c>
@@ -4258,7 +4344,7 @@
       <c r="C46">
         <v>1300</v>
       </c>
-      <c r="D46" s="27" t="s">
+      <c r="D46" s="20" t="s">
         <v>195</v>
       </c>
       <c r="E46" t="s">
@@ -4304,7 +4390,7 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-copernicus.jpg</v>
       </c>
-      <c r="AN46" s="21" t="s">
+      <c r="AN46" s="23" t="s">
         <v>203</v>
       </c>
       <c r="AS46" t="s">
@@ -4317,7 +4403,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:48" ht="375" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>218</v>
       </c>
@@ -4327,7 +4413,7 @@
       <c r="C47">
         <v>525</v>
       </c>
-      <c r="D47" s="27" t="s">
+      <c r="D47" s="20" t="s">
         <v>219</v>
       </c>
       <c r="E47" t="s">
@@ -4374,7 +4460,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:48" ht="180" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:48" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>224</v>
       </c>
@@ -4384,7 +4470,7 @@
       <c r="C48">
         <v>235</v>
       </c>
-      <c r="D48" s="27" t="s">
+      <c r="D48" s="20" t="s">
         <v>226</v>
       </c>
       <c r="E48" t="s">
@@ -4447,7 +4533,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>229</v>
       </c>
@@ -4457,7 +4543,7 @@
       <c r="C49">
         <v>450</v>
       </c>
-      <c r="D49" s="27" t="s">
+      <c r="D49" s="20" t="s">
         <v>248</v>
       </c>
       <c r="E49" t="s">
@@ -4484,7 +4570,7 @@
         <f t="shared" si="0"/>
         <v>covers/birch-grove.jpg</v>
       </c>
-      <c r="AN49" s="24" t="s">
+      <c r="AN49" s="22" t="s">
         <v>232</v>
       </c>
       <c r="AS49" t="s">
@@ -4497,7 +4583,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>234</v>
       </c>
@@ -4507,7 +4593,7 @@
       <c r="C50">
         <v>750</v>
       </c>
-      <c r="D50" s="27" t="s">
+      <c r="D50" s="20" t="s">
         <v>233</v>
       </c>
       <c r="E50" t="s">
@@ -4535,7 +4621,7 @@
         <f t="shared" si="0"/>
         <v>covers/danton-thermidor.jpg</v>
       </c>
-      <c r="AN50" s="21" t="s">
+      <c r="AN50" s="23" t="s">
         <v>238</v>
       </c>
       <c r="AS50" t="s">
@@ -4548,7 +4634,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>239</v>
       </c>
@@ -4558,7 +4644,7 @@
       <c r="C51">
         <v>800</v>
       </c>
-      <c r="D51" s="27" t="s">
+      <c r="D51" s="20" t="s">
         <v>240</v>
       </c>
       <c r="E51" t="s">
@@ -4585,7 +4671,7 @@
         <f t="shared" si="0"/>
         <v>covers/coming-spring.jpg</v>
       </c>
-      <c r="AN51" s="24" t="s">
+      <c r="AN51" s="22" t="s">
         <v>241</v>
       </c>
       <c r="AS51" t="s">
@@ -4598,7 +4684,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:51" ht="399.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:51" ht="399.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>276</v>
       </c>
@@ -4608,7 +4694,7 @@
       <c r="C52">
         <v>900</v>
       </c>
-      <c r="D52" s="27" t="s">
+      <c r="D52" s="20" t="s">
         <v>245</v>
       </c>
       <c r="E52" t="s">
@@ -4645,7 +4731,7 @@
         <f t="shared" si="0"/>
         <v>covers/the-homeless.jpg</v>
       </c>
-      <c r="AN52" s="20" t="s">
+      <c r="AN52" s="22" t="s">
         <v>244</v>
       </c>
       <c r="AS52" t="s">
@@ -4658,7 +4744,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="1:51" ht="285" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>253</v>
       </c>
@@ -4668,7 +4754,7 @@
       <c r="C53">
         <v>900</v>
       </c>
-      <c r="D53" s="27" t="s">
+      <c r="D53" s="20" t="s">
         <v>249</v>
       </c>
       <c r="E53" t="s">
@@ -4716,7 +4802,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:51" ht="315" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>254</v>
       </c>
@@ -4726,13 +4812,13 @@
       <c r="C54">
         <v>600</v>
       </c>
-      <c r="D54" s="27" t="s">
+      <c r="D54" s="20" t="s">
         <v>255</v>
       </c>
       <c r="E54" t="s">
         <v>256</v>
       </c>
-      <c r="F54" s="28" t="s">
+      <c r="F54" s="21" t="s">
         <v>257</v>
       </c>
       <c r="P54" s="2" t="s">
@@ -4766,7 +4852,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:51" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>260</v>
       </c>
@@ -4776,7 +4862,7 @@
       <c r="C55">
         <v>850</v>
       </c>
-      <c r="D55" s="27" t="s">
+      <c r="D55" s="20" t="s">
         <v>261</v>
       </c>
       <c r="E55" t="s">
@@ -4822,7 +4908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:51" ht="330" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>265</v>
       </c>
@@ -4832,7 +4918,7 @@
       <c r="C56">
         <v>860</v>
       </c>
-      <c r="D56" s="27" t="s">
+      <c r="D56" s="20" t="s">
         <v>266</v>
       </c>
       <c r="E56" t="s">
@@ -4878,7 +4964,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:51" ht="390" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>268</v>
       </c>
@@ -4888,7 +4974,7 @@
       <c r="C57">
         <v>870</v>
       </c>
-      <c r="D57" s="27" t="s">
+      <c r="D57" s="20" t="s">
         <v>269</v>
       </c>
       <c r="E57" t="s">
@@ -4934,7 +5020,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:51" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>271</v>
       </c>
@@ -4944,7 +5030,7 @@
       <c r="C58">
         <v>553</v>
       </c>
-      <c r="D58" s="27" t="s">
+      <c r="D58" s="20" t="s">
         <v>272</v>
       </c>
       <c r="E58" t="s">
@@ -4988,7 +5074,7 @@
         <f t="shared" si="0"/>
         <v>covers/red-prince.jpg</v>
       </c>
-      <c r="AN58" s="21" t="s">
+      <c r="AN58" s="23" t="s">
         <v>275</v>
       </c>
       <c r="AS58" t="s">
@@ -5001,101 +5087,458 @@
         <v>30</v>
       </c>
     </row>
-    <row r="59" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:51" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>277</v>
+      </c>
+      <c r="B59" t="s">
+        <v>88</v>
+      </c>
+      <c r="C59">
+        <v>572</v>
+      </c>
+      <c r="D59" s="20" t="s">
+        <v>278</v>
+      </c>
+      <c r="E59" t="s">
+        <v>279</v>
+      </c>
+      <c r="G59" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="I59" s="7">
+        <v>45</v>
+      </c>
+      <c r="O59" s="12">
+        <v>9780801444715</v>
+      </c>
       <c r="P59" s="2"/>
       <c r="Q59" s="7"/>
       <c r="Y59" s="4"/>
       <c r="Z59" s="4"/>
-      <c r="AN59" s="25"/>
-    </row>
-    <row r="60" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AH59" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/adam-mickiewicz.jpg</v>
+      </c>
+      <c r="AN59" s="23" t="s">
+        <v>280</v>
+      </c>
+      <c r="AS59" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT59" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV59" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="60" spans="1:51" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>283</v>
+      </c>
+      <c r="B60" t="s">
+        <v>131</v>
+      </c>
+      <c r="C60">
+        <v>832</v>
+      </c>
+      <c r="D60" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="E60" t="s">
+        <v>51</v>
+      </c>
+      <c r="F60" t="s">
+        <v>286</v>
+      </c>
+      <c r="G60" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H60" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="I60" s="7">
+        <v>31</v>
+      </c>
+      <c r="O60" s="12">
+        <v>9781911414018</v>
+      </c>
       <c r="P60" s="2"/>
       <c r="Q60" s="7"/>
       <c r="Y60" s="4"/>
       <c r="Z60" s="4"/>
-      <c r="AN60" s="25"/>
-    </row>
-    <row r="61" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AH60" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/forefathers-eve.jpg</v>
+      </c>
+      <c r="AN60" s="23" t="s">
+        <v>284</v>
+      </c>
+      <c r="AS60" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT60" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV60" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="61" spans="1:51" x14ac:dyDescent="0.45">
+      <c r="A61" t="s">
+        <v>288</v>
+      </c>
+      <c r="B61" t="s">
+        <v>131</v>
+      </c>
+      <c r="C61">
+        <v>900</v>
+      </c>
+      <c r="D61" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="E61" t="s">
+        <v>51</v>
+      </c>
+      <c r="F61" t="s">
+        <v>286</v>
+      </c>
+      <c r="G61" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="H61" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="I61" s="7">
+        <v>27</v>
+      </c>
+      <c r="O61" s="12">
+        <v>9781804840016</v>
+      </c>
       <c r="P61" s="2"/>
       <c r="Q61" s="7"/>
       <c r="Y61" s="4"/>
       <c r="Z61" s="4"/>
-    </row>
-    <row r="62" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="P62" s="2"/>
-      <c r="Q62" s="7"/>
+      <c r="AH61" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/ballads-romances.jpg</v>
+      </c>
+      <c r="AN61" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="AS61" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT61" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV61" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="62" spans="1:51" x14ac:dyDescent="0.45">
+      <c r="A62" t="s">
+        <v>290</v>
+      </c>
+      <c r="B62" t="s">
+        <v>75</v>
+      </c>
+      <c r="C62">
+        <v>902</v>
+      </c>
+      <c r="D62" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="E62" t="s">
+        <v>132</v>
+      </c>
+      <c r="F62" t="s">
+        <v>292</v>
+      </c>
+      <c r="P62" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q62" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="R62" s="3">
+        <v>16</v>
+      </c>
+      <c r="X62" s="15">
+        <v>9780374528300</v>
+      </c>
       <c r="Y62" s="4"/>
       <c r="Z62" s="4"/>
-    </row>
-    <row r="63" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="P63" s="2"/>
-      <c r="Q63" s="7"/>
+      <c r="AH62" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/native-realm.jpg</v>
+      </c>
+      <c r="AN62" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="AS62" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT62" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV62" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:51" x14ac:dyDescent="0.45">
+      <c r="A63" t="s">
+        <v>294</v>
+      </c>
+      <c r="B63" t="s">
+        <v>88</v>
+      </c>
+      <c r="C63">
+        <v>903</v>
+      </c>
+      <c r="D63" s="20" t="s">
+        <v>295</v>
+      </c>
+      <c r="E63" t="s">
+        <v>132</v>
+      </c>
+      <c r="P63" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q63" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="R63" s="3">
+        <v>41</v>
+      </c>
+      <c r="X63" s="15">
+        <v>9780520044777</v>
+      </c>
       <c r="Y63" s="4"/>
       <c r="Z63" s="4"/>
-    </row>
-    <row r="64" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="Q64" s="7"/>
+      <c r="AH63" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/history-lit-milosz.jpg</v>
+      </c>
+      <c r="AN63" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="AS63" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT63" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV63" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="64" spans="1:51" x14ac:dyDescent="0.45">
+      <c r="A64" t="s">
+        <v>298</v>
+      </c>
+      <c r="B64" t="s">
+        <v>299</v>
+      </c>
+      <c r="C64">
+        <v>872</v>
+      </c>
+      <c r="D64" s="20" t="s">
+        <v>297</v>
+      </c>
+      <c r="E64" t="s">
+        <v>300</v>
+      </c>
+      <c r="P64" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q64" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="R64" s="3">
+        <v>22</v>
+      </c>
+      <c r="X64" s="15">
+        <v>9780520044760</v>
+      </c>
       <c r="Y64" s="4"/>
       <c r="Z64" s="4"/>
-    </row>
-    <row r="65" spans="17:40" x14ac:dyDescent="0.25">
-      <c r="Q65" s="7"/>
+      <c r="AH64" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/postwar-polish-poetry.jpg</v>
+      </c>
+      <c r="AN64" s="22" t="s">
+        <v>302</v>
+      </c>
+      <c r="AS64" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT64" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV64" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="65" spans="1:48" x14ac:dyDescent="0.45">
+      <c r="A65" t="s">
+        <v>303</v>
+      </c>
+      <c r="B65" t="s">
+        <v>75</v>
+      </c>
+      <c r="C65">
+        <v>457</v>
+      </c>
+      <c r="D65" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="E65" t="s">
+        <v>132</v>
+      </c>
+      <c r="P65" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q65" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="R65" s="3">
+        <v>13</v>
+      </c>
+      <c r="X65" s="15">
+        <v>9780679728566</v>
+      </c>
       <c r="Y65" s="4"/>
       <c r="Z65" s="4"/>
-    </row>
-    <row r="66" spans="17:40" x14ac:dyDescent="0.25">
+      <c r="AH65" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/captive-mind.jpg</v>
+      </c>
+      <c r="AN65" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="AS65" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT65" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV65" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="66" spans="1:48" x14ac:dyDescent="0.45">
+      <c r="A66" t="s">
+        <v>307</v>
+      </c>
+      <c r="B66" t="s">
+        <v>131</v>
+      </c>
+      <c r="C66">
+        <v>1100</v>
+      </c>
+      <c r="D66" s="20" t="s">
+        <v>306</v>
+      </c>
+      <c r="E66" t="s">
+        <v>207</v>
+      </c>
+      <c r="F66" t="s">
+        <v>308</v>
+      </c>
+      <c r="P66" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="Q66" s="7"/>
+      <c r="R66" s="3">
+        <v>14</v>
+      </c>
+      <c r="X66" s="15">
+        <v>9781419679995</v>
+      </c>
       <c r="Y66" s="4"/>
       <c r="Z66" s="4"/>
-    </row>
-    <row r="67" spans="17:40" x14ac:dyDescent="0.25">
+      <c r="AH66" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/selected-masterpieces.jpg</v>
+      </c>
+      <c r="AN66" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="AS66" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT66" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV66" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="67" spans="1:48" x14ac:dyDescent="0.45">
       <c r="Q67" s="7"/>
       <c r="Y67" s="4"/>
       <c r="Z67" s="4"/>
-    </row>
-    <row r="68" spans="17:40" x14ac:dyDescent="0.25">
+      <c r="AN67" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="AS67" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT67" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV67" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" spans="1:48" x14ac:dyDescent="0.45">
       <c r="Q68" s="7"/>
       <c r="Y68" s="4"/>
       <c r="Z68" s="4"/>
     </row>
-    <row r="69" spans="17:40" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:48" x14ac:dyDescent="0.45">
       <c r="Q69" s="7"/>
       <c r="Y69" s="4"/>
       <c r="Z69" s="4"/>
     </row>
-    <row r="70" spans="17:40" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:48" x14ac:dyDescent="0.45">
       <c r="Q70" s="7"/>
       <c r="Y70" s="4"/>
       <c r="Z70" s="4"/>
     </row>
-    <row r="71" spans="17:40" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:48" x14ac:dyDescent="0.45">
       <c r="Q71" s="7"/>
       <c r="Y71" s="4"/>
       <c r="Z71" s="4"/>
       <c r="AA71" s="4"/>
     </row>
-    <row r="72" spans="17:40" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:48" x14ac:dyDescent="0.45">
       <c r="Q72" s="7"/>
       <c r="Y72" s="4"/>
       <c r="Z72" s="4"/>
     </row>
-    <row r="73" spans="17:40" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:48" x14ac:dyDescent="0.45">
       <c r="Q73" s="7"/>
       <c r="Y73" s="4"/>
       <c r="Z73" s="4"/>
     </row>
-    <row r="74" spans="17:40" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:48" x14ac:dyDescent="0.45">
       <c r="Q74" s="7"/>
       <c r="Y74" s="4"/>
       <c r="Z74" s="4"/>
     </row>
-    <row r="75" spans="17:40" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:48" x14ac:dyDescent="0.45">
       <c r="Q75" s="7"/>
       <c r="Y75" s="4"/>
       <c r="Z75" s="4"/>
       <c r="AG75" s="5"/>
     </row>
-    <row r="76" spans="17:40" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:48" x14ac:dyDescent="0.45">
       <c r="Q76" s="7"/>
       <c r="W76" s="9"/>
       <c r="Y76" s="4"/>
@@ -5103,9 +5546,8 @@
       <c r="AF76" s="8"/>
       <c r="AG76" s="5"/>
       <c r="AM76" s="11"/>
-      <c r="AN76" s="24"/>
-    </row>
-    <row r="77" spans="17:40" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:48" x14ac:dyDescent="0.45">
       <c r="Q77" s="7"/>
       <c r="W77" s="9"/>
       <c r="Y77" s="4"/>
@@ -5113,9 +5555,8 @@
       <c r="AF77" s="8"/>
       <c r="AG77" s="5"/>
       <c r="AM77" s="11"/>
-      <c r="AN77" s="24"/>
-    </row>
-    <row r="78" spans="17:40" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:48" x14ac:dyDescent="0.45">
       <c r="Q78" s="7"/>
       <c r="W78" s="9"/>
       <c r="Y78" s="4"/>
@@ -5123,58 +5564,51 @@
       <c r="AF78" s="8"/>
       <c r="AG78" s="5"/>
       <c r="AM78" s="11"/>
-      <c r="AN78" s="24"/>
-    </row>
-    <row r="79" spans="17:40" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:48" x14ac:dyDescent="0.45">
       <c r="Q79" s="7"/>
       <c r="W79" s="9"/>
       <c r="Y79" s="4"/>
       <c r="AF79" s="8"/>
       <c r="AG79" s="5"/>
       <c r="AM79" s="11"/>
-      <c r="AN79" s="24"/>
-    </row>
-    <row r="80" spans="17:40" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:48" x14ac:dyDescent="0.45">
       <c r="Q80" s="7"/>
       <c r="W80" s="9"/>
       <c r="AF80" s="8"/>
       <c r="AG80" s="5"/>
       <c r="AM80" s="11"/>
-      <c r="AN80" s="24"/>
-    </row>
-    <row r="81" spans="17:40" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="17:39" x14ac:dyDescent="0.45">
       <c r="Q81" s="7"/>
       <c r="W81" s="9"/>
       <c r="AF81" s="8"/>
       <c r="AG81" s="5"/>
       <c r="AM81" s="11"/>
-      <c r="AN81" s="24"/>
-    </row>
-    <row r="82" spans="17:40" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="17:39" x14ac:dyDescent="0.45">
       <c r="Q82" s="7"/>
       <c r="W82" s="9"/>
       <c r="AF82" s="8"/>
       <c r="AG82" s="5"/>
       <c r="AM82" s="11"/>
-      <c r="AN82" s="24"/>
-    </row>
-    <row r="83" spans="17:40" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="17:39" x14ac:dyDescent="0.45">
       <c r="W83" s="9"/>
       <c r="AF83" s="8"/>
       <c r="AG83" s="5"/>
       <c r="AM83" s="11"/>
-      <c r="AN83" s="24"/>
-    </row>
-    <row r="84" spans="17:40" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="17:39" x14ac:dyDescent="0.45">
       <c r="W84" s="9"/>
       <c r="AF84" s="8"/>
       <c r="AM84" s="11"/>
-      <c r="AN84" s="24"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y85:Z1048576 P85:Q1048576 Q43:Q47 O76:P84 O44 AG44 X44 Y80:Y84 H72:H1048576 G59:G1048576 X75:X83 G47 G49:G57 P64:P75" xr:uid="{D2C177B6-092A-4420-B1E2-D1681CD512E9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y85:Z1048576 P85:Q1048576 Q43:Q47 O76:P84 O44 AG44 X44 Y80:Y84 H72:H1048576 G62:G1048576 X75:X83 G47 G49:G57 P67:P75" xr:uid="{D2C177B6-092A-4420-B1E2-D1681CD512E9}">
       <formula1>"hardcover, paperback, eBook, audiobook1"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR76:AS84 AS85:AT1048576 AS1:AT75" xr:uid="{F1FB7CD6-B38A-4A39-862C-8A1111411C8C}">

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/the-polish-atheneum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="667" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF2A58CC-873C-4C51-ABDA-78089D885BDA}"/>
+  <xr:revisionPtr revIDLastSave="672" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39E3FE35-1C0D-4E6D-8043-24063579BBE9}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
+    <workbookView xWindow="3060" yWindow="570" windowWidth="23220" windowHeight="14940" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1043,9 +1043,6 @@
     <t>postwar-polish-poetry</t>
   </si>
   <si>
-    <t>Poery</t>
-  </si>
-  <si>
     <t>Czesław Miłosz (ed.)</t>
   </si>
   <si>
@@ -1074,6 +1071,9 @@
   </si>
   <si>
     <t>The selection of poems in this anthology may seem a bit unorthodox for Polish literature experts. I have no degree or expertise in any sort of literary research, which may well be the reason for my bizarre taste as presented here. I have tried my very best to include mainly those poems that are obligatory readings in Polish high schools, so that the English Reader can have the chance to get to know a portion of the choicest Polish poetry that an average Pole has willy-nilly come across in his life (one of the poems happens to be a well-known Christmas carol, even).</t>
+  </si>
+  <si>
+    <t>Genre Fiction</t>
   </si>
 </sst>
 </file>
@@ -1247,8 +1247,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1584,28 +1584,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01CE5F32-AD1D-47CB-A8F1-52ACBFFA0BE8}">
   <dimension ref="A1:AY84"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.1328125" customWidth="1"/>
-    <col min="2" max="3" width="13.73046875" customWidth="1"/>
+    <col min="1" max="1" width="29.140625" customWidth="1"/>
+    <col min="2" max="3" width="13.7109375" customWidth="1"/>
     <col min="4" max="4" width="46" style="20" customWidth="1"/>
     <col min="5" max="6" width="46" customWidth="1"/>
-    <col min="7" max="9" width="9.1328125" style="7"/>
+    <col min="7" max="9" width="9.140625" style="7"/>
     <col min="10" max="11" width="9" style="7"/>
-    <col min="12" max="14" width="9.1328125" style="7"/>
+    <col min="12" max="14" width="9.140625" style="7"/>
     <col min="15" max="15" width="16" style="12" customWidth="1"/>
-    <col min="16" max="23" width="9.1328125" style="3"/>
+    <col min="16" max="23" width="9.140625" style="3"/>
     <col min="24" max="24" width="17" style="15" customWidth="1"/>
-    <col min="25" max="32" width="9.1328125" style="5"/>
+    <col min="25" max="32" width="9.140625" style="5"/>
     <col min="33" max="33" width="22" style="8" customWidth="1"/>
-    <col min="34" max="34" width="26.265625" customWidth="1"/>
+    <col min="34" max="34" width="26.28515625" customWidth="1"/>
     <col min="37" max="37" width="16" customWidth="1"/>
-    <col min="39" max="39" width="21.1328125" customWidth="1"/>
-    <col min="40" max="40" width="95.86328125" style="22" customWidth="1"/>
-    <col min="41" max="44" width="19.73046875" customWidth="1"/>
+    <col min="39" max="39" width="21.140625" customWidth="1"/>
+    <col min="40" max="40" width="95.85546875" style="22" customWidth="1"/>
+    <col min="41" max="44" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -1828,7 +1828,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1899,7 +1899,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -1965,7 +1965,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>77</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -2153,7 +2153,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -2220,7 +2220,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -2327,7 +2327,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -2380,7 +2380,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>62</v>
       </c>
@@ -2446,7 +2446,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>69</v>
       </c>
@@ -2555,7 +2555,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>73</v>
       </c>
@@ -2605,7 +2605,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>74</v>
       </c>
@@ -2655,7 +2655,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>130</v>
       </c>
@@ -2705,7 +2705,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>81</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>129</v>
       </c>
@@ -2815,7 +2815,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>85</v>
       </c>
@@ -2870,7 +2870,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>86</v>
       </c>
@@ -2925,12 +2925,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>90</v>
       </c>
       <c r="B22" t="s">
-        <v>79</v>
+        <v>309</v>
       </c>
       <c r="C22">
         <v>600</v>
@@ -2978,12 +2978,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>94</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>309</v>
       </c>
       <c r="C23">
         <v>200</v>
@@ -3031,12 +3031,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>128</v>
       </c>
       <c r="B24" t="s">
-        <v>79</v>
+        <v>309</v>
       </c>
       <c r="C24">
         <v>600</v>
@@ -3084,7 +3084,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>112</v>
       </c>
@@ -3143,7 +3143,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>101</v>
       </c>
@@ -3227,7 +3227,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>102</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>111</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>110</v>
       </c>
@@ -3404,7 +3404,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>123</v>
       </c>
@@ -3479,7 +3479,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>124</v>
       </c>
@@ -3554,7 +3554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>125</v>
       </c>
@@ -3619,7 +3619,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>157</v>
       </c>
@@ -3664,7 +3664,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>161</v>
       </c>
@@ -3720,7 +3720,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>164</v>
       </c>
@@ -3765,7 +3765,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>152</v>
       </c>
@@ -3810,7 +3810,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>153</v>
       </c>
@@ -3867,7 +3867,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>154</v>
       </c>
@@ -3921,7 +3921,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>155</v>
       </c>
@@ -3978,7 +3978,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>209</v>
       </c>
@@ -4021,7 +4021,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>156</v>
       </c>
@@ -4067,7 +4067,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>205</v>
       </c>
@@ -4127,7 +4127,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>197</v>
       </c>
@@ -4196,7 +4196,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>200</v>
       </c>
@@ -4265,7 +4265,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>199</v>
       </c>
@@ -4334,7 +4334,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>198</v>
       </c>
@@ -4403,7 +4403,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>218</v>
       </c>
@@ -4460,7 +4460,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>224</v>
       </c>
@@ -4533,7 +4533,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>229</v>
       </c>
@@ -4583,7 +4583,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>234</v>
       </c>
@@ -4634,7 +4634,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>239</v>
       </c>
@@ -4684,7 +4684,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:51" ht="399.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:51" ht="399.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>276</v>
       </c>
@@ -4744,7 +4744,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>253</v>
       </c>
@@ -4802,12 +4802,12 @@
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>254</v>
       </c>
       <c r="B54" t="s">
-        <v>79</v>
+        <v>309</v>
       </c>
       <c r="C54">
         <v>600</v>
@@ -4852,12 +4852,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>260</v>
       </c>
       <c r="B55" t="s">
-        <v>79</v>
+        <v>309</v>
       </c>
       <c r="C55">
         <v>850</v>
@@ -4908,12 +4908,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>265</v>
       </c>
       <c r="B56" t="s">
-        <v>79</v>
+        <v>309</v>
       </c>
       <c r="C56">
         <v>860</v>
@@ -4964,12 +4964,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>268</v>
       </c>
       <c r="B57" t="s">
-        <v>79</v>
+        <v>309</v>
       </c>
       <c r="C57">
         <v>870</v>
@@ -5020,7 +5020,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>271</v>
       </c>
@@ -5087,7 +5087,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="59" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>277</v>
       </c>
@@ -5136,7 +5136,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>283</v>
       </c>
@@ -5188,7 +5188,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>288</v>
       </c>
@@ -5240,7 +5240,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>290</v>
       </c>
@@ -5290,7 +5290,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>294</v>
       </c>
@@ -5325,7 +5325,7 @@
         <v>covers/history-lit-milosz.jpg</v>
       </c>
       <c r="AN63" s="22" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="AS63" t="s">
         <v>23</v>
@@ -5337,12 +5337,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:51" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>298</v>
       </c>
       <c r="B64" t="s">
-        <v>299</v>
+        <v>131</v>
       </c>
       <c r="C64">
         <v>872</v>
@@ -5351,7 +5351,7 @@
         <v>297</v>
       </c>
       <c r="E64" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="P64" s="2" t="s">
         <v>117</v>
@@ -5372,21 +5372,21 @@
         <v>covers/postwar-polish-poetry.jpg</v>
       </c>
       <c r="AN64" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="AS64" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT64" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV64" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="65" spans="1:48" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>302</v>
-      </c>
-      <c r="AS64" t="s">
-        <v>23</v>
-      </c>
-      <c r="AT64" t="s">
-        <v>23</v>
-      </c>
-      <c r="AV64" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="65" spans="1:48" x14ac:dyDescent="0.45">
-      <c r="A65" t="s">
-        <v>303</v>
       </c>
       <c r="B65" t="s">
         <v>75</v>
@@ -5395,7 +5395,7 @@
         <v>457</v>
       </c>
       <c r="D65" s="20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E65" t="s">
         <v>132</v>
@@ -5419,7 +5419,7 @@
         <v>covers/captive-mind.jpg</v>
       </c>
       <c r="AN65" s="22" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AS65" t="s">
         <v>23</v>
@@ -5431,9 +5431,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B66" t="s">
         <v>131</v>
@@ -5442,13 +5442,13 @@
         <v>1100</v>
       </c>
       <c r="D66" s="20" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E66" t="s">
         <v>207</v>
       </c>
       <c r="F66" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="P66" s="2" t="s">
         <v>117</v>
@@ -5467,7 +5467,7 @@
         <v>covers/selected-masterpieces.jpg</v>
       </c>
       <c r="AN66" s="22" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="AS66" t="s">
         <v>23</v>
@@ -5479,12 +5479,12 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:48" x14ac:dyDescent="0.25">
       <c r="Q67" s="7"/>
       <c r="Y67" s="4"/>
       <c r="Z67" s="4"/>
       <c r="AN67" s="22" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AS67" t="s">
         <v>23</v>
@@ -5496,49 +5496,49 @@
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:48" x14ac:dyDescent="0.25">
       <c r="Q68" s="7"/>
       <c r="Y68" s="4"/>
       <c r="Z68" s="4"/>
     </row>
-    <row r="69" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:48" x14ac:dyDescent="0.25">
       <c r="Q69" s="7"/>
       <c r="Y69" s="4"/>
       <c r="Z69" s="4"/>
     </row>
-    <row r="70" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:48" x14ac:dyDescent="0.25">
       <c r="Q70" s="7"/>
       <c r="Y70" s="4"/>
       <c r="Z70" s="4"/>
     </row>
-    <row r="71" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:48" x14ac:dyDescent="0.25">
       <c r="Q71" s="7"/>
       <c r="Y71" s="4"/>
       <c r="Z71" s="4"/>
       <c r="AA71" s="4"/>
     </row>
-    <row r="72" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:48" x14ac:dyDescent="0.25">
       <c r="Q72" s="7"/>
       <c r="Y72" s="4"/>
       <c r="Z72" s="4"/>
     </row>
-    <row r="73" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:48" x14ac:dyDescent="0.25">
       <c r="Q73" s="7"/>
       <c r="Y73" s="4"/>
       <c r="Z73" s="4"/>
     </row>
-    <row r="74" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:48" x14ac:dyDescent="0.25">
       <c r="Q74" s="7"/>
       <c r="Y74" s="4"/>
       <c r="Z74" s="4"/>
     </row>
-    <row r="75" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:48" x14ac:dyDescent="0.25">
       <c r="Q75" s="7"/>
       <c r="Y75" s="4"/>
       <c r="Z75" s="4"/>
       <c r="AG75" s="5"/>
     </row>
-    <row r="76" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:48" x14ac:dyDescent="0.25">
       <c r="Q76" s="7"/>
       <c r="W76" s="9"/>
       <c r="Y76" s="4"/>
@@ -5547,7 +5547,7 @@
       <c r="AG76" s="5"/>
       <c r="AM76" s="11"/>
     </row>
-    <row r="77" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:48" x14ac:dyDescent="0.25">
       <c r="Q77" s="7"/>
       <c r="W77" s="9"/>
       <c r="Y77" s="4"/>
@@ -5556,7 +5556,7 @@
       <c r="AG77" s="5"/>
       <c r="AM77" s="11"/>
     </row>
-    <row r="78" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:48" x14ac:dyDescent="0.25">
       <c r="Q78" s="7"/>
       <c r="W78" s="9"/>
       <c r="Y78" s="4"/>
@@ -5565,7 +5565,7 @@
       <c r="AG78" s="5"/>
       <c r="AM78" s="11"/>
     </row>
-    <row r="79" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:48" x14ac:dyDescent="0.25">
       <c r="Q79" s="7"/>
       <c r="W79" s="9"/>
       <c r="Y79" s="4"/>
@@ -5573,34 +5573,34 @@
       <c r="AG79" s="5"/>
       <c r="AM79" s="11"/>
     </row>
-    <row r="80" spans="1:48" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:48" x14ac:dyDescent="0.25">
       <c r="Q80" s="7"/>
       <c r="W80" s="9"/>
       <c r="AF80" s="8"/>
       <c r="AG80" s="5"/>
       <c r="AM80" s="11"/>
     </row>
-    <row r="81" spans="17:39" x14ac:dyDescent="0.45">
+    <row r="81" spans="17:39" x14ac:dyDescent="0.25">
       <c r="Q81" s="7"/>
       <c r="W81" s="9"/>
       <c r="AF81" s="8"/>
       <c r="AG81" s="5"/>
       <c r="AM81" s="11"/>
     </row>
-    <row r="82" spans="17:39" x14ac:dyDescent="0.45">
+    <row r="82" spans="17:39" x14ac:dyDescent="0.25">
       <c r="Q82" s="7"/>
       <c r="W82" s="9"/>
       <c r="AF82" s="8"/>
       <c r="AG82" s="5"/>
       <c r="AM82" s="11"/>
     </row>
-    <row r="83" spans="17:39" x14ac:dyDescent="0.45">
+    <row r="83" spans="17:39" x14ac:dyDescent="0.25">
       <c r="W83" s="9"/>
       <c r="AF83" s="8"/>
       <c r="AG83" s="5"/>
       <c r="AM83" s="11"/>
     </row>
-    <row r="84" spans="17:39" x14ac:dyDescent="0.45">
+    <row r="84" spans="17:39" x14ac:dyDescent="0.25">
       <c r="W84" s="9"/>
       <c r="AF84" s="8"/>
       <c r="AM84" s="11"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/the-polish-atheneum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="672" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39E3FE35-1C0D-4E6D-8043-24063579BBE9}"/>
+  <xr:revisionPtr revIDLastSave="779" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9C527AC-DAD7-43AE-A525-C60275F26A30}"/>
   <bookViews>
-    <workbookView xWindow="3060" yWindow="570" windowWidth="23220" windowHeight="14940" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="326">
   <si>
     <t>cover</t>
   </si>
@@ -233,9 +233,6 @@
     <t>In desert and wilderness</t>
   </si>
   <si>
-    <t>Classics; Books in Focus</t>
-  </si>
-  <si>
     <t>Castorp</t>
   </si>
   <si>
@@ -305,9 +302,6 @@
     <t>Polish History</t>
   </si>
   <si>
-    <t>Books in Focus; Fiction</t>
-  </si>
-  <si>
     <t>solaris</t>
   </si>
   <si>
@@ -333,12 +327,6 @@
   </si>
   <si>
     <t>Chahary</t>
-  </si>
-  <si>
-    <t>Books in Focus</t>
-  </si>
-  <si>
-    <t>Fiction; Books in Focus</t>
   </si>
   <si>
     <t>melicles</t>
@@ -765,9 +753,6 @@
 What we do with this text, this clue, Huelle seems to say, is up to us.&lt;/p&gt;</t>
   </si>
   <si>
-    <t>Books in Focus; Young Adult</t>
-  </si>
-  <si>
     <t>Young Adult</t>
   </si>
   <si>
@@ -1074,6 +1059,75 @@
   </si>
   <si>
     <t>Genre Fiction</t>
+  </si>
+  <si>
+    <t>Serpent's Tail</t>
+  </si>
+  <si>
+    <t>Young Adult; Genre Fiction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hyenas &amp; Lotuses: A Novel from the Time of Ancient Egypt </t>
+  </si>
+  <si>
+    <t>hyenas-lotuses</t>
+  </si>
+  <si>
+    <t>Andrzej Niwinski</t>
+  </si>
+  <si>
+    <t>Royal Hawaiian Press</t>
+  </si>
+  <si>
+    <t>Hyenas and Lotuses is a novel taking place in the 11th century BC, with the historical background of the authentic dramatic events of that era. The novel is a result of many years of research. All characters are well embedded in historical realities, similarly events of everyday life (the way of eating meals, the way of closing and opening the door, measures, etc…) correspond to reality. While writing, Professor Andrzej Niwinski tried to faithfully reproduce the atmosphere of a given scene: a chapter in which the action takes place in the Valley of the Kings, was written in the Valley of the Kings, and the chapter in which the hero is in the port of Aswan, was written in that place. The names of people and places are consistent with the period in which the novel was staged (11th century BC), but the words such as: Egypt, Nile or Thebes, were assigned much later. As a curiosity, the book was written on four continents: started it in New Zealand, then continued on the return journey through Asia (airport in Singapore), a significant part was created in Africa (Egypt), the rest in Europe.</t>
+  </si>
+  <si>
+    <t>&lt;p&gt;Elzbieta Cherezinska's The Widow Queen is the epic story of a Polish queen whose life and name were all but forgotten until now.&lt;/p&gt;
+&lt;p&gt;The bold one, they call her- too bold for most. To her father, the great duke of Poland, Swietoslawa and her two sisters represent three chances for an alliance. Three marriages on which to build his empire. But Swietoslawa refuses to be simply a pawn in her father's schemes; she seeks a throne of her own, with no husband by her side. the gods may grant her wish, but crowns sit heavy, and power is a sword that cuts both ways.&lt;/p&gt;</t>
+  </si>
+  <si>
+    <t>Elzbieta Cherezińska</t>
+  </si>
+  <si>
+    <t>Widow Queen</t>
+  </si>
+  <si>
+    <t>widow-queen</t>
+  </si>
+  <si>
+    <t>The Bold</t>
+  </si>
+  <si>
+    <t>“Elzbieta Cherezinska writes with great depth and imagination, bringing to life seductive and detailed worlds."</t>
+  </si>
+  <si>
+    <t>Olga Tokarczuk, Nobel Prize Laureate and Man Booker Prize winning author of Flights</t>
+  </si>
+  <si>
+    <t>"Elzbieta Cherezinska brings epic history to life with her own unique and recognizable voice."</t>
+  </si>
+  <si>
+    <t>Tomek Baginski, Executive Producer, The Witcher, Netflix</t>
+  </si>
+  <si>
+    <t>The Last Crown</t>
+  </si>
+  <si>
+    <t>last-crown</t>
+  </si>
+  <si>
+    <t>Maya Zakrzewska-Pim</t>
+  </si>
+  <si>
+    <t>Across Baltic shores, English battlegrounds, and the land of Northern Lights, The Last Crown is the follow up to The Widow Queen, and the epic conclusion of Swietoslawa's journey from Polish princess to Queen of Denmark &amp; Sweden and Queen Mother of England.
+The web of love and lies is thicker than ever as we reunite with players spread across the board of Europe in this sequel to The Widow Queen. Our heroes and enemies alike are beholden to the hands of fate.
+While Olav Tryggvason reclaims the throne of Norway and baptizes the land by blood, King Sven in Denmark is filled with rage at his once comrade. Not only does Olav threaten Sven’s hold on Norway, but his hold on his own wife -- the woman with two crowns, three sons, and a heart long spoken for. Swietoslawa, the Bold One.
+Meanwhile, those Swietoslawa trusts most -- Astrid, her sister, Sigvald, her brother-in-law and head of the Jomsvikings, and even her own son, Olaf -- take shocking, selfish action, with consequences that will reverberate for years to come.
+For the storm of unrequited love destroys all in its path.
+At the Publisher's request, this title is being sold without Digital Rights Management Software (DRM) applied.</t>
+  </si>
+  <si>
+    <t>Forge Books</t>
   </si>
 </sst>
 </file>
@@ -1218,7 +1272,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -1228,18 +1282,15 @@
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1247,8 +1298,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1264,6 +1315,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1583,25 +1638,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01CE5F32-AD1D-47CB-A8F1-52ACBFFA0BE8}">
-  <dimension ref="A1:AY84"/>
+  <dimension ref="A1:AY69"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.140625" customWidth="1"/>
     <col min="2" max="3" width="13.7109375" customWidth="1"/>
-    <col min="4" max="4" width="46" style="20" customWidth="1"/>
+    <col min="4" max="4" width="46" style="17" customWidth="1"/>
     <col min="5" max="6" width="46" customWidth="1"/>
     <col min="7" max="9" width="9.140625" style="7"/>
     <col min="10" max="11" width="9" style="7"/>
     <col min="12" max="14" width="9.140625" style="7"/>
-    <col min="15" max="15" width="16" style="12" customWidth="1"/>
+    <col min="15" max="15" width="28.85546875" style="10" customWidth="1"/>
     <col min="16" max="23" width="9.140625" style="3"/>
-    <col min="24" max="24" width="17" style="15" customWidth="1"/>
+    <col min="24" max="24" width="17" style="13" customWidth="1"/>
     <col min="25" max="32" width="9.140625" style="5"/>
     <col min="33" max="33" width="22" style="8" customWidth="1"/>
     <col min="34" max="34" width="26.28515625" customWidth="1"/>
     <col min="37" max="37" width="16" customWidth="1"/>
     <col min="39" max="39" width="21.140625" customWidth="1"/>
-    <col min="40" max="40" width="95.85546875" style="22" customWidth="1"/>
+    <col min="40" max="40" width="95.85546875" style="19" customWidth="1"/>
     <col min="41" max="44" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1610,12 +1665,12 @@
         <v>13</v>
       </c>
       <c r="B1" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C1" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="17" t="s">
         <v>24</v>
       </c>
       <c r="E1" t="s">
@@ -1625,85 +1680,85 @@
         <v>32</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="H1" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="L1" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="O1" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="P1" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="R1" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="S1" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="T1" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="Q1" s="2" t="s">
+      <c r="U1" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="X1" s="13" t="s">
         <v>177</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="Y1" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z1" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="AA1" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="AB1" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="X1" s="15" t="s">
+      <c r="AC1" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="Y1" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z1" s="4" t="s">
+      <c r="AD1" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="AA1" s="5" t="s">
+      <c r="AE1" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="AB1" s="5" t="s">
+      <c r="AF1" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="AC1" s="5" t="s">
+      <c r="AG1" s="8" t="s">
         <v>185</v>
-      </c>
-      <c r="AD1" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="AE1" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="AF1" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="AG1" s="8" t="s">
-        <v>189</v>
       </c>
       <c r="AH1" t="s">
         <v>0</v>
@@ -1723,20 +1778,20 @@
       <c r="AM1" t="s">
         <v>21</v>
       </c>
-      <c r="AN1" s="22" t="s">
+      <c r="AN1" s="19" t="s">
         <v>27</v>
       </c>
       <c r="AO1" t="s">
+        <v>206</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>209</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>207</v>
+      </c>
+      <c r="AR1" t="s">
         <v>210</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>213</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>211</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>214</v>
       </c>
       <c r="AS1" t="s">
         <v>22</v>
@@ -1765,28 +1820,28 @@
         <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C2">
         <v>100</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="16" t="s">
         <v>1</v>
       </c>
       <c r="E2" t="s">
         <v>2</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I2" s="7">
         <v>25</v>
       </c>
-      <c r="O2" s="12">
+      <c r="O2" s="10">
         <v>9780684812199</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q2" s="2"/>
       <c r="R2" s="3">
@@ -1798,11 +1853,11 @@
       <c r="T2" s="3">
         <v>15</v>
       </c>
-      <c r="X2" s="16">
+      <c r="X2" s="14">
         <v>9780306809330</v>
       </c>
       <c r="Y2" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Z2" s="4"/>
       <c r="AA2" s="5">
@@ -1833,28 +1888,28 @@
         <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C3">
         <v>200</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="16" t="s">
         <v>3</v>
       </c>
       <c r="E3" t="s">
         <v>4</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I3" s="7">
         <v>36</v>
       </c>
-      <c r="O3" s="12">
+      <c r="O3" s="10">
         <v>9780312625924</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q3" s="2"/>
       <c r="R3" s="3">
@@ -1866,11 +1921,11 @@
       <c r="T3" s="3">
         <v>15</v>
       </c>
-      <c r="X3" s="16">
+      <c r="X3" s="14">
         <v>9780312625948</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Z3" s="4"/>
       <c r="AA3" s="5">
@@ -1886,7 +1941,7 @@
         <v>9781429964395</v>
       </c>
       <c r="AH3" t="str">
-        <f t="shared" ref="AH3:AH66" si="0">"covers/" &amp; A3 &amp; ".jpg"</f>
+        <f t="shared" ref="AH3:AH65" si="0">"covers/" &amp; A3 &amp; ".jpg"</f>
         <v>covers/peasant-prince.jpg</v>
       </c>
       <c r="AS3" t="s">
@@ -1904,23 +1959,23 @@
         <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C4">
         <v>300</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="16" t="s">
         <v>5</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="G4" s="6"/>
-      <c r="O4" s="12">
+      <c r="O4" s="10">
         <v>9780008411251</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q4" s="2"/>
       <c r="R4" s="3">
@@ -1932,11 +1987,11 @@
       <c r="T4" s="3">
         <v>16</v>
       </c>
-      <c r="X4" s="16">
+      <c r="X4" s="14">
         <v>9780008521684</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Z4" s="4"/>
       <c r="AA4" s="5">
@@ -1967,22 +2022,22 @@
     </row>
     <row r="5" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C5">
         <v>400</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="16" t="s">
         <v>7</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I5" s="7">
         <v>44</v>
@@ -1993,14 +2048,14 @@
       <c r="K5" s="7">
         <v>38</v>
       </c>
-      <c r="O5" s="13">
+      <c r="O5" s="11">
         <v>9780300252200</v>
       </c>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
-      <c r="X5" s="16"/>
+      <c r="X5" s="14"/>
       <c r="Y5" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Z5" s="4"/>
       <c r="AA5" s="5">
@@ -2034,19 +2089,19 @@
         <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C6">
         <v>500</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="16" t="s">
         <v>9</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I6" s="7">
         <v>93</v>
@@ -2057,14 +2112,14 @@
       <c r="K6" s="7">
         <v>44</v>
       </c>
-      <c r="O6" s="13">
+      <c r="O6" s="11">
         <v>9781472816030</v>
       </c>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
-      <c r="X6" s="16"/>
+      <c r="X6" s="14"/>
       <c r="Y6" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Z6" s="4"/>
       <c r="AA6" s="5">
@@ -2098,12 +2153,12 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C7">
         <v>600</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="16" t="s">
         <v>11</v>
       </c>
       <c r="E7" t="s">
@@ -2113,16 +2168,16 @@
         <v>33</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I7" s="7">
         <v>27</v>
       </c>
-      <c r="O7" s="13">
+      <c r="O7" s="11">
         <v>9781607720041</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="3">
@@ -2134,7 +2189,7 @@
       <c r="T7" s="3">
         <v>18</v>
       </c>
-      <c r="X7" s="16">
+      <c r="X7" s="14">
         <v>9781607720058</v>
       </c>
       <c r="Y7" s="4"/>
@@ -2163,7 +2218,7 @@
       <c r="C8">
         <v>750</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="16" t="s">
         <v>41</v>
       </c>
       <c r="E8" t="s">
@@ -2173,9 +2228,9 @@
         <v>44</v>
       </c>
       <c r="G8" s="6"/>
-      <c r="O8" s="13"/>
+      <c r="O8" s="11"/>
       <c r="P8" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" s="3">
@@ -2187,11 +2242,11 @@
       <c r="T8" s="3">
         <v>14</v>
       </c>
-      <c r="X8" s="16">
+      <c r="X8" s="14">
         <v>9781590173831</v>
       </c>
       <c r="Y8" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Z8" s="4"/>
       <c r="AA8" s="5">
@@ -2230,7 +2285,7 @@
       <c r="C9">
         <v>250</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="D9" s="16" t="s">
         <v>47</v>
       </c>
       <c r="E9" t="s">
@@ -2240,9 +2295,9 @@
         <v>45</v>
       </c>
       <c r="G9" s="6"/>
-      <c r="O9" s="13"/>
+      <c r="O9" s="11"/>
       <c r="P9" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" s="3">
@@ -2254,7 +2309,7 @@
       <c r="T9" s="3">
         <v>17</v>
       </c>
-      <c r="X9" s="16">
+      <c r="X9" s="14">
         <v>9780241524244</v>
       </c>
       <c r="Y9" s="4"/>
@@ -2283,7 +2338,7 @@
       <c r="C10">
         <v>350</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="16" t="s">
         <v>49</v>
       </c>
       <c r="E10" t="s">
@@ -2293,10 +2348,10 @@
         <v>52</v>
       </c>
       <c r="G10" s="6"/>
-      <c r="H10" s="14"/>
-      <c r="O10" s="13"/>
+      <c r="H10" s="12"/>
+      <c r="O10" s="11"/>
       <c r="P10" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="3">
@@ -2308,7 +2363,7 @@
       <c r="T10" s="3">
         <v>13</v>
       </c>
-      <c r="X10" s="16">
+      <c r="X10" s="14">
         <v>9781939810007</v>
       </c>
       <c r="Y10" s="4"/>
@@ -2332,12 +2387,12 @@
         <v>57</v>
       </c>
       <c r="B11" t="s">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="C11">
         <v>450</v>
       </c>
-      <c r="D11" s="19" t="s">
+      <c r="D11" s="16" t="s">
         <v>53</v>
       </c>
       <c r="E11" t="s">
@@ -2347,9 +2402,9 @@
         <v>55</v>
       </c>
       <c r="G11" s="6"/>
-      <c r="O11" s="13"/>
+      <c r="O11" s="11"/>
       <c r="P11" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" s="3">
@@ -2361,7 +2416,7 @@
       <c r="T11" s="3">
         <v>17</v>
       </c>
-      <c r="X11" s="16">
+      <c r="X11" s="14">
         <v>9780875807072</v>
       </c>
       <c r="Y11" s="4"/>
@@ -2385,12 +2440,12 @@
         <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C12">
         <v>1050</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="17" t="s">
         <v>64</v>
       </c>
       <c r="E12" t="s">
@@ -2400,7 +2455,7 @@
         <v>63</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="I12" s="7">
         <v>22</v>
@@ -2411,11 +2466,11 @@
       <c r="K12" s="7">
         <v>15</v>
       </c>
-      <c r="O12" s="13">
+      <c r="O12" s="11">
         <v>9798872593621</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="3">
@@ -2427,7 +2482,7 @@
       <c r="T12" s="3">
         <v>14</v>
       </c>
-      <c r="X12" s="16">
+      <c r="X12" s="14">
         <v>9798245149318</v>
       </c>
       <c r="Y12" s="4"/>
@@ -2451,12 +2506,12 @@
         <v>61</v>
       </c>
       <c r="B13" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C13">
         <v>650</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="16" t="s">
         <v>58</v>
       </c>
       <c r="E13" t="s">
@@ -2466,20 +2521,20 @@
         <v>60</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H13" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I13" s="7">
         <v>24</v>
       </c>
-      <c r="O13" s="13">
+      <c r="O13" s="11">
         <v>9789998791732</v>
       </c>
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
-      <c r="X13" s="16"/>
+      <c r="X13" s="14"/>
       <c r="Y13" s="4"/>
       <c r="Z13" s="4"/>
       <c r="AH13" t="str">
@@ -2496,7 +2551,7 @@
         <v>31</v>
       </c>
       <c r="AX13" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="AY13">
         <v>1</v>
@@ -2504,29 +2559,31 @@
     </row>
     <row r="14" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="C14">
         <v>100</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" t="s">
         <v>66</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>67</v>
       </c>
-      <c r="F14" t="s">
-        <v>68</v>
-      </c>
       <c r="G14" s="6"/>
-      <c r="O14" s="13"/>
+      <c r="O14" s="11"/>
       <c r="P14" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q14" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>305</v>
+      </c>
       <c r="R14" s="3">
         <v>15</v>
       </c>
@@ -2536,7 +2593,7 @@
       <c r="T14" s="3">
         <v>10</v>
       </c>
-      <c r="X14" s="16">
+      <c r="X14" s="14">
         <v>9781852429454</v>
       </c>
       <c r="Y14" s="4"/>
@@ -2557,24 +2614,24 @@
     </row>
     <row r="15" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B15" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C15">
         <v>100</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="E15" t="s">
         <v>70</v>
       </c>
-      <c r="E15" t="s">
-        <v>71</v>
-      </c>
       <c r="G15" s="6"/>
-      <c r="O15" s="13"/>
+      <c r="O15" s="11"/>
       <c r="P15" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" s="3">
@@ -2586,7 +2643,7 @@
       <c r="T15" s="3">
         <v>12</v>
       </c>
-      <c r="X15" s="16">
+      <c r="X15" s="14">
         <v>9780679738015</v>
       </c>
       <c r="Y15" s="4"/>
@@ -2607,24 +2664,24 @@
     </row>
     <row r="16" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>73</v>
+      </c>
+      <c r="B16" t="s">
         <v>74</v>
-      </c>
-      <c r="B16" t="s">
-        <v>75</v>
       </c>
       <c r="C16">
         <v>400</v>
       </c>
-      <c r="D16" s="19" t="s">
-        <v>72</v>
+      <c r="D16" s="16" t="s">
+        <v>71</v>
       </c>
       <c r="E16" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G16" s="6"/>
-      <c r="O16" s="13"/>
+      <c r="O16" s="11"/>
       <c r="P16" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="3">
@@ -2636,7 +2693,7 @@
       <c r="T16" s="3">
         <v>12</v>
       </c>
-      <c r="X16" s="16">
+      <c r="X16" s="14">
         <v>9780141188034</v>
       </c>
       <c r="Y16" s="4"/>
@@ -2657,24 +2714,24 @@
     </row>
     <row r="17" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B17" t="s">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="C17">
         <v>400</v>
       </c>
-      <c r="D17" s="19" t="s">
-        <v>76</v>
+      <c r="D17" s="16" t="s">
+        <v>75</v>
       </c>
       <c r="E17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="G17" s="6"/>
-      <c r="O17" s="13"/>
+      <c r="O17" s="11"/>
       <c r="P17" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" s="3">
@@ -2686,7 +2743,7 @@
       <c r="T17" s="3">
         <v>11</v>
       </c>
-      <c r="X17" s="16">
+      <c r="X17" s="14">
         <v>9780375726293</v>
       </c>
       <c r="Y17" s="4"/>
@@ -2707,28 +2764,28 @@
     </row>
     <row r="18" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C18">
         <v>600</v>
       </c>
-      <c r="D18" s="19" t="s">
-        <v>80</v>
+      <c r="D18" s="16" t="s">
+        <v>79</v>
       </c>
       <c r="E18" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F18" t="s">
         <v>60</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H18" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I18" s="7">
         <v>25</v>
@@ -2739,7 +2796,7 @@
       <c r="K18" s="7">
         <v>22</v>
       </c>
-      <c r="O18" s="13">
+      <c r="O18" s="11">
         <v>9782919820382</v>
       </c>
       <c r="P18" s="2"/>
@@ -2762,28 +2819,28 @@
     </row>
     <row r="19" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="B19" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C19">
         <v>800</v>
       </c>
-      <c r="D19" s="19" t="s">
-        <v>82</v>
+      <c r="D19" s="16" t="s">
+        <v>81</v>
       </c>
       <c r="E19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F19" t="s">
         <v>60</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H19" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I19" s="7">
         <v>25</v>
@@ -2794,7 +2851,7 @@
       <c r="K19" s="7">
         <v>20</v>
       </c>
-      <c r="O19" s="13">
+      <c r="O19" s="11">
         <v>9789998793729</v>
       </c>
       <c r="P19" s="2"/>
@@ -2817,28 +2874,28 @@
     </row>
     <row r="20" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C20">
         <v>900</v>
       </c>
-      <c r="D20" s="19" t="s">
-        <v>83</v>
+      <c r="D20" s="16" t="s">
+        <v>82</v>
       </c>
       <c r="E20" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F20" t="s">
         <v>60</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H20" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I20" s="7">
         <v>27</v>
@@ -2849,7 +2906,7 @@
       <c r="K20" s="7">
         <v>22</v>
       </c>
-      <c r="O20" s="13">
+      <c r="O20" s="11">
         <v>9782919840052</v>
       </c>
       <c r="P20" s="2"/>
@@ -2872,28 +2929,28 @@
     </row>
     <row r="21" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C21">
         <v>1000</v>
       </c>
-      <c r="D21" s="19" t="s">
-        <v>84</v>
+      <c r="D21" s="16" t="s">
+        <v>83</v>
       </c>
       <c r="E21" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F21" t="s">
         <v>60</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H21" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I21" s="7">
         <v>25</v>
@@ -2904,7 +2961,7 @@
       <c r="K21" s="7">
         <v>20</v>
       </c>
-      <c r="O21" s="13">
+      <c r="O21" s="11">
         <v>9782919820290</v>
       </c>
       <c r="P21" s="2"/>
@@ -2927,27 +2984,27 @@
     </row>
     <row r="22" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B22" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C22">
         <v>600</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="D22" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" t="s">
+        <v>90</v>
+      </c>
+      <c r="F22" t="s">
         <v>91</v>
       </c>
-      <c r="E22" t="s">
-        <v>92</v>
-      </c>
-      <c r="F22" t="s">
-        <v>93</v>
-      </c>
       <c r="G22" s="6"/>
-      <c r="O22" s="13"/>
+      <c r="O22" s="11"/>
       <c r="P22" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" s="3">
@@ -2959,7 +3016,7 @@
       <c r="T22" s="3">
         <v>8</v>
       </c>
-      <c r="X22" s="15">
+      <c r="X22" s="13">
         <v>9780156027601</v>
       </c>
       <c r="Y22" s="4"/>
@@ -2980,27 +3037,27 @@
     </row>
     <row r="23" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B23" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C23">
         <v>200</v>
       </c>
-      <c r="D23" s="19" t="s">
-        <v>95</v>
+      <c r="D23" s="16" t="s">
+        <v>93</v>
       </c>
       <c r="E23" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F23" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G23" s="6"/>
-      <c r="O23" s="13"/>
+      <c r="O23" s="11"/>
       <c r="P23" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q23" s="2"/>
       <c r="R23" s="3">
@@ -3012,7 +3069,7 @@
       <c r="T23" s="3">
         <v>12</v>
       </c>
-      <c r="X23" s="15">
+      <c r="X23" s="13">
         <v>9780156306300</v>
       </c>
       <c r="Y23" s="4"/>
@@ -3033,27 +3090,27 @@
     </row>
     <row r="24" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="B24" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C24">
         <v>600</v>
       </c>
-      <c r="D24" s="19" t="s">
-        <v>97</v>
+      <c r="D24" s="16" t="s">
+        <v>95</v>
       </c>
       <c r="E24" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F24" t="s">
         <v>52</v>
       </c>
       <c r="G24" s="6"/>
-      <c r="O24" s="13"/>
+      <c r="O24" s="11"/>
       <c r="P24" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" s="3">
@@ -3065,7 +3122,7 @@
       <c r="T24" s="3">
         <v>13</v>
       </c>
-      <c r="X24" s="15">
+      <c r="X24" s="13">
         <v>9780262357685</v>
       </c>
       <c r="Y24" s="4"/>
@@ -3086,16 +3143,16 @@
     </row>
     <row r="25" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="C25">
         <v>100</v>
       </c>
-      <c r="D25" s="19" t="s">
-        <v>98</v>
+      <c r="D25" s="16" t="s">
+        <v>96</v>
       </c>
       <c r="E25" t="s">
         <v>59</v>
@@ -3104,9 +3161,9 @@
         <v>60</v>
       </c>
       <c r="G25" s="6"/>
-      <c r="O25" s="13"/>
+      <c r="O25" s="11"/>
       <c r="P25" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" s="3">
@@ -3118,7 +3175,7 @@
       <c r="T25" s="3">
         <v>15</v>
       </c>
-      <c r="X25" s="15">
+      <c r="X25" s="13">
         <v>9782919840106</v>
       </c>
       <c r="Y25" s="4"/>
@@ -3137,7 +3194,7 @@
         <v>31</v>
       </c>
       <c r="AX25" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="AY25">
         <v>4</v>
@@ -3145,28 +3202,28 @@
     </row>
     <row r="26" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B26" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C26">
         <v>100</v>
       </c>
-      <c r="D26" s="19" t="s">
-        <v>105</v>
+      <c r="D26" s="16" t="s">
+        <v>101</v>
       </c>
       <c r="E26" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F26" t="s">
         <v>60</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H26" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I26" s="7">
         <v>24</v>
@@ -3177,11 +3234,11 @@
       <c r="K26" s="7">
         <v>20</v>
       </c>
-      <c r="O26" s="13">
+      <c r="O26" s="11">
         <v>9789998791671</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" s="3">
@@ -3193,7 +3250,7 @@
       <c r="T26" s="3">
         <v>15</v>
       </c>
-      <c r="X26" s="15">
+      <c r="X26" s="13">
         <v>9789998791664</v>
       </c>
       <c r="Y26" s="4"/>
@@ -3202,20 +3259,20 @@
         <f t="shared" si="0"/>
         <v>covers/melicles.jpg</v>
       </c>
-      <c r="AN26" s="22" t="s">
+      <c r="AN26" s="19" t="s">
+        <v>208</v>
+      </c>
+      <c r="AO26" t="s">
+        <v>211</v>
+      </c>
+      <c r="AP26" t="s">
+        <v>187</v>
+      </c>
+      <c r="AQ26" t="s">
         <v>212</v>
       </c>
-      <c r="AO26" t="s">
-        <v>215</v>
-      </c>
-      <c r="AP26" t="s">
-        <v>191</v>
-      </c>
-      <c r="AQ26" t="s">
-        <v>216</v>
-      </c>
       <c r="AR26" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="AS26" t="s">
         <v>23</v>
@@ -3229,28 +3286,28 @@
     </row>
     <row r="27" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B27" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C27">
         <v>600</v>
       </c>
-      <c r="D27" s="19" t="s">
-        <v>106</v>
+      <c r="D27" s="16" t="s">
+        <v>102</v>
       </c>
       <c r="E27" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="F27" t="s">
         <v>60</v>
       </c>
       <c r="G27" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H27" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I27" s="7">
         <v>24</v>
@@ -3261,7 +3318,7 @@
       <c r="K27" s="7">
         <v>20</v>
       </c>
-      <c r="O27" s="13">
+      <c r="O27" s="11">
         <v>9789998791794</v>
       </c>
       <c r="P27" s="2"/>
@@ -3284,16 +3341,16 @@
     </row>
     <row r="28" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="B28" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C28">
         <v>220</v>
       </c>
-      <c r="D28" s="19" t="s">
-        <v>109</v>
+      <c r="D28" s="16" t="s">
+        <v>105</v>
       </c>
       <c r="E28" t="s">
         <v>12</v>
@@ -3302,10 +3359,10 @@
         <v>60</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H28" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I28" s="7">
         <v>21</v>
@@ -3316,7 +3373,7 @@
       <c r="K28" s="7">
         <v>18</v>
       </c>
-      <c r="O28" s="12">
+      <c r="O28" s="10">
         <v>9782919820481</v>
       </c>
       <c r="P28" s="2"/>
@@ -3337,7 +3394,7 @@
         <v>31</v>
       </c>
       <c r="AX28" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="AY28">
         <v>1</v>
@@ -3345,28 +3402,28 @@
     </row>
     <row r="29" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B29" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C29">
         <v>200</v>
       </c>
-      <c r="D29" s="19" t="s">
-        <v>108</v>
+      <c r="D29" s="16" t="s">
+        <v>104</v>
       </c>
       <c r="E29" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="F29" t="s">
         <v>60</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H29" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I29" s="7">
         <v>21</v>
@@ -3377,7 +3434,7 @@
       <c r="K29" s="7">
         <v>18</v>
       </c>
-      <c r="O29" s="12">
+      <c r="O29" s="10">
         <v>9782919820153</v>
       </c>
       <c r="P29" s="2"/>
@@ -3398,7 +3455,7 @@
         <v>31</v>
       </c>
       <c r="AX29" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="AY29">
         <v>1</v>
@@ -3406,7 +3463,7 @@
     </row>
     <row r="30" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B30" t="s">
         <v>40</v>
@@ -3414,44 +3471,44 @@
       <c r="C30">
         <v>250</v>
       </c>
-      <c r="D30" s="19" t="s">
-        <v>120</v>
+      <c r="D30" s="16" t="s">
+        <v>116</v>
       </c>
       <c r="E30" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F30" t="s">
         <v>60</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H30" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I30" s="7">
         <v>24</v>
       </c>
-      <c r="O30" s="13">
+      <c r="O30" s="11">
         <v>9789998793781</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="R30" s="3">
         <v>16</v>
       </c>
-      <c r="X30" s="15">
+      <c r="X30" s="13">
         <v>9789998793774</v>
       </c>
       <c r="Y30" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Z30" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AA30" s="5">
         <v>10</v>
@@ -3473,7 +3530,7 @@
         <v>31</v>
       </c>
       <c r="AX30" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="AY30">
         <v>1</v>
@@ -3481,7 +3538,7 @@
     </row>
     <row r="31" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B31" t="s">
         <v>40</v>
@@ -3489,44 +3546,44 @@
       <c r="C31">
         <v>450</v>
       </c>
-      <c r="D31" s="19" t="s">
-        <v>121</v>
+      <c r="D31" s="16" t="s">
+        <v>117</v>
       </c>
       <c r="E31" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F31" t="s">
         <v>60</v>
       </c>
       <c r="G31" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H31" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I31" s="7">
         <v>25</v>
       </c>
-      <c r="O31" s="13">
+      <c r="O31" s="11">
         <v>9782919820047</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="R31" s="3">
         <v>17</v>
       </c>
-      <c r="X31" s="15">
+      <c r="X31" s="13">
         <v>9782919820054</v>
       </c>
       <c r="Y31" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Z31" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AA31" s="5">
         <v>10</v>
@@ -3548,7 +3605,7 @@
         <v>31</v>
       </c>
       <c r="AX31" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="AY31">
         <v>2</v>
@@ -3556,7 +3613,7 @@
     </row>
     <row r="32" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="B32" t="s">
         <v>40</v>
@@ -3564,37 +3621,37 @@
       <c r="C32">
         <v>650</v>
       </c>
-      <c r="D32" s="19" t="s">
-        <v>122</v>
+      <c r="D32" s="16" t="s">
+        <v>118</v>
       </c>
       <c r="E32" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="F32" t="s">
         <v>60</v>
       </c>
       <c r="G32" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H32" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I32" s="7">
         <v>32</v>
       </c>
-      <c r="O32" s="13">
+      <c r="O32" s="11">
         <v>9782919820467</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="R32" s="3">
         <v>18</v>
       </c>
-      <c r="X32" s="15">
+      <c r="X32" s="13">
         <v>9782919820450</v>
       </c>
       <c r="Y32" s="4"/>
@@ -3613,7 +3670,7 @@
         <v>31</v>
       </c>
       <c r="AX32" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="AY32">
         <v>3</v>
@@ -3621,31 +3678,31 @@
     </row>
     <row r="33" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B33" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C33">
         <v>100</v>
       </c>
-      <c r="D33" s="19" t="s">
-        <v>158</v>
+      <c r="D33" s="16" t="s">
+        <v>154</v>
       </c>
       <c r="E33" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G33" s="6"/>
       <c r="P33" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="R33" s="3">
         <v>14</v>
       </c>
-      <c r="X33" s="15">
+      <c r="X33" s="13">
         <v>9780062095886</v>
       </c>
       <c r="Y33" s="4"/>
@@ -3666,42 +3723,42 @@
     </row>
     <row r="34" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="B34" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C34">
         <v>200</v>
       </c>
-      <c r="D34" s="20" t="s">
-        <v>159</v>
+      <c r="D34" s="17" t="s">
+        <v>155</v>
       </c>
       <c r="E34" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H34" s="7" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="I34" s="7">
         <v>38</v>
       </c>
-      <c r="O34" s="12">
+      <c r="O34" s="10">
         <v>9780151003532</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="R34" s="3">
         <v>11</v>
       </c>
-      <c r="X34" s="16">
+      <c r="X34" s="14">
         <v>9780156011464</v>
       </c>
       <c r="Y34" s="4"/>
@@ -3722,31 +3779,31 @@
     </row>
     <row r="35" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B35" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C35">
         <v>300</v>
       </c>
-      <c r="D35" s="20" t="s">
-        <v>162</v>
+      <c r="D35" s="17" t="s">
+        <v>158</v>
       </c>
       <c r="E35" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G35" s="6"/>
       <c r="P35" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="R35" s="3">
         <v>18</v>
       </c>
-      <c r="X35" s="15">
+      <c r="X35" s="13">
         <v>9781400043293</v>
       </c>
       <c r="Y35" s="4"/>
@@ -3767,31 +3824,31 @@
     </row>
     <row r="36" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="B36" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C36">
         <v>400</v>
       </c>
-      <c r="D36" s="20" t="s">
-        <v>139</v>
+      <c r="D36" s="17" t="s">
+        <v>135</v>
       </c>
       <c r="E36" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G36" s="6"/>
       <c r="P36" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="R36" s="3">
         <v>15</v>
       </c>
-      <c r="X36" s="15">
+      <c r="X36" s="13">
         <v>9780374528614</v>
       </c>
       <c r="Y36" s="4"/>
@@ -3812,43 +3869,43 @@
     </row>
     <row r="37" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="B37" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C37">
         <v>600</v>
       </c>
-      <c r="D37" s="20" t="s">
-        <v>144</v>
+      <c r="D37" s="17" t="s">
+        <v>140</v>
       </c>
       <c r="E37" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F37" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G37" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H37" s="7" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="I37" s="7">
         <v>16</v>
       </c>
-      <c r="O37" s="12">
+      <c r="O37" s="10">
         <v>9780393067798</v>
       </c>
       <c r="P37" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" s="3">
         <v>19</v>
       </c>
-      <c r="X37" s="15">
+      <c r="X37" s="13">
         <v>9780393345551</v>
       </c>
       <c r="Y37" s="4"/>
@@ -3869,40 +3926,40 @@
     </row>
     <row r="38" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="B38" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C38">
         <v>700</v>
       </c>
-      <c r="D38" s="20" t="s">
-        <v>143</v>
+      <c r="D38" s="17" t="s">
+        <v>139</v>
       </c>
       <c r="E38" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H38" s="7" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I38" s="7">
         <v>30</v>
       </c>
-      <c r="O38" s="12">
+      <c r="O38" s="10">
         <v>9780544126022</v>
       </c>
       <c r="P38" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q38" s="2"/>
       <c r="R38" s="3">
         <v>11</v>
       </c>
-      <c r="X38" s="15">
+      <c r="X38" s="13">
         <v>9780544705159</v>
       </c>
       <c r="Y38" s="4"/>
@@ -3923,43 +3980,43 @@
     </row>
     <row r="39" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="B39" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C39">
         <v>800</v>
       </c>
-      <c r="D39" s="20" t="s">
-        <v>145</v>
-      </c>
-      <c r="E39" s="10" t="s">
-        <v>146</v>
+      <c r="D39" s="17" t="s">
+        <v>141</v>
+      </c>
+      <c r="E39" s="9" t="s">
+        <v>142</v>
       </c>
       <c r="F39" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H39" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I39" s="7">
         <v>25</v>
       </c>
-      <c r="O39" s="12">
+      <c r="O39" s="10">
         <v>9788367602488</v>
       </c>
       <c r="P39" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" s="3">
         <v>11</v>
       </c>
-      <c r="X39" s="15">
+      <c r="X39" s="13">
         <v>9788367602471</v>
       </c>
       <c r="Y39" s="4"/>
@@ -3980,29 +4037,29 @@
     </row>
     <row r="40" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="B40" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C40">
         <v>900</v>
       </c>
-      <c r="D40" s="20" t="s">
-        <v>148</v>
+      <c r="D40" s="17" t="s">
+        <v>144</v>
       </c>
       <c r="E40" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G40" s="6"/>
       <c r="P40" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q40" s="2"/>
       <c r="R40" s="3">
         <v>7</v>
       </c>
-      <c r="X40" s="15">
+      <c r="X40" s="13">
         <v>9798802065853</v>
       </c>
       <c r="Y40" s="4"/>
@@ -4023,32 +4080,32 @@
     </row>
     <row r="41" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B41" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C41">
         <v>1000</v>
       </c>
-      <c r="D41" s="20" t="s">
-        <v>151</v>
+      <c r="D41" s="17" t="s">
+        <v>147</v>
       </c>
       <c r="E41" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F41" t="s">
         <v>52</v>
       </c>
       <c r="G41" s="6"/>
       <c r="P41" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" s="3">
         <v>14</v>
       </c>
-      <c r="X41" s="15">
+      <c r="X41" s="13">
         <v>9781931243810</v>
       </c>
       <c r="Y41" s="4"/>
@@ -4069,43 +4126,43 @@
     </row>
     <row r="42" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B42" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C42">
         <v>1100</v>
       </c>
-      <c r="D42" s="20" t="s">
-        <v>206</v>
+      <c r="D42" s="17" t="s">
+        <v>202</v>
       </c>
       <c r="E42" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="F42" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H42" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I42" s="7">
         <v>19</v>
       </c>
-      <c r="O42" s="12">
+      <c r="O42" s="10">
         <v>9788367602426</v>
       </c>
       <c r="P42" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q42" s="2"/>
       <c r="R42" s="3">
         <v>9.99</v>
       </c>
-      <c r="X42" s="15">
+      <c r="X42" s="13">
         <v>9788367602419</v>
       </c>
       <c r="Y42" s="4"/>
@@ -4114,8 +4171,8 @@
         <f t="shared" si="0"/>
         <v>covers/new-poems-ukr-po.jpg</v>
       </c>
-      <c r="AN42" s="22" t="s">
-        <v>208</v>
+      <c r="AN42" s="19" t="s">
+        <v>204</v>
       </c>
       <c r="AS42" t="s">
         <v>23</v>
@@ -4129,49 +4186,49 @@
     </row>
     <row r="43" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="B43" t="s">
-        <v>222</v>
+        <v>306</v>
       </c>
       <c r="C43">
         <v>1000</v>
       </c>
-      <c r="D43" s="20" t="s">
-        <v>193</v>
+      <c r="D43" s="17" t="s">
+        <v>189</v>
       </c>
       <c r="E43" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F43" t="s">
         <v>60</v>
       </c>
       <c r="G43" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H43" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I43" s="7">
         <v>26</v>
       </c>
-      <c r="O43" s="12">
+      <c r="O43" s="10">
         <v>9782919820863</v>
       </c>
       <c r="P43" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="R43" s="3">
         <v>13</v>
       </c>
-      <c r="X43" s="15">
+      <c r="X43" s="13">
         <v>9782919820856</v>
       </c>
       <c r="Y43" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Z43" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AA43" s="5">
         <v>2.99</v>
@@ -4183,8 +4240,8 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-templars.jpg</v>
       </c>
-      <c r="AN43" s="22" t="s">
-        <v>202</v>
+      <c r="AN43" s="19" t="s">
+        <v>198</v>
       </c>
       <c r="AS43" t="s">
         <v>23</v>
@@ -4198,49 +4255,49 @@
     </row>
     <row r="44" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="B44" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C44">
         <v>1100</v>
       </c>
-      <c r="D44" s="20" t="s">
-        <v>194</v>
+      <c r="D44" s="17" t="s">
+        <v>190</v>
       </c>
       <c r="E44" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F44" t="s">
         <v>60</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H44" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I44" s="7">
         <v>25</v>
       </c>
-      <c r="O44" s="12">
+      <c r="O44" s="10">
         <v>9782919840014</v>
       </c>
       <c r="P44" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="R44" s="3">
         <v>17</v>
       </c>
-      <c r="X44" s="15">
+      <c r="X44" s="13">
         <v>9782919840021</v>
       </c>
       <c r="Y44" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Z44" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AA44" s="5">
         <v>9.99</v>
@@ -4252,8 +4309,8 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-mysteries.jpg</v>
       </c>
-      <c r="AN44" s="22" t="s">
-        <v>204</v>
+      <c r="AN44" s="19" t="s">
+        <v>200</v>
       </c>
       <c r="AS44" t="s">
         <v>23</v>
@@ -4267,49 +4324,49 @@
     </row>
     <row r="45" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="B45" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C45">
         <v>1200</v>
       </c>
-      <c r="D45" s="20" t="s">
-        <v>196</v>
+      <c r="D45" s="17" t="s">
+        <v>192</v>
       </c>
       <c r="E45" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F45" t="s">
         <v>60</v>
       </c>
       <c r="G45" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H45" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I45" s="7">
         <v>25</v>
       </c>
-      <c r="O45" s="12">
+      <c r="O45" s="10">
         <v>9782919820955</v>
       </c>
       <c r="P45" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="R45" s="3">
         <v>15</v>
       </c>
-      <c r="X45" s="16">
+      <c r="X45" s="14">
         <v>9782919820948</v>
       </c>
       <c r="Y45" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Z45" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AA45" s="5">
         <v>9.99</v>
@@ -4321,8 +4378,8 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-bandits.jpg</v>
       </c>
-      <c r="AN45" s="22" t="s">
-        <v>201</v>
+      <c r="AN45" s="19" t="s">
+        <v>197</v>
       </c>
       <c r="AS45" t="s">
         <v>23</v>
@@ -4336,49 +4393,49 @@
     </row>
     <row r="46" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="B46" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C46">
         <v>1300</v>
       </c>
-      <c r="D46" s="20" t="s">
-        <v>195</v>
+      <c r="D46" s="17" t="s">
+        <v>191</v>
       </c>
       <c r="E46" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="F46" t="s">
         <v>60</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H46" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="I46" s="7">
         <v>25</v>
       </c>
-      <c r="O46" s="12">
+      <c r="O46" s="10">
         <v>9782919820917</v>
       </c>
       <c r="P46" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="R46" s="3">
         <v>13</v>
       </c>
-      <c r="X46" s="15">
+      <c r="X46" s="13">
         <v>9782919820900</v>
       </c>
       <c r="Y46" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Z46" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AA46" s="5">
         <v>9.99</v>
@@ -4390,8 +4447,8 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-copernicus.jpg</v>
       </c>
-      <c r="AN46" s="23" t="s">
-        <v>203</v>
+      <c r="AN46" s="20" t="s">
+        <v>199</v>
       </c>
       <c r="AS46" t="s">
         <v>23</v>
@@ -4405,37 +4462,37 @@
     </row>
     <row r="47" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="B47" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C47">
         <v>525</v>
       </c>
-      <c r="D47" s="20" t="s">
-        <v>219</v>
+      <c r="D47" s="17" t="s">
+        <v>215</v>
       </c>
       <c r="E47" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P47" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="R47" s="3">
         <v>19</v>
       </c>
-      <c r="X47" s="15">
+      <c r="X47" s="13">
         <v>9781905583393</v>
       </c>
       <c r="Y47" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Z47" s="4" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="AA47" s="5">
         <v>5.99</v>
@@ -4447,8 +4504,8 @@
         <f t="shared" si="0"/>
         <v>covers/cold-sea.jpg</v>
       </c>
-      <c r="AN47" s="22" t="s">
-        <v>221</v>
+      <c r="AN47" s="19" t="s">
+        <v>217</v>
       </c>
       <c r="AS47" t="s">
         <v>23</v>
@@ -4462,7 +4519,7 @@
     </row>
     <row r="48" spans="1:48" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B48" t="s">
         <v>40</v>
@@ -4470,41 +4527,41 @@
       <c r="C48">
         <v>235</v>
       </c>
-      <c r="D48" s="20" t="s">
-        <v>226</v>
+      <c r="D48" s="17" t="s">
+        <v>221</v>
       </c>
       <c r="E48" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="F48" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H48" s="7" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="I48" s="7">
         <v>47</v>
       </c>
-      <c r="O48" s="17">
+      <c r="O48" s="15">
         <v>9780670834280</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q48" s="7" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="R48" s="3">
         <v>22</v>
       </c>
-      <c r="X48" s="18">
+      <c r="X48" s="13">
         <v>9780140445800</v>
       </c>
       <c r="Y48" s="4" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="Z48" s="4" t="str">
         <f>Q48</f>
@@ -4520,8 +4577,8 @@
         <f t="shared" si="0"/>
         <v>covers/saragossa.jpg</v>
       </c>
-      <c r="AN48" s="23" t="s">
-        <v>225</v>
+      <c r="AN48" s="20" t="s">
+        <v>220</v>
       </c>
       <c r="AS48" t="s">
         <v>23</v>
@@ -4535,7 +4592,7 @@
     </row>
     <row r="49" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="B49" t="s">
         <v>40</v>
@@ -4543,25 +4600,25 @@
       <c r="C49">
         <v>450</v>
       </c>
-      <c r="D49" s="20" t="s">
-        <v>248</v>
+      <c r="D49" s="17" t="s">
+        <v>243</v>
       </c>
       <c r="E49" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="F49" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P49" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q49" s="7" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="R49" s="3">
         <v>28</v>
       </c>
-      <c r="X49" s="15">
+      <c r="X49" s="13">
         <v>9789639241459</v>
       </c>
       <c r="Y49" s="4"/>
@@ -4570,8 +4627,8 @@
         <f t="shared" si="0"/>
         <v>covers/birch-grove.jpg</v>
       </c>
-      <c r="AN49" s="22" t="s">
-        <v>232</v>
+      <c r="AN49" s="19" t="s">
+        <v>227</v>
       </c>
       <c r="AS49" t="s">
         <v>23</v>
@@ -4585,7 +4642,7 @@
     </row>
     <row r="50" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="B50" t="s">
         <v>40</v>
@@ -4593,26 +4650,26 @@
       <c r="C50">
         <v>750</v>
       </c>
-      <c r="D50" s="20" t="s">
-        <v>233</v>
+      <c r="D50" s="17" t="s">
+        <v>228</v>
       </c>
       <c r="E50" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F50" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="O50" s="6"/>
       <c r="P50" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q50" s="7" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="R50" s="3">
         <v>22</v>
       </c>
-      <c r="X50" s="15">
+      <c r="X50" s="13">
         <v>9780810108066</v>
       </c>
       <c r="Y50" s="4"/>
@@ -4621,8 +4678,8 @@
         <f t="shared" si="0"/>
         <v>covers/danton-thermidor.jpg</v>
       </c>
-      <c r="AN50" s="23" t="s">
-        <v>238</v>
+      <c r="AN50" s="20" t="s">
+        <v>233</v>
       </c>
       <c r="AS50" t="s">
         <v>23</v>
@@ -4636,7 +4693,7 @@
     </row>
     <row r="51" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B51" t="s">
         <v>40</v>
@@ -4644,25 +4701,25 @@
       <c r="C51">
         <v>800</v>
       </c>
-      <c r="D51" s="20" t="s">
-        <v>240</v>
+      <c r="D51" s="17" t="s">
+        <v>235</v>
       </c>
       <c r="E51" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="F51" t="s">
         <v>52</v>
       </c>
       <c r="P51" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q51" s="7" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="R51" s="3">
         <v>39</v>
       </c>
-      <c r="X51" s="15">
+      <c r="X51" s="13">
         <v>9789637326899</v>
       </c>
       <c r="Y51" s="4"/>
@@ -4671,8 +4728,8 @@
         <f t="shared" si="0"/>
         <v>covers/coming-spring.jpg</v>
       </c>
-      <c r="AN51" s="22" t="s">
-        <v>241</v>
+      <c r="AN51" s="19" t="s">
+        <v>236</v>
       </c>
       <c r="AS51" t="s">
         <v>23</v>
@@ -4684,56 +4741,54 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:51" ht="399.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>276</v>
+        <v>248</v>
       </c>
       <c r="B52" t="s">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="C52">
         <v>900</v>
       </c>
-      <c r="D52" s="20" t="s">
+      <c r="D52" s="17" t="s">
+        <v>244</v>
+      </c>
+      <c r="E52" t="s">
         <v>245</v>
       </c>
-      <c r="E52" t="s">
-        <v>242</v>
-      </c>
-      <c r="F52" t="s">
+      <c r="P52" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q52" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="P52" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q52" s="7" t="s">
+      <c r="R52" s="3">
+        <v>57.99</v>
+      </c>
+      <c r="X52" s="13">
+        <v>9781412865432</v>
+      </c>
+      <c r="Y52" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z52" s="5" t="str">
+        <f>Q52</f>
+        <v>Routledge</v>
+      </c>
+      <c r="AA52" s="5">
+        <v>44</v>
+      </c>
+      <c r="AG52" s="8">
+        <v>9781351623674</v>
+      </c>
+      <c r="AH52" t="str">
+        <f t="shared" si="0"/>
+        <v>covers/beniowski.jpg</v>
+      </c>
+      <c r="AN52" s="19" t="s">
         <v>247</v>
       </c>
-      <c r="R52" s="3">
-        <v>24.99</v>
-      </c>
-      <c r="X52" s="15">
-        <v>9781589881846</v>
-      </c>
-      <c r="Y52" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z52" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="AA52" s="5">
-        <v>9.99</v>
-      </c>
-      <c r="AG52" s="8">
-        <v>9781589883802</v>
-      </c>
-      <c r="AH52" t="str">
-        <f t="shared" si="0"/>
-        <v>covers/the-homeless.jpg</v>
-      </c>
-      <c r="AN52" s="22" t="s">
-        <v>244</v>
-      </c>
       <c r="AS52" t="s">
         <v>23</v>
       </c>
@@ -4741,56 +4796,48 @@
         <v>23</v>
       </c>
       <c r="AV52" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="53" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>249</v>
+      </c>
+      <c r="B53" t="s">
+        <v>304</v>
+      </c>
+      <c r="C53">
+        <v>600</v>
+      </c>
+      <c r="D53" s="17" t="s">
+        <v>250</v>
+      </c>
+      <c r="E53" t="s">
+        <v>251</v>
+      </c>
+      <c r="F53" s="18" t="s">
+        <v>252</v>
+      </c>
+      <c r="P53" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q53" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="B53" t="s">
-        <v>88</v>
-      </c>
-      <c r="C53">
-        <v>900</v>
-      </c>
-      <c r="D53" s="20" t="s">
-        <v>249</v>
-      </c>
-      <c r="E53" t="s">
-        <v>250</v>
-      </c>
-      <c r="P53" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q53" s="7" t="s">
-        <v>251</v>
-      </c>
       <c r="R53" s="3">
-        <v>57.99</v>
-      </c>
-      <c r="X53" s="15">
-        <v>9781412865432</v>
-      </c>
-      <c r="Y53" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="Z53" s="5" t="str">
-        <f>Q53</f>
-        <v>Routledge</v>
-      </c>
-      <c r="AA53" s="5">
-        <v>44</v>
-      </c>
-      <c r="AG53" s="8">
-        <v>9781351623674</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="X53" s="13">
+        <v>9780316498845</v>
+      </c>
+      <c r="Y53" s="4"/>
+      <c r="Z53" s="4"/>
       <c r="AH53" t="str">
         <f t="shared" si="0"/>
-        <v>covers/beniowski.jpg</v>
-      </c>
-      <c r="AN53" s="22" t="s">
-        <v>252</v>
+        <v>covers/witcher-set.jpg</v>
+      </c>
+      <c r="AN53" s="20" t="s">
+        <v>254</v>
       </c>
       <c r="AS53" t="s">
         <v>23</v>
@@ -4799,57 +4846,63 @@
         <v>23</v>
       </c>
       <c r="AV53" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B54" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C54">
-        <v>600</v>
-      </c>
-      <c r="D54" s="20" t="s">
-        <v>255</v>
+        <v>850</v>
+      </c>
+      <c r="D54" s="17" t="s">
+        <v>256</v>
       </c>
       <c r="E54" t="s">
-        <v>256</v>
-      </c>
-      <c r="F54" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="F54" t="s">
         <v>257</v>
       </c>
       <c r="P54" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q54" s="7" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="R54" s="3">
-        <v>50</v>
-      </c>
-      <c r="X54" s="15">
-        <v>9780316498845</v>
+        <v>18</v>
+      </c>
+      <c r="X54" s="13">
+        <v>9780316423694</v>
       </c>
       <c r="Y54" s="4"/>
       <c r="Z54" s="4"/>
       <c r="AH54" t="str">
         <f t="shared" si="0"/>
-        <v>covers/witcher-set.jpg</v>
-      </c>
-      <c r="AN54" s="23" t="s">
+        <v>covers/tower-fools.jpg</v>
+      </c>
+      <c r="AN54" s="19" t="s">
+        <v>258</v>
+      </c>
+      <c r="AS54" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT54" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV54" t="s">
+        <v>31</v>
+      </c>
+      <c r="AX54" t="s">
         <v>259</v>
       </c>
-      <c r="AS54" t="s">
-        <v>23</v>
-      </c>
-      <c r="AT54" t="s">
-        <v>23</v>
-      </c>
-      <c r="AV54" t="s">
-        <v>31</v>
+      <c r="AY54">
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:51" x14ac:dyDescent="0.25">
@@ -4857,40 +4910,40 @@
         <v>260</v>
       </c>
       <c r="B55" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C55">
-        <v>850</v>
-      </c>
-      <c r="D55" s="20" t="s">
+        <v>860</v>
+      </c>
+      <c r="D55" s="17" t="s">
         <v>261</v>
       </c>
       <c r="E55" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F55" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="P55" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q55" s="7" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="R55" s="3">
-        <v>18</v>
-      </c>
-      <c r="X55" s="15">
-        <v>9780316423694</v>
+        <v>9.99</v>
+      </c>
+      <c r="X55" s="13">
+        <v>9780316423717</v>
       </c>
       <c r="Y55" s="4"/>
       <c r="Z55" s="4"/>
       <c r="AH55" t="str">
         <f t="shared" si="0"/>
-        <v>covers/tower-fools.jpg</v>
-      </c>
-      <c r="AN55" s="22" t="s">
-        <v>263</v>
+        <v>covers/warrior-god.jpg</v>
+      </c>
+      <c r="AN55" s="20" t="s">
+        <v>262</v>
       </c>
       <c r="AS55" t="s">
         <v>23</v>
@@ -4902,51 +4955,51 @@
         <v>31</v>
       </c>
       <c r="AX55" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="AY55">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="B56" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="C56">
-        <v>860</v>
-      </c>
-      <c r="D56" s="20" t="s">
-        <v>266</v>
+        <v>870</v>
+      </c>
+      <c r="D56" s="17" t="s">
+        <v>264</v>
       </c>
       <c r="E56" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="F56" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="P56" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q56" s="7" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="R56" s="3">
-        <v>9.99</v>
-      </c>
-      <c r="X56" s="15">
-        <v>9780316423717</v>
+        <v>16</v>
+      </c>
+      <c r="X56" s="13">
+        <v>9780316423755</v>
       </c>
       <c r="Y56" s="4"/>
       <c r="Z56" s="4"/>
       <c r="AH56" t="str">
         <f t="shared" si="0"/>
-        <v>covers/warrior-god.jpg</v>
-      </c>
-      <c r="AN56" s="23" t="s">
-        <v>267</v>
+        <v>covers/light-perpetua.jpg</v>
+      </c>
+      <c r="AN56" s="19" t="s">
+        <v>265</v>
       </c>
       <c r="AS56" t="s">
         <v>23</v>
@@ -4958,50 +5011,67 @@
         <v>31</v>
       </c>
       <c r="AX56" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="AY56">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>266</v>
+      </c>
+      <c r="B57" t="s">
+        <v>87</v>
+      </c>
+      <c r="C57">
+        <v>553</v>
+      </c>
+      <c r="D57" s="17" t="s">
+        <v>267</v>
+      </c>
+      <c r="E57" t="s">
         <v>268</v>
       </c>
-      <c r="B57" t="s">
-        <v>309</v>
-      </c>
-      <c r="C57">
-        <v>870</v>
-      </c>
-      <c r="D57" s="20" t="s">
+      <c r="G57" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H57" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="E57" t="s">
-        <v>256</v>
-      </c>
-      <c r="F57" t="s">
-        <v>262</v>
+      <c r="I57" s="7">
+        <v>28</v>
+      </c>
+      <c r="O57" s="10">
+        <v>9780465002375</v>
       </c>
       <c r="P57" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q57" s="7" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="R57" s="3">
-        <v>16</v>
-      </c>
-      <c r="X57" s="15">
-        <v>9780316423755</v>
-      </c>
-      <c r="Y57" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="X57" s="13">
+        <v>9781845951207</v>
+      </c>
+      <c r="Y57" s="4" t="s">
+        <v>114</v>
+      </c>
       <c r="Z57" s="4"/>
+      <c r="AA57" s="5">
+        <v>8.99</v>
+      </c>
+      <c r="AG57" s="8">
+        <v>9780465012473</v>
+      </c>
       <c r="AH57" t="str">
         <f t="shared" si="0"/>
-        <v>covers/light-perpetua.jpg</v>
-      </c>
-      <c r="AN57" s="22" t="s">
+        <v>covers/red-prince.jpg</v>
+      </c>
+      <c r="AN57" s="20" t="s">
         <v>270</v>
       </c>
       <c r="AS57" t="s">
@@ -5011,70 +5081,46 @@
         <v>23</v>
       </c>
       <c r="AV57" t="s">
-        <v>31</v>
-      </c>
-      <c r="AX57" t="s">
-        <v>264</v>
-      </c>
-      <c r="AY57">
-        <v>3</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B58" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C58">
-        <v>553</v>
-      </c>
-      <c r="D58" s="20" t="s">
-        <v>272</v>
+        <v>572</v>
+      </c>
+      <c r="D58" s="17" t="s">
+        <v>273</v>
       </c>
       <c r="E58" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H58" s="7" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="I58" s="7">
-        <v>28</v>
-      </c>
-      <c r="O58" s="12">
-        <v>9780465002375</v>
-      </c>
-      <c r="P58" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q58" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="R58" s="3">
-        <v>22</v>
-      </c>
-      <c r="X58" s="15">
-        <v>9781845951207</v>
-      </c>
-      <c r="Y58" s="4" t="s">
-        <v>118</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="O58" s="10">
+        <v>9780801444715</v>
+      </c>
+      <c r="P58" s="2"/>
+      <c r="Q58" s="7"/>
+      <c r="Y58" s="4"/>
       <c r="Z58" s="4"/>
-      <c r="AA58" s="5">
-        <v>8.99</v>
-      </c>
-      <c r="AG58" s="8">
-        <v>9780465012473</v>
-      </c>
       <c r="AH58" t="str">
         <f t="shared" si="0"/>
-        <v>covers/red-prince.jpg</v>
-      </c>
-      <c r="AN58" s="23" t="s">
+        <v>covers/adam-mickiewicz.jpg</v>
+      </c>
+      <c r="AN58" s="20" t="s">
         <v>275</v>
       </c>
       <c r="AS58" t="s">
@@ -5089,31 +5135,34 @@
     </row>
     <row r="59" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>278</v>
+      </c>
+      <c r="B59" t="s">
+        <v>127</v>
+      </c>
+      <c r="C59">
+        <v>832</v>
+      </c>
+      <c r="D59" s="17" t="s">
         <v>277</v>
       </c>
-      <c r="B59" t="s">
-        <v>88</v>
-      </c>
-      <c r="C59">
-        <v>572</v>
-      </c>
-      <c r="D59" s="20" t="s">
-        <v>278</v>
-      </c>
       <c r="E59" t="s">
-        <v>279</v>
+        <v>51</v>
+      </c>
+      <c r="F59" t="s">
+        <v>281</v>
       </c>
       <c r="G59" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H59" s="7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I59" s="7">
-        <v>45</v>
-      </c>
-      <c r="O59" s="12">
-        <v>9780801444715</v>
+        <v>31</v>
+      </c>
+      <c r="O59" s="10">
+        <v>9781911414018</v>
       </c>
       <c r="P59" s="2"/>
       <c r="Q59" s="7"/>
@@ -5121,10 +5170,10 @@
       <c r="Z59" s="4"/>
       <c r="AH59" t="str">
         <f t="shared" si="0"/>
-        <v>covers/adam-mickiewicz.jpg</v>
-      </c>
-      <c r="AN59" s="23" t="s">
-        <v>280</v>
+        <v>covers/forefathers-eve.jpg</v>
+      </c>
+      <c r="AN59" s="20" t="s">
+        <v>279</v>
       </c>
       <c r="AS59" t="s">
         <v>23</v>
@@ -5133,7 +5182,7 @@
         <v>23</v>
       </c>
       <c r="AV59" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="60" spans="1:51" x14ac:dyDescent="0.25">
@@ -5141,31 +5190,31 @@
         <v>283</v>
       </c>
       <c r="B60" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C60">
-        <v>832</v>
-      </c>
-      <c r="D60" s="20" t="s">
+        <v>900</v>
+      </c>
+      <c r="D60" s="17" t="s">
         <v>282</v>
       </c>
       <c r="E60" t="s">
         <v>51</v>
       </c>
       <c r="F60" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="I60" s="7">
-        <v>31</v>
-      </c>
-      <c r="O60" s="12">
-        <v>9781911414018</v>
+        <v>27</v>
+      </c>
+      <c r="O60" s="10">
+        <v>9781804840016</v>
       </c>
       <c r="P60" s="2"/>
       <c r="Q60" s="7"/>
@@ -5173,9 +5222,9 @@
       <c r="Z60" s="4"/>
       <c r="AH60" t="str">
         <f t="shared" si="0"/>
-        <v>covers/forefathers-eve.jpg</v>
-      </c>
-      <c r="AN60" s="23" t="s">
+        <v>covers/ballads-romances.jpg</v>
+      </c>
+      <c r="AN60" s="19" t="s">
         <v>284</v>
       </c>
       <c r="AS60" t="s">
@@ -5190,45 +5239,44 @@
     </row>
     <row r="61" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B61" t="s">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="C61">
-        <v>900</v>
-      </c>
-      <c r="D61" s="20" t="s">
+        <v>902</v>
+      </c>
+      <c r="D61" s="17" t="s">
+        <v>286</v>
+      </c>
+      <c r="E61" t="s">
+        <v>128</v>
+      </c>
+      <c r="F61" t="s">
         <v>287</v>
       </c>
-      <c r="E61" t="s">
-        <v>51</v>
-      </c>
-      <c r="F61" t="s">
-        <v>286</v>
-      </c>
-      <c r="G61" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="H61" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="I61" s="7">
-        <v>27</v>
-      </c>
-      <c r="O61" s="12">
-        <v>9781804840016</v>
-      </c>
-      <c r="P61" s="2"/>
-      <c r="Q61" s="7"/>
+      <c r="G61" s="6"/>
+      <c r="P61" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q61" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="R61" s="3">
+        <v>16</v>
+      </c>
+      <c r="X61" s="13">
+        <v>9780374528300</v>
+      </c>
       <c r="Y61" s="4"/>
       <c r="Z61" s="4"/>
       <c r="AH61" t="str">
         <f t="shared" si="0"/>
-        <v>covers/ballads-romances.jpg</v>
-      </c>
-      <c r="AN61" s="22" t="s">
-        <v>289</v>
+        <v>covers/native-realm.jpg</v>
+      </c>
+      <c r="AN61" s="19" t="s">
+        <v>288</v>
       </c>
       <c r="AS61" t="s">
         <v>23</v>
@@ -5242,43 +5290,41 @@
     </row>
     <row r="62" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
+        <v>289</v>
+      </c>
+      <c r="B62" t="s">
+        <v>87</v>
+      </c>
+      <c r="C62">
+        <v>903</v>
+      </c>
+      <c r="D62" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="B62" t="s">
-        <v>75</v>
-      </c>
-      <c r="C62">
-        <v>902</v>
-      </c>
-      <c r="D62" s="20" t="s">
+      <c r="E62" t="s">
+        <v>128</v>
+      </c>
+      <c r="G62" s="6"/>
+      <c r="P62" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q62" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="E62" t="s">
-        <v>132</v>
-      </c>
-      <c r="F62" t="s">
-        <v>292</v>
-      </c>
-      <c r="P62" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q62" s="7" t="s">
-        <v>140</v>
-      </c>
       <c r="R62" s="3">
-        <v>16</v>
-      </c>
-      <c r="X62" s="15">
-        <v>9780374528300</v>
+        <v>41</v>
+      </c>
+      <c r="X62" s="13">
+        <v>9780520044777</v>
       </c>
       <c r="Y62" s="4"/>
       <c r="Z62" s="4"/>
       <c r="AH62" t="str">
         <f t="shared" si="0"/>
-        <v>covers/native-realm.jpg</v>
-      </c>
-      <c r="AN62" s="22" t="s">
-        <v>293</v>
+        <v>covers/history-lit-milosz.jpg</v>
+      </c>
+      <c r="AN62" s="19" t="s">
+        <v>295</v>
       </c>
       <c r="AS62" t="s">
         <v>23</v>
@@ -5292,40 +5338,41 @@
     </row>
     <row r="63" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>293</v>
+      </c>
+      <c r="B63" t="s">
+        <v>127</v>
+      </c>
+      <c r="C63">
+        <v>872</v>
+      </c>
+      <c r="D63" s="17" t="s">
+        <v>292</v>
+      </c>
+      <c r="E63" t="s">
         <v>294</v>
       </c>
-      <c r="B63" t="s">
-        <v>88</v>
-      </c>
-      <c r="C63">
-        <v>903</v>
-      </c>
-      <c r="D63" s="20" t="s">
-        <v>295</v>
-      </c>
-      <c r="E63" t="s">
-        <v>132</v>
-      </c>
+      <c r="G63" s="6"/>
       <c r="P63" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q63" s="7" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="R63" s="3">
-        <v>41</v>
-      </c>
-      <c r="X63" s="15">
-        <v>9780520044777</v>
+        <v>22</v>
+      </c>
+      <c r="X63" s="13">
+        <v>9780520044760</v>
       </c>
       <c r="Y63" s="4"/>
       <c r="Z63" s="4"/>
       <c r="AH63" t="str">
         <f t="shared" si="0"/>
-        <v>covers/history-lit-milosz.jpg</v>
-      </c>
-      <c r="AN63" s="22" t="s">
-        <v>300</v>
+        <v>covers/postwar-polish-poetry.jpg</v>
+      </c>
+      <c r="AN63" s="19" t="s">
+        <v>296</v>
       </c>
       <c r="AS63" t="s">
         <v>23</v>
@@ -5339,87 +5386,90 @@
     </row>
     <row r="64" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>297</v>
+      </c>
+      <c r="B64" t="s">
+        <v>74</v>
+      </c>
+      <c r="C64">
+        <v>457</v>
+      </c>
+      <c r="D64" s="17" t="s">
         <v>298</v>
       </c>
-      <c r="B64" t="s">
-        <v>131</v>
-      </c>
-      <c r="C64">
-        <v>872</v>
-      </c>
-      <c r="D64" s="20" t="s">
-        <v>297</v>
-      </c>
       <c r="E64" t="s">
-        <v>299</v>
-      </c>
+        <v>128</v>
+      </c>
+      <c r="G64" s="6"/>
       <c r="P64" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="Q64" s="7" t="s">
-        <v>296</v>
+        <v>269</v>
       </c>
       <c r="R64" s="3">
-        <v>22</v>
-      </c>
-      <c r="X64" s="15">
-        <v>9780520044760</v>
+        <v>13</v>
+      </c>
+      <c r="X64" s="13">
+        <v>9780679728566</v>
       </c>
       <c r="Y64" s="4"/>
       <c r="Z64" s="4"/>
       <c r="AH64" t="str">
         <f t="shared" si="0"/>
-        <v>covers/postwar-polish-poetry.jpg</v>
-      </c>
-      <c r="AN64" s="22" t="s">
+        <v>covers/captive-mind.jpg</v>
+      </c>
+      <c r="AN64" s="19" t="s">
+        <v>299</v>
+      </c>
+      <c r="AS64" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT64" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV64" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="65" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>301</v>
       </c>
-      <c r="AS64" t="s">
-        <v>23</v>
-      </c>
-      <c r="AT64" t="s">
-        <v>23</v>
-      </c>
-      <c r="AV64" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="65" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
+      <c r="B65" t="s">
+        <v>127</v>
+      </c>
+      <c r="C65">
+        <v>1100</v>
+      </c>
+      <c r="D65" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="E65" t="s">
+        <v>203</v>
+      </c>
+      <c r="F65" t="s">
         <v>302</v>
       </c>
-      <c r="B65" t="s">
-        <v>75</v>
-      </c>
-      <c r="C65">
-        <v>457</v>
-      </c>
-      <c r="D65" s="20" t="s">
-        <v>303</v>
-      </c>
-      <c r="E65" t="s">
-        <v>132</v>
-      </c>
+      <c r="G65" s="6"/>
       <c r="P65" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q65" s="7" t="s">
-        <v>274</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="Q65" s="7"/>
       <c r="R65" s="3">
-        <v>13</v>
-      </c>
-      <c r="X65" s="15">
-        <v>9780679728566</v>
+        <v>14</v>
+      </c>
+      <c r="X65" s="13">
+        <v>9781419679995</v>
       </c>
       <c r="Y65" s="4"/>
       <c r="Z65" s="4"/>
       <c r="AH65" t="str">
         <f t="shared" si="0"/>
-        <v>covers/captive-mind.jpg</v>
-      </c>
-      <c r="AN65" s="22" t="s">
-        <v>304</v>
+        <v>covers/selected-masterpieces.jpg</v>
+      </c>
+      <c r="AN65" s="19" t="s">
+        <v>303</v>
       </c>
       <c r="AS65" t="s">
         <v>23</v>
@@ -5431,43 +5481,54 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:48" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:51" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B66" t="s">
-        <v>131</v>
+        <v>78</v>
       </c>
       <c r="C66">
-        <v>1100</v>
-      </c>
-      <c r="D66" s="20" t="s">
-        <v>305</v>
+        <v>1200</v>
+      </c>
+      <c r="D66" s="17" t="s">
+        <v>307</v>
       </c>
       <c r="E66" t="s">
-        <v>207</v>
-      </c>
-      <c r="F66" t="s">
-        <v>307</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="G66" s="6"/>
       <c r="P66" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q66" s="7"/>
+        <v>113</v>
+      </c>
+      <c r="Q66" s="7" t="s">
+        <v>310</v>
+      </c>
       <c r="R66" s="3">
-        <v>14</v>
-      </c>
-      <c r="X66" s="15">
-        <v>9781419679995</v>
-      </c>
-      <c r="Y66" s="4"/>
-      <c r="Z66" s="4"/>
+        <v>30</v>
+      </c>
+      <c r="X66" s="13">
+        <v>9781734860610</v>
+      </c>
+      <c r="Y66" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z66" s="4" t="str">
+        <f>Q66</f>
+        <v>Royal Hawaiian Press</v>
+      </c>
+      <c r="AA66" s="5">
+        <v>9.99</v>
+      </c>
+      <c r="AG66" s="8">
+        <v>9781386745006</v>
+      </c>
       <c r="AH66" t="str">
-        <f t="shared" si="0"/>
-        <v>covers/selected-masterpieces.jpg</v>
-      </c>
-      <c r="AN66" s="22" t="s">
-        <v>304</v>
+        <f>"covers/" &amp; A66 &amp; ".jpg"</f>
+        <v>covers/hyenas-lotuses.jpg</v>
+      </c>
+      <c r="AN66" s="19" t="s">
+        <v>311</v>
       </c>
       <c r="AS66" t="s">
         <v>23</v>
@@ -5479,12 +5540,65 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="Q67" s="7"/>
-      <c r="Y67" s="4"/>
-      <c r="Z67" s="4"/>
-      <c r="AN67" s="22" t="s">
-        <v>308</v>
+    <row r="67" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>315</v>
+      </c>
+      <c r="B67" t="s">
+        <v>78</v>
+      </c>
+      <c r="C67">
+        <v>1300</v>
+      </c>
+      <c r="D67" s="17" t="s">
+        <v>314</v>
+      </c>
+      <c r="E67" t="s">
+        <v>313</v>
+      </c>
+      <c r="G67" s="6"/>
+      <c r="P67" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q67" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="R67" s="3">
+        <v>19</v>
+      </c>
+      <c r="X67" s="13">
+        <v>9781250218018</v>
+      </c>
+      <c r="Y67" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z67" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="AA67" s="5">
+        <v>11.99</v>
+      </c>
+      <c r="AG67" s="8">
+        <v>9781250217981</v>
+      </c>
+      <c r="AH67" t="str">
+        <f>"covers/" &amp; A67 &amp; ".jpg"</f>
+        <v>covers/widow-queen.jpg</v>
+      </c>
+      <c r="AN67" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="AO67" t="s">
+        <v>317</v>
+      </c>
+      <c r="AP67" t="s">
+        <v>318</v>
+      </c>
+      <c r="AQ67" t="s">
+        <v>319</v>
+      </c>
+      <c r="AR67" t="s">
+        <v>320</v>
       </c>
       <c r="AS67" t="s">
         <v>23</v>
@@ -5495,123 +5609,160 @@
       <c r="AV67" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="68" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="Q68" s="7"/>
+      <c r="AX67" t="s">
+        <v>316</v>
+      </c>
+      <c r="AY67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>322</v>
+      </c>
+      <c r="B68" t="s">
+        <v>78</v>
+      </c>
+      <c r="C68">
+        <v>1350</v>
+      </c>
+      <c r="D68" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="E68" t="s">
+        <v>313</v>
+      </c>
+      <c r="F68" t="s">
+        <v>323</v>
+      </c>
+      <c r="G68" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H68" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="I68" s="7">
+        <v>28.99</v>
+      </c>
+      <c r="O68" s="10">
+        <v>9781250775740</v>
+      </c>
+      <c r="P68" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q68" s="7" t="s">
+        <v>325</v>
+      </c>
+      <c r="R68" s="3">
+        <v>20.99</v>
+      </c>
+      <c r="X68" s="13">
+        <v>9781250775764</v>
+      </c>
       <c r="Y68" s="4"/>
       <c r="Z68" s="4"/>
-    </row>
-    <row r="69" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="Q69" s="7"/>
-      <c r="Y69" s="4"/>
-      <c r="Z69" s="4"/>
-    </row>
-    <row r="70" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="Q70" s="7"/>
-      <c r="Y70" s="4"/>
-      <c r="Z70" s="4"/>
-    </row>
-    <row r="71" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="Q71" s="7"/>
-      <c r="Y71" s="4"/>
-      <c r="Z71" s="4"/>
-      <c r="AA71" s="4"/>
-    </row>
-    <row r="72" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="Q72" s="7"/>
-      <c r="Y72" s="4"/>
-      <c r="Z72" s="4"/>
-    </row>
-    <row r="73" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="Q73" s="7"/>
-      <c r="Y73" s="4"/>
-      <c r="Z73" s="4"/>
-    </row>
-    <row r="74" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="Q74" s="7"/>
-      <c r="Y74" s="4"/>
-      <c r="Z74" s="4"/>
-    </row>
-    <row r="75" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="Q75" s="7"/>
-      <c r="Y75" s="4"/>
-      <c r="Z75" s="4"/>
-      <c r="AG75" s="5"/>
-    </row>
-    <row r="76" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="Q76" s="7"/>
-      <c r="W76" s="9"/>
-      <c r="Y76" s="4"/>
-      <c r="Z76" s="4"/>
-      <c r="AF76" s="8"/>
-      <c r="AG76" s="5"/>
-      <c r="AM76" s="11"/>
-    </row>
-    <row r="77" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="Q77" s="7"/>
-      <c r="W77" s="9"/>
-      <c r="Y77" s="4"/>
-      <c r="Z77" s="4"/>
-      <c r="AF77" s="8"/>
-      <c r="AG77" s="5"/>
-      <c r="AM77" s="11"/>
-    </row>
-    <row r="78" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="Q78" s="7"/>
-      <c r="W78" s="9"/>
-      <c r="Y78" s="4"/>
-      <c r="Z78" s="4"/>
-      <c r="AF78" s="8"/>
-      <c r="AG78" s="5"/>
-      <c r="AM78" s="11"/>
-    </row>
-    <row r="79" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="Q79" s="7"/>
-      <c r="W79" s="9"/>
-      <c r="Y79" s="4"/>
-      <c r="AF79" s="8"/>
-      <c r="AG79" s="5"/>
-      <c r="AM79" s="11"/>
-    </row>
-    <row r="80" spans="1:48" x14ac:dyDescent="0.25">
-      <c r="Q80" s="7"/>
-      <c r="W80" s="9"/>
-      <c r="AF80" s="8"/>
-      <c r="AG80" s="5"/>
-      <c r="AM80" s="11"/>
-    </row>
-    <row r="81" spans="17:39" x14ac:dyDescent="0.25">
-      <c r="Q81" s="7"/>
-      <c r="W81" s="9"/>
-      <c r="AF81" s="8"/>
-      <c r="AG81" s="5"/>
-      <c r="AM81" s="11"/>
-    </row>
-    <row r="82" spans="17:39" x14ac:dyDescent="0.25">
-      <c r="Q82" s="7"/>
-      <c r="W82" s="9"/>
-      <c r="AF82" s="8"/>
-      <c r="AG82" s="5"/>
-      <c r="AM82" s="11"/>
-    </row>
-    <row r="83" spans="17:39" x14ac:dyDescent="0.25">
-      <c r="W83" s="9"/>
-      <c r="AF83" s="8"/>
-      <c r="AG83" s="5"/>
-      <c r="AM83" s="11"/>
-    </row>
-    <row r="84" spans="17:39" x14ac:dyDescent="0.25">
-      <c r="W84" s="9"/>
-      <c r="AF84" s="8"/>
-      <c r="AM84" s="11"/>
+      <c r="AH68" t="str">
+        <f>"covers/" &amp; A68 &amp; ".jpg"</f>
+        <v>covers/last-crown.jpg</v>
+      </c>
+      <c r="AN68" s="19" t="s">
+        <v>324</v>
+      </c>
+      <c r="AO68" t="s">
+        <v>317</v>
+      </c>
+      <c r="AP68" t="s">
+        <v>318</v>
+      </c>
+      <c r="AQ68" t="s">
+        <v>319</v>
+      </c>
+      <c r="AR68" t="s">
+        <v>320</v>
+      </c>
+      <c r="AS68" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT68" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV68" t="s">
+        <v>31</v>
+      </c>
+      <c r="AX68" t="s">
+        <v>316</v>
+      </c>
+      <c r="AY68">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>271</v>
+      </c>
+      <c r="B69" t="s">
+        <v>40</v>
+      </c>
+      <c r="C69">
+        <v>900</v>
+      </c>
+      <c r="D69" s="17" t="s">
+        <v>240</v>
+      </c>
+      <c r="E69" t="s">
+        <v>237</v>
+      </c>
+      <c r="F69" t="s">
+        <v>241</v>
+      </c>
+      <c r="P69" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q69" s="7" t="s">
+        <v>242</v>
+      </c>
+      <c r="R69" s="3">
+        <v>24.99</v>
+      </c>
+      <c r="X69" s="13">
+        <v>9781589881846</v>
+      </c>
+      <c r="Y69" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z69" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="AA69" s="5">
+        <v>9.99</v>
+      </c>
+      <c r="AG69" s="8">
+        <v>9781589883802</v>
+      </c>
+      <c r="AH69" t="str">
+        <f t="shared" ref="AH69" si="1">"covers/" &amp; A69 &amp; ".jpg"</f>
+        <v>covers/the-homeless.jpg</v>
+      </c>
+      <c r="AN69" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="AS69" t="s">
+        <v>23</v>
+      </c>
+      <c r="AT69" t="s">
+        <v>23</v>
+      </c>
+      <c r="AV69" t="s">
+        <v>31</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y85:Z1048576 P85:Q1048576 Q43:Q47 O76:P84 O44 AG44 X44 Y80:Y84 H72:H1048576 G62:G1048576 X75:X83 G47 G49:G57 P67:P75" xr:uid="{D2C177B6-092A-4420-B1E2-D1681CD512E9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P70:Q1048576 H70:H1048576 Q43:Q47 O44 AG44 X44 G47 Y70:Z1048576 G69:G1048576 G49:G56" xr:uid="{D2C177B6-092A-4420-B1E2-D1681CD512E9}">
       <formula1>"hardcover, paperback, eBook, audiobook1"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AR76:AS84 AS85:AT1048576 AS1:AT75" xr:uid="{F1FB7CD6-B38A-4A39-862C-8A1111411C8C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AS1:AT1048576" xr:uid="{F1FB7CD6-B38A-4A39-862C-8A1111411C8C}">
       <formula1>"yes, no"</formula1>
     </dataValidation>
   </dataValidations>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/the-polish-atheneum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1763" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AD62E5E-EBF4-493A-87BB-950F315172FF}"/>
+  <xr:revisionPtr revIDLastSave="1784" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5E08E28-F7BD-4B60-BC07-B1C3636C7431}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1421" uniqueCount="626">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="631">
   <si>
     <t>cover</t>
   </si>
@@ -1741,9 +1741,6 @@
     <t>Eliza Marciniak</t>
   </si>
   <si>
-    <t>Srone Tablets</t>
-  </si>
-  <si>
     <t>stone-tablets</t>
   </si>
   <si>
@@ -2672,9 +2669,6 @@
 In their new story, the creators of The Lost Soul—Nobel prize in literature winner Olga Tokarczuk and illustrator Joanna Concejo—show us a world of obsession with personal appearance and self-promotion, where happiness is an imperative, and the cult of youth rules.</t>
   </si>
   <si>
-    <t>Trhe Lost Soul</t>
-  </si>
-  <si>
     <t>lost-soul</t>
   </si>
   <si>
@@ -2716,6 +2710,37 @@
   </si>
   <si>
     <t>Mud Sweeter Than Honey: Voices of Communist Albania</t>
+  </si>
+  <si>
+    <t>Stone Tablets</t>
+  </si>
+  <si>
+    <t>The Lost Soul</t>
+  </si>
+  <si>
+    <t>torn-curtain</t>
+  </si>
+  <si>
+    <t>Karolina and the Torn Curtain</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ‘An ingenious marriage of comedy and crime.’ Olga Tokarczuk, 2018 winner of the Nobel Prize in Literature
+Shortlisted for the EBRD Literature Prize 2022
+For fans of The Thursday Murder Club and Frank Tallis's Vienna Blood comes the thrilling sequel to the critically-acclaimed Mrs Mohr Goes Missing
+Easter, 1895.
+The biggest event in the Catholic calendar is a disaster in Zofia Turbotyńska’s household. Her maid Karolina has handed in her notice and worse, gone missing. When Karolina’s body is discovered, violated and stabbed, Zofia knows she has to investigate.
+Following a trail that leads her from the poorest districts of Galicia to the highest echelons of society, Zofia uncovers a web of gang crimes, sex-trafficking and corruption that will force her to question everything she knows. 
+Set against the backdrop of the women’s cause, Karolina, or the Torn Curtain refuses to turn a blind eye to the injustices and inequalities of its era – and ours.
+Praise for the series:
+‘The sprightly narrative and vivid evocation of turn-of-the-century Poland make for an enjoyable tale.’ Guardian
+‘It’s fun and sparky and the glimpse of  turn-of-the-century Polish manners and mores is beguiling.’ Daily Mail
+‘The story fuses high comedy with an evocative portrayal of the period.’ Sunday Express</t>
+  </si>
+  <si>
+    <t>Point Blank</t>
+  </si>
+  <si>
+    <t>Zofia Turbotynska Mysteries</t>
   </si>
 </sst>
 </file>
@@ -2892,7 +2917,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2916,18 +2941,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2935,6 +2953,12 @@
     <xf numFmtId="1" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3285,15 +3309,15 @@
     <col min="12" max="14" width="9.140625" style="7"/>
     <col min="15" max="15" width="28.85546875" style="10" customWidth="1"/>
     <col min="16" max="23" width="9.140625" style="3"/>
-    <col min="24" max="24" width="17" style="28" customWidth="1"/>
+    <col min="24" max="24" width="17" style="21" customWidth="1"/>
     <col min="25" max="32" width="9.140625" style="5"/>
     <col min="33" max="33" width="22" style="8" customWidth="1"/>
     <col min="34" max="35" width="26.28515625" customWidth="1"/>
     <col min="38" max="38" width="16" customWidth="1"/>
     <col min="40" max="40" width="21.140625" customWidth="1"/>
-    <col min="41" max="41" width="95.85546875" style="17" customWidth="1"/>
-    <col min="42" max="42" width="19.7109375" style="24" customWidth="1"/>
-    <col min="43" max="45" width="19.7109375" style="19" customWidth="1"/>
+    <col min="41" max="41" width="95.85546875" style="25" customWidth="1"/>
+    <col min="42" max="42" width="19.7109375" style="26" customWidth="1"/>
+    <col min="43" max="45" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:52" x14ac:dyDescent="0.25">
@@ -3366,7 +3390,7 @@
       <c r="W1" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="X1" s="28" t="s">
+      <c r="X1" s="21" t="s">
         <v>175</v>
       </c>
       <c r="Y1" s="4" t="s">
@@ -3417,19 +3441,19 @@
       <c r="AN1" t="s">
         <v>21</v>
       </c>
-      <c r="AO1" s="17" t="s">
+      <c r="AO1" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="AP1" s="24" t="s">
+      <c r="AP1" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="AQ1" s="19" t="s">
+      <c r="AQ1" t="s">
         <v>207</v>
       </c>
-      <c r="AR1" s="19" t="s">
+      <c r="AR1" t="s">
         <v>205</v>
       </c>
-      <c r="AS1" s="19" t="s">
+      <c r="AS1" t="s">
         <v>208</v>
       </c>
       <c r="AT1" t="s">
@@ -3492,7 +3516,7 @@
       <c r="T2" s="3">
         <v>15</v>
       </c>
-      <c r="X2" s="29">
+      <c r="X2" s="22">
         <v>9780306809330</v>
       </c>
       <c r="Y2" s="4" t="s">
@@ -3515,19 +3539,19 @@
         <f>"covers/" &amp; A2 &amp; ".jpg"</f>
         <v>covers/chopin-in-paris.jpg</v>
       </c>
-      <c r="AO2" s="17" t="s">
+      <c r="AO2" s="25" t="s">
         <v>324</v>
       </c>
-      <c r="AP2" s="24" t="s">
+      <c r="AP2" s="26" t="s">
         <v>325</v>
       </c>
-      <c r="AQ2" s="19" t="s">
+      <c r="AQ2" t="s">
         <v>326</v>
       </c>
-      <c r="AR2" s="19" t="s">
+      <c r="AR2" t="s">
         <v>327</v>
       </c>
-      <c r="AS2" s="19" t="s">
+      <c r="AS2" t="s">
         <v>328</v>
       </c>
       <c r="AT2" t="s">
@@ -3578,7 +3602,7 @@
       <c r="T3" s="3">
         <v>15</v>
       </c>
-      <c r="X3" s="29">
+      <c r="X3" s="22">
         <v>9780312625948</v>
       </c>
       <c r="Y3" s="4" t="s">
@@ -3601,7 +3625,7 @@
         <f t="shared" ref="AH3:AH66" si="0">"covers/" &amp; A3 &amp; ".jpg"</f>
         <v>covers/peasant-prince.jpg</v>
       </c>
-      <c r="AO3" s="17" t="s">
+      <c r="AO3" s="25" t="s">
         <v>329</v>
       </c>
       <c r="AT3" t="s">
@@ -3647,7 +3671,7 @@
       <c r="T4" s="3">
         <v>16</v>
       </c>
-      <c r="X4" s="29">
+      <c r="X4" s="22">
         <v>9780008521684</v>
       </c>
       <c r="Y4" s="4" t="s">
@@ -3670,19 +3694,19 @@
         <f t="shared" si="0"/>
         <v>covers/izabela-the-valiant.jpg</v>
       </c>
-      <c r="AO4" s="17" t="s">
+      <c r="AO4" s="25" t="s">
         <v>330</v>
       </c>
-      <c r="AP4" s="25" t="s">
+      <c r="AP4" s="27" t="s">
         <v>331</v>
       </c>
-      <c r="AQ4" s="19" t="s">
+      <c r="AQ4" t="s">
         <v>333</v>
       </c>
-      <c r="AR4" s="20" t="s">
+      <c r="AR4" s="17" t="s">
         <v>334</v>
       </c>
-      <c r="AS4" s="19" t="s">
+      <c r="AS4" t="s">
         <v>332</v>
       </c>
       <c r="AT4" t="s">
@@ -3728,17 +3752,17 @@
       </c>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
-      <c r="X5" s="29"/>
+      <c r="X5" s="22"/>
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
       <c r="AH5" t="str">
         <f t="shared" si="0"/>
         <v>covers/light-and-flame.jpg</v>
       </c>
-      <c r="AO5" s="17" t="s">
+      <c r="AO5" s="25" t="s">
         <v>335</v>
       </c>
-      <c r="AP5" s="24" t="s">
+      <c r="AP5" s="26" t="s">
         <v>336</v>
       </c>
       <c r="AT5" t="s">
@@ -3784,7 +3808,7 @@
       </c>
       <c r="P6" s="2"/>
       <c r="Q6" s="2"/>
-      <c r="X6" s="29"/>
+      <c r="X6" s="22"/>
       <c r="Y6" s="4" t="s">
         <v>114</v>
       </c>
@@ -3805,7 +3829,7 @@
         <f t="shared" si="0"/>
         <v>covers/trail-of-hope.jpg</v>
       </c>
-      <c r="AO6" s="17" t="s">
+      <c r="AO6" s="25" t="s">
         <v>337</v>
       </c>
       <c r="AT6" t="s">
@@ -3859,7 +3883,7 @@
       <c r="T7" s="3">
         <v>18</v>
       </c>
-      <c r="X7" s="29">
+      <c r="X7" s="22">
         <v>9781607720058</v>
       </c>
       <c r="Y7" s="4"/>
@@ -3868,10 +3892,10 @@
         <f t="shared" si="0"/>
         <v>covers/303-squadron.jpg</v>
       </c>
-      <c r="AO7" s="17" t="s">
+      <c r="AO7" s="25" t="s">
         <v>338</v>
       </c>
-      <c r="AP7" s="24" t="s">
+      <c r="AP7" s="26" t="s">
         <v>339</v>
       </c>
       <c r="AT7" t="s">
@@ -3918,7 +3942,7 @@
       <c r="T8" s="3">
         <v>14</v>
       </c>
-      <c r="X8" s="29">
+      <c r="X8" s="22">
         <v>9781590173831</v>
       </c>
       <c r="Y8" s="4" t="s">
@@ -3941,7 +3965,7 @@
         <f t="shared" si="0"/>
         <v>covers/the-doll.jpg</v>
       </c>
-      <c r="AO8" s="17" t="s">
+      <c r="AO8" s="25" t="s">
         <v>341</v>
       </c>
       <c r="AT8" t="s">
@@ -3988,7 +4012,7 @@
       <c r="T9" s="3">
         <v>17</v>
       </c>
-      <c r="X9" s="29">
+      <c r="X9" s="22">
         <v>9780241524244</v>
       </c>
       <c r="Y9" s="4"/>
@@ -3997,7 +4021,7 @@
         <f t="shared" si="0"/>
         <v>covers/the-peasants.jpg</v>
       </c>
-      <c r="AO9" s="17" t="s">
+      <c r="AO9" s="25" t="s">
         <v>340</v>
       </c>
       <c r="AT9" t="s">
@@ -4045,7 +4069,7 @@
       <c r="T10" s="3">
         <v>13</v>
       </c>
-      <c r="X10" s="29">
+      <c r="X10" s="22">
         <v>9781939810007</v>
       </c>
       <c r="Y10" s="4"/>
@@ -4054,10 +4078,10 @@
         <f t="shared" si="0"/>
         <v>covers/pan-tadeusz.jpg</v>
       </c>
-      <c r="AO10" s="17" t="s">
+      <c r="AO10" s="25" t="s">
         <v>359</v>
       </c>
-      <c r="AP10" s="24" t="s">
+      <c r="AP10" s="26" t="s">
         <v>360</v>
       </c>
       <c r="AT10" t="s">
@@ -4104,7 +4128,7 @@
       <c r="T11" s="3">
         <v>17</v>
       </c>
-      <c r="X11" s="29">
+      <c r="X11" s="22">
         <v>9780875807072</v>
       </c>
       <c r="Y11" s="4"/>
@@ -4113,10 +4137,10 @@
         <f t="shared" si="0"/>
         <v>covers/choucas.jpg</v>
       </c>
-      <c r="AO11" s="17" t="s">
+      <c r="AO11" s="25" t="s">
         <v>361</v>
       </c>
-      <c r="AP11" s="24" t="s">
+      <c r="AP11" s="26" t="s">
         <v>362</v>
       </c>
       <c r="AT11" t="s">
@@ -4176,7 +4200,7 @@
       <c r="T12" s="3">
         <v>14</v>
       </c>
-      <c r="X12" s="29">
+      <c r="X12" s="22">
         <v>9798245149318</v>
       </c>
       <c r="Y12" s="4"/>
@@ -4185,7 +4209,7 @@
         <f t="shared" si="0"/>
         <v>covers/desert-wilderness.jpg</v>
       </c>
-      <c r="AO12" s="17" t="s">
+      <c r="AO12" s="25" t="s">
         <v>363</v>
       </c>
       <c r="AT12" t="s">
@@ -4231,14 +4255,14 @@
       </c>
       <c r="P13" s="2"/>
       <c r="Q13" s="2"/>
-      <c r="X13" s="29"/>
+      <c r="X13" s="22"/>
       <c r="Y13" s="4"/>
       <c r="Z13" s="4"/>
       <c r="AH13" t="str">
         <f t="shared" si="0"/>
         <v>covers/forest-folk.jpg</v>
       </c>
-      <c r="AO13" s="17" t="s">
+      <c r="AO13" s="25" t="s">
         <v>364</v>
       </c>
       <c r="AT13" t="s">
@@ -4293,7 +4317,7 @@
       <c r="T14" s="3">
         <v>10</v>
       </c>
-      <c r="X14" s="29">
+      <c r="X14" s="22">
         <v>9781852429454</v>
       </c>
       <c r="Y14" s="4"/>
@@ -4302,10 +4326,10 @@
         <f t="shared" si="0"/>
         <v>covers/castorp.jpg</v>
       </c>
-      <c r="AO14" s="17" t="s">
+      <c r="AO14" s="25" t="s">
         <v>365</v>
       </c>
-      <c r="AP14" s="24" t="s">
+      <c r="AP14" s="26" t="s">
         <v>366</v>
       </c>
       <c r="AT14" t="s">
@@ -4352,7 +4376,7 @@
       <c r="T15" s="3">
         <v>12</v>
       </c>
-      <c r="X15" s="29">
+      <c r="X15" s="22">
         <v>9780679738015</v>
       </c>
       <c r="Y15" s="4"/>
@@ -4361,10 +4385,10 @@
         <f t="shared" si="0"/>
         <v>covers/shah-of-shahs.jpg</v>
       </c>
-      <c r="AO15" s="17" t="s">
+      <c r="AO15" s="25" t="s">
         <v>367</v>
       </c>
-      <c r="AP15" s="24" t="s">
+      <c r="AP15" s="26" t="s">
         <v>369</v>
       </c>
       <c r="AT15" t="s">
@@ -4411,7 +4435,7 @@
       <c r="T16" s="3">
         <v>12</v>
       </c>
-      <c r="X16" s="29">
+      <c r="X16" s="22">
         <v>9780141188034</v>
       </c>
       <c r="Y16" s="4"/>
@@ -4420,10 +4444,10 @@
         <f t="shared" si="0"/>
         <v>covers/the-emperor.jpg</v>
       </c>
-      <c r="AO16" s="17" t="s">
+      <c r="AO16" s="25" t="s">
         <v>370</v>
       </c>
-      <c r="AP16" s="24" t="s">
+      <c r="AP16" s="26" t="s">
         <v>371</v>
       </c>
       <c r="AT16" t="s">
@@ -4446,7 +4470,7 @@
       <c r="C17">
         <v>420</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="19" t="s">
         <v>75</v>
       </c>
       <c r="E17" t="s">
@@ -4456,7 +4480,7 @@
         <v>368</v>
       </c>
       <c r="G17" s="6"/>
-      <c r="O17" s="21"/>
+      <c r="O17" s="18"/>
       <c r="P17" s="2" t="s">
         <v>113</v>
       </c>
@@ -4470,7 +4494,7 @@
       <c r="T17" s="3">
         <v>11</v>
       </c>
-      <c r="X17" s="29">
+      <c r="X17" s="22">
         <v>9780375726293</v>
       </c>
       <c r="Y17" s="4"/>
@@ -4479,12 +4503,9 @@
         <f>"covers/" &amp; A17 &amp; ".jpg"</f>
         <v>covers/another-day-of-life.jpg</v>
       </c>
-      <c r="AO17" s="23" t="s">
+      <c r="AO17" s="28" t="s">
         <v>377</v>
       </c>
-      <c r="AQ17"/>
-      <c r="AR17"/>
-      <c r="AS17"/>
       <c r="AT17" t="s">
         <v>23</v>
       </c>
@@ -4525,7 +4546,7 @@
       <c r="R18" s="3">
         <v>17</v>
       </c>
-      <c r="X18" s="29">
+      <c r="X18" s="22">
         <v>9780679779070</v>
       </c>
       <c r="Y18" s="4"/>
@@ -4534,10 +4555,10 @@
         <f>"covers/" &amp; A18 &amp; ".jpg"</f>
         <v>covers/shadow-of-sun.jpg</v>
       </c>
-      <c r="AO18" s="17" t="s">
+      <c r="AO18" s="25" t="s">
         <v>375</v>
       </c>
-      <c r="AP18" s="24" t="s">
+      <c r="AP18" s="26" t="s">
         <v>376</v>
       </c>
       <c r="AT18" t="s">
@@ -4595,7 +4616,7 @@
         <f t="shared" si="0"/>
         <v>covers/meeting-in-oea.jpg</v>
       </c>
-      <c r="AO19" s="17" t="s">
+      <c r="AO19" s="25" t="s">
         <v>378</v>
       </c>
       <c r="AT19" t="s">
@@ -4653,7 +4674,7 @@
         <f t="shared" si="0"/>
         <v>covers/seven-against-thebes.jpg</v>
       </c>
-      <c r="AO20" s="17" t="s">
+      <c r="AO20" s="25" t="s">
         <v>379</v>
       </c>
       <c r="AT20" t="s">
@@ -4711,7 +4732,7 @@
         <f t="shared" si="0"/>
         <v>covers/emperor-julian.jpg</v>
       </c>
-      <c r="AO21" s="17" t="s">
+      <c r="AO21" s="25" t="s">
         <v>380</v>
       </c>
       <c r="AT21" t="s">
@@ -4769,7 +4790,7 @@
         <f t="shared" si="0"/>
         <v>covers/last-olympiad.jpg</v>
       </c>
-      <c r="AO22" s="17" t="s">
+      <c r="AO22" s="25" t="s">
         <v>381</v>
       </c>
       <c r="AT22" t="s">
@@ -4816,7 +4837,7 @@
       <c r="T23" s="3">
         <v>8</v>
       </c>
-      <c r="X23" s="28">
+      <c r="X23" s="21">
         <v>9780156027601</v>
       </c>
       <c r="Y23" s="4"/>
@@ -4825,7 +4846,7 @@
         <f t="shared" si="0"/>
         <v>covers/solaris.jpg</v>
       </c>
-      <c r="AO23" s="17" t="s">
+      <c r="AO23" s="25" t="s">
         <v>382</v>
       </c>
       <c r="AT23" t="s">
@@ -4872,7 +4893,7 @@
       <c r="T24" s="3">
         <v>12</v>
       </c>
-      <c r="X24" s="28">
+      <c r="X24" s="21">
         <v>9780156306300</v>
       </c>
       <c r="Y24" s="4"/>
@@ -4881,7 +4902,7 @@
         <f t="shared" si="0"/>
         <v>covers/fiasco.jpg</v>
       </c>
-      <c r="AO24" s="17" t="s">
+      <c r="AO24" s="25" t="s">
         <v>383</v>
       </c>
       <c r="AT24" t="s">
@@ -4928,7 +4949,7 @@
       <c r="T25" s="3">
         <v>13</v>
       </c>
-      <c r="X25" s="28">
+      <c r="X25" s="21">
         <v>9780262357685</v>
       </c>
       <c r="Y25" s="4"/>
@@ -4937,7 +4958,7 @@
         <f t="shared" si="0"/>
         <v>covers/the-invincible.jpg</v>
       </c>
-      <c r="AO25" s="17" t="s">
+      <c r="AO25" s="25" t="s">
         <v>384</v>
       </c>
       <c r="AT25" t="s">
@@ -4984,7 +5005,7 @@
       <c r="T26" s="3">
         <v>15</v>
       </c>
-      <c r="X26" s="28">
+      <c r="X26" s="21">
         <v>9782919840106</v>
       </c>
       <c r="Y26" s="4"/>
@@ -5059,7 +5080,7 @@
       <c r="T27" s="3">
         <v>15</v>
       </c>
-      <c r="X27" s="28">
+      <c r="X27" s="21">
         <v>9789998791664</v>
       </c>
       <c r="Y27" s="4"/>
@@ -5068,19 +5089,19 @@
         <f t="shared" si="0"/>
         <v>covers/melicles.jpg</v>
       </c>
-      <c r="AO27" s="17" t="s">
+      <c r="AO27" s="25" t="s">
         <v>206</v>
       </c>
-      <c r="AP27" s="24" t="s">
+      <c r="AP27" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="AQ27" s="19" t="s">
+      <c r="AQ27" t="s">
         <v>185</v>
       </c>
-      <c r="AR27" s="19" t="s">
+      <c r="AR27" t="s">
         <v>210</v>
       </c>
-      <c r="AS27" s="19" t="s">
+      <c r="AS27" t="s">
         <v>211</v>
       </c>
       <c r="AT27" t="s">
@@ -5138,7 +5159,7 @@
         <f t="shared" si="0"/>
         <v>covers/diossos.jpg</v>
       </c>
-      <c r="AO28" s="17" t="s">
+      <c r="AO28" s="25" t="s">
         <v>385</v>
       </c>
       <c r="AT28" t="s">
@@ -5196,7 +5217,7 @@
         <f t="shared" si="0"/>
         <v>covers/white-jaguar-1.jpg</v>
       </c>
-      <c r="AO29" s="17" t="s">
+      <c r="AO29" s="25" t="s">
         <v>387</v>
       </c>
       <c r="AT29" t="s">
@@ -5260,7 +5281,7 @@
         <f t="shared" si="0"/>
         <v>covers/ships-minos-1.jpg</v>
       </c>
-      <c r="AO30" s="17" t="s">
+      <c r="AO30" s="25" t="s">
         <v>386</v>
       </c>
       <c r="AT30" t="s">
@@ -5319,7 +5340,7 @@
       <c r="R31" s="3">
         <v>16</v>
       </c>
-      <c r="X31" s="28">
+      <c r="X31" s="21">
         <v>9789998793774</v>
       </c>
       <c r="Y31" s="4" t="s">
@@ -5338,7 +5359,7 @@
         <f t="shared" si="0"/>
         <v>covers/divine-julius.jpg</v>
       </c>
-      <c r="AO31" s="17" t="s">
+      <c r="AO31" s="25" t="s">
         <v>388</v>
       </c>
       <c r="AT31" t="s">
@@ -5397,7 +5418,7 @@
       <c r="R32" s="3">
         <v>17</v>
       </c>
-      <c r="X32" s="28">
+      <c r="X32" s="21">
         <v>9782919820054</v>
       </c>
       <c r="Y32" s="4" t="s">
@@ -5416,7 +5437,7 @@
         <f t="shared" si="0"/>
         <v>covers/naso-the-poet.jpg</v>
       </c>
-      <c r="AO32" s="17" t="s">
+      <c r="AO32" s="25" t="s">
         <v>389</v>
       </c>
       <c r="AT32" t="s">
@@ -5475,7 +5496,7 @@
       <c r="R33" s="3">
         <v>18</v>
       </c>
-      <c r="X33" s="28">
+      <c r="X33" s="21">
         <v>9782919820450</v>
       </c>
       <c r="Y33" s="4"/>
@@ -5484,7 +5505,7 @@
         <f t="shared" si="0"/>
         <v>covers/tiberius-caesar.jpg</v>
       </c>
-      <c r="AO33" s="17" t="s">
+      <c r="AO33" s="25" t="s">
         <v>390</v>
       </c>
       <c r="AT33" t="s">
@@ -5529,7 +5550,7 @@
       <c r="R34" s="3">
         <v>14</v>
       </c>
-      <c r="X34" s="28">
+      <c r="X34" s="21">
         <v>9780062095886</v>
       </c>
       <c r="Y34" s="4"/>
@@ -5538,7 +5559,7 @@
         <f t="shared" si="0"/>
         <v>covers/milosz-selected-and-last-poems.jpg</v>
       </c>
-      <c r="AO34" s="17" t="s">
+      <c r="AO34" s="25" t="s">
         <v>391</v>
       </c>
       <c r="AT34" t="s">
@@ -5588,7 +5609,7 @@
       <c r="R35" s="3">
         <v>11</v>
       </c>
-      <c r="X35" s="29">
+      <c r="X35" s="22">
         <v>9780156011464</v>
       </c>
       <c r="Y35" s="4"/>
@@ -5597,7 +5618,7 @@
         <f t="shared" si="0"/>
         <v>covers/poems-new-and-szymborska.jpg</v>
       </c>
-      <c r="AO35" s="17" t="s">
+      <c r="AO35" s="25" t="s">
         <v>392</v>
       </c>
       <c r="AT35" t="s">
@@ -5636,7 +5657,7 @@
       <c r="R36" s="3">
         <v>17</v>
       </c>
-      <c r="X36" s="29">
+      <c r="X36" s="22">
         <v>9780060783952</v>
       </c>
       <c r="Y36" s="4"/>
@@ -5645,10 +5666,10 @@
         <f t="shared" si="0"/>
         <v>covers/poems-herbert.jpg</v>
       </c>
-      <c r="AO36" s="17" t="s">
+      <c r="AO36" s="25" t="s">
         <v>393</v>
       </c>
-      <c r="AP36" s="24" t="s">
+      <c r="AP36" s="26" t="s">
         <v>394</v>
       </c>
       <c r="AT36" t="s">
@@ -5687,7 +5708,7 @@
       <c r="R37" s="3">
         <v>15</v>
       </c>
-      <c r="X37" s="28">
+      <c r="X37" s="21">
         <v>9780374528614</v>
       </c>
       <c r="Y37" s="4"/>
@@ -5696,10 +5717,10 @@
         <f t="shared" si="0"/>
         <v>covers/without-end.jpg</v>
       </c>
-      <c r="AO37" s="17" t="s">
+      <c r="AO37" s="25" t="s">
         <v>396</v>
       </c>
-      <c r="AP37" s="24" t="s">
+      <c r="AP37" s="26" t="s">
         <v>397</v>
       </c>
       <c r="AT37" t="s">
@@ -5753,7 +5774,7 @@
       <c r="R38" s="3">
         <v>19</v>
       </c>
-      <c r="X38" s="28">
+      <c r="X38" s="21">
         <v>9780393345551</v>
       </c>
       <c r="Y38" s="4"/>
@@ -5762,10 +5783,10 @@
         <f t="shared" si="0"/>
         <v>covers/sobbing-superpower.jpg</v>
       </c>
-      <c r="AO38" s="17" t="s">
+      <c r="AO38" s="25" t="s">
         <v>398</v>
       </c>
-      <c r="AP38" s="24" t="s">
+      <c r="AP38" s="26" t="s">
         <v>399</v>
       </c>
       <c r="AT38" t="s">
@@ -5816,7 +5837,7 @@
       <c r="R39" s="3">
         <v>11</v>
       </c>
-      <c r="X39" s="28">
+      <c r="X39" s="21">
         <v>9780544705159</v>
       </c>
       <c r="Y39" s="4"/>
@@ -5825,10 +5846,10 @@
         <f t="shared" si="0"/>
         <v>covers/map-collected-and-last.jpg</v>
       </c>
-      <c r="AO39" s="17" t="s">
+      <c r="AO39" s="25" t="s">
         <v>400</v>
       </c>
-      <c r="AP39" s="24" t="s">
+      <c r="AP39" s="26" t="s">
         <v>401</v>
       </c>
       <c r="AT39" t="s">
@@ -5882,7 +5903,7 @@
       <c r="R40" s="3">
         <v>11</v>
       </c>
-      <c r="X40" s="28">
+      <c r="X40" s="21">
         <v>9788367602471</v>
       </c>
       <c r="Y40" s="4"/>
@@ -5891,7 +5912,7 @@
         <f t="shared" si="0"/>
         <v>covers/from-tree-of-knowledge.jpg</v>
       </c>
-      <c r="AO40" s="17" t="s">
+      <c r="AO40" s="25" t="s">
         <v>402</v>
       </c>
       <c r="AT40" t="s">
@@ -5928,7 +5949,7 @@
       <c r="R41" s="3">
         <v>7</v>
       </c>
-      <c r="X41" s="28">
+      <c r="X41" s="21">
         <v>9798802065853</v>
       </c>
       <c r="Y41" s="4"/>
@@ -5937,7 +5958,7 @@
         <f t="shared" si="0"/>
         <v>covers/krzysztof-kamil-baczynski.jpg</v>
       </c>
-      <c r="AO41" s="17" t="s">
+      <c r="AO41" s="25" t="s">
         <v>403</v>
       </c>
       <c r="AT41" t="s">
@@ -5977,7 +5998,7 @@
       <c r="R42" s="3">
         <v>14</v>
       </c>
-      <c r="X42" s="28">
+      <c r="X42" s="21">
         <v>9781931243810</v>
       </c>
       <c r="Y42" s="4"/>
@@ -5986,7 +6007,7 @@
         <f t="shared" si="0"/>
         <v>covers/white-magic-baczynski.jpg</v>
       </c>
-      <c r="AO42" s="17" t="s">
+      <c r="AO42" s="25" t="s">
         <v>404</v>
       </c>
       <c r="AT42" t="s">
@@ -6040,7 +6061,7 @@
       <c r="R43" s="3">
         <v>9.99</v>
       </c>
-      <c r="X43" s="28">
+      <c r="X43" s="21">
         <v>9788367602419</v>
       </c>
       <c r="Y43" s="4"/>
@@ -6049,7 +6070,7 @@
         <f t="shared" si="0"/>
         <v>covers/new-poems-ukr-po.jpg</v>
       </c>
-      <c r="AO43" s="17" t="s">
+      <c r="AO43" s="25" t="s">
         <v>202</v>
       </c>
       <c r="AT43" t="s">
@@ -6103,7 +6124,7 @@
       <c r="R44" s="3">
         <v>13</v>
       </c>
-      <c r="X44" s="28">
+      <c r="X44" s="21">
         <v>9782919820856</v>
       </c>
       <c r="Y44" s="4" t="s">
@@ -6122,7 +6143,7 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-templars.jpg</v>
       </c>
-      <c r="AO44" s="17" t="s">
+      <c r="AO44" s="25" t="s">
         <v>196</v>
       </c>
       <c r="AT44" t="s">
@@ -6176,7 +6197,7 @@
       <c r="R45" s="3">
         <v>17</v>
       </c>
-      <c r="X45" s="28">
+      <c r="X45" s="21">
         <v>9782919840021</v>
       </c>
       <c r="Y45" s="4" t="s">
@@ -6195,7 +6216,7 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-mysteries.jpg</v>
       </c>
-      <c r="AO45" s="17" t="s">
+      <c r="AO45" s="25" t="s">
         <v>198</v>
       </c>
       <c r="AT45" t="s">
@@ -6249,7 +6270,7 @@
       <c r="R46" s="3">
         <v>15</v>
       </c>
-      <c r="X46" s="29">
+      <c r="X46" s="22">
         <v>9782919820948</v>
       </c>
       <c r="Y46" s="4" t="s">
@@ -6268,7 +6289,7 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-bandits.jpg</v>
       </c>
-      <c r="AO46" s="17" t="s">
+      <c r="AO46" s="25" t="s">
         <v>195</v>
       </c>
       <c r="AT46" t="s">
@@ -6322,7 +6343,7 @@
       <c r="R47" s="3">
         <v>13</v>
       </c>
-      <c r="X47" s="28">
+      <c r="X47" s="21">
         <v>9782919820900</v>
       </c>
       <c r="Y47" s="4" t="s">
@@ -6341,7 +6362,7 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-copernicus.jpg</v>
       </c>
-      <c r="AO47" s="18" t="s">
+      <c r="AO47" s="29" t="s">
         <v>197</v>
       </c>
       <c r="AT47" t="s">
@@ -6377,12 +6398,12 @@
         <v>113</v>
       </c>
       <c r="Q48" s="2" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="R48" s="3">
         <v>19</v>
       </c>
-      <c r="X48" s="28">
+      <c r="X48" s="21">
         <v>9781905583393</v>
       </c>
       <c r="Y48" s="4" t="s">
@@ -6401,7 +6422,7 @@
         <f t="shared" si="0"/>
         <v>covers/cold-sea.jpg</v>
       </c>
-      <c r="AO48" s="17" t="s">
+      <c r="AO48" s="25" t="s">
         <v>215</v>
       </c>
       <c r="AT48" t="s">
@@ -6454,7 +6475,7 @@
       <c r="R49" s="3">
         <v>22</v>
       </c>
-      <c r="X49" s="28">
+      <c r="X49" s="21">
         <v>9780140445800</v>
       </c>
       <c r="Y49" s="4" t="s">
@@ -6474,7 +6495,7 @@
         <f t="shared" si="0"/>
         <v>covers/saragossa.jpg</v>
       </c>
-      <c r="AO49" s="18" t="s">
+      <c r="AO49" s="29" t="s">
         <v>218</v>
       </c>
       <c r="AT49" t="s">
@@ -6515,7 +6536,7 @@
       <c r="R50" s="3">
         <v>28</v>
       </c>
-      <c r="X50" s="28">
+      <c r="X50" s="21">
         <v>9789639241459</v>
       </c>
       <c r="Y50" s="4"/>
@@ -6524,7 +6545,7 @@
         <f t="shared" si="0"/>
         <v>covers/birch-grove.jpg</v>
       </c>
-      <c r="AO50" s="17" t="s">
+      <c r="AO50" s="25" t="s">
         <v>225</v>
       </c>
       <c r="AT50" t="s">
@@ -6566,7 +6587,7 @@
       <c r="R51" s="3">
         <v>22</v>
       </c>
-      <c r="X51" s="28">
+      <c r="X51" s="21">
         <v>9780810108066</v>
       </c>
       <c r="Y51" s="4"/>
@@ -6575,7 +6596,7 @@
         <f t="shared" si="0"/>
         <v>covers/danton-thermidor.jpg</v>
       </c>
-      <c r="AO51" s="18" t="s">
+      <c r="AO51" s="29" t="s">
         <v>231</v>
       </c>
       <c r="AT51" t="s">
@@ -6616,7 +6637,7 @@
       <c r="R52" s="3">
         <v>39</v>
       </c>
-      <c r="X52" s="28">
+      <c r="X52" s="21">
         <v>9789637326899</v>
       </c>
       <c r="Y52" s="4"/>
@@ -6625,7 +6646,7 @@
         <f t="shared" si="0"/>
         <v>covers/coming-spring.jpg</v>
       </c>
-      <c r="AO52" s="17" t="s">
+      <c r="AO52" s="25" t="s">
         <v>234</v>
       </c>
       <c r="AT52" t="s">
@@ -6663,7 +6684,7 @@
       <c r="R53" s="3">
         <v>57.99</v>
       </c>
-      <c r="X53" s="28">
+      <c r="X53" s="21">
         <v>9781412865432</v>
       </c>
       <c r="Y53" s="4" t="s">
@@ -6683,7 +6704,7 @@
         <f t="shared" si="0"/>
         <v>covers/beniowski.jpg</v>
       </c>
-      <c r="AO53" s="17" t="s">
+      <c r="AO53" s="25" t="s">
         <v>245</v>
       </c>
       <c r="AT53" t="s">
@@ -6724,7 +6745,7 @@
       <c r="R54" s="3">
         <v>50</v>
       </c>
-      <c r="X54" s="28">
+      <c r="X54" s="21">
         <v>9780316498845</v>
       </c>
       <c r="Y54" s="4"/>
@@ -6733,7 +6754,7 @@
         <f t="shared" si="0"/>
         <v>covers/witcher-set.jpg</v>
       </c>
-      <c r="AO54" s="18" t="s">
+      <c r="AO54" s="29" t="s">
         <v>252</v>
       </c>
       <c r="AT54" t="s">
@@ -6774,7 +6795,7 @@
       <c r="R55" s="3">
         <v>18</v>
       </c>
-      <c r="X55" s="28">
+      <c r="X55" s="21">
         <v>9780316423694</v>
       </c>
       <c r="Y55" s="4"/>
@@ -6783,7 +6804,7 @@
         <f t="shared" si="0"/>
         <v>covers/tower-fools.jpg</v>
       </c>
-      <c r="AO55" s="17" t="s">
+      <c r="AO55" s="25" t="s">
         <v>256</v>
       </c>
       <c r="AT55" t="s">
@@ -6830,7 +6851,7 @@
       <c r="R56" s="3">
         <v>9.99</v>
       </c>
-      <c r="X56" s="28">
+      <c r="X56" s="21">
         <v>9780316423717</v>
       </c>
       <c r="Y56" s="4"/>
@@ -6839,7 +6860,7 @@
         <f t="shared" si="0"/>
         <v>covers/warrior-god.jpg</v>
       </c>
-      <c r="AO56" s="18" t="s">
+      <c r="AO56" s="29" t="s">
         <v>260</v>
       </c>
       <c r="AT56" t="s">
@@ -6886,7 +6907,7 @@
       <c r="R57" s="3">
         <v>16</v>
       </c>
-      <c r="X57" s="28">
+      <c r="X57" s="21">
         <v>9780316423755</v>
       </c>
       <c r="Y57" s="4"/>
@@ -6895,7 +6916,7 @@
         <f t="shared" si="0"/>
         <v>covers/light-perpetua.jpg</v>
       </c>
-      <c r="AO57" s="17" t="s">
+      <c r="AO57" s="25" t="s">
         <v>263</v>
       </c>
       <c r="AT57" t="s">
@@ -6951,7 +6972,7 @@
       <c r="R58" s="3">
         <v>22</v>
       </c>
-      <c r="X58" s="28">
+      <c r="X58" s="21">
         <v>9781845951207</v>
       </c>
       <c r="Y58" s="4" t="s">
@@ -6968,7 +6989,7 @@
         <f t="shared" si="0"/>
         <v>covers/red-prince.jpg</v>
       </c>
-      <c r="AO58" s="18" t="s">
+      <c r="AO58" s="29" t="s">
         <v>268</v>
       </c>
       <c r="AT58" t="s">
@@ -7017,7 +7038,7 @@
         <f t="shared" si="0"/>
         <v>covers/adam-mickiewicz.jpg</v>
       </c>
-      <c r="AO59" s="18" t="s">
+      <c r="AO59" s="29" t="s">
         <v>273</v>
       </c>
       <c r="AT59" t="s">
@@ -7069,7 +7090,7 @@
         <f t="shared" si="0"/>
         <v>covers/forefathers-eve.jpg</v>
       </c>
-      <c r="AO60" s="18" t="s">
+      <c r="AO60" s="29" t="s">
         <v>277</v>
       </c>
       <c r="AT60" t="s">
@@ -7121,7 +7142,7 @@
         <f t="shared" si="0"/>
         <v>covers/ballads-romances.jpg</v>
       </c>
-      <c r="AO61" s="17" t="s">
+      <c r="AO61" s="25" t="s">
         <v>282</v>
       </c>
       <c r="AT61" t="s">
@@ -7163,7 +7184,7 @@
       <c r="R62" s="3">
         <v>16</v>
       </c>
-      <c r="X62" s="28">
+      <c r="X62" s="21">
         <v>9780374528300</v>
       </c>
       <c r="Y62" s="4"/>
@@ -7172,7 +7193,7 @@
         <f t="shared" si="0"/>
         <v>covers/native-realm.jpg</v>
       </c>
-      <c r="AO62" s="17" t="s">
+      <c r="AO62" s="25" t="s">
         <v>286</v>
       </c>
       <c r="AT62" t="s">
@@ -7211,7 +7232,7 @@
       <c r="R63" s="3">
         <v>41</v>
       </c>
-      <c r="X63" s="28">
+      <c r="X63" s="21">
         <v>9780520044777</v>
       </c>
       <c r="Y63" s="4"/>
@@ -7220,7 +7241,7 @@
         <f t="shared" si="0"/>
         <v>covers/history-lit-milosz.jpg</v>
       </c>
-      <c r="AO63" s="17" t="s">
+      <c r="AO63" s="25" t="s">
         <v>293</v>
       </c>
       <c r="AT63" t="s">
@@ -7259,7 +7280,7 @@
       <c r="R64" s="3">
         <v>22</v>
       </c>
-      <c r="X64" s="28">
+      <c r="X64" s="21">
         <v>9780520044760</v>
       </c>
       <c r="Y64" s="4"/>
@@ -7268,7 +7289,7 @@
         <f t="shared" si="0"/>
         <v>covers/postwar-polish-poetry.jpg</v>
       </c>
-      <c r="AO64" s="17" t="s">
+      <c r="AO64" s="25" t="s">
         <v>294</v>
       </c>
       <c r="AT64" t="s">
@@ -7307,7 +7328,7 @@
       <c r="R65" s="3">
         <v>13</v>
       </c>
-      <c r="X65" s="28">
+      <c r="X65" s="21">
         <v>9780679728566</v>
       </c>
       <c r="Y65" s="4"/>
@@ -7316,7 +7337,7 @@
         <f t="shared" si="0"/>
         <v>covers/captive-mind.jpg</v>
       </c>
-      <c r="AO65" s="17" t="s">
+      <c r="AO65" s="25" t="s">
         <v>297</v>
       </c>
       <c r="AT65" t="s">
@@ -7356,7 +7377,7 @@
       <c r="R66" s="3">
         <v>14</v>
       </c>
-      <c r="X66" s="28">
+      <c r="X66" s="21">
         <v>9781419679995</v>
       </c>
       <c r="Y66" s="4"/>
@@ -7365,7 +7386,7 @@
         <f t="shared" si="0"/>
         <v>covers/selected-masterpieces.jpg</v>
       </c>
-      <c r="AO66" s="17" t="s">
+      <c r="AO66" s="25" t="s">
         <v>301</v>
       </c>
       <c r="AT66" t="s">
@@ -7404,7 +7425,7 @@
       <c r="R67" s="3">
         <v>30</v>
       </c>
-      <c r="X67" s="28">
+      <c r="X67" s="21">
         <v>9781734860610</v>
       </c>
       <c r="Y67" s="4" t="s">
@@ -7424,7 +7445,7 @@
         <f>"covers/" &amp; A67 &amp; ".jpg"</f>
         <v>covers/hyenas-lotuses.jpg</v>
       </c>
-      <c r="AO67" s="17" t="s">
+      <c r="AO67" s="25" t="s">
         <v>309</v>
       </c>
       <c r="AT67" t="s">
@@ -7463,7 +7484,7 @@
       <c r="R68" s="3">
         <v>19</v>
       </c>
-      <c r="X68" s="28">
+      <c r="X68" s="21">
         <v>9781250218018</v>
       </c>
       <c r="Y68" s="4" t="s">
@@ -7482,19 +7503,19 @@
         <f>"covers/" &amp; A68 &amp; ".jpg"</f>
         <v>covers/widow-queen.jpg</v>
       </c>
-      <c r="AO68" s="17" t="s">
+      <c r="AO68" s="25" t="s">
         <v>310</v>
       </c>
-      <c r="AP68" s="24" t="s">
+      <c r="AP68" s="26" t="s">
         <v>315</v>
       </c>
-      <c r="AQ68" s="19" t="s">
+      <c r="AQ68" t="s">
         <v>316</v>
       </c>
-      <c r="AR68" s="19" t="s">
+      <c r="AR68" t="s">
         <v>317</v>
       </c>
-      <c r="AS68" s="19" t="s">
+      <c r="AS68" t="s">
         <v>318</v>
       </c>
       <c r="AT68" t="s">
@@ -7553,7 +7574,7 @@
       <c r="R69" s="3">
         <v>20.99</v>
       </c>
-      <c r="X69" s="28">
+      <c r="X69" s="21">
         <v>9781250775764</v>
       </c>
       <c r="Y69" s="4"/>
@@ -7562,19 +7583,19 @@
         <f>"covers/" &amp; A69 &amp; ".jpg"</f>
         <v>covers/last-crown.jpg</v>
       </c>
-      <c r="AO69" s="17" t="s">
+      <c r="AO69" s="25" t="s">
         <v>322</v>
       </c>
-      <c r="AP69" s="24" t="s">
+      <c r="AP69" s="26" t="s">
         <v>315</v>
       </c>
-      <c r="AQ69" s="19" t="s">
+      <c r="AQ69" t="s">
         <v>316</v>
       </c>
-      <c r="AR69" s="19" t="s">
+      <c r="AR69" t="s">
         <v>317</v>
       </c>
-      <c r="AS69" s="19" t="s">
+      <c r="AS69" t="s">
         <v>318</v>
       </c>
       <c r="AT69" t="s">
@@ -7622,7 +7643,7 @@
       <c r="R70" s="3">
         <v>24.99</v>
       </c>
-      <c r="X70" s="28">
+      <c r="X70" s="21">
         <v>9781589881846</v>
       </c>
       <c r="Y70" s="4" t="s">
@@ -7641,7 +7662,7 @@
         <f t="shared" ref="AH70" si="1">"covers/" &amp; A70 &amp; ".jpg"</f>
         <v>covers/the-homeless.jpg</v>
       </c>
-      <c r="AO70" s="17" t="s">
+      <c r="AO70" s="25" t="s">
         <v>237</v>
       </c>
       <c r="AT70" t="s">
@@ -7683,19 +7704,19 @@
       <c r="R71" s="3">
         <v>17</v>
       </c>
-      <c r="X71" s="28">
+      <c r="X71" s="21">
         <v>9780300181678</v>
       </c>
       <c r="Y71" s="4"/>
       <c r="Z71" s="4"/>
       <c r="AH71" t="str">
-        <f>"covers/" &amp; A71 &amp; ".jpg"</f>
+        <f t="shared" ref="AH71:AH98" si="2">"covers/" &amp; A71 &amp; ".jpg"</f>
         <v>covers/ferdydurke.jpg</v>
       </c>
-      <c r="AO71" s="17" t="s">
+      <c r="AO71" s="25" t="s">
         <v>345</v>
       </c>
-      <c r="AP71" s="24" t="s">
+      <c r="AP71" s="26" t="s">
         <v>347</v>
       </c>
       <c r="AT71" t="s">
@@ -7737,19 +7758,19 @@
       <c r="R72" s="3">
         <v>17</v>
       </c>
-      <c r="X72" s="28">
+      <c r="X72" s="21">
         <v>9780802162526</v>
       </c>
       <c r="Y72" s="4"/>
       <c r="Z72" s="4"/>
       <c r="AH72" t="str">
-        <f>"covers/" &amp; A72 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/the-possessed.jpg</v>
       </c>
-      <c r="AO72" s="17" t="s">
+      <c r="AO72" s="25" t="s">
         <v>348</v>
       </c>
-      <c r="AP72" s="24" t="s">
+      <c r="AP72" s="26" t="s">
         <v>352</v>
       </c>
       <c r="AT72" t="s">
@@ -7791,19 +7812,19 @@
       <c r="R73" s="3">
         <v>18</v>
       </c>
-      <c r="X73" s="28">
+      <c r="X73" s="21">
         <v>9780525534204</v>
       </c>
       <c r="Y73" s="4"/>
       <c r="Z73" s="4"/>
       <c r="AH73" t="str">
-        <f>"covers/" &amp; A73 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/flights.jpg</v>
       </c>
-      <c r="AO73" s="17" t="s">
+      <c r="AO73" s="25" t="s">
         <v>357</v>
       </c>
-      <c r="AP73" s="24" t="s">
+      <c r="AP73" s="26" t="s">
         <v>358</v>
       </c>
       <c r="AT73" t="s">
@@ -7845,16 +7866,16 @@
       <c r="R74" s="3">
         <v>15</v>
       </c>
-      <c r="X74" s="28">
+      <c r="X74" s="21">
         <v>9781628971637</v>
       </c>
       <c r="Y74" s="4"/>
       <c r="Z74" s="4"/>
       <c r="AH74" t="str">
-        <f>"covers/" &amp; A74 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/gestures.jpg</v>
       </c>
-      <c r="AO74" s="17" t="s">
+      <c r="AO74" s="25" t="s">
         <v>409</v>
       </c>
       <c r="AT74" t="s">
@@ -7896,19 +7917,19 @@
       <c r="R75" s="3">
         <v>15</v>
       </c>
-      <c r="X75" s="28">
+      <c r="X75" s="21">
         <v>9781945492235</v>
       </c>
       <c r="Y75" s="4"/>
       <c r="Z75" s="4"/>
       <c r="AH75" t="str">
-        <f>"covers/" &amp; A75 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/accommodations.jpg</v>
       </c>
-      <c r="AO75" s="17" t="s">
+      <c r="AO75" s="25" t="s">
         <v>412</v>
       </c>
-      <c r="AP75" s="24" t="s">
+      <c r="AP75" s="26" t="s">
         <v>413</v>
       </c>
       <c r="AT75" t="s">
@@ -7950,19 +7971,19 @@
       <c r="R76" s="3">
         <v>20</v>
       </c>
-      <c r="X76" s="28">
+      <c r="X76" s="21">
         <v>9781945492044</v>
       </c>
       <c r="Y76" s="4"/>
       <c r="Z76" s="4"/>
       <c r="AH76" t="str">
-        <f>"covers/" &amp; A76 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/swallowing-mercury.jpg</v>
       </c>
-      <c r="AO76" s="17" t="s">
+      <c r="AO76" s="25" t="s">
         <v>421</v>
       </c>
-      <c r="AP76" s="24" t="s">
+      <c r="AP76" s="26" t="s">
         <v>420</v>
       </c>
       <c r="AT76" t="s">
@@ -7977,7 +7998,7 @@
     </row>
     <row r="77" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B77" t="s">
         <v>78</v>
@@ -7986,10 +8007,10 @@
         <v>576</v>
       </c>
       <c r="D77" s="15" t="s">
-        <v>423</v>
+        <v>624</v>
       </c>
       <c r="E77" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="F77" t="s">
         <v>239</v>
@@ -7999,19 +8020,19 @@
         <v>113</v>
       </c>
       <c r="Q77" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="X77" s="28">
+        <v>426</v>
+      </c>
+      <c r="X77" s="21">
         <v>9781589880900</v>
       </c>
       <c r="Y77" s="4"/>
       <c r="Z77" s="4"/>
       <c r="AH77" t="str">
-        <f>"covers/" &amp; A77 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/stone-tablets.jpg</v>
       </c>
-      <c r="AO77" s="17" t="s">
-        <v>426</v>
+      <c r="AO77" s="25" t="s">
+        <v>425</v>
       </c>
       <c r="AT77" t="s">
         <v>23</v>
@@ -8025,7 +8046,7 @@
     </row>
     <row r="78" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B78" t="s">
         <v>78</v>
@@ -8034,10 +8055,10 @@
         <v>625</v>
       </c>
       <c r="D78" s="15" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E78" s="15" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F78" t="s">
         <v>374</v>
@@ -8047,19 +8068,19 @@
         <v>113</v>
       </c>
       <c r="Q78" s="7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="R78" s="3">
         <v>17</v>
       </c>
-      <c r="X78" s="28">
+      <c r="X78" s="21">
         <v>9780802160430</v>
       </c>
       <c r="Y78" s="4" t="s">
         <v>114</v>
       </c>
       <c r="Z78" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="AA78" s="5">
         <v>9.99</v>
@@ -8068,14 +8089,14 @@
         <v>9780802162236</v>
       </c>
       <c r="AH78" t="str">
-        <f>"covers/" &amp; A78 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/beautiful-mrs-seidenman.jpg</v>
       </c>
-      <c r="AO78" s="17" t="s">
+      <c r="AO78" s="25" t="s">
+        <v>428</v>
+      </c>
+      <c r="AP78" s="26" t="s">
         <v>429</v>
-      </c>
-      <c r="AP78" s="24" t="s">
-        <v>430</v>
       </c>
       <c r="AT78" t="s">
         <v>23</v>
@@ -8089,7 +8110,7 @@
     </row>
     <row r="79" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B79" t="s">
         <v>216</v>
@@ -8098,10 +8119,10 @@
         <v>750</v>
       </c>
       <c r="D79" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="E79" t="s">
         <v>436</v>
-      </c>
-      <c r="E79" t="s">
-        <v>437</v>
       </c>
       <c r="F79" t="s">
         <v>422</v>
@@ -8111,22 +8132,22 @@
         <v>113</v>
       </c>
       <c r="Q79" s="7" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="R79" s="3">
         <v>15</v>
       </c>
-      <c r="X79" s="28">
+      <c r="X79" s="21">
         <v>9781782695141</v>
       </c>
       <c r="Y79" s="4"/>
       <c r="Z79" s="4"/>
       <c r="AH79" t="str">
-        <f>"covers/" &amp; A79 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/nosegood-investigates.jpg</v>
       </c>
-      <c r="AO79" s="26" t="s">
-        <v>434</v>
+      <c r="AO79" s="30" t="s">
+        <v>433</v>
       </c>
       <c r="AT79" t="s">
         <v>23</v>
@@ -8140,7 +8161,7 @@
     </row>
     <row r="80" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B80" t="s">
         <v>74</v>
@@ -8149,10 +8170,10 @@
         <v>800</v>
       </c>
       <c r="D80" s="15" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E80" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F80" t="s">
         <v>67</v>
@@ -8162,25 +8183,25 @@
         <v>113</v>
       </c>
       <c r="Q80" s="7" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="R80" s="3">
         <v>19</v>
       </c>
-      <c r="X80" s="28">
+      <c r="X80" s="21">
         <v>9780143129752</v>
       </c>
       <c r="Y80" s="4"/>
       <c r="Z80" s="4"/>
       <c r="AH80" t="str">
-        <f>"covers/" &amp; A80 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/feed-dictator.jpg</v>
       </c>
-      <c r="AO80" s="17" t="s">
-        <v>443</v>
-      </c>
-      <c r="AP80" s="24" t="s">
+      <c r="AO80" s="25" t="s">
         <v>442</v>
+      </c>
+      <c r="AP80" s="26" t="s">
+        <v>441</v>
       </c>
       <c r="AT80" t="s">
         <v>23</v>
@@ -8192,9 +8213,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B81" t="s">
         <v>74</v>
@@ -8203,10 +8224,10 @@
         <v>810</v>
       </c>
       <c r="D81" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="E81" t="s">
         <v>444</v>
-      </c>
-      <c r="E81" t="s">
-        <v>445</v>
       </c>
       <c r="F81" t="s">
         <v>67</v>
@@ -8216,25 +8237,25 @@
         <v>113</v>
       </c>
       <c r="Q81" s="7" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="R81" s="3">
         <v>20</v>
       </c>
-      <c r="X81" s="28">
+      <c r="X81" s="21">
         <v>9781805330011</v>
       </c>
       <c r="Y81" s="4"/>
       <c r="Z81" s="4"/>
       <c r="AH81" t="str">
-        <f>"covers/" &amp; A81 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/city-lions.jpg</v>
       </c>
-      <c r="AO81" s="17" t="s">
+      <c r="AO81" s="25" t="s">
+        <v>446</v>
+      </c>
+      <c r="AP81" s="26" t="s">
         <v>447</v>
-      </c>
-      <c r="AP81" s="24" t="s">
-        <v>448</v>
       </c>
       <c r="AT81" t="s">
         <v>23</v>
@@ -8246,9 +8267,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:49" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:52" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B82" t="s">
         <v>74</v>
@@ -8257,10 +8278,10 @@
         <v>820</v>
       </c>
       <c r="D82" s="15" t="s">
+        <v>451</v>
+      </c>
+      <c r="E82" t="s">
         <v>452</v>
-      </c>
-      <c r="E82" t="s">
-        <v>453</v>
       </c>
       <c r="F82" t="s">
         <v>67</v>
@@ -8270,25 +8291,25 @@
         <v>113</v>
       </c>
       <c r="Q82" s="7" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="R82" s="3">
         <v>16</v>
       </c>
-      <c r="X82" s="28">
+      <c r="X82" s="21">
         <v>9781948830508</v>
       </c>
       <c r="Y82" s="4"/>
       <c r="Z82" s="4"/>
       <c r="AH82" t="str">
-        <f>"covers/" &amp; A82 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/roosters-dogs.jpg</v>
       </c>
-      <c r="AO82" s="17" t="s">
+      <c r="AO82" s="25" t="s">
+        <v>454</v>
+      </c>
+      <c r="AP82" s="26" t="s">
         <v>455</v>
-      </c>
-      <c r="AP82" s="24" t="s">
-        <v>456</v>
       </c>
       <c r="AT82" t="s">
         <v>23</v>
@@ -8300,9 +8321,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="83" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B83" t="s">
         <v>78</v>
@@ -8311,10 +8332,10 @@
         <v>930</v>
       </c>
       <c r="D83" s="15" t="s">
+        <v>459</v>
+      </c>
+      <c r="E83" t="s">
         <v>460</v>
-      </c>
-      <c r="E83" t="s">
-        <v>461</v>
       </c>
       <c r="F83" t="s">
         <v>67</v>
@@ -8324,25 +8345,25 @@
         <v>113</v>
       </c>
       <c r="Q83" s="7" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="R83" s="3">
         <v>16</v>
       </c>
-      <c r="X83" s="28">
+      <c r="X83" s="21">
         <v>9780857057143</v>
       </c>
       <c r="Y83" s="4"/>
       <c r="Z83" s="4"/>
       <c r="AH83" t="str">
-        <f>"covers/" &amp; A83 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/stained-glass.jpg</v>
       </c>
-      <c r="AO83" s="17" t="s">
+      <c r="AO83" s="25" t="s">
+        <v>457</v>
+      </c>
+      <c r="AP83" s="26" t="s">
         <v>458</v>
-      </c>
-      <c r="AP83" s="24" t="s">
-        <v>459</v>
       </c>
       <c r="AT83" t="s">
         <v>23</v>
@@ -8354,18 +8375,18 @@
         <v>31</v>
       </c>
     </row>
-    <row r="84" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B84" t="s">
         <v>74</v>
       </c>
-      <c r="D84" s="27" t="s">
-        <v>463</v>
+      <c r="D84" s="20" t="s">
+        <v>462</v>
       </c>
       <c r="E84" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F84" t="s">
         <v>67</v>
@@ -8375,19 +8396,19 @@
         <v>113</v>
       </c>
       <c r="Q84" s="7" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="R84" s="3">
         <v>50</v>
       </c>
-      <c r="X84" s="28">
+      <c r="X84" s="21">
         <v>9781781680810</v>
       </c>
       <c r="Y84" s="4" t="s">
         <v>114</v>
       </c>
       <c r="Z84" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AA84" s="5">
         <v>20</v>
@@ -8396,14 +8417,14 @@
         <v>9781781684061</v>
       </c>
       <c r="AH84" t="str">
-        <f>"covers/" &amp; A84 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/ryszard-k-a-life.jpg</v>
       </c>
-      <c r="AO84" s="17" t="s">
+      <c r="AO84" s="25" t="s">
+        <v>466</v>
+      </c>
+      <c r="AP84" s="26" t="s">
         <v>467</v>
-      </c>
-      <c r="AP84" s="24" t="s">
-        <v>468</v>
       </c>
       <c r="AT84" t="s">
         <v>23</v>
@@ -8415,9 +8436,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B85" t="s">
         <v>78</v>
@@ -8426,7 +8447,7 @@
         <v>970</v>
       </c>
       <c r="D85" s="15" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E85" t="s">
         <v>201</v>
@@ -8439,12 +8460,12 @@
         <v>113</v>
       </c>
       <c r="Q85" s="7" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="R85" s="3">
         <v>17</v>
       </c>
-      <c r="X85" s="28">
+      <c r="X85" s="21">
         <v>9780192855565</v>
       </c>
       <c r="Y85" s="4" t="s">
@@ -8461,14 +8482,14 @@
         <v>9780192668080</v>
       </c>
       <c r="AH85" t="str">
-        <f>"covers/" &amp; A85 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/warsaw-tales.jpg</v>
       </c>
-      <c r="AO85" s="17" t="s">
+      <c r="AO85" s="25" t="s">
+        <v>470</v>
+      </c>
+      <c r="AP85" s="26" t="s">
         <v>471</v>
-      </c>
-      <c r="AP85" s="24" t="s">
-        <v>472</v>
       </c>
       <c r="AT85" t="s">
         <v>23</v>
@@ -8480,9 +8501,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="86" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B86" t="s">
         <v>302</v>
@@ -8491,10 +8512,10 @@
         <v>920</v>
       </c>
       <c r="D86" s="15" t="s">
+        <v>479</v>
+      </c>
+      <c r="E86" t="s">
         <v>480</v>
-      </c>
-      <c r="E86" t="s">
-        <v>481</v>
       </c>
       <c r="F86" t="s">
         <v>67</v>
@@ -8504,25 +8525,25 @@
         <v>113</v>
       </c>
       <c r="Q86" s="7" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="R86" s="3">
         <v>16</v>
       </c>
-      <c r="X86" s="28">
+      <c r="X86" s="21">
         <v>9780358161462</v>
       </c>
       <c r="Y86" s="4"/>
       <c r="Z86" s="4"/>
       <c r="AH86" t="str">
-        <f>"covers/" &amp; A86 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/mohr-missing.jpg</v>
       </c>
-      <c r="AO86" s="17" t="s">
+      <c r="AO86" s="25" t="s">
+        <v>482</v>
+      </c>
+      <c r="AP86" s="26" t="s">
         <v>483</v>
-      </c>
-      <c r="AP86" s="24" t="s">
-        <v>484</v>
       </c>
       <c r="AT86" t="s">
         <v>23</v>
@@ -8533,10 +8554,16 @@
       <c r="AW86" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="87" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="AY86" t="s">
+        <v>630</v>
+      </c>
+      <c r="AZ86">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B87" t="s">
         <v>74</v>
@@ -8545,10 +8572,10 @@
         <v>943</v>
       </c>
       <c r="D87" s="15" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E87" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F87" t="s">
         <v>67</v>
@@ -8558,25 +8585,25 @@
         <v>113</v>
       </c>
       <c r="Q87" s="7" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="R87" s="3">
         <v>20</v>
       </c>
-      <c r="X87" s="28">
+      <c r="X87" s="21">
         <v>9780143137184</v>
       </c>
       <c r="Y87" s="4"/>
       <c r="Z87" s="4"/>
       <c r="AH87" t="str">
-        <f>"covers/" &amp; A87 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/cooking-kremlin.jpg</v>
       </c>
-      <c r="AO87" s="17" t="s">
-        <v>489</v>
-      </c>
-      <c r="AP87" s="24" t="s">
+      <c r="AO87" s="25" t="s">
         <v>488</v>
+      </c>
+      <c r="AP87" s="26" t="s">
+        <v>487</v>
       </c>
       <c r="AT87" t="s">
         <v>23</v>
@@ -8588,9 +8615,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B88" t="s">
         <v>216</v>
@@ -8599,35 +8626,35 @@
         <v>970</v>
       </c>
       <c r="D88" s="15" t="s">
+        <v>490</v>
+      </c>
+      <c r="E88" t="s">
         <v>491</v>
       </c>
-      <c r="E88" t="s">
-        <v>492</v>
-      </c>
       <c r="F88" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G88" s="6"/>
       <c r="P88" s="2" t="s">
         <v>113</v>
       </c>
       <c r="Q88" s="7" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="R88" s="3">
         <v>24</v>
       </c>
-      <c r="X88" s="28">
+      <c r="X88" s="21">
         <v>9781565124424</v>
       </c>
       <c r="Y88" s="4"/>
       <c r="Z88" s="4"/>
       <c r="AH88" t="str">
-        <f>"covers/" &amp; A88 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/matt-the-first.jpg</v>
       </c>
-      <c r="AO88" s="17" t="s">
-        <v>493</v>
+      <c r="AO88" s="25" t="s">
+        <v>492</v>
       </c>
       <c r="AT88" t="s">
         <v>23</v>
@@ -8639,9 +8666,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="89" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B89" t="s">
         <v>216</v>
@@ -8650,10 +8677,10 @@
         <v>555</v>
       </c>
       <c r="D89" s="15" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="E89" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F89" t="s">
         <v>67</v>
@@ -8662,7 +8689,7 @@
         <v>112</v>
       </c>
       <c r="H89" s="7" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="I89" s="7">
         <v>17.95</v>
@@ -8673,14 +8700,14 @@
       <c r="Y89" s="4"/>
       <c r="Z89" s="4"/>
       <c r="AH89" t="str">
-        <f>"covers/" &amp; A89 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/kaytek-wizard.jpg</v>
       </c>
-      <c r="AO89" s="17" t="s">
+      <c r="AO89" s="25" t="s">
+        <v>497</v>
+      </c>
+      <c r="AP89" s="26" t="s">
         <v>498</v>
-      </c>
-      <c r="AP89" s="24" t="s">
-        <v>499</v>
       </c>
       <c r="AT89" t="s">
         <v>23</v>
@@ -8692,9 +8719,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B90" t="s">
         <v>74</v>
@@ -8703,38 +8730,38 @@
         <v>933</v>
       </c>
       <c r="D90" s="15" t="s">
+        <v>500</v>
+      </c>
+      <c r="E90" t="s">
         <v>501</v>
       </c>
-      <c r="E90" t="s">
-        <v>502</v>
-      </c>
       <c r="F90" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="G90" s="6"/>
       <c r="P90" s="2" t="s">
         <v>113</v>
       </c>
       <c r="Q90" s="7" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="R90" s="3">
         <v>17.95</v>
       </c>
-      <c r="X90" s="28">
+      <c r="X90" s="21">
         <v>9781590176658</v>
       </c>
       <c r="Y90" s="4"/>
       <c r="Z90" s="4"/>
       <c r="AH90" t="str">
-        <f>"covers/" &amp; A90 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/miron-memoir.jpg</v>
       </c>
-      <c r="AO90" s="17" t="s">
-        <v>505</v>
-      </c>
-      <c r="AP90" s="24" t="s">
+      <c r="AO90" s="25" t="s">
         <v>504</v>
+      </c>
+      <c r="AP90" s="26" t="s">
+        <v>503</v>
       </c>
       <c r="AT90" t="s">
         <v>23</v>
@@ -8746,9 +8773,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="91" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B91" t="s">
         <v>74</v>
@@ -8757,10 +8784,10 @@
         <v>1020</v>
       </c>
       <c r="D91" s="15" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="E91" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F91" t="s">
         <v>67</v>
@@ -8770,22 +8797,22 @@
         <v>113</v>
       </c>
       <c r="Q91" s="7" t="s">
-        <v>503</v>
-      </c>
-      <c r="X91" s="28">
+        <v>502</v>
+      </c>
+      <c r="X91" s="21">
         <v>9781681372563</v>
       </c>
       <c r="Y91" s="4"/>
       <c r="Z91" s="4"/>
       <c r="AH91" t="str">
-        <f>"covers/" &amp; A91 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/inhuman-land.jpg</v>
       </c>
-      <c r="AO91" s="17" t="s">
-        <v>512</v>
-      </c>
-      <c r="AP91" s="24" t="s">
+      <c r="AO91" s="25" t="s">
         <v>511</v>
+      </c>
+      <c r="AP91" s="26" t="s">
+        <v>510</v>
       </c>
       <c r="AT91" t="s">
         <v>23</v>
@@ -8797,9 +8824,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="92" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B92" t="s">
         <v>74</v>
@@ -8808,10 +8835,10 @@
         <v>955</v>
       </c>
       <c r="D92" s="15" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E92" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F92" t="s">
         <v>67</v>
@@ -8820,7 +8847,7 @@
         <v>112</v>
       </c>
       <c r="H92" s="7" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="I92" s="7">
         <v>28</v>
@@ -8833,18 +8860,15 @@
       <c r="Y92" s="4"/>
       <c r="Z92" s="4"/>
       <c r="AH92" t="str">
-        <f>"covers/" &amp; A92 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/mud-sweeter.jpg</v>
       </c>
-      <c r="AO92" s="23" t="s">
-        <v>478</v>
-      </c>
-      <c r="AP92" s="24" t="s">
+      <c r="AO92" s="28" t="s">
         <v>477</v>
       </c>
-      <c r="AQ92"/>
-      <c r="AR92"/>
-      <c r="AS92"/>
+      <c r="AP92" s="26" t="s">
+        <v>476</v>
+      </c>
       <c r="AT92" t="s">
         <v>23</v>
       </c>
@@ -8855,9 +8879,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="93" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B93" t="s">
         <v>78</v>
@@ -8866,7 +8890,7 @@
         <v>467</v>
       </c>
       <c r="D93" s="15" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="E93" t="s">
         <v>355</v>
@@ -8891,14 +8915,14 @@
       <c r="Y93" s="4"/>
       <c r="Z93" s="4"/>
       <c r="AH93" t="str">
-        <f>"covers/" &amp; A93 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/house-of-day.jpg</v>
       </c>
-      <c r="AO93" s="17" t="s">
-        <v>516</v>
-      </c>
-      <c r="AP93" s="24" t="s">
+      <c r="AO93" s="25" t="s">
         <v>515</v>
+      </c>
+      <c r="AP93" s="26" t="s">
+        <v>514</v>
       </c>
       <c r="AT93" t="s">
         <v>23</v>
@@ -8910,9 +8934,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="94" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B94" t="str">
         <f>B92</f>
@@ -8922,10 +8946,10 @@
         <v>493</v>
       </c>
       <c r="D94" s="15" t="s">
+        <v>517</v>
+      </c>
+      <c r="E94" t="s">
         <v>518</v>
-      </c>
-      <c r="E94" t="s">
-        <v>519</v>
       </c>
       <c r="F94" t="s">
         <v>67</v>
@@ -8935,25 +8959,25 @@
         <v>113</v>
       </c>
       <c r="Q94" s="7" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="R94" s="3">
         <v>27.95</v>
       </c>
-      <c r="X94" s="28">
+      <c r="X94" s="21">
         <v>9781953943705</v>
       </c>
       <c r="Y94" s="4"/>
       <c r="Z94" s="4"/>
       <c r="AH94" t="str">
-        <f>"covers/" &amp; A94 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/garden-memory.jpg</v>
       </c>
-      <c r="AO94" s="17" t="s">
+      <c r="AO94" s="25" t="s">
+        <v>519</v>
+      </c>
+      <c r="AP94" s="26" t="s">
         <v>520</v>
-      </c>
-      <c r="AP94" s="24" t="s">
-        <v>521</v>
       </c>
       <c r="AT94" t="s">
         <v>23</v>
@@ -8965,9 +8989,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="95" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B95" t="s">
         <v>78</v>
@@ -8976,41 +9000,41 @@
         <v>666</v>
       </c>
       <c r="D95" s="15" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="E95" t="s">
+        <v>524</v>
+      </c>
+      <c r="F95" t="s">
         <v>525</v>
-      </c>
-      <c r="F95" t="s">
-        <v>526</v>
       </c>
       <c r="G95" s="6"/>
       <c r="P95" s="2" t="s">
         <v>113</v>
       </c>
       <c r="Q95" s="7" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="R95" s="3">
         <v>16</v>
       </c>
-      <c r="X95" s="28">
+      <c r="X95" s="21">
         <v>9781939931115</v>
       </c>
       <c r="Y95" s="4"/>
       <c r="Z95" s="4"/>
       <c r="AH95" t="str">
-        <f>"covers/" &amp; A95 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/killing-dog.jpg</v>
       </c>
       <c r="AI95">
         <v>2014</v>
       </c>
-      <c r="AO95" s="17" t="s">
+      <c r="AO95" s="25" t="s">
+        <v>527</v>
+      </c>
+      <c r="AP95" s="26" t="s">
         <v>528</v>
-      </c>
-      <c r="AP95" s="24" t="s">
-        <v>529</v>
       </c>
       <c r="AT95" t="s">
         <v>23</v>
@@ -9022,9 +9046,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="96" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B96" t="s">
         <v>78</v>
@@ -9033,25 +9057,25 @@
         <v>780</v>
       </c>
       <c r="D96" s="15" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="E96" t="s">
+        <v>524</v>
+      </c>
+      <c r="F96" t="s">
         <v>525</v>
-      </c>
-      <c r="F96" t="s">
-        <v>526</v>
       </c>
       <c r="G96" s="6"/>
       <c r="P96" s="2" t="s">
         <v>113</v>
       </c>
       <c r="Q96" s="7" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="R96" s="3">
         <v>16</v>
       </c>
-      <c r="X96" s="28">
+      <c r="X96" s="21">
         <v>9781939931122</v>
       </c>
       <c r="Y96" s="4" t="s">
@@ -9068,17 +9092,17 @@
         <v>9781939931184</v>
       </c>
       <c r="AH96" t="str">
-        <f>"covers/" &amp; A96 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/all-backs.jpg</v>
       </c>
       <c r="AI96">
         <v>2014</v>
       </c>
-      <c r="AO96" s="17" t="s">
-        <v>533</v>
-      </c>
-      <c r="AP96" s="24" t="s">
+      <c r="AO96" s="25" t="s">
         <v>532</v>
+      </c>
+      <c r="AP96" s="26" t="s">
+        <v>531</v>
       </c>
       <c r="AT96" t="s">
         <v>23</v>
@@ -9092,7 +9116,7 @@
     </row>
     <row r="97" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B97" t="s">
         <v>78</v>
@@ -9101,32 +9125,32 @@
         <v>810</v>
       </c>
       <c r="D97" s="15" t="s">
+        <v>533</v>
+      </c>
+      <c r="E97" t="s">
+        <v>524</v>
+      </c>
+      <c r="F97" t="s">
         <v>534</v>
-      </c>
-      <c r="E97" t="s">
-        <v>525</v>
-      </c>
-      <c r="F97" t="s">
-        <v>535</v>
       </c>
       <c r="G97" s="6"/>
       <c r="P97" s="2" t="s">
         <v>113</v>
       </c>
       <c r="Q97" s="7" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="R97" s="3">
         <v>35</v>
       </c>
-      <c r="X97" s="30">
+      <c r="X97" s="23">
         <v>9780875806976</v>
       </c>
       <c r="Y97" s="4" t="s">
         <v>114</v>
       </c>
       <c r="Z97" s="4" t="str">
-        <f t="shared" ref="Z86:Z149" si="2">Q97</f>
+        <f t="shared" ref="Z97:Z98" si="3">Q97</f>
         <v>Northern Illinois University Press</v>
       </c>
       <c r="AA97" s="5">
@@ -9136,14 +9160,14 @@
         <v>9781609090951</v>
       </c>
       <c r="AH97" t="str">
-        <f>"covers/" &amp; A97 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/beautiful-twentysomethings.jpg</v>
       </c>
-      <c r="AO97" s="17" t="s">
-        <v>538</v>
-      </c>
-      <c r="AP97" s="24" t="s">
+      <c r="AO97" s="25" t="s">
         <v>537</v>
+      </c>
+      <c r="AP97" s="26" t="s">
+        <v>536</v>
       </c>
       <c r="AT97" t="s">
         <v>23</v>
@@ -9157,7 +9181,7 @@
     </row>
     <row r="98" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B98" t="s">
         <v>78</v>
@@ -9166,10 +9190,10 @@
         <v>880</v>
       </c>
       <c r="D98" s="15" t="s">
+        <v>540</v>
+      </c>
+      <c r="E98" t="s">
         <v>541</v>
-      </c>
-      <c r="E98" t="s">
-        <v>542</v>
       </c>
       <c r="F98" t="s">
         <v>67</v>
@@ -9179,7 +9203,7 @@
         <v>113</v>
       </c>
       <c r="Q98" s="7" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="R98" s="3">
         <v>24</v>
@@ -9188,7 +9212,7 @@
         <v>114</v>
       </c>
       <c r="Z98" s="4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>Seven Stories Press</v>
       </c>
       <c r="AA98" s="5">
@@ -9198,14 +9222,14 @@
         <v>9781644210178</v>
       </c>
       <c r="AH98" t="str">
-        <f>"covers/" &amp; A98 &amp; ".jpg"</f>
+        <f t="shared" si="2"/>
         <v>covers/laras-wars.jpg</v>
       </c>
-      <c r="AO98" s="17" t="s">
-        <v>545</v>
-      </c>
-      <c r="AP98" s="24" t="s">
+      <c r="AO98" s="25" t="s">
         <v>544</v>
+      </c>
+      <c r="AP98" s="26" t="s">
+        <v>543</v>
       </c>
       <c r="AT98" t="s">
         <v>23</v>
@@ -9219,7 +9243,7 @@
     </row>
     <row r="99" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B99" t="s">
         <v>78</v>
@@ -9228,10 +9252,10 @@
         <v>1230</v>
       </c>
       <c r="D99" s="15" t="s">
+        <v>545</v>
+      </c>
+      <c r="E99" t="s">
         <v>546</v>
-      </c>
-      <c r="E99" t="s">
-        <v>547</v>
       </c>
       <c r="F99" t="s">
         <v>67</v>
@@ -9241,19 +9265,19 @@
         <v>113</v>
       </c>
       <c r="Q99" s="7" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="R99" s="3">
         <v>18</v>
       </c>
-      <c r="X99" s="28">
+      <c r="X99" s="21">
         <v>9781644213759</v>
       </c>
       <c r="Y99" s="4" t="s">
         <v>114</v>
       </c>
       <c r="Z99" s="4" t="str">
-        <f t="shared" ref="Z99:Z100" si="3">Q99</f>
+        <f t="shared" ref="Z99:Z100" si="4">Q99</f>
         <v>Seven Stories Press</v>
       </c>
       <c r="AA99" s="5">
@@ -9263,14 +9287,14 @@
         <v>9781644213766</v>
       </c>
       <c r="AH99" t="str">
-        <f t="shared" ref="AH99:AH114" si="4">"covers/" &amp; A99 &amp; ".jpg"</f>
+        <f t="shared" ref="AH99:AH115" si="5">"covers/" &amp; A99 &amp; ".jpg"</f>
         <v>covers/little-beauty.jpg</v>
       </c>
-      <c r="AO99" s="17" t="s">
-        <v>549</v>
-      </c>
-      <c r="AP99" s="24" t="s">
+      <c r="AO99" s="25" t="s">
         <v>548</v>
+      </c>
+      <c r="AP99" s="26" t="s">
+        <v>547</v>
       </c>
       <c r="AT99" t="s">
         <v>23</v>
@@ -9284,7 +9308,7 @@
     </row>
     <row r="100" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B100" t="s">
         <v>74</v>
@@ -9293,32 +9317,32 @@
         <v>1230</v>
       </c>
       <c r="D100" s="15" t="s">
+        <v>550</v>
+      </c>
+      <c r="E100" t="s">
+        <v>509</v>
+      </c>
+      <c r="F100" t="s">
         <v>551</v>
-      </c>
-      <c r="E100" t="s">
-        <v>510</v>
-      </c>
-      <c r="F100" t="s">
-        <v>552</v>
       </c>
       <c r="G100" s="6"/>
       <c r="P100" s="2" t="s">
         <v>113</v>
       </c>
       <c r="Q100" s="7" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="R100" s="3">
         <v>17</v>
       </c>
-      <c r="X100" s="28">
+      <c r="X100" s="21">
         <v>9781681372587</v>
       </c>
       <c r="Y100" s="4" t="s">
         <v>114</v>
       </c>
       <c r="Z100" s="4" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>NYRB Classics</v>
       </c>
       <c r="AA100" s="5">
@@ -9328,14 +9352,14 @@
         <v>9781681372594</v>
       </c>
       <c r="AH100" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>covers/lectures-proust.jpg</v>
       </c>
-      <c r="AO100" s="17" t="s">
+      <c r="AO100" s="25" t="s">
+        <v>552</v>
+      </c>
+      <c r="AP100" s="26" t="s">
         <v>553</v>
-      </c>
-      <c r="AP100" s="24" t="s">
-        <v>554</v>
       </c>
       <c r="AT100" t="s">
         <v>23</v>
@@ -9349,7 +9373,7 @@
     </row>
     <row r="101" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B101" t="s">
         <v>74</v>
@@ -9358,32 +9382,32 @@
         <v>1245</v>
       </c>
       <c r="D101" s="15" t="s">
+        <v>555</v>
+      </c>
+      <c r="E101" t="s">
+        <v>509</v>
+      </c>
+      <c r="F101" t="s">
         <v>556</v>
-      </c>
-      <c r="E101" t="s">
-        <v>510</v>
-      </c>
-      <c r="F101" t="s">
-        <v>557</v>
       </c>
       <c r="G101" s="6"/>
       <c r="P101" s="2" t="s">
         <v>113</v>
       </c>
       <c r="Q101" s="7" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="R101" s="3">
         <v>18</v>
       </c>
-      <c r="X101" s="28">
+      <c r="X101" s="21">
         <v>9781681374864</v>
       </c>
       <c r="Y101" s="4" t="s">
         <v>114</v>
       </c>
       <c r="Z101" s="4" t="str">
-        <f t="shared" ref="Z101" si="5">Q101</f>
+        <f t="shared" ref="Z101" si="6">Q101</f>
         <v>NYRB Classics</v>
       </c>
       <c r="AA101" s="5">
@@ -9393,14 +9417,14 @@
         <v>9781681374871</v>
       </c>
       <c r="AH101" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>covers/Starobielsk-essays.jpg</v>
       </c>
-      <c r="AO101" s="17" t="s">
-        <v>560</v>
-      </c>
-      <c r="AP101" s="24" t="s">
+      <c r="AO101" s="25" t="s">
         <v>559</v>
+      </c>
+      <c r="AP101" s="26" t="s">
+        <v>558</v>
       </c>
       <c r="AT101" t="s">
         <v>23</v>
@@ -9414,7 +9438,7 @@
     </row>
     <row r="102" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B102" t="s">
         <v>87</v>
@@ -9423,19 +9447,19 @@
         <v>1300</v>
       </c>
       <c r="D102" s="15" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E102" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="F102" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G102" s="6" t="s">
         <v>112</v>
       </c>
       <c r="H102" s="7" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="I102" s="7">
         <v>30</v>
@@ -9453,7 +9477,7 @@
       <c r="R102" s="3">
         <v>37</v>
       </c>
-      <c r="X102" s="28">
+      <c r="X102" s="21">
         <v>9780374536374</v>
       </c>
       <c r="Y102" s="4" t="s">
@@ -9470,14 +9494,14 @@
         <v>9780374710323</v>
       </c>
       <c r="AH102" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>covers/jedwabne-crime.jpg</v>
       </c>
-      <c r="AO102" s="17" t="s">
+      <c r="AO102" s="25" t="s">
+        <v>560</v>
+      </c>
+      <c r="AP102" s="26" t="s">
         <v>561</v>
-      </c>
-      <c r="AP102" s="24" t="s">
-        <v>562</v>
       </c>
       <c r="AT102" t="s">
         <v>23</v>
@@ -9491,7 +9515,7 @@
     </row>
     <row r="103" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B103" t="s">
         <v>127</v>
@@ -9500,25 +9524,25 @@
         <v>1300</v>
       </c>
       <c r="D103" s="15" t="s">
+        <v>566</v>
+      </c>
+      <c r="E103" t="s">
         <v>567</v>
       </c>
-      <c r="E103" t="s">
-        <v>568</v>
-      </c>
       <c r="F103" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G103" s="6"/>
       <c r="P103" s="2" t="s">
         <v>113</v>
       </c>
       <c r="Q103" s="7" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="R103" s="3">
         <v>15</v>
       </c>
-      <c r="X103" s="28">
+      <c r="X103" s="21">
         <v>9781681377308</v>
       </c>
       <c r="Y103" s="4" t="s">
@@ -9535,14 +9559,14 @@
         <v>9781681377315</v>
       </c>
       <c r="AH103" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>covers/ginczanka-firebird.jpg</v>
       </c>
-      <c r="AO103" s="17" t="s">
-        <v>571</v>
-      </c>
-      <c r="AP103" s="24" t="s">
+      <c r="AO103" s="25" t="s">
         <v>570</v>
+      </c>
+      <c r="AP103" s="26" t="s">
+        <v>569</v>
       </c>
       <c r="AT103" t="s">
         <v>23</v>
@@ -9556,7 +9580,7 @@
     </row>
     <row r="104" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B104" t="s">
         <v>127</v>
@@ -9565,25 +9589,25 @@
         <v>1350</v>
       </c>
       <c r="D104" s="15" t="s">
+        <v>572</v>
+      </c>
+      <c r="E104" t="s">
         <v>573</v>
       </c>
-      <c r="E104" t="s">
-        <v>574</v>
-      </c>
       <c r="F104" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G104" s="6"/>
       <c r="P104" s="2" t="s">
         <v>113</v>
       </c>
       <c r="Q104" s="7" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="R104" s="3">
         <v>15</v>
       </c>
-      <c r="X104" s="31">
+      <c r="X104" s="24">
         <v>9781681371603</v>
       </c>
       <c r="Y104" s="4" t="s">
@@ -9600,14 +9624,14 @@
         <v>9781681371610</v>
       </c>
       <c r="AH104" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>covers/life-grows.jpg</v>
       </c>
-      <c r="AO104" s="17" t="s">
+      <c r="AO104" s="25" t="s">
+        <v>575</v>
+      </c>
+      <c r="AP104" s="26" t="s">
         <v>576</v>
-      </c>
-      <c r="AP104" s="24" t="s">
-        <v>577</v>
       </c>
       <c r="AT104" t="s">
         <v>23</v>
@@ -9621,7 +9645,7 @@
     </row>
     <row r="105" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B105" t="s">
         <v>78</v>
@@ -9630,10 +9654,10 @@
         <v>1340</v>
       </c>
       <c r="D105" s="15" t="s">
+        <v>579</v>
+      </c>
+      <c r="E105" t="s">
         <v>580</v>
-      </c>
-      <c r="E105" t="s">
-        <v>581</v>
       </c>
       <c r="F105" t="s">
         <v>67</v>
@@ -9643,19 +9667,19 @@
         <v>113</v>
       </c>
       <c r="Q105" s="7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="R105" s="3">
         <v>17</v>
       </c>
-      <c r="X105" s="28">
+      <c r="X105" s="21">
         <v>9781068740404</v>
       </c>
       <c r="Y105" s="4" t="s">
         <v>114</v>
       </c>
       <c r="Z105" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="AA105" s="5">
         <v>9.5</v>
@@ -9664,11 +9688,11 @@
         <v>9781068740411</v>
       </c>
       <c r="AH105" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>covers/voracious.jpg</v>
       </c>
-      <c r="AO105" s="17" t="s">
-        <v>579</v>
+      <c r="AO105" s="25" t="s">
+        <v>578</v>
       </c>
       <c r="AT105" t="s">
         <v>23</v>
@@ -9682,7 +9706,7 @@
     </row>
     <row r="106" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B106" t="s">
         <v>78</v>
@@ -9691,10 +9715,10 @@
         <v>1370</v>
       </c>
       <c r="D106" s="15" t="s">
+        <v>583</v>
+      </c>
+      <c r="E106" t="s">
         <v>584</v>
-      </c>
-      <c r="E106" t="s">
-        <v>585</v>
       </c>
       <c r="F106" t="s">
         <v>67</v>
@@ -9704,12 +9728,12 @@
         <v>113</v>
       </c>
       <c r="Q106" s="7" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="R106" s="3">
         <v>18</v>
       </c>
-      <c r="X106" s="28">
+      <c r="X106" s="21">
         <v>9781786074980</v>
       </c>
       <c r="Y106" s="4" t="s">
@@ -9726,14 +9750,14 @@
         <v>9781786073594</v>
       </c>
       <c r="AH106" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>covers/lala.jpg</v>
       </c>
-      <c r="AO106" s="17" t="s">
-        <v>588</v>
-      </c>
-      <c r="AP106" s="24" t="s">
-        <v>586</v>
+      <c r="AO106" s="25" t="s">
+        <v>587</v>
+      </c>
+      <c r="AP106" s="26" t="s">
+        <v>585</v>
       </c>
       <c r="AT106" t="s">
         <v>23</v>
@@ -9747,7 +9771,7 @@
     </row>
     <row r="107" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B107" t="s">
         <v>74</v>
@@ -9756,10 +9780,10 @@
         <v>1450</v>
       </c>
       <c r="D107" s="15" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="E107" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F107" t="s">
         <v>67</v>
@@ -9769,12 +9793,12 @@
         <v>113</v>
       </c>
       <c r="Q107" s="7" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="R107" s="3">
         <v>24</v>
       </c>
-      <c r="X107" s="28">
+      <c r="X107" s="21">
         <v>9780143129745</v>
       </c>
       <c r="Y107" s="4" t="s">
@@ -9791,14 +9815,14 @@
         <v>9781101993385</v>
       </c>
       <c r="AH107" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>covers/dancing-bears.jpg</v>
       </c>
-      <c r="AO107" s="17" t="s">
-        <v>593</v>
-      </c>
-      <c r="AP107" s="24" t="s">
+      <c r="AO107" s="25" t="s">
         <v>592</v>
+      </c>
+      <c r="AP107" s="26" t="s">
+        <v>591</v>
       </c>
       <c r="AT107" t="s">
         <v>23</v>
@@ -9812,7 +9836,7 @@
     </row>
     <row r="108" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B108" t="s">
         <v>302</v>
@@ -9821,10 +9845,10 @@
         <v>1350</v>
       </c>
       <c r="D108" s="15" t="s">
+        <v>593</v>
+      </c>
+      <c r="E108" t="s">
         <v>594</v>
-      </c>
-      <c r="E108" t="s">
-        <v>595</v>
       </c>
       <c r="F108" t="s">
         <v>67</v>
@@ -9834,12 +9858,12 @@
         <v>113</v>
       </c>
       <c r="Q108" s="7" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="R108" s="3">
         <v>15</v>
       </c>
-      <c r="X108" s="28">
+      <c r="X108" s="21">
         <v>9781503935860</v>
       </c>
       <c r="Y108" s="4" t="s">
@@ -9856,14 +9880,14 @@
         <v>9781503990869</v>
       </c>
       <c r="AH108" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>covers/rage.jpg</v>
       </c>
-      <c r="AO108" s="17" t="s">
+      <c r="AO108" s="25" t="s">
+        <v>597</v>
+      </c>
+      <c r="AP108" s="26" t="s">
         <v>598</v>
-      </c>
-      <c r="AP108" s="24" t="s">
-        <v>599</v>
       </c>
       <c r="AT108" t="s">
         <v>23</v>
@@ -9877,7 +9901,7 @@
     </row>
     <row r="109" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B109" t="s">
         <v>302</v>
@@ -9886,10 +9910,10 @@
         <v>1370</v>
       </c>
       <c r="D109" s="15" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E109" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="F109" t="s">
         <v>67</v>
@@ -9899,22 +9923,22 @@
         <v>113</v>
       </c>
       <c r="Q109" s="7" t="s">
-        <v>602</v>
-      </c>
-      <c r="X109" s="28">
+        <v>601</v>
+      </c>
+      <c r="X109" s="21">
         <v>9781908524027</v>
       </c>
       <c r="Y109" s="4"/>
       <c r="Z109" s="4"/>
       <c r="AH109" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>covers/grain-truth.jpg</v>
       </c>
-      <c r="AO109" s="17" t="s">
+      <c r="AO109" s="25" t="s">
+        <v>603</v>
+      </c>
+      <c r="AP109" s="26" t="s">
         <v>604</v>
-      </c>
-      <c r="AP109" s="24" t="s">
-        <v>605</v>
       </c>
       <c r="AT109" t="s">
         <v>23</v>
@@ -9926,7 +9950,7 @@
         <v>31</v>
       </c>
       <c r="AY109" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AZ109">
         <v>1</v>
@@ -9934,7 +9958,7 @@
     </row>
     <row r="110" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B110" t="s">
         <v>78</v>
@@ -9943,7 +9967,7 @@
         <v>1250</v>
       </c>
       <c r="D110" s="15" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="E110" t="s">
         <v>355</v>
@@ -9973,14 +9997,14 @@
       <c r="R110" s="3">
         <v>19</v>
       </c>
-      <c r="X110" s="28">
+      <c r="X110" s="21">
         <v>9780525541349</v>
       </c>
       <c r="Y110" s="4" t="s">
         <v>114</v>
       </c>
       <c r="Z110" s="4" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AA110" s="5">
         <v>9</v>
@@ -9989,11 +10013,11 @@
         <v>9781910695562</v>
       </c>
       <c r="AH110" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>covers/over-the-bones.jpg</v>
       </c>
-      <c r="AO110" s="17" t="s">
-        <v>609</v>
+      <c r="AO110" s="25" t="s">
+        <v>608</v>
       </c>
       <c r="AT110" t="s">
         <v>23</v>
@@ -10005,7 +10029,7 @@
         <v>31</v>
       </c>
       <c r="AY110" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="AZ110">
         <v>2</v>
@@ -10013,7 +10037,7 @@
     </row>
     <row r="111" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B111" t="s">
         <v>78</v>
@@ -10022,7 +10046,7 @@
         <v>1235</v>
       </c>
       <c r="D111" s="15" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="E111" t="s">
         <v>355</v>
@@ -10052,7 +10076,7 @@
       <c r="R111" s="3">
         <v>12.5</v>
       </c>
-      <c r="X111" s="28">
+      <c r="X111" s="21">
         <v>9780593087503</v>
       </c>
       <c r="Y111" s="4" t="s">
@@ -10069,14 +10093,14 @@
         <v>9780593087497</v>
       </c>
       <c r="AH111" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>covers/jacobs-books.jpg</v>
       </c>
-      <c r="AO111" s="17" t="s">
+      <c r="AO111" s="25" t="s">
+        <v>611</v>
+      </c>
+      <c r="AP111" s="26" t="s">
         <v>612</v>
-      </c>
-      <c r="AP111" s="24" t="s">
-        <v>613</v>
       </c>
       <c r="AT111" t="s">
         <v>23</v>
@@ -10090,7 +10114,7 @@
     </row>
     <row r="112" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B112" t="s">
         <v>78</v>
@@ -10099,7 +10123,7 @@
         <v>1270</v>
       </c>
       <c r="D112" s="15" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="E112" t="s">
         <v>355</v>
@@ -10129,7 +10153,7 @@
       <c r="R112" s="3">
         <v>20</v>
       </c>
-      <c r="X112" s="28">
+      <c r="X112" s="21">
         <v>9780593712955</v>
       </c>
       <c r="Y112" s="4" t="s">
@@ -10146,14 +10170,14 @@
         <v>9781804271094</v>
       </c>
       <c r="AH112" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>covers/empusium.jpg</v>
       </c>
-      <c r="AO112" s="17" t="s">
+      <c r="AO112" s="25" t="s">
+        <v>615</v>
+      </c>
+      <c r="AP112" s="26" t="s">
         <v>616</v>
-      </c>
-      <c r="AP112" s="24" t="s">
-        <v>617</v>
       </c>
       <c r="AT112" t="s">
         <v>23</v>
@@ -10165,9 +10189,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="113" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B113" t="s">
         <v>78</v>
@@ -10176,7 +10200,7 @@
         <v>1500</v>
       </c>
       <c r="D113" s="15" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="E113" t="s">
         <v>355</v>
@@ -10188,7 +10212,7 @@
         <v>112</v>
       </c>
       <c r="H113" s="7" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I113" s="7">
         <v>24</v>
@@ -10202,7 +10226,7 @@
         <v>114</v>
       </c>
       <c r="Z113" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AA113" s="5">
         <v>14</v>
@@ -10211,11 +10235,11 @@
         <v>9781644214480</v>
       </c>
       <c r="AH113" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>covers/mr-distinctive.jpg</v>
       </c>
-      <c r="AO113" s="17" t="s">
-        <v>620</v>
+      <c r="AO113" s="25" t="s">
+        <v>619</v>
       </c>
       <c r="AT113" t="s">
         <v>23</v>
@@ -10227,9 +10251,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="114" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:52" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B114" t="s">
         <v>78</v>
@@ -10238,7 +10262,7 @@
         <v>1600</v>
       </c>
       <c r="D114" s="15" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="E114" t="s">
         <v>355</v>
@@ -10250,7 +10274,7 @@
         <v>112</v>
       </c>
       <c r="H114" s="7" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="I114" s="7">
         <v>23</v>
@@ -10264,7 +10288,7 @@
         <v>114</v>
       </c>
       <c r="Z114" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AA114" s="5">
         <v>14</v>
@@ -10273,14 +10297,14 @@
         <v>9781644210352</v>
       </c>
       <c r="AH114" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>covers/lost-soul.jpg</v>
       </c>
-      <c r="AO114" s="17" t="s">
-        <v>624</v>
-      </c>
-      <c r="AP114" s="24" t="s">
-        <v>623</v>
+      <c r="AO114" s="25" t="s">
+        <v>622</v>
+      </c>
+      <c r="AP114" s="26" t="s">
+        <v>621</v>
       </c>
       <c r="AT114" t="s">
         <v>23</v>
@@ -10292,90 +10316,139 @@
         <v>31</v>
       </c>
     </row>
-    <row r="115" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>626</v>
+      </c>
+      <c r="B115" t="s">
+        <v>302</v>
+      </c>
+      <c r="C115">
+        <v>1540</v>
+      </c>
+      <c r="D115" s="15" t="s">
+        <v>627</v>
+      </c>
+      <c r="E115" t="s">
+        <v>480</v>
+      </c>
       <c r="G115" s="6"/>
-      <c r="P115" s="2"/>
-      <c r="Q115" s="7"/>
-      <c r="Y115" s="4"/>
-      <c r="Z115" s="4"/>
-    </row>
-    <row r="116" spans="1:49" x14ac:dyDescent="0.25">
+      <c r="P115" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q115" s="7" t="s">
+        <v>629</v>
+      </c>
+      <c r="R115" s="3">
+        <v>19.5</v>
+      </c>
+      <c r="X115" s="21">
+        <v>9781786079299</v>
+      </c>
+      <c r="Y115" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z115" s="4" t="str">
+        <f>Q115</f>
+        <v>Point Blank</v>
+      </c>
+      <c r="AA115" s="5">
+        <v>8.5</v>
+      </c>
+      <c r="AG115" s="8">
+        <v>9781786079282</v>
+      </c>
+      <c r="AH115" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/torn-curtain.jpg</v>
+      </c>
+      <c r="AO115" s="25" t="s">
+        <v>628</v>
+      </c>
+      <c r="AY115" t="s">
+        <v>630</v>
+      </c>
+      <c r="AZ115">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="116" spans="1:52" x14ac:dyDescent="0.25">
       <c r="G116" s="6"/>
       <c r="P116" s="2"/>
       <c r="Q116" s="7"/>
       <c r="Y116" s="4"/>
       <c r="Z116" s="4"/>
     </row>
-    <row r="117" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:52" x14ac:dyDescent="0.25">
       <c r="G117" s="6"/>
       <c r="P117" s="2"/>
       <c r="Q117" s="7"/>
       <c r="Y117" s="4"/>
       <c r="Z117" s="4"/>
     </row>
-    <row r="118" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:52" x14ac:dyDescent="0.25">
       <c r="G118" s="6"/>
       <c r="P118" s="2"/>
       <c r="Q118" s="7"/>
       <c r="Y118" s="4"/>
       <c r="Z118" s="4"/>
     </row>
-    <row r="119" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:52" x14ac:dyDescent="0.25">
       <c r="G119" s="6"/>
       <c r="P119" s="2"/>
       <c r="Q119" s="7"/>
       <c r="Y119" s="4"/>
       <c r="Z119" s="4"/>
     </row>
-    <row r="120" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:52" x14ac:dyDescent="0.25">
       <c r="G120" s="6"/>
       <c r="Q120" s="7"/>
       <c r="Y120" s="4"/>
       <c r="Z120" s="4"/>
     </row>
-    <row r="121" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:52" x14ac:dyDescent="0.25">
       <c r="G121" s="6"/>
       <c r="Q121" s="7"/>
       <c r="Y121" s="4"/>
       <c r="Z121" s="4"/>
     </row>
-    <row r="122" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:52" x14ac:dyDescent="0.25">
       <c r="G122" s="6"/>
       <c r="Q122" s="7"/>
       <c r="Y122" s="4"/>
       <c r="Z122" s="4"/>
     </row>
-    <row r="123" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:52" x14ac:dyDescent="0.25">
       <c r="G123" s="6"/>
       <c r="Q123" s="7"/>
       <c r="Y123" s="4"/>
       <c r="Z123" s="4"/>
     </row>
-    <row r="124" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:52" x14ac:dyDescent="0.25">
       <c r="G124" s="6"/>
       <c r="Q124" s="7"/>
       <c r="Y124" s="4"/>
       <c r="Z124" s="4"/>
     </row>
-    <row r="125" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:52" x14ac:dyDescent="0.25">
       <c r="G125" s="6"/>
       <c r="Q125" s="7"/>
       <c r="Y125" s="4"/>
       <c r="Z125" s="4"/>
     </row>
-    <row r="126" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:52" x14ac:dyDescent="0.25">
       <c r="G126" s="6"/>
       <c r="Q126" s="7"/>
       <c r="Y126" s="4"/>
       <c r="Z126" s="4"/>
     </row>
-    <row r="127" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:52" x14ac:dyDescent="0.25">
       <c r="G127" s="6"/>
       <c r="Q127" s="7"/>
       <c r="Y127" s="4"/>
       <c r="Z127" s="4"/>
     </row>
-    <row r="128" spans="1:49" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:52" x14ac:dyDescent="0.25">
       <c r="G128" s="6"/>
       <c r="Q128" s="7"/>
       <c r="Y128" s="4"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/the-polish-atheneum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1784" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A5E08E28-F7BD-4B60-BC07-B1C3636C7431}"/>
+  <xr:revisionPtr revIDLastSave="1823" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34FBFB24-C824-4EB6-88D4-D2784BED9AF9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="642">
   <si>
     <t>cover</t>
   </si>
@@ -2741,6 +2741,44 @@
   </si>
   <si>
     <t>Zofia Turbotynska Mysteries</t>
+  </si>
+  <si>
+    <t>on-niemen</t>
+  </si>
+  <si>
+    <t>On the Niemen</t>
+  </si>
+  <si>
+    <t>Eliza Orzeszkowa</t>
+  </si>
+  <si>
+    <t>Michelle Granas</t>
+  </si>
+  <si>
+    <t>B00I90VP7K</t>
+  </si>
+  <si>
+    <t>In the early 1900s, Eliza Orzeszkowa was repeatedly a top contender, with Leo Tolstoy, for the Nobel Prize in literature. Neither won. Nevertheless, her novels have remained classics of Polish literature, and her most famous, On the Niemen, is not only an unusual love story, but is strikingly relevant today.
+Unhappy after being abandoned by her fiancé, Justyna, an impoverished young woman who lives in a manor house belonging to relatives, desires a life of greater usefulness. While being pursued by a wealthy aristocrat and by her former love – now married – she meets Jan, a man of lower social standing, who introduces her to a different world: one of closeness to nature, manual labor, and communal enjoyments. To leave the manor for a farmstead would be a very peculiar proceeding, however, and furthermore, the farming community is feuding with Justyna's uncle.
+Set in the 1880s among the Polish population in a part of what was once the Polish-Lithuanian Commonwealth, the story involves the consequences of the January Uprising, twenty years before, against Russian rule. The characters are drawn from a cross section of society and the novel's topics include love, social justice, egotism and materialism, the psychological effects of war, the emancipation of women, marriage as partnership, drug addiction, dignity, obligations to one's fellow humans, what it means to be civilized – and joy.</t>
+  </si>
+  <si>
+    <t>“[Marta] reminds you, too, that it’s not just the hottest contemporary novels that are crying out to be translated – it’s also hidden gems like this, that give us a richer sense of a particular tradition’s literary history.”—Kasia Bartoszynska, Three Percent
+“This translation, the skilful work of Anna Gąsienica Byrcyn and Stephanie Kraft, well renders the simple, unadorned language of the original Polish version, and the book comes in John Bukowczyk’s Polish and Polish-American Studies Series that is already well established and well-known for choosing manuscripts in terms of excellence. Marta will find its reader among lovers of literature as well as academics studying women writers and the literature of the second half of the nineteenth century. It will provide important reading material for courses in literature at the university level—not only those with a focus on women’s writing, but also those concerned with ‘the other Europe’ and its women."—Bożena Karwowska, Polish Review</t>
+  </si>
+  <si>
+    <t>marta</t>
+  </si>
+  <si>
+    <t>Marta</t>
+  </si>
+  <si>
+    <t>Ohio Press University</t>
+  </si>
+  <si>
+    <t>Eliza Orzeszkowa was a trailblazing Polish novelist who, alongside Leo Tolstoy and Henryk Sienkiewicz, was a finalist for the 1905 Nobel Prize in Literature. Of her many works of social realism, Marta (1873) is among the best known, but until now it has not been available in English. Easily a peer of The Awakening and A Doll’s House, the novel was well ahead of the English literature of its time in attacking the ways the labor market failed women.
+Suddenly widowed, the previously middle-class Marta Świcka is left penniless and launched into a grim battle for her survival and that of her small daughter. As she applies for job after job in Warsaw—portrayed here as an every-city, an unforgiving commercial landscape that could be any European metropolis of the time—she is told time after time that only men will be hired, that men need jobs because they are fathers and heads of families.
+Marta burns with Orzeszkowa’s feminist conviction that sexism was not just an annoyance but a threat to the survival of women and children. It anticipated the need for social safety nets whose existence we take for granted today, and could easily read as an indictment of current efforts to dismantle those very programs. Tightly plotted and exquisitely translated by Anna Gąsienica-Byrcyn and Stephanie Kraft, Marta resonates beyond its Polish setting to find its place in women’s studies, labor history, and among other works of nineteenth-century literature and literature of social change.</t>
   </si>
 </sst>
 </file>
@@ -2917,7 +2955,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2953,12 +2991,18 @@
     <xf numFmtId="1" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -9287,7 +9331,7 @@
         <v>9781644213766</v>
       </c>
       <c r="AH99" t="str">
-        <f t="shared" ref="AH99:AH115" si="5">"covers/" &amp; A99 &amp; ".jpg"</f>
+        <f t="shared" ref="AH99:AH117" si="5">"covers/" &amp; A99 &amp; ".jpg"</f>
         <v>covers/little-beauty.jpg</v>
       </c>
       <c r="AO99" s="25" t="s">
@@ -10365,6 +10409,15 @@
       <c r="AO115" s="25" t="s">
         <v>628</v>
       </c>
+      <c r="AT115" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU115" t="s">
+        <v>23</v>
+      </c>
+      <c r="AW115" t="s">
+        <v>31</v>
+      </c>
       <c r="AY115" t="s">
         <v>630</v>
       </c>
@@ -10372,19 +10425,131 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:52" ht="255" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>631</v>
+      </c>
+      <c r="B116" t="s">
+        <v>40</v>
+      </c>
+      <c r="C116">
+        <v>1543</v>
+      </c>
+      <c r="D116" s="15" t="s">
+        <v>632</v>
+      </c>
+      <c r="E116" t="s">
+        <v>633</v>
+      </c>
+      <c r="F116" t="s">
+        <v>634</v>
+      </c>
       <c r="G116" s="6"/>
-      <c r="P116" s="2"/>
-      <c r="Q116" s="7"/>
-      <c r="Y116" s="4"/>
-      <c r="Z116" s="4"/>
-    </row>
-    <row r="117" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="G117" s="6"/>
+      <c r="P116" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q116" s="7" t="str">
+        <f>F116</f>
+        <v>Michelle Granas</v>
+      </c>
+      <c r="R116" s="3">
+        <v>24</v>
+      </c>
+      <c r="X116" s="21">
+        <v>9780988859296</v>
+      </c>
+      <c r="Y116" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z116" s="4" t="str">
+        <f>Q116</f>
+        <v>Michelle Granas</v>
+      </c>
+      <c r="AA116" s="5">
+        <v>2.99</v>
+      </c>
+      <c r="AG116" s="8" t="s">
+        <v>635</v>
+      </c>
+      <c r="AH116" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/on-niemen.jpg</v>
+      </c>
+      <c r="AO116" s="31" t="s">
+        <v>636</v>
+      </c>
+      <c r="AT116" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU116" t="s">
+        <v>23</v>
+      </c>
+      <c r="AW116" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="117" spans="1:52" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>638</v>
+      </c>
+      <c r="B117" t="s">
+        <v>40</v>
+      </c>
+      <c r="C117">
+        <v>1570</v>
+      </c>
+      <c r="D117" s="15" t="s">
+        <v>639</v>
+      </c>
+      <c r="E117" t="s">
+        <v>633</v>
+      </c>
+      <c r="G117" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H117" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="I117" s="7">
+        <v>25</v>
+      </c>
+      <c r="O117" s="10">
+        <v>9780821423134</v>
+      </c>
       <c r="P117" s="2"/>
       <c r="Q117" s="7"/>
-      <c r="Y117" s="4"/>
-      <c r="Z117" s="4"/>
+      <c r="Y117" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z117" s="4" t="str">
+        <f>H117</f>
+        <v>Ohio Press University</v>
+      </c>
+      <c r="AA117" s="5">
+        <v>24</v>
+      </c>
+      <c r="AG117" s="8">
+        <v>9780821446294</v>
+      </c>
+      <c r="AH117" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/marta.jpg</v>
+      </c>
+      <c r="AO117" s="31" t="s">
+        <v>641</v>
+      </c>
+      <c r="AP117" s="32" t="s">
+        <v>637</v>
+      </c>
+      <c r="AT117" t="s">
+        <v>23</v>
+      </c>
+      <c r="AU117" t="s">
+        <v>23</v>
+      </c>
+      <c r="AW117" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="118" spans="1:52" x14ac:dyDescent="0.25">
       <c r="G118" s="6"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/the-polish-atheneum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1823" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34FBFB24-C824-4EB6-88D4-D2784BED9AF9}"/>
+  <xr:revisionPtr revIDLastSave="1950" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8548D08B-ACBC-468E-A918-208869E1934F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
@@ -16,6 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1458" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="693">
   <si>
     <t>cover</t>
   </si>
@@ -2779,6 +2780,200 @@
     <t>Eliza Orzeszkowa was a trailblazing Polish novelist who, alongside Leo Tolstoy and Henryk Sienkiewicz, was a finalist for the 1905 Nobel Prize in Literature. Of her many works of social realism, Marta (1873) is among the best known, but until now it has not been available in English. Easily a peer of The Awakening and A Doll’s House, the novel was well ahead of the English literature of its time in attacking the ways the labor market failed women.
 Suddenly widowed, the previously middle-class Marta Świcka is left penniless and launched into a grim battle for her survival and that of her small daughter. As she applies for job after job in Warsaw—portrayed here as an every-city, an unforgiving commercial landscape that could be any European metropolis of the time—she is told time after time that only men will be hired, that men need jobs because they are fathers and heads of families.
 Marta burns with Orzeszkowa’s feminist conviction that sexism was not just an annoyance but a threat to the survival of women and children. It anticipated the need for social safety nets whose existence we take for granted today, and could easily read as an indictment of current efforts to dismantle those very programs. Tightly plotted and exquisitely translated by Anna Gąsienica-Byrcyn and Stephanie Kraft, Marta resonates beyond its Polish setting to find its place in women’s studies, labor history, and among other works of nineteenth-century literature and literature of social change.</t>
+  </si>
+  <si>
+    <t>Stephanie Kraft, Anna Gąsienica Byrcyn</t>
+  </si>
+  <si>
+    <t>Aleksander's Antiquities</t>
+  </si>
+  <si>
+    <t>The Dedalus Book of Polish Fantasy</t>
+  </si>
+  <si>
+    <t>B008GRP3XS</t>
+  </si>
+  <si>
+    <t>The Mannequins' Ball</t>
+  </si>
+  <si>
+    <t>Conversations with an Executioner: 255 Days Imprisoned with the Nazi who Destroyed the Warsaw Ghett</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Named a best book of 2019 by TIME, NPR, Kirkus, Publishers Weekly, and BookRiot.
+PEN America Translation Prize longlist
+Warwick Prize for Women in Translation shortlist
+“A marvelously weird and fablelike mystery. . . . Authors with Tokarczuk’s vending machine of phrasing . . . and gimlet eye for human behavior. . . are rarely also masters of pacing and suspense. But even as Tokarczuk sticks landing after landing . . . her asides are never desultory or a liability. They are more like little cuts — quick, exacting and purposefully belated in their bleeding. . . . This book is not a mere whodunit: It’s a philosophical fairy tale about life and death that’s been trying to spill its secrets. Secrets that, if you’ve kept your ear to the ground, you knew in your bones all along.” — New York Times Book Review
+“While it adopts the straightforward structure of a murder mystery, [the book features] macabre humor and morbid philosophical interludes [that] are distinctive to its author. . . [and an] excellent payoff at the finale. . . . As for Ms. Tokarczuk, there’s no doubt: She’s a gifted, original writer, and the appearance of her novels in English is a welcome development.”— The Wall Street Journal
+“Drive Your Plow is exhilarating in a way that feels fierce and private, almost inarticulable; it’s one of the most existentially refreshing novels I’ve read in a long time.” — The New Yorker
+“A paean to nature. . . a sort of ode to Blake. . . [and] a lament. . . Does Tokarczuk transcend Blake? Arguable —perhaps.” — NPR
+“A brilliant literary murder mystery.”  –Chicago Tribune
+“ A winding, imaginative, genre-defying story. Part murder mystery, part fairy tale, Drive Your Plow is a thrilling philosophical examination of the ways in which some living creatures are privileged above others.” – TIME
+“Shimmering with subversive brilliance . . . . this is not your conventional crime story—for Tokarczuk is not your conventional writer. Through her extraordinary talent and intellect, and her ‘thinking novels,’ she ponders and tackles larger ecological and political issues. The stakes are always high; Tokarczuk repeatedly rises to the occasion and raises a call to arms.”—HuffPost 
+“Sometimes the opening sentence of a first-person narrative can so vividly capture the personality of its speaker that you immediately want to spend all the time you can in their company. That’s the case with . . . Drive Your Plow Over the Bones of the Dead  . . .  [a] barbed and subversive tale about what it takes to challenge the complacency of the powers that be.” —Boston Globe 
+“Bewitching. . .. Serious crosscurrents … explore everything from animal rights to predetermination to the way society stigmatizes and marginalizes those it considers mad, strange or simply different . . . Tokarczuk is capable of miracles and ensures that this extraordinary novel soars.” —Minneapolis Star Tribune 
+"Sardonic humour and gothic plot-twists add a layer of macabre rustic comedy." – The Economist 
+"One of the funniest books of the year.” – The Guardian
+ “Written with humor, charm, and a great talent for mystery … a sharp, memorable alternative to those dime-a-dozen beach bag potboilers without losing any of the whodunnit appeal.” —Town &amp; Country </t>
+  </si>
+  <si>
+    <t>video_1_title</t>
+  </si>
+  <si>
+    <t>video_1_description</t>
+  </si>
+  <si>
+    <t>video_1_id</t>
+  </si>
+  <si>
+    <t>q7ASutCFetE</t>
+  </si>
+  <si>
+    <t>ANOTHER DAY OF LIFE Official Trailer</t>
+  </si>
+  <si>
+    <t>The 2018 adult animated drama film directed by Raúl de la Fuente and Damian Nenow, based on Ryszard Kapuściński's autobiographical account, Another Day of Life, is a co-production between Poland, Spain, Belgium, Germany and Hungary. It combines brilliant animated material and interviews with the survivors of the drama. It has won a number of international awards and has an eye popping rating of 83% on Rotten Tomatoes.</t>
+  </si>
+  <si>
+    <t>Awul3lNlh3Y</t>
+  </si>
+  <si>
+    <t>Martin Scorsese Presents Masterpieces of Polish Cinema</t>
+  </si>
+  <si>
+    <t>Martin Scorsese Presents: Masterpieces of Polish Cinema is a 21-film series released by Milestone in partnership with Propaganda Foundation, DI Factory, CRF, KinoRP and The Film Foundation. The series features brand-new restorations of classic works from some of Poland's most accomplished and lauded filmmakers, spanning the period from 1957--1987. Here, Martin Scorcese presents a short introduction to the film.</t>
+  </si>
+  <si>
+    <t>video_2_title</t>
+  </si>
+  <si>
+    <t>video_2_description</t>
+  </si>
+  <si>
+    <t>video_3_id</t>
+  </si>
+  <si>
+    <t>video_2_id</t>
+  </si>
+  <si>
+    <t>2GtcgGn5NFs</t>
+  </si>
+  <si>
+    <t>The Manuscript Found in Saragossa (2025) - Trailer Concept</t>
+  </si>
+  <si>
+    <t>ZjO1VXqX5-U</t>
+  </si>
+  <si>
+    <t>Dreams within Dreams the Wonderful Weird World of the The Saragossa Manuscript, 1965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loved by Buñuel, praised by Kubrick, and rescued from obscurity by Jerry Garcia—“The Saragossa Manuscript” has one of the wildest afterlives in film history. </t>
+  </si>
+  <si>
+    <t>A very deft trailer (very-well made with the help of AI) for an imaginary 2025 film version of the book.</t>
+  </si>
+  <si>
+    <t>video_3_title</t>
+  </si>
+  <si>
+    <t>video_3_description</t>
+  </si>
+  <si>
+    <t>The Dedalus Book of Polish Fantasy is a 1996 anthology of Polish speculative fiction, edited and translated by Wiesiek Powaga and published in the United Kingdom by Dedalus Books in their Dedalus Books of Fantasy series of European literary fantasy anthologies.
+The anthology features twenty short stories spanning two centuries of Polish literature, written by authors including Witold Gombrowicz, Stefan Grabiński, Sławomir Mrożek, Władysław Reymont, Bruno Schulz, and Jacek Dukaj.
+The collection's unifying theme is the exploration of evil, often personified in the devil or another demonic entity or entities. The genres include Gothic, surrealism, dystopian satire, even science fiction.
+The anthology has been praised for its thematic coherence, its portrayal of "the reality of evil", and its demonstration of how the Polish literary tradition differs from Western European approaches to similar themes.</t>
+  </si>
+  <si>
+    <t>Dedalus Limited</t>
+  </si>
+  <si>
+    <t>dedalus-fantasy</t>
+  </si>
+  <si>
+    <t>Jarosław Iwaszkiewicz, Stefan Grabiński, Sławomir Mrożek, Władysław Reymont, Bruno Schulz, Jacek Dukaj</t>
+  </si>
+  <si>
+    <t>Miroslłw Lipinski</t>
+  </si>
+  <si>
+    <t>Stefan Grabiński</t>
+  </si>
+  <si>
+    <t>The Dark Domain</t>
+  </si>
+  <si>
+    <t>dark-domain</t>
+  </si>
+  <si>
+    <t>...reading The Dark Domain by Stephan Grabinski is such a revelatory experience. Because here is a writer for whom supernatural horror is manifest precisely in modernity - in electricity, fire-stations, trains:the uncanny as the bad conscience of today. Sometimes Grabinski is known as the Polish Poe but this is misleading. Where Poe's horror is agonised, a kind of extended shriek, Grabinski's is cerebral, investigative. His protagonists are tortured and aghast, but not because they suffer at the caprice of Lovecraftian blind idiot gods: Grabinski's universe is strange and its principles are perhaps not what we expect, but they are principles - rules- and it is in their exploration that the mystery lies. This is horror as rigour.'
+China Mieville in The Guardian</t>
+  </si>
+  <si>
+    <t>Grabinski's commitment to a marriage of the newly announced unconscious with the supernatural gives his extravagances some conviction. These short stories offer the pleasure of myths we can crack and skilfully chilling denouements.'
+David Buckley in The Observer
+'Psycho-fantasies, doom-saturated tales of lonely men lost in hostile terrain, but the melancholy lifts to provide wonderful odd scenes, like the watchmaker whose death stops all the town clocks and the phantom train that always turns up unannounced, surprising the station staff'
+Time Out
+'Stories that brilliantly convey his love of supernatural horror. It is not the horror of haunted houses or castles, but that found in everyday modernity around him. In this dark selection, lonely souls travel on trains, coming face to face with sinister conductors and wanton women.'
+The Herald</t>
+  </si>
+  <si>
+    <t>A Polish Book of Monsters</t>
+  </si>
+  <si>
+    <t>A Polish Book of Monsters contains five stories of speculative fiction edited and translated from the Polish by Michael Kandel, award-winning translator of the fiction of Stanislaw Lem. From dystopian science fiction to fabled fantasy, these dark tales grip us through the authors' ability to create utterly convincing alien worlds that nonetheless reflect our own.</t>
+  </si>
+  <si>
+    <t>PIASA Books</t>
+  </si>
+  <si>
+    <t>polish-monsters</t>
+  </si>
+  <si>
+    <t>Daniel Gerould, Bruno Jaslenski</t>
+  </si>
+  <si>
+    <t>mannequins-ball</t>
+  </si>
+  <si>
+    <t>This play, by Futurist poet Bruno Jasienski, is an outstanding example of the joining of left-wing politics and avant-garde interest in human mechanization that characterized the experimental theatre of Poland in the inter-war years.
+Stalinism and the purges cut short Jasienski's career and prevented productions of his play for many years - except for a brilliant constructivist staging in Prague in 1933. The Mannequins' Ball can now take its place along with Capek's R.U.R. as one of the major twentieth-century dramas making use of the themes and techniques of human automata.
+Reproduced in this volume are the eight woodcuts by Moor which accompanied the original Moscow publication in 1931.</t>
+  </si>
+  <si>
+    <t>conversations-executioner</t>
+  </si>
+  <si>
+    <t>A remarkable firsthand account of the rise and fall of the Nazis told from the inside of a prison cell.
+The first complete English translation of the international classic work of World War II literature and investigative journalism.
+Warsaw, 1949: freedom fighter and journalist Kazimierz Moczarski is being held in a maximum-security prison, accused of being an enemy of the state by the Polish secret police. A survivor of the Warsaw Uprising, he is horrified to find himself locked up in a cell with the notorious Nazi official responsible for the destruction of the Warsaw Ghetto and the death of over 50,000 people: Jürgen Stroop.
+For 255 days, Stroop talks to Moczarski of his life, entirely unrepentant of the crimes for which he would soon be executed himself. Conversations with an Executioner is Moczarski’s firsthand account of these extraordinary exchanges, giving disturbing insight into the mind of one of history’s most brutal war criminals.
+Through his conversations with Stroop, Moczarski details the opportunities that the rise of the Nazi party in Germany presented for marginalized, mediocre characters like Stroop to gain prestige and power under the new regime—and the consequences that came for them after its fall. Unflinchingly examining some of humanity’s darkest moments, his work is a towering literary achievement, steeped in keen journalistic enterprise and psychological insight.
+Widely translated and adapted for stage and screen in over 15 languages, this lost classic of World War II literature is now available in its first ever complete English translation.</t>
+  </si>
+  <si>
+    <t>Kazimierz Moczarski</t>
+  </si>
+  <si>
+    <t>Sean Gasper Bye</t>
+  </si>
+  <si>
+    <t>Steerforth</t>
+  </si>
+  <si>
+    <t>"This fascinating revelation of how a good little middle class boy turns into a Nazi mass murderer is all the more chilling for the forensic, at times witty, style in which his horrified cellmate and near-victim records it. A page-turner and must-read for understanding the workings of the Holocaust."
+—Adam Zamoyski, author of Poland: A History
+"Quite simply one of the most remarkable books to emerge out of World War II. Part unlikely memoir and part biography, it gives an insight into the Nazi mind that is as fascinating as it is chilling. Outstanding."
+—Roger Moorehouse, author of Wolfpack: Inside Hitler’s U-Boat War
+"A remarkable document. By turns shocking and chilling but always compelling, Moczarski's prison conversations with a senior, serial and shameless Nazi killer provide an invaluable insight into the heart of a hideous ideology."
+—Jonathan Dimbleby, author of Endgame 1944
+"Essential reading for all those interested in the Nazi occupation of Poland, the mass murder of Polish Jews and the larger history of the Second World War."
+—Antony Polonsky, Emeritus Professor of Holocaust Studies, Brandeis University and Chief Historian, Global Education Outreach Project, Museum of Polish Jews in Warsaw
+"A remarkable feat of reportage and timely insight into the Nazi mind."
+—Charlie English, author of The CIA Book Club
+"An intriguing document that portrays Stroop as the exemplary perpetrator: a mediocrity promoted above his abilities, but fanatical in his allegiance to Hitler, Himmler and Nazi ideology. Moczarski, working from memory, brings to light the workings of the Nazi mind with penetrating insight."
+—Dan Stone, author of The Holocaust: An Unfinished History</t>
   </si>
 </sst>
 </file>
@@ -2955,7 +3150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -2991,18 +3186,13 @@
     <xf numFmtId="1" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3341,7 +3531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01CE5F32-AD1D-47CB-A8F1-52ACBFFA0BE8}">
-  <dimension ref="A1:AZ166"/>
+  <dimension ref="A1:BI167"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.140625" customWidth="1"/>
@@ -3359,12 +3549,13 @@
     <col min="34" max="35" width="26.28515625" customWidth="1"/>
     <col min="38" max="38" width="16" customWidth="1"/>
     <col min="40" max="40" width="21.140625" customWidth="1"/>
-    <col min="41" max="41" width="95.85546875" style="25" customWidth="1"/>
-    <col min="42" max="42" width="19.7109375" style="26" customWidth="1"/>
-    <col min="43" max="45" width="19.7109375" customWidth="1"/>
+    <col min="41" max="49" width="19.7109375" customWidth="1"/>
+    <col min="50" max="50" width="95.85546875" style="25" customWidth="1"/>
+    <col min="51" max="51" width="66.85546875" style="26" customWidth="1"/>
+    <col min="52" max="54" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -3485,44 +3676,71 @@
       <c r="AN1" t="s">
         <v>21</v>
       </c>
-      <c r="AO1" s="25" t="s">
+      <c r="AO1" t="s">
+        <v>649</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>650</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>651</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>658</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>659</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>661</v>
+      </c>
+      <c r="AU1" t="s">
+        <v>668</v>
+      </c>
+      <c r="AV1" t="s">
+        <v>669</v>
+      </c>
+      <c r="AW1" t="s">
+        <v>660</v>
+      </c>
+      <c r="AX1" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="AP1" s="26" t="s">
+      <c r="AY1" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AZ1" t="s">
         <v>207</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="BA1" t="s">
         <v>205</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="BB1" t="s">
         <v>208</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="BC1" t="s">
         <v>22</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="BD1" t="s">
         <v>38</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="BE1" t="s">
         <v>28</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="BF1" t="s">
         <v>29</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="BG1" t="s">
         <v>34</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="BH1" t="s">
         <v>35</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BI1" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -3583,32 +3801,32 @@
         <f>"covers/" &amp; A2 &amp; ".jpg"</f>
         <v>covers/chopin-in-paris.jpg</v>
       </c>
-      <c r="AO2" s="25" t="s">
+      <c r="AX2" s="25" t="s">
         <v>324</v>
       </c>
-      <c r="AP2" s="26" t="s">
+      <c r="AY2" s="26" t="s">
         <v>325</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AZ2" t="s">
         <v>326</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="BA2" t="s">
         <v>327</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="BB2" t="s">
         <v>328</v>
       </c>
-      <c r="AT2" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU2" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW2" t="s">
+      <c r="BC2" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD2" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF2" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -3669,20 +3887,20 @@
         <f t="shared" ref="AH3:AH66" si="0">"covers/" &amp; A3 &amp; ".jpg"</f>
         <v>covers/peasant-prince.jpg</v>
       </c>
-      <c r="AO3" s="25" t="s">
+      <c r="AX3" s="25" t="s">
         <v>329</v>
       </c>
-      <c r="AT3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU3" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW3" t="s">
+      <c r="BC3" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD3" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -3738,32 +3956,32 @@
         <f t="shared" si="0"/>
         <v>covers/izabela-the-valiant.jpg</v>
       </c>
-      <c r="AO4" s="25" t="s">
+      <c r="AX4" s="25" t="s">
         <v>330</v>
       </c>
-      <c r="AP4" s="27" t="s">
+      <c r="AY4" s="27" t="s">
         <v>331</v>
       </c>
-      <c r="AQ4" t="s">
+      <c r="AZ4" t="s">
         <v>333</v>
       </c>
-      <c r="AR4" s="17" t="s">
+      <c r="BA4" s="17" t="s">
         <v>334</v>
       </c>
-      <c r="AS4" t="s">
+      <c r="BB4" t="s">
         <v>332</v>
       </c>
-      <c r="AT4" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU4" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW4" t="s">
+      <c r="BC4" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD4" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -3803,23 +4021,23 @@
         <f t="shared" si="0"/>
         <v>covers/light-and-flame.jpg</v>
       </c>
-      <c r="AO5" s="25" t="s">
+      <c r="AX5" s="25" t="s">
         <v>335</v>
       </c>
-      <c r="AP5" s="26" t="s">
+      <c r="AY5" s="26" t="s">
         <v>336</v>
       </c>
-      <c r="AT5" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU5" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW5" t="s">
+      <c r="BC5" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD5" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -3873,20 +4091,20 @@
         <f t="shared" si="0"/>
         <v>covers/trail-of-hope.jpg</v>
       </c>
-      <c r="AO6" s="25" t="s">
+      <c r="AX6" s="25" t="s">
         <v>337</v>
       </c>
-      <c r="AT6" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU6" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW6" t="s">
+      <c r="BC6" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD6" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF6" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -3936,23 +4154,23 @@
         <f t="shared" si="0"/>
         <v>covers/303-squadron.jpg</v>
       </c>
-      <c r="AO7" s="25" t="s">
+      <c r="AX7" s="25" t="s">
         <v>338</v>
       </c>
-      <c r="AP7" s="26" t="s">
+      <c r="AY7" s="26" t="s">
         <v>339</v>
       </c>
-      <c r="AT7" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU7" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW7" t="s">
+      <c r="BC7" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD7" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF7" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -4009,20 +4227,20 @@
         <f t="shared" si="0"/>
         <v>covers/the-doll.jpg</v>
       </c>
-      <c r="AO8" s="25" t="s">
+      <c r="AX8" s="25" t="s">
         <v>341</v>
       </c>
-      <c r="AT8" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU8" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW8" t="s">
+      <c r="BC8" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD8" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF8" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -4065,20 +4283,20 @@
         <f t="shared" si="0"/>
         <v>covers/the-peasants.jpg</v>
       </c>
-      <c r="AO9" s="25" t="s">
+      <c r="AX9" s="25" t="s">
         <v>340</v>
       </c>
-      <c r="AT9" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU9" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW9" t="s">
+      <c r="BC9" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD9" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF9" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -4122,23 +4340,23 @@
         <f t="shared" si="0"/>
         <v>covers/pan-tadeusz.jpg</v>
       </c>
-      <c r="AO10" s="25" t="s">
+      <c r="AX10" s="25" t="s">
         <v>359</v>
       </c>
-      <c r="AP10" s="26" t="s">
+      <c r="AY10" s="26" t="s">
         <v>360</v>
       </c>
-      <c r="AT10" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU10" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW10" t="s">
+      <c r="BC10" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD10" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -4181,23 +4399,23 @@
         <f t="shared" si="0"/>
         <v>covers/choucas.jpg</v>
       </c>
-      <c r="AO11" s="25" t="s">
+      <c r="AX11" s="25" t="s">
         <v>361</v>
       </c>
-      <c r="AP11" s="26" t="s">
+      <c r="AY11" s="26" t="s">
         <v>362</v>
       </c>
-      <c r="AT11" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU11" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW11" t="s">
+      <c r="BC11" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD11" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>62</v>
       </c>
@@ -4253,20 +4471,20 @@
         <f t="shared" si="0"/>
         <v>covers/desert-wilderness.jpg</v>
       </c>
-      <c r="AO12" s="25" t="s">
+      <c r="AX12" s="25" t="s">
         <v>363</v>
       </c>
-      <c r="AT12" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU12" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW12" t="s">
+      <c r="BC12" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD12" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -4306,26 +4524,26 @@
         <f t="shared" si="0"/>
         <v>covers/forest-folk.jpg</v>
       </c>
-      <c r="AO13" s="25" t="s">
+      <c r="AX13" s="25" t="s">
         <v>364</v>
       </c>
-      <c r="AT13" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU13" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW13" t="s">
+      <c r="BC13" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD13" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF13" t="s">
         <v>31</v>
       </c>
-      <c r="AY13" t="s">
+      <c r="BH13" t="s">
         <v>123</v>
       </c>
-      <c r="AZ13">
+      <c r="BI13">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -4370,23 +4588,23 @@
         <f t="shared" si="0"/>
         <v>covers/castorp.jpg</v>
       </c>
-      <c r="AO14" s="25" t="s">
+      <c r="AX14" s="25" t="s">
         <v>365</v>
       </c>
-      <c r="AP14" s="26" t="s">
+      <c r="AY14" s="26" t="s">
         <v>366</v>
       </c>
-      <c r="AT14" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU14" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW14" t="s">
+      <c r="BC14" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD14" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF14" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>72</v>
       </c>
@@ -4429,23 +4647,23 @@
         <f t="shared" si="0"/>
         <v>covers/shah-of-shahs.jpg</v>
       </c>
-      <c r="AO15" s="25" t="s">
+      <c r="AX15" s="25" t="s">
         <v>367</v>
       </c>
-      <c r="AP15" s="26" t="s">
+      <c r="AY15" s="26" t="s">
         <v>369</v>
       </c>
-      <c r="AT15" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU15" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW15" t="s">
+      <c r="BC15" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD15" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF15" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>73</v>
       </c>
@@ -4488,23 +4706,23 @@
         <f t="shared" si="0"/>
         <v>covers/the-emperor.jpg</v>
       </c>
-      <c r="AO16" s="25" t="s">
+      <c r="AX16" s="25" t="s">
         <v>370</v>
       </c>
-      <c r="AP16" s="26" t="s">
+      <c r="AY16" s="26" t="s">
         <v>371</v>
       </c>
-      <c r="AT16" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU16" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW16" t="s">
+      <c r="BC16" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD16" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF16" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>126</v>
       </c>
@@ -4547,20 +4765,29 @@
         <f>"covers/" &amp; A17 &amp; ".jpg"</f>
         <v>covers/another-day-of-life.jpg</v>
       </c>
-      <c r="AO17" s="28" t="s">
+      <c r="AO17" t="s">
+        <v>653</v>
+      </c>
+      <c r="AP17" t="s">
+        <v>654</v>
+      </c>
+      <c r="AQ17" t="s">
+        <v>652</v>
+      </c>
+      <c r="AX17" s="28" t="s">
         <v>377</v>
       </c>
-      <c r="AT17" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU17" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW17" t="s">
+      <c r="BC17" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD17" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF17" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>372</v>
       </c>
@@ -4599,23 +4826,23 @@
         <f>"covers/" &amp; A18 &amp; ".jpg"</f>
         <v>covers/shadow-of-sun.jpg</v>
       </c>
-      <c r="AO18" s="25" t="s">
+      <c r="AX18" s="25" t="s">
         <v>375</v>
       </c>
-      <c r="AP18" s="26" t="s">
+      <c r="AY18" s="26" t="s">
         <v>376</v>
       </c>
-      <c r="AT18" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU18" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW18" t="s">
+      <c r="BC18" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD18" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>80</v>
       </c>
@@ -4660,20 +4887,26 @@
         <f t="shared" si="0"/>
         <v>covers/meeting-in-oea.jpg</v>
       </c>
-      <c r="AO19" s="25" t="s">
+      <c r="AX19" s="25" t="s">
         <v>378</v>
       </c>
-      <c r="AT19" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU19" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW19" t="s">
+      <c r="BC19" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD19" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF19" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="20" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BH19" t="s">
+        <v>643</v>
+      </c>
+      <c r="BI19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>125</v>
       </c>
@@ -4718,20 +4951,26 @@
         <f t="shared" si="0"/>
         <v>covers/seven-against-thebes.jpg</v>
       </c>
-      <c r="AO20" s="25" t="s">
+      <c r="AX20" s="25" t="s">
         <v>379</v>
       </c>
-      <c r="AT20" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU20" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW20" t="s">
+      <c r="BC20" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD20" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF20" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="21" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BH20" t="s">
+        <v>643</v>
+      </c>
+      <c r="BI20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>84</v>
       </c>
@@ -4776,20 +5015,26 @@
         <f t="shared" si="0"/>
         <v>covers/emperor-julian.jpg</v>
       </c>
-      <c r="AO21" s="25" t="s">
+      <c r="AX21" s="25" t="s">
         <v>380</v>
       </c>
-      <c r="AT21" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU21" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW21" t="s">
+      <c r="BC21" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD21" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF21" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="22" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BH21" t="s">
+        <v>643</v>
+      </c>
+      <c r="BI21">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>85</v>
       </c>
@@ -4834,20 +5079,26 @@
         <f t="shared" si="0"/>
         <v>covers/last-olympiad.jpg</v>
       </c>
-      <c r="AO22" s="25" t="s">
+      <c r="AX22" s="25" t="s">
         <v>381</v>
       </c>
-      <c r="AT22" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU22" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW22" t="s">
+      <c r="BC22" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD22" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF22" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="23" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BH22" t="s">
+        <v>643</v>
+      </c>
+      <c r="BI22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>88</v>
       </c>
@@ -4890,20 +5141,20 @@
         <f t="shared" si="0"/>
         <v>covers/solaris.jpg</v>
       </c>
-      <c r="AO23" s="25" t="s">
+      <c r="AX23" s="25" t="s">
         <v>382</v>
       </c>
-      <c r="AT23" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU23" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW23" t="s">
+      <c r="BC23" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD23" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF23" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>92</v>
       </c>
@@ -4946,20 +5197,20 @@
         <f t="shared" si="0"/>
         <v>covers/fiasco.jpg</v>
       </c>
-      <c r="AO24" s="25" t="s">
+      <c r="AX24" s="25" t="s">
         <v>383</v>
       </c>
-      <c r="AT24" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU24" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW24" t="s">
+      <c r="BC24" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD24" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF24" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>124</v>
       </c>
@@ -5002,20 +5253,20 @@
         <f t="shared" si="0"/>
         <v>covers/the-invincible.jpg</v>
       </c>
-      <c r="AO25" s="25" t="s">
+      <c r="AX25" s="25" t="s">
         <v>384</v>
       </c>
-      <c r="AT25" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU25" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW25" t="s">
+      <c r="BC25" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD25" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF25" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>108</v>
       </c>
@@ -5058,23 +5309,23 @@
         <f t="shared" si="0"/>
         <v>covers/chahary.jpg</v>
       </c>
-      <c r="AT26" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU26" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW26" t="s">
+      <c r="BC26" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD26" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF26" t="s">
         <v>31</v>
       </c>
-      <c r="AY26" t="s">
+      <c r="BH26" t="s">
         <v>123</v>
       </c>
-      <c r="AZ26">
+      <c r="BI26">
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>97</v>
       </c>
@@ -5133,32 +5384,32 @@
         <f t="shared" si="0"/>
         <v>covers/melicles.jpg</v>
       </c>
-      <c r="AO27" s="25" t="s">
+      <c r="AX27" s="25" t="s">
         <v>206</v>
       </c>
-      <c r="AP27" s="26" t="s">
+      <c r="AY27" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="AQ27" t="s">
+      <c r="AZ27" t="s">
         <v>185</v>
       </c>
-      <c r="AR27" t="s">
+      <c r="BA27" t="s">
         <v>210</v>
       </c>
-      <c r="AS27" t="s">
+      <c r="BB27" t="s">
         <v>211</v>
       </c>
-      <c r="AT27" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU27" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW27" t="s">
+      <c r="BC27" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD27" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF27" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>98</v>
       </c>
@@ -5203,20 +5454,20 @@
         <f t="shared" si="0"/>
         <v>covers/diossos.jpg</v>
       </c>
-      <c r="AO28" s="25" t="s">
+      <c r="AX28" s="25" t="s">
         <v>385</v>
       </c>
-      <c r="AT28" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU28" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW28" t="s">
+      <c r="BC28" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD28" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF28" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>107</v>
       </c>
@@ -5261,26 +5512,26 @@
         <f t="shared" si="0"/>
         <v>covers/white-jaguar-1.jpg</v>
       </c>
-      <c r="AO29" s="25" t="s">
+      <c r="AX29" s="25" t="s">
         <v>387</v>
       </c>
-      <c r="AT29" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU29" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW29" t="s">
+      <c r="BC29" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD29" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF29" t="s">
         <v>31</v>
       </c>
-      <c r="AY29" t="s">
+      <c r="BH29" t="s">
         <v>105</v>
       </c>
-      <c r="AZ29">
+      <c r="BI29">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>106</v>
       </c>
@@ -5325,26 +5576,26 @@
         <f t="shared" si="0"/>
         <v>covers/ships-minos-1.jpg</v>
       </c>
-      <c r="AO30" s="25" t="s">
+      <c r="AX30" s="25" t="s">
         <v>386</v>
       </c>
-      <c r="AT30" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU30" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW30" t="s">
+      <c r="BC30" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD30" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF30" t="s">
         <v>31</v>
       </c>
-      <c r="AY30" t="s">
+      <c r="BH30" t="s">
         <v>104</v>
       </c>
-      <c r="AZ30">
+      <c r="BI30">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>119</v>
       </c>
@@ -5403,26 +5654,26 @@
         <f t="shared" si="0"/>
         <v>covers/divine-julius.jpg</v>
       </c>
-      <c r="AO31" s="25" t="s">
+      <c r="AX31" s="25" t="s">
         <v>388</v>
       </c>
-      <c r="AT31" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU31" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW31" t="s">
+      <c r="BC31" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD31" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF31" t="s">
         <v>31</v>
       </c>
-      <c r="AY31" t="s">
+      <c r="BH31" t="s">
         <v>122</v>
       </c>
-      <c r="AZ31">
+      <c r="BI31">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>120</v>
       </c>
@@ -5481,26 +5732,26 @@
         <f t="shared" si="0"/>
         <v>covers/naso-the-poet.jpg</v>
       </c>
-      <c r="AO32" s="25" t="s">
+      <c r="AX32" s="25" t="s">
         <v>389</v>
       </c>
-      <c r="AT32" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU32" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW32" t="s">
+      <c r="BC32" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD32" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF32" t="s">
         <v>31</v>
       </c>
-      <c r="AY32" t="s">
+      <c r="BH32" t="s">
         <v>122</v>
       </c>
-      <c r="AZ32">
+      <c r="BI32">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>121</v>
       </c>
@@ -5549,26 +5800,26 @@
         <f t="shared" si="0"/>
         <v>covers/tiberius-caesar.jpg</v>
       </c>
-      <c r="AO33" s="25" t="s">
+      <c r="AX33" s="25" t="s">
         <v>390</v>
       </c>
-      <c r="AT33" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU33" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW33" t="s">
+      <c r="BC33" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD33" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF33" t="s">
         <v>31</v>
       </c>
-      <c r="AY33" t="s">
+      <c r="BH33" t="s">
         <v>122</v>
       </c>
-      <c r="AZ33">
+      <c r="BI33">
         <v>3</v>
       </c>
     </row>
-    <row r="34" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>153</v>
       </c>
@@ -5603,20 +5854,20 @@
         <f t="shared" si="0"/>
         <v>covers/milosz-selected-and-last-poems.jpg</v>
       </c>
-      <c r="AO34" s="25" t="s">
+      <c r="AX34" s="25" t="s">
         <v>391</v>
       </c>
-      <c r="AT34" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU34" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW34" t="s">
+      <c r="BC34" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD34" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF34" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>157</v>
       </c>
@@ -5662,20 +5913,20 @@
         <f t="shared" si="0"/>
         <v>covers/poems-new-and-szymborska.jpg</v>
       </c>
-      <c r="AO35" s="25" t="s">
+      <c r="AX35" s="25" t="s">
         <v>392</v>
       </c>
-      <c r="AT35" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU35" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW35" t="s">
+      <c r="BC35" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD35" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF35" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>158</v>
       </c>
@@ -5710,23 +5961,23 @@
         <f t="shared" si="0"/>
         <v>covers/poems-herbert.jpg</v>
       </c>
-      <c r="AO36" s="25" t="s">
+      <c r="AX36" s="25" t="s">
         <v>393</v>
       </c>
-      <c r="AP36" s="26" t="s">
+      <c r="AY36" s="26" t="s">
         <v>394</v>
       </c>
-      <c r="AT36" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU36" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW36" t="s">
+      <c r="BC36" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD36" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF36" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="37" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>148</v>
       </c>
@@ -5761,23 +6012,23 @@
         <f t="shared" si="0"/>
         <v>covers/without-end.jpg</v>
       </c>
-      <c r="AO37" s="25" t="s">
+      <c r="AX37" s="25" t="s">
         <v>396</v>
       </c>
-      <c r="AP37" s="26" t="s">
+      <c r="AY37" s="26" t="s">
         <v>397</v>
       </c>
-      <c r="AT37" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU37" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW37" t="s">
+      <c r="BC37" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD37" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF37" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>149</v>
       </c>
@@ -5827,23 +6078,23 @@
         <f t="shared" si="0"/>
         <v>covers/sobbing-superpower.jpg</v>
       </c>
-      <c r="AO38" s="25" t="s">
+      <c r="AX38" s="25" t="s">
         <v>398</v>
       </c>
-      <c r="AP38" s="26" t="s">
+      <c r="AY38" s="26" t="s">
         <v>399</v>
       </c>
-      <c r="AT38" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU38" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW38" t="s">
+      <c r="BC38" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD38" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF38" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="39" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>150</v>
       </c>
@@ -5890,23 +6141,23 @@
         <f t="shared" si="0"/>
         <v>covers/map-collected-and-last.jpg</v>
       </c>
-      <c r="AO39" s="25" t="s">
+      <c r="AX39" s="25" t="s">
         <v>400</v>
       </c>
-      <c r="AP39" s="26" t="s">
+      <c r="AY39" s="26" t="s">
         <v>401</v>
       </c>
-      <c r="AT39" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU39" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW39" t="s">
+      <c r="BC39" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD39" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF39" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>151</v>
       </c>
@@ -5956,20 +6207,20 @@
         <f t="shared" si="0"/>
         <v>covers/from-tree-of-knowledge.jpg</v>
       </c>
-      <c r="AO40" s="25" t="s">
+      <c r="AX40" s="25" t="s">
         <v>402</v>
       </c>
-      <c r="AT40" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU40" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW40" t="s">
+      <c r="BC40" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD40" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF40" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>203</v>
       </c>
@@ -6002,20 +6253,20 @@
         <f t="shared" si="0"/>
         <v>covers/krzysztof-kamil-baczynski.jpg</v>
       </c>
-      <c r="AO41" s="25" t="s">
+      <c r="AX41" s="25" t="s">
         <v>403</v>
       </c>
-      <c r="AT41" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU41" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW41" t="s">
+      <c r="BC41" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD41" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF41" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>152</v>
       </c>
@@ -6051,20 +6302,20 @@
         <f t="shared" si="0"/>
         <v>covers/white-magic-baczynski.jpg</v>
       </c>
-      <c r="AO42" s="25" t="s">
+      <c r="AX42" s="25" t="s">
         <v>404</v>
       </c>
-      <c r="AT42" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU42" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW42" t="s">
+      <c r="BC42" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD42" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF42" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>199</v>
       </c>
@@ -6114,20 +6365,20 @@
         <f t="shared" si="0"/>
         <v>covers/new-poems-ukr-po.jpg</v>
       </c>
-      <c r="AO43" s="25" t="s">
+      <c r="AX43" s="25" t="s">
         <v>202</v>
       </c>
-      <c r="AT43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU43" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW43" t="s">
+      <c r="BC43" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD43" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF43" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>191</v>
       </c>
@@ -6187,20 +6438,20 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-templars.jpg</v>
       </c>
-      <c r="AO44" s="25" t="s">
+      <c r="AX44" s="25" t="s">
         <v>196</v>
       </c>
-      <c r="AT44" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU44" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW44" t="s">
+      <c r="BC44" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD44" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF44" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>194</v>
       </c>
@@ -6260,20 +6511,20 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-mysteries.jpg</v>
       </c>
-      <c r="AO45" s="25" t="s">
+      <c r="AX45" s="25" t="s">
         <v>198</v>
       </c>
-      <c r="AT45" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU45" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW45" t="s">
+      <c r="BC45" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD45" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF45" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>193</v>
       </c>
@@ -6333,20 +6584,20 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-bandits.jpg</v>
       </c>
-      <c r="AO46" s="25" t="s">
+      <c r="AX46" s="25" t="s">
         <v>195</v>
       </c>
-      <c r="AT46" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU46" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW46" t="s">
+      <c r="BC46" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD46" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF46" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>192</v>
       </c>
@@ -6406,20 +6657,20 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-copernicus.jpg</v>
       </c>
-      <c r="AO47" s="29" t="s">
+      <c r="AX47" s="29" t="s">
         <v>197</v>
       </c>
-      <c r="AT47" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU47" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW47" t="s">
+      <c r="BC47" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD47" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF47" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>212</v>
       </c>
@@ -6466,20 +6717,20 @@
         <f t="shared" si="0"/>
         <v>covers/cold-sea.jpg</v>
       </c>
-      <c r="AO48" s="25" t="s">
+      <c r="AX48" s="25" t="s">
         <v>215</v>
       </c>
-      <c r="AT48" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU48" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW48" t="s">
+      <c r="BC48" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD48" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF48" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>217</v>
       </c>
@@ -6539,20 +6790,47 @@
         <f t="shared" si="0"/>
         <v>covers/saragossa.jpg</v>
       </c>
-      <c r="AO49" s="29" t="s">
+      <c r="AO49" t="s">
+        <v>656</v>
+      </c>
+      <c r="AP49" t="s">
+        <v>657</v>
+      </c>
+      <c r="AQ49" t="s">
+        <v>655</v>
+      </c>
+      <c r="AR49" t="s">
+        <v>663</v>
+      </c>
+      <c r="AS49" t="s">
+        <v>667</v>
+      </c>
+      <c r="AT49" t="s">
+        <v>662</v>
+      </c>
+      <c r="AU49" t="s">
+        <v>665</v>
+      </c>
+      <c r="AV49" t="s">
+        <v>666</v>
+      </c>
+      <c r="AW49" t="s">
+        <v>664</v>
+      </c>
+      <c r="AX49" s="29" t="s">
         <v>218</v>
       </c>
-      <c r="AT49" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU49" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW49" t="s">
+      <c r="BC49" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD49" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF49" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>222</v>
       </c>
@@ -6589,20 +6867,20 @@
         <f t="shared" si="0"/>
         <v>covers/birch-grove.jpg</v>
       </c>
-      <c r="AO50" s="25" t="s">
+      <c r="AX50" s="25" t="s">
         <v>225</v>
       </c>
-      <c r="AT50" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU50" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW50" t="s">
+      <c r="BC50" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD50" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF50" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>227</v>
       </c>
@@ -6640,20 +6918,20 @@
         <f t="shared" si="0"/>
         <v>covers/danton-thermidor.jpg</v>
       </c>
-      <c r="AO51" s="29" t="s">
+      <c r="AX51" s="29" t="s">
         <v>231</v>
       </c>
-      <c r="AT51" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU51" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW51" t="s">
+      <c r="BC51" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD51" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF51" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>232</v>
       </c>
@@ -6690,20 +6968,20 @@
         <f t="shared" si="0"/>
         <v>covers/coming-spring.jpg</v>
       </c>
-      <c r="AO52" s="25" t="s">
+      <c r="AX52" s="25" t="s">
         <v>234</v>
       </c>
-      <c r="AT52" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU52" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW52" t="s">
+      <c r="BC52" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD52" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF52" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>246</v>
       </c>
@@ -6748,20 +7026,20 @@
         <f t="shared" si="0"/>
         <v>covers/beniowski.jpg</v>
       </c>
-      <c r="AO53" s="25" t="s">
+      <c r="AX53" s="25" t="s">
         <v>245</v>
       </c>
-      <c r="AT53" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU53" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW53" t="s">
+      <c r="BC53" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD53" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF53" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="54" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>247</v>
       </c>
@@ -6798,20 +7076,20 @@
         <f t="shared" si="0"/>
         <v>covers/witcher-set.jpg</v>
       </c>
-      <c r="AO54" s="29" t="s">
+      <c r="AX54" s="29" t="s">
         <v>252</v>
       </c>
-      <c r="AT54" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU54" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW54" t="s">
+      <c r="BC54" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD54" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF54" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>253</v>
       </c>
@@ -6848,26 +7126,26 @@
         <f t="shared" si="0"/>
         <v>covers/tower-fools.jpg</v>
       </c>
-      <c r="AO55" s="25" t="s">
+      <c r="AX55" s="25" t="s">
         <v>256</v>
       </c>
-      <c r="AT55" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU55" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW55" t="s">
+      <c r="BC55" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD55" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF55" t="s">
         <v>31</v>
       </c>
-      <c r="AY55" t="s">
+      <c r="BH55" t="s">
         <v>257</v>
       </c>
-      <c r="AZ55">
+      <c r="BI55">
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>258</v>
       </c>
@@ -6904,26 +7182,26 @@
         <f t="shared" si="0"/>
         <v>covers/warrior-god.jpg</v>
       </c>
-      <c r="AO56" s="29" t="s">
+      <c r="AX56" s="29" t="s">
         <v>260</v>
       </c>
-      <c r="AT56" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU56" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW56" t="s">
+      <c r="BC56" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD56" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF56" t="s">
         <v>31</v>
       </c>
-      <c r="AY56" t="s">
+      <c r="BH56" t="s">
         <v>257</v>
       </c>
-      <c r="AZ56">
+      <c r="BI56">
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>261</v>
       </c>
@@ -6960,26 +7238,26 @@
         <f t="shared" si="0"/>
         <v>covers/light-perpetua.jpg</v>
       </c>
-      <c r="AO57" s="25" t="s">
+      <c r="AX57" s="25" t="s">
         <v>263</v>
       </c>
-      <c r="AT57" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU57" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW57" t="s">
+      <c r="BC57" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD57" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF57" t="s">
         <v>31</v>
       </c>
-      <c r="AY57" t="s">
+      <c r="BH57" t="s">
         <v>257</v>
       </c>
-      <c r="AZ57">
+      <c r="BI57">
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>264</v>
       </c>
@@ -7033,20 +7311,20 @@
         <f t="shared" si="0"/>
         <v>covers/red-prince.jpg</v>
       </c>
-      <c r="AO58" s="29" t="s">
+      <c r="AX58" s="29" t="s">
         <v>268</v>
       </c>
-      <c r="AT58" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU58" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW58" t="s">
+      <c r="BC58" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD58" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF58" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="59" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>270</v>
       </c>
@@ -7082,20 +7360,20 @@
         <f t="shared" si="0"/>
         <v>covers/adam-mickiewicz.jpg</v>
       </c>
-      <c r="AO59" s="29" t="s">
+      <c r="AX59" s="29" t="s">
         <v>273</v>
       </c>
-      <c r="AT59" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU59" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW59" t="s">
+      <c r="BC59" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD59" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF59" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>276</v>
       </c>
@@ -7134,20 +7412,20 @@
         <f t="shared" si="0"/>
         <v>covers/forefathers-eve.jpg</v>
       </c>
-      <c r="AO60" s="29" t="s">
+      <c r="AX60" s="29" t="s">
         <v>277</v>
       </c>
-      <c r="AT60" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU60" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW60" t="s">
+      <c r="BC60" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD60" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF60" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>281</v>
       </c>
@@ -7186,20 +7464,20 @@
         <f t="shared" si="0"/>
         <v>covers/ballads-romances.jpg</v>
       </c>
-      <c r="AO61" s="25" t="s">
+      <c r="AX61" s="25" t="s">
         <v>282</v>
       </c>
-      <c r="AT61" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU61" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW61" t="s">
+      <c r="BC61" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD61" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF61" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>283</v>
       </c>
@@ -7237,20 +7515,20 @@
         <f t="shared" si="0"/>
         <v>covers/native-realm.jpg</v>
       </c>
-      <c r="AO62" s="25" t="s">
+      <c r="AX62" s="25" t="s">
         <v>286</v>
       </c>
-      <c r="AT62" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU62" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW62" t="s">
+      <c r="BC62" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD62" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF62" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>287</v>
       </c>
@@ -7285,20 +7563,20 @@
         <f t="shared" si="0"/>
         <v>covers/history-lit-milosz.jpg</v>
       </c>
-      <c r="AO63" s="25" t="s">
+      <c r="AX63" s="25" t="s">
         <v>293</v>
       </c>
-      <c r="AT63" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU63" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW63" t="s">
+      <c r="BC63" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD63" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF63" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>291</v>
       </c>
@@ -7333,20 +7611,20 @@
         <f t="shared" si="0"/>
         <v>covers/postwar-polish-poetry.jpg</v>
       </c>
-      <c r="AO64" s="25" t="s">
+      <c r="AX64" s="25" t="s">
         <v>294</v>
       </c>
-      <c r="AT64" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU64" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW64" t="s">
+      <c r="BC64" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD64" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF64" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>295</v>
       </c>
@@ -7381,20 +7659,20 @@
         <f t="shared" si="0"/>
         <v>covers/captive-mind.jpg</v>
       </c>
-      <c r="AO65" s="25" t="s">
+      <c r="AX65" s="25" t="s">
         <v>297</v>
       </c>
-      <c r="AT65" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU65" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW65" t="s">
+      <c r="BC65" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD65" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF65" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>299</v>
       </c>
@@ -7430,20 +7708,20 @@
         <f t="shared" si="0"/>
         <v>covers/selected-masterpieces.jpg</v>
       </c>
-      <c r="AO66" s="25" t="s">
+      <c r="AX66" s="25" t="s">
         <v>301</v>
       </c>
-      <c r="AT66" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU66" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW66" t="s">
+      <c r="BC66" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD66" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF66" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>306</v>
       </c>
@@ -7489,20 +7767,20 @@
         <f>"covers/" &amp; A67 &amp; ".jpg"</f>
         <v>covers/hyenas-lotuses.jpg</v>
       </c>
-      <c r="AO67" s="25" t="s">
+      <c r="AX67" s="25" t="s">
         <v>309</v>
       </c>
-      <c r="AT67" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU67" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW67" t="s">
+      <c r="BC67" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD67" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF67" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>313</v>
       </c>
@@ -7547,38 +7825,38 @@
         <f>"covers/" &amp; A68 &amp; ".jpg"</f>
         <v>covers/widow-queen.jpg</v>
       </c>
-      <c r="AO68" s="25" t="s">
+      <c r="AX68" s="25" t="s">
         <v>310</v>
       </c>
-      <c r="AP68" s="26" t="s">
+      <c r="AY68" s="26" t="s">
         <v>315</v>
       </c>
-      <c r="AQ68" t="s">
+      <c r="AZ68" t="s">
         <v>316</v>
       </c>
-      <c r="AR68" t="s">
+      <c r="BA68" t="s">
         <v>317</v>
       </c>
-      <c r="AS68" t="s">
+      <c r="BB68" t="s">
         <v>318</v>
       </c>
-      <c r="AT68" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU68" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW68" t="s">
+      <c r="BC68" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD68" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF68" t="s">
         <v>31</v>
       </c>
-      <c r="AY68" t="s">
+      <c r="BH68" t="s">
         <v>314</v>
       </c>
-      <c r="AZ68">
+      <c r="BI68">
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>320</v>
       </c>
@@ -7627,38 +7905,38 @@
         <f>"covers/" &amp; A69 &amp; ".jpg"</f>
         <v>covers/last-crown.jpg</v>
       </c>
-      <c r="AO69" s="25" t="s">
+      <c r="AX69" s="25" t="s">
         <v>322</v>
       </c>
-      <c r="AP69" s="26" t="s">
+      <c r="AY69" s="26" t="s">
         <v>315</v>
       </c>
-      <c r="AQ69" t="s">
+      <c r="AZ69" t="s">
         <v>316</v>
       </c>
-      <c r="AR69" t="s">
+      <c r="BA69" t="s">
         <v>317</v>
       </c>
-      <c r="AS69" t="s">
+      <c r="BB69" t="s">
         <v>318</v>
       </c>
-      <c r="AT69" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU69" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW69" t="s">
+      <c r="BC69" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD69" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF69" t="s">
         <v>31</v>
       </c>
-      <c r="AY69" t="s">
+      <c r="BH69" t="s">
         <v>314</v>
       </c>
-      <c r="AZ69">
+      <c r="BI69">
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>269</v>
       </c>
@@ -7706,20 +7984,20 @@
         <f t="shared" ref="AH70" si="1">"covers/" &amp; A70 &amp; ".jpg"</f>
         <v>covers/the-homeless.jpg</v>
       </c>
-      <c r="AO70" s="25" t="s">
+      <c r="AX70" s="25" t="s">
         <v>237</v>
       </c>
-      <c r="AT70" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU70" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW70" t="s">
+      <c r="BC70" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD70" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF70" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>342</v>
       </c>
@@ -7757,23 +8035,23 @@
         <f t="shared" ref="AH71:AH98" si="2">"covers/" &amp; A71 &amp; ".jpg"</f>
         <v>covers/ferdydurke.jpg</v>
       </c>
-      <c r="AO71" s="25" t="s">
+      <c r="AX71" s="25" t="s">
         <v>345</v>
       </c>
-      <c r="AP71" s="26" t="s">
+      <c r="AY71" s="26" t="s">
         <v>347</v>
       </c>
-      <c r="AT71" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU71" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW71" t="s">
+      <c r="BC71" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD71" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF71" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>350</v>
       </c>
@@ -7811,23 +8089,23 @@
         <f t="shared" si="2"/>
         <v>covers/the-possessed.jpg</v>
       </c>
-      <c r="AO72" s="25" t="s">
+      <c r="AX72" s="25" t="s">
         <v>348</v>
       </c>
-      <c r="AP72" s="26" t="s">
+      <c r="AY72" s="26" t="s">
         <v>352</v>
       </c>
-      <c r="AT72" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU72" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW72" t="s">
+      <c r="BC72" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD72" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF72" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>354</v>
       </c>
@@ -7865,23 +8143,23 @@
         <f t="shared" si="2"/>
         <v>covers/flights.jpg</v>
       </c>
-      <c r="AO73" s="25" t="s">
+      <c r="AX73" s="25" t="s">
         <v>357</v>
       </c>
-      <c r="AP73" s="26" t="s">
+      <c r="AY73" s="26" t="s">
         <v>358</v>
       </c>
-      <c r="AT73" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU73" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW73" t="s">
+      <c r="BC73" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD73" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF73" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>405</v>
       </c>
@@ -7919,20 +8197,20 @@
         <f t="shared" si="2"/>
         <v>covers/gestures.jpg</v>
       </c>
-      <c r="AO74" s="25" t="s">
+      <c r="AX74" s="25" t="s">
         <v>409</v>
       </c>
-      <c r="AT74" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU74" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW74" t="s">
+      <c r="BC74" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD74" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF74" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="75" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>415</v>
       </c>
@@ -7970,23 +8248,23 @@
         <f t="shared" si="2"/>
         <v>covers/accommodations.jpg</v>
       </c>
-      <c r="AO75" s="25" t="s">
+      <c r="AX75" s="25" t="s">
         <v>412</v>
       </c>
-      <c r="AP75" s="26" t="s">
+      <c r="AY75" s="26" t="s">
         <v>413</v>
       </c>
-      <c r="AT75" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU75" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW75" t="s">
+      <c r="BC75" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD75" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF75" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="76" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>418</v>
       </c>
@@ -8024,23 +8302,23 @@
         <f t="shared" si="2"/>
         <v>covers/swallowing-mercury.jpg</v>
       </c>
-      <c r="AO76" s="25" t="s">
+      <c r="AX76" s="25" t="s">
         <v>421</v>
       </c>
-      <c r="AP76" s="26" t="s">
+      <c r="AY76" s="26" t="s">
         <v>420</v>
       </c>
-      <c r="AT76" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU76" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW76" t="s">
+      <c r="BC76" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD76" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF76" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="77" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>423</v>
       </c>
@@ -8075,20 +8353,20 @@
         <f t="shared" si="2"/>
         <v>covers/stone-tablets.jpg</v>
       </c>
-      <c r="AO77" s="25" t="s">
+      <c r="AX77" s="25" t="s">
         <v>425</v>
       </c>
-      <c r="AT77" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU77" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW77" t="s">
+      <c r="BC77" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD77" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF77" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="78" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>427</v>
       </c>
@@ -8136,23 +8414,23 @@
         <f t="shared" si="2"/>
         <v>covers/beautiful-mrs-seidenman.jpg</v>
       </c>
-      <c r="AO78" s="25" t="s">
+      <c r="AX78" s="25" t="s">
         <v>428</v>
       </c>
-      <c r="AP78" s="26" t="s">
+      <c r="AY78" s="26" t="s">
         <v>429</v>
       </c>
-      <c r="AT78" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU78" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW78" t="s">
+      <c r="BC78" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD78" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF78" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="79" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>434</v>
       </c>
@@ -8190,20 +8468,20 @@
         <f t="shared" si="2"/>
         <v>covers/nosegood-investigates.jpg</v>
       </c>
-      <c r="AO79" s="30" t="s">
+      <c r="AX79" s="30" t="s">
         <v>433</v>
       </c>
-      <c r="AT79" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU79" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW79" t="s">
+      <c r="BC79" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD79" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF79" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="80" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>440</v>
       </c>
@@ -8241,23 +8519,23 @@
         <f t="shared" si="2"/>
         <v>covers/feed-dictator.jpg</v>
       </c>
-      <c r="AO80" s="25" t="s">
+      <c r="AX80" s="25" t="s">
         <v>442</v>
       </c>
-      <c r="AP80" s="26" t="s">
+      <c r="AY80" s="26" t="s">
         <v>441</v>
       </c>
-      <c r="AT80" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU80" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW80" t="s">
+      <c r="BC80" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD80" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF80" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>445</v>
       </c>
@@ -8295,23 +8573,23 @@
         <f t="shared" si="2"/>
         <v>covers/city-lions.jpg</v>
       </c>
-      <c r="AO81" s="25" t="s">
+      <c r="AX81" s="25" t="s">
         <v>446</v>
       </c>
-      <c r="AP81" s="26" t="s">
+      <c r="AY81" s="26" t="s">
         <v>447</v>
       </c>
-      <c r="AT81" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU81" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW81" t="s">
+      <c r="BC81" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD81" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF81" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:52" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:61" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>450</v>
       </c>
@@ -8349,23 +8627,23 @@
         <f t="shared" si="2"/>
         <v>covers/roosters-dogs.jpg</v>
       </c>
-      <c r="AO82" s="25" t="s">
+      <c r="AX82" s="25" t="s">
         <v>454</v>
       </c>
-      <c r="AP82" s="26" t="s">
+      <c r="AY82" s="26" t="s">
         <v>455</v>
       </c>
-      <c r="AT82" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU82" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW82" t="s">
+      <c r="BC82" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD82" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF82" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="83" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>456</v>
       </c>
@@ -8403,23 +8681,23 @@
         <f t="shared" si="2"/>
         <v>covers/stained-glass.jpg</v>
       </c>
-      <c r="AO83" s="25" t="s">
+      <c r="AX83" s="25" t="s">
         <v>457</v>
       </c>
-      <c r="AP83" s="26" t="s">
+      <c r="AY83" s="26" t="s">
         <v>458</v>
       </c>
-      <c r="AT83" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU83" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW83" t="s">
+      <c r="BC83" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD83" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF83" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="84" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>463</v>
       </c>
@@ -8464,23 +8742,23 @@
         <f t="shared" si="2"/>
         <v>covers/ryszard-k-a-life.jpg</v>
       </c>
-      <c r="AO84" s="25" t="s">
+      <c r="AX84" s="25" t="s">
         <v>466</v>
       </c>
-      <c r="AP84" s="26" t="s">
+      <c r="AY84" s="26" t="s">
         <v>467</v>
       </c>
-      <c r="AT84" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU84" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW84" t="s">
+      <c r="BC84" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD84" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF84" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>468</v>
       </c>
@@ -8529,23 +8807,23 @@
         <f t="shared" si="2"/>
         <v>covers/warsaw-tales.jpg</v>
       </c>
-      <c r="AO85" s="25" t="s">
+      <c r="AX85" s="25" t="s">
         <v>470</v>
       </c>
-      <c r="AP85" s="26" t="s">
+      <c r="AY85" s="26" t="s">
         <v>471</v>
       </c>
-      <c r="AT85" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU85" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW85" t="s">
+      <c r="BC85" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD85" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF85" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="86" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>478</v>
       </c>
@@ -8583,29 +8861,29 @@
         <f t="shared" si="2"/>
         <v>covers/mohr-missing.jpg</v>
       </c>
-      <c r="AO86" s="25" t="s">
+      <c r="AX86" s="25" t="s">
         <v>482</v>
       </c>
-      <c r="AP86" s="26" t="s">
+      <c r="AY86" s="26" t="s">
         <v>483</v>
       </c>
-      <c r="AT86" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU86" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW86" t="s">
+      <c r="BC86" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD86" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF86" t="s">
         <v>31</v>
       </c>
-      <c r="AY86" t="s">
+      <c r="BH86" t="s">
         <v>630</v>
       </c>
-      <c r="AZ86">
+      <c r="BI86">
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>485</v>
       </c>
@@ -8643,23 +8921,23 @@
         <f t="shared" si="2"/>
         <v>covers/cooking-kremlin.jpg</v>
       </c>
-      <c r="AO87" s="25" t="s">
+      <c r="AX87" s="25" t="s">
         <v>488</v>
       </c>
-      <c r="AP87" s="26" t="s">
+      <c r="AY87" s="26" t="s">
         <v>487</v>
       </c>
-      <c r="AT87" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU87" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW87" t="s">
+      <c r="BC87" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD87" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF87" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>489</v>
       </c>
@@ -8697,20 +8975,20 @@
         <f t="shared" si="2"/>
         <v>covers/matt-the-first.jpg</v>
       </c>
-      <c r="AO88" s="25" t="s">
+      <c r="AX88" s="25" t="s">
         <v>492</v>
       </c>
-      <c r="AT88" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU88" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW88" t="s">
+      <c r="BC88" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD88" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF88" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="89" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>496</v>
       </c>
@@ -8747,23 +9025,23 @@
         <f t="shared" si="2"/>
         <v>covers/kaytek-wizard.jpg</v>
       </c>
-      <c r="AO89" s="25" t="s">
+      <c r="AX89" s="25" t="s">
         <v>497</v>
       </c>
-      <c r="AP89" s="26" t="s">
+      <c r="AY89" s="26" t="s">
         <v>498</v>
       </c>
-      <c r="AT89" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU89" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW89" t="s">
+      <c r="BC89" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD89" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF89" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>506</v>
       </c>
@@ -8801,23 +9079,23 @@
         <f t="shared" si="2"/>
         <v>covers/miron-memoir.jpg</v>
       </c>
-      <c r="AO90" s="25" t="s">
+      <c r="AX90" s="25" t="s">
         <v>504</v>
       </c>
-      <c r="AP90" s="26" t="s">
+      <c r="AY90" s="26" t="s">
         <v>503</v>
       </c>
-      <c r="AT90" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU90" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW90" t="s">
+      <c r="BC90" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD90" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF90" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="91" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>508</v>
       </c>
@@ -8852,23 +9130,23 @@
         <f t="shared" si="2"/>
         <v>covers/inhuman-land.jpg</v>
       </c>
-      <c r="AO91" s="25" t="s">
+      <c r="AX91" s="25" t="s">
         <v>511</v>
       </c>
-      <c r="AP91" s="26" t="s">
+      <c r="AY91" s="26" t="s">
         <v>510</v>
       </c>
-      <c r="AT91" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU91" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW91" t="s">
+      <c r="BC91" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD91" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF91" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="92" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>473</v>
       </c>
@@ -8907,23 +9185,23 @@
         <f t="shared" si="2"/>
         <v>covers/mud-sweeter.jpg</v>
       </c>
-      <c r="AO92" s="28" t="s">
+      <c r="AX92" s="28" t="s">
         <v>477</v>
       </c>
-      <c r="AP92" s="26" t="s">
+      <c r="AY92" s="26" t="s">
         <v>476</v>
       </c>
-      <c r="AT92" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU92" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW92" t="s">
+      <c r="BC92" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD92" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF92" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="93" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>513</v>
       </c>
@@ -8962,23 +9240,23 @@
         <f t="shared" si="2"/>
         <v>covers/house-of-day.jpg</v>
       </c>
-      <c r="AO93" s="25" t="s">
+      <c r="AX93" s="25" t="s">
         <v>515</v>
       </c>
-      <c r="AP93" s="26" t="s">
+      <c r="AY93" s="26" t="s">
         <v>514</v>
       </c>
-      <c r="AT93" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU93" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW93" t="s">
+      <c r="BC93" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD93" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF93" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="94" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>516</v>
       </c>
@@ -9017,23 +9295,23 @@
         <f t="shared" si="2"/>
         <v>covers/garden-memory.jpg</v>
       </c>
-      <c r="AO94" s="25" t="s">
+      <c r="AX94" s="25" t="s">
         <v>519</v>
       </c>
-      <c r="AP94" s="26" t="s">
+      <c r="AY94" s="26" t="s">
         <v>520</v>
       </c>
-      <c r="AT94" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU94" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW94" t="s">
+      <c r="BC94" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD94" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF94" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="95" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>523</v>
       </c>
@@ -9074,23 +9352,23 @@
       <c r="AI95">
         <v>2014</v>
       </c>
-      <c r="AO95" s="25" t="s">
+      <c r="AX95" s="25" t="s">
         <v>527</v>
       </c>
-      <c r="AP95" s="26" t="s">
+      <c r="AY95" s="26" t="s">
         <v>528</v>
       </c>
-      <c r="AT95" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU95" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW95" t="s">
+      <c r="BC95" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD95" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF95" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="96" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>529</v>
       </c>
@@ -9142,23 +9420,23 @@
       <c r="AI96">
         <v>2014</v>
       </c>
-      <c r="AO96" s="25" t="s">
+      <c r="AX96" s="25" t="s">
         <v>532</v>
       </c>
-      <c r="AP96" s="26" t="s">
+      <c r="AY96" s="26" t="s">
         <v>531</v>
       </c>
-      <c r="AT96" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU96" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW96" t="s">
+      <c r="BC96" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD96" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF96" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="97" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>538</v>
       </c>
@@ -9207,23 +9485,23 @@
         <f t="shared" si="2"/>
         <v>covers/beautiful-twentysomethings.jpg</v>
       </c>
-      <c r="AO97" s="25" t="s">
+      <c r="AX97" s="25" t="s">
         <v>537</v>
       </c>
-      <c r="AP97" s="26" t="s">
+      <c r="AY97" s="26" t="s">
         <v>536</v>
       </c>
-      <c r="AT97" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU97" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW97" t="s">
+      <c r="BC97" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD97" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF97" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="98" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>539</v>
       </c>
@@ -9269,23 +9547,23 @@
         <f t="shared" si="2"/>
         <v>covers/laras-wars.jpg</v>
       </c>
-      <c r="AO98" s="25" t="s">
+      <c r="AX98" s="25" t="s">
         <v>544</v>
       </c>
-      <c r="AP98" s="26" t="s">
+      <c r="AY98" s="26" t="s">
         <v>543</v>
       </c>
-      <c r="AT98" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU98" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW98" t="s">
+      <c r="BC98" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD98" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF98" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="99" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>549</v>
       </c>
@@ -9331,26 +9609,26 @@
         <v>9781644213766</v>
       </c>
       <c r="AH99" t="str">
-        <f t="shared" ref="AH99:AH117" si="5">"covers/" &amp; A99 &amp; ".jpg"</f>
+        <f t="shared" ref="AH99:AH121" si="5">"covers/" &amp; A99 &amp; ".jpg"</f>
         <v>covers/little-beauty.jpg</v>
       </c>
-      <c r="AO99" s="25" t="s">
+      <c r="AX99" s="25" t="s">
         <v>548</v>
       </c>
-      <c r="AP99" s="26" t="s">
+      <c r="AY99" s="26" t="s">
         <v>547</v>
       </c>
-      <c r="AT99" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU99" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW99" t="s">
+      <c r="BC99" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD99" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF99" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="100" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>554</v>
       </c>
@@ -9399,23 +9677,23 @@
         <f t="shared" si="5"/>
         <v>covers/lectures-proust.jpg</v>
       </c>
-      <c r="AO100" s="25" t="s">
+      <c r="AX100" s="25" t="s">
         <v>552</v>
       </c>
-      <c r="AP100" s="26" t="s">
+      <c r="AY100" s="26" t="s">
         <v>553</v>
       </c>
-      <c r="AT100" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU100" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW100" t="s">
+      <c r="BC100" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD100" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF100" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="101" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>557</v>
       </c>
@@ -9464,23 +9742,23 @@
         <f t="shared" si="5"/>
         <v>covers/Starobielsk-essays.jpg</v>
       </c>
-      <c r="AO101" s="25" t="s">
+      <c r="AX101" s="25" t="s">
         <v>559</v>
       </c>
-      <c r="AP101" s="26" t="s">
+      <c r="AY101" s="26" t="s">
         <v>558</v>
       </c>
-      <c r="AT101" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU101" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW101" t="s">
+      <c r="BC101" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD101" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF101" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="102" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>563</v>
       </c>
@@ -9541,23 +9819,23 @@
         <f t="shared" si="5"/>
         <v>covers/jedwabne-crime.jpg</v>
       </c>
-      <c r="AO102" s="25" t="s">
+      <c r="AX102" s="25" t="s">
         <v>560</v>
       </c>
-      <c r="AP102" s="26" t="s">
+      <c r="AY102" s="26" t="s">
         <v>561</v>
       </c>
-      <c r="AT102" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU102" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW102" t="s">
+      <c r="BC102" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD102" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF102" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="103" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>571</v>
       </c>
@@ -9606,23 +9884,23 @@
         <f t="shared" si="5"/>
         <v>covers/ginczanka-firebird.jpg</v>
       </c>
-      <c r="AO103" s="25" t="s">
+      <c r="AX103" s="25" t="s">
         <v>570</v>
       </c>
-      <c r="AP103" s="26" t="s">
+      <c r="AY103" s="26" t="s">
         <v>569</v>
       </c>
-      <c r="AT103" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU103" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW103" t="s">
+      <c r="BC103" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD103" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF103" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="104" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>574</v>
       </c>
@@ -9671,23 +9949,23 @@
         <f t="shared" si="5"/>
         <v>covers/life-grows.jpg</v>
       </c>
-      <c r="AO104" s="25" t="s">
+      <c r="AX104" s="25" t="s">
         <v>575</v>
       </c>
-      <c r="AP104" s="26" t="s">
+      <c r="AY104" s="26" t="s">
         <v>576</v>
       </c>
-      <c r="AT104" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU104" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW104" t="s">
+      <c r="BC104" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD104" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF104" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="105" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>577</v>
       </c>
@@ -9735,20 +10013,20 @@
         <f t="shared" si="5"/>
         <v>covers/voracious.jpg</v>
       </c>
-      <c r="AO105" s="25" t="s">
+      <c r="AX105" s="25" t="s">
         <v>578</v>
       </c>
-      <c r="AT105" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU105" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW105" t="s">
+      <c r="BC105" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD105" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF105" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="106" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>582</v>
       </c>
@@ -9797,23 +10075,23 @@
         <f t="shared" si="5"/>
         <v>covers/lala.jpg</v>
       </c>
-      <c r="AO106" s="25" t="s">
+      <c r="AX106" s="25" t="s">
         <v>587</v>
       </c>
-      <c r="AP106" s="26" t="s">
+      <c r="AY106" s="26" t="s">
         <v>585</v>
       </c>
-      <c r="AT106" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU106" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW106" t="s">
+      <c r="BC106" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD106" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF106" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="107" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>588</v>
       </c>
@@ -9862,23 +10140,23 @@
         <f t="shared" si="5"/>
         <v>covers/dancing-bears.jpg</v>
       </c>
-      <c r="AO107" s="25" t="s">
+      <c r="AX107" s="25" t="s">
         <v>592</v>
       </c>
-      <c r="AP107" s="26" t="s">
+      <c r="AY107" s="26" t="s">
         <v>591</v>
       </c>
-      <c r="AT107" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU107" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW107" t="s">
+      <c r="BC107" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD107" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF107" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="108" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>595</v>
       </c>
@@ -9927,23 +10205,29 @@
         <f t="shared" si="5"/>
         <v>covers/rage.jpg</v>
       </c>
-      <c r="AO108" s="25" t="s">
+      <c r="AX108" s="25" t="s">
         <v>597</v>
       </c>
-      <c r="AP108" s="26" t="s">
+      <c r="AY108" s="26" t="s">
         <v>598</v>
       </c>
-      <c r="AT108" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU108" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW108" t="s">
+      <c r="BC108" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD108" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF108" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="109" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BH108" t="s">
+        <v>602</v>
+      </c>
+      <c r="BI108">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>599</v>
       </c>
@@ -9978,29 +10262,29 @@
         <f t="shared" si="5"/>
         <v>covers/grain-truth.jpg</v>
       </c>
-      <c r="AO109" s="25" t="s">
+      <c r="AX109" s="25" t="s">
         <v>603</v>
       </c>
-      <c r="AP109" s="26" t="s">
+      <c r="AY109" s="26" t="s">
         <v>604</v>
       </c>
-      <c r="AT109" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU109" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW109" t="s">
+      <c r="BC109" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD109" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF109" t="s">
         <v>31</v>
       </c>
-      <c r="AY109" t="s">
+      <c r="BH109" t="s">
         <v>602</v>
       </c>
-      <c r="AZ109">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="110" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="BI109">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>606</v>
       </c>
@@ -10060,26 +10344,23 @@
         <f t="shared" si="5"/>
         <v>covers/over-the-bones.jpg</v>
       </c>
-      <c r="AO110" s="25" t="s">
+      <c r="AX110" s="25" t="s">
         <v>608</v>
       </c>
-      <c r="AT110" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU110" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW110" t="s">
+      <c r="AY110" s="26" t="s">
+        <v>648</v>
+      </c>
+      <c r="BC110" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD110" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF110" t="s">
         <v>31</v>
       </c>
-      <c r="AY110" t="s">
-        <v>602</v>
-      </c>
-      <c r="AZ110">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="111" spans="1:52" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>609</v>
       </c>
@@ -10140,23 +10421,23 @@
         <f t="shared" si="5"/>
         <v>covers/jacobs-books.jpg</v>
       </c>
-      <c r="AO111" s="25" t="s">
+      <c r="AX111" s="25" t="s">
         <v>611</v>
       </c>
-      <c r="AP111" s="26" t="s">
+      <c r="AY111" s="26" t="s">
         <v>612</v>
       </c>
-      <c r="AT111" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU111" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW111" t="s">
+      <c r="BC111" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD111" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF111" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="112" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>613</v>
       </c>
@@ -10217,23 +10498,23 @@
         <f t="shared" si="5"/>
         <v>covers/empusium.jpg</v>
       </c>
-      <c r="AO112" s="25" t="s">
+      <c r="AX112" s="25" t="s">
         <v>615</v>
       </c>
-      <c r="AP112" s="26" t="s">
+      <c r="AY112" s="26" t="s">
         <v>616</v>
       </c>
-      <c r="AT112" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU112" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW112" t="s">
+      <c r="BC112" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD112" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF112" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="113" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>618</v>
       </c>
@@ -10282,20 +10563,20 @@
         <f t="shared" si="5"/>
         <v>covers/mr-distinctive.jpg</v>
       </c>
-      <c r="AO113" s="25" t="s">
+      <c r="AX113" s="25" t="s">
         <v>619</v>
       </c>
-      <c r="AT113" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU113" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW113" t="s">
+      <c r="BC113" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD113" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF113" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="114" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>620</v>
       </c>
@@ -10344,23 +10625,23 @@
         <f t="shared" si="5"/>
         <v>covers/lost-soul.jpg</v>
       </c>
-      <c r="AO114" s="25" t="s">
+      <c r="AX114" s="25" t="s">
         <v>622</v>
       </c>
-      <c r="AP114" s="26" t="s">
+      <c r="AY114" s="26" t="s">
         <v>621</v>
       </c>
-      <c r="AT114" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU114" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW114" t="s">
+      <c r="BC114" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD114" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF114" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="115" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>626</v>
       </c>
@@ -10406,26 +10687,26 @@
         <f t="shared" si="5"/>
         <v>covers/torn-curtain.jpg</v>
       </c>
-      <c r="AO115" s="25" t="s">
+      <c r="AX115" s="25" t="s">
         <v>628</v>
       </c>
-      <c r="AT115" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU115" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW115" t="s">
+      <c r="BC115" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD115" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF115" t="s">
         <v>31</v>
       </c>
-      <c r="AY115" t="s">
+      <c r="BH115" t="s">
         <v>630</v>
       </c>
-      <c r="AZ115">
+      <c r="BI115">
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:52" ht="255" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>631</v>
       </c>
@@ -10475,20 +10756,20 @@
         <f t="shared" si="5"/>
         <v>covers/on-niemen.jpg</v>
       </c>
-      <c r="AO116" s="31" t="s">
+      <c r="AX116" s="25" t="s">
         <v>636</v>
       </c>
-      <c r="AT116" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU116" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW116" t="s">
+      <c r="BC116" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD116" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF116" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="117" spans="1:52" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>638</v>
       </c>
@@ -10503,6 +10784,9 @@
       </c>
       <c r="E117" t="s">
         <v>633</v>
+      </c>
+      <c r="F117" s="1" t="s">
+        <v>642</v>
       </c>
       <c r="G117" s="6" t="s">
         <v>112</v>
@@ -10535,85 +10819,305 @@
         <f t="shared" si="5"/>
         <v>covers/marta.jpg</v>
       </c>
-      <c r="AO117" s="31" t="s">
+      <c r="AX117" s="25" t="s">
         <v>641</v>
       </c>
-      <c r="AP117" s="32" t="s">
+      <c r="AY117" s="26" t="s">
         <v>637</v>
       </c>
-      <c r="AT117" t="s">
-        <v>23</v>
-      </c>
-      <c r="AU117" t="s">
-        <v>23</v>
-      </c>
-      <c r="AW117" t="s">
+      <c r="BC117" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD117" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF117" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="118" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>672</v>
+      </c>
+      <c r="B118" t="s">
+        <v>302</v>
+      </c>
+      <c r="C118">
+        <v>1600</v>
+      </c>
+      <c r="D118" s="15" t="s">
+        <v>644</v>
+      </c>
+      <c r="E118" t="s">
+        <v>673</v>
+      </c>
       <c r="G118" s="6"/>
       <c r="P118" s="2"/>
       <c r="Q118" s="7"/>
-      <c r="Y118" s="4"/>
-      <c r="Z118" s="4"/>
-    </row>
-    <row r="119" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="Y118" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z118" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="AA118" s="5">
+        <v>17</v>
+      </c>
+      <c r="AG118" s="8" t="s">
+        <v>645</v>
+      </c>
+      <c r="AH118" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/dedalus-fantasy.jpg</v>
+      </c>
+      <c r="AX118" s="25" t="s">
+        <v>670</v>
+      </c>
+      <c r="BC118" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD118" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF118" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="119" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>677</v>
+      </c>
+      <c r="B119" t="s">
+        <v>302</v>
+      </c>
+      <c r="C119">
+        <v>1610</v>
+      </c>
+      <c r="D119" s="15" t="s">
+        <v>676</v>
+      </c>
+      <c r="E119" t="s">
+        <v>675</v>
+      </c>
+      <c r="F119" t="s">
+        <v>674</v>
+      </c>
       <c r="G119" s="6"/>
-      <c r="P119" s="2"/>
-      <c r="Q119" s="7"/>
-      <c r="Y119" s="4"/>
-      <c r="Z119" s="4"/>
-    </row>
-    <row r="120" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="P119" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q119" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="R119" s="3">
+        <v>13.1</v>
+      </c>
+      <c r="X119" s="21">
+        <v>9781909232044</v>
+      </c>
+      <c r="Y119" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z119" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="AA119" s="5">
+        <v>8.0500000000000007</v>
+      </c>
+      <c r="AG119" s="8">
+        <v>9781907650666</v>
+      </c>
+      <c r="AH119" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/dark-domain.jpg</v>
+      </c>
+      <c r="AX119" s="30" t="s">
+        <v>678</v>
+      </c>
+      <c r="AY119" s="27" t="s">
+        <v>679</v>
+      </c>
+      <c r="BC119" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD119" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF119" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="120" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>685</v>
+      </c>
+      <c r="D120" s="15" t="s">
+        <v>646</v>
+      </c>
+      <c r="E120" t="s">
+        <v>684</v>
+      </c>
       <c r="G120" s="6"/>
+      <c r="P120" s="2"/>
       <c r="Q120" s="7"/>
-      <c r="Y120" s="4"/>
-      <c r="Z120" s="4"/>
-    </row>
-    <row r="121" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="Y120" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z120" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="AA120" s="5">
+        <v>61.99</v>
+      </c>
+      <c r="AG120" s="8">
+        <v>9781134425419</v>
+      </c>
+      <c r="AH120" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/mannequins-ball.jpg</v>
+      </c>
+      <c r="AX120" s="31" t="s">
+        <v>686</v>
+      </c>
+      <c r="BC120" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD120" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF120" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="121" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>687</v>
+      </c>
+      <c r="B121" t="s">
+        <v>74</v>
+      </c>
+      <c r="C121">
+        <v>1320</v>
+      </c>
+      <c r="D121" s="15" t="s">
+        <v>647</v>
+      </c>
+      <c r="E121" t="s">
+        <v>689</v>
+      </c>
+      <c r="F121" t="s">
+        <v>690</v>
+      </c>
       <c r="G121" s="6"/>
-      <c r="Q121" s="7"/>
+      <c r="P121" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q121" s="7" t="s">
+        <v>691</v>
+      </c>
+      <c r="R121" s="3">
+        <v>24.95</v>
+      </c>
+      <c r="X121" s="21">
+        <v>9781586424480</v>
+      </c>
       <c r="Y121" s="4"/>
       <c r="Z121" s="4"/>
-    </row>
-    <row r="122" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="AH121" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/conversations-executioner.jpg</v>
+      </c>
+      <c r="AX121" s="25" t="s">
+        <v>688</v>
+      </c>
+      <c r="AY121" s="26" t="s">
+        <v>692</v>
+      </c>
+      <c r="BC121" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD121" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF121" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="122" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>683</v>
+      </c>
+      <c r="C122">
+        <v>1620</v>
+      </c>
+      <c r="D122" s="15" t="s">
+        <v>680</v>
+      </c>
+      <c r="E122" t="s">
+        <v>201</v>
+      </c>
+      <c r="F122" t="s">
+        <v>94</v>
+      </c>
       <c r="G122" s="6"/>
-      <c r="Q122" s="7"/>
+      <c r="P122" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q122" s="7" t="s">
+        <v>682</v>
+      </c>
+      <c r="T122" s="3">
+        <v>10</v>
+      </c>
+      <c r="X122" s="21">
+        <v>9780940962705</v>
+      </c>
       <c r="Y122" s="4"/>
       <c r="Z122" s="4"/>
-    </row>
-    <row r="123" spans="1:52" x14ac:dyDescent="0.25">
+      <c r="AX122" s="25" t="s">
+        <v>681</v>
+      </c>
+      <c r="BC122" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD122" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF122" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="123" spans="1:61" x14ac:dyDescent="0.25">
       <c r="G123" s="6"/>
       <c r="Q123" s="7"/>
       <c r="Y123" s="4"/>
       <c r="Z123" s="4"/>
     </row>
-    <row r="124" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:61" x14ac:dyDescent="0.25">
       <c r="G124" s="6"/>
       <c r="Q124" s="7"/>
       <c r="Y124" s="4"/>
       <c r="Z124" s="4"/>
     </row>
-    <row r="125" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:61" x14ac:dyDescent="0.25">
       <c r="G125" s="6"/>
       <c r="Q125" s="7"/>
       <c r="Y125" s="4"/>
       <c r="Z125" s="4"/>
     </row>
-    <row r="126" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:61" x14ac:dyDescent="0.25">
       <c r="G126" s="6"/>
       <c r="Q126" s="7"/>
       <c r="Y126" s="4"/>
       <c r="Z126" s="4"/>
     </row>
-    <row r="127" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:61" x14ac:dyDescent="0.25">
       <c r="G127" s="6"/>
       <c r="Q127" s="7"/>
       <c r="Y127" s="4"/>
       <c r="Z127" s="4"/>
     </row>
-    <row r="128" spans="1:52" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:61" x14ac:dyDescent="0.25">
       <c r="G128" s="6"/>
       <c r="Q128" s="7"/>
       <c r="Y128" s="4"/>
@@ -10772,6 +11276,7 @@
     <row r="154" spans="7:26" x14ac:dyDescent="0.25">
       <c r="G154" s="6"/>
       <c r="Q154" s="7"/>
+      <c r="Y154" s="4"/>
       <c r="Z154" s="4"/>
     </row>
     <row r="155" spans="7:26" x14ac:dyDescent="0.25">
@@ -10804,37 +11309,42 @@
       <c r="Q160" s="7"/>
       <c r="Z160" s="4"/>
     </row>
-    <row r="161" spans="17:26" x14ac:dyDescent="0.25">
+    <row r="161" spans="7:26" x14ac:dyDescent="0.25">
+      <c r="G161" s="6"/>
       <c r="Q161" s="7"/>
       <c r="Z161" s="4"/>
     </row>
-    <row r="162" spans="17:26" x14ac:dyDescent="0.25">
+    <row r="162" spans="7:26" x14ac:dyDescent="0.25">
       <c r="Q162" s="7"/>
       <c r="Z162" s="4"/>
     </row>
-    <row r="163" spans="17:26" x14ac:dyDescent="0.25">
+    <row r="163" spans="7:26" x14ac:dyDescent="0.25">
       <c r="Q163" s="7"/>
       <c r="Z163" s="4"/>
     </row>
-    <row r="164" spans="17:26" x14ac:dyDescent="0.25">
+    <row r="164" spans="7:26" x14ac:dyDescent="0.25">
       <c r="Q164" s="7"/>
       <c r="Z164" s="4"/>
     </row>
-    <row r="165" spans="17:26" x14ac:dyDescent="0.25">
+    <row r="165" spans="7:26" x14ac:dyDescent="0.25">
       <c r="Q165" s="7"/>
       <c r="Z165" s="4"/>
     </row>
-    <row r="166" spans="17:26" x14ac:dyDescent="0.25">
+    <row r="166" spans="7:26" x14ac:dyDescent="0.25">
       <c r="Q166" s="7"/>
       <c r="Z166" s="4"/>
+    </row>
+    <row r="167" spans="7:26" x14ac:dyDescent="0.25">
+      <c r="Q167" s="7"/>
+      <c r="Z167" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G50:G57 Z167:Z1048576 O45 AG45 X45 G48 Q167:Q1048576 P120:P1048576 Y154:Y1048576 G161:H1048576" xr:uid="{D2C177B6-092A-4420-B1E2-D1681CD512E9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G50:G57 Z168:Z1048576 O45 AG45 X45 G48 Q168:Q1048576 G162:H1048576 Y155:Y1048576 P123:P1048576" xr:uid="{D2C177B6-092A-4420-B1E2-D1681CD512E9}">
       <formula1>"hardcover, paperback, eBook, audiobook1"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AT1:AU1048576" xr:uid="{F1FB7CD6-B38A-4A39-862C-8A1111411C8C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC1:BD1048576" xr:uid="{F1FB7CD6-B38A-4A39-862C-8A1111411C8C}">
       <formula1>"yes, no"</formula1>
     </dataValidation>
   </dataValidations>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/the-polish-atheneum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1950" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8548D08B-ACBC-468E-A918-208869E1934F}"/>
+  <xr:revisionPtr revIDLastSave="1953" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58382AB3-A809-43D6-BD37-D119A0DCAC78}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
@@ -16,7 +16,6 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1541" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="694">
   <si>
     <t>cover</t>
   </si>
@@ -2974,6 +2973,15 @@
 —Charlie English, author of The CIA Book Club
 "An intriguing document that portrays Stroop as the exemplary perpetrator: a mediocrity promoted above his abilities, but fanatical in his allegiance to Hitler, Himmler and Nazi ideology. Moczarski, working from memory, brings to light the workings of the Nazi mind with penetrating insight."
 —Dan Stone, author of The Holocaust: An Unfinished History</t>
+  </si>
+  <si>
+    <t>Another Day of Life (1976) by Ryszard Kapuściński has received immense critical praise, widely regarded as a classic of modern war reportage and a masterpiece of 20th-century journalism. It is praised for transcending traditional reporting to become a profound, personal, and poetic work of literature. 
+Key themes of critical acclaim include:
+Elevating Reportage to Literature: Critics emphasize that the book is not merely a collection of facts, but a "surrealistic diary" and a "hallucinatory trip" that reads like a thriller while capturing the profound fear, loneliness, and confusion of covering a civil war.
+Immersion and "Literature by Foot": Kapuściński is lauded for staying in Luanda while other foreign correspondents left, providing a vivid, intimate look at the collapse of colonial Angola. His method of "personal reportage" is celebrated for its commitment to witnessing events firsthand.
+Humanitarian Focus over Political Bias: Unlike conventional war reporting, the book is praised for its lack of contempt or cynical detachment. Instead, it focuses on the "humanity" of the individuals caught in the conflict—the soldiers, refugees, and civilians.
+Poetic and Evocative Prose: The work is described as a "poetic and eloquent" account that uses "metaphorically rich narrative" to convey the chaos and terror of war.
+A Personal Chronicle: Kapuściński regarded this as one of his most personal works, focusing on the sheer uncertainty of survival—waking up and realizing you have survived "another day of life".</t>
   </si>
 </sst>
 </file>
@@ -3150,7 +3158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3192,7 +3200,6 @@
     <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4777,6 +4784,9 @@
       <c r="AX17" s="28" t="s">
         <v>377</v>
       </c>
+      <c r="AY17" s="26" t="s">
+        <v>693</v>
+      </c>
       <c r="BC17" t="s">
         <v>23</v>
       </c>
@@ -10976,7 +10986,7 @@
         <f t="shared" si="5"/>
         <v>covers/mannequins-ball.jpg</v>
       </c>
-      <c r="AX120" s="31" t="s">
+      <c r="AX120" s="26" t="s">
         <v>686</v>
       </c>
       <c r="BC120" t="s">

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/the-polish-atheneum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1953" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58382AB3-A809-43D6-BD37-D119A0DCAC78}"/>
+  <xr:revisionPtr revIDLastSave="1976" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E6B505A-E4D1-404C-8B52-CC3422237E5D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
+    <workbookView xWindow="1830" yWindow="660" windowWidth="23220" windowHeight="14940" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1542" uniqueCount="694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="711">
   <si>
     <t>cover</t>
   </si>
@@ -2982,6 +2982,57 @@
 Humanitarian Focus over Political Bias: Unlike conventional war reporting, the book is praised for its lack of contempt or cynical detachment. Instead, it focuses on the "humanity" of the individuals caught in the conflict—the soldiers, refugees, and civilians.
 Poetic and Evocative Prose: The work is described as a "poetic and eloquent" account that uses "metaphorically rich narrative" to convey the chaos and terror of war.
 A Personal Chronicle: Kapuściński regarded this as one of his most personal works, focusing on the sheer uncertainty of survival—waking up and realizing you have survived "another day of life".</t>
+  </si>
+  <si>
+    <t>Translating Pan Tadeusz: A Conversation with Bill Johnston</t>
+  </si>
+  <si>
+    <t>YsBN1gaX-8g</t>
+  </si>
+  <si>
+    <t>Bill Johnston, professor of comparative literature, Indiana University, discusses translating Pan Tadeusz.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winner of the Grand Jury and FIPRESCI prizes at the 1972 Cannes Film Festival and based on the novel by Stanisław Lem, SOLARIS is a cerebral, emotive space odyssey about memory, grief and love. When cosmonaut/psychologist Kris Kelvin (Donatas Banionis) is sent to investigate the mysterious death of a doctor onboard a space station orbiting the planet Solaris, he initially believes the remaining crew to have lost their minds. Then, he begins to experience strange apparitions of his own, encountering his seven-years-dead wife (Natalya Bondarchuk) and gradually losing sight of the line between reality and the darkest recesses of his inner psyche. DIR/SCR Andrei Tarkovsky; SCR Fridrikh Gorenshtein, from the novel by Stanisław Lem; PROD Vyacheslav Tarasov. USSR, 1972, color, 167 min. In Russian with English subtitles. </t>
+  </si>
+  <si>
+    <t>SOLARIS (1972) Trailer | Lem 2021: I've Seen the Future</t>
+  </si>
+  <si>
+    <t>wT8Y7DGQn7M</t>
+  </si>
+  <si>
+    <t>SOLARIS (2002) - Official Movie Trailer</t>
+  </si>
+  <si>
+    <t>rvm7WMbXfeY</t>
+  </si>
+  <si>
+    <t>The Defective God | Solaris</t>
+  </si>
+  <si>
+    <t>niIZVU-0fZg</t>
+  </si>
+  <si>
+    <t>Solaris by Stanisław Lem is a 1961 Polish philosophical science fiction novel that explores the limits of human understanding through the story of a psychologist sent to a space station orbiting the mysterious planet covered by a sentient ocean called Solaris.</t>
+  </si>
+  <si>
+    <t>THE PEASANTS | Official Trailer (2024)</t>
+  </si>
+  <si>
+    <t>-1in2FMBKmo</t>
+  </si>
+  <si>
+    <t>THE PEASANTS Trailer | TIFF 2023</t>
+  </si>
+  <si>
+    <t>O8nME5pUHPo</t>
+  </si>
+  <si>
+    <t>THE PEASANTS | Extended Preview</t>
+  </si>
+  <si>
+    <t>Jh10LL50i_s</t>
   </si>
 </sst>
 </file>
@@ -3194,12 +3245,12 @@
     <xf numFmtId="1" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4290,6 +4341,24 @@
         <f t="shared" si="0"/>
         <v>covers/the-peasants.jpg</v>
       </c>
+      <c r="AO9" t="s">
+        <v>705</v>
+      </c>
+      <c r="AQ9" s="17" t="s">
+        <v>706</v>
+      </c>
+      <c r="AR9" t="s">
+        <v>707</v>
+      </c>
+      <c r="AT9" t="s">
+        <v>708</v>
+      </c>
+      <c r="AU9" t="s">
+        <v>709</v>
+      </c>
+      <c r="AW9" t="s">
+        <v>710</v>
+      </c>
       <c r="AX9" s="25" t="s">
         <v>340</v>
       </c>
@@ -4346,6 +4415,15 @@
       <c r="AH10" t="str">
         <f t="shared" si="0"/>
         <v>covers/pan-tadeusz.jpg</v>
+      </c>
+      <c r="AO10" t="s">
+        <v>694</v>
+      </c>
+      <c r="AP10" t="s">
+        <v>696</v>
+      </c>
+      <c r="AQ10" t="s">
+        <v>695</v>
       </c>
       <c r="AX10" s="25" t="s">
         <v>359</v>
@@ -5150,6 +5228,30 @@
       <c r="AH23" t="str">
         <f t="shared" si="0"/>
         <v>covers/solaris.jpg</v>
+      </c>
+      <c r="AO23" t="s">
+        <v>698</v>
+      </c>
+      <c r="AP23" t="s">
+        <v>697</v>
+      </c>
+      <c r="AQ23" t="s">
+        <v>699</v>
+      </c>
+      <c r="AR23" t="s">
+        <v>700</v>
+      </c>
+      <c r="AT23" t="s">
+        <v>701</v>
+      </c>
+      <c r="AU23" t="s">
+        <v>702</v>
+      </c>
+      <c r="AV23" t="s">
+        <v>704</v>
+      </c>
+      <c r="AW23" t="s">
+        <v>703</v>
       </c>
       <c r="AX23" s="25" t="s">
         <v>382</v>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/the-polish-atheneum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1976" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E6B505A-E4D1-404C-8B52-CC3422237E5D}"/>
+  <xr:revisionPtr revIDLastSave="2456" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6291917E-3CDA-4510-9F64-56AC5D94AA7D}"/>
   <bookViews>
-    <workbookView xWindow="1830" yWindow="660" windowWidth="23220" windowHeight="14940" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1559" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1875" uniqueCount="853">
   <si>
     <t>cover</t>
   </si>
@@ -3033,6 +3033,537 @@
   </si>
   <si>
     <t>Jh10LL50i_s</t>
+  </si>
+  <si>
+    <t>Another Day of Life Official Trailer</t>
+  </si>
+  <si>
+    <t>A2WVFaVSZ3A</t>
+  </si>
+  <si>
+    <t>"Another Day of Life" - trailer</t>
+  </si>
+  <si>
+    <t>H0ujMbACCS0</t>
+  </si>
+  <si>
+    <t>nfY_wtIyWuU</t>
+  </si>
+  <si>
+    <t>Mother Joan of the Angels (Modern Trailer)</t>
+  </si>
+  <si>
+    <t>MOTHER JOAN OF THE ANGELS is better than The Devils | reaction &amp; commentary</t>
+  </si>
+  <si>
+    <t>P-bxhbHsGVQ</t>
+  </si>
+  <si>
+    <t>Mother Joanna of the Angels, one of the stories in this collection, was the basis for a highly acclaimed film.</t>
+  </si>
+  <si>
+    <t>Mother Joan of the Angels is a 1961 demonic possession film by Jerzy Kawalerowicz. 
+Based on the Loudun possessions (later made famous by Ken Russell's The Devils), the film takes place after the burning of Father Grandier and the fallout with the convent of possessed nuns. Father Józef Suryn (Mieczyslaw Voit) is sent after many failed exorcisms, and comes head to head with Mother Joan (Lucyna Winnicka), who is simultaneously afflicted by and ecstatic in her possession. He delves deeper and deeper into the darkness to try to determine what the demon is, and how he may stop it. 
+Kawalerowicz was a seminal director to emerge in Polish cinema: he helmed the Polish Film School, and founded the KADR production company, lending to the production of films by himself, Andrej Wajda, Tadeusz Konwicki, and Andrej Munk, among others. He made films amidst the political turmoil of communist Poland, and aspects of that resistance to orthodoxy and control can be seen in this film.</t>
+  </si>
+  <si>
+    <t>mass-arras</t>
+  </si>
+  <si>
+    <t>A Mass for Arras</t>
+  </si>
+  <si>
+    <t>"In the spring of 1458, the town of Arras was visited by the disasters of plague and hunger. In the course of a month, nearly a fifth of the citizens lost their lives.
+"For reasons that remain unclear, the famous Vauderie d'Arras took place in October of 1461. Jews and witches were subjected to cruel persecution; there were trials for supposed heresies, as well as an outbreak of looting and crime. It was three weeks before calm returned...."
+With this historical tragedy at its core, A Mass for Arras explores the personal and political consequences of fear, fanaticism, and fascism in the story of Jan, a young member of the intelligentsia. Arrogantly pious and full of revolutionary zeal, Jan wholeheartedly participates in the torments inflicted on the "outsiders" in the name of moral and political righteousness. Yet when faced with escalating violence and, ultimately, his own downfall, he must choose between sincere commitment to the isolated village that adopted him and horror at a society gone mad.
+A Mass for Arras addresses themes of freedom and responsibility, individualism and conformity, and memory and loss. It is a moving account of a young man's coming-of-age in a time of disease and death, a profound political allegory of life in an emergent totalitarian state, a chilling indictment of government-sponsored repression and societal complicity, and a cautionary tale about the tendency of history to repeat itself, whether in fifteenth-century France, postwar Poland, or somewhere still closer to our own time and place.
+"Gripping and persuasive.... About the forces now raging in the former Yugoslavia and Soviet Union, Mr. Szczypiorski seems to have shown uncanny prescience."--The New York Times Book Review
+"Haunting, direct, and technically masterful."--New York Newsday
+"The novel's philosophical sophistication and historical verisimilitude makes it far greater than mere allegory."--Boston Sunday Globe
+"[Szczypiorski's] breadth of experience, and of suffering, is distilled into this remarkable book which, although it is allegorical in form and brimming with abstract ideas, pulsates with a very human vitality."--Sunday Telegraph (London)
+"A thought-provoking meditation on the human tendency to find meaning in suffering by blaming others and to pervert ideals to base means.... Simply, elegantly, and yet with great power, Szczypiorski lays out the dangers of a worldview clearly reminiscent of Eastern Europe before the fall of communism."--Library Journal
+"[Szczypiorski's] resonant story is a timely meditation on crimes committed in the name of religion and on the misplaced faith the ruled place in their rulers. The translation preserves the pungent medieval atmosphere, evoking a mindset that, the author implies, is very much alive today."--Publishers Weekly
+"A fascinating and well-written parable about the horrors of totalitarianism and the combination of hysteria and indifference that allow it to metastasize."--Booklist
+Andrzej Szczypiorski was born in Warsaw in 1924, where he lived at the time of his death in May 2000. He fought in the Resistance Movement during the German Occupation of Poland, took part in the Warsaw uprising of 1944, and survived time in a concentration camp. Under the postwar regime, he published many novels, plays, and essays in the underground press, joined the opposition movement, was interned during the government crackdown, and helped found the Solidarity Congress of Polish culture. He was the author of The Beautiful Mrs. Seidenman and the recipient of the PEN Club award for A Mass for Arras, which has been published to great international acclaim.
+Richard Lourie is the translator of Andrei Sakharov's Memoirs and Czeslaw Milosz's Visions from San Francisco Bay. His own works include the novels The Autobiography of Joseph Stalin, First Loyalty, Zero Gravity and the true-crime account of a Russian serial killer, Hunting the Devil. He has also written for The New York Times, The Washington Post, The New Republic, and The Nation.</t>
+  </si>
+  <si>
+    <t>At the core of this novel is the true fifteenth-century tragedy of, first, plague and hunger and, later, the brutal persecution of Jews and witches in the small French town of Arras. A Mass for Arras explores the personal and political consequences of fear, fanaticism, and fascism in the story of Jan, a young member of the intelligentsia. Arrogantly pious and full of revolutionary zeal, Jan wholeheartedly participates in the torments inflicted on the "outsiders" in the name of moral and political righteousness. Yet when faced with escalating violence and, ultimately, his own downfall, he must choose between sincere commitment to the isolated village that adopted him and horror at a society gone mad. A Mass for Arras addresses themes of freedom and responsibility, individualism and conformity, and memory and loss. It is a moving account of a young man's coming-of-age in a time of disease and death, a profound political allegory of life in an emergent totalitarian state, a chilling indictment of government-sponsored repression and societal complicity, and a cautionary tale about the tendency of history to repeat itself, whether in fifteenth-century France, postwar Poland, or somewhere still closer to our own time and place.</t>
+  </si>
+  <si>
+    <t>salt-earth</t>
+  </si>
+  <si>
+    <t>The Salt of the Earth</t>
+  </si>
+  <si>
+    <t>Pushkin Prress</t>
+  </si>
+  <si>
+    <t>One of the small number of contemporary works which extend into the sphere of the mythical and epical. --Thomas Mann</t>
+  </si>
+  <si>
+    <t>The classic pacifist novel by a major Polish writer, who was nominated for the Nobel Prize
+At the beginning of the twentieth century the villagers of the Carpathian mountains lead a simple life, much as they have always done. The modern world has yet to reach the inhabitants of this remote region of the Habsburg Empire. Among them is Piotr, a bandy-legged peasant, who wants nothing more from life than an official railway cap, a cottage, and a bride with a dowry.
+But then the First World War reaches the mountains and Piotr is drafted into the army. All the weight of imperial authority is used to mould him into an unthinking fighting machine, forced to fight a war he does not understand, for interests other than his own.
+The Salt of the Earth is a classic war novel and a powerfully pacifist tale about the consequences of war for ordinary men.
+Józef Wittlin was born in 1896 and served in the Austro-Hungarian army during the First World War. His experiences inspired him to write The Salt of the Earth. Published in 1935 to great success, it received the Polish National Academy Prize, won Wittlin a nomination for the Nobel Prize, and has since been translated into 14 languages. Wittlin was also a translator and a poet, penning numerous essays including 'My Lwów', included in City of Lions, also published by Pushkin Press. With the outbreak of the Second World War he fled to France and then to New York, where he died in 1976.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Daniel Gerould </t>
+  </si>
+  <si>
+    <t>7-plays</t>
+  </si>
+  <si>
+    <t>Witkiewicz: Seven Plays</t>
+  </si>
+  <si>
+    <t>Martin E. Segal Theatre Center Publ.</t>
+  </si>
+  <si>
+    <t>One of Poland’s most important artists and writers of the 20th Century, this collection includes: The Pragmatists, Tumor Brainiowicz, Gyubal Wahazar, The Anonymous Work, The Cuttlefish, Dainty Shapes and Hairy Apes, and The Beelzebub Sonata. Also included is “A Few Words about the Role of the Actor in the Theatre of Pure Form,” a key section of his major theoretical treatise.</t>
+  </si>
+  <si>
+    <t>Overflowing with hyper-vivid characters and precipitous actions, these dramas constitute Witkiewicz's "portrait of the artist," offering a panorama of a demented era headed for disaster as well as a cracked mirror reflecting the author's own protean faces. Lucille Lortel Distinguished Professor of Theatre and Comparative Literature at the Graduate Center, City University of New York; Executive Director, Martin E. Segal Theatre Center; editor, Slavic and East European Performance; editor, Routledge Harwood Polish and East European Theatre Archive; author of Witkacy, Guillotine: Its Legend and Lore, Theatre/Theory/Theatre, and translations of Polish and Russian drama.</t>
+  </si>
+  <si>
+    <t>self-woman</t>
+  </si>
+  <si>
+    <t>Self-Portrait with Woman</t>
+  </si>
+  <si>
+    <t>Kamil, a Warsaw sociologist, is summoned to Geneva to participate in an oral history project about the collapse of Eastern European communism and resolves to tell his own story through a gallery of portraits of the many women he has loved. These reminiscences emerge against the broader canvas of circumstances and events that have shaped the past sixty years of Poland’s turbulent, tragic history. Soon he finds himself inexorably drawn to his interrogator from the “free” world; the chronicler of his life, the keeper of his secrets, and his heart’s last hope for redemptive love. Self-Portrait with Woman is at once a haunting and lyrical portrait of a man, of a country, and of the twilight years of an era.</t>
+  </si>
+  <si>
+    <t>From Library Journal
+Some authors present life under Communism as an end in itself. A few rare authors use this traumatic experience as a vehicle to explore broader human themes. In this novel, it is romantic love. Kamil is invited to Switzerland to participate in a project that seeks to document the experiences of ordinary people living, first, under Communism and, later, with its collapse. The protagonist tells his story by recounting some of the women he has loved, and although a bit about the state is revealed, mostly the novel explores his innermost feelings toward love and his vulnerability in romantic encounters?emotions not often revealed by men. Szczypiorski shows terrific flashes of wit, melancholy, and insight into the human and political conditions he recalls. His ability to build characters and establish a dialog with himself is outstanding; it is not exaggerating to rank him alongside Ivan Klima and Milan Kundera as a major East European writer. A necessary purchase for all solid fiction collections; libraries that did not purchase his Mass for Arras (LJ 6/1/93) and The Beautiful Mrs. Seidenman (LJ 11/15/89) may want to buy them now.?Olivia Opello, Onondaga Cty. P.L., Syracuse, N.Y.
+Copyright 1995 Reed Business Information, Inc.
+From Booklist
+Kamil, an aging Polish intellectual, is summoned to Geneva, Switzerland, to take part in an oral history project that seeks to record ordinary Eastern Europeans' experiences of historical interest--concentration camps, war, postwar hopes and disillusionment, resistance, and the mixed blessings of liberation--in order to document the collapse of Communism in Eastern Europe. Met by his guide and interviewer, Kamil immediately embarks on a new relationship with this wealthy, attractive Swiss matron taping his recollections. He soon finds that his life can be explored only in terms of his relationships with women over his lifetime. Kamil ruminates on the complex realities of men and women, indifference and involvement, powerlessness and freedom, love and hate, tenderness and cruelty, life and death, relentless guilt and the eternal hope of redemption. Szczypiorski (whose Beautiful Mrs. Seidenman, 1990, first brought him to the attention of readers of English) turns one individual's history into a powerful portrait of recent--and timeless--human dilemmas. Mary Carroll</t>
+  </si>
+  <si>
+    <t>The Conspiracy of Feelings and The Little Theatre of the Green Goose</t>
+  </si>
+  <si>
+    <t>green-goose</t>
+  </si>
+  <si>
+    <t>Two outstanding examples of socialist-themed plays are combined in this remarkable volume.
+The Conspiracy of Feelings by Yurii Olesha (1899-1960) is based on his highly respected short novel Envy about the struggle between the old and new in Soviet society. The play, called The Conspiracy of Feelings, is not a simple adaptation, but an original work that reconceived the novel. The play explores the precarious position of the intelligentsia in the new collective state.
+The Little Theatre of The Green Goose was written by Konstanty Ildefons Galczynski (1905-53) who was one of Poland's most beloved poets. After World War II, he began work as a playwright, inventing a colorful theatre troupe of performers (animal and human) and contributing a new instalment of The Little Theatre of the Green Goose each week to Przekroj, the Cracow literary magazine. Intended for reading only, The Green Goose went unperformed in Galczynski's life and was finally staged in 1955 and gained a permanent place in the theatre and became a force for the creation of the new Polish drama that flourished in the 1960s.</t>
+  </si>
+  <si>
+    <t>Drama</t>
+  </si>
+  <si>
+    <t>The Mrozek Reader</t>
+  </si>
+  <si>
+    <t>Sławomir Mrożek</t>
+  </si>
+  <si>
+    <t>mrozek-reader</t>
+  </si>
+  <si>
+    <t>Sławomir Mrożek has reigned as the pre-eminent playwright and satirist of Eastern Europe for the past half-century. A sharp critic of all oppressive systems during the Cold War, he began his career as a young enthusiast for the new Communist regime in the early 1950s. It didn’t take long, however, until he was deemed such a threat that his work was banned not only in his native Poland, but also in all Eastern bloc countries. After the fall of Communism, he returned home from self imposed exile in the West and was recognized as a major literary figure. This reissue of fourteen plays and ten short stories, along with a sampling of his capricious cartoons, affirms Mrożek’s mastery of a wide spectrum of styles, and illustrates the development of his talent over the decades. From the vantage point of the twenty-first century, Mrożek’s questioning of authority, his razor-sharp sense of the comic, and his spirit of contradiction seem as fresh, and as relevant, as ever.</t>
+  </si>
+  <si>
+    <t>The Witkiewicz Reader</t>
+  </si>
+  <si>
+    <t>Stanisław Ignacy Witkiewicz</t>
+  </si>
+  <si>
+    <t>Forgotten during the Stalin years, Stanislaw Witkiewicz (1885-1939) was rediscovered in his native Poland only after the liberalization of 1956, when his works came to play a major role in freeing the arts from socialist realism. This collection, the first anthology in English, presents Witkiewicz in the full range of his creative and intellectual activities. The Witkiewicz Reader includes excerpts from three novels; four complete plays; letters to Malinowski; and selections from aesthetic, social, and philosophical essays detailing Witkiewicz's theory of Pure Form, his metaphysical system, and his apocalyptic view of the fate of civilization.</t>
+  </si>
+  <si>
+    <t>witkacy-reader</t>
+  </si>
+  <si>
+    <t>Postal Indiscretions: The Correspondence of Tadeusz Borowski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alicia Nitecki </t>
+  </si>
+  <si>
+    <t>Tadeusz Borowski</t>
+  </si>
+  <si>
+    <t>borowski-letters</t>
+  </si>
+  <si>
+    <t>In a brief life deeply and traumatically disrupted by two years in concentration camps as a political prisoner, Tadeusz Borowski (1922–1951) was tragically destined to become one of the most eloquent witnesses to the Holocaust in Poland. His recollections and stories, the most famous of which is This Way for the Gas, Ladies and Gentlemen, document in stark historical, literary, and personal terms the experience of the camps and its cost to humanity.  ​
+This correspondence in this volume expands on the insights of Borowski’s published work and extends to the less-documented aftermath of the Holocaust in postwar Poland and East Germany. The volume opens with Borowski’s letter to his mother from Pawiak Prison the day after his arrest and closes with an unsigned telegram informing his parents of his suicide. The letters to and from family members, friends, and literary figures offer an indispensable picture of the world in the wake of the Nazis—and of the indelible stain that experience left upon the literature, politics, and life of Eastern Europe, in particular upon one gifted and doomed writer.</t>
+  </si>
+  <si>
+    <t>Ashes and Diamonds</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Jerzy Andrzejewski</t>
+  </si>
+  <si>
+    <t>Originally published in Poland in 1948, and acclaimed as one of the finest postwar Polish novels, Ashes and Diamonds takes place in the spring of 1945, as the nation is in the throes of its transformation to People' Poland. Communists, socialists, and nationalists; thieves and black marketeers; servants and fading aristocrats; veteran terrorists and bands of murderous children bewitched by the lure of crime and adventure—all of these converge on a provincial town's chief hotel, a microcosm of an uprooted world.</t>
+  </si>
+  <si>
+    <t>ashes-diamonds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Holy Week: A Novel of the Warsaw Ghetto Uprising </t>
+  </si>
+  <si>
+    <t>holy-week</t>
+  </si>
+  <si>
+    <t>J. D. Welsh</t>
+  </si>
+  <si>
+    <t>Review
+“The understated quality of this nominally realistic yet strangely allegorical short novel contributes to Holy Week’s mesmerizing power.”
+― Magill Book Reviews
+“A tight, dramatic novel.... If its immediacy proved off-putting to contemporary readers, today that urgency is its greatest strength.”
+― Nextbook
+“There is among people no greater or more absolutedividing line than between the happiness of some and the suffering of others. Affairs great and smalldivide people, yet none so sharply as the inequalityof fate.”
+― from Holy Week
+“With the first English edition of Holy Week― a tightly wound story that can be devoured in one long sitting ― we can at last discover a little-known work from one of Poland's leading 20th century novelists.... Holy Week― ably translated by a team of (University of Pittsburgh) students under the guidance of Oscar Swan ― has an immediacy and verisimilitude impossible for someone not on the scene.”
+― Los Angeles Times Book Review
+“Creates in one slim volume a vivid world peopled by believable and sympathetic characters whose lives depict with gripping accuracy an entire historical era.... Urgently recommended to all readers with an interest in world history.”
+― Library Journal, starred review
+“Andrzejewski here turns an unsparing eye on the ways in which professed Christians dealt with―or failed to address―the annihilation of their Jewish compatriots.... The world Andrzejewski conjures here may be relentlessly grim, but his tale is, as always, compelling.”
+― BookForum, Dec/Jan 2007
+“The relentless conflicts between and within these characters transform what appears to be a simple issue of national neglect into a hauntingly real drama of agonizing personal decisions and personal failures.”
+― Virginia Quarterly Review</t>
+  </si>
+  <si>
+    <t>At the height of the Nazi extermination campaign in the Warsaw Ghetto, a young Jewish woman, Irena, seeks the protection of her former lover, a young architect, Jan Malecki. By taking her in, he puts his own life and the safety of his family at risk. Over a four-day period, Tuesday through Friday of Holy Week 1943, as Irena becomes increasingly traumatized by her situation, Malecki questions his decision to shelter Irena in the apartment where Malecki, his pregnant wife, and his younger brother reside. Added to his dilemma is the broader context of Poles’ attitudes toward the “Jewish question” and the plight of the Jews locked in the ghetto during the final moments of its existence.
+Few fictional works dealing with the war have been written so close in time to the events that inspired them. No other Polish novel treats the range of Polish attitudes toward the Jews with such unflinching honesty.</t>
+  </si>
+  <si>
+    <t>The Madman and the Nun and The Crazy Locomotive: Three Plays (including The Water Hen)</t>
+  </si>
+  <si>
+    <t>witkacy-3-plays</t>
+  </si>
+  <si>
+    <t>Applause</t>
+  </si>
+  <si>
+    <t>Startling discontinuities and surprises erupt throughout these avant-garde landscapes by Poland's outstanding modern dramatist where duchesses and policemen, gangsters and surrealist painters, psychiatrists and locomotive engineers wander in and out, kill one another, and carry on philosophical conversations at the same time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here in Our Auschwitz and Other Stories </t>
+  </si>
+  <si>
+    <t>here-in-our</t>
+  </si>
+  <si>
+    <t>Jerzy Andrzejewski</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Madeline G. Levine </t>
+  </si>
+  <si>
+    <t>The most complete English-language collection of the prose of Tadeusz Borowski, the most challenging chronicler of Auschwitz, with a foreword by Timothy Snyder, author of On Tyranny
+In 1943, the twenty-year-old Polish poet Tadeusz Borowski was arrested and deported to Auschwitz as a political prisoner. What he experienced in the camp left him convinced that no one who survived Auschwitz was innocent.
+All were complicit; the camp regime depended on this. Borowski’s tales present the horrors of the camp as reflections of basic human nature and impulse, stripped of the artificial boundaries of culture and custom. Inside the camp, the strongest of the prisoners form uneasy alliances with their captors and one another, watching unflinchingly as the weak scrabble and struggle against their inevitable fate. In the last analysis, suffering is never ennobling and goodness is tantamount to suicide.
+Bringing together for the first time in English Borowski’s major writings and many previously uncollected works, this is the most complete collection of stories in a new, authoritative translation, with a substantial foreword by Timothy Snyder that speaks to its enduring relevance.</t>
+  </si>
+  <si>
+    <t>Borowski's sharp-edged descriptions of life in Nazi concentration camps shatter the limits of even Kafka's most surreal imaginings...conducting a conversation with darkness...in an icy style that cloaks hot rage.
+-- "Wall Street Journal"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To Begin Where I Am: Selected Essays </t>
+  </si>
+  <si>
+    <t>Madeline Levine</t>
+  </si>
+  <si>
+    <t>A comprehensive selection of essays--some never before translated into English--by the Nobel Laureate.
+To Begin Where I Am brings together a rich sampling of poet Czeslaw Milosz's prose writings. Spanning more than a half century, from an impassioned essay on human nature, wartime atrocities, and their challenge to ethical beliefs, written in 1942 in the form of a letter to his friend Jerzy Andrzejewski, to brief biographical sketches and poetic prose pieces from the late 1990s, this volume presents Milosz the prose writer in all his multiple, beguiling guises. The incisive, sardonic analyst of the seductive power of communism is also the author of tender, elegiac portraits of friends famous and obscure; the witty commentator on Polish complexes writes lyrically of the California landscape. Two great themes predominate in these essays, several of which have never appeared before in English: Milosz's personal struggle to sustain his religious faith, and his unswerving allegiance to a poetry that is "on the side of man."</t>
+  </si>
+  <si>
+    <t>“To Begin Where I Am stands as the most complete one-volume edition of Milosz's prose writings available in English by "arguably the greatest living poet.” ―Edward Hirsch, The New York Times Book Review
+“Milosz's vigorous and sinewy prose is that of a man of a particular historical moment...The reader will find, in both the expository essays and the incomparable portraits of his contemporaries, Milosz's characteristic intensity, momentum, and savage intelligence.” ―Helen Vendler, Harper's Magazine
+“Extraordinary...These 400 or so pages document the development, over seven decades, of a great mind.” ―The Economist
+“Beguiling...[Milosz] displays his genius for wedding palpable, personal loss to larger themes...[To Begin Where I Am] grants privileged access to a singular literary mind.” ―Carlin Romano, The Philadelphia Inquirer
+“[This collection] could not have come at a better time...A remarkable body of work...Enlightening.” ―Cynthia L. Haven, San Francisco Chronicle Book Review</t>
+  </si>
+  <si>
+    <t>to-begin-where</t>
+  </si>
+  <si>
+    <t>melchior-w</t>
+  </si>
+  <si>
+    <t>Melchior Wankowicz: Poland’s Master of the Written Word</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aleksandra Ziólkowska-Boehm </t>
+  </si>
+  <si>
+    <t>Lexington Books</t>
+  </si>
+  <si>
+    <t>“The book contains sources, eyewitnesses, interviews, and conversations Melchior Wankowicz had with his wife, friends and co-authors. . . She edited Melchior Wankowicz's selected works, providing extensive notes at the end of each chapter, in addition to the bibliography. His fascinating life will be of great interest to all writers.” ―Polish American Journal
+“Chapter 2, "The Trial of Melchior Wankowicz -- 1964," is the most important and fascinating section of the book.... This book is a tribute to Wankowicz, the writer.” ―The Polish Review
+“Dr. Aleksandra Ziolkowska-Boehm has written an excellent book on her master and guru, Melchior Wankowicz (1892–1974). Generally recognized as an unsurpassed master of literary journalism, he had set high standards for that type of writing, distinguishing himself with his 3 volume study "Monte Cassino" (1945), dealing with a major victory of Polish troops in WW II. Serving as Wankowicz's associate for two plus years, she has become an expert on her subject, and aptly demonstrated how much she has learned from her master. The book, written with her elegant style, sparkled with anecdotes and humor, may very well serve as a perfect example of a modern Polish contribution to American literary studies.” ―Jerzy Krzyzanowski, Ohio State University
+“I found this book fascinating and delightful. Ziolkowska-Boehm recorded with freshness and directness her memories of one of Poland's greatest writers. This is clearly a great book.” ―Karl Maramorosch, Rutgers University
+“An intimate portrait of Wankowicz, the writer, public figure, family man, and one-time prisoner of the Communist regime. Important documents accompany the narrative.” ―Piotr Wandycz, Yale University
+“Wankowicz combined first class literary writing with outstanding reportage. He was a free spirit, going against the tide of émigré opinion by returning to then communist Poland for good in 1958. But he also protested publicly, with other writers, against communist repression of Polish culture in March 1964, after which he was briefly imprisoned and put on trial on rigged charges. Aleksandra Ziolkowska-Boehm, a prolific author herself, and Wankowicz’s secretary in the last years of his life, has written a fine, documented account of this extraordinary individual and his writings.” ―Anna M. Cienciala, University of Kansas
+“A wonderful sketch of the tension between the writer and the Party.” ―Bruce Johansen, University of Nebraska Omaha
+“Melchior Wankowicz: Poland’s Master of the Written Word . . . . is a captivating although somehow eclectic portrait of a great humanist with a pragmatic approach to life, a prolific hard working writer, bon vivant, thinker, husband, father and most of all a fabulous reporter and storyteller. ... Melchior Wankowicz: Poland’s Master of the Written Word comes at a good time. . . . I am convinced that thanks to Aleksandra Ziolkowska-Boehm latest book, Melchior Wankowicz will always have plenty of readers.” ―Cosmopolitan</t>
+  </si>
+  <si>
+    <t>In Melchior Wankowicz: Poland’s Master of the Written Word, Aleksandra Ziolkowska-Boehm examines the life and writing of famous Polish writer Melchior Wankowicz, author of legendary work “The Battle of Monte Cassino”.
+Acclaimed by his readers and critics alike, Melchior Wankowicz was famous for creating his theory of reportage, i.e. the “mosaic method” where the events of many people were implanted into the life of one person. Melchior Wankowicz put into words the beautiful, tragic and heroic events of Polish history that provided a form of sustenance for a people that thrive on patriotism and love of their country. Wankowicz’s books shaped national consciousness, glorified the heroism of the Polish soldier. Later in his life, Wankowicz personally set an example by standing up to the Communist party that brought him to trail for his work.
+In this book, Ziolkowska-Boehm offers a critical examination of Wankowicz’s work informed by her experiences as his private secretary. Her access to the author’s personal archives shed new light on the life and work of the man considered by many to be “the father of Polish reportage.”</t>
+  </si>
+  <si>
+    <t>Melchior Wankowicz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Battle of Monte Cassino </t>
+  </si>
+  <si>
+    <t>monte-cassino</t>
+  </si>
+  <si>
+    <t>“Melchior Wankowicz (1892-1974) was Poland’s greatest twentieth-century writer of factual narratives, who created an original model of literary reportage that later inspired outstanding Polish reporters such as Ryszard Kapuscinski and Hanna Krall. He traveled throughout Poland, Mexico, the Soviet Union, Palestine and the United States and wrote about the Bolshevik Revolution, interwar Poland and World War II. He also had an extraordinary life: he was a politician, journalist, publisher, soldier, emigrant, and, at the end of his life, an enemy of the authorities of the People’s Republic of Poland. The Battle of Monte Cassino (1945-47) is a monumental work concerning one of the largest and bloodiest battles of World War II. In May 1944, the Allies defeated the German army with the significant participation of Polish soldiers. Wankowicz speaks of this battle in a colorful and realistic way, emphasizing the modern nature of the struggle on the slopes of the Italian redoubt. He polemicizes against the Romantic view of war, underscoring the role of ordinary soldiers, each of whom has a separate biography and character. An integral element of the reportage are photos, maps and drawings, quotes from military reports and orders, as well as numerous conversations with participants in the battle. There are few such suggestive and moving accounts of war in world literature.” ―Maciej Urbanowski, Jagiellonian University
+“On May 20, 1944, Joseph Goebbels wrote in his diary: “The capture of Cassino is, of course, a great event for the enemy. It is deeply embarrassing for us that, together with the English, Poles also entered the ruined city.” Meanwhile, what was a shame for Goebbels was a source of glory for the Poles. To this day, the capture of Monte Cassino, which opened the route to Rome for the Allies, is a source of national pride. One of the central streets in Warsaw is named after General Wladyslaw Anders, the Polish commander. How did the Poles arrive at Monte Cassino? The path began with their defeat in the struggle in September 1939 against the invading Germans, invading Poland from the West, and the Soviets ― initially Hitler’s allies ― who occupied of the eastern lands of pre-war Poland. Then, following Hitler’s attack on the USSR, Stalin agreed to create a Polish army from among the Poles who had been exiled deep into his country, to send them out of his way. For he already had other plans for Poland, and did not need these soldiers either then or in the future. Following a long journey, they reached the Italian front, where General Anders undertook the attack on Monte Cassino, which was already underway. He knew that many soldiers would die. However, he hoped that any success they achieved would improve Poland’s chances in the eyes of the Allies ― despite their need to cooperate with Stalin in the fight against Hitler. The Poles won the victory at Monte Cassino, but little more. Those who died were buried in the cemetery in Cassino, and General Anders, who died in 1970 in London, was buried among them, according to his wishes. The victory did not tip the Allied political scales in Poland’s favor, and the country became a satellite of the USSR. During the Communist years, the story of this battle was hushed up. It was only after the fall of Communism in Poland in 1989 that a monument to the battle was erected in Warsaw, carved from Italian marble, the work of Gustaw Zemla and Wojciech Zablocki, 1999). A popular song was about the battle (“Czerwone maki na Monte Cassino” [The Red Poppies on Monte Cassino]), was composed by Alfred Schütz, to words by Feliks Konarski). This book, The Battle of Monte Cassino (1945-1947, published in Poland only in 1958) is the best-known work of reporter and war correspondent Melchior Wankowicz ― who was with the soldiers at that time.” ―Marcin Kula, University of Warsaw
+“In the private libraries of many Poles, The Battle of Monte Cassino is still a unique item. It is often venerated with an respect approaching that accorded to Pan Tadeusz, the national epic by poet Adam Mickiewicz ― treated like a true relic. From the very start, readers clearly understood that Melchior Wankowicz had created not only a wonderful battle reportage, but also an act of faith in a free Poland and free Poles. Throughout the difficult years of Communist rule, this great book, in praise of the armed deeds of Polish soldiers, gave their countrymen a reason for national pride, awakening that perhaps most beautiful, but also the most difficult love ― love of the homeland.” ―Krzysztof Maslon, author of The Curse of Contradiction
+“I belong to the generation that not only read, but also listened to and watched, Melchior Wankowicz on radio and television. Among his numerous public statements, the one that remains both in my heart and my memory was the moving story of the Battle of Monte Cassino, with its painful drama that inspired the collective imagination ― otherwise, perhaps, dominated by the image of the “Red Poppies on Monte Cassino,” that song which inevitably idealizes reality. Thanks to Wankowicz's account, we come to understand the soldier’s hardship, sweat, pain, and fear - in short, all the cruel truth of war. Thanks to its store of strategic and military details, the readers of Melchior Wankowicz’s most famous book, widely recognized as a work written with extraordinary skill, are able to explore it in depth. If a new generation of great war reporters have developed and matured in contemporary Poland, I am sure that its representatives look with gratitude upon their Master Wankowicz, gladly admitting 'we all come from him.'” ―Jan Miodek, University of Wroclaw</t>
+  </si>
+  <si>
+    <t>Melchior Wankowicz’s The Battle of Monte Cassino is a unique contribution to the history of World War II, indeed the history of war in general. Composed by the Polish master of reportage, this book provides the reader with an exhaustive history of one of the greatest triumphs of Polish arms: the conquest of the German redoubt of Monte Cassino, after months of intense fighting, which provided the Allies with an open road for their progress through the Italian peninsula and, finally, to victory over the Nazis in Europe. The history of the Battle of Monte Cassino (17 January ― 19 May 1944), centered on the Benedictine cloister of the same name, which was a key sector of the Nazi Army’s ‘Gustav Line’ of defense. Besides the history of the long Allied siege and the eventual victory won through the efforts of General Anders’ II Polish Corps, Wankowicz provides an on-the-spot account of the battle, at which he was present, setting the reader in the very midst of operations by his thorough and lively interviews with the soldiers who took part in it.</t>
+  </si>
+  <si>
+    <t>schulz-hijack</t>
+  </si>
+  <si>
+    <t>Bruno Schulz: An Artist, a Murder, and the Hijacking of History</t>
+  </si>
+  <si>
+    <t>Benjamin Balint</t>
+  </si>
+  <si>
+    <t>W. W. Norton and Company</t>
+  </si>
+  <si>
+    <t>Winner of the 73rd National Jewish Book Award for Biography
+A New York Times Book Review Editors' Choice
+A fresh portrait of the Polish-Jewish writer and artist, and a gripping account of the secret operation to rescue his last artworks.
+The twentieth-century artist Bruno Schulz was born an Austrian, lived as a Pole, and died a Jew. First a citizen of the Habsburg monarchy, he would, without moving, become the subject of the West Ukrainian People’s Republic, the Second Polish Republic, the USSR, and, finally, the Third Reich.
+Yet to use his own metaphor, Schulz remained throughout a citizen of the Republic of Dreams. He was a master of twentieth-century imaginative fiction who mapped the anxious perplexities of his time; Isaac Bashevis Singer called him “one of the most remarkable writers who ever lived.” Schulz was also a talented illustrator and graphic artist whose masochistic drawings would catch the eye of a sadistic Nazi officer. Schulz’s art became the currency in which he bought life.
+Drawing on extensive new reporting and archival research, Benjamin Balint chases the inventive murals Schulz painted on the walls of an SS villa—the last traces of his vanished world—into multiple dimensions of the artist’s life and afterlife. Sixty years after Schulz was murdered, those murals were miraculously rediscovered, only to be secretly smuggled by Israeli agents to Jerusalem. The ensuing international furor summoned broader perplexities, not just about who has the right to curate orphaned artworks and to construe their meanings, but about who can claim to stand guard over the legacy of Jews killed in the Nazi slaughter.
+By re-creating the artist’s milieu at a crossroads not just of Jewish and Polish culture but of art, sex, and violence, Bruno Schulz itself stands as an act of belated restitution, offering a kaleidoscopic portrait of a life with all its paradoxes and curtailed possibilities.</t>
+  </si>
+  <si>
+    <t>Winner of the Sami Rohr Prize for Jewish Literature
+“Dramatic and illuminating.… [R]aises momentous questions about nationality, religion, literature, and even the Holocaust.”
+―Adam Kirsch, The Atlantic
+“Fascinating and forensically scrupulous.”
+―John Banville, The Guardian
+“Thoughtful and provocative.”
+―Ruth Franklin, The Wall Street Journal
+“[Balint is] a gifted cultural historian with a scholarly sensibility.”
+―Lev Mendes, The New York Times Book Review
+“Absorbing.… Balint’s scrupulous and sardonic prose makes you love Kafka, and dread the law.”
+―The Economist
+“A tale pitting two Goliaths against one octogenarian David, untangled in exacting, riveting detail.… [A] must-read.”
+―Rebecca Schuman, Slate</t>
+  </si>
+  <si>
+    <t>cinnamon</t>
+  </si>
+  <si>
+    <t>The Cinnamon Shops and Other Stories</t>
+  </si>
+  <si>
+    <t>Bruno Schulz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">John Curran Davis </t>
+  </si>
+  <si>
+    <t>CreateSpace Independent Publishing Platform</t>
+  </si>
+  <si>
+    <t>In The Cinnamon Shops and Other Stories, Bruno Schulz describes in fantastical, mythologised terms the cloth merchant's shop where he grew up and the bizarre antics of his father, such as turning the attic into an aviary and expounding strange theories on mannequins. Two sides of the Galician town of Drohobycz are seen: the old town full of ancient mystery is contrasted with newer districts that have sprung up in response to oil mining in the area. The language is poetic, heady and oneiric, employing a rich system of imagery incorporating books and labyrinths.</t>
+  </si>
+  <si>
+    <t>This Way for the Gas, Ladies and Gentlemen</t>
+  </si>
+  <si>
+    <t>to-the-gas</t>
+  </si>
+  <si>
+    <t>Barbara Vedder, Michael Kandel</t>
+  </si>
+  <si>
+    <t>Penguin Classics</t>
+  </si>
+  <si>
+    <t>Tadeusz Borowski’s concentration camp stories were based on his own experiences surviving Auschwitz and Dachau. In spare, brutal prose he describes a world where where the will to survive overrides compassion and prisoners eat, work and sleep a few yards from where others are murdered; where the difference between human beings is reduced to a second bowl of soup, an extra blanket or the luxury of a pair of shoes with thick soles; and where the line between normality and abnormality vanishes. Published in Poland after the Second World War, these stories constitute a masterwork of world literature.
+For more than seventy years, Penguin has been the leading publisher of classic literature in the English-speaking world. With more than 1,700 titles, Penguin Classics represents a global bookshelf of the best works throughout history and across genres and disciplines. Readers trust the series to provide authoritative texts enhanced by introductions and notes by distinguished scholars and contemporary authors, as well as up-to-date translations by award-winning translators.</t>
+  </si>
+  <si>
+    <t>The Street of Crocodiles and Other Stories</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Celina Wieniewska </t>
+  </si>
+  <si>
+    <t>The collected fiction of "one of the most original imaginations in modern Europe" (Cynthia Ozick)
+The untimely death of Polish writer Bruno Schulz at the hands of a Gestapo officer stands as one of the great losses to modern literature, but since his death, word of his extraordinary literary voice has won him an international readership. This volume brings together Schulz's complete fiction, including The Street of Crocodiles, praised by The New York Review of Books as "a masterpiece . . . marvelously inventive"; his final surviving work, Sanatorium Under the Sign of the Hourglass; and three short stories. Illustrated with Schulz's luminous original drawings, this edition beautifully showcases the distinctive surrealist vision of one of the twentieth century's most gifted and influential writers.
+For more than seventy years, Penguin has been the leading publisher of classic literature in the English-speaking world. With more than 1,700 titles, Penguin Classics represents a global bookshelf of the best works throughout history and across genres and disciplines. Readers trust the series to provide authoritative texts enhanced by introductions and notes by distinguished scholars and contemporary authors, as well as up-to-date translations by award-winning translators.</t>
+  </si>
+  <si>
+    <t>street-crocodiles</t>
+  </si>
+  <si>
+    <t>Nocturnal Apparitions: Essential Stories</t>
+  </si>
+  <si>
+    <t>Stanley Bill</t>
+  </si>
+  <si>
+    <t>Pushkin Collection</t>
+  </si>
+  <si>
+    <t>nocturnal-apparitions</t>
+  </si>
+  <si>
+    <t>A stunning new collection featuring fresh translations of Bruno Schulz's 15 most captivating short stories, in a beautiful Pushkin Collection edition
+Includes a new translation of a recently discovered story, believed to be the first-ever published work by this legendary cult writer
+The stories in this collection are rich, tangled, and suffused with mystery and wonder. In the narrowing, winding city streets, strange figures roam. Great flocks of birds soar over rooftops, obscuring the sun. Cockroaches appear through cracks and scuttle across floorboards. Individuals careen from university buildings to dimly lit parlour rooms, through strange shops and endless storms.
+Crowded with moments of stunning beauty, the 15 stories in his collection showcases Schulz's darkly modern sensibility, and his essential status as one of the great transformers of the ordinary into the fantastical:
+August, A Visitation, Birds, Pan, Cinnamon Shops, The Street of Crocodiles, Cockroaches, The Gale, The Night of the Great Season (from Cinnamon Shops)
+The Book, The Age of Genius, A July Night, My Father Joins the Firefighters, Father’s Final Escape (from Sanatorium under the Sign of the Hourglass)
+Undula--a new translation of Schulz's recently discovered first published story</t>
+  </si>
+  <si>
+    <t>"An accessible, exhilarating introduction to Schulz’s oeuvre."
+—The Washington Post
+“Stanley Bill’s translations come as an invigorating reminder of the uncanny verbal sorcery behind this unique voice and vision.... The results, hauntingly phrased, can be suitably weird—but never impenetrable... Bill catches the outrageous wit of Schulz’s nightmare tableaux.”
+—The Wall Street Journal
+"The supreme virtuoso of Polish fiction... Genius"
+—Jewish Chronicle</t>
+  </si>
+  <si>
+    <t>Vahazar: or On the Uplands of Absurdity</t>
+  </si>
+  <si>
+    <t>vahazar</t>
+  </si>
+  <si>
+    <t>BLACK SCAT BOOKS</t>
+  </si>
+  <si>
+    <t>“Witkiewicz takes up and continues the vein of dream and grotesque fantasy exemplified by the late Strindberg or by Wedekind; his ideas are closely paralleled by those of the surrealists and Antonin Artaud which culminated in the masterpieces of the dramatists of the absurd—Beckett, Ionesco, Genet, Arrabal—of the late nineteen forties and the nineteen fifties.” -Martin Esslin Stanisław Ignacy Witkiewicz (pen name: Witkacy) was desperate to get out of revolutionary St. Petersburg after the Bolsheviks seized power. Back in Poland, eager to make money and a name for himself, Witkacy began to write plays in a style that he called “Pure Form,” which foreshadowed the Theatre of the Absurd. By the time that he wrote VAHAZAR (1921), Witkacy had achieved a dreamlike dramaturgy: centered on the paranoid and crazed despot, Vahazar, and spiraling outwards through an anthill society of automatons, religious cults, and quack scientific and social theories, this play is about being trapped in nothingness. This translation of the play by Celina Wieniewska was commissioned by Stefan Themerson in 1967, and later announced as a forthcoming title by the legendary Gaberbocchus Press. Somehow the project was sidetracked and has never appeared until this Black Scat Books publication. Paul Rosheim, publisher of Obscure Publications and scholar of Themersonia, provides an introduction with biographical information about Witkacy and the story of this translation. The book also includes an appendix featuring Franciszka Themerson’s “Vahazar: A Few Suggestions for Design.”</t>
+  </si>
+  <si>
+    <t>Women: A Novel about Polish Life</t>
+  </si>
+  <si>
+    <t>Michał Henryk Dziewicki</t>
+  </si>
+  <si>
+    <t>women</t>
+  </si>
+  <si>
+    <t>Young Poland Revisited</t>
+  </si>
+  <si>
+    <t>B0CS97TPFV</t>
+  </si>
+  <si>
+    <t>The turn of the twentieth century witnessed the emergence of a vibrant cultural and artistic movement in Poland known as Young Poland (Młoda Polska). Occur-ring at a time when Poland as a free nation had not existed for 100 years, it was characterized by a fervent de-sire for artistic renewal and societal transformation, giving rise to a multitude of talents across various disciplines. Among the prominent figures of this period was Zofia Nałkowska (1884-1954), a trailblazing Polish writer whose literary contributions played a crucial role in shaping the intellectual landscape of her time.
+Women, one of Nałkowska’s earliest works--written when she was just twenty-two--is a profound exploration of female experience at a crucial juncture in history . Published early in the century against the backdrop of societal upheavals and the growing feminist movement, the novel stands as a poignant and complex portrayal of women’s lives, aspirations, and struggles.</t>
+  </si>
+  <si>
+    <t>Boundary</t>
+  </si>
+  <si>
+    <t>boundary</t>
+  </si>
+  <si>
+    <t>Ursula Phillips</t>
+  </si>
+  <si>
+    <t>Available for the first time in English, Zofia Nalkowska's Boundary was originally published as Granica in Poland in 1935. The modernist novel was widely discussed upon its publication and praised for its psychological realism and stylistic and compositional artistry. Over the years, it has been translated into several languages and made into a feature film, and remains a standard text in the Polish secondary school curriculum.
+Nalkowska was a pioneer of feminist fiction in Central Europe. Her observation of inequality in the treatment of men and women is at the heart of Boundary, which explores a transgressive love affair and its repercussions. She perceived that men—especially of the upper and middle classes—felt free to have sexual relations with lower class women, whereas it was not socially acceptable for women of any class to have sexual relations outside of marriage, or even admit to enjoying sex. This meant that working class women were seduced and then abandoned when they became pregnant, leaving them with the stigma of illegitimate children and the problem of finding work. Meanwhile, the higher class wives found themselves betrayed. While Boundary can be interpreted as a novel about power and its abuses, it contains several dimensions—philosophical, emotional, existential, moral—that render it a consummate piece of social criticism. An elegantly composed work of imaginative fiction, it does not preach or offer solutions. Ursula Phillips's excellent translation will interest readers of early twentieth century novels and scholars and students of Polish literature, feminist studies, and European modernism.</t>
+  </si>
+  <si>
+    <t>Boundary impresses with its formal and stylistic artistry, which comes through in Ursula Phillips's translation, the first into English.
+― Times Literary Supplement
+Zofia Nalkowska has written a first-class novel.... It is amazing that we have had to wait over eighty years to read it in English, and we should be grateful that we can now do so.
+― The Modern Novel</t>
+  </si>
+  <si>
+    <t>The Romance of Teresa Hennert</t>
+  </si>
+  <si>
+    <t>Northern Illinois University</t>
+  </si>
+  <si>
+    <t>The Romance of Teresa Hennert is a masterpiece of psychological realism and a still-shocking portrait of mixed motives and bad behavior. It renders a tragicomic vision of what happens when a society is suddenly deprived of the struggle that had defined it for more than a century. Written in 1922, just four years after Poland achieved independence from its neighboring empires, the novel focuses on a Warsaw community of officers, bureaucrats, intellectuals, wives, and lovers, all of them adrift in a hell of their own making―the long-sought freedom to shape their own destiny. At the center of this milieu is Teresa Hennert, whose youthful charm, modern habits, and apparent indifference to the emotional torment of those around her make her an inescapable object of their fascination and desire.
+Told in multiple voices and from numerous perspectives, Zofia Nalkowska's novel is a mosaic of dysfunction at all levels of the new Polish society, from a bumbling lieutenant who cannot stand his home life to a young Communist who believes his forebears have made a mess that only the next generation can clean up. In this world, ideological battles, personal animosity, postwar trauma, and infidelity become inextricably bound together, driving these colorful, increasingly confused characters toward corruption, suicide, and murder. Nalkowska (1884–1954), though long neglected in the West, was a central figure in the literary life of interwar Poland and was an early pioneer of feminist fiction in Central Europe. Her spare, witty prose will surprise contemporary readers with its frank sexuality and stark illustration of dreams gone horribly, humiliatingly, dramatically awry.</t>
+  </si>
+  <si>
+    <t>Megan Thomas, Ewa Malachowska-Pasek</t>
+  </si>
+  <si>
+    <t>The characters' differing points of view, with the narrator's ironic omniscience never far away, are exceptionally well rendered in this translation, which contains helpful historical footnotes and is part of a project to bring the modernist works of Nalkowska to the attention of English readers.
+― The Times Literary Supplement
+The Romance of Teresa Hennert is a sometimes scathing, sometimes sardonically funny sketch of the affairs-commercial, political, amatory-of a very small segment of Warsaw society in the early years of the newly established Polish republic. It is a thoroughly accomplished translation.
+-- Madeline G. Levine, University of North Carolina</t>
+  </si>
+  <si>
+    <t>romance-teresa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medallions </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diana Kuprel </t>
+  </si>
+  <si>
+    <t>medalions</t>
+  </si>
+  <si>
+    <t>From Corsets to Communism: The Life and Times of Zofia Nalkowska</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jenny Robertson </t>
+  </si>
+  <si>
+    <t>Scotland Street Press</t>
+  </si>
+  <si>
+    <t>corsets</t>
+  </si>
+  <si>
+    <t>‘I had only one eye, I was hungry and cold, yet I wanted to live… so that I could tell it all just as I’ve told you.’ - From Zofia Nalkowska’s Medallions (1947).
+Witness to two world wars and Poland’s struggle for independence, Zofia Nalkowska’s commitment to recording all is her gift to European literature. Her own story of love affairs, family loyalty and survival is remarkable in itself. Yet, her determination to record others’ truth, however painful, ties her fate to a nation whose battle for identity is both brutal and romantic. Her most renowned work, Medallions, a collection of short stories, exposes and restores dignity to people reduced, through Nazi occupation, to burnt out ghettos and guillotined heads heaped ‘like potatoes’. In contrast, as a keen and visionary observer of beauty, Nalkowska is innovative in exploring motherhood’s psychological imprint and the blurred boundaries of male and female relationships. Drawing on her own background as a poet and Polish Studies graduate, Jenny’s Robertson’s literary biography celebrates the achievements of a pioneering writer whose love of life not only propelled her to fame, but gave her the courage to witness atrocity. In doing so, Nalkowska’s life and writing reflect and inform Europe's cultural heritage.
+Report an issue with this produc</t>
+  </si>
+  <si>
+    <t>Medallions is a collection of eight documentary stories originally published in Poland in 1946 that recount Nazi war crimes under the German occupation of the country. The author, Zofia Nalkowska, was a member of a special committee for the investigation of Nazi crimes in Poland, and the stories reflect facts she learned from victims and witnesses to atrocities inflicted on Polish civilians.
+Considered a masterpiece of antifascist world literature, Medallions stands as the culmination of Nalkowska's literary style, a style the Polish writer Witold Gombrowicz once described as "the iron capital of her art and one of the very few exportables in our national literature." More than mere historical record, Medallions offers the reader startling immediacy, the repetition of an event as it persists in the testimonial present, in the scars on the consciousness and conscience of individuals.</t>
+  </si>
+  <si>
+    <t>"[A] powerful and important work." —Jewish Book World</t>
+  </si>
+  <si>
+    <t>Nałkowska</t>
+  </si>
+  <si>
+    <t>Schulz</t>
+  </si>
+  <si>
+    <t>Wańkowicz</t>
   </si>
 </sst>
 </file>
@@ -3209,7 +3740,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -3245,12 +3776,14 @@
     <xf numFmtId="1" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3607,9 +4140,11 @@
     <col min="34" max="35" width="26.28515625" customWidth="1"/>
     <col min="38" max="38" width="16" customWidth="1"/>
     <col min="40" max="40" width="21.140625" customWidth="1"/>
-    <col min="41" max="49" width="19.7109375" customWidth="1"/>
-    <col min="50" max="50" width="95.85546875" style="25" customWidth="1"/>
-    <col min="51" max="51" width="66.85546875" style="26" customWidth="1"/>
+    <col min="41" max="44" width="19.7109375" customWidth="1"/>
+    <col min="45" max="45" width="19.7109375" style="25" customWidth="1"/>
+    <col min="46" max="49" width="19.7109375" customWidth="1"/>
+    <col min="50" max="50" width="95.85546875" style="27" customWidth="1"/>
+    <col min="51" max="51" width="66.85546875" style="28" customWidth="1"/>
     <col min="52" max="54" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3746,7 +4281,7 @@
       <c r="AR1" t="s">
         <v>658</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AS1" s="25" t="s">
         <v>659</v>
       </c>
       <c r="AT1" t="s">
@@ -3761,10 +4296,10 @@
       <c r="AW1" t="s">
         <v>660</v>
       </c>
-      <c r="AX1" s="25" t="s">
+      <c r="AX1" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="AY1" s="26" t="s">
+      <c r="AY1" s="28" t="s">
         <v>204</v>
       </c>
       <c r="AZ1" t="s">
@@ -3859,10 +4394,10 @@
         <f>"covers/" &amp; A2 &amp; ".jpg"</f>
         <v>covers/chopin-in-paris.jpg</v>
       </c>
-      <c r="AX2" s="25" t="s">
+      <c r="AX2" s="27" t="s">
         <v>324</v>
       </c>
-      <c r="AY2" s="26" t="s">
+      <c r="AY2" s="28" t="s">
         <v>325</v>
       </c>
       <c r="AZ2" t="s">
@@ -3945,7 +4480,7 @@
         <f t="shared" ref="AH3:AH66" si="0">"covers/" &amp; A3 &amp; ".jpg"</f>
         <v>covers/peasant-prince.jpg</v>
       </c>
-      <c r="AX3" s="25" t="s">
+      <c r="AX3" s="27" t="s">
         <v>329</v>
       </c>
       <c r="BC3" t="s">
@@ -4014,10 +4549,10 @@
         <f t="shared" si="0"/>
         <v>covers/izabela-the-valiant.jpg</v>
       </c>
-      <c r="AX4" s="25" t="s">
+      <c r="AX4" s="27" t="s">
         <v>330</v>
       </c>
-      <c r="AY4" s="27" t="s">
+      <c r="AY4" s="29" t="s">
         <v>331</v>
       </c>
       <c r="AZ4" t="s">
@@ -4079,10 +4614,10 @@
         <f t="shared" si="0"/>
         <v>covers/light-and-flame.jpg</v>
       </c>
-      <c r="AX5" s="25" t="s">
+      <c r="AX5" s="27" t="s">
         <v>335</v>
       </c>
-      <c r="AY5" s="26" t="s">
+      <c r="AY5" s="28" t="s">
         <v>336</v>
       </c>
       <c r="BC5" t="s">
@@ -4149,7 +4684,7 @@
         <f t="shared" si="0"/>
         <v>covers/trail-of-hope.jpg</v>
       </c>
-      <c r="AX6" s="25" t="s">
+      <c r="AX6" s="27" t="s">
         <v>337</v>
       </c>
       <c r="BC6" t="s">
@@ -4212,10 +4747,10 @@
         <f t="shared" si="0"/>
         <v>covers/303-squadron.jpg</v>
       </c>
-      <c r="AX7" s="25" t="s">
+      <c r="AX7" s="27" t="s">
         <v>338</v>
       </c>
-      <c r="AY7" s="26" t="s">
+      <c r="AY7" s="28" t="s">
         <v>339</v>
       </c>
       <c r="BC7" t="s">
@@ -4285,7 +4820,7 @@
         <f t="shared" si="0"/>
         <v>covers/the-doll.jpg</v>
       </c>
-      <c r="AX8" s="25" t="s">
+      <c r="AX8" s="27" t="s">
         <v>341</v>
       </c>
       <c r="BC8" t="s">
@@ -4359,7 +4894,7 @@
       <c r="AW9" t="s">
         <v>710</v>
       </c>
-      <c r="AX9" s="25" t="s">
+      <c r="AX9" s="27" t="s">
         <v>340</v>
       </c>
       <c r="BC9" t="s">
@@ -4425,10 +4960,10 @@
       <c r="AQ10" t="s">
         <v>695</v>
       </c>
-      <c r="AX10" s="25" t="s">
+      <c r="AX10" s="27" t="s">
         <v>359</v>
       </c>
-      <c r="AY10" s="26" t="s">
+      <c r="AY10" s="28" t="s">
         <v>360</v>
       </c>
       <c r="BC10" t="s">
@@ -4484,10 +5019,10 @@
         <f t="shared" si="0"/>
         <v>covers/choucas.jpg</v>
       </c>
-      <c r="AX11" s="25" t="s">
+      <c r="AX11" s="27" t="s">
         <v>361</v>
       </c>
-      <c r="AY11" s="26" t="s">
+      <c r="AY11" s="28" t="s">
         <v>362</v>
       </c>
       <c r="BC11" t="s">
@@ -4556,7 +5091,7 @@
         <f t="shared" si="0"/>
         <v>covers/desert-wilderness.jpg</v>
       </c>
-      <c r="AX12" s="25" t="s">
+      <c r="AX12" s="27" t="s">
         <v>363</v>
       </c>
       <c r="BC12" t="s">
@@ -4609,7 +5144,7 @@
         <f t="shared" si="0"/>
         <v>covers/forest-folk.jpg</v>
       </c>
-      <c r="AX13" s="25" t="s">
+      <c r="AX13" s="27" t="s">
         <v>364</v>
       </c>
       <c r="BC13" t="s">
@@ -4673,10 +5208,10 @@
         <f t="shared" si="0"/>
         <v>covers/castorp.jpg</v>
       </c>
-      <c r="AX14" s="25" t="s">
+      <c r="AX14" s="27" t="s">
         <v>365</v>
       </c>
-      <c r="AY14" s="26" t="s">
+      <c r="AY14" s="28" t="s">
         <v>366</v>
       </c>
       <c r="BC14" t="s">
@@ -4732,10 +5267,10 @@
         <f t="shared" si="0"/>
         <v>covers/shah-of-shahs.jpg</v>
       </c>
-      <c r="AX15" s="25" t="s">
+      <c r="AX15" s="27" t="s">
         <v>367</v>
       </c>
-      <c r="AY15" s="26" t="s">
+      <c r="AY15" s="28" t="s">
         <v>369</v>
       </c>
       <c r="BC15" t="s">
@@ -4791,10 +5326,10 @@
         <f t="shared" si="0"/>
         <v>covers/the-emperor.jpg</v>
       </c>
-      <c r="AX16" s="25" t="s">
+      <c r="AX16" s="27" t="s">
         <v>370</v>
       </c>
-      <c r="AY16" s="26" t="s">
+      <c r="AY16" s="28" t="s">
         <v>371</v>
       </c>
       <c r="BC16" t="s">
@@ -4859,10 +5394,22 @@
       <c r="AQ17" t="s">
         <v>652</v>
       </c>
-      <c r="AX17" s="28" t="s">
+      <c r="AR17" t="s">
+        <v>711</v>
+      </c>
+      <c r="AT17" t="s">
+        <v>712</v>
+      </c>
+      <c r="AU17" t="s">
+        <v>713</v>
+      </c>
+      <c r="AW17" t="s">
+        <v>714</v>
+      </c>
+      <c r="AX17" s="30" t="s">
         <v>377</v>
       </c>
-      <c r="AY17" s="26" t="s">
+      <c r="AY17" s="28" t="s">
         <v>693</v>
       </c>
       <c r="BC17" t="s">
@@ -4914,10 +5461,10 @@
         <f>"covers/" &amp; A18 &amp; ".jpg"</f>
         <v>covers/shadow-of-sun.jpg</v>
       </c>
-      <c r="AX18" s="25" t="s">
+      <c r="AX18" s="27" t="s">
         <v>375</v>
       </c>
-      <c r="AY18" s="26" t="s">
+      <c r="AY18" s="28" t="s">
         <v>376</v>
       </c>
       <c r="BC18" t="s">
@@ -4975,7 +5522,7 @@
         <f t="shared" si="0"/>
         <v>covers/meeting-in-oea.jpg</v>
       </c>
-      <c r="AX19" s="25" t="s">
+      <c r="AX19" s="27" t="s">
         <v>378</v>
       </c>
       <c r="BC19" t="s">
@@ -5039,7 +5586,7 @@
         <f t="shared" si="0"/>
         <v>covers/seven-against-thebes.jpg</v>
       </c>
-      <c r="AX20" s="25" t="s">
+      <c r="AX20" s="27" t="s">
         <v>379</v>
       </c>
       <c r="BC20" t="s">
@@ -5103,7 +5650,7 @@
         <f t="shared" si="0"/>
         <v>covers/emperor-julian.jpg</v>
       </c>
-      <c r="AX21" s="25" t="s">
+      <c r="AX21" s="27" t="s">
         <v>380</v>
       </c>
       <c r="BC21" t="s">
@@ -5167,7 +5714,7 @@
         <f t="shared" si="0"/>
         <v>covers/last-olympiad.jpg</v>
       </c>
-      <c r="AX22" s="25" t="s">
+      <c r="AX22" s="27" t="s">
         <v>381</v>
       </c>
       <c r="BC22" t="s">
@@ -5253,7 +5800,7 @@
       <c r="AW23" t="s">
         <v>703</v>
       </c>
-      <c r="AX23" s="25" t="s">
+      <c r="AX23" s="27" t="s">
         <v>382</v>
       </c>
       <c r="BC23" t="s">
@@ -5309,7 +5856,7 @@
         <f t="shared" si="0"/>
         <v>covers/fiasco.jpg</v>
       </c>
-      <c r="AX24" s="25" t="s">
+      <c r="AX24" s="27" t="s">
         <v>383</v>
       </c>
       <c r="BC24" t="s">
@@ -5365,7 +5912,7 @@
         <f t="shared" si="0"/>
         <v>covers/the-invincible.jpg</v>
       </c>
-      <c r="AX25" s="25" t="s">
+      <c r="AX25" s="27" t="s">
         <v>384</v>
       </c>
       <c r="BC25" t="s">
@@ -5496,10 +6043,10 @@
         <f t="shared" si="0"/>
         <v>covers/melicles.jpg</v>
       </c>
-      <c r="AX27" s="25" t="s">
+      <c r="AX27" s="27" t="s">
         <v>206</v>
       </c>
-      <c r="AY27" s="26" t="s">
+      <c r="AY27" s="28" t="s">
         <v>209</v>
       </c>
       <c r="AZ27" t="s">
@@ -5566,7 +6113,7 @@
         <f t="shared" si="0"/>
         <v>covers/diossos.jpg</v>
       </c>
-      <c r="AX28" s="25" t="s">
+      <c r="AX28" s="27" t="s">
         <v>385</v>
       </c>
       <c r="BC28" t="s">
@@ -5624,7 +6171,7 @@
         <f t="shared" si="0"/>
         <v>covers/white-jaguar-1.jpg</v>
       </c>
-      <c r="AX29" s="25" t="s">
+      <c r="AX29" s="27" t="s">
         <v>387</v>
       </c>
       <c r="BC29" t="s">
@@ -5688,7 +6235,7 @@
         <f t="shared" si="0"/>
         <v>covers/ships-minos-1.jpg</v>
       </c>
-      <c r="AX30" s="25" t="s">
+      <c r="AX30" s="27" t="s">
         <v>386</v>
       </c>
       <c r="BC30" t="s">
@@ -5766,7 +6313,7 @@
         <f t="shared" si="0"/>
         <v>covers/divine-julius.jpg</v>
       </c>
-      <c r="AX31" s="25" t="s">
+      <c r="AX31" s="27" t="s">
         <v>388</v>
       </c>
       <c r="BC31" t="s">
@@ -5844,7 +6391,7 @@
         <f t="shared" si="0"/>
         <v>covers/naso-the-poet.jpg</v>
       </c>
-      <c r="AX32" s="25" t="s">
+      <c r="AX32" s="27" t="s">
         <v>389</v>
       </c>
       <c r="BC32" t="s">
@@ -5912,7 +6459,7 @@
         <f t="shared" si="0"/>
         <v>covers/tiberius-caesar.jpg</v>
       </c>
-      <c r="AX33" s="25" t="s">
+      <c r="AX33" s="27" t="s">
         <v>390</v>
       </c>
       <c r="BC33" t="s">
@@ -5966,7 +6513,7 @@
         <f t="shared" si="0"/>
         <v>covers/milosz-selected-and-last-poems.jpg</v>
       </c>
-      <c r="AX34" s="25" t="s">
+      <c r="AX34" s="27" t="s">
         <v>391</v>
       </c>
       <c r="BC34" t="s">
@@ -6025,7 +6572,7 @@
         <f t="shared" si="0"/>
         <v>covers/poems-new-and-szymborska.jpg</v>
       </c>
-      <c r="AX35" s="25" t="s">
+      <c r="AX35" s="27" t="s">
         <v>392</v>
       </c>
       <c r="BC35" t="s">
@@ -6073,10 +6620,10 @@
         <f t="shared" si="0"/>
         <v>covers/poems-herbert.jpg</v>
       </c>
-      <c r="AX36" s="25" t="s">
+      <c r="AX36" s="27" t="s">
         <v>393</v>
       </c>
-      <c r="AY36" s="26" t="s">
+      <c r="AY36" s="28" t="s">
         <v>394</v>
       </c>
       <c r="BC36" t="s">
@@ -6124,10 +6671,10 @@
         <f t="shared" si="0"/>
         <v>covers/without-end.jpg</v>
       </c>
-      <c r="AX37" s="25" t="s">
+      <c r="AX37" s="27" t="s">
         <v>396</v>
       </c>
-      <c r="AY37" s="26" t="s">
+      <c r="AY37" s="28" t="s">
         <v>397</v>
       </c>
       <c r="BC37" t="s">
@@ -6190,10 +6737,10 @@
         <f t="shared" si="0"/>
         <v>covers/sobbing-superpower.jpg</v>
       </c>
-      <c r="AX38" s="25" t="s">
+      <c r="AX38" s="27" t="s">
         <v>398</v>
       </c>
-      <c r="AY38" s="26" t="s">
+      <c r="AY38" s="28" t="s">
         <v>399</v>
       </c>
       <c r="BC38" t="s">
@@ -6253,10 +6800,10 @@
         <f t="shared" si="0"/>
         <v>covers/map-collected-and-last.jpg</v>
       </c>
-      <c r="AX39" s="25" t="s">
+      <c r="AX39" s="27" t="s">
         <v>400</v>
       </c>
-      <c r="AY39" s="26" t="s">
+      <c r="AY39" s="28" t="s">
         <v>401</v>
       </c>
       <c r="BC39" t="s">
@@ -6319,7 +6866,7 @@
         <f t="shared" si="0"/>
         <v>covers/from-tree-of-knowledge.jpg</v>
       </c>
-      <c r="AX40" s="25" t="s">
+      <c r="AX40" s="27" t="s">
         <v>402</v>
       </c>
       <c r="BC40" t="s">
@@ -6365,7 +6912,7 @@
         <f t="shared" si="0"/>
         <v>covers/krzysztof-kamil-baczynski.jpg</v>
       </c>
-      <c r="AX41" s="25" t="s">
+      <c r="AX41" s="27" t="s">
         <v>403</v>
       </c>
       <c r="BC41" t="s">
@@ -6414,7 +6961,7 @@
         <f t="shared" si="0"/>
         <v>covers/white-magic-baczynski.jpg</v>
       </c>
-      <c r="AX42" s="25" t="s">
+      <c r="AX42" s="27" t="s">
         <v>404</v>
       </c>
       <c r="BC42" t="s">
@@ -6477,7 +7024,7 @@
         <f t="shared" si="0"/>
         <v>covers/new-poems-ukr-po.jpg</v>
       </c>
-      <c r="AX43" s="25" t="s">
+      <c r="AX43" s="27" t="s">
         <v>202</v>
       </c>
       <c r="BC43" t="s">
@@ -6550,7 +7097,7 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-templars.jpg</v>
       </c>
-      <c r="AX44" s="25" t="s">
+      <c r="AX44" s="27" t="s">
         <v>196</v>
       </c>
       <c r="BC44" t="s">
@@ -6623,7 +7170,7 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-mysteries.jpg</v>
       </c>
-      <c r="AX45" s="25" t="s">
+      <c r="AX45" s="27" t="s">
         <v>198</v>
       </c>
       <c r="BC45" t="s">
@@ -6696,7 +7243,7 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-bandits.jpg</v>
       </c>
-      <c r="AX46" s="25" t="s">
+      <c r="AX46" s="27" t="s">
         <v>195</v>
       </c>
       <c r="BC46" t="s">
@@ -6769,7 +7316,7 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-copernicus.jpg</v>
       </c>
-      <c r="AX47" s="29" t="s">
+      <c r="AX47" s="31" t="s">
         <v>197</v>
       </c>
       <c r="BC47" t="s">
@@ -6829,7 +7376,7 @@
         <f t="shared" si="0"/>
         <v>covers/cold-sea.jpg</v>
       </c>
-      <c r="AX48" s="25" t="s">
+      <c r="AX48" s="27" t="s">
         <v>215</v>
       </c>
       <c r="BC48" t="s">
@@ -6914,7 +7461,7 @@
       <c r="AR49" t="s">
         <v>663</v>
       </c>
-      <c r="AS49" t="s">
+      <c r="AS49" s="25" t="s">
         <v>667</v>
       </c>
       <c r="AT49" t="s">
@@ -6929,7 +7476,7 @@
       <c r="AW49" t="s">
         <v>664</v>
       </c>
-      <c r="AX49" s="29" t="s">
+      <c r="AX49" s="31" t="s">
         <v>218</v>
       </c>
       <c r="BC49" t="s">
@@ -6979,7 +7526,7 @@
         <f t="shared" si="0"/>
         <v>covers/birch-grove.jpg</v>
       </c>
-      <c r="AX50" s="25" t="s">
+      <c r="AX50" s="27" t="s">
         <v>225</v>
       </c>
       <c r="BC50" t="s">
@@ -7030,7 +7577,7 @@
         <f t="shared" si="0"/>
         <v>covers/danton-thermidor.jpg</v>
       </c>
-      <c r="AX51" s="29" t="s">
+      <c r="AX51" s="31" t="s">
         <v>231</v>
       </c>
       <c r="BC51" t="s">
@@ -7080,7 +7627,7 @@
         <f t="shared" si="0"/>
         <v>covers/coming-spring.jpg</v>
       </c>
-      <c r="AX52" s="25" t="s">
+      <c r="AX52" s="27" t="s">
         <v>234</v>
       </c>
       <c r="BC52" t="s">
@@ -7138,7 +7685,7 @@
         <f t="shared" si="0"/>
         <v>covers/beniowski.jpg</v>
       </c>
-      <c r="AX53" s="25" t="s">
+      <c r="AX53" s="27" t="s">
         <v>245</v>
       </c>
       <c r="BC53" t="s">
@@ -7188,7 +7735,7 @@
         <f t="shared" si="0"/>
         <v>covers/witcher-set.jpg</v>
       </c>
-      <c r="AX54" s="29" t="s">
+      <c r="AX54" s="31" t="s">
         <v>252</v>
       </c>
       <c r="BC54" t="s">
@@ -7238,7 +7785,7 @@
         <f t="shared" si="0"/>
         <v>covers/tower-fools.jpg</v>
       </c>
-      <c r="AX55" s="25" t="s">
+      <c r="AX55" s="27" t="s">
         <v>256</v>
       </c>
       <c r="BC55" t="s">
@@ -7294,7 +7841,7 @@
         <f t="shared" si="0"/>
         <v>covers/warrior-god.jpg</v>
       </c>
-      <c r="AX56" s="29" t="s">
+      <c r="AX56" s="31" t="s">
         <v>260</v>
       </c>
       <c r="BC56" t="s">
@@ -7350,7 +7897,7 @@
         <f t="shared" si="0"/>
         <v>covers/light-perpetua.jpg</v>
       </c>
-      <c r="AX57" s="25" t="s">
+      <c r="AX57" s="27" t="s">
         <v>263</v>
       </c>
       <c r="BC57" t="s">
@@ -7423,7 +7970,7 @@
         <f t="shared" si="0"/>
         <v>covers/red-prince.jpg</v>
       </c>
-      <c r="AX58" s="29" t="s">
+      <c r="AX58" s="31" t="s">
         <v>268</v>
       </c>
       <c r="BC58" t="s">
@@ -7472,7 +8019,7 @@
         <f t="shared" si="0"/>
         <v>covers/adam-mickiewicz.jpg</v>
       </c>
-      <c r="AX59" s="29" t="s">
+      <c r="AX59" s="31" t="s">
         <v>273</v>
       </c>
       <c r="BC59" t="s">
@@ -7524,7 +8071,7 @@
         <f t="shared" si="0"/>
         <v>covers/forefathers-eve.jpg</v>
       </c>
-      <c r="AX60" s="29" t="s">
+      <c r="AX60" s="31" t="s">
         <v>277</v>
       </c>
       <c r="BC60" t="s">
@@ -7576,7 +8123,7 @@
         <f t="shared" si="0"/>
         <v>covers/ballads-romances.jpg</v>
       </c>
-      <c r="AX61" s="25" t="s">
+      <c r="AX61" s="27" t="s">
         <v>282</v>
       </c>
       <c r="BC61" t="s">
@@ -7627,7 +8174,7 @@
         <f t="shared" si="0"/>
         <v>covers/native-realm.jpg</v>
       </c>
-      <c r="AX62" s="25" t="s">
+      <c r="AX62" s="27" t="s">
         <v>286</v>
       </c>
       <c r="BC62" t="s">
@@ -7675,7 +8222,7 @@
         <f t="shared" si="0"/>
         <v>covers/history-lit-milosz.jpg</v>
       </c>
-      <c r="AX63" s="25" t="s">
+      <c r="AX63" s="27" t="s">
         <v>293</v>
       </c>
       <c r="BC63" t="s">
@@ -7723,7 +8270,7 @@
         <f t="shared" si="0"/>
         <v>covers/postwar-polish-poetry.jpg</v>
       </c>
-      <c r="AX64" s="25" t="s">
+      <c r="AX64" s="27" t="s">
         <v>294</v>
       </c>
       <c r="BC64" t="s">
@@ -7771,7 +8318,7 @@
         <f t="shared" si="0"/>
         <v>covers/captive-mind.jpg</v>
       </c>
-      <c r="AX65" s="25" t="s">
+      <c r="AX65" s="27" t="s">
         <v>297</v>
       </c>
       <c r="BC65" t="s">
@@ -7820,7 +8367,7 @@
         <f t="shared" si="0"/>
         <v>covers/selected-masterpieces.jpg</v>
       </c>
-      <c r="AX66" s="25" t="s">
+      <c r="AX66" s="27" t="s">
         <v>301</v>
       </c>
       <c r="BC66" t="s">
@@ -7879,7 +8426,7 @@
         <f>"covers/" &amp; A67 &amp; ".jpg"</f>
         <v>covers/hyenas-lotuses.jpg</v>
       </c>
-      <c r="AX67" s="25" t="s">
+      <c r="AX67" s="27" t="s">
         <v>309</v>
       </c>
       <c r="BC67" t="s">
@@ -7937,10 +8484,10 @@
         <f>"covers/" &amp; A68 &amp; ".jpg"</f>
         <v>covers/widow-queen.jpg</v>
       </c>
-      <c r="AX68" s="25" t="s">
+      <c r="AX68" s="27" t="s">
         <v>310</v>
       </c>
-      <c r="AY68" s="26" t="s">
+      <c r="AY68" s="28" t="s">
         <v>315</v>
       </c>
       <c r="AZ68" t="s">
@@ -8017,10 +8564,10 @@
         <f>"covers/" &amp; A69 &amp; ".jpg"</f>
         <v>covers/last-crown.jpg</v>
       </c>
-      <c r="AX69" s="25" t="s">
+      <c r="AX69" s="27" t="s">
         <v>322</v>
       </c>
-      <c r="AY69" s="26" t="s">
+      <c r="AY69" s="28" t="s">
         <v>315</v>
       </c>
       <c r="AZ69" t="s">
@@ -8096,7 +8643,7 @@
         <f t="shared" ref="AH70" si="1">"covers/" &amp; A70 &amp; ".jpg"</f>
         <v>covers/the-homeless.jpg</v>
       </c>
-      <c r="AX70" s="25" t="s">
+      <c r="AX70" s="27" t="s">
         <v>237</v>
       </c>
       <c r="BC70" t="s">
@@ -8147,10 +8694,10 @@
         <f t="shared" ref="AH71:AH98" si="2">"covers/" &amp; A71 &amp; ".jpg"</f>
         <v>covers/ferdydurke.jpg</v>
       </c>
-      <c r="AX71" s="25" t="s">
+      <c r="AX71" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="AY71" s="26" t="s">
+      <c r="AY71" s="28" t="s">
         <v>347</v>
       </c>
       <c r="BC71" t="s">
@@ -8201,10 +8748,10 @@
         <f t="shared" si="2"/>
         <v>covers/the-possessed.jpg</v>
       </c>
-      <c r="AX72" s="25" t="s">
+      <c r="AX72" s="27" t="s">
         <v>348</v>
       </c>
-      <c r="AY72" s="26" t="s">
+      <c r="AY72" s="28" t="s">
         <v>352</v>
       </c>
       <c r="BC72" t="s">
@@ -8255,10 +8802,10 @@
         <f t="shared" si="2"/>
         <v>covers/flights.jpg</v>
       </c>
-      <c r="AX73" s="25" t="s">
+      <c r="AX73" s="27" t="s">
         <v>357</v>
       </c>
-      <c r="AY73" s="26" t="s">
+      <c r="AY73" s="28" t="s">
         <v>358</v>
       </c>
       <c r="BC73" t="s">
@@ -8309,7 +8856,7 @@
         <f t="shared" si="2"/>
         <v>covers/gestures.jpg</v>
       </c>
-      <c r="AX74" s="25" t="s">
+      <c r="AX74" s="27" t="s">
         <v>409</v>
       </c>
       <c r="BC74" t="s">
@@ -8360,10 +8907,10 @@
         <f t="shared" si="2"/>
         <v>covers/accommodations.jpg</v>
       </c>
-      <c r="AX75" s="25" t="s">
+      <c r="AX75" s="27" t="s">
         <v>412</v>
       </c>
-      <c r="AY75" s="26" t="s">
+      <c r="AY75" s="28" t="s">
         <v>413</v>
       </c>
       <c r="BC75" t="s">
@@ -8414,10 +8961,10 @@
         <f t="shared" si="2"/>
         <v>covers/swallowing-mercury.jpg</v>
       </c>
-      <c r="AX76" s="25" t="s">
+      <c r="AX76" s="27" t="s">
         <v>421</v>
       </c>
-      <c r="AY76" s="26" t="s">
+      <c r="AY76" s="28" t="s">
         <v>420</v>
       </c>
       <c r="BC76" t="s">
@@ -8465,7 +9012,7 @@
         <f t="shared" si="2"/>
         <v>covers/stone-tablets.jpg</v>
       </c>
-      <c r="AX77" s="25" t="s">
+      <c r="AX77" s="27" t="s">
         <v>425</v>
       </c>
       <c r="BC77" t="s">
@@ -8526,10 +9073,10 @@
         <f t="shared" si="2"/>
         <v>covers/beautiful-mrs-seidenman.jpg</v>
       </c>
-      <c r="AX78" s="25" t="s">
+      <c r="AX78" s="27" t="s">
         <v>428</v>
       </c>
-      <c r="AY78" s="26" t="s">
+      <c r="AY78" s="28" t="s">
         <v>429</v>
       </c>
       <c r="BC78" t="s">
@@ -8580,7 +9127,7 @@
         <f t="shared" si="2"/>
         <v>covers/nosegood-investigates.jpg</v>
       </c>
-      <c r="AX79" s="30" t="s">
+      <c r="AX79" s="32" t="s">
         <v>433</v>
       </c>
       <c r="BC79" t="s">
@@ -8631,10 +9178,10 @@
         <f t="shared" si="2"/>
         <v>covers/feed-dictator.jpg</v>
       </c>
-      <c r="AX80" s="25" t="s">
+      <c r="AX80" s="27" t="s">
         <v>442</v>
       </c>
-      <c r="AY80" s="26" t="s">
+      <c r="AY80" s="28" t="s">
         <v>441</v>
       </c>
       <c r="BC80" t="s">
@@ -8685,10 +9232,10 @@
         <f t="shared" si="2"/>
         <v>covers/city-lions.jpg</v>
       </c>
-      <c r="AX81" s="25" t="s">
+      <c r="AX81" s="27" t="s">
         <v>446</v>
       </c>
-      <c r="AY81" s="26" t="s">
+      <c r="AY81" s="28" t="s">
         <v>447</v>
       </c>
       <c r="BC81" t="s">
@@ -8739,10 +9286,10 @@
         <f t="shared" si="2"/>
         <v>covers/roosters-dogs.jpg</v>
       </c>
-      <c r="AX82" s="25" t="s">
+      <c r="AX82" s="27" t="s">
         <v>454</v>
       </c>
-      <c r="AY82" s="26" t="s">
+      <c r="AY82" s="28" t="s">
         <v>455</v>
       </c>
       <c r="BC82" t="s">
@@ -8793,10 +9340,10 @@
         <f t="shared" si="2"/>
         <v>covers/stained-glass.jpg</v>
       </c>
-      <c r="AX83" s="25" t="s">
+      <c r="AX83" s="27" t="s">
         <v>457</v>
       </c>
-      <c r="AY83" s="26" t="s">
+      <c r="AY83" s="28" t="s">
         <v>458</v>
       </c>
       <c r="BC83" t="s">
@@ -8854,10 +9401,10 @@
         <f t="shared" si="2"/>
         <v>covers/ryszard-k-a-life.jpg</v>
       </c>
-      <c r="AX84" s="25" t="s">
+      <c r="AX84" s="27" t="s">
         <v>466</v>
       </c>
-      <c r="AY84" s="26" t="s">
+      <c r="AY84" s="28" t="s">
         <v>467</v>
       </c>
       <c r="BC84" t="s">
@@ -8919,10 +9466,10 @@
         <f t="shared" si="2"/>
         <v>covers/warsaw-tales.jpg</v>
       </c>
-      <c r="AX85" s="25" t="s">
+      <c r="AX85" s="27" t="s">
         <v>470</v>
       </c>
-      <c r="AY85" s="26" t="s">
+      <c r="AY85" s="28" t="s">
         <v>471</v>
       </c>
       <c r="BC85" t="s">
@@ -8973,10 +9520,10 @@
         <f t="shared" si="2"/>
         <v>covers/mohr-missing.jpg</v>
       </c>
-      <c r="AX86" s="25" t="s">
+      <c r="AX86" s="27" t="s">
         <v>482</v>
       </c>
-      <c r="AY86" s="26" t="s">
+      <c r="AY86" s="28" t="s">
         <v>483</v>
       </c>
       <c r="BC86" t="s">
@@ -9033,10 +9580,10 @@
         <f t="shared" si="2"/>
         <v>covers/cooking-kremlin.jpg</v>
       </c>
-      <c r="AX87" s="25" t="s">
+      <c r="AX87" s="27" t="s">
         <v>488</v>
       </c>
-      <c r="AY87" s="26" t="s">
+      <c r="AY87" s="28" t="s">
         <v>487</v>
       </c>
       <c r="BC87" t="s">
@@ -9087,7 +9634,7 @@
         <f t="shared" si="2"/>
         <v>covers/matt-the-first.jpg</v>
       </c>
-      <c r="AX88" s="25" t="s">
+      <c r="AX88" s="27" t="s">
         <v>492</v>
       </c>
       <c r="BC88" t="s">
@@ -9137,10 +9684,10 @@
         <f t="shared" si="2"/>
         <v>covers/kaytek-wizard.jpg</v>
       </c>
-      <c r="AX89" s="25" t="s">
+      <c r="AX89" s="27" t="s">
         <v>497</v>
       </c>
-      <c r="AY89" s="26" t="s">
+      <c r="AY89" s="28" t="s">
         <v>498</v>
       </c>
       <c r="BC89" t="s">
@@ -9191,10 +9738,10 @@
         <f t="shared" si="2"/>
         <v>covers/miron-memoir.jpg</v>
       </c>
-      <c r="AX90" s="25" t="s">
+      <c r="AX90" s="27" t="s">
         <v>504</v>
       </c>
-      <c r="AY90" s="26" t="s">
+      <c r="AY90" s="28" t="s">
         <v>503</v>
       </c>
       <c r="BC90" t="s">
@@ -9242,10 +9789,10 @@
         <f t="shared" si="2"/>
         <v>covers/inhuman-land.jpg</v>
       </c>
-      <c r="AX91" s="25" t="s">
+      <c r="AX91" s="27" t="s">
         <v>511</v>
       </c>
-      <c r="AY91" s="26" t="s">
+      <c r="AY91" s="28" t="s">
         <v>510</v>
       </c>
       <c r="BC91" t="s">
@@ -9297,10 +9844,10 @@
         <f t="shared" si="2"/>
         <v>covers/mud-sweeter.jpg</v>
       </c>
-      <c r="AX92" s="28" t="s">
+      <c r="AX92" s="30" t="s">
         <v>477</v>
       </c>
-      <c r="AY92" s="26" t="s">
+      <c r="AY92" s="28" t="s">
         <v>476</v>
       </c>
       <c r="BC92" t="s">
@@ -9352,10 +9899,10 @@
         <f t="shared" si="2"/>
         <v>covers/house-of-day.jpg</v>
       </c>
-      <c r="AX93" s="25" t="s">
+      <c r="AX93" s="27" t="s">
         <v>515</v>
       </c>
-      <c r="AY93" s="26" t="s">
+      <c r="AY93" s="28" t="s">
         <v>514</v>
       </c>
       <c r="BC93" t="s">
@@ -9407,10 +9954,10 @@
         <f t="shared" si="2"/>
         <v>covers/garden-memory.jpg</v>
       </c>
-      <c r="AX94" s="25" t="s">
+      <c r="AX94" s="27" t="s">
         <v>519</v>
       </c>
-      <c r="AY94" s="26" t="s">
+      <c r="AY94" s="28" t="s">
         <v>520</v>
       </c>
       <c r="BC94" t="s">
@@ -9464,10 +10011,10 @@
       <c r="AI95">
         <v>2014</v>
       </c>
-      <c r="AX95" s="25" t="s">
+      <c r="AX95" s="27" t="s">
         <v>527</v>
       </c>
-      <c r="AY95" s="26" t="s">
+      <c r="AY95" s="28" t="s">
         <v>528</v>
       </c>
       <c r="BC95" t="s">
@@ -9532,10 +10079,10 @@
       <c r="AI96">
         <v>2014</v>
       </c>
-      <c r="AX96" s="25" t="s">
+      <c r="AX96" s="27" t="s">
         <v>532</v>
       </c>
-      <c r="AY96" s="26" t="s">
+      <c r="AY96" s="28" t="s">
         <v>531</v>
       </c>
       <c r="BC96" t="s">
@@ -9597,10 +10144,10 @@
         <f t="shared" si="2"/>
         <v>covers/beautiful-twentysomethings.jpg</v>
       </c>
-      <c r="AX97" s="25" t="s">
+      <c r="AX97" s="27" t="s">
         <v>537</v>
       </c>
-      <c r="AY97" s="26" t="s">
+      <c r="AY97" s="28" t="s">
         <v>536</v>
       </c>
       <c r="BC97" t="s">
@@ -9659,10 +10206,10 @@
         <f t="shared" si="2"/>
         <v>covers/laras-wars.jpg</v>
       </c>
-      <c r="AX98" s="25" t="s">
+      <c r="AX98" s="27" t="s">
         <v>544</v>
       </c>
-      <c r="AY98" s="26" t="s">
+      <c r="AY98" s="28" t="s">
         <v>543</v>
       </c>
       <c r="BC98" t="s">
@@ -9721,13 +10268,13 @@
         <v>9781644213766</v>
       </c>
       <c r="AH99" t="str">
-        <f t="shared" ref="AH99:AH121" si="5">"covers/" &amp; A99 &amp; ".jpg"</f>
+        <f t="shared" ref="AH99:AH148" si="5">"covers/" &amp; A99 &amp; ".jpg"</f>
         <v>covers/little-beauty.jpg</v>
       </c>
-      <c r="AX99" s="25" t="s">
+      <c r="AX99" s="27" t="s">
         <v>548</v>
       </c>
-      <c r="AY99" s="26" t="s">
+      <c r="AY99" s="28" t="s">
         <v>547</v>
       </c>
       <c r="BC99" t="s">
@@ -9789,10 +10336,10 @@
         <f t="shared" si="5"/>
         <v>covers/lectures-proust.jpg</v>
       </c>
-      <c r="AX100" s="25" t="s">
+      <c r="AX100" s="27" t="s">
         <v>552</v>
       </c>
-      <c r="AY100" s="26" t="s">
+      <c r="AY100" s="28" t="s">
         <v>553</v>
       </c>
       <c r="BC100" t="s">
@@ -9854,10 +10401,10 @@
         <f t="shared" si="5"/>
         <v>covers/Starobielsk-essays.jpg</v>
       </c>
-      <c r="AX101" s="25" t="s">
+      <c r="AX101" s="27" t="s">
         <v>559</v>
       </c>
-      <c r="AY101" s="26" t="s">
+      <c r="AY101" s="28" t="s">
         <v>558</v>
       </c>
       <c r="BC101" t="s">
@@ -9931,10 +10478,10 @@
         <f t="shared" si="5"/>
         <v>covers/jedwabne-crime.jpg</v>
       </c>
-      <c r="AX102" s="25" t="s">
+      <c r="AX102" s="27" t="s">
         <v>560</v>
       </c>
-      <c r="AY102" s="26" t="s">
+      <c r="AY102" s="28" t="s">
         <v>561</v>
       </c>
       <c r="BC102" t="s">
@@ -9996,10 +10543,10 @@
         <f t="shared" si="5"/>
         <v>covers/ginczanka-firebird.jpg</v>
       </c>
-      <c r="AX103" s="25" t="s">
+      <c r="AX103" s="27" t="s">
         <v>570</v>
       </c>
-      <c r="AY103" s="26" t="s">
+      <c r="AY103" s="28" t="s">
         <v>569</v>
       </c>
       <c r="BC103" t="s">
@@ -10061,10 +10608,10 @@
         <f t="shared" si="5"/>
         <v>covers/life-grows.jpg</v>
       </c>
-      <c r="AX104" s="25" t="s">
+      <c r="AX104" s="27" t="s">
         <v>575</v>
       </c>
-      <c r="AY104" s="26" t="s">
+      <c r="AY104" s="28" t="s">
         <v>576</v>
       </c>
       <c r="BC104" t="s">
@@ -10125,7 +10672,7 @@
         <f t="shared" si="5"/>
         <v>covers/voracious.jpg</v>
       </c>
-      <c r="AX105" s="25" t="s">
+      <c r="AX105" s="27" t="s">
         <v>578</v>
       </c>
       <c r="BC105" t="s">
@@ -10187,10 +10734,10 @@
         <f t="shared" si="5"/>
         <v>covers/lala.jpg</v>
       </c>
-      <c r="AX106" s="25" t="s">
+      <c r="AX106" s="27" t="s">
         <v>587</v>
       </c>
-      <c r="AY106" s="26" t="s">
+      <c r="AY106" s="28" t="s">
         <v>585</v>
       </c>
       <c r="BC106" t="s">
@@ -10252,10 +10799,10 @@
         <f t="shared" si="5"/>
         <v>covers/dancing-bears.jpg</v>
       </c>
-      <c r="AX107" s="25" t="s">
+      <c r="AX107" s="27" t="s">
         <v>592</v>
       </c>
-      <c r="AY107" s="26" t="s">
+      <c r="AY107" s="28" t="s">
         <v>591</v>
       </c>
       <c r="BC107" t="s">
@@ -10317,10 +10864,10 @@
         <f t="shared" si="5"/>
         <v>covers/rage.jpg</v>
       </c>
-      <c r="AX108" s="25" t="s">
+      <c r="AX108" s="27" t="s">
         <v>597</v>
       </c>
-      <c r="AY108" s="26" t="s">
+      <c r="AY108" s="28" t="s">
         <v>598</v>
       </c>
       <c r="BC108" t="s">
@@ -10374,10 +10921,10 @@
         <f t="shared" si="5"/>
         <v>covers/grain-truth.jpg</v>
       </c>
-      <c r="AX109" s="25" t="s">
+      <c r="AX109" s="27" t="s">
         <v>603</v>
       </c>
-      <c r="AY109" s="26" t="s">
+      <c r="AY109" s="28" t="s">
         <v>604</v>
       </c>
       <c r="BC109" t="s">
@@ -10456,10 +11003,10 @@
         <f t="shared" si="5"/>
         <v>covers/over-the-bones.jpg</v>
       </c>
-      <c r="AX110" s="25" t="s">
+      <c r="AX110" s="27" t="s">
         <v>608</v>
       </c>
-      <c r="AY110" s="26" t="s">
+      <c r="AY110" s="28" t="s">
         <v>648</v>
       </c>
       <c r="BC110" t="s">
@@ -10533,10 +11080,10 @@
         <f t="shared" si="5"/>
         <v>covers/jacobs-books.jpg</v>
       </c>
-      <c r="AX111" s="25" t="s">
+      <c r="AX111" s="27" t="s">
         <v>611</v>
       </c>
-      <c r="AY111" s="26" t="s">
+      <c r="AY111" s="28" t="s">
         <v>612</v>
       </c>
       <c r="BC111" t="s">
@@ -10610,10 +11157,10 @@
         <f t="shared" si="5"/>
         <v>covers/empusium.jpg</v>
       </c>
-      <c r="AX112" s="25" t="s">
+      <c r="AX112" s="27" t="s">
         <v>615</v>
       </c>
-      <c r="AY112" s="26" t="s">
+      <c r="AY112" s="28" t="s">
         <v>616</v>
       </c>
       <c r="BC112" t="s">
@@ -10675,7 +11222,7 @@
         <f t="shared" si="5"/>
         <v>covers/mr-distinctive.jpg</v>
       </c>
-      <c r="AX113" s="25" t="s">
+      <c r="AX113" s="27" t="s">
         <v>619</v>
       </c>
       <c r="BC113" t="s">
@@ -10737,10 +11284,10 @@
         <f t="shared" si="5"/>
         <v>covers/lost-soul.jpg</v>
       </c>
-      <c r="AX114" s="25" t="s">
+      <c r="AX114" s="27" t="s">
         <v>622</v>
       </c>
-      <c r="AY114" s="26" t="s">
+      <c r="AY114" s="28" t="s">
         <v>621</v>
       </c>
       <c r="BC114" t="s">
@@ -10799,7 +11346,7 @@
         <f t="shared" si="5"/>
         <v>covers/torn-curtain.jpg</v>
       </c>
-      <c r="AX115" s="25" t="s">
+      <c r="AX115" s="27" t="s">
         <v>628</v>
       </c>
       <c r="BC115" t="s">
@@ -10868,7 +11415,7 @@
         <f t="shared" si="5"/>
         <v>covers/on-niemen.jpg</v>
       </c>
-      <c r="AX116" s="25" t="s">
+      <c r="AX116" s="27" t="s">
         <v>636</v>
       </c>
       <c r="BC116" t="s">
@@ -10931,10 +11478,10 @@
         <f t="shared" si="5"/>
         <v>covers/marta.jpg</v>
       </c>
-      <c r="AX117" s="25" t="s">
+      <c r="AX117" s="27" t="s">
         <v>641</v>
       </c>
-      <c r="AY117" s="26" t="s">
+      <c r="AY117" s="28" t="s">
         <v>637</v>
       </c>
       <c r="BC117" t="s">
@@ -10982,7 +11529,25 @@
         <f t="shared" si="5"/>
         <v>covers/dedalus-fantasy.jpg</v>
       </c>
-      <c r="AX118" s="25" t="s">
+      <c r="AO118" t="s">
+        <v>716</v>
+      </c>
+      <c r="AP118" t="s">
+        <v>719</v>
+      </c>
+      <c r="AQ118" t="s">
+        <v>715</v>
+      </c>
+      <c r="AR118" t="s">
+        <v>717</v>
+      </c>
+      <c r="AS118" s="25" t="s">
+        <v>720</v>
+      </c>
+      <c r="AT118" t="s">
+        <v>718</v>
+      </c>
+      <c r="AX118" s="27" t="s">
         <v>670</v>
       </c>
       <c r="BC118" t="s">
@@ -11043,10 +11608,10 @@
         <f t="shared" si="5"/>
         <v>covers/dark-domain.jpg</v>
       </c>
-      <c r="AX119" s="30" t="s">
+      <c r="AX119" s="32" t="s">
         <v>678</v>
       </c>
-      <c r="AY119" s="27" t="s">
+      <c r="AY119" s="29" t="s">
         <v>679</v>
       </c>
       <c r="BC119" t="s">
@@ -11062,6 +11627,12 @@
     <row r="120" spans="1:61" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>685</v>
+      </c>
+      <c r="B120" t="s">
+        <v>302</v>
+      </c>
+      <c r="C120">
+        <v>1300</v>
       </c>
       <c r="D120" s="15" t="s">
         <v>646</v>
@@ -11088,7 +11659,7 @@
         <f t="shared" si="5"/>
         <v>covers/mannequins-ball.jpg</v>
       </c>
-      <c r="AX120" s="26" t="s">
+      <c r="AX120" s="28" t="s">
         <v>686</v>
       </c>
       <c r="BC120" t="s">
@@ -11139,10 +11710,10 @@
         <f t="shared" si="5"/>
         <v>covers/conversations-executioner.jpg</v>
       </c>
-      <c r="AX121" s="25" t="s">
+      <c r="AX121" s="27" t="s">
         <v>688</v>
       </c>
-      <c r="AY121" s="26" t="s">
+      <c r="AY121" s="28" t="s">
         <v>692</v>
       </c>
       <c r="BC121" t="s">
@@ -11159,6 +11730,9 @@
       <c r="A122" t="s">
         <v>683</v>
       </c>
+      <c r="B122" t="s">
+        <v>302</v>
+      </c>
       <c r="C122">
         <v>1620</v>
       </c>
@@ -11186,7 +11760,11 @@
       </c>
       <c r="Y122" s="4"/>
       <c r="Z122" s="4"/>
-      <c r="AX122" s="25" t="s">
+      <c r="AH122" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/polish-monsters.jpg</v>
+      </c>
+      <c r="AX122" s="27" t="s">
         <v>681</v>
       </c>
       <c r="BC122" t="s">
@@ -11200,260 +11778,1783 @@
       </c>
     </row>
     <row r="123" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>721</v>
+      </c>
+      <c r="B123" t="s">
+        <v>78</v>
+      </c>
+      <c r="C123">
+        <v>1230</v>
+      </c>
+      <c r="D123" s="15" t="s">
+        <v>722</v>
+      </c>
+      <c r="E123" t="s">
+        <v>431</v>
+      </c>
       <c r="G123" s="6"/>
-      <c r="Q123" s="7"/>
-      <c r="Y123" s="4"/>
-      <c r="Z123" s="4"/>
+      <c r="P123" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q123" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="R123" s="3">
+        <v>12</v>
+      </c>
+      <c r="X123" s="21">
+        <v>9780802134028</v>
+      </c>
+      <c r="Y123" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z123" s="4" t="str">
+        <f>Q123</f>
+        <v>Grove Press</v>
+      </c>
+      <c r="AA123" s="5">
+        <v>12</v>
+      </c>
+      <c r="AG123" s="8">
+        <v>9780802162267</v>
+      </c>
+      <c r="AH123" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/mass-arras.jpg</v>
+      </c>
+      <c r="AX123" s="27" t="s">
+        <v>724</v>
+      </c>
+      <c r="AY123" s="28" t="s">
+        <v>723</v>
+      </c>
+      <c r="BC123" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD123" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF123" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="124" spans="1:61" x14ac:dyDescent="0.25">
-      <c r="G124" s="6"/>
-      <c r="Q124" s="7"/>
-      <c r="Y124" s="4"/>
-      <c r="Z124" s="4"/>
+      <c r="A124" t="s">
+        <v>725</v>
+      </c>
+      <c r="B124" t="s">
+        <v>78</v>
+      </c>
+      <c r="C124">
+        <v>1380</v>
+      </c>
+      <c r="D124" s="15" t="s">
+        <v>726</v>
+      </c>
+      <c r="E124" t="s">
+        <v>142</v>
+      </c>
+      <c r="F124" t="s">
+        <v>143</v>
+      </c>
+      <c r="G124" s="6" t="str">
+        <f>G117</f>
+        <v>Hardcover</v>
+      </c>
+      <c r="H124" s="7" t="s">
+        <v>727</v>
+      </c>
+      <c r="I124" s="7">
+        <v>48</v>
+      </c>
+      <c r="O124" s="10">
+        <v>9781782274704</v>
+      </c>
+      <c r="P124" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q124" s="7" t="str">
+        <f>H124</f>
+        <v>Pushkin Prress</v>
+      </c>
+      <c r="R124" s="3">
+        <v>15</v>
+      </c>
+      <c r="X124" s="21">
+        <v>9781782274728</v>
+      </c>
+      <c r="Y124" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z124" s="4" t="str">
+        <f>Q124</f>
+        <v>Pushkin Prress</v>
+      </c>
+      <c r="AA124" s="5">
+        <v>11.14</v>
+      </c>
+      <c r="AG124" s="8">
+        <v>9781782274711</v>
+      </c>
+      <c r="AH124" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/salt-earth.jpg</v>
+      </c>
+      <c r="AX124" s="27" t="s">
+        <v>729</v>
+      </c>
+      <c r="AY124" s="28" t="s">
+        <v>728</v>
+      </c>
+      <c r="BC124" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD124" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF124" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="125" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>731</v>
+      </c>
+      <c r="B125" t="s">
+        <v>743</v>
+      </c>
+      <c r="C125">
+        <v>1450</v>
+      </c>
+      <c r="D125" s="15" t="s">
+        <v>732</v>
+      </c>
+      <c r="E125" t="s">
+        <v>749</v>
+      </c>
+      <c r="F125" t="s">
+        <v>730</v>
+      </c>
       <c r="G125" s="6"/>
-      <c r="Q125" s="7"/>
+      <c r="P125" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q125" s="7" t="s">
+        <v>733</v>
+      </c>
+      <c r="R125" s="3">
+        <v>20</v>
+      </c>
+      <c r="X125" s="21">
+        <v>9780966615265</v>
+      </c>
       <c r="Y125" s="4"/>
       <c r="Z125" s="4"/>
+      <c r="AH125" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/7-plays.jpg</v>
+      </c>
+      <c r="AX125" s="27" t="s">
+        <v>734</v>
+      </c>
+      <c r="AY125" s="28" t="s">
+        <v>735</v>
+      </c>
+      <c r="BC125" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD125" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF125" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="126" spans="1:61" x14ac:dyDescent="0.25">
-      <c r="G126" s="6"/>
-      <c r="Q126" s="7"/>
-      <c r="Y126" s="4"/>
-      <c r="Z126" s="4"/>
+      <c r="A126" t="s">
+        <v>736</v>
+      </c>
+      <c r="B126" t="s">
+        <v>78</v>
+      </c>
+      <c r="C126">
+        <v>1115</v>
+      </c>
+      <c r="D126" s="15" t="s">
+        <v>737</v>
+      </c>
+      <c r="E126" t="s">
+        <v>431</v>
+      </c>
+      <c r="G126" s="6" t="str">
+        <f>G124</f>
+        <v>Hardcover</v>
+      </c>
+      <c r="H126" s="7" t="str">
+        <f>Q126</f>
+        <v>Grove Press</v>
+      </c>
+      <c r="I126" s="7">
+        <v>10</v>
+      </c>
+      <c r="O126" s="10">
+        <v>9780802115676</v>
+      </c>
+      <c r="P126" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q126" s="7" t="str">
+        <f>Q123</f>
+        <v>Grove Press</v>
+      </c>
+      <c r="R126" s="3">
+        <v>12</v>
+      </c>
+      <c r="X126" s="21">
+        <v>9780802134882</v>
+      </c>
+      <c r="Y126" s="4" t="str">
+        <f>Y124</f>
+        <v>Ebook</v>
+      </c>
+      <c r="Z126" s="4" t="str">
+        <f>Q126</f>
+        <v>Grove Press</v>
+      </c>
+      <c r="AA126" s="5">
+        <v>12</v>
+      </c>
+      <c r="AG126" s="8">
+        <v>9780802162274</v>
+      </c>
+      <c r="AH126" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/self-woman.jpg</v>
+      </c>
+      <c r="AX126" s="27" t="s">
+        <v>738</v>
+      </c>
+      <c r="AY126" s="28" t="s">
+        <v>739</v>
+      </c>
+      <c r="BC126" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD126" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF126" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="127" spans="1:61" x14ac:dyDescent="0.25">
-      <c r="G127" s="6"/>
-      <c r="Q127" s="7"/>
-      <c r="Y127" s="4"/>
-      <c r="Z127" s="4"/>
+      <c r="A127" t="s">
+        <v>741</v>
+      </c>
+      <c r="B127" t="s">
+        <v>743</v>
+      </c>
+      <c r="C127">
+        <v>1200</v>
+      </c>
+      <c r="D127" s="15" t="s">
+        <v>740</v>
+      </c>
+      <c r="E127" t="str">
+        <f>F125</f>
+        <v xml:space="preserve">Daniel Gerould </v>
+      </c>
+      <c r="G127" s="6" t="str">
+        <f>G126</f>
+        <v>Hardcover</v>
+      </c>
+      <c r="H127" s="7" t="str">
+        <f>Q127</f>
+        <v>Routledge</v>
+      </c>
+      <c r="I127" s="7">
+        <v>127</v>
+      </c>
+      <c r="O127" s="10">
+        <v>9780415275040</v>
+      </c>
+      <c r="P127" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q127" s="7" t="s">
+        <v>244</v>
+      </c>
+      <c r="R127" s="3">
+        <v>37</v>
+      </c>
+      <c r="X127" s="21">
+        <v>9780415866354</v>
+      </c>
+      <c r="Y127" s="4" t="str">
+        <f>Y126</f>
+        <v>Ebook</v>
+      </c>
+      <c r="Z127" s="4" t="str">
+        <f>Q127</f>
+        <v>Routledge</v>
+      </c>
+      <c r="AA127" s="5">
+        <v>29</v>
+      </c>
+      <c r="AG127" s="8">
+        <v>9781136474781</v>
+      </c>
+      <c r="AH127" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/green-goose.jpg</v>
+      </c>
+      <c r="AX127" s="27" t="s">
+        <v>742</v>
+      </c>
+      <c r="BC127" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD127" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF127" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="128" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>746</v>
+      </c>
+      <c r="B128" t="s">
+        <v>743</v>
+      </c>
+      <c r="C128">
+        <v>1210</v>
+      </c>
+      <c r="D128" s="15" t="s">
+        <v>744</v>
+      </c>
+      <c r="E128" t="s">
+        <v>745</v>
+      </c>
+      <c r="F128" t="str">
+        <f>F125</f>
+        <v xml:space="preserve">Daniel Gerould </v>
+      </c>
       <c r="G128" s="6"/>
-      <c r="Q128" s="7"/>
+      <c r="P128" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q128" s="7" t="str">
+        <f>Q126</f>
+        <v>Grove Press</v>
+      </c>
+      <c r="R128" s="3">
+        <v>18</v>
+      </c>
+      <c r="X128" s="21">
+        <v>9780802140661</v>
+      </c>
       <c r="Y128" s="4"/>
       <c r="Z128" s="4"/>
-    </row>
-    <row r="129" spans="7:26" x14ac:dyDescent="0.25">
+      <c r="AH128" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/mrozek-reader.jpg</v>
+      </c>
+      <c r="AX128" s="27" t="s">
+        <v>747</v>
+      </c>
+      <c r="BC128" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD128" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF128" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="129" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>751</v>
+      </c>
+      <c r="B129" t="s">
+        <v>743</v>
+      </c>
+      <c r="C129">
+        <v>1205</v>
+      </c>
+      <c r="D129" s="15" t="s">
+        <v>748</v>
+      </c>
+      <c r="E129" t="s">
+        <v>749</v>
+      </c>
+      <c r="F129" t="str">
+        <f>F128</f>
+        <v xml:space="preserve">Daniel Gerould </v>
+      </c>
       <c r="G129" s="6"/>
-      <c r="Q129" s="7"/>
+      <c r="P129" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q129" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="R129" s="3">
+        <v>35</v>
+      </c>
+      <c r="X129" s="21">
+        <v>9780810109940</v>
+      </c>
       <c r="Y129" s="4"/>
       <c r="Z129" s="4"/>
-    </row>
-    <row r="130" spans="7:26" x14ac:dyDescent="0.25">
-      <c r="G130" s="6"/>
-      <c r="Q130" s="7"/>
+      <c r="AH129" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/witkacy-reader.jpg</v>
+      </c>
+      <c r="AX129" s="27" t="s">
+        <v>750</v>
+      </c>
+      <c r="BC129" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD129" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF129" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="130" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>755</v>
+      </c>
+      <c r="B130" t="s">
+        <v>74</v>
+      </c>
+      <c r="C130">
+        <v>1102</v>
+      </c>
+      <c r="D130" s="15" t="s">
+        <v>752</v>
+      </c>
+      <c r="E130" t="s">
+        <v>754</v>
+      </c>
+      <c r="F130" t="s">
+        <v>753</v>
+      </c>
+      <c r="G130" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H130" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="I130" s="7">
+        <v>60</v>
+      </c>
+      <c r="O130" s="10">
+        <v>9780810122031</v>
+      </c>
+      <c r="P130" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q130" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="R130" s="3">
+        <v>30</v>
+      </c>
+      <c r="X130" s="21">
+        <v>9780810129603</v>
+      </c>
       <c r="Y130" s="4"/>
       <c r="Z130" s="4"/>
-    </row>
-    <row r="131" spans="7:26" x14ac:dyDescent="0.25">
-      <c r="G131" s="6"/>
-      <c r="Q131" s="7"/>
+      <c r="AH130" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/borowski-letters.jpg</v>
+      </c>
+      <c r="AX130" s="27" t="s">
+        <v>756</v>
+      </c>
+      <c r="BC130" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD130" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF130" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="131" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>760</v>
+      </c>
+      <c r="B131" t="s">
+        <v>78</v>
+      </c>
+      <c r="C131">
+        <v>1207</v>
+      </c>
+      <c r="D131" s="15" t="s">
+        <v>757</v>
+      </c>
+      <c r="E131" t="s">
+        <v>758</v>
+      </c>
+      <c r="F131" t="s">
+        <v>763</v>
+      </c>
+      <c r="P131" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q131" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="R131" s="3">
+        <v>22</v>
+      </c>
+      <c r="X131" s="21">
+        <v>9780810115194</v>
+      </c>
       <c r="Y131" s="4"/>
       <c r="Z131" s="4"/>
-    </row>
-    <row r="132" spans="7:26" x14ac:dyDescent="0.25">
-      <c r="G132" s="6"/>
-      <c r="Q132" s="7"/>
-      <c r="Y132" s="4"/>
-      <c r="Z132" s="4"/>
-    </row>
-    <row r="133" spans="7:26" x14ac:dyDescent="0.25">
+      <c r="AH131" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/ashes-diamonds.jpg</v>
+      </c>
+      <c r="AX131" s="27" t="s">
+        <v>759</v>
+      </c>
+      <c r="BC131" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD131" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF131" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="132" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>762</v>
+      </c>
+      <c r="B132" t="s">
+        <v>78</v>
+      </c>
+      <c r="C132">
+        <v>1209</v>
+      </c>
+      <c r="D132" s="15" t="s">
+        <v>761</v>
+      </c>
+      <c r="E132" t="s">
+        <v>772</v>
+      </c>
+      <c r="G132" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H132" s="7" t="s">
+        <v>640</v>
+      </c>
+      <c r="I132" s="7">
+        <v>40</v>
+      </c>
+      <c r="O132" s="10">
+        <v>9780821417157</v>
+      </c>
+      <c r="P132" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q132" s="7" t="str">
+        <f>H132</f>
+        <v>Ohio Press University</v>
+      </c>
+      <c r="R132" s="3">
+        <v>22</v>
+      </c>
+      <c r="X132" s="21">
+        <v>9780821417164</v>
+      </c>
+      <c r="Y132" s="4" t="str">
+        <f>Y127</f>
+        <v>Ebook</v>
+      </c>
+      <c r="Z132" s="4" t="str">
+        <f>Q132</f>
+        <v>Ohio Press University</v>
+      </c>
+      <c r="AA132" s="5">
+        <v>22</v>
+      </c>
+      <c r="AG132" s="8">
+        <v>9780821442203</v>
+      </c>
+      <c r="AH132" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/holy-week.jpg</v>
+      </c>
+      <c r="AX132" s="27" t="s">
+        <v>765</v>
+      </c>
+      <c r="AY132" s="28" t="s">
+        <v>764</v>
+      </c>
+      <c r="BC132" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD132" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF132" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="133" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>767</v>
+      </c>
+      <c r="B133" t="s">
+        <v>743</v>
+      </c>
+      <c r="C133">
+        <v>1402</v>
+      </c>
+      <c r="D133" s="15" t="s">
+        <v>766</v>
+      </c>
+      <c r="E133" t="s">
+        <v>749</v>
+      </c>
       <c r="G133" s="6"/>
-      <c r="Q133" s="7"/>
-      <c r="Y133" s="4"/>
-      <c r="Z133" s="4"/>
-    </row>
-    <row r="134" spans="7:26" x14ac:dyDescent="0.25">
-      <c r="G134" s="6"/>
+      <c r="P133" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q133" s="7" t="s">
+        <v>768</v>
+      </c>
+      <c r="R133" s="3">
+        <v>15</v>
+      </c>
+      <c r="X133" s="21">
+        <v>9780936839837</v>
+      </c>
+      <c r="Y133" s="4" t="str">
+        <f>Y132</f>
+        <v>Ebook</v>
+      </c>
+      <c r="Z133" s="4" t="str">
+        <f>Q133</f>
+        <v>Applause</v>
+      </c>
+      <c r="AA133" s="5">
+        <v>14</v>
+      </c>
+      <c r="AG133" s="8">
+        <v>9781617745591</v>
+      </c>
+      <c r="AH133" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/witkacy-3-plays.jpg</v>
+      </c>
+      <c r="AX133" s="27" t="s">
+        <v>769</v>
+      </c>
+      <c r="BC133" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD133" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF133" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="134" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>771</v>
+      </c>
+      <c r="B134" t="s">
+        <v>78</v>
+      </c>
+      <c r="C134">
+        <v>550</v>
+      </c>
+      <c r="D134" s="15" t="s">
+        <v>770</v>
+      </c>
+      <c r="E134" t="s">
+        <v>754</v>
+      </c>
+      <c r="F134" t="s">
+        <v>773</v>
+      </c>
+      <c r="G134" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H134" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="I134" s="7">
+        <v>26</v>
+      </c>
+      <c r="O134" s="10">
+        <v>9780300116908</v>
+      </c>
+      <c r="P134" s="2"/>
       <c r="Q134" s="7"/>
-      <c r="Y134" s="4"/>
-      <c r="Z134" s="4"/>
-    </row>
-    <row r="135" spans="7:26" x14ac:dyDescent="0.25">
-      <c r="G135" s="6"/>
-      <c r="Q135" s="7"/>
+      <c r="Y134" s="4" t="str">
+        <f>Y133</f>
+        <v>Ebook</v>
+      </c>
+      <c r="Z134" s="4" t="str">
+        <f>H134</f>
+        <v>Yale University Press</v>
+      </c>
+      <c r="AA134" s="5">
+        <v>15</v>
+      </c>
+      <c r="AG134" s="8">
+        <v>9780300160208</v>
+      </c>
+      <c r="AH134" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/here-in-our.jpg</v>
+      </c>
+      <c r="AX134" s="27" t="s">
+        <v>774</v>
+      </c>
+      <c r="AY134" s="28" t="s">
+        <v>775</v>
+      </c>
+      <c r="BC134" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD134" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF134" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="135" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>780</v>
+      </c>
+      <c r="B135" t="s">
+        <v>74</v>
+      </c>
+      <c r="C135">
+        <v>850</v>
+      </c>
+      <c r="D135" s="15" t="s">
+        <v>776</v>
+      </c>
+      <c r="E135" t="s">
+        <v>128</v>
+      </c>
+      <c r="F135" t="s">
+        <v>777</v>
+      </c>
+      <c r="G135" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H135" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="I135" s="7">
+        <v>23</v>
+      </c>
+      <c r="O135" s="10">
+        <v>9780374258900</v>
+      </c>
+      <c r="P135" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q135" s="7" t="str">
+        <f>H135</f>
+        <v>Farrar, Strauss and Giroux</v>
+      </c>
+      <c r="R135" s="3">
+        <v>14</v>
+      </c>
+      <c r="X135" s="21">
+        <v>9780374528591</v>
+      </c>
       <c r="Y135" s="4"/>
       <c r="Z135" s="4"/>
-    </row>
-    <row r="136" spans="7:26" x14ac:dyDescent="0.25">
-      <c r="G136" s="6"/>
-      <c r="Q136" s="7"/>
-      <c r="Y136" s="4"/>
-      <c r="Z136" s="4"/>
-    </row>
-    <row r="137" spans="7:26" x14ac:dyDescent="0.25">
-      <c r="G137" s="6"/>
+      <c r="AH135" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/to-begin-where.jpg</v>
+      </c>
+      <c r="AX135" s="27" t="s">
+        <v>778</v>
+      </c>
+      <c r="AY135" s="28" t="s">
+        <v>779</v>
+      </c>
+      <c r="BC135" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD135" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF135" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="136" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>781</v>
+      </c>
+      <c r="B136" t="s">
+        <v>74</v>
+      </c>
+      <c r="C136">
+        <v>992</v>
+      </c>
+      <c r="D136" s="15" t="s">
+        <v>782</v>
+      </c>
+      <c r="E136" t="s">
+        <v>783</v>
+      </c>
+      <c r="G136" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H136" s="7" t="s">
+        <v>784</v>
+      </c>
+      <c r="I136" s="7">
+        <v>100</v>
+      </c>
+      <c r="O136" s="10">
+        <v>9780739175903</v>
+      </c>
+      <c r="P136" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q136" s="7" t="str">
+        <f>H136</f>
+        <v>Lexington Books</v>
+      </c>
+      <c r="R136" s="3">
+        <v>57</v>
+      </c>
+      <c r="X136" s="21">
+        <v>9781498556330</v>
+      </c>
+      <c r="Y136" s="4" t="str">
+        <f>Y134</f>
+        <v>Ebook</v>
+      </c>
+      <c r="Z136" s="4" t="str">
+        <f>Q136</f>
+        <v>Lexington Books</v>
+      </c>
+      <c r="AA136" s="5">
+        <v>54</v>
+      </c>
+      <c r="AG136" s="8">
+        <v>9780739175910</v>
+      </c>
+      <c r="AH136" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/melchior-w.jpg</v>
+      </c>
+      <c r="AX136" s="27" t="s">
+        <v>786</v>
+      </c>
+      <c r="AY136" s="28" t="s">
+        <v>785</v>
+      </c>
+      <c r="BC136" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD136" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF136" t="s">
+        <v>30</v>
+      </c>
+      <c r="BH136" t="s">
+        <v>852</v>
+      </c>
+      <c r="BI136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>789</v>
+      </c>
+      <c r="B137" t="s">
+        <v>87</v>
+      </c>
+      <c r="C137">
+        <v>903</v>
+      </c>
+      <c r="D137" t="s">
+        <v>788</v>
+      </c>
+      <c r="E137" s="15" t="s">
+        <v>787</v>
+      </c>
+      <c r="F137" t="s">
+        <v>279</v>
+      </c>
+      <c r="G137" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H137" s="7" t="str">
+        <f>H136</f>
+        <v>Lexington Books</v>
+      </c>
+      <c r="I137" s="7">
+        <v>160</v>
+      </c>
+      <c r="O137" s="10">
+        <v>9781666920215</v>
+      </c>
+      <c r="P137" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="Q137" s="7"/>
-      <c r="Y137" s="4"/>
-      <c r="Z137" s="4"/>
-    </row>
-    <row r="138" spans="7:26" x14ac:dyDescent="0.25">
-      <c r="G138" s="6"/>
+      <c r="Y137" s="4" t="str">
+        <f>Y136</f>
+        <v>Ebook</v>
+      </c>
+      <c r="Z137" s="4" t="str">
+        <f>Z136</f>
+        <v>Lexington Books</v>
+      </c>
+      <c r="AA137" s="5">
+        <v>144</v>
+      </c>
+      <c r="AG137" s="8">
+        <v>9781666920215</v>
+      </c>
+      <c r="AH137" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/monte-cassino.jpg</v>
+      </c>
+      <c r="AX137" s="27" t="s">
+        <v>791</v>
+      </c>
+      <c r="AY137" s="28" t="s">
+        <v>790</v>
+      </c>
+      <c r="BC137" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD137" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF137" t="s">
+        <v>31</v>
+      </c>
+      <c r="BH137" t="s">
+        <v>852</v>
+      </c>
+      <c r="BI137">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>792</v>
+      </c>
+      <c r="B138" t="s">
+        <v>74</v>
+      </c>
+      <c r="C138">
+        <v>1002</v>
+      </c>
+      <c r="D138" s="15" t="s">
+        <v>793</v>
+      </c>
+      <c r="E138" t="s">
+        <v>794</v>
+      </c>
+      <c r="G138" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H138" s="7" t="s">
+        <v>795</v>
+      </c>
+      <c r="I138" s="7">
+        <v>22</v>
+      </c>
+      <c r="O138" s="10">
+        <v>9780393866575</v>
+      </c>
+      <c r="P138" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="Q138" s="7"/>
-      <c r="Y138" s="4"/>
-      <c r="Z138" s="4"/>
-    </row>
-    <row r="139" spans="7:26" x14ac:dyDescent="0.25">
+      <c r="Y138" s="4" t="str">
+        <f>Y137</f>
+        <v>Ebook</v>
+      </c>
+      <c r="Z138" s="4" t="str">
+        <f>H138</f>
+        <v>W. W. Norton and Company</v>
+      </c>
+      <c r="AA138" s="5">
+        <v>16</v>
+      </c>
+      <c r="AG138" s="8">
+        <v>9780393866582</v>
+      </c>
+      <c r="AH138" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/schulz-hijack.jpg</v>
+      </c>
+      <c r="AX138" s="27" t="s">
+        <v>796</v>
+      </c>
+      <c r="AY138" s="28" t="s">
+        <v>797</v>
+      </c>
+      <c r="BC138" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD138" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF138" t="s">
+        <v>30</v>
+      </c>
+      <c r="BH138" t="s">
+        <v>851</v>
+      </c>
+      <c r="BI138">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>798</v>
+      </c>
+      <c r="B139" t="s">
+        <v>78</v>
+      </c>
+      <c r="C139">
+        <v>921</v>
+      </c>
+      <c r="D139" s="15" t="s">
+        <v>799</v>
+      </c>
+      <c r="E139" t="s">
+        <v>800</v>
+      </c>
+      <c r="F139" t="s">
+        <v>801</v>
+      </c>
       <c r="G139" s="6"/>
+      <c r="P139" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="Q139" s="7"/>
+      <c r="R139" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="S139" s="3">
+        <v>8</v>
+      </c>
+      <c r="X139" s="21">
+        <v>9781517543655</v>
+      </c>
       <c r="Y139" s="4"/>
       <c r="Z139" s="4"/>
-    </row>
-    <row r="140" spans="7:26" x14ac:dyDescent="0.25">
+      <c r="AH139" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/cinnamon.jpg</v>
+      </c>
+      <c r="AX139" s="27" t="s">
+        <v>803</v>
+      </c>
+      <c r="BC139" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD139" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF139" t="s">
+        <v>31</v>
+      </c>
+      <c r="BH139" t="s">
+        <v>851</v>
+      </c>
+      <c r="BI139">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="140" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>805</v>
+      </c>
+      <c r="B140" t="s">
+        <v>78</v>
+      </c>
+      <c r="C140">
+        <v>932</v>
+      </c>
+      <c r="D140" s="15" t="s">
+        <v>804</v>
+      </c>
+      <c r="E140" t="str">
+        <f>E134</f>
+        <v>Tadeusz Borowski</v>
+      </c>
+      <c r="F140" t="s">
+        <v>806</v>
+      </c>
       <c r="G140" s="6"/>
+      <c r="P140" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="Q140" s="7"/>
+      <c r="R140" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="S140" s="3">
+        <v>12</v>
+      </c>
+      <c r="X140" s="21">
+        <v>9780140186246</v>
+      </c>
       <c r="Y140" s="4"/>
       <c r="Z140" s="4"/>
-    </row>
-    <row r="141" spans="7:26" x14ac:dyDescent="0.25">
+      <c r="AH140" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/to-the-gas.jpg</v>
+      </c>
+      <c r="AX140" s="27" t="s">
+        <v>808</v>
+      </c>
+      <c r="BC140" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD140" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF140" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="141" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>812</v>
+      </c>
+      <c r="B141" t="s">
+        <v>78</v>
+      </c>
+      <c r="C141">
+        <v>944</v>
+      </c>
+      <c r="D141" s="15" t="s">
+        <v>809</v>
+      </c>
+      <c r="E141" t="str">
+        <f>E139</f>
+        <v>Bruno Schulz</v>
+      </c>
+      <c r="F141" t="s">
+        <v>810</v>
+      </c>
       <c r="G141" s="6"/>
+      <c r="P141" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="Q141" s="7"/>
+      <c r="R141" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="S141" s="3">
+        <v>17</v>
+      </c>
+      <c r="X141" s="21">
+        <v>9780143105145</v>
+      </c>
       <c r="Y141" s="4"/>
       <c r="Z141" s="4"/>
-    </row>
-    <row r="142" spans="7:26" x14ac:dyDescent="0.25">
+      <c r="AH141" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/street-crocodiles.jpg</v>
+      </c>
+      <c r="AX141" s="27" t="s">
+        <v>811</v>
+      </c>
+      <c r="BC141" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD141" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF141" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="142" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>816</v>
+      </c>
+      <c r="B142" t="s">
+        <v>78</v>
+      </c>
+      <c r="C142">
+        <v>945</v>
+      </c>
+      <c r="D142" s="15" t="s">
+        <v>813</v>
+      </c>
+      <c r="E142" t="str">
+        <f>E141</f>
+        <v>Bruno Schulz</v>
+      </c>
+      <c r="F142" t="s">
+        <v>814</v>
+      </c>
       <c r="G142" s="6"/>
+      <c r="P142" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="Q142" s="7"/>
-      <c r="Y142" s="4"/>
-      <c r="Z142" s="4"/>
-    </row>
-    <row r="143" spans="7:26" x14ac:dyDescent="0.25">
+      <c r="R142" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="S142" s="3">
+        <v>11</v>
+      </c>
+      <c r="X142" s="21">
+        <v>9781782277897</v>
+      </c>
+      <c r="Y142" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z142" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="AA142" s="5">
+        <v>11</v>
+      </c>
+      <c r="AG142" s="8">
+        <v>9781782277903</v>
+      </c>
+      <c r="AH142" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/nocturnal-apparitions.jpg</v>
+      </c>
+      <c r="AX142" s="27" t="s">
+        <v>817</v>
+      </c>
+      <c r="AY142" s="28" t="s">
+        <v>818</v>
+      </c>
+      <c r="BC142" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD142" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF142" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="143" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>820</v>
+      </c>
+      <c r="B143" t="s">
+        <v>78</v>
+      </c>
+      <c r="C143">
+        <v>988</v>
+      </c>
+      <c r="D143" s="15" t="s">
+        <v>819</v>
+      </c>
+      <c r="E143" t="str">
+        <f>E133</f>
+        <v>Stanisław Ignacy Witkiewicz</v>
+      </c>
+      <c r="F143" t="s">
+        <v>810</v>
+      </c>
       <c r="G143" s="6"/>
+      <c r="P143" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="Q143" s="7"/>
+      <c r="R143" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="S143" s="3">
+        <v>13</v>
+      </c>
+      <c r="X143" s="21">
+        <v>9780692519554</v>
+      </c>
       <c r="Y143" s="4"/>
       <c r="Z143" s="4"/>
-    </row>
-    <row r="144" spans="7:26" x14ac:dyDescent="0.25">
+      <c r="AH143" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/vahazar.jpg</v>
+      </c>
+      <c r="AX143" s="27" t="s">
+        <v>822</v>
+      </c>
+      <c r="BC143" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD143" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF143" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="144" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>825</v>
+      </c>
+      <c r="B144" t="s">
+        <v>78</v>
+      </c>
+      <c r="C144">
+        <v>989</v>
+      </c>
+      <c r="D144" s="15" t="s">
+        <v>823</v>
+      </c>
+      <c r="E144" t="s">
+        <v>54</v>
+      </c>
+      <c r="F144" t="s">
+        <v>824</v>
+      </c>
       <c r="G144" s="6"/>
+      <c r="P144" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="Q144" s="7"/>
-      <c r="Y144" s="4"/>
-      <c r="Z144" s="4"/>
-    </row>
-    <row r="145" spans="7:26" x14ac:dyDescent="0.25">
+      <c r="R144" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="S144" s="3">
+        <v>12</v>
+      </c>
+      <c r="X144" s="21">
+        <v>9780979123672</v>
+      </c>
+      <c r="Y144" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z144" s="4" t="str">
+        <f>R144</f>
+        <v>Young Poland Revisited</v>
+      </c>
+      <c r="AA144" s="5">
+        <v>4.5</v>
+      </c>
+      <c r="AG144" s="8" t="s">
+        <v>827</v>
+      </c>
+      <c r="AH144" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/women.jpg</v>
+      </c>
+      <c r="AX144" s="27" t="s">
+        <v>828</v>
+      </c>
+      <c r="BC144" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD144" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF144" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="145" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>830</v>
+      </c>
+      <c r="B145" t="s">
+        <v>78</v>
+      </c>
+      <c r="C145">
+        <v>1001</v>
+      </c>
+      <c r="D145" s="15" t="s">
+        <v>829</v>
+      </c>
+      <c r="E145" t="s">
+        <v>54</v>
+      </c>
+      <c r="F145" t="s">
+        <v>831</v>
+      </c>
       <c r="G145" s="6"/>
+      <c r="P145" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="Q145" s="7"/>
-      <c r="Y145" s="4"/>
-      <c r="Z145" s="4"/>
-    </row>
-    <row r="146" spans="7:26" x14ac:dyDescent="0.25">
+      <c r="R145" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="S145" s="3">
+        <v>28</v>
+      </c>
+      <c r="X145" s="21">
+        <v>9780875807409</v>
+      </c>
+      <c r="Y145" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z145" s="4" t="str">
+        <f>R145</f>
+        <v>Northern Illinois University</v>
+      </c>
+      <c r="AA145" s="5">
+        <v>17</v>
+      </c>
+      <c r="AG145" s="26">
+        <v>9781609092016</v>
+      </c>
+      <c r="AH145" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/boundary.jpg</v>
+      </c>
+      <c r="AX145" s="27" t="s">
+        <v>832</v>
+      </c>
+      <c r="AY145" s="28" t="s">
+        <v>833</v>
+      </c>
+      <c r="BC145" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD145" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF145" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="146" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>839</v>
+      </c>
+      <c r="B146" t="s">
+        <v>78</v>
+      </c>
+      <c r="C146">
+        <v>1003</v>
+      </c>
+      <c r="D146" s="15" t="s">
+        <v>834</v>
+      </c>
+      <c r="E146" t="s">
+        <v>54</v>
+      </c>
+      <c r="F146" t="s">
+        <v>837</v>
+      </c>
       <c r="G146" s="6"/>
+      <c r="P146" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="Q146" s="7"/>
+      <c r="R146" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="S146" s="3">
+        <v>12</v>
+      </c>
+      <c r="X146" s="21">
+        <v>9780875807102</v>
+      </c>
       <c r="Y146" s="4"/>
       <c r="Z146" s="4"/>
-    </row>
-    <row r="147" spans="7:26" x14ac:dyDescent="0.25">
-      <c r="G147" s="6"/>
+      <c r="AH146" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/romance-teresa.jpg</v>
+      </c>
+      <c r="AX146" s="27" t="s">
+        <v>836</v>
+      </c>
+      <c r="AY146" s="28" t="s">
+        <v>838</v>
+      </c>
+      <c r="BC146" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD146" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF146" t="s">
+        <v>31</v>
+      </c>
+      <c r="BH146" t="s">
+        <v>850</v>
+      </c>
+      <c r="BI146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>842</v>
+      </c>
+      <c r="B147" t="s">
+        <v>78</v>
+      </c>
+      <c r="C147">
+        <v>1005</v>
+      </c>
+      <c r="D147" s="15" t="s">
+        <v>840</v>
+      </c>
+      <c r="E147" t="s">
+        <v>54</v>
+      </c>
+      <c r="F147" t="s">
+        <v>841</v>
+      </c>
+      <c r="G147" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="H147" s="7" t="str">
+        <f>R147</f>
+        <v>Northwestern University Press</v>
+      </c>
+      <c r="I147" s="7">
+        <v>45</v>
+      </c>
+      <c r="O147" s="10">
+        <v>9780810117426</v>
+      </c>
+      <c r="P147" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="Q147" s="7"/>
+      <c r="R147" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="S147" s="3">
+        <v>15</v>
+      </c>
+      <c r="X147" s="21">
+        <v>9780810117433</v>
+      </c>
       <c r="Y147" s="4"/>
       <c r="Z147" s="4"/>
-    </row>
-    <row r="148" spans="7:26" x14ac:dyDescent="0.25">
+      <c r="AH147" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/medalions.jpg</v>
+      </c>
+      <c r="AX147" s="27" t="s">
+        <v>848</v>
+      </c>
+      <c r="AY147" s="28" t="s">
+        <v>849</v>
+      </c>
+      <c r="BC147" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD147" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF147" t="s">
+        <v>31</v>
+      </c>
+      <c r="BH147" t="s">
+        <v>850</v>
+      </c>
+      <c r="BI147">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="148" spans="1:61" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>846</v>
+      </c>
+      <c r="B148" t="s">
+        <v>74</v>
+      </c>
+      <c r="C148">
+        <v>951</v>
+      </c>
+      <c r="D148" s="15" t="s">
+        <v>843</v>
+      </c>
+      <c r="E148" t="s">
+        <v>844</v>
+      </c>
       <c r="G148" s="6"/>
+      <c r="P148" s="2" t="s">
+        <v>113</v>
+      </c>
       <c r="Q148" s="7"/>
+      <c r="R148" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="S148" s="3">
+        <v>23</v>
+      </c>
+      <c r="X148" s="21">
+        <v>9781910895320</v>
+      </c>
       <c r="Y148" s="4"/>
       <c r="Z148" s="4"/>
-    </row>
-    <row r="149" spans="7:26" x14ac:dyDescent="0.25">
+      <c r="AH148" t="str">
+        <f t="shared" si="5"/>
+        <v>covers/corsets.jpg</v>
+      </c>
+      <c r="AX148" s="27" t="s">
+        <v>847</v>
+      </c>
+      <c r="BC148" t="s">
+        <v>23</v>
+      </c>
+      <c r="BD148" t="s">
+        <v>23</v>
+      </c>
+      <c r="BF148" t="s">
+        <v>30</v>
+      </c>
+      <c r="BH148" t="s">
+        <v>850</v>
+      </c>
+      <c r="BI148">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="149" spans="1:61" x14ac:dyDescent="0.25">
       <c r="G149" s="6"/>
+      <c r="P149" s="2"/>
       <c r="Q149" s="7"/>
       <c r="Y149" s="4"/>
       <c r="Z149" s="4"/>
     </row>
-    <row r="150" spans="7:26" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:61" x14ac:dyDescent="0.25">
       <c r="G150" s="6"/>
+      <c r="P150" s="2"/>
       <c r="Q150" s="7"/>
       <c r="Y150" s="4"/>
       <c r="Z150" s="4"/>
     </row>
-    <row r="151" spans="7:26" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:61" x14ac:dyDescent="0.25">
       <c r="G151" s="6"/>
+      <c r="P151" s="2"/>
       <c r="Q151" s="7"/>
       <c r="Y151" s="4"/>
       <c r="Z151" s="4"/>
     </row>
-    <row r="152" spans="7:26" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:61" x14ac:dyDescent="0.25">
       <c r="G152" s="6"/>
+      <c r="P152" s="2"/>
       <c r="Q152" s="7"/>
       <c r="Y152" s="4"/>
       <c r="Z152" s="4"/>
     </row>
-    <row r="153" spans="7:26" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:61" x14ac:dyDescent="0.25">
       <c r="G153" s="6"/>
+      <c r="P153" s="2"/>
       <c r="Q153" s="7"/>
       <c r="Y153" s="4"/>
       <c r="Z153" s="4"/>
     </row>
-    <row r="154" spans="7:26" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:61" x14ac:dyDescent="0.25">
       <c r="G154" s="6"/>
+      <c r="P154" s="2"/>
       <c r="Q154" s="7"/>
       <c r="Y154" s="4"/>
       <c r="Z154" s="4"/>
     </row>
-    <row r="155" spans="7:26" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:61" x14ac:dyDescent="0.25">
       <c r="G155" s="6"/>
+      <c r="P155" s="2"/>
       <c r="Q155" s="7"/>
       <c r="Z155" s="4"/>
     </row>
-    <row r="156" spans="7:26" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:61" x14ac:dyDescent="0.25">
       <c r="G156" s="6"/>
+      <c r="P156" s="2"/>
       <c r="Q156" s="7"/>
       <c r="Z156" s="4"/>
     </row>
-    <row r="157" spans="7:26" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:61" x14ac:dyDescent="0.25">
       <c r="G157" s="6"/>
+      <c r="P157" s="2"/>
       <c r="Q157" s="7"/>
       <c r="Z157" s="4"/>
     </row>
-    <row r="158" spans="7:26" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:61" x14ac:dyDescent="0.25">
       <c r="G158" s="6"/>
+      <c r="P158" s="2"/>
       <c r="Q158" s="7"/>
       <c r="Z158" s="4"/>
     </row>
-    <row r="159" spans="7:26" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:61" x14ac:dyDescent="0.25">
       <c r="G159" s="6"/>
+      <c r="P159" s="2"/>
       <c r="Q159" s="7"/>
       <c r="Z159" s="4"/>
     </row>
-    <row r="160" spans="7:26" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:61" x14ac:dyDescent="0.25">
       <c r="G160" s="6"/>
+      <c r="P160" s="2"/>
       <c r="Q160" s="7"/>
       <c r="Z160" s="4"/>
     </row>
     <row r="161" spans="7:26" x14ac:dyDescent="0.25">
       <c r="G161" s="6"/>
+      <c r="P161" s="2"/>
       <c r="Q161" s="7"/>
       <c r="Z161" s="4"/>
     </row>
     <row r="162" spans="7:26" x14ac:dyDescent="0.25">
+      <c r="P162" s="2"/>
       <c r="Q162" s="7"/>
       <c r="Z162" s="4"/>
     </row>
     <row r="163" spans="7:26" x14ac:dyDescent="0.25">
+      <c r="P163" s="2"/>
       <c r="Q163" s="7"/>
       <c r="Z163" s="4"/>
     </row>
     <row r="164" spans="7:26" x14ac:dyDescent="0.25">
+      <c r="P164" s="2"/>
       <c r="Q164" s="7"/>
       <c r="Z164" s="4"/>
     </row>
     <row r="165" spans="7:26" x14ac:dyDescent="0.25">
+      <c r="P165" s="2"/>
       <c r="Q165" s="7"/>
       <c r="Z165" s="4"/>
     </row>
     <row r="166" spans="7:26" x14ac:dyDescent="0.25">
+      <c r="P166" s="2"/>
       <c r="Q166" s="7"/>
       <c r="Z166" s="4"/>
     </row>
     <row r="167" spans="7:26" x14ac:dyDescent="0.25">
+      <c r="P167" s="2"/>
       <c r="Q167" s="7"/>
       <c r="Z167" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G50:G57 Z168:Z1048576 O45 AG45 X45 G48 Q168:Q1048576 G162:H1048576 Y155:Y1048576 P123:P1048576" xr:uid="{D2C177B6-092A-4420-B1E2-D1681CD512E9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G50:G57 Z168:Z1048576 O45 AG45 X45 G48 G162:H1048576 Y155:Y1048576 P168:Q1048576" xr:uid="{D2C177B6-092A-4420-B1E2-D1681CD512E9}">
       <formula1>"hardcover, paperback, eBook, audiobook1"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BC1:BD1048576" xr:uid="{F1FB7CD6-B38A-4A39-862C-8A1111411C8C}">

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/the-polish-atheneum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3384" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E9B8C9D-086E-4EEF-87DB-5C66815CC704}"/>
+  <xr:revisionPtr revIDLastSave="3430" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DEAB5FEC-D249-4E06-8ACD-319075EAA374}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2387" uniqueCount="1071">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2394" uniqueCount="1076">
   <si>
     <t>cover</t>
   </si>
@@ -3566,9 +3566,6 @@
     <t>Witkiewicz</t>
   </si>
   <si>
-    <t>Young Adult, Genre Fiction</t>
-  </si>
-  <si>
     <t>Phantoms of Breslau: An Inspector Mock Investigation</t>
   </si>
   <si>
@@ -4298,9 +4295,6 @@
     <t>An Expendable Soul: Life and Love In Siberian Exile 1870</t>
   </si>
   <si>
-    <t>enmperor-julian</t>
-  </si>
-  <si>
     <t>killing-auntie</t>
   </si>
   <si>
@@ -4405,6 +4399,27 @@
   </si>
   <si>
     <t>A former astronaut turned private detective is dispatched to Naples to discover the pattern in a mysterious series of deaths and disappearances occurring at a seaside spa. A Helen and Kurt Wolff Book</t>
+  </si>
+  <si>
+    <t>emperor-julian</t>
+  </si>
+  <si>
+    <t>The Fair Folk and Little Orphan Mary: A Tale about Gnomes</t>
+  </si>
+  <si>
+    <t>Maria Konopnicka</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christopher Adam Zakrzewski </t>
+  </si>
+  <si>
+    <t>little-orphan-mary</t>
+  </si>
+  <si>
+    <t>A classic children’s tale about Gnomes, appealing equally, if not more so, to the adult child. Written in rich, lyrical prose, frequently shifting into the peasant dialect and interspersed with sundry verses and songs, the tale is replete with mytho-folkloric motifs, legends, superstitions, historical and biblical references, magical depictions of natural phenomena, the sunsets, the twilights, the dawns; the changing seasons, the shadows, the colors, the sounds and silences, Poland’s diverse landscape, her fields, forests and mountains, along with her flora and fauna, and realistic descriptions of late 19th-century Polish rural life. Not least among The Fair Folk’s charms is the author’s whimsical sense of humor—a humor that often rises to a level of high hilarity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cherry Orchard </t>
   </si>
 </sst>
 </file>
@@ -4603,7 +4618,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4660,13 +4675,12 @@
     <xf numFmtId="1" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5009,7 +5023,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="29.140625" customWidth="1"/>
-    <col min="2" max="3" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="50.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
     <col min="4" max="4" width="46" style="15" customWidth="1"/>
     <col min="5" max="7" width="46" customWidth="1"/>
     <col min="8" max="10" width="9.140625" style="7"/>
@@ -5027,7 +5042,7 @@
     <col min="46" max="46" width="19.7109375" style="25" customWidth="1"/>
     <col min="47" max="50" width="19.7109375" customWidth="1"/>
     <col min="51" max="51" width="95.85546875" style="34" customWidth="1"/>
-    <col min="52" max="52" width="66.85546875" style="38" customWidth="1"/>
+    <col min="52" max="52" width="66.85546875" style="25" customWidth="1"/>
     <col min="53" max="55" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5051,7 +5066,7 @@
         <v>32</v>
       </c>
       <c r="G1" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="H1" s="6" t="s">
         <v>108</v>
@@ -5185,7 +5200,7 @@
       <c r="AY1" s="34" t="s">
         <v>27</v>
       </c>
-      <c r="AZ1" s="38" t="s">
+      <c r="AZ1" s="25" t="s">
         <v>203</v>
       </c>
       <c r="BA1" t="s">
@@ -5283,7 +5298,7 @@
       <c r="AY2" s="34" t="s">
         <v>323</v>
       </c>
-      <c r="AZ2" s="38" t="s">
+      <c r="AZ2" s="25" t="s">
         <v>324</v>
       </c>
       <c r="BA2" t="s">
@@ -5438,7 +5453,7 @@
       <c r="AY4" s="34" t="s">
         <v>329</v>
       </c>
-      <c r="AZ4" s="40" t="s">
+      <c r="AZ4" s="39" t="s">
         <v>330</v>
       </c>
       <c r="BA4" t="s">
@@ -5503,7 +5518,7 @@
       <c r="AY5" s="34" t="s">
         <v>334</v>
       </c>
-      <c r="AZ5" s="38" t="s">
+      <c r="AZ5" s="25" t="s">
         <v>335</v>
       </c>
       <c r="BD5" t="s">
@@ -5636,7 +5651,7 @@
       <c r="AY7" s="34" t="s">
         <v>337</v>
       </c>
-      <c r="AZ7" s="38" t="s">
+      <c r="AZ7" s="25" t="s">
         <v>338</v>
       </c>
       <c r="BD7" t="s">
@@ -5850,7 +5865,7 @@
       <c r="AY10" s="34" t="s">
         <v>358</v>
       </c>
-      <c r="AZ10" s="38" t="s">
+      <c r="AZ10" s="25" t="s">
         <v>359</v>
       </c>
       <c r="BD10" t="s">
@@ -5909,7 +5924,7 @@
       <c r="AY11" s="34" t="s">
         <v>360</v>
       </c>
-      <c r="AZ11" s="38" t="s">
+      <c r="AZ11" s="25" t="s">
         <v>361</v>
       </c>
       <c r="BD11" t="s">
@@ -6098,7 +6113,7 @@
       <c r="AY14" s="34" t="s">
         <v>364</v>
       </c>
-      <c r="AZ14" s="38" t="s">
+      <c r="AZ14" s="25" t="s">
         <v>365</v>
       </c>
       <c r="BD14" t="s">
@@ -6157,7 +6172,7 @@
       <c r="AY15" s="34" t="s">
         <v>366</v>
       </c>
-      <c r="AZ15" s="38" t="s">
+      <c r="AZ15" s="25" t="s">
         <v>368</v>
       </c>
       <c r="BD15" t="s">
@@ -6216,7 +6231,7 @@
       <c r="AY16" s="34" t="s">
         <v>369</v>
       </c>
-      <c r="AZ16" s="38" t="s">
+      <c r="AZ16" s="25" t="s">
         <v>370</v>
       </c>
       <c r="BD16" t="s">
@@ -6296,7 +6311,7 @@
       <c r="AY17" s="35" t="s">
         <v>376</v>
       </c>
-      <c r="AZ17" s="38" t="s">
+      <c r="AZ17" s="25" t="s">
         <v>692</v>
       </c>
       <c r="BD17" t="s">
@@ -6351,7 +6366,7 @@
       <c r="AY18" s="34" t="s">
         <v>374</v>
       </c>
-      <c r="AZ18" s="38" t="s">
+      <c r="AZ18" s="25" t="s">
         <v>375</v>
       </c>
       <c r="BD18" t="s">
@@ -6642,7 +6657,7 @@
     </row>
     <row r="22" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="B22" t="s">
         <v>74</v>
@@ -6651,7 +6666,7 @@
         <v>621</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E22" t="s">
         <v>77</v>
@@ -6720,7 +6735,7 @@
         <v>covers/herod-king.jpg</v>
       </c>
       <c r="AY22" s="34" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="BE22" t="s">
         <v>23</v>
@@ -6734,7 +6749,7 @@
     </row>
     <row r="23" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="B23" t="s">
         <v>74</v>
@@ -6743,7 +6758,7 @@
         <v>622</v>
       </c>
       <c r="D23" s="14" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="E23" t="s">
         <v>77</v>
@@ -6812,7 +6827,7 @@
         <v>covers/titus-berenice.jpg</v>
       </c>
       <c r="AY23" s="34" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="BE23" t="s">
         <v>23</v>
@@ -6826,7 +6841,7 @@
     </row>
     <row r="24" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="B24" t="s">
         <v>74</v>
@@ -6835,7 +6850,7 @@
         <v>623</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="E24" t="s">
         <v>77</v>
@@ -6904,7 +6919,7 @@
         <v>covers/rome-jerusalem.jpg</v>
       </c>
       <c r="AY24" s="34" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="BE24" t="s">
         <v>23</v>
@@ -6918,7 +6933,7 @@
     </row>
     <row r="25" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="B25" t="s">
         <v>74</v>
@@ -6927,7 +6942,7 @@
         <v>1075</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="E25" t="s">
         <v>77</v>
@@ -6996,7 +7011,7 @@
         <v>covers/constantine.jpg</v>
       </c>
       <c r="AY25" s="34" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="BE25" t="s">
         <v>23</v>
@@ -7010,7 +7025,7 @@
     </row>
     <row r="26" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="B26" t="s">
         <v>74</v>
@@ -7019,7 +7034,7 @@
         <v>1076</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="E26" t="s">
         <v>77</v>
@@ -7088,7 +7103,7 @@
         <v>covers/devils-brood.jpg</v>
       </c>
       <c r="AY26" s="34" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="BE26" t="s">
         <v>23</v>
@@ -7102,7 +7117,7 @@
     </row>
     <row r="27" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>1041</v>
+        <v>1069</v>
       </c>
       <c r="B27" t="s">
         <v>74</v>
@@ -7177,7 +7192,7 @@
       </c>
       <c r="AI27" t="str">
         <f t="shared" si="0"/>
-        <v>covers/enmperor-julian.jpg</v>
+        <v>covers/emperor-julian.jpg</v>
       </c>
       <c r="AY27" s="34" t="s">
         <v>379</v>
@@ -7485,7 +7500,7 @@
     </row>
     <row r="32" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
       <c r="B32" t="s">
         <v>78</v>
@@ -7494,7 +7509,7 @@
         <v>420</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="E32" t="s">
         <v>59</v>
@@ -7535,11 +7550,11 @@
         <v>9782919820139</v>
       </c>
       <c r="Z32" s="4" t="str">
-        <f>Z31</f>
+        <f t="shared" ref="Z32:AA34" si="6">Z31</f>
         <v>Ebook</v>
       </c>
       <c r="AA32" s="4" t="str">
-        <f>AA31</f>
+        <f t="shared" si="6"/>
         <v>Mondrala Press</v>
       </c>
       <c r="AB32" s="5">
@@ -7613,11 +7628,11 @@
         <v>9789998791664</v>
       </c>
       <c r="Z33" s="4" t="str">
-        <f>Z32</f>
+        <f t="shared" si="6"/>
         <v>Ebook</v>
       </c>
       <c r="AA33" s="4" t="str">
-        <f>AA32</f>
+        <f t="shared" si="6"/>
         <v>Mondrala Press</v>
       </c>
       <c r="AB33" s="5">
@@ -7639,7 +7654,7 @@
       <c r="AY33" s="34" t="s">
         <v>205</v>
       </c>
-      <c r="AZ33" s="38" t="s">
+      <c r="AZ33" s="25" t="s">
         <v>208</v>
       </c>
       <c r="BA33" t="s">
@@ -7701,11 +7716,11 @@
       <c r="Q34" s="2"/>
       <c r="R34" s="2"/>
       <c r="Z34" s="4" t="str">
-        <f>Z33</f>
+        <f t="shared" si="6"/>
         <v>Ebook</v>
       </c>
       <c r="AA34" s="4" t="str">
-        <f>AA33</f>
+        <f t="shared" si="6"/>
         <v>Mondrala Press</v>
       </c>
       <c r="AB34" s="5">
@@ -8234,7 +8249,7 @@
       <c r="AY42" s="34" t="s">
         <v>392</v>
       </c>
-      <c r="AZ42" s="38" t="s">
+      <c r="AZ42" s="25" t="s">
         <v>393</v>
       </c>
       <c r="BD42" t="s">
@@ -8285,7 +8300,7 @@
       <c r="AY43" s="34" t="s">
         <v>395</v>
       </c>
-      <c r="AZ43" s="38" t="s">
+      <c r="AZ43" s="25" t="s">
         <v>396</v>
       </c>
       <c r="BD43" t="s">
@@ -8351,7 +8366,7 @@
       <c r="AY44" s="34" t="s">
         <v>397</v>
       </c>
-      <c r="AZ44" s="38" t="s">
+      <c r="AZ44" s="25" t="s">
         <v>398</v>
       </c>
       <c r="BD44" t="s">
@@ -8414,7 +8429,7 @@
       <c r="AY45" s="34" t="s">
         <v>399</v>
       </c>
-      <c r="AZ45" s="38" t="s">
+      <c r="AZ45" s="25" t="s">
         <v>400</v>
       </c>
       <c r="BD45" t="s">
@@ -8726,7 +8741,7 @@
         <v>193</v>
       </c>
       <c r="B51" t="s">
-        <v>853</v>
+        <v>303</v>
       </c>
       <c r="C51">
         <v>1100</v>
@@ -8799,7 +8814,7 @@
         <v>192</v>
       </c>
       <c r="B52" t="s">
-        <v>853</v>
+        <v>303</v>
       </c>
       <c r="C52">
         <v>1200</v>
@@ -8872,7 +8887,7 @@
         <v>191</v>
       </c>
       <c r="B53" t="s">
-        <v>853</v>
+        <v>303</v>
       </c>
       <c r="C53">
         <v>1300</v>
@@ -10099,7 +10114,7 @@
       <c r="AY74" s="34" t="s">
         <v>309</v>
       </c>
-      <c r="AZ74" s="38" t="s">
+      <c r="AZ74" s="25" t="s">
         <v>314</v>
       </c>
       <c r="BA74" t="s">
@@ -10179,7 +10194,7 @@
       <c r="AY75" s="34" t="s">
         <v>321</v>
       </c>
-      <c r="AZ75" s="38" t="s">
+      <c r="AZ75" s="25" t="s">
         <v>314</v>
       </c>
       <c r="BA75" t="s">
@@ -10252,7 +10267,7 @@
         <v>9781589883802</v>
       </c>
       <c r="AI76" t="str">
-        <f t="shared" ref="AI76" si="6">"covers/" &amp; A76 &amp; ".jpg"</f>
+        <f t="shared" ref="AI76" si="7">"covers/" &amp; A76 &amp; ".jpg"</f>
         <v>covers/the-homeless.jpg</v>
       </c>
       <c r="AY76" s="34" t="s">
@@ -10303,13 +10318,13 @@
       <c r="Z77" s="4"/>
       <c r="AA77" s="4"/>
       <c r="AI77" t="str">
-        <f t="shared" ref="AI77:AI104" si="7">"covers/" &amp; A77 &amp; ".jpg"</f>
+        <f t="shared" ref="AI77:AI104" si="8">"covers/" &amp; A77 &amp; ".jpg"</f>
         <v>covers/ferdydurke.jpg</v>
       </c>
       <c r="AY77" s="34" t="s">
         <v>344</v>
       </c>
-      <c r="AZ77" s="38" t="s">
+      <c r="AZ77" s="25" t="s">
         <v>346</v>
       </c>
       <c r="BD77" t="s">
@@ -10357,13 +10372,13 @@
       <c r="Z78" s="4"/>
       <c r="AA78" s="4"/>
       <c r="AI78" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/the-possessed.jpg</v>
       </c>
       <c r="AY78" s="34" t="s">
         <v>347</v>
       </c>
-      <c r="AZ78" s="38" t="s">
+      <c r="AZ78" s="25" t="s">
         <v>351</v>
       </c>
       <c r="BD78" t="s">
@@ -10411,13 +10426,13 @@
       <c r="Z79" s="4"/>
       <c r="AA79" s="4"/>
       <c r="AI79" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/flights.jpg</v>
       </c>
       <c r="AY79" s="34" t="s">
         <v>356</v>
       </c>
-      <c r="AZ79" s="38" t="s">
+      <c r="AZ79" s="25" t="s">
         <v>357</v>
       </c>
       <c r="BD79" t="s">
@@ -10465,7 +10480,7 @@
       <c r="Z80" s="4"/>
       <c r="AA80" s="4"/>
       <c r="AI80" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/gestures.jpg</v>
       </c>
       <c r="AY80" s="34" t="s">
@@ -10516,13 +10531,13 @@
       <c r="Z81" s="4"/>
       <c r="AA81" s="4"/>
       <c r="AI81" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/accommodations.jpg</v>
       </c>
       <c r="AY81" s="34" t="s">
         <v>411</v>
       </c>
-      <c r="AZ81" s="38" t="s">
+      <c r="AZ81" s="25" t="s">
         <v>412</v>
       </c>
       <c r="BD81" t="s">
@@ -10570,13 +10585,13 @@
       <c r="Z82" s="4"/>
       <c r="AA82" s="4"/>
       <c r="AI82" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/swallowing-mercury.jpg</v>
       </c>
       <c r="AY82" s="34" t="s">
         <v>420</v>
       </c>
-      <c r="AZ82" s="38" t="s">
+      <c r="AZ82" s="25" t="s">
         <v>419</v>
       </c>
       <c r="BD82" t="s">
@@ -10621,7 +10636,7 @@
       <c r="Z83" s="4"/>
       <c r="AA83" s="4"/>
       <c r="AI83" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/stone-tablets.jpg</v>
       </c>
       <c r="AY83" s="34" t="s">
@@ -10682,13 +10697,13 @@
         <v>9780802162236</v>
       </c>
       <c r="AI84" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/beautiful-mrs-seidenman.jpg</v>
       </c>
       <c r="AY84" s="34" t="s">
         <v>427</v>
       </c>
-      <c r="AZ84" s="38" t="s">
+      <c r="AZ84" s="25" t="s">
         <v>428</v>
       </c>
       <c r="BD84" t="s">
@@ -10736,7 +10751,7 @@
       <c r="Z85" s="4"/>
       <c r="AA85" s="4"/>
       <c r="AI85" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/nosegood-investigates.jpg</v>
       </c>
       <c r="AY85" s="37" t="s">
@@ -10787,13 +10802,13 @@
       <c r="Z86" s="4"/>
       <c r="AA86" s="4"/>
       <c r="AI86" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/feed-dictator.jpg</v>
       </c>
       <c r="AY86" s="34" t="s">
         <v>441</v>
       </c>
-      <c r="AZ86" s="38" t="s">
+      <c r="AZ86" s="25" t="s">
         <v>440</v>
       </c>
       <c r="BD86" t="s">
@@ -10841,13 +10856,13 @@
       <c r="Z87" s="4"/>
       <c r="AA87" s="4"/>
       <c r="AI87" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/city-lions.jpg</v>
       </c>
       <c r="AY87" s="34" t="s">
         <v>445</v>
       </c>
-      <c r="AZ87" s="38" t="s">
+      <c r="AZ87" s="25" t="s">
         <v>446</v>
       </c>
       <c r="BD87" t="s">
@@ -10895,13 +10910,13 @@
       <c r="Z88" s="4"/>
       <c r="AA88" s="4"/>
       <c r="AI88" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/roosters-dogs.jpg</v>
       </c>
       <c r="AY88" s="34" t="s">
         <v>453</v>
       </c>
-      <c r="AZ88" s="38" t="s">
+      <c r="AZ88" s="25" t="s">
         <v>454</v>
       </c>
       <c r="BD88" t="s">
@@ -10949,13 +10964,13 @@
       <c r="Z89" s="4"/>
       <c r="AA89" s="4"/>
       <c r="AI89" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/stained-glass.jpg</v>
       </c>
       <c r="AY89" s="34" t="s">
         <v>456</v>
       </c>
-      <c r="AZ89" s="38" t="s">
+      <c r="AZ89" s="25" t="s">
         <v>457</v>
       </c>
       <c r="BD89" t="s">
@@ -11010,13 +11025,13 @@
         <v>9781781684061</v>
       </c>
       <c r="AI90" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/ryszard-k-a-life.jpg</v>
       </c>
       <c r="AY90" s="34" t="s">
         <v>465</v>
       </c>
-      <c r="AZ90" s="38" t="s">
+      <c r="AZ90" s="25" t="s">
         <v>466</v>
       </c>
       <c r="BD90" t="s">
@@ -11075,13 +11090,13 @@
         <v>9780192668080</v>
       </c>
       <c r="AI91" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/warsaw-tales.jpg</v>
       </c>
       <c r="AY91" s="34" t="s">
         <v>469</v>
       </c>
-      <c r="AZ91" s="38" t="s">
+      <c r="AZ91" s="25" t="s">
         <v>470</v>
       </c>
       <c r="BD91" t="s">
@@ -11129,13 +11144,13 @@
       <c r="Z92" s="4"/>
       <c r="AA92" s="4"/>
       <c r="AI92" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/mohr-missing.jpg</v>
       </c>
       <c r="AY92" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="AZ92" s="38" t="s">
+      <c r="AZ92" s="25" t="s">
         <v>482</v>
       </c>
       <c r="BD92" t="s">
@@ -11189,13 +11204,13 @@
       <c r="Z93" s="4"/>
       <c r="AA93" s="4"/>
       <c r="AI93" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/cooking-kremlin.jpg</v>
       </c>
       <c r="AY93" s="34" t="s">
         <v>487</v>
       </c>
-      <c r="AZ93" s="38" t="s">
+      <c r="AZ93" s="25" t="s">
         <v>486</v>
       </c>
       <c r="BD93" t="s">
@@ -11243,7 +11258,7 @@
       <c r="Z94" s="4"/>
       <c r="AA94" s="4"/>
       <c r="AI94" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/matt-the-first.jpg</v>
       </c>
       <c r="AY94" s="34" t="s">
@@ -11293,13 +11308,13 @@
       <c r="Z95" s="4"/>
       <c r="AA95" s="4"/>
       <c r="AI95" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/kaytek-wizard.jpg</v>
       </c>
       <c r="AY95" s="34" t="s">
         <v>496</v>
       </c>
-      <c r="AZ95" s="38" t="s">
+      <c r="AZ95" s="25" t="s">
         <v>497</v>
       </c>
       <c r="BD95" t="s">
@@ -11347,13 +11362,13 @@
       <c r="Z96" s="4"/>
       <c r="AA96" s="4"/>
       <c r="AI96" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/miron-memoir.jpg</v>
       </c>
       <c r="AY96" s="34" t="s">
         <v>503</v>
       </c>
-      <c r="AZ96" s="38" t="s">
+      <c r="AZ96" s="25" t="s">
         <v>502</v>
       </c>
       <c r="BD96" t="s">
@@ -11398,13 +11413,13 @@
       <c r="Z97" s="4"/>
       <c r="AA97" s="4"/>
       <c r="AI97" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/inhuman-land.jpg</v>
       </c>
       <c r="AY97" s="34" t="s">
         <v>510</v>
       </c>
-      <c r="AZ97" s="38" t="s">
+      <c r="AZ97" s="25" t="s">
         <v>509</v>
       </c>
       <c r="BD97" t="s">
@@ -11453,13 +11468,13 @@
       <c r="Z98" s="4"/>
       <c r="AA98" s="4"/>
       <c r="AI98" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/mud-sweeter.jpg</v>
       </c>
       <c r="AY98" s="35" t="s">
         <v>476</v>
       </c>
-      <c r="AZ98" s="38" t="s">
+      <c r="AZ98" s="25" t="s">
         <v>475</v>
       </c>
       <c r="BD98" t="s">
@@ -11508,13 +11523,13 @@
       <c r="Z99" s="4"/>
       <c r="AA99" s="4"/>
       <c r="AI99" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/house-of-day.jpg</v>
       </c>
       <c r="AY99" s="34" t="s">
         <v>514</v>
       </c>
-      <c r="AZ99" s="38" t="s">
+      <c r="AZ99" s="25" t="s">
         <v>513</v>
       </c>
       <c r="BD99" t="s">
@@ -11563,13 +11578,13 @@
       <c r="Z100" s="4"/>
       <c r="AA100" s="4"/>
       <c r="AI100" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/garden-memory.jpg</v>
       </c>
       <c r="AY100" s="34" t="s">
         <v>518</v>
       </c>
-      <c r="AZ100" s="38" t="s">
+      <c r="AZ100" s="25" t="s">
         <v>519</v>
       </c>
       <c r="BD100" t="s">
@@ -11617,7 +11632,7 @@
       <c r="Z101" s="4"/>
       <c r="AA101" s="4"/>
       <c r="AI101" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/killing-dog.jpg</v>
       </c>
       <c r="AJ101">
@@ -11626,7 +11641,7 @@
       <c r="AY101" s="34" t="s">
         <v>526</v>
       </c>
-      <c r="AZ101" s="38" t="s">
+      <c r="AZ101" s="25" t="s">
         <v>527</v>
       </c>
       <c r="BD101" t="s">
@@ -11685,7 +11700,7 @@
         <v>9781939931184</v>
       </c>
       <c r="AI102" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/all-backs.jpg</v>
       </c>
       <c r="AJ102">
@@ -11694,7 +11709,7 @@
       <c r="AY102" s="34" t="s">
         <v>531</v>
       </c>
-      <c r="AZ102" s="38" t="s">
+      <c r="AZ102" s="25" t="s">
         <v>530</v>
       </c>
       <c r="BD102" t="s">
@@ -11743,7 +11758,7 @@
         <v>113</v>
       </c>
       <c r="AA103" s="4" t="str">
-        <f t="shared" ref="AA103:AA104" si="8">R103</f>
+        <f t="shared" ref="AA103:AA104" si="9">R103</f>
         <v>Northern Illinois University Press</v>
       </c>
       <c r="AB103" s="5">
@@ -11753,13 +11768,13 @@
         <v>9781609090951</v>
       </c>
       <c r="AI103" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/beautiful-twentysomethings.jpg</v>
       </c>
       <c r="AY103" s="34" t="s">
         <v>536</v>
       </c>
-      <c r="AZ103" s="38" t="s">
+      <c r="AZ103" s="25" t="s">
         <v>535</v>
       </c>
       <c r="BD103" t="s">
@@ -11805,7 +11820,7 @@
         <v>113</v>
       </c>
       <c r="AA104" s="4" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>Seven Stories Press</v>
       </c>
       <c r="AB104" s="5">
@@ -11815,13 +11830,13 @@
         <v>9781644210178</v>
       </c>
       <c r="AI104" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>covers/laras-wars.jpg</v>
       </c>
       <c r="AY104" s="34" t="s">
         <v>543</v>
       </c>
-      <c r="AZ104" s="38" t="s">
+      <c r="AZ104" s="25" t="s">
         <v>542</v>
       </c>
       <c r="BD104" t="s">
@@ -11870,7 +11885,7 @@
         <v>113</v>
       </c>
       <c r="AA105" s="4" t="str">
-        <f t="shared" ref="AA105:AA106" si="9">R105</f>
+        <f t="shared" ref="AA105:AA106" si="10">R105</f>
         <v>Seven Stories Press</v>
       </c>
       <c r="AB105" s="5">
@@ -11880,13 +11895,13 @@
         <v>9781644213766</v>
       </c>
       <c r="AI105" t="str">
-        <f t="shared" ref="AI105:AI133" si="10">"covers/" &amp; A105 &amp; ".jpg"</f>
+        <f t="shared" ref="AI105:AI133" si="11">"covers/" &amp; A105 &amp; ".jpg"</f>
         <v>covers/little-beauty.jpg</v>
       </c>
       <c r="AY105" s="34" t="s">
         <v>547</v>
       </c>
-      <c r="AZ105" s="38" t="s">
+      <c r="AZ105" s="25" t="s">
         <v>546</v>
       </c>
       <c r="BD105" t="s">
@@ -11935,7 +11950,7 @@
         <v>113</v>
       </c>
       <c r="AA106" s="4" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>NYRB Classics</v>
       </c>
       <c r="AB106" s="5">
@@ -11945,13 +11960,13 @@
         <v>9781681372594</v>
       </c>
       <c r="AI106" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/lectures-proust.jpg</v>
       </c>
       <c r="AY106" s="34" t="s">
         <v>551</v>
       </c>
-      <c r="AZ106" s="38" t="s">
+      <c r="AZ106" s="25" t="s">
         <v>552</v>
       </c>
       <c r="BD106" t="s">
@@ -12000,7 +12015,7 @@
         <v>113</v>
       </c>
       <c r="AA107" s="4" t="str">
-        <f t="shared" ref="AA107" si="11">R107</f>
+        <f t="shared" ref="AA107" si="12">R107</f>
         <v>NYRB Classics</v>
       </c>
       <c r="AB107" s="5">
@@ -12010,13 +12025,13 @@
         <v>9781681374871</v>
       </c>
       <c r="AI107" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/Starobielsk-essays.jpg</v>
       </c>
       <c r="AY107" s="34" t="s">
         <v>558</v>
       </c>
-      <c r="AZ107" s="38" t="s">
+      <c r="AZ107" s="25" t="s">
         <v>557</v>
       </c>
       <c r="BD107" t="s">
@@ -12087,13 +12102,13 @@
         <v>9780374710323</v>
       </c>
       <c r="AI108" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/jedwabne-crime.jpg</v>
       </c>
       <c r="AY108" s="34" t="s">
         <v>559</v>
       </c>
-      <c r="AZ108" s="38" t="s">
+      <c r="AZ108" s="25" t="s">
         <v>560</v>
       </c>
       <c r="BD108" t="s">
@@ -12152,13 +12167,13 @@
         <v>9781681377315</v>
       </c>
       <c r="AI109" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/ginczanka-firebird.jpg</v>
       </c>
       <c r="AY109" s="34" t="s">
         <v>569</v>
       </c>
-      <c r="AZ109" s="38" t="s">
+      <c r="AZ109" s="25" t="s">
         <v>568</v>
       </c>
       <c r="BD109" t="s">
@@ -12217,13 +12232,13 @@
         <v>9781681371610</v>
       </c>
       <c r="AI110" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/life-grows.jpg</v>
       </c>
       <c r="AY110" s="34" t="s">
         <v>574</v>
       </c>
-      <c r="AZ110" s="38" t="s">
+      <c r="AZ110" s="25" t="s">
         <v>575</v>
       </c>
       <c r="BD110" t="s">
@@ -12281,7 +12296,7 @@
         <v>9781068740411</v>
       </c>
       <c r="AI111" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/voracious.jpg</v>
       </c>
       <c r="AY111" s="34" t="s">
@@ -12343,13 +12358,13 @@
         <v>9781786073594</v>
       </c>
       <c r="AI112" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/lala.jpg</v>
       </c>
       <c r="AY112" s="34" t="s">
         <v>586</v>
       </c>
-      <c r="AZ112" s="38" t="s">
+      <c r="AZ112" s="25" t="s">
         <v>584</v>
       </c>
       <c r="BD112" t="s">
@@ -12408,13 +12423,13 @@
         <v>9781101993385</v>
       </c>
       <c r="AI113" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/dancing-bears.jpg</v>
       </c>
       <c r="AY113" s="34" t="s">
         <v>591</v>
       </c>
-      <c r="AZ113" s="38" t="s">
+      <c r="AZ113" s="25" t="s">
         <v>590</v>
       </c>
       <c r="BD113" t="s">
@@ -12473,13 +12488,13 @@
         <v>9781503990869</v>
       </c>
       <c r="AI114" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/rage.jpg</v>
       </c>
       <c r="AY114" s="34" t="s">
         <v>596</v>
       </c>
-      <c r="AZ114" s="38" t="s">
+      <c r="AZ114" s="25" t="s">
         <v>597</v>
       </c>
       <c r="BD114" t="s">
@@ -12530,13 +12545,13 @@
       <c r="Z115" s="4"/>
       <c r="AA115" s="4"/>
       <c r="AI115" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/grain-truth.jpg</v>
       </c>
       <c r="AY115" s="34" t="s">
         <v>602</v>
       </c>
-      <c r="AZ115" s="38" t="s">
+      <c r="AZ115" s="25" t="s">
         <v>603</v>
       </c>
       <c r="BD115" t="s">
@@ -12612,13 +12627,13 @@
         <v>9781910695562</v>
       </c>
       <c r="AI116" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/over-the-bones.jpg</v>
       </c>
       <c r="AY116" s="34" t="s">
         <v>607</v>
       </c>
-      <c r="AZ116" s="38" t="s">
+      <c r="AZ116" s="25" t="s">
         <v>647</v>
       </c>
       <c r="BD116" t="s">
@@ -12689,13 +12704,13 @@
         <v>9780593087497</v>
       </c>
       <c r="AI117" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/jacobs-books.jpg</v>
       </c>
       <c r="AY117" s="34" t="s">
         <v>610</v>
       </c>
-      <c r="AZ117" s="38" t="s">
+      <c r="AZ117" s="25" t="s">
         <v>611</v>
       </c>
       <c r="BD117" t="s">
@@ -12766,13 +12781,13 @@
         <v>9781804271094</v>
       </c>
       <c r="AI118" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/empusium.jpg</v>
       </c>
       <c r="AY118" s="34" t="s">
         <v>614</v>
       </c>
-      <c r="AZ118" s="38" t="s">
+      <c r="AZ118" s="25" t="s">
         <v>615</v>
       </c>
       <c r="BD118" t="s">
@@ -12831,7 +12846,7 @@
         <v>9781644214480</v>
       </c>
       <c r="AI119" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/mr-distinctive.jpg</v>
       </c>
       <c r="AY119" s="34" t="s">
@@ -12893,13 +12908,13 @@
         <v>9781644210352</v>
       </c>
       <c r="AI120" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/lost-soul.jpg</v>
       </c>
       <c r="AY120" s="34" t="s">
         <v>621</v>
       </c>
-      <c r="AZ120" s="38" t="s">
+      <c r="AZ120" s="25" t="s">
         <v>620</v>
       </c>
       <c r="BD120" t="s">
@@ -12955,7 +12970,7 @@
         <v>9781786079282</v>
       </c>
       <c r="AI121" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/torn-curtain.jpg</v>
       </c>
       <c r="AY121" s="34" t="s">
@@ -13024,7 +13039,7 @@
         <v>634</v>
       </c>
       <c r="AI122" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/on-niemen.jpg</v>
       </c>
       <c r="AY122" s="34" t="s">
@@ -13088,13 +13103,13 @@
         <v>9780821446294</v>
       </c>
       <c r="AI123" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/marta.jpg</v>
       </c>
       <c r="AY123" s="34" t="s">
         <v>640</v>
       </c>
-      <c r="AZ123" s="38" t="s">
+      <c r="AZ123" s="25" t="s">
         <v>636</v>
       </c>
       <c r="BD123" t="s">
@@ -13139,7 +13154,7 @@
         <v>644</v>
       </c>
       <c r="AI124" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/dedalus-fantasy.jpg</v>
       </c>
       <c r="AP124" t="s">
@@ -13218,13 +13233,13 @@
         <v>9781907650666</v>
       </c>
       <c r="AI125" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/dark-domain.jpg</v>
       </c>
       <c r="AY125" s="37" t="s">
         <v>677</v>
       </c>
-      <c r="AZ125" s="40" t="s">
+      <c r="AZ125" s="39" t="s">
         <v>678</v>
       </c>
       <c r="BD125" t="s">
@@ -13269,10 +13284,10 @@
         <v>9781134425419</v>
       </c>
       <c r="AI126" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/mannequins-ball.jpg</v>
       </c>
-      <c r="AY126" s="38" t="s">
+      <c r="AY126" s="25" t="s">
         <v>685</v>
       </c>
       <c r="BD126" t="s">
@@ -13320,13 +13335,13 @@
       <c r="Z127" s="4"/>
       <c r="AA127" s="4"/>
       <c r="AI127" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/conversations-executioner.jpg</v>
       </c>
       <c r="AY127" s="34" t="s">
         <v>687</v>
       </c>
-      <c r="AZ127" s="38" t="s">
+      <c r="AZ127" s="25" t="s">
         <v>691</v>
       </c>
       <c r="BD127" t="s">
@@ -13374,7 +13389,7 @@
       <c r="Z128" s="4"/>
       <c r="AA128" s="4"/>
       <c r="AI128" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/polish-monsters.jpg</v>
       </c>
       <c r="AY128" s="34" t="s">
@@ -13433,13 +13448,13 @@
         <v>9780802162267</v>
       </c>
       <c r="AI129" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/mass-arras.jpg</v>
       </c>
       <c r="AY129" s="34" t="s">
         <v>723</v>
       </c>
-      <c r="AZ129" s="38" t="s">
+      <c r="AZ129" s="25" t="s">
         <v>722</v>
       </c>
       <c r="BD129" t="s">
@@ -13511,13 +13526,13 @@
         <v>9781782274711</v>
       </c>
       <c r="AI130" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/salt-earth.jpg</v>
       </c>
       <c r="AY130" s="34" t="s">
         <v>728</v>
       </c>
-      <c r="AZ130" s="38" t="s">
+      <c r="AZ130" s="25" t="s">
         <v>727</v>
       </c>
       <c r="BD130" t="s">
@@ -13565,13 +13580,13 @@
       <c r="Z131" s="4"/>
       <c r="AA131" s="4"/>
       <c r="AI131" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/7-plays.jpg</v>
       </c>
       <c r="AY131" s="34" t="s">
         <v>733</v>
       </c>
-      <c r="AZ131" s="38" t="s">
+      <c r="AZ131" s="25" t="s">
         <v>734</v>
       </c>
       <c r="BD131" t="s">
@@ -13642,13 +13657,13 @@
         <v>9780802162274</v>
       </c>
       <c r="AI132" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/self-woman.jpg</v>
       </c>
       <c r="AY132" s="34" t="s">
         <v>737</v>
       </c>
-      <c r="AZ132" s="38" t="s">
+      <c r="AZ132" s="25" t="s">
         <v>738</v>
       </c>
       <c r="BD132" t="s">
@@ -13719,7 +13734,7 @@
         <v>9781136474781</v>
       </c>
       <c r="AI133" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>covers/green-goose.jpg</v>
       </c>
       <c r="AY133" s="34" t="s">
@@ -13772,7 +13787,7 @@
       <c r="Z134" s="4"/>
       <c r="AA134" s="4"/>
       <c r="AI134" t="str">
-        <f t="shared" ref="AI134:AI192" si="12">"covers/" &amp; A134 &amp; ".jpg"</f>
+        <f t="shared" ref="AI134:AI193" si="13">"covers/" &amp; A134 &amp; ".jpg"</f>
         <v>covers/mrozek-reader.jpg</v>
       </c>
       <c r="AY134" s="34" t="s">
@@ -13824,7 +13839,7 @@
       <c r="Z135" s="4"/>
       <c r="AA135" s="4"/>
       <c r="AI135" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/witkacy-reader.jpg</v>
       </c>
       <c r="AY135" s="34" t="s">
@@ -13892,7 +13907,7 @@
       <c r="Z136" s="4"/>
       <c r="AA136" s="4"/>
       <c r="AI136" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/borowski-letters.jpg</v>
       </c>
       <c r="AY136" s="34" t="s">
@@ -13942,7 +13957,7 @@
       <c r="Z137" s="4"/>
       <c r="AA137" s="4"/>
       <c r="AI137" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/ashes-diamonds.jpg</v>
       </c>
       <c r="AY137" s="34" t="s">
@@ -14014,13 +14029,13 @@
         <v>9780821442203</v>
       </c>
       <c r="AI138" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/holy-week.jpg</v>
       </c>
       <c r="AY138" s="34" t="s">
         <v>764</v>
       </c>
-      <c r="AZ138" s="38" t="s">
+      <c r="AZ138" s="25" t="s">
         <v>763</v>
       </c>
       <c r="BD138" t="s">
@@ -14077,7 +14092,7 @@
         <v>9781617745591</v>
       </c>
       <c r="AI139" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/witkacy-3-plays.jpg</v>
       </c>
       <c r="AY139" s="34" t="s">
@@ -14148,13 +14163,13 @@
         <v>9780300160208</v>
       </c>
       <c r="AI140" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/here-in-our.jpg</v>
       </c>
       <c r="AY140" s="34" t="s">
         <v>773</v>
       </c>
-      <c r="AZ140" s="38" t="s">
+      <c r="AZ140" s="25" t="s">
         <v>774</v>
       </c>
       <c r="BD140" t="s">
@@ -14214,13 +14229,13 @@
       <c r="Z141" s="4"/>
       <c r="AA141" s="4"/>
       <c r="AI141" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/to-begin-where.jpg</v>
       </c>
       <c r="AY141" s="34" t="s">
         <v>777</v>
       </c>
-      <c r="AZ141" s="38" t="s">
+      <c r="AZ141" s="25" t="s">
         <v>778</v>
       </c>
       <c r="BD141" t="s">
@@ -14289,13 +14304,13 @@
         <v>9780739175910</v>
       </c>
       <c r="AI142" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/melchior-w.jpg</v>
       </c>
       <c r="AY142" s="34" t="s">
         <v>785</v>
       </c>
-      <c r="AZ142" s="38" t="s">
+      <c r="AZ142" s="25" t="s">
         <v>784</v>
       </c>
       <c r="BD142" t="s">
@@ -14365,13 +14380,13 @@
         <v>9781666920215</v>
       </c>
       <c r="AI143" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/monte-cassino.jpg</v>
       </c>
       <c r="AY143" s="34" t="s">
         <v>790</v>
       </c>
-      <c r="AZ143" s="38" t="s">
+      <c r="AZ143" s="25" t="s">
         <v>789</v>
       </c>
       <c r="BD143" t="s">
@@ -14437,13 +14452,13 @@
         <v>9780393866582</v>
       </c>
       <c r="AI144" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/schulz-hijack.jpg</v>
       </c>
       <c r="AY144" s="34" t="s">
         <v>795</v>
       </c>
-      <c r="AZ144" s="38" t="s">
+      <c r="AZ144" s="25" t="s">
         <v>796</v>
       </c>
       <c r="BD144" t="s">
@@ -14498,7 +14513,7 @@
       <c r="Z145" s="4"/>
       <c r="AA145" s="4"/>
       <c r="AI145" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/cinnamon.jpg</v>
       </c>
       <c r="AY145" s="34" t="s">
@@ -14557,7 +14572,7 @@
       <c r="Z146" s="4"/>
       <c r="AA146" s="4"/>
       <c r="AI146" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/to-the-gas.jpg</v>
       </c>
       <c r="AY146" s="34" t="s">
@@ -14610,7 +14625,7 @@
       <c r="Z147" s="4"/>
       <c r="AA147" s="4"/>
       <c r="AI147" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/street-crocodiles.jpg</v>
       </c>
       <c r="AY147" s="34" t="s">
@@ -14673,13 +14688,13 @@
         <v>9781782277903</v>
       </c>
       <c r="AI148" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/nocturnal-apparitions.jpg</v>
       </c>
       <c r="AY148" s="34" t="s">
         <v>816</v>
       </c>
-      <c r="AZ148" s="38" t="s">
+      <c r="AZ148" s="25" t="s">
         <v>817</v>
       </c>
       <c r="BD148" t="s">
@@ -14729,7 +14744,7 @@
       <c r="Z149" s="4"/>
       <c r="AA149" s="4"/>
       <c r="AI149" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/vahazar.jpg</v>
       </c>
       <c r="AY149" s="34" t="s">
@@ -14792,7 +14807,7 @@
         <v>826</v>
       </c>
       <c r="AI150" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/women.jpg</v>
       </c>
       <c r="AY150" s="34" t="s">
@@ -14855,13 +14870,13 @@
         <v>9781609092016</v>
       </c>
       <c r="AI151" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/boundary.jpg</v>
       </c>
       <c r="AY151" s="34" t="s">
         <v>831</v>
       </c>
-      <c r="AZ151" s="38" t="s">
+      <c r="AZ151" s="25" t="s">
         <v>832</v>
       </c>
       <c r="BD151" t="s">
@@ -14910,13 +14925,13 @@
       <c r="Z152" s="4"/>
       <c r="AA152" s="4"/>
       <c r="AI152" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/romance-teresa.jpg</v>
       </c>
       <c r="AY152" s="34" t="s">
         <v>835</v>
       </c>
-      <c r="AZ152" s="38" t="s">
+      <c r="AZ152" s="25" t="s">
         <v>837</v>
       </c>
       <c r="BD152" t="s">
@@ -14983,13 +14998,13 @@
       <c r="Z153" s="4"/>
       <c r="AA153" s="4"/>
       <c r="AI153" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/medalions.jpg</v>
       </c>
       <c r="AY153" s="34" t="s">
         <v>847</v>
       </c>
-      <c r="AZ153" s="38" t="s">
+      <c r="AZ153" s="25" t="s">
         <v>848</v>
       </c>
       <c r="BD153" t="s">
@@ -15041,7 +15056,7 @@
       <c r="Z154" s="4"/>
       <c r="AA154" s="4"/>
       <c r="AI154" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/corsets.jpg</v>
       </c>
       <c r="AY154" s="34" t="s">
@@ -15065,7 +15080,7 @@
     </row>
     <row r="155" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B155" t="s">
         <v>301</v>
@@ -15074,13 +15089,13 @@
         <v>834</v>
       </c>
       <c r="D155" s="15" t="s">
+        <v>853</v>
+      </c>
+      <c r="E155" t="s">
         <v>854</v>
       </c>
-      <c r="E155" t="s">
-        <v>855</v>
-      </c>
       <c r="F155" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H155" s="6"/>
       <c r="Q155" s="2"/>
@@ -15089,7 +15104,7 @@
         <v>113</v>
       </c>
       <c r="AA155" s="4" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AB155" s="5">
         <v>3.3</v>
@@ -15098,11 +15113,11 @@
         <v>9781849168472</v>
       </c>
       <c r="AI155" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/phtanoms-breslau.jpg</v>
       </c>
       <c r="AY155" s="34" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="BD155" t="s">
         <v>23</v>
@@ -15116,7 +15131,7 @@
     </row>
     <row r="156" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="B156" t="s">
         <v>301</v>
@@ -15125,13 +15140,13 @@
         <v>835</v>
       </c>
       <c r="D156" s="28" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="E156" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="F156" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H156" s="6"/>
       <c r="Q156" s="2"/>
@@ -15140,7 +15155,7 @@
         <v>113</v>
       </c>
       <c r="AA156" s="4" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AB156" s="5">
         <v>6</v>
@@ -15149,14 +15164,14 @@
         <v>9781849166591</v>
       </c>
       <c r="AI156" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/death-breslau.jpg</v>
       </c>
       <c r="AY156" s="34" t="s">
+        <v>861</v>
+      </c>
+      <c r="AZ156" s="25" t="s">
         <v>862</v>
-      </c>
-      <c r="AZ156" s="38" t="s">
-        <v>863</v>
       </c>
       <c r="BD156" t="s">
         <v>23</v>
@@ -15170,7 +15185,7 @@
     </row>
     <row r="157" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="B157" t="s">
         <v>301</v>
@@ -15179,19 +15194,19 @@
         <v>835</v>
       </c>
       <c r="D157" s="15" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="E157" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="F157" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H157" s="6" t="s">
         <v>111</v>
       </c>
       <c r="I157" s="7" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J157" s="7">
         <v>25</v>
@@ -15205,7 +15220,7 @@
         <v>113</v>
       </c>
       <c r="AA157" s="4" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AB157" s="5">
         <v>3.3</v>
@@ -15214,14 +15229,14 @@
         <v>9781849166850</v>
       </c>
       <c r="AI157" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/end-breslau.jpg</v>
       </c>
       <c r="AY157" s="34" t="s">
+        <v>866</v>
+      </c>
+      <c r="AZ157" s="25" t="s">
         <v>867</v>
-      </c>
-      <c r="AZ157" s="38" t="s">
-        <v>868</v>
       </c>
       <c r="BD157" t="s">
         <v>23</v>
@@ -15235,7 +15250,7 @@
     </row>
     <row r="158" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B158" t="s">
         <v>301</v>
@@ -15244,20 +15259,20 @@
         <v>836</v>
       </c>
       <c r="D158" s="15" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="E158" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="F158" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="H158" s="6"/>
       <c r="Q158" s="2" t="s">
         <v>112</v>
       </c>
       <c r="R158" s="7" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="S158" s="3">
         <v>17</v>
@@ -15269,11 +15284,11 @@
         <v>9781849166256</v>
       </c>
       <c r="AI158" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/minotaur.jpg</v>
       </c>
       <c r="AY158" s="34" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="BD158" t="s">
         <v>23</v>
@@ -15287,7 +15302,7 @@
     </row>
     <row r="159" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B159" t="s">
         <v>78</v>
@@ -15296,13 +15311,13 @@
         <v>756</v>
       </c>
       <c r="D159" s="15" t="s">
+        <v>872</v>
+      </c>
+      <c r="E159" t="s">
         <v>873</v>
       </c>
-      <c r="E159" t="s">
+      <c r="F159" t="s">
         <v>874</v>
-      </c>
-      <c r="F159" t="s">
-        <v>875</v>
       </c>
       <c r="H159" s="6"/>
       <c r="Q159" s="2" t="s">
@@ -15331,14 +15346,14 @@
         <v>9780810142886</v>
       </c>
       <c r="AI159" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/niko-dyzma.jpg</v>
       </c>
       <c r="AY159" s="34" t="s">
-        <v>877</v>
-      </c>
-      <c r="AZ159" s="38" t="s">
         <v>876</v>
+      </c>
+      <c r="AZ159" s="25" t="s">
+        <v>875</v>
       </c>
       <c r="BD159" t="s">
         <v>23</v>
@@ -15352,7 +15367,7 @@
     </row>
     <row r="160" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B160" t="s">
         <v>126</v>
@@ -15361,20 +15376,20 @@
         <v>820</v>
       </c>
       <c r="D160" s="15" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="E160" t="s">
         <v>70</v>
       </c>
       <c r="F160" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="H160" s="6"/>
       <c r="Q160" s="2" t="s">
         <v>112</v>
       </c>
       <c r="R160" s="7" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="S160" s="3">
         <v>17</v>
@@ -15385,14 +15400,14 @@
       <c r="Z160" s="4"/>
       <c r="AA160" s="4"/>
       <c r="AI160" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/wrote-stone.jpg</v>
       </c>
       <c r="AY160" s="34" t="s">
-        <v>882</v>
-      </c>
-      <c r="AZ160" s="38" t="s">
         <v>881</v>
+      </c>
+      <c r="AZ160" s="25" t="s">
+        <v>880</v>
       </c>
       <c r="BD160" t="s">
         <v>23</v>
@@ -15406,7 +15421,7 @@
     </row>
     <row r="161" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="B161" t="s">
         <v>78</v>
@@ -15415,16 +15430,16 @@
         <v>975</v>
       </c>
       <c r="D161" s="15" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="E161" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="F161" t="s">
         <v>830</v>
       </c>
       <c r="G161" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="H161" s="6" t="s">
         <v>111</v>
@@ -15443,7 +15458,7 @@
         <v>112</v>
       </c>
       <c r="R161" s="7" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="S161" s="3">
         <v>20</v>
@@ -15465,14 +15480,14 @@
         <v>9788088628347</v>
       </c>
       <c r="AI161" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/phoebe-hicks.jpg</v>
       </c>
       <c r="AY161" s="34" t="s">
-        <v>887</v>
-      </c>
-      <c r="AZ161" s="38" t="s">
-        <v>890</v>
+        <v>886</v>
+      </c>
+      <c r="AZ161" s="25" t="s">
+        <v>889</v>
       </c>
       <c r="BD161" t="s">
         <v>23</v>
@@ -15486,7 +15501,7 @@
     </row>
     <row r="162" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B162" t="s">
         <v>78</v>
@@ -15495,20 +15510,20 @@
         <v>980</v>
       </c>
       <c r="D162" s="15" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E162" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="F162" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="H162" s="6"/>
       <c r="Q162" s="2" t="s">
         <v>112</v>
       </c>
       <c r="R162" s="7" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="S162" s="3">
         <v>20</v>
@@ -15518,11 +15533,11 @@
       </c>
       <c r="AA162" s="4"/>
       <c r="AI162" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/roman-spring.jpg</v>
       </c>
       <c r="AY162" s="34" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="BD162" t="s">
         <v>23</v>
@@ -15536,7 +15551,7 @@
     </row>
     <row r="163" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B163" t="s">
         <v>126</v>
@@ -15545,10 +15560,10 @@
         <v>891</v>
       </c>
       <c r="D163" s="15" t="s">
+        <v>896</v>
+      </c>
+      <c r="E163" t="s">
         <v>897</v>
-      </c>
-      <c r="E163" t="s">
-        <v>898</v>
       </c>
       <c r="F163" t="s">
         <v>278</v>
@@ -15589,14 +15604,14 @@
         <v>9781804840528</v>
       </c>
       <c r="AI163" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/kochanowski-selected.jpg</v>
       </c>
       <c r="AY163" s="34" t="s">
+        <v>900</v>
+      </c>
+      <c r="AZ163" s="25" t="s">
         <v>901</v>
-      </c>
-      <c r="AZ163" s="38" t="s">
-        <v>902</v>
       </c>
       <c r="BD163" t="s">
         <v>23</v>
@@ -15610,7 +15625,7 @@
     </row>
     <row r="164" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B164" t="s">
         <v>126</v>
@@ -15619,20 +15634,20 @@
         <v>899</v>
       </c>
       <c r="D164" s="15" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="E164" t="s">
+        <v>904</v>
+      </c>
+      <c r="F164" t="s">
         <v>905</v>
-      </c>
-      <c r="F164" t="s">
-        <v>906</v>
       </c>
       <c r="H164" s="6"/>
       <c r="Q164" s="2" t="s">
         <v>112</v>
       </c>
       <c r="R164" s="7" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="S164" s="3">
         <v>21</v>
@@ -15654,14 +15669,14 @@
         <v>9780691213040</v>
       </c>
       <c r="AI164" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/sounds-feelings.jpg</v>
       </c>
       <c r="AY164" s="34" t="s">
-        <v>909</v>
-      </c>
-      <c r="AZ164" s="38" t="s">
         <v>908</v>
+      </c>
+      <c r="AZ164" s="25" t="s">
+        <v>907</v>
       </c>
       <c r="BD164" t="s">
         <v>23</v>
@@ -15675,7 +15690,7 @@
     </row>
     <row r="165" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B165" t="s">
         <v>78</v>
@@ -15684,10 +15699,10 @@
         <v>945</v>
       </c>
       <c r="D165" s="15" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E165" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F165" t="s">
         <v>830</v>
@@ -15719,11 +15734,11 @@
         <v>9781609090692</v>
       </c>
       <c r="AI165" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/the-heathen.jpg</v>
       </c>
       <c r="AY165" s="34" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="BD165" t="s">
         <v>23</v>
@@ -15737,7 +15752,7 @@
     </row>
     <row r="166" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="B166" t="s">
         <v>78</v>
@@ -15746,10 +15761,10 @@
         <v>947</v>
       </c>
       <c r="D166" s="15" t="s">
+        <v>914</v>
+      </c>
+      <c r="E166" t="s">
         <v>915</v>
-      </c>
-      <c r="E166" t="s">
-        <v>916</v>
       </c>
       <c r="F166" t="s">
         <v>830</v>
@@ -15772,14 +15787,14 @@
       </c>
       <c r="AA166" s="4"/>
       <c r="AI166" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/malvina.jpg</v>
       </c>
       <c r="AY166" s="34" t="s">
+        <v>916</v>
+      </c>
+      <c r="AZ166" s="25" t="s">
         <v>917</v>
-      </c>
-      <c r="AZ166" s="38" t="s">
-        <v>918</v>
       </c>
       <c r="BD166" t="s">
         <v>23</v>
@@ -15793,7 +15808,7 @@
     </row>
     <row r="167" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="B167" t="s">
         <v>78</v>
@@ -15802,10 +15817,10 @@
         <v>923</v>
       </c>
       <c r="D167" s="15" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="E167" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F167" t="s">
         <v>830</v>
@@ -15815,7 +15830,7 @@
         <v>112</v>
       </c>
       <c r="R167" s="7" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="S167" s="3">
         <v>15</v>
@@ -15827,20 +15842,20 @@
         <v>113</v>
       </c>
       <c r="AA167" s="4" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="AB167" s="5">
         <v>15</v>
       </c>
       <c r="AH167" s="8" t="s">
+        <v>923</v>
+      </c>
+      <c r="AI167" t="str">
+        <f t="shared" si="13"/>
+        <v>covers/bird-streets.jpg</v>
+      </c>
+      <c r="AY167" s="29" t="s">
         <v>924</v>
-      </c>
-      <c r="AI167" t="str">
-        <f t="shared" si="12"/>
-        <v>covers/bird-streets.jpg</v>
-      </c>
-      <c r="AY167" s="29" t="s">
-        <v>925</v>
       </c>
       <c r="BD167" t="s">
         <v>23</v>
@@ -15854,7 +15869,7 @@
     </row>
     <row r="168" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B168" t="s">
         <v>742</v>
@@ -15863,13 +15878,13 @@
         <v>945</v>
       </c>
       <c r="D168" s="15" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="E168" t="s">
         <v>748</v>
       </c>
       <c r="F168" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="H168" s="6" t="s">
         <v>111</v>
@@ -15910,11 +15925,11 @@
         <v>9781135299897</v>
       </c>
       <c r="AI168" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/country-house.jpg</v>
       </c>
       <c r="AY168" s="30" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="BD168" t="s">
         <v>23</v>
@@ -15928,7 +15943,7 @@
     </row>
     <row r="169" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B169" t="s">
         <v>215</v>
@@ -15937,19 +15952,19 @@
         <v>955</v>
       </c>
       <c r="D169" s="15" t="s">
+        <v>931</v>
+      </c>
+      <c r="E169" t="s">
         <v>932</v>
       </c>
-      <c r="E169" t="s">
+      <c r="G169" t="s">
         <v>933</v>
-      </c>
-      <c r="G169" t="s">
-        <v>934</v>
       </c>
       <c r="H169" s="6" t="s">
         <v>111</v>
       </c>
       <c r="I169" s="7" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="J169" s="7">
         <v>17</v>
@@ -15962,11 +15977,11 @@
       <c r="Z169" s="4"/>
       <c r="AA169" s="4"/>
       <c r="AI169" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/locomotive.jpg</v>
       </c>
       <c r="AY169" s="31" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="BD169" t="s">
         <v>23</v>
@@ -15980,7 +15995,7 @@
     </row>
     <row r="170" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="B170" t="s">
         <v>215</v>
@@ -15989,16 +16004,16 @@
         <v>1005</v>
       </c>
       <c r="D170" s="32" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="E170" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="H170" s="6" t="s">
         <v>111</v>
       </c>
       <c r="I170" s="7" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="J170" s="7">
         <v>110</v>
@@ -16011,11 +16026,11 @@
       <c r="Z170" s="4"/>
       <c r="AA170" s="4"/>
       <c r="AI170" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/zofia-stry.jpg</v>
       </c>
       <c r="AY170" s="29" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="BD170" t="s">
         <v>23</v>
@@ -16029,7 +16044,7 @@
     </row>
     <row r="171" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B171" t="s">
         <v>215</v>
@@ -16038,19 +16053,19 @@
         <v>1007</v>
       </c>
       <c r="D171" s="15" t="s">
+        <v>941</v>
+      </c>
+      <c r="E171" t="s">
         <v>942</v>
       </c>
-      <c r="E171" t="s">
+      <c r="F171" t="s">
         <v>943</v>
-      </c>
-      <c r="F171" t="s">
-        <v>944</v>
       </c>
       <c r="H171" s="6" t="s">
         <v>111</v>
       </c>
       <c r="I171" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="J171" s="7">
         <v>21</v>
@@ -16083,14 +16098,14 @@
         <v>0.99</v>
       </c>
       <c r="AH171" s="8" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="AI171" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/67-tales.jpg</v>
       </c>
       <c r="AY171" s="34" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="BD171" t="s">
         <v>23</v>
@@ -16104,7 +16119,7 @@
     </row>
     <row r="172" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B172" t="s">
         <v>74</v>
@@ -16113,10 +16128,10 @@
         <v>1008</v>
       </c>
       <c r="D172" s="15" t="s">
+        <v>947</v>
+      </c>
+      <c r="E172" t="s">
         <v>948</v>
-      </c>
-      <c r="E172" t="s">
-        <v>949</v>
       </c>
       <c r="H172" s="6" t="s">
         <v>111</v>
@@ -16142,17 +16157,17 @@
         <v>48</v>
       </c>
       <c r="AH172" s="8" t="s">
+        <v>949</v>
+      </c>
+      <c r="AI172" t="str">
+        <f t="shared" si="13"/>
+        <v>covers/triumph-provocation.jpg</v>
+      </c>
+      <c r="AY172" s="34" t="s">
+        <v>951</v>
+      </c>
+      <c r="AZ172" s="25" t="s">
         <v>950</v>
-      </c>
-      <c r="AI172" t="str">
-        <f t="shared" si="12"/>
-        <v>covers/triumph-provocation.jpg</v>
-      </c>
-      <c r="AY172" s="34" t="s">
-        <v>952</v>
-      </c>
-      <c r="AZ172" s="38" t="s">
-        <v>951</v>
       </c>
       <c r="BD172" t="s">
         <v>23</v>
@@ -16166,7 +16181,7 @@
     </row>
     <row r="173" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="B173" t="s">
         <v>215</v>
@@ -16175,16 +16190,16 @@
         <v>1009</v>
       </c>
       <c r="D173" s="15" t="s">
+        <v>953</v>
+      </c>
+      <c r="E173" t="s">
         <v>954</v>
       </c>
-      <c r="E173" t="s">
+      <c r="F173" t="s">
+        <v>956</v>
+      </c>
+      <c r="G173" t="s">
         <v>955</v>
-      </c>
-      <c r="F173" t="s">
-        <v>957</v>
-      </c>
-      <c r="G173" t="s">
-        <v>956</v>
       </c>
       <c r="H173" s="6" t="s">
         <v>111</v>
@@ -16204,7 +16219,7 @@
         <v>Paperback</v>
       </c>
       <c r="R173" s="2" t="str">
-        <f t="shared" ref="R173" si="13">R171</f>
+        <f t="shared" ref="R173" si="14">R171</f>
         <v>Independently published</v>
       </c>
       <c r="S173" s="2">
@@ -16216,11 +16231,11 @@
       <c r="Z173" s="4"/>
       <c r="AA173" s="4"/>
       <c r="AI173" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/sindbad.jpg</v>
       </c>
       <c r="AY173" s="34" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="BD173" t="s">
         <v>23</v>
@@ -16234,7 +16249,7 @@
     </row>
     <row r="174" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="B174" t="s">
         <v>126</v>
@@ -16243,13 +16258,13 @@
         <v>1010</v>
       </c>
       <c r="D174" s="15" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E174" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="F174" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H174" s="6"/>
       <c r="Q174" s="2" t="str">
@@ -16269,11 +16284,11 @@
       <c r="Z174" s="4"/>
       <c r="AA174" s="4"/>
       <c r="AI174" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/beyond-beyond.jpg</v>
       </c>
       <c r="AY174" s="34" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="BD174" t="s">
         <v>23</v>
@@ -16287,7 +16302,7 @@
     </row>
     <row r="175" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B175" t="s">
         <v>126</v>
@@ -16296,21 +16311,21 @@
         <v>1020</v>
       </c>
       <c r="D175" s="15" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="E175" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="F175" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H175" s="6"/>
       <c r="Q175" s="2" t="str">
-        <f t="shared" ref="Q175:Q177" si="14">Q174</f>
+        <f t="shared" ref="Q175:Q177" si="15">Q174</f>
         <v>Paperback</v>
       </c>
       <c r="R175" s="2" t="str">
-        <f t="shared" ref="R175:R176" si="15">R174</f>
+        <f t="shared" ref="R175:R176" si="16">R174</f>
         <v>Independently published</v>
       </c>
       <c r="S175" s="3">
@@ -16322,11 +16337,11 @@
       <c r="Z175" s="4"/>
       <c r="AA175" s="4"/>
       <c r="AI175" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/marvellations.jpg</v>
       </c>
-      <c r="AY175" s="39" t="s">
-        <v>965</v>
+      <c r="AY175" s="38" t="s">
+        <v>964</v>
       </c>
       <c r="BD175" t="s">
         <v>23</v>
@@ -16340,7 +16355,7 @@
     </row>
     <row r="176" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="B176" t="s">
         <v>126</v>
@@ -16349,21 +16364,21 @@
         <v>1030</v>
       </c>
       <c r="D176" s="15" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="E176" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="F176" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H176" s="6"/>
       <c r="Q176" s="2" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Paperback</v>
       </c>
       <c r="R176" s="2" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="16"/>
         <v>Independently published</v>
       </c>
       <c r="S176" s="3">
@@ -16375,11 +16390,11 @@
       <c r="Z176" s="4"/>
       <c r="AA176" s="4"/>
       <c r="AI176" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/33-poems.jpg</v>
       </c>
       <c r="AY176" s="34" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="BD176" t="s">
         <v>23</v>
@@ -16393,7 +16408,7 @@
     </row>
     <row r="177" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="B177" t="s">
         <v>74</v>
@@ -16402,18 +16417,18 @@
         <v>1057</v>
       </c>
       <c r="D177" s="15" t="s">
+        <v>969</v>
+      </c>
+      <c r="E177" t="s">
         <v>970</v>
-      </c>
-      <c r="E177" t="s">
-        <v>971</v>
       </c>
       <c r="H177" s="6"/>
       <c r="Q177" s="2" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>Paperback</v>
       </c>
       <c r="R177" s="2" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="S177" s="3">
         <v>25</v>
@@ -16424,11 +16439,11 @@
       <c r="Z177" s="4"/>
       <c r="AA177" s="4"/>
       <c r="AI177" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/on-writing.jpg</v>
       </c>
       <c r="AY177" s="34" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="BD177" t="s">
         <v>23</v>
@@ -16442,7 +16457,7 @@
     </row>
     <row r="178" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="B178" t="s">
         <v>74</v>
@@ -16451,7 +16466,7 @@
         <v>1058</v>
       </c>
       <c r="D178" s="15" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="E178" t="s">
         <v>200</v>
@@ -16460,7 +16475,7 @@
         <v>111</v>
       </c>
       <c r="I178" s="7" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="J178" s="7">
         <v>130</v>
@@ -16485,14 +16500,14 @@
       <c r="Z178" s="4"/>
       <c r="AA178" s="4"/>
       <c r="AI178" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/polish-lit-as-world.jpg</v>
       </c>
       <c r="AY178" s="34" t="s">
+        <v>976</v>
+      </c>
+      <c r="AZ178" s="25" t="s">
         <v>977</v>
-      </c>
-      <c r="AZ178" s="38" t="s">
-        <v>978</v>
       </c>
       <c r="BD178" t="s">
         <v>23</v>
@@ -16506,7 +16521,7 @@
     </row>
     <row r="179" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="B179" t="s">
         <v>126</v>
@@ -16515,13 +16530,13 @@
         <v>1059</v>
       </c>
       <c r="D179" s="15" t="s">
+        <v>978</v>
+      </c>
+      <c r="E179" t="s">
         <v>979</v>
       </c>
-      <c r="E179" t="s">
+      <c r="F179" t="s">
         <v>980</v>
-      </c>
-      <c r="F179" t="s">
-        <v>981</v>
       </c>
       <c r="H179" s="6"/>
       <c r="Q179" s="2" t="str">
@@ -16529,7 +16544,7 @@
         <v>Paperback</v>
       </c>
       <c r="R179" s="2" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="S179" s="3">
         <v>16</v>
@@ -16540,11 +16555,11 @@
       <c r="Z179" s="4"/>
       <c r="AA179" s="4"/>
       <c r="AI179" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/folding-star.jpg</v>
       </c>
       <c r="AY179" s="34" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="BD179" t="s">
         <v>23</v>
@@ -16558,7 +16573,7 @@
     </row>
     <row r="180" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="B180" t="s">
         <v>126</v>
@@ -16567,13 +16582,13 @@
         <v>1060</v>
       </c>
       <c r="D180" s="15" t="s">
+        <v>984</v>
+      </c>
+      <c r="E180" t="s">
         <v>985</v>
       </c>
-      <c r="E180" t="s">
-        <v>986</v>
-      </c>
       <c r="F180" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H180" s="6"/>
       <c r="Q180" s="2" t="str">
@@ -16581,7 +16596,7 @@
         <v>Paperback</v>
       </c>
       <c r="R180" s="2" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="S180" s="3">
         <v>16</v>
@@ -16592,11 +16607,11 @@
       <c r="Z180" s="4"/>
       <c r="AA180" s="4"/>
       <c r="AI180" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/world-shared.jpg</v>
       </c>
       <c r="AY180" s="34" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="BD180" t="s">
         <v>23</v>
@@ -16610,7 +16625,7 @@
     </row>
     <row r="181" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="B181" t="s">
         <v>126</v>
@@ -16619,13 +16634,13 @@
         <v>1061</v>
       </c>
       <c r="D181" s="15" t="s">
+        <v>996</v>
+      </c>
+      <c r="E181" t="s">
         <v>997</v>
       </c>
-      <c r="E181" t="s">
+      <c r="F181" t="s">
         <v>998</v>
-      </c>
-      <c r="F181" t="s">
-        <v>999</v>
       </c>
       <c r="H181" s="6"/>
       <c r="Q181" s="2" t="str">
@@ -16633,7 +16648,7 @@
         <v>Paperback</v>
       </c>
       <c r="R181" s="2" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="S181" s="3">
         <v>16</v>
@@ -16652,14 +16667,14 @@
         <v>9781935744535</v>
       </c>
       <c r="AI181" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/poems-norwid.jpg</v>
       </c>
       <c r="AY181" s="34" t="s">
+        <v>990</v>
+      </c>
+      <c r="AZ181" s="25" t="s">
         <v>991</v>
-      </c>
-      <c r="AZ181" s="38" t="s">
-        <v>992</v>
       </c>
       <c r="BD181" t="s">
         <v>23</v>
@@ -16673,7 +16688,7 @@
     </row>
     <row r="182" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="B182" t="s">
         <v>126</v>
@@ -16682,16 +16697,16 @@
         <v>1061</v>
       </c>
       <c r="D182" s="15" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="E182" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="H182" s="6" t="s">
         <v>111</v>
       </c>
       <c r="I182" s="7" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="J182" s="7">
         <v>46</v>
@@ -16716,14 +16731,14 @@
         <v>9780674270190</v>
       </c>
       <c r="AI182" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/sound-modern.jpg</v>
       </c>
       <c r="AY182" s="34" t="s">
-        <v>1001</v>
-      </c>
-      <c r="AZ182" s="38" t="s">
         <v>1000</v>
+      </c>
+      <c r="AZ182" s="25" t="s">
+        <v>999</v>
       </c>
       <c r="BD182" t="s">
         <v>23</v>
@@ -16737,7 +16752,7 @@
     </row>
     <row r="183" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="B183" t="s">
         <v>78</v>
@@ -16746,13 +16761,13 @@
         <v>1062</v>
       </c>
       <c r="D183" s="15" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E183" t="s">
         <v>1003</v>
       </c>
-      <c r="E183" t="s">
-        <v>1004</v>
-      </c>
       <c r="F183" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H183" s="6"/>
       <c r="Q183" s="2" t="str">
@@ -16783,14 +16798,14 @@
         <v>9780802195289</v>
       </c>
       <c r="AI183" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/pornografia.jpg</v>
       </c>
       <c r="AY183" s="34" t="s">
+        <v>1004</v>
+      </c>
+      <c r="AZ183" s="25" t="s">
         <v>1005</v>
-      </c>
-      <c r="AZ183" s="38" t="s">
-        <v>1006</v>
       </c>
       <c r="BD183" t="s">
         <v>23</v>
@@ -16804,7 +16819,7 @@
     </row>
     <row r="184" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="B184" t="s">
         <v>78</v>
@@ -16813,17 +16828,17 @@
         <v>1063</v>
       </c>
       <c r="D184" s="15" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="E184" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F184" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H184" s="6"/>
       <c r="Q184" s="2" t="str">
-        <f>Q183</f>
+        <f t="shared" ref="Q184:Q191" si="17">Q183</f>
         <v>Paperback</v>
       </c>
       <c r="R184" s="2" t="s">
@@ -16849,14 +16864,14 @@
         <v>9780300207019</v>
       </c>
       <c r="AI184" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/transatlantic.jpg</v>
       </c>
       <c r="AY184" s="34" t="s">
-        <v>1010</v>
-      </c>
-      <c r="AZ184" s="38" t="s">
         <v>1009</v>
+      </c>
+      <c r="AZ184" s="25" t="s">
+        <v>1008</v>
       </c>
       <c r="BD184" t="s">
         <v>23</v>
@@ -16870,7 +16885,7 @@
     </row>
     <row r="185" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="B185" t="s">
         <v>78</v>
@@ -16879,16 +16894,16 @@
         <v>1064</v>
       </c>
       <c r="D185" s="15" t="s">
+        <v>1011</v>
+      </c>
+      <c r="E185" t="s">
         <v>1012</v>
-      </c>
-      <c r="E185" t="s">
-        <v>1013</v>
       </c>
       <c r="H185" s="6" t="s">
         <v>111</v>
       </c>
       <c r="I185" s="7" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="J185" s="7">
         <v>40</v>
@@ -16897,7 +16912,7 @@
         <v>9781019403907</v>
       </c>
       <c r="Q185" s="2" t="str">
-        <f>Q184</f>
+        <f t="shared" si="17"/>
         <v>Paperback</v>
       </c>
       <c r="R185" s="2" t="str">
@@ -16913,11 +16928,11 @@
       <c r="Z185" s="4"/>
       <c r="AA185" s="4"/>
       <c r="AI185" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/angels-dust.jpg</v>
       </c>
       <c r="AY185" s="34" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="BD185" t="s">
         <v>23</v>
@@ -16931,7 +16946,7 @@
     </row>
     <row r="186" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="B186" t="s">
         <v>78</v>
@@ -16940,24 +16955,24 @@
         <v>1065</v>
       </c>
       <c r="D186" s="15" t="s">
+        <v>1016</v>
+      </c>
+      <c r="E186" t="s">
         <v>1017</v>
       </c>
-      <c r="E186" t="s">
+      <c r="F186" t="s">
         <v>1018</v>
       </c>
-      <c r="F186" t="s">
+      <c r="G186" t="s">
         <v>1019</v>
-      </c>
-      <c r="G186" t="s">
-        <v>1020</v>
       </c>
       <c r="H186" s="6"/>
       <c r="Q186" s="2" t="str">
-        <f>Q185</f>
+        <f t="shared" si="17"/>
         <v>Paperback</v>
       </c>
       <c r="R186" s="2" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="S186" s="3">
         <v>18</v>
@@ -16980,14 +16995,14 @@
         <v>9788086264752</v>
       </c>
       <c r="AI186" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/burn-paris.jpg</v>
       </c>
       <c r="AY186" s="34" t="s">
+        <v>1020</v>
+      </c>
+      <c r="AZ186" s="25" t="s">
         <v>1021</v>
-      </c>
-      <c r="AZ186" s="38" t="s">
-        <v>1022</v>
       </c>
       <c r="BD186" t="s">
         <v>23</v>
@@ -17001,7 +17016,7 @@
     </row>
     <row r="187" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="B187" t="s">
         <v>78</v>
@@ -17010,21 +17025,21 @@
         <v>1070</v>
       </c>
       <c r="D187" s="15" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="E187" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="F187" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="H187" s="6"/>
       <c r="Q187" s="2" t="str">
-        <f>Q186</f>
+        <f t="shared" si="17"/>
         <v>Paperback</v>
       </c>
       <c r="R187" s="2" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="S187" s="3">
         <v>13</v>
@@ -17047,14 +17062,14 @@
         <v>9781939931238</v>
       </c>
       <c r="AI187" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/killing-auntie.jpg</v>
       </c>
       <c r="AY187" s="34" t="s">
-        <v>1047</v>
-      </c>
-      <c r="AZ187" s="38" t="s">
-        <v>1048</v>
+        <v>1045</v>
+      </c>
+      <c r="AZ187" s="25" t="s">
+        <v>1046</v>
       </c>
       <c r="BD187" t="s">
         <v>23</v>
@@ -17068,7 +17083,7 @@
     </row>
     <row r="188" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="B188" t="s">
         <v>74</v>
@@ -17077,19 +17092,19 @@
         <v>1071</v>
       </c>
       <c r="D188" s="15" t="s">
+        <v>1041</v>
+      </c>
+      <c r="E188" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F188" t="s">
         <v>1043</v>
-      </c>
-      <c r="E188" t="s">
-        <v>1051</v>
-      </c>
-      <c r="F188" t="s">
-        <v>1045</v>
       </c>
       <c r="H188" s="6" t="s">
         <v>111</v>
       </c>
       <c r="I188" s="7" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="J188" s="7">
         <v>119</v>
@@ -17098,11 +17113,11 @@
         <v>9781644694770</v>
       </c>
       <c r="Q188" s="2" t="str">
-        <f>Q187</f>
+        <f t="shared" si="17"/>
         <v>Paperback</v>
       </c>
       <c r="R188" s="2" t="str">
-        <f t="shared" ref="R188:R236" si="16">I188</f>
+        <f t="shared" ref="R188:R236" si="18">I188</f>
         <v>Academic Studies Press</v>
       </c>
       <c r="S188" s="3">
@@ -17126,14 +17141,14 @@
         <v>9781644694794</v>
       </c>
       <c r="AI188" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/palestine-3rd.jpg</v>
       </c>
       <c r="AY188" s="34" t="s">
-        <v>1053</v>
-      </c>
-      <c r="AZ188" s="38" t="s">
-        <v>1054</v>
+        <v>1051</v>
+      </c>
+      <c r="AZ188" s="25" t="s">
+        <v>1052</v>
       </c>
       <c r="BD188" t="s">
         <v>23</v>
@@ -17147,7 +17162,7 @@
     </row>
     <row r="189" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="B189" t="s">
         <v>78</v>
@@ -17156,18 +17171,18 @@
         <v>1072</v>
       </c>
       <c r="D189" s="15" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="E189" t="str">
         <f>E168</f>
         <v>Stanisław Ignacy Witkiewicz</v>
       </c>
       <c r="F189" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="H189" s="6"/>
       <c r="Q189" s="2" t="str">
-        <f>Q188</f>
+        <f t="shared" si="17"/>
         <v>Paperback</v>
       </c>
       <c r="R189" s="2" t="s">
@@ -17182,19 +17197,19 @@
       <c r="Z189" s="4"/>
       <c r="AA189" s="4"/>
       <c r="AI189" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/insatiability.jpg</v>
       </c>
       <c r="AY189" s="34" t="s">
-        <v>1058</v>
-      </c>
-      <c r="AZ189" s="38" t="s">
-        <v>1059</v>
+        <v>1056</v>
+      </c>
+      <c r="AZ189" s="25" t="s">
+        <v>1057</v>
       </c>
     </row>
     <row r="190" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="B190" t="s">
         <v>301</v>
@@ -17203,21 +17218,21 @@
         <v>575</v>
       </c>
       <c r="D190" s="15" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="E190" t="s">
         <v>89</v>
       </c>
       <c r="F190" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="H190" s="6"/>
       <c r="Q190" s="2" t="str">
-        <f>Q189</f>
+        <f t="shared" si="17"/>
         <v>Paperback</v>
       </c>
       <c r="R190" s="2" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="S190" s="3">
         <v>12</v>
@@ -17228,16 +17243,16 @@
       <c r="Z190" s="4"/>
       <c r="AA190" s="4"/>
       <c r="AI190" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/pirx.jpg</v>
       </c>
       <c r="AY190" s="34" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="191" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
       <c r="B191" t="s">
         <v>301</v>
@@ -17246,21 +17261,21 @@
         <v>873</v>
       </c>
       <c r="D191" s="15" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="E191" t="s">
         <v>89</v>
       </c>
       <c r="F191" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="H191" s="6"/>
       <c r="Q191" s="2" t="str">
-        <f>Q190</f>
+        <f t="shared" si="17"/>
         <v>Paperback</v>
       </c>
       <c r="R191" s="2" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="S191" s="3">
         <v>11</v>
@@ -17271,16 +17286,16 @@
       <c r="Z191" s="4"/>
       <c r="AA191" s="4"/>
       <c r="AI191" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/chain-chance.jpg</v>
       </c>
       <c r="AY191" s="34" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="192" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="B192" t="s">
         <v>74</v>
@@ -17289,15 +17304,14 @@
         <v>874</v>
       </c>
       <c r="D192" s="15" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E192" t="s">
         <v>127</v>
       </c>
       <c r="F192" t="s">
-        <v>1057</v>
-      </c>
-      <c r="H192" s="6"/>
+        <v>1055</v>
+      </c>
       <c r="Q192" s="2" t="str">
         <f>Q190</f>
         <v>Paperback</v>
@@ -17314,148 +17328,202 @@
       <c r="Z192" s="4"/>
       <c r="AA192" s="4"/>
       <c r="AI192" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>covers/ulro.jpg</v>
       </c>
       <c r="AY192" s="34" t="s">
-        <v>1066</v>
-      </c>
-      <c r="AZ192" s="38" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="193" spans="8:27" x14ac:dyDescent="0.25">
-      <c r="H193" s="6"/>
-      <c r="R193" s="2">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="Z193" s="4"/>
-      <c r="AA193" s="4"/>
-    </row>
-    <row r="194" spans="8:27" x14ac:dyDescent="0.25">
+        <v>1064</v>
+      </c>
+      <c r="AZ192" s="25" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="193" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B193" t="s">
+        <v>215</v>
+      </c>
+      <c r="D193" s="15" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E193" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F193" t="s">
+        <v>1072</v>
+      </c>
+      <c r="H193" s="6" t="str">
+        <f>H188</f>
+        <v>Hardcover</v>
+      </c>
+      <c r="I193" s="10" t="s">
+        <v>1075</v>
+      </c>
+      <c r="J193" s="7">
+        <v>58</v>
+      </c>
+      <c r="P193" s="10">
+        <v>9798887196886</v>
+      </c>
+      <c r="Q193" s="2" t="str">
+        <f>Q191</f>
+        <v>Paperback</v>
+      </c>
+      <c r="R193" s="2" t="str">
+        <f>I193</f>
+        <v xml:space="preserve">Cherry Orchard </v>
+      </c>
+      <c r="S193" s="3">
+        <v>25</v>
+      </c>
+      <c r="Y193" s="21">
+        <v>9798887196893</v>
+      </c>
+      <c r="Z193" s="4" t="str">
+        <f>Z188</f>
+        <v>Ebook</v>
+      </c>
+      <c r="AA193" s="4" t="str">
+        <f>R193</f>
+        <v xml:space="preserve">Cherry Orchard </v>
+      </c>
+      <c r="AB193" s="5">
+        <v>24</v>
+      </c>
+      <c r="AH193" s="8">
+        <v>9798887196916</v>
+      </c>
+      <c r="AI193" t="str">
+        <f t="shared" si="13"/>
+        <v>covers/little-orphan-mary.jpg</v>
+      </c>
+      <c r="AY193" s="34" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="194" spans="1:51" x14ac:dyDescent="0.25">
       <c r="H194" s="6"/>
-      <c r="R194" s="2">
-        <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
+      <c r="I194" s="10"/>
+      <c r="Q194" s="2"/>
       <c r="Z194" s="4"/>
       <c r="AA194" s="4"/>
     </row>
-    <row r="195" spans="8:27" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:51" x14ac:dyDescent="0.25">
       <c r="H195" s="6"/>
       <c r="R195" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z195" s="4"/>
       <c r="AA195" s="4"/>
     </row>
-    <row r="196" spans="8:27" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:51" x14ac:dyDescent="0.25">
       <c r="H196" s="6"/>
       <c r="R196" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z196" s="4"/>
       <c r="AA196" s="4"/>
     </row>
-    <row r="197" spans="8:27" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:51" x14ac:dyDescent="0.25">
       <c r="H197" s="6"/>
       <c r="R197" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z197" s="4"/>
       <c r="AA197" s="4"/>
     </row>
-    <row r="198" spans="8:27" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:51" x14ac:dyDescent="0.25">
       <c r="H198" s="6"/>
       <c r="R198" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z198" s="4"/>
       <c r="AA198" s="4"/>
     </row>
-    <row r="199" spans="8:27" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:51" x14ac:dyDescent="0.25">
       <c r="H199" s="6"/>
       <c r="R199" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z199" s="4"/>
       <c r="AA199" s="4"/>
     </row>
-    <row r="200" spans="8:27" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:51" x14ac:dyDescent="0.25">
       <c r="H200" s="6"/>
       <c r="R200" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z200" s="4"/>
       <c r="AA200" s="4"/>
     </row>
-    <row r="201" spans="8:27" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:51" x14ac:dyDescent="0.25">
       <c r="H201" s="6"/>
       <c r="R201" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z201" s="4"/>
       <c r="AA201" s="4"/>
     </row>
-    <row r="202" spans="8:27" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:51" x14ac:dyDescent="0.25">
       <c r="R202" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z202" s="4"/>
       <c r="AA202" s="4"/>
     </row>
-    <row r="203" spans="8:27" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:51" x14ac:dyDescent="0.25">
       <c r="R203" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z203" s="4"/>
       <c r="AA203" s="4"/>
     </row>
-    <row r="204" spans="8:27" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:51" x14ac:dyDescent="0.25">
       <c r="R204" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z204" s="4"/>
       <c r="AA204" s="4"/>
     </row>
-    <row r="205" spans="8:27" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:51" x14ac:dyDescent="0.25">
       <c r="R205" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z205" s="4"/>
       <c r="AA205" s="4"/>
     </row>
-    <row r="206" spans="8:27" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:51" x14ac:dyDescent="0.25">
       <c r="R206" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z206" s="4"/>
       <c r="AA206" s="4"/>
     </row>
-    <row r="207" spans="8:27" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:51" x14ac:dyDescent="0.25">
       <c r="R207" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z207" s="4"/>
       <c r="AA207" s="4"/>
     </row>
-    <row r="208" spans="8:27" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:51" x14ac:dyDescent="0.25">
       <c r="R208" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z208" s="4"/>
@@ -17463,7 +17531,7 @@
     </row>
     <row r="209" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R209" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z209" s="4"/>
@@ -17471,7 +17539,7 @@
     </row>
     <row r="210" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R210" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z210" s="4"/>
@@ -17479,7 +17547,7 @@
     </row>
     <row r="211" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R211" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z211" s="4"/>
@@ -17487,7 +17555,7 @@
     </row>
     <row r="212" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R212" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z212" s="4"/>
@@ -17495,7 +17563,7 @@
     </row>
     <row r="213" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R213" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z213" s="4"/>
@@ -17503,7 +17571,7 @@
     </row>
     <row r="214" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R214" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z214" s="4"/>
@@ -17511,7 +17579,7 @@
     </row>
     <row r="215" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R215" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z215" s="4"/>
@@ -17519,7 +17587,7 @@
     </row>
     <row r="216" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R216" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z216" s="4"/>
@@ -17527,7 +17595,7 @@
     </row>
     <row r="217" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R217" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z217" s="4"/>
@@ -17535,7 +17603,7 @@
     </row>
     <row r="218" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R218" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z218" s="4"/>
@@ -17543,7 +17611,7 @@
     </row>
     <row r="219" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R219" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z219" s="4"/>
@@ -17551,7 +17619,7 @@
     </row>
     <row r="220" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R220" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z220" s="4"/>
@@ -17559,7 +17627,7 @@
     </row>
     <row r="221" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R221" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z221" s="4"/>
@@ -17567,7 +17635,7 @@
     </row>
     <row r="222" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R222" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z222" s="4"/>
@@ -17575,7 +17643,7 @@
     </row>
     <row r="223" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R223" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z223" s="4"/>
@@ -17583,7 +17651,7 @@
     </row>
     <row r="224" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R224" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z224" s="4"/>
@@ -17591,7 +17659,7 @@
     </row>
     <row r="225" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R225" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z225" s="4"/>
@@ -17599,7 +17667,7 @@
     </row>
     <row r="226" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R226" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z226" s="4"/>
@@ -17607,7 +17675,7 @@
     </row>
     <row r="227" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R227" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z227" s="4"/>
@@ -17615,7 +17683,7 @@
     </row>
     <row r="228" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R228" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z228" s="4"/>
@@ -17623,7 +17691,7 @@
     </row>
     <row r="229" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R229" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z229" s="4"/>
@@ -17631,7 +17699,7 @@
     </row>
     <row r="230" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R230" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z230" s="4"/>
@@ -17639,7 +17707,7 @@
     </row>
     <row r="231" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R231" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z231" s="4"/>
@@ -17647,7 +17715,7 @@
     </row>
     <row r="232" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R232" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z232" s="4"/>
@@ -17655,7 +17723,7 @@
     </row>
     <row r="233" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R233" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z233" s="4"/>
@@ -17663,7 +17731,7 @@
     </row>
     <row r="234" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R234" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z234" s="4"/>
@@ -17671,7 +17739,7 @@
     </row>
     <row r="235" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R235" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z235" s="4"/>
@@ -17679,7 +17747,7 @@
     </row>
     <row r="236" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R236" s="2">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="Z236" s="4"/>
@@ -17738,7 +17806,7 @@
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H56:H63 P51 AH51 Y51 H54 H202:H1048576 I197:I1048576 Z162 Z245:AA1048576 R237:R1048576 Q193:Q1048576" xr:uid="{D2C177B6-092A-4420-B1E2-D1681CD512E9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H56:H63 P51 AH51 Y51 H54 H202:H1048576 I197:I1048576 Z162 Z245:AA1048576 R237:R1048576 Q195:Q1048576" xr:uid="{D2C177B6-092A-4420-B1E2-D1681CD512E9}">
       <formula1>"hardcover, paperback, eBook, audiobook1"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="BE1:BE26 BD1:BD23 BD27:BE1048576" xr:uid="{F1FB7CD6-B38A-4A39-862C-8A1111411C8C}">

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/the-polish-atheneum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3449" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF5CB37D-7E22-43E1-BAB5-4CC43E88DE92}"/>
+  <xr:revisionPtr revIDLastSave="3450" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7198AE63-1622-44D1-A945-72EFA975CFD9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
@@ -4407,9 +4407,6 @@
     <t xml:space="preserve">Cherry Orchard </t>
   </si>
   <si>
-    <t>phtantoms-breslau</t>
-  </si>
-  <si>
     <t>Young Reader</t>
   </si>
   <si>
@@ -4420,6 +4417,9 @@
   </si>
   <si>
     <t>Young Reader; Genre Fiction</t>
+  </si>
+  <si>
+    <t>phantoms-breslau</t>
   </si>
 </sst>
 </file>
@@ -5942,7 +5942,7 @@
         <v>62</v>
       </c>
       <c r="B12" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C12">
         <v>1050</v>
@@ -6011,7 +6011,7 @@
         <v>61</v>
       </c>
       <c r="B13" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="C13">
         <v>650</v>
@@ -7579,7 +7579,7 @@
         <v>96</v>
       </c>
       <c r="B33" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C33">
         <v>100</v>
@@ -7681,7 +7681,7 @@
         <v>97</v>
       </c>
       <c r="B34" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C34">
         <v>600</v>
@@ -7757,7 +7757,7 @@
         <v>104</v>
       </c>
       <c r="B35" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="C35">
         <v>220</v>
@@ -7821,7 +7821,7 @@
         <v>103</v>
       </c>
       <c r="B36" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="C36">
         <v>200</v>
@@ -8668,7 +8668,7 @@
         <v>188</v>
       </c>
       <c r="B50" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C50">
         <v>1000</v>
@@ -8741,7 +8741,7 @@
         <v>191</v>
       </c>
       <c r="B51" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C51">
         <v>1100</v>
@@ -8814,7 +8814,7 @@
         <v>190</v>
       </c>
       <c r="B52" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C52">
         <v>1200</v>
@@ -8887,7 +8887,7 @@
         <v>189</v>
       </c>
       <c r="B53" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="C53">
         <v>1300</v>
@@ -10721,7 +10721,7 @@
         <v>429</v>
       </c>
       <c r="B85" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C85">
         <v>750</v>
@@ -11228,7 +11228,7 @@
         <v>484</v>
       </c>
       <c r="B94" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C94">
         <v>970</v>
@@ -11279,7 +11279,7 @@
         <v>491</v>
       </c>
       <c r="B95" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C95">
         <v>555</v>
@@ -15080,7 +15080,7 @@
     </row>
     <row r="155" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="B155" t="s">
         <v>298</v>
@@ -15114,7 +15114,7 @@
       </c>
       <c r="AI155" t="str">
         <f t="shared" si="13"/>
-        <v>covers/phtantoms-breslau.jpg</v>
+        <v>covers/phantoms-breslau.jpg</v>
       </c>
       <c r="AY155" s="34" t="s">
         <v>852</v>
@@ -15946,7 +15946,7 @@
         <v>925</v>
       </c>
       <c r="B169" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C169">
         <v>955</v>
@@ -15998,7 +15998,7 @@
         <v>932</v>
       </c>
       <c r="B170" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C170">
         <v>1005</v>
@@ -16047,7 +16047,7 @@
         <v>935</v>
       </c>
       <c r="B171" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C171">
         <v>1007</v>
@@ -16184,7 +16184,7 @@
         <v>947</v>
       </c>
       <c r="B173" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="C173">
         <v>1009</v>
@@ -17343,7 +17343,7 @@
         <v>1068</v>
       </c>
       <c r="B193" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="D193" s="15" t="s">
         <v>1065</v>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/the-polish-atheneum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3450" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7198AE63-1622-44D1-A945-72EFA975CFD9}"/>
+  <xr:revisionPtr revIDLastSave="3453" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34E9F0B4-A03E-4CC5-BA7F-D423DBFD12C1}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
@@ -15137,7 +15137,7 @@
         <v>298</v>
       </c>
       <c r="C156">
-        <v>835</v>
+        <v>1012</v>
       </c>
       <c r="D156" s="28" t="s">
         <v>854</v>
@@ -15191,7 +15191,7 @@
         <v>298</v>
       </c>
       <c r="C157">
-        <v>835</v>
+        <v>975</v>
       </c>
       <c r="D157" s="15" t="s">
         <v>859</v>
@@ -15256,7 +15256,7 @@
         <v>298</v>
       </c>
       <c r="C158">
-        <v>836</v>
+        <v>1200</v>
       </c>
       <c r="D158" s="15" t="s">
         <v>863</v>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/the-polish-atheneum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3453" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34E9F0B4-A03E-4CC5-BA7F-D423DBFD12C1}"/>
+  <xr:revisionPtr revIDLastSave="3460" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48BE1738-A350-41A9-A23D-EBF837E281E6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
@@ -9439,7 +9439,7 @@
         <v>298</v>
       </c>
       <c r="C62">
-        <v>860</v>
+        <v>1045</v>
       </c>
       <c r="D62" s="15" t="s">
         <v>255</v>
@@ -9495,7 +9495,7 @@
         <v>298</v>
       </c>
       <c r="C63">
-        <v>870</v>
+        <v>1250</v>
       </c>
       <c r="D63" s="15" t="s">
         <v>258</v>
@@ -11117,7 +11117,7 @@
         <v>298</v>
       </c>
       <c r="C92">
-        <v>920</v>
+        <v>320</v>
       </c>
       <c r="D92" s="15" t="s">
         <v>474</v>
@@ -12450,7 +12450,7 @@
         <v>298</v>
       </c>
       <c r="C114">
-        <v>1350</v>
+        <v>750</v>
       </c>
       <c r="D114" s="15" t="s">
         <v>588</v>
@@ -12935,7 +12935,7 @@
         <v>298</v>
       </c>
       <c r="C121">
-        <v>1540</v>
+        <v>775</v>
       </c>
       <c r="D121" s="15" t="s">
         <v>622</v>
@@ -13196,7 +13196,7 @@
         <v>298</v>
       </c>
       <c r="C125">
-        <v>1610</v>
+        <v>927</v>
       </c>
       <c r="D125" s="15" t="s">
         <v>671</v>
@@ -17258,7 +17258,7 @@
         <v>298</v>
       </c>
       <c r="C191">
-        <v>873</v>
+        <v>1741</v>
       </c>
       <c r="D191" s="15" t="s">
         <v>1062</v>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/the-polish-atheneum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3460" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{48BE1738-A350-41A9-A23D-EBF837E281E6}"/>
+  <xr:revisionPtr revIDLastSave="3463" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1410AA8F-F6CB-4C14-AEF5-A21E8F38AE0F}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2394" uniqueCount="1076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2398" uniqueCount="1076">
   <si>
     <t>cover</t>
   </si>
@@ -7573,6 +7573,21 @@
         <f t="shared" si="0"/>
         <v>covers/anima-vilis.jpg</v>
       </c>
+      <c r="BD32" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE32" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG32" t="s">
+        <v>31</v>
+      </c>
+      <c r="BI32" t="s">
+        <v>120</v>
+      </c>
+      <c r="BJ32">
+        <v>2</v>
+      </c>
     </row>
     <row r="33" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A33" t="s">

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/the-polish-atheneum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3463" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1410AA8F-F6CB-4C14-AEF5-A21E8F38AE0F}"/>
+  <xr:revisionPtr revIDLastSave="3555" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5460FCC2-3C56-4E0B-AEE8-F2FE0A5260C6}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2398" uniqueCount="1076">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2449" uniqueCount="1093">
   <si>
     <t>cover</t>
   </si>
@@ -4420,6 +4420,60 @@
   </si>
   <si>
     <t>phantoms-breslau</t>
+  </si>
+  <si>
+    <t>w2vQGGdtwYA</t>
+  </si>
+  <si>
+    <t>David French &amp; Peter Kenny on Translating the Witcher</t>
+  </si>
+  <si>
+    <t>POrkp0NRrqc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+The Witcher Books - Should You Read Them?</t>
+  </si>
+  <si>
+    <t>-xwIqyfPTz4</t>
+  </si>
+  <si>
+    <t>The Witcher - An Introduction</t>
+  </si>
+  <si>
+    <t>KGbNYStMslc</t>
+  </si>
+  <si>
+    <t>The Hussite Trilogy by Andrzej Sapkowski</t>
+  </si>
+  <si>
+    <t>EIhypFAoWhY</t>
+  </si>
+  <si>
+    <t>The Tower of Fools (Hussite Trilogy, 1) by Andrzej Sapkowski</t>
+  </si>
+  <si>
+    <t>Makiwiecki</t>
+  </si>
+  <si>
+    <t>Kapuścinski</t>
+  </si>
+  <si>
+    <t>miracle-fair</t>
+  </si>
+  <si>
+    <t>Miracle Fair: Selected Poems of Wislawa Szymborska</t>
+  </si>
+  <si>
+    <t xml:space="preserve">W. W. Norton </t>
+  </si>
+  <si>
+    <t>"Miracle Fair is Szymborska at her very best."―Harvard Book Review
+Winner of the Heldt Prize for Translation. A new translation of the Nobel Prize-winning Polish poet, with an introduction by Czeslaw Milosz. This long-awaited volume samples the full range of Wislawa Szymborska's major themes: the ironies of love, the wonders of nature's beauty, and the illusory character of art. Szymborska's voice emerges as that of a gentle subversive, self-deprecating in its wit, yet graced with a gift for coaxing the extraordinary out of the ordinary.</t>
+  </si>
+  <si>
+    <t>Miracle Fair is Szymborska at her very best. -- Harvard Book Review
+What Szymborska calls 'the joy of writing' also becomes, in this book, the joy of reading. -- Edward Hirsch</t>
   </si>
 </sst>
 </file>
@@ -4618,7 +4672,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4639,9 +4693,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="1" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4681,6 +4732,23 @@
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5020,33 +5088,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01CE5F32-AD1D-47CB-A8F1-52ACBFFA0BE8}">
   <dimension ref="A1:BJ244"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="29.140625" customWidth="1"/>
-    <col min="2" max="2" width="50.85546875" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="29.1328125" customWidth="1"/>
+    <col min="2" max="2" width="50.86328125" customWidth="1"/>
+    <col min="3" max="3" width="13.73046875" customWidth="1"/>
     <col min="4" max="4" width="46" style="15" customWidth="1"/>
     <col min="5" max="7" width="46" customWidth="1"/>
-    <col min="8" max="10" width="9.140625" style="7"/>
+    <col min="8" max="10" width="9.1328125" style="7"/>
     <col min="11" max="12" width="9" style="7"/>
-    <col min="13" max="15" width="9.140625" style="7"/>
-    <col min="16" max="16" width="28.85546875" style="10" customWidth="1"/>
-    <col min="17" max="24" width="9.140625" style="3"/>
-    <col min="25" max="25" width="17" style="21" customWidth="1"/>
-    <col min="26" max="33" width="9.140625" style="5"/>
+    <col min="13" max="15" width="9.1328125" style="7"/>
+    <col min="16" max="16" width="28.86328125" style="10" customWidth="1"/>
+    <col min="17" max="24" width="9.1328125" style="3"/>
+    <col min="25" max="25" width="17" style="20" customWidth="1"/>
+    <col min="26" max="33" width="9.1328125" style="5"/>
     <col min="34" max="34" width="22" style="8" customWidth="1"/>
-    <col min="35" max="36" width="26.28515625" customWidth="1"/>
+    <col min="35" max="36" width="26.265625" customWidth="1"/>
     <col min="39" max="39" width="16" customWidth="1"/>
-    <col min="41" max="41" width="21.140625" customWidth="1"/>
-    <col min="42" max="45" width="19.7109375" customWidth="1"/>
-    <col min="46" max="46" width="19.7109375" style="25" customWidth="1"/>
-    <col min="47" max="50" width="19.7109375" customWidth="1"/>
-    <col min="51" max="51" width="95.85546875" style="34" customWidth="1"/>
-    <col min="52" max="52" width="66.85546875" style="25" customWidth="1"/>
-    <col min="53" max="55" width="19.7109375" customWidth="1"/>
+    <col min="41" max="41" width="21.1328125" customWidth="1"/>
+    <col min="42" max="45" width="19.73046875" customWidth="1"/>
+    <col min="46" max="46" width="19.73046875" style="24" customWidth="1"/>
+    <col min="47" max="50" width="19.73046875" customWidth="1"/>
+    <col min="51" max="51" width="95.86328125" style="33" customWidth="1"/>
+    <col min="52" max="52" width="66.86328125" style="24" customWidth="1"/>
+    <col min="53" max="55" width="19.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -5119,7 +5187,7 @@
       <c r="X1" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="Y1" s="21" t="s">
+      <c r="Y1" s="20" t="s">
         <v>172</v>
       </c>
       <c r="Z1" s="4" t="s">
@@ -5182,7 +5250,7 @@
       <c r="AS1" t="s">
         <v>653</v>
       </c>
-      <c r="AT1" s="25" t="s">
+      <c r="AT1" s="24" t="s">
         <v>654</v>
       </c>
       <c r="AU1" t="s">
@@ -5197,10 +5265,10 @@
       <c r="AX1" t="s">
         <v>655</v>
       </c>
-      <c r="AY1" s="34" t="s">
+      <c r="AY1" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="AZ1" s="25" t="s">
+      <c r="AZ1" s="24" t="s">
         <v>201</v>
       </c>
       <c r="BA1" t="s">
@@ -5234,7 +5302,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -5272,7 +5340,7 @@
       <c r="U2" s="3">
         <v>15</v>
       </c>
-      <c r="Y2" s="22">
+      <c r="Y2" s="21">
         <v>9780306809330</v>
       </c>
       <c r="Z2" s="4" t="s">
@@ -5295,10 +5363,10 @@
         <f>"covers/" &amp; A2 &amp; ".jpg"</f>
         <v>covers/chopin-in-paris.jpg</v>
       </c>
-      <c r="AY2" s="34" t="s">
+      <c r="AY2" s="33" t="s">
         <v>319</v>
       </c>
-      <c r="AZ2" s="25" t="s">
+      <c r="AZ2" s="24" t="s">
         <v>320</v>
       </c>
       <c r="BA2" t="s">
@@ -5320,7 +5388,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -5358,7 +5426,7 @@
       <c r="U3" s="3">
         <v>15</v>
       </c>
-      <c r="Y3" s="22">
+      <c r="Y3" s="21">
         <v>9780312625948</v>
       </c>
       <c r="Z3" s="4" t="s">
@@ -5381,7 +5449,7 @@
         <f t="shared" ref="AI3:AI72" si="0">"covers/" &amp; A3 &amp; ".jpg"</f>
         <v>covers/peasant-prince.jpg</v>
       </c>
-      <c r="AY3" s="34" t="s">
+      <c r="AY3" s="33" t="s">
         <v>324</v>
       </c>
       <c r="BD3" t="s">
@@ -5394,7 +5462,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -5427,7 +5495,7 @@
       <c r="U4" s="3">
         <v>16</v>
       </c>
-      <c r="Y4" s="22">
+      <c r="Y4" s="21">
         <v>9780008521684</v>
       </c>
       <c r="Z4" s="4" t="s">
@@ -5450,16 +5518,16 @@
         <f t="shared" si="0"/>
         <v>covers/izabela-the-valiant.jpg</v>
       </c>
-      <c r="AY4" s="34" t="s">
+      <c r="AY4" s="33" t="s">
         <v>325</v>
       </c>
-      <c r="AZ4" s="39" t="s">
+      <c r="AZ4" s="38" t="s">
         <v>326</v>
       </c>
       <c r="BA4" t="s">
         <v>328</v>
       </c>
-      <c r="BB4" s="17" t="s">
+      <c r="BB4" s="16" t="s">
         <v>329</v>
       </c>
       <c r="BC4" t="s">
@@ -5475,7 +5543,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -5508,17 +5576,17 @@
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
-      <c r="Y5" s="22"/>
+      <c r="Y5" s="21"/>
       <c r="Z5" s="4"/>
       <c r="AA5" s="4"/>
       <c r="AI5" t="str">
         <f t="shared" si="0"/>
         <v>covers/light-and-flame.jpg</v>
       </c>
-      <c r="AY5" s="34" t="s">
+      <c r="AY5" s="33" t="s">
         <v>330</v>
       </c>
-      <c r="AZ5" s="25" t="s">
+      <c r="AZ5" s="24" t="s">
         <v>331</v>
       </c>
       <c r="BD5" t="s">
@@ -5531,7 +5599,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -5564,7 +5632,7 @@
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
-      <c r="Y6" s="22"/>
+      <c r="Y6" s="21"/>
       <c r="Z6" s="4" t="s">
         <v>111</v>
       </c>
@@ -5585,7 +5653,7 @@
         <f t="shared" si="0"/>
         <v>covers/trail-of-hope.jpg</v>
       </c>
-      <c r="AY6" s="34" t="s">
+      <c r="AY6" s="33" t="s">
         <v>332</v>
       </c>
       <c r="BD6" t="s">
@@ -5598,7 +5666,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -5639,7 +5707,7 @@
       <c r="U7" s="3">
         <v>18</v>
       </c>
-      <c r="Y7" s="22">
+      <c r="Y7" s="21">
         <v>9781607720058</v>
       </c>
       <c r="Z7" s="4"/>
@@ -5648,10 +5716,10 @@
         <f t="shared" si="0"/>
         <v>covers/303-squadron.jpg</v>
       </c>
-      <c r="AY7" s="34" t="s">
+      <c r="AY7" s="33" t="s">
         <v>333</v>
       </c>
-      <c r="AZ7" s="25" t="s">
+      <c r="AZ7" s="24" t="s">
         <v>334</v>
       </c>
       <c r="BD7" t="s">
@@ -5664,7 +5732,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -5698,7 +5766,7 @@
       <c r="U8" s="3">
         <v>14</v>
       </c>
-      <c r="Y8" s="22">
+      <c r="Y8" s="21">
         <v>9781590173831</v>
       </c>
       <c r="Z8" s="4" t="s">
@@ -5721,7 +5789,7 @@
         <f t="shared" si="0"/>
         <v>covers/the-doll.jpg</v>
       </c>
-      <c r="AY8" s="34" t="s">
+      <c r="AY8" s="33" t="s">
         <v>336</v>
       </c>
       <c r="BD8" t="s">
@@ -5734,7 +5802,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -5768,7 +5836,7 @@
       <c r="U9" s="3">
         <v>17</v>
       </c>
-      <c r="Y9" s="22">
+      <c r="Y9" s="21">
         <v>9780241524244</v>
       </c>
       <c r="Z9" s="4"/>
@@ -5780,7 +5848,7 @@
       <c r="AP9" t="s">
         <v>700</v>
       </c>
-      <c r="AR9" s="17" t="s">
+      <c r="AR9" s="16" t="s">
         <v>701</v>
       </c>
       <c r="AS9" t="s">
@@ -5795,7 +5863,7 @@
       <c r="AX9" t="s">
         <v>705</v>
       </c>
-      <c r="AY9" s="34" t="s">
+      <c r="AY9" s="33" t="s">
         <v>335</v>
       </c>
       <c r="BD9" t="s">
@@ -5808,7 +5876,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -5844,7 +5912,7 @@
       <c r="U10" s="3">
         <v>13</v>
       </c>
-      <c r="Y10" s="22">
+      <c r="Y10" s="21">
         <v>9781939810007</v>
       </c>
       <c r="Z10" s="4"/>
@@ -5862,10 +5930,10 @@
       <c r="AR10" t="s">
         <v>690</v>
       </c>
-      <c r="AY10" s="34" t="s">
+      <c r="AY10" s="33" t="s">
         <v>354</v>
       </c>
-      <c r="AZ10" s="25" t="s">
+      <c r="AZ10" s="24" t="s">
         <v>355</v>
       </c>
       <c r="BD10" t="s">
@@ -5878,7 +5946,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -5912,7 +5980,7 @@
       <c r="U11" s="3">
         <v>17</v>
       </c>
-      <c r="Y11" s="22">
+      <c r="Y11" s="21">
         <v>9780875807072</v>
       </c>
       <c r="Z11" s="4"/>
@@ -5921,10 +5989,10 @@
         <f t="shared" si="0"/>
         <v>covers/choucas.jpg</v>
       </c>
-      <c r="AY11" s="34" t="s">
+      <c r="AY11" s="33" t="s">
         <v>356</v>
       </c>
-      <c r="AZ11" s="25" t="s">
+      <c r="AZ11" s="24" t="s">
         <v>357</v>
       </c>
       <c r="BD11" t="s">
@@ -5936,8 +6004,14 @@
       <c r="BG11" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="12" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BI11" t="s">
+        <v>845</v>
+      </c>
+      <c r="BJ11">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>62</v>
       </c>
@@ -5984,7 +6058,7 @@
       <c r="U12" s="3">
         <v>14</v>
       </c>
-      <c r="Y12" s="22">
+      <c r="Y12" s="21">
         <v>9798245149318</v>
       </c>
       <c r="Z12" s="4"/>
@@ -5993,7 +6067,7 @@
         <f t="shared" si="0"/>
         <v>covers/desert-wilderness.jpg</v>
       </c>
-      <c r="AY12" s="34" t="s">
+      <c r="AY12" s="33" t="s">
         <v>358</v>
       </c>
       <c r="BD12" t="s">
@@ -6006,7 +6080,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -6039,14 +6113,14 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" s="2"/>
-      <c r="Y13" s="22"/>
+      <c r="Y13" s="21"/>
       <c r="Z13" s="4"/>
       <c r="AA13" s="4"/>
       <c r="AI13" t="str">
         <f t="shared" si="0"/>
         <v>covers/forest-folk.jpg</v>
       </c>
-      <c r="AY13" s="34" t="s">
+      <c r="AY13" s="33" t="s">
         <v>359</v>
       </c>
       <c r="BD13" t="s">
@@ -6065,7 +6139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -6101,7 +6175,7 @@
       <c r="U14" s="3">
         <v>10</v>
       </c>
-      <c r="Y14" s="22">
+      <c r="Y14" s="21">
         <v>9781852429454</v>
       </c>
       <c r="Z14" s="4"/>
@@ -6110,10 +6184,10 @@
         <f t="shared" si="0"/>
         <v>covers/castorp.jpg</v>
       </c>
-      <c r="AY14" s="34" t="s">
+      <c r="AY14" s="33" t="s">
         <v>360</v>
       </c>
-      <c r="AZ14" s="25" t="s">
+      <c r="AZ14" s="24" t="s">
         <v>361</v>
       </c>
       <c r="BD14" t="s">
@@ -6126,7 +6200,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>72</v>
       </c>
@@ -6160,7 +6234,7 @@
       <c r="U15" s="3">
         <v>12</v>
       </c>
-      <c r="Y15" s="22">
+      <c r="Y15" s="21">
         <v>9780679738015</v>
       </c>
       <c r="Z15" s="4"/>
@@ -6169,10 +6243,10 @@
         <f t="shared" si="0"/>
         <v>covers/shah-of-shahs.jpg</v>
       </c>
-      <c r="AY15" s="34" t="s">
+      <c r="AY15" s="33" t="s">
         <v>362</v>
       </c>
-      <c r="AZ15" s="25" t="s">
+      <c r="AZ15" s="24" t="s">
         <v>364</v>
       </c>
       <c r="BD15" t="s">
@@ -6184,8 +6258,14 @@
       <c r="BG15" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="16" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BI15" t="s">
+        <v>1087</v>
+      </c>
+      <c r="BJ15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>73</v>
       </c>
@@ -6193,7 +6273,7 @@
         <v>74</v>
       </c>
       <c r="C16">
-        <v>400</v>
+        <v>978</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>71</v>
@@ -6219,7 +6299,7 @@
       <c r="U16" s="3">
         <v>12</v>
       </c>
-      <c r="Y16" s="22">
+      <c r="Y16" s="21">
         <v>9780141188034</v>
       </c>
       <c r="Z16" s="4"/>
@@ -6228,10 +6308,10 @@
         <f t="shared" si="0"/>
         <v>covers/the-emperor.jpg</v>
       </c>
-      <c r="AY16" s="34" t="s">
+      <c r="AY16" s="33" t="s">
         <v>365</v>
       </c>
-      <c r="AZ16" s="25" t="s">
+      <c r="AZ16" s="24" t="s">
         <v>366</v>
       </c>
       <c r="BD16" t="s">
@@ -6243,8 +6323,14 @@
       <c r="BG16" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="17" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BI16" t="s">
+        <v>1087</v>
+      </c>
+      <c r="BJ16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>123</v>
       </c>
@@ -6252,9 +6338,9 @@
         <v>74</v>
       </c>
       <c r="C17">
-        <v>420</v>
-      </c>
-      <c r="D17" s="19" t="s">
+        <v>200</v>
+      </c>
+      <c r="D17" s="18" t="s">
         <v>75</v>
       </c>
       <c r="E17" t="s">
@@ -6264,7 +6350,7 @@
         <v>363</v>
       </c>
       <c r="H17" s="6"/>
-      <c r="P17" s="18"/>
+      <c r="P17" s="17"/>
       <c r="Q17" s="2" t="s">
         <v>110</v>
       </c>
@@ -6278,7 +6364,7 @@
       <c r="U17" s="3">
         <v>11</v>
       </c>
-      <c r="Y17" s="22">
+      <c r="Y17" s="21">
         <v>9780375726293</v>
       </c>
       <c r="Z17" s="4"/>
@@ -6308,10 +6394,10 @@
       <c r="AX17" t="s">
         <v>709</v>
       </c>
-      <c r="AY17" s="35" t="s">
+      <c r="AY17" s="34" t="s">
         <v>372</v>
       </c>
-      <c r="AZ17" s="25" t="s">
+      <c r="AZ17" s="24" t="s">
         <v>688</v>
       </c>
       <c r="BD17" t="s">
@@ -6323,8 +6409,14 @@
       <c r="BG17" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="18" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BI17" t="s">
+        <v>1087</v>
+      </c>
+      <c r="BJ17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>367</v>
       </c>
@@ -6332,7 +6424,7 @@
         <v>74</v>
       </c>
       <c r="C18">
-        <v>440</v>
+        <v>1400</v>
       </c>
       <c r="D18" s="14" t="s">
         <v>368</v>
@@ -6354,7 +6446,7 @@
       <c r="S18" s="3">
         <v>17</v>
       </c>
-      <c r="Y18" s="22">
+      <c r="Y18" s="21">
         <v>9780679779070</v>
       </c>
       <c r="Z18" s="4"/>
@@ -6363,10 +6455,10 @@
         <f>"covers/" &amp; A18 &amp; ".jpg"</f>
         <v>covers/shadow-of-sun.jpg</v>
       </c>
-      <c r="AY18" s="34" t="s">
+      <c r="AY18" s="33" t="s">
         <v>370</v>
       </c>
-      <c r="AZ18" s="25" t="s">
+      <c r="AZ18" s="24" t="s">
         <v>371</v>
       </c>
       <c r="BD18" t="s">
@@ -6378,8 +6470,14 @@
       <c r="BG18" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="19" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BI18" t="s">
+        <v>1087</v>
+      </c>
+      <c r="BJ18">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>122</v>
       </c>
@@ -6423,7 +6521,7 @@
         <f>I19</f>
         <v>Mondrala Press</v>
       </c>
-      <c r="Y19" s="21">
+      <c r="Y19" s="20">
         <v>9789998795204</v>
       </c>
       <c r="Z19" s="4" t="s">
@@ -6446,7 +6544,7 @@
         <f>"covers/" &amp; A19 &amp; ".jpg"</f>
         <v>covers/seven-against-thebes.jpg</v>
       </c>
-      <c r="AY19" s="34" t="s">
+      <c r="AY19" s="33" t="s">
         <v>374</v>
       </c>
       <c r="BD19" t="s">
@@ -6465,7 +6563,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>84</v>
       </c>
@@ -6518,7 +6616,7 @@
       <c r="U20" s="3">
         <v>11</v>
       </c>
-      <c r="Y20" s="21">
+      <c r="Y20" s="20">
         <v>9782919820306</v>
       </c>
       <c r="Z20" s="4" t="s">
@@ -6541,7 +6639,7 @@
         <f>"covers/" &amp; A20 &amp; ".jpg"</f>
         <v>covers/last-olympiad.jpg</v>
       </c>
-      <c r="AY20" s="34" t="s">
+      <c r="AY20" s="33" t="s">
         <v>376</v>
       </c>
       <c r="BD20" t="s">
@@ -6560,7 +6658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>80</v>
       </c>
@@ -6613,7 +6711,7 @@
       <c r="U21" s="3">
         <v>15</v>
       </c>
-      <c r="Y21" s="21">
+      <c r="Y21" s="20">
         <v>9782919820382</v>
       </c>
       <c r="Z21" s="4" t="s">
@@ -6636,7 +6734,7 @@
         <f t="shared" si="0"/>
         <v>covers/meeting-in-oea.jpg</v>
       </c>
-      <c r="AY21" s="34" t="s">
+      <c r="AY21" s="33" t="s">
         <v>373</v>
       </c>
       <c r="BD21" t="s">
@@ -6655,7 +6753,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>1018</v>
       </c>
@@ -6708,7 +6806,7 @@
       <c r="U22" s="3">
         <v>15</v>
       </c>
-      <c r="Y22" s="21">
+      <c r="Y22" s="20">
         <v>9782919820658</v>
       </c>
       <c r="Z22" s="4" t="s">
@@ -6734,7 +6832,7 @@
         <f t="shared" si="0"/>
         <v>covers/herod-king.jpg</v>
       </c>
-      <c r="AY22" s="34" t="s">
+      <c r="AY22" s="33" t="s">
         <v>1023</v>
       </c>
       <c r="BE22" t="s">
@@ -6742,12 +6840,15 @@
       </c>
       <c r="BG22" t="s">
         <v>31</v>
+      </c>
+      <c r="BI22" t="s">
+        <v>638</v>
       </c>
       <c r="BJ22">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>1020</v>
       </c>
@@ -6800,7 +6901,7 @@
       <c r="U23" s="3">
         <v>13</v>
       </c>
-      <c r="Y23" s="21">
+      <c r="Y23" s="20">
         <v>9782919820528</v>
       </c>
       <c r="Z23" s="4" t="s">
@@ -6826,7 +6927,7 @@
         <f t="shared" si="0"/>
         <v>covers/titus-berenice.jpg</v>
       </c>
-      <c r="AY23" s="34" t="s">
+      <c r="AY23" s="33" t="s">
         <v>1022</v>
       </c>
       <c r="BE23" t="s">
@@ -6834,12 +6935,15 @@
       </c>
       <c r="BG23" t="s">
         <v>31</v>
+      </c>
+      <c r="BI23" t="s">
+        <v>638</v>
       </c>
       <c r="BJ23">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>1024</v>
       </c>
@@ -6892,7 +6996,7 @@
       <c r="U24" s="3">
         <v>15</v>
       </c>
-      <c r="Y24" s="21">
+      <c r="Y24" s="20">
         <v>9782919820689</v>
       </c>
       <c r="Z24" s="4" t="s">
@@ -6918,7 +7022,7 @@
         <f t="shared" si="0"/>
         <v>covers/rome-jerusalem.jpg</v>
       </c>
-      <c r="AY24" s="34" t="s">
+      <c r="AY24" s="33" t="s">
         <v>1026</v>
       </c>
       <c r="BE24" t="s">
@@ -6926,12 +7030,15 @@
       </c>
       <c r="BG24" t="s">
         <v>31</v>
+      </c>
+      <c r="BI24" t="s">
+        <v>638</v>
       </c>
       <c r="BJ24">
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>1027</v>
       </c>
@@ -6984,7 +7091,7 @@
       <c r="U25" s="3">
         <v>15</v>
       </c>
-      <c r="Y25" s="21">
+      <c r="Y25" s="20">
         <v>9782919820740</v>
       </c>
       <c r="Z25" s="4" t="s">
@@ -7010,7 +7117,7 @@
         <f t="shared" si="0"/>
         <v>covers/constantine.jpg</v>
       </c>
-      <c r="AY25" s="34" t="s">
+      <c r="AY25" s="33" t="s">
         <v>1029</v>
       </c>
       <c r="BE25" t="s">
@@ -7018,12 +7125,15 @@
       </c>
       <c r="BG25" t="s">
         <v>31</v>
+      </c>
+      <c r="BI25" t="s">
+        <v>638</v>
       </c>
       <c r="BJ25">
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>1030</v>
       </c>
@@ -7076,7 +7186,7 @@
       <c r="U26" s="3">
         <v>15</v>
       </c>
-      <c r="Y26" s="21">
+      <c r="Y26" s="20">
         <v>9782919820771</v>
       </c>
       <c r="Z26" s="4" t="s">
@@ -7102,7 +7212,7 @@
         <f t="shared" si="0"/>
         <v>covers/devils-brood.jpg</v>
       </c>
-      <c r="AY26" s="34" t="s">
+      <c r="AY26" s="33" t="s">
         <v>1032</v>
       </c>
       <c r="BE26" t="s">
@@ -7110,12 +7220,15 @@
       </c>
       <c r="BG26" t="s">
         <v>31</v>
+      </c>
+      <c r="BI26" t="s">
+        <v>638</v>
       </c>
       <c r="BJ26">
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>1064</v>
       </c>
@@ -7168,7 +7281,7 @@
       <c r="U27" s="3">
         <v>16</v>
       </c>
-      <c r="Y27" s="21">
+      <c r="Y27" s="20">
         <v>9782919840052</v>
       </c>
       <c r="Z27" s="4" t="s">
@@ -7194,7 +7307,7 @@
         <f t="shared" si="0"/>
         <v>covers/emperor-julian.jpg</v>
       </c>
-      <c r="AY27" s="34" t="s">
+      <c r="AY27" s="33" t="s">
         <v>375</v>
       </c>
       <c r="BD27" t="s">
@@ -7213,7 +7326,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>87</v>
       </c>
@@ -7221,7 +7334,7 @@
         <v>298</v>
       </c>
       <c r="C28">
-        <v>600</v>
+        <v>1120</v>
       </c>
       <c r="D28" s="14" t="s">
         <v>88</v>
@@ -7247,7 +7360,7 @@
       <c r="U28" s="3">
         <v>8</v>
       </c>
-      <c r="Y28" s="21">
+      <c r="Y28" s="20">
         <v>9780156027601</v>
       </c>
       <c r="Z28" s="4"/>
@@ -7280,7 +7393,7 @@
       <c r="AX28" t="s">
         <v>698</v>
       </c>
-      <c r="AY28" s="34" t="s">
+      <c r="AY28" s="33" t="s">
         <v>377</v>
       </c>
       <c r="BD28" t="s">
@@ -7293,7 +7406,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>91</v>
       </c>
@@ -7327,7 +7440,7 @@
       <c r="U29" s="3">
         <v>12</v>
       </c>
-      <c r="Y29" s="21">
+      <c r="Y29" s="20">
         <v>9780156306300</v>
       </c>
       <c r="Z29" s="4"/>
@@ -7336,7 +7449,7 @@
         <f t="shared" si="0"/>
         <v>covers/fiasco.jpg</v>
       </c>
-      <c r="AY29" s="34" t="s">
+      <c r="AY29" s="33" t="s">
         <v>378</v>
       </c>
       <c r="BD29" t="s">
@@ -7349,7 +7462,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>121</v>
       </c>
@@ -7357,7 +7470,7 @@
         <v>298</v>
       </c>
       <c r="C30">
-        <v>600</v>
+        <v>806</v>
       </c>
       <c r="D30" s="14" t="s">
         <v>94</v>
@@ -7383,7 +7496,7 @@
       <c r="U30" s="3">
         <v>13</v>
       </c>
-      <c r="Y30" s="21">
+      <c r="Y30" s="20">
         <v>9780262357685</v>
       </c>
       <c r="Z30" s="4"/>
@@ -7392,7 +7505,7 @@
         <f t="shared" si="0"/>
         <v>covers/the-invincible.jpg</v>
       </c>
-      <c r="AY30" s="34" t="s">
+      <c r="AY30" s="33" t="s">
         <v>379</v>
       </c>
       <c r="BD30" t="s">
@@ -7405,7 +7518,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>105</v>
       </c>
@@ -7455,7 +7568,7 @@
       <c r="U31" s="3">
         <v>15</v>
       </c>
-      <c r="Y31" s="21">
+      <c r="Y31" s="20">
         <v>9782919840106</v>
       </c>
       <c r="Z31" s="4" t="str">
@@ -7498,7 +7611,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>1033</v>
       </c>
@@ -7546,7 +7659,7 @@
       <c r="U32" s="3">
         <v>13</v>
       </c>
-      <c r="Y32" s="21">
+      <c r="Y32" s="20">
         <v>9782919820139</v>
       </c>
       <c r="Z32" s="4" t="str">
@@ -7589,7 +7702,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>96</v>
       </c>
@@ -7639,7 +7752,7 @@
       <c r="U33" s="3">
         <v>15</v>
       </c>
-      <c r="Y33" s="21">
+      <c r="Y33" s="20">
         <v>9789998791664</v>
       </c>
       <c r="Z33" s="4" t="str">
@@ -7666,10 +7779,10 @@
         <f t="shared" si="0"/>
         <v>covers/melicles.jpg</v>
       </c>
-      <c r="AY33" s="34" t="s">
+      <c r="AY33" s="33" t="s">
         <v>203</v>
       </c>
-      <c r="AZ33" s="25" t="s">
+      <c r="AZ33" s="24" t="s">
         <v>206</v>
       </c>
       <c r="BA33" t="s">
@@ -7690,8 +7803,14 @@
       <c r="BG33" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="34" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BI33" t="s">
+        <v>1086</v>
+      </c>
+      <c r="BJ33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>97</v>
       </c>
@@ -7754,7 +7873,7 @@
         <f t="shared" si="0"/>
         <v>covers/diossos.jpg</v>
       </c>
-      <c r="AY34" s="34" t="s">
+      <c r="AY34" s="33" t="s">
         <v>380</v>
       </c>
       <c r="BD34" t="s">
@@ -7766,8 +7885,14 @@
       <c r="BG34" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="35" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BI34" t="s">
+        <v>1086</v>
+      </c>
+      <c r="BJ34">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>104</v>
       </c>
@@ -7812,7 +7937,7 @@
         <f t="shared" si="0"/>
         <v>covers/white-jaguar-1.jpg</v>
       </c>
-      <c r="AY35" s="34" t="s">
+      <c r="AY35" s="33" t="s">
         <v>382</v>
       </c>
       <c r="BD35" t="s">
@@ -7831,7 +7956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>103</v>
       </c>
@@ -7876,7 +8001,7 @@
         <f t="shared" si="0"/>
         <v>covers/ships-minos-1.jpg</v>
       </c>
-      <c r="AY36" s="34" t="s">
+      <c r="AY36" s="33" t="s">
         <v>381</v>
       </c>
       <c r="BD36" t="s">
@@ -7895,7 +8020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>116</v>
       </c>
@@ -7935,7 +8060,7 @@
       <c r="S37" s="3">
         <v>16</v>
       </c>
-      <c r="Y37" s="21">
+      <c r="Y37" s="20">
         <v>9789998793774</v>
       </c>
       <c r="Z37" s="4" t="s">
@@ -7954,7 +8079,7 @@
         <f t="shared" si="0"/>
         <v>covers/divine-julius.jpg</v>
       </c>
-      <c r="AY37" s="34" t="s">
+      <c r="AY37" s="33" t="s">
         <v>383</v>
       </c>
       <c r="BD37" t="s">
@@ -7973,7 +8098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>117</v>
       </c>
@@ -8013,7 +8138,7 @@
       <c r="S38" s="3">
         <v>17</v>
       </c>
-      <c r="Y38" s="21">
+      <c r="Y38" s="20">
         <v>9782919820054</v>
       </c>
       <c r="Z38" s="4" t="s">
@@ -8032,7 +8157,7 @@
         <f t="shared" si="0"/>
         <v>covers/naso-the-poet.jpg</v>
       </c>
-      <c r="AY38" s="34" t="s">
+      <c r="AY38" s="33" t="s">
         <v>384</v>
       </c>
       <c r="BD38" t="s">
@@ -8051,7 +8176,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>118</v>
       </c>
@@ -8091,7 +8216,7 @@
       <c r="S39" s="3">
         <v>18</v>
       </c>
-      <c r="Y39" s="21">
+      <c r="Y39" s="20">
         <v>9782919820450</v>
       </c>
       <c r="Z39" s="4"/>
@@ -8100,7 +8225,7 @@
         <f t="shared" si="0"/>
         <v>covers/tiberius-caesar.jpg</v>
       </c>
-      <c r="AY39" s="34" t="s">
+      <c r="AY39" s="33" t="s">
         <v>385</v>
       </c>
       <c r="BD39" t="s">
@@ -8119,7 +8244,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>150</v>
       </c>
@@ -8145,7 +8270,7 @@
       <c r="S40" s="3">
         <v>14</v>
       </c>
-      <c r="Y40" s="21">
+      <c r="Y40" s="20">
         <v>9780062095886</v>
       </c>
       <c r="Z40" s="4"/>
@@ -8154,7 +8279,7 @@
         <f t="shared" si="0"/>
         <v>covers/milosz-selected-and-last-poems.jpg</v>
       </c>
-      <c r="AY40" s="34" t="s">
+      <c r="AY40" s="33" t="s">
         <v>386</v>
       </c>
       <c r="BD40" t="s">
@@ -8167,7 +8292,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>154</v>
       </c>
@@ -8204,7 +8329,7 @@
       <c r="S41" s="3">
         <v>11</v>
       </c>
-      <c r="Y41" s="22">
+      <c r="Y41" s="21">
         <v>9780156011464</v>
       </c>
       <c r="Z41" s="4"/>
@@ -8213,7 +8338,7 @@
         <f t="shared" si="0"/>
         <v>covers/poems-new-and-szymborska.jpg</v>
       </c>
-      <c r="AY41" s="34" t="s">
+      <c r="AY41" s="33" t="s">
         <v>387</v>
       </c>
       <c r="BD41" t="s">
@@ -8226,7 +8351,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>155</v>
       </c>
@@ -8252,7 +8377,7 @@
       <c r="S42" s="3">
         <v>17</v>
       </c>
-      <c r="Y42" s="22">
+      <c r="Y42" s="21">
         <v>9780060783952</v>
       </c>
       <c r="Z42" s="4"/>
@@ -8261,10 +8386,10 @@
         <f t="shared" si="0"/>
         <v>covers/poems-herbert.jpg</v>
       </c>
-      <c r="AY42" s="34" t="s">
+      <c r="AY42" s="33" t="s">
         <v>388</v>
       </c>
-      <c r="AZ42" s="25" t="s">
+      <c r="AZ42" s="24" t="s">
         <v>389</v>
       </c>
       <c r="BD42" t="s">
@@ -8277,7 +8402,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>145</v>
       </c>
@@ -8303,7 +8428,7 @@
       <c r="S43" s="3">
         <v>15</v>
       </c>
-      <c r="Y43" s="21">
+      <c r="Y43" s="20">
         <v>9780374528614</v>
       </c>
       <c r="Z43" s="4"/>
@@ -8312,10 +8437,10 @@
         <f t="shared" si="0"/>
         <v>covers/without-end.jpg</v>
       </c>
-      <c r="AY43" s="34" t="s">
+      <c r="AY43" s="33" t="s">
         <v>391</v>
       </c>
-      <c r="AZ43" s="25" t="s">
+      <c r="AZ43" s="24" t="s">
         <v>392</v>
       </c>
       <c r="BD43" t="s">
@@ -8328,7 +8453,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>146</v>
       </c>
@@ -8369,7 +8494,7 @@
       <c r="S44" s="3">
         <v>19</v>
       </c>
-      <c r="Y44" s="21">
+      <c r="Y44" s="20">
         <v>9780393345551</v>
       </c>
       <c r="Z44" s="4"/>
@@ -8378,10 +8503,10 @@
         <f t="shared" si="0"/>
         <v>covers/sobbing-superpower.jpg</v>
       </c>
-      <c r="AY44" s="34" t="s">
+      <c r="AY44" s="33" t="s">
         <v>393</v>
       </c>
-      <c r="AZ44" s="25" t="s">
+      <c r="AZ44" s="24" t="s">
         <v>394</v>
       </c>
       <c r="BD44" t="s">
@@ -8394,7 +8519,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>147</v>
       </c>
@@ -8432,7 +8557,7 @@
       <c r="S45" s="3">
         <v>11</v>
       </c>
-      <c r="Y45" s="21">
+      <c r="Y45" s="20">
         <v>9780544705159</v>
       </c>
       <c r="Z45" s="4"/>
@@ -8441,10 +8566,10 @@
         <f t="shared" si="0"/>
         <v>covers/map-collected-and-last.jpg</v>
       </c>
-      <c r="AY45" s="34" t="s">
+      <c r="AY45" s="33" t="s">
         <v>395</v>
       </c>
-      <c r="AZ45" s="25" t="s">
+      <c r="AZ45" s="24" t="s">
         <v>396</v>
       </c>
       <c r="BD45" t="s">
@@ -8457,7 +8582,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>148</v>
       </c>
@@ -8498,7 +8623,7 @@
       <c r="S46" s="3">
         <v>11</v>
       </c>
-      <c r="Y46" s="21">
+      <c r="Y46" s="20">
         <v>9788367602471</v>
       </c>
       <c r="Z46" s="4"/>
@@ -8507,7 +8632,7 @@
         <f t="shared" si="0"/>
         <v>covers/from-tree-of-knowledge.jpg</v>
       </c>
-      <c r="AY46" s="34" t="s">
+      <c r="AY46" s="33" t="s">
         <v>397</v>
       </c>
       <c r="BD46" t="s">
@@ -8520,7 +8645,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>200</v>
       </c>
@@ -8544,7 +8669,7 @@
       <c r="S47" s="3">
         <v>7</v>
       </c>
-      <c r="Y47" s="21">
+      <c r="Y47" s="20">
         <v>9798802065853</v>
       </c>
       <c r="Z47" s="4"/>
@@ -8553,7 +8678,7 @@
         <f t="shared" si="0"/>
         <v>covers/krzysztof-kamil-baczynski.jpg</v>
       </c>
-      <c r="AY47" s="34" t="s">
+      <c r="AY47" s="33" t="s">
         <v>398</v>
       </c>
       <c r="BD47" t="s">
@@ -8566,7 +8691,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>149</v>
       </c>
@@ -8593,7 +8718,7 @@
       <c r="S48" s="3">
         <v>14</v>
       </c>
-      <c r="Y48" s="21">
+      <c r="Y48" s="20">
         <v>9781931243810</v>
       </c>
       <c r="Z48" s="4"/>
@@ -8602,7 +8727,7 @@
         <f t="shared" si="0"/>
         <v>covers/white-magic-baczynski.jpg</v>
       </c>
-      <c r="AY48" s="34" t="s">
+      <c r="AY48" s="33" t="s">
         <v>399</v>
       </c>
       <c r="BD48" t="s">
@@ -8615,7 +8740,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>196</v>
       </c>
@@ -8656,7 +8781,7 @@
       <c r="S49" s="3">
         <v>9.99</v>
       </c>
-      <c r="Y49" s="21">
+      <c r="Y49" s="20">
         <v>9788367602419</v>
       </c>
       <c r="Z49" s="4"/>
@@ -8665,7 +8790,7 @@
         <f t="shared" si="0"/>
         <v>covers/new-poems-ukr-po.jpg</v>
       </c>
-      <c r="AY49" s="34" t="s">
+      <c r="AY49" s="33" t="s">
         <v>199</v>
       </c>
       <c r="BD49" t="s">
@@ -8678,7 +8803,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>188</v>
       </c>
@@ -8686,7 +8811,7 @@
         <v>1074</v>
       </c>
       <c r="C50">
-        <v>1000</v>
+        <v>602</v>
       </c>
       <c r="D50" s="15" t="s">
         <v>184</v>
@@ -8719,7 +8844,7 @@
       <c r="S50" s="3">
         <v>13</v>
       </c>
-      <c r="Y50" s="21">
+      <c r="Y50" s="20">
         <v>9782919820856</v>
       </c>
       <c r="Z50" s="4" t="s">
@@ -8738,7 +8863,7 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-templars.jpg</v>
       </c>
-      <c r="AY50" s="34" t="s">
+      <c r="AY50" s="33" t="s">
         <v>193</v>
       </c>
       <c r="BD50" t="s">
@@ -8751,7 +8876,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>191</v>
       </c>
@@ -8792,7 +8917,7 @@
       <c r="S51" s="3">
         <v>17</v>
       </c>
-      <c r="Y51" s="21">
+      <c r="Y51" s="20">
         <v>9782919840021</v>
       </c>
       <c r="Z51" s="4" t="s">
@@ -8811,7 +8936,7 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-mysteries.jpg</v>
       </c>
-      <c r="AY51" s="34" t="s">
+      <c r="AY51" s="33" t="s">
         <v>195</v>
       </c>
       <c r="BD51" t="s">
@@ -8824,7 +8949,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>190</v>
       </c>
@@ -8865,7 +8990,7 @@
       <c r="S52" s="3">
         <v>15</v>
       </c>
-      <c r="Y52" s="22">
+      <c r="Y52" s="21">
         <v>9782919820948</v>
       </c>
       <c r="Z52" s="4" t="s">
@@ -8884,7 +9009,7 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-bandits.jpg</v>
       </c>
-      <c r="AY52" s="34" t="s">
+      <c r="AY52" s="33" t="s">
         <v>192</v>
       </c>
       <c r="BD52" t="s">
@@ -8897,7 +9022,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>189</v>
       </c>
@@ -8938,7 +9063,7 @@
       <c r="S53" s="3">
         <v>13</v>
       </c>
-      <c r="Y53" s="21">
+      <c r="Y53" s="20">
         <v>9782919820900</v>
       </c>
       <c r="Z53" s="4" t="s">
@@ -8957,7 +9082,7 @@
         <f t="shared" si="0"/>
         <v>covers/wheels-copernicus.jpg</v>
       </c>
-      <c r="AY53" s="36" t="s">
+      <c r="AY53" s="35" t="s">
         <v>194</v>
       </c>
       <c r="BD53" t="s">
@@ -8970,7 +9095,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="54" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>209</v>
       </c>
@@ -8998,7 +9123,7 @@
       <c r="S54" s="3">
         <v>19</v>
       </c>
-      <c r="Y54" s="21">
+      <c r="Y54" s="20">
         <v>9781905583393</v>
       </c>
       <c r="Z54" s="4" t="s">
@@ -9017,7 +9142,7 @@
         <f t="shared" si="0"/>
         <v>covers/cold-sea.jpg</v>
       </c>
-      <c r="AY54" s="34" t="s">
+      <c r="AY54" s="33" t="s">
         <v>212</v>
       </c>
       <c r="BD54" t="s">
@@ -9030,7 +9155,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>213</v>
       </c>
@@ -9070,7 +9195,7 @@
       <c r="S55" s="3">
         <v>22</v>
       </c>
-      <c r="Y55" s="21">
+      <c r="Y55" s="20">
         <v>9780140445800</v>
       </c>
       <c r="Z55" s="4" t="s">
@@ -9102,7 +9227,7 @@
       <c r="AS55" t="s">
         <v>658</v>
       </c>
-      <c r="AT55" s="25" t="s">
+      <c r="AT55" s="24" t="s">
         <v>662</v>
       </c>
       <c r="AU55" t="s">
@@ -9117,7 +9242,7 @@
       <c r="AX55" t="s">
         <v>659</v>
       </c>
-      <c r="AY55" s="36" t="s">
+      <c r="AY55" s="35" t="s">
         <v>214</v>
       </c>
       <c r="BD55" t="s">
@@ -9130,7 +9255,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="56" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>218</v>
       </c>
@@ -9158,7 +9283,7 @@
       <c r="S56" s="3">
         <v>28</v>
       </c>
-      <c r="Y56" s="21">
+      <c r="Y56" s="20">
         <v>9789639241459</v>
       </c>
       <c r="Z56" s="4"/>
@@ -9167,7 +9292,7 @@
         <f t="shared" si="0"/>
         <v>covers/birch-grove.jpg</v>
       </c>
-      <c r="AY56" s="34" t="s">
+      <c r="AY56" s="33" t="s">
         <v>221</v>
       </c>
       <c r="BD56" t="s">
@@ -9180,15 +9305,15 @@
         <v>31</v>
       </c>
     </row>
-    <row r="57" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>223</v>
       </c>
       <c r="B57" t="s">
-        <v>40</v>
+        <v>738</v>
       </c>
       <c r="C57">
-        <v>750</v>
+        <v>320</v>
       </c>
       <c r="D57" s="15" t="s">
         <v>222</v>
@@ -9209,7 +9334,7 @@
       <c r="S57" s="3">
         <v>22</v>
       </c>
-      <c r="Y57" s="21">
+      <c r="Y57" s="20">
         <v>9780810108066</v>
       </c>
       <c r="Z57" s="4"/>
@@ -9218,7 +9343,7 @@
         <f t="shared" si="0"/>
         <v>covers/danton-thermidor.jpg</v>
       </c>
-      <c r="AY57" s="36" t="s">
+      <c r="AY57" s="35" t="s">
         <v>227</v>
       </c>
       <c r="BD57" t="s">
@@ -9231,7 +9356,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="58" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>228</v>
       </c>
@@ -9259,7 +9384,7 @@
       <c r="S58" s="3">
         <v>39</v>
       </c>
-      <c r="Y58" s="21">
+      <c r="Y58" s="20">
         <v>9789637326899</v>
       </c>
       <c r="Z58" s="4"/>
@@ -9268,7 +9393,7 @@
         <f t="shared" si="0"/>
         <v>covers/coming-spring.jpg</v>
       </c>
-      <c r="AY58" s="34" t="s">
+      <c r="AY58" s="33" t="s">
         <v>230</v>
       </c>
       <c r="BD58" t="s">
@@ -9281,7 +9406,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="59" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>242</v>
       </c>
@@ -9306,7 +9431,7 @@
       <c r="S59" s="3">
         <v>57.99</v>
       </c>
-      <c r="Y59" s="21">
+      <c r="Y59" s="20">
         <v>9781412865432</v>
       </c>
       <c r="Z59" s="4" t="s">
@@ -9326,7 +9451,7 @@
         <f t="shared" si="0"/>
         <v>covers/beniowski.jpg</v>
       </c>
-      <c r="AY59" s="34" t="s">
+      <c r="AY59" s="33" t="s">
         <v>241</v>
       </c>
       <c r="BD59" t="s">
@@ -9339,58 +9464,96 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:62" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
+    <row r="60" spans="1:62" s="39" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A60" s="39" t="s">
         <v>243</v>
       </c>
-      <c r="B60" t="s">
+      <c r="B60" s="39" t="s">
         <v>298</v>
       </c>
       <c r="C60">
-        <v>600</v>
-      </c>
-      <c r="D60" s="15" t="s">
+        <v>603</v>
+      </c>
+      <c r="D60" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E60" s="39" t="s">
         <v>245</v>
       </c>
-      <c r="F60" s="16" t="s">
+      <c r="F60" s="39" t="s">
         <v>246</v>
       </c>
-      <c r="G60" s="16"/>
-      <c r="Q60" s="2" t="s">
+      <c r="H60" s="41"/>
+      <c r="I60" s="41"/>
+      <c r="J60" s="41"/>
+      <c r="K60" s="41"/>
+      <c r="L60" s="41"/>
+      <c r="M60" s="41"/>
+      <c r="N60" s="41"/>
+      <c r="O60" s="41"/>
+      <c r="P60" s="41"/>
+      <c r="Q60" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="R60" s="7" t="s">
+      <c r="R60" s="41" t="s">
         <v>247</v>
       </c>
-      <c r="S60" s="3">
+      <c r="S60" s="43">
         <v>50</v>
       </c>
-      <c r="Y60" s="21">
+      <c r="T60" s="43"/>
+      <c r="U60" s="43"/>
+      <c r="V60" s="43"/>
+      <c r="W60" s="43"/>
+      <c r="X60" s="43"/>
+      <c r="Y60" s="44">
         <v>9780316498845</v>
       </c>
-      <c r="Z60" s="4"/>
-      <c r="AA60" s="4"/>
-      <c r="AI60" t="str">
+      <c r="Z60" s="45"/>
+      <c r="AA60" s="45"/>
+      <c r="AB60" s="46"/>
+      <c r="AC60" s="46"/>
+      <c r="AD60" s="46"/>
+      <c r="AE60" s="46"/>
+      <c r="AF60" s="46"/>
+      <c r="AG60" s="46"/>
+      <c r="AH60" s="46"/>
+      <c r="AI60" s="39" t="str">
         <f t="shared" si="0"/>
         <v>covers/witcher-set.jpg</v>
       </c>
-      <c r="AY60" s="36" t="s">
+      <c r="AP60" s="39" t="s">
+        <v>1077</v>
+      </c>
+      <c r="AR60" s="39" t="s">
+        <v>1076</v>
+      </c>
+      <c r="AS60" s="39" t="s">
+        <v>1079</v>
+      </c>
+      <c r="AU60" s="39" t="s">
+        <v>1078</v>
+      </c>
+      <c r="AV60" s="39" t="s">
+        <v>1081</v>
+      </c>
+      <c r="AX60" s="47" t="s">
+        <v>1080</v>
+      </c>
+      <c r="AY60" s="48" t="s">
         <v>248</v>
       </c>
-      <c r="BD60" t="s">
-        <v>23</v>
-      </c>
-      <c r="BE60" t="s">
-        <v>23</v>
-      </c>
-      <c r="BG60" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="61" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BD60" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE60" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG60" s="39" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="61" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>249</v>
       </c>
@@ -9418,7 +9581,7 @@
       <c r="S61" s="3">
         <v>18</v>
       </c>
-      <c r="Y61" s="21">
+      <c r="Y61" s="20">
         <v>9780316423694</v>
       </c>
       <c r="Z61" s="4"/>
@@ -9427,7 +9590,19 @@
         <f t="shared" si="0"/>
         <v>covers/tower-fools.jpg</v>
       </c>
-      <c r="AY61" s="34" t="s">
+      <c r="AP61" s="39" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AR61" t="s">
+        <v>1082</v>
+      </c>
+      <c r="AS61" t="s">
+        <v>1085</v>
+      </c>
+      <c r="AU61" t="s">
+        <v>1084</v>
+      </c>
+      <c r="AY61" s="33" t="s">
         <v>252</v>
       </c>
       <c r="BD61" t="s">
@@ -9446,7 +9621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>254</v>
       </c>
@@ -9474,7 +9649,7 @@
       <c r="S62" s="3">
         <v>9.99</v>
       </c>
-      <c r="Y62" s="21">
+      <c r="Y62" s="20">
         <v>9780316423717</v>
       </c>
       <c r="Z62" s="4"/>
@@ -9483,7 +9658,13 @@
         <f t="shared" si="0"/>
         <v>covers/warrior-god.jpg</v>
       </c>
-      <c r="AY62" s="36" t="s">
+      <c r="AP62" s="39" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AR62" t="s">
+        <v>1082</v>
+      </c>
+      <c r="AY62" s="35" t="s">
         <v>256</v>
       </c>
       <c r="BD62" t="s">
@@ -9502,7 +9683,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>257</v>
       </c>
@@ -9530,7 +9711,7 @@
       <c r="S63" s="3">
         <v>16</v>
       </c>
-      <c r="Y63" s="21">
+      <c r="Y63" s="20">
         <v>9780316423755</v>
       </c>
       <c r="Z63" s="4"/>
@@ -9539,7 +9720,13 @@
         <f t="shared" si="0"/>
         <v>covers/light-perpetua.jpg</v>
       </c>
-      <c r="AY63" s="34" t="s">
+      <c r="AP63" s="39" t="s">
+        <v>1083</v>
+      </c>
+      <c r="AR63" t="s">
+        <v>1082</v>
+      </c>
+      <c r="AY63" s="33" t="s">
         <v>259</v>
       </c>
       <c r="BD63" t="s">
@@ -9558,7 +9745,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>260</v>
       </c>
@@ -9595,7 +9782,7 @@
       <c r="S64" s="3">
         <v>22</v>
       </c>
-      <c r="Y64" s="21">
+      <c r="Y64" s="20">
         <v>9781845951207</v>
       </c>
       <c r="Z64" s="4" t="s">
@@ -9612,7 +9799,7 @@
         <f t="shared" si="0"/>
         <v>covers/red-prince.jpg</v>
       </c>
-      <c r="AY64" s="36" t="s">
+      <c r="AY64" s="35" t="s">
         <v>264</v>
       </c>
       <c r="BD64" t="s">
@@ -9625,7 +9812,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="65" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>266</v>
       </c>
@@ -9661,7 +9848,7 @@
         <f t="shared" si="0"/>
         <v>covers/adam-mickiewicz.jpg</v>
       </c>
-      <c r="AY65" s="36" t="s">
+      <c r="AY65" s="35" t="s">
         <v>269</v>
       </c>
       <c r="BD65" t="s">
@@ -9674,7 +9861,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>272</v>
       </c>
@@ -9713,7 +9900,7 @@
         <f t="shared" si="0"/>
         <v>covers/forefathers-eve.jpg</v>
       </c>
-      <c r="AY66" s="36" t="s">
+      <c r="AY66" s="35" t="s">
         <v>273</v>
       </c>
       <c r="BD66" t="s">
@@ -9726,7 +9913,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>277</v>
       </c>
@@ -9765,7 +9952,7 @@
         <f t="shared" si="0"/>
         <v>covers/ballads-romances.jpg</v>
       </c>
-      <c r="AY67" s="34" t="s">
+      <c r="AY67" s="33" t="s">
         <v>278</v>
       </c>
       <c r="BD67" t="s">
@@ -9778,7 +9965,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>279</v>
       </c>
@@ -9807,7 +9994,7 @@
       <c r="S68" s="3">
         <v>16</v>
       </c>
-      <c r="Y68" s="21">
+      <c r="Y68" s="20">
         <v>9780374528300</v>
       </c>
       <c r="Z68" s="4"/>
@@ -9816,7 +10003,7 @@
         <f t="shared" si="0"/>
         <v>covers/native-realm.jpg</v>
       </c>
-      <c r="AY68" s="34" t="s">
+      <c r="AY68" s="33" t="s">
         <v>282</v>
       </c>
       <c r="BD68" t="s">
@@ -9829,7 +10016,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>283</v>
       </c>
@@ -9855,7 +10042,7 @@
       <c r="S69" s="3">
         <v>41</v>
       </c>
-      <c r="Y69" s="21">
+      <c r="Y69" s="20">
         <v>9780520044777</v>
       </c>
       <c r="Z69" s="4"/>
@@ -9864,7 +10051,7 @@
         <f t="shared" si="0"/>
         <v>covers/history-lit-milosz.jpg</v>
       </c>
-      <c r="AY69" s="34" t="s">
+      <c r="AY69" s="33" t="s">
         <v>289</v>
       </c>
       <c r="BD69" t="s">
@@ -9877,7 +10064,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>287</v>
       </c>
@@ -9903,7 +10090,7 @@
       <c r="S70" s="3">
         <v>22</v>
       </c>
-      <c r="Y70" s="21">
+      <c r="Y70" s="20">
         <v>9780520044760</v>
       </c>
       <c r="Z70" s="4"/>
@@ -9912,7 +10099,7 @@
         <f t="shared" si="0"/>
         <v>covers/postwar-polish-poetry.jpg</v>
       </c>
-      <c r="AY70" s="34" t="s">
+      <c r="AY70" s="33" t="s">
         <v>290</v>
       </c>
       <c r="BD70" t="s">
@@ -9925,7 +10112,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>291</v>
       </c>
@@ -9951,7 +10138,7 @@
       <c r="S71" s="3">
         <v>13</v>
       </c>
-      <c r="Y71" s="21">
+      <c r="Y71" s="20">
         <v>9780679728566</v>
       </c>
       <c r="Z71" s="4"/>
@@ -9960,7 +10147,7 @@
         <f t="shared" si="0"/>
         <v>covers/captive-mind.jpg</v>
       </c>
-      <c r="AY71" s="34" t="s">
+      <c r="AY71" s="33" t="s">
         <v>293</v>
       </c>
       <c r="BD71" t="s">
@@ -9973,7 +10160,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>295</v>
       </c>
@@ -10000,7 +10187,7 @@
       <c r="S72" s="3">
         <v>14</v>
       </c>
-      <c r="Y72" s="21">
+      <c r="Y72" s="20">
         <v>9781419679995</v>
       </c>
       <c r="Z72" s="4"/>
@@ -10009,7 +10196,7 @@
         <f t="shared" si="0"/>
         <v>covers/selected-masterpieces.jpg</v>
       </c>
-      <c r="AY72" s="34" t="s">
+      <c r="AY72" s="33" t="s">
         <v>297</v>
       </c>
       <c r="BD72" t="s">
@@ -10022,7 +10209,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>301</v>
       </c>
@@ -10048,7 +10235,7 @@
       <c r="S73" s="3">
         <v>30</v>
       </c>
-      <c r="Y73" s="21">
+      <c r="Y73" s="20">
         <v>9781734860610</v>
       </c>
       <c r="Z73" s="4" t="s">
@@ -10068,7 +10255,7 @@
         <f>"covers/" &amp; A73 &amp; ".jpg"</f>
         <v>covers/hyenas-lotuses.jpg</v>
       </c>
-      <c r="AY73" s="34" t="s">
+      <c r="AY73" s="33" t="s">
         <v>304</v>
       </c>
       <c r="BD73" t="s">
@@ -10081,7 +10268,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>308</v>
       </c>
@@ -10107,7 +10294,7 @@
       <c r="S74" s="3">
         <v>19</v>
       </c>
-      <c r="Y74" s="21">
+      <c r="Y74" s="20">
         <v>9781250218018</v>
       </c>
       <c r="Z74" s="4" t="s">
@@ -10126,10 +10313,10 @@
         <f>"covers/" &amp; A74 &amp; ".jpg"</f>
         <v>covers/widow-queen.jpg</v>
       </c>
-      <c r="AY74" s="34" t="s">
+      <c r="AY74" s="33" t="s">
         <v>305</v>
       </c>
-      <c r="AZ74" s="25" t="s">
+      <c r="AZ74" s="24" t="s">
         <v>310</v>
       </c>
       <c r="BA74" t="s">
@@ -10157,7 +10344,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>315</v>
       </c>
@@ -10197,7 +10384,7 @@
       <c r="S75" s="3">
         <v>20.99</v>
       </c>
-      <c r="Y75" s="21">
+      <c r="Y75" s="20">
         <v>9781250775764</v>
       </c>
       <c r="Z75" s="4"/>
@@ -10206,10 +10393,10 @@
         <f>"covers/" &amp; A75 &amp; ".jpg"</f>
         <v>covers/last-crown.jpg</v>
       </c>
-      <c r="AY75" s="34" t="s">
+      <c r="AY75" s="33" t="s">
         <v>317</v>
       </c>
-      <c r="AZ75" s="25" t="s">
+      <c r="AZ75" s="24" t="s">
         <v>310</v>
       </c>
       <c r="BA75" t="s">
@@ -10237,7 +10424,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>265</v>
       </c>
@@ -10266,7 +10453,7 @@
       <c r="S76" s="3">
         <v>24.99</v>
       </c>
-      <c r="Y76" s="21">
+      <c r="Y76" s="20">
         <v>9781589881846</v>
       </c>
       <c r="Z76" s="4" t="s">
@@ -10285,7 +10472,7 @@
         <f t="shared" ref="AI76" si="7">"covers/" &amp; A76 &amp; ".jpg"</f>
         <v>covers/the-homeless.jpg</v>
       </c>
-      <c r="AY76" s="34" t="s">
+      <c r="AY76" s="33" t="s">
         <v>233</v>
       </c>
       <c r="BD76" t="s">
@@ -10298,7 +10485,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="77" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>337</v>
       </c>
@@ -10327,7 +10514,7 @@
       <c r="S77" s="3">
         <v>17</v>
       </c>
-      <c r="Y77" s="21">
+      <c r="Y77" s="20">
         <v>9780300181678</v>
       </c>
       <c r="Z77" s="4"/>
@@ -10336,10 +10523,10 @@
         <f t="shared" ref="AI77:AI104" si="8">"covers/" &amp; A77 &amp; ".jpg"</f>
         <v>covers/ferdydurke.jpg</v>
       </c>
-      <c r="AY77" s="34" t="s">
+      <c r="AY77" s="33" t="s">
         <v>340</v>
       </c>
-      <c r="AZ77" s="25" t="s">
+      <c r="AZ77" s="24" t="s">
         <v>342</v>
       </c>
       <c r="BD77" t="s">
@@ -10352,7 +10539,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="78" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>345</v>
       </c>
@@ -10381,7 +10568,7 @@
       <c r="S78" s="3">
         <v>17</v>
       </c>
-      <c r="Y78" s="21">
+      <c r="Y78" s="20">
         <v>9780802162526</v>
       </c>
       <c r="Z78" s="4"/>
@@ -10390,10 +10577,10 @@
         <f t="shared" si="8"/>
         <v>covers/the-possessed.jpg</v>
       </c>
-      <c r="AY78" s="34" t="s">
+      <c r="AY78" s="33" t="s">
         <v>343</v>
       </c>
-      <c r="AZ78" s="25" t="s">
+      <c r="AZ78" s="24" t="s">
         <v>347</v>
       </c>
       <c r="BD78" t="s">
@@ -10406,7 +10593,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="79" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>349</v>
       </c>
@@ -10435,7 +10622,7 @@
       <c r="S79" s="3">
         <v>18</v>
       </c>
-      <c r="Y79" s="21">
+      <c r="Y79" s="20">
         <v>9780525534204</v>
       </c>
       <c r="Z79" s="4"/>
@@ -10444,10 +10631,10 @@
         <f t="shared" si="8"/>
         <v>covers/flights.jpg</v>
       </c>
-      <c r="AY79" s="34" t="s">
+      <c r="AY79" s="33" t="s">
         <v>352</v>
       </c>
-      <c r="AZ79" s="25" t="s">
+      <c r="AZ79" s="24" t="s">
         <v>353</v>
       </c>
       <c r="BD79" t="s">
@@ -10460,7 +10647,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="80" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>400</v>
       </c>
@@ -10489,7 +10676,7 @@
       <c r="S80" s="3">
         <v>15</v>
       </c>
-      <c r="Y80" s="21">
+      <c r="Y80" s="20">
         <v>9781628971637</v>
       </c>
       <c r="Z80" s="4"/>
@@ -10498,7 +10685,7 @@
         <f t="shared" si="8"/>
         <v>covers/gestures.jpg</v>
       </c>
-      <c r="AY80" s="34" t="s">
+      <c r="AY80" s="33" t="s">
         <v>404</v>
       </c>
       <c r="BD80" t="s">
@@ -10511,7 +10698,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>410</v>
       </c>
@@ -10540,7 +10727,7 @@
       <c r="S81" s="3">
         <v>15</v>
       </c>
-      <c r="Y81" s="21">
+      <c r="Y81" s="20">
         <v>9781945492235</v>
       </c>
       <c r="Z81" s="4"/>
@@ -10549,10 +10736,10 @@
         <f t="shared" si="8"/>
         <v>covers/accommodations.jpg</v>
       </c>
-      <c r="AY81" s="34" t="s">
+      <c r="AY81" s="33" t="s">
         <v>407</v>
       </c>
-      <c r="AZ81" s="25" t="s">
+      <c r="AZ81" s="24" t="s">
         <v>408</v>
       </c>
       <c r="BD81" t="s">
@@ -10565,7 +10752,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>413</v>
       </c>
@@ -10594,7 +10781,7 @@
       <c r="S82" s="3">
         <v>20</v>
       </c>
-      <c r="Y82" s="21">
+      <c r="Y82" s="20">
         <v>9781945492044</v>
       </c>
       <c r="Z82" s="4"/>
@@ -10603,10 +10790,10 @@
         <f t="shared" si="8"/>
         <v>covers/swallowing-mercury.jpg</v>
       </c>
-      <c r="AY82" s="34" t="s">
+      <c r="AY82" s="33" t="s">
         <v>416</v>
       </c>
-      <c r="AZ82" s="25" t="s">
+      <c r="AZ82" s="24" t="s">
         <v>415</v>
       </c>
       <c r="BD82" t="s">
@@ -10619,7 +10806,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="83" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>418</v>
       </c>
@@ -10645,7 +10832,7 @@
       <c r="R83" s="7" t="s">
         <v>421</v>
       </c>
-      <c r="Y83" s="21">
+      <c r="Y83" s="20">
         <v>9781589880900</v>
       </c>
       <c r="Z83" s="4"/>
@@ -10654,7 +10841,7 @@
         <f t="shared" si="8"/>
         <v>covers/stone-tablets.jpg</v>
       </c>
-      <c r="AY83" s="34" t="s">
+      <c r="AY83" s="33" t="s">
         <v>420</v>
       </c>
       <c r="BD83" t="s">
@@ -10667,7 +10854,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="84" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>422</v>
       </c>
@@ -10696,7 +10883,7 @@
       <c r="S84" s="3">
         <v>17</v>
       </c>
-      <c r="Y84" s="21">
+      <c r="Y84" s="20">
         <v>9780802160430</v>
       </c>
       <c r="Z84" s="4" t="s">
@@ -10715,10 +10902,10 @@
         <f t="shared" si="8"/>
         <v>covers/beautiful-mrs-seidenman.jpg</v>
       </c>
-      <c r="AY84" s="34" t="s">
+      <c r="AY84" s="33" t="s">
         <v>423</v>
       </c>
-      <c r="AZ84" s="25" t="s">
+      <c r="AZ84" s="24" t="s">
         <v>424</v>
       </c>
       <c r="BD84" t="s">
@@ -10731,7 +10918,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>429</v>
       </c>
@@ -10760,7 +10947,7 @@
       <c r="S85" s="3">
         <v>15</v>
       </c>
-      <c r="Y85" s="21">
+      <c r="Y85" s="20">
         <v>9781782695141</v>
       </c>
       <c r="Z85" s="4"/>
@@ -10769,7 +10956,7 @@
         <f t="shared" si="8"/>
         <v>covers/nosegood-investigates.jpg</v>
       </c>
-      <c r="AY85" s="37" t="s">
+      <c r="AY85" s="36" t="s">
         <v>428</v>
       </c>
       <c r="BD85" t="s">
@@ -10782,7 +10969,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="86" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>435</v>
       </c>
@@ -10811,7 +10998,7 @@
       <c r="S86" s="3">
         <v>19</v>
       </c>
-      <c r="Y86" s="21">
+      <c r="Y86" s="20">
         <v>9780143129752</v>
       </c>
       <c r="Z86" s="4"/>
@@ -10820,10 +11007,10 @@
         <f t="shared" si="8"/>
         <v>covers/feed-dictator.jpg</v>
       </c>
-      <c r="AY86" s="34" t="s">
+      <c r="AY86" s="33" t="s">
         <v>437</v>
       </c>
-      <c r="AZ86" s="25" t="s">
+      <c r="AZ86" s="24" t="s">
         <v>436</v>
       </c>
       <c r="BD86" t="s">
@@ -10836,7 +11023,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>440</v>
       </c>
@@ -10865,7 +11052,7 @@
       <c r="S87" s="3">
         <v>20</v>
       </c>
-      <c r="Y87" s="21">
+      <c r="Y87" s="20">
         <v>9781805330011</v>
       </c>
       <c r="Z87" s="4"/>
@@ -10874,10 +11061,10 @@
         <f t="shared" si="8"/>
         <v>covers/city-lions.jpg</v>
       </c>
-      <c r="AY87" s="34" t="s">
+      <c r="AY87" s="33" t="s">
         <v>441</v>
       </c>
-      <c r="AZ87" s="25" t="s">
+      <c r="AZ87" s="24" t="s">
         <v>442</v>
       </c>
       <c r="BD87" t="s">
@@ -10890,7 +11077,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="1:62" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:62" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>445</v>
       </c>
@@ -10919,7 +11106,7 @@
       <c r="S88" s="3">
         <v>16</v>
       </c>
-      <c r="Y88" s="21">
+      <c r="Y88" s="20">
         <v>9781948830508</v>
       </c>
       <c r="Z88" s="4"/>
@@ -10928,10 +11115,10 @@
         <f t="shared" si="8"/>
         <v>covers/roosters-dogs.jpg</v>
       </c>
-      <c r="AY88" s="34" t="s">
+      <c r="AY88" s="33" t="s">
         <v>449</v>
       </c>
-      <c r="AZ88" s="25" t="s">
+      <c r="AZ88" s="24" t="s">
         <v>450</v>
       </c>
       <c r="BD88" t="s">
@@ -10944,7 +11131,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="89" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>451</v>
       </c>
@@ -10973,7 +11160,7 @@
       <c r="S89" s="3">
         <v>16</v>
       </c>
-      <c r="Y89" s="21">
+      <c r="Y89" s="20">
         <v>9780857057143</v>
       </c>
       <c r="Z89" s="4"/>
@@ -10982,10 +11169,10 @@
         <f t="shared" si="8"/>
         <v>covers/stained-glass.jpg</v>
       </c>
-      <c r="AY89" s="34" t="s">
+      <c r="AY89" s="33" t="s">
         <v>452</v>
       </c>
-      <c r="AZ89" s="25" t="s">
+      <c r="AZ89" s="24" t="s">
         <v>453</v>
       </c>
       <c r="BD89" t="s">
@@ -10998,14 +11185,17 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>458</v>
       </c>
       <c r="B90" t="s">
         <v>74</v>
       </c>
-      <c r="D90" s="20" t="s">
+      <c r="C90">
+        <v>875</v>
+      </c>
+      <c r="D90" s="19" t="s">
         <v>457</v>
       </c>
       <c r="E90" t="s">
@@ -11024,7 +11214,7 @@
       <c r="S90" s="3">
         <v>50</v>
       </c>
-      <c r="Y90" s="21">
+      <c r="Y90" s="20">
         <v>9781781680810</v>
       </c>
       <c r="Z90" s="4" t="s">
@@ -11043,10 +11233,10 @@
         <f t="shared" si="8"/>
         <v>covers/ryszard-k-a-life.jpg</v>
       </c>
-      <c r="AY90" s="34" t="s">
+      <c r="AY90" s="33" t="s">
         <v>461</v>
       </c>
-      <c r="AZ90" s="25" t="s">
+      <c r="AZ90" s="24" t="s">
         <v>462</v>
       </c>
       <c r="BD90" t="s">
@@ -11058,8 +11248,14 @@
       <c r="BG90" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="91" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BI90" t="s">
+        <v>1087</v>
+      </c>
+      <c r="BJ90">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>463</v>
       </c>
@@ -11088,7 +11284,7 @@
       <c r="S91" s="3">
         <v>17</v>
       </c>
-      <c r="Y91" s="21">
+      <c r="Y91" s="20">
         <v>9780192855565</v>
       </c>
       <c r="Z91" s="4" t="s">
@@ -11108,10 +11304,10 @@
         <f t="shared" si="8"/>
         <v>covers/warsaw-tales.jpg</v>
       </c>
-      <c r="AY91" s="34" t="s">
+      <c r="AY91" s="33" t="s">
         <v>465</v>
       </c>
-      <c r="AZ91" s="25" t="s">
+      <c r="AZ91" s="24" t="s">
         <v>466</v>
       </c>
       <c r="BD91" t="s">
@@ -11124,7 +11320,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="92" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>473</v>
       </c>
@@ -11153,7 +11349,7 @@
       <c r="S92" s="3">
         <v>16</v>
       </c>
-      <c r="Y92" s="21">
+      <c r="Y92" s="20">
         <v>9780358161462</v>
       </c>
       <c r="Z92" s="4"/>
@@ -11162,10 +11358,10 @@
         <f t="shared" si="8"/>
         <v>covers/mohr-missing.jpg</v>
       </c>
-      <c r="AY92" s="34" t="s">
+      <c r="AY92" s="33" t="s">
         <v>477</v>
       </c>
-      <c r="AZ92" s="25" t="s">
+      <c r="AZ92" s="24" t="s">
         <v>478</v>
       </c>
       <c r="BD92" t="s">
@@ -11184,7 +11380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>480</v>
       </c>
@@ -11213,7 +11409,7 @@
       <c r="S93" s="3">
         <v>20</v>
       </c>
-      <c r="Y93" s="21">
+      <c r="Y93" s="20">
         <v>9780143137184</v>
       </c>
       <c r="Z93" s="4"/>
@@ -11222,10 +11418,10 @@
         <f t="shared" si="8"/>
         <v>covers/cooking-kremlin.jpg</v>
       </c>
-      <c r="AY93" s="34" t="s">
+      <c r="AY93" s="33" t="s">
         <v>483</v>
       </c>
-      <c r="AZ93" s="25" t="s">
+      <c r="AZ93" s="24" t="s">
         <v>482</v>
       </c>
       <c r="BD93" t="s">
@@ -11238,7 +11434,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="94" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>484</v>
       </c>
@@ -11267,7 +11463,7 @@
       <c r="S94" s="3">
         <v>24</v>
       </c>
-      <c r="Y94" s="21">
+      <c r="Y94" s="20">
         <v>9781565124424</v>
       </c>
       <c r="Z94" s="4"/>
@@ -11276,7 +11472,7 @@
         <f t="shared" si="8"/>
         <v>covers/matt-the-first.jpg</v>
       </c>
-      <c r="AY94" s="34" t="s">
+      <c r="AY94" s="33" t="s">
         <v>487</v>
       </c>
       <c r="BD94" t="s">
@@ -11289,7 +11485,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="95" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>491</v>
       </c>
@@ -11326,10 +11522,10 @@
         <f t="shared" si="8"/>
         <v>covers/kaytek-wizard.jpg</v>
       </c>
-      <c r="AY95" s="34" t="s">
+      <c r="AY95" s="33" t="s">
         <v>492</v>
       </c>
-      <c r="AZ95" s="25" t="s">
+      <c r="AZ95" s="24" t="s">
         <v>493</v>
       </c>
       <c r="BD95" t="s">
@@ -11342,7 +11538,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="96" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>501</v>
       </c>
@@ -11371,7 +11567,7 @@
       <c r="S96" s="3">
         <v>17.95</v>
       </c>
-      <c r="Y96" s="21">
+      <c r="Y96" s="20">
         <v>9781590176658</v>
       </c>
       <c r="Z96" s="4"/>
@@ -11380,10 +11576,10 @@
         <f t="shared" si="8"/>
         <v>covers/miron-memoir.jpg</v>
       </c>
-      <c r="AY96" s="34" t="s">
+      <c r="AY96" s="33" t="s">
         <v>499</v>
       </c>
-      <c r="AZ96" s="25" t="s">
+      <c r="AZ96" s="24" t="s">
         <v>498</v>
       </c>
       <c r="BD96" t="s">
@@ -11396,7 +11592,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="97" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>503</v>
       </c>
@@ -11422,7 +11618,7 @@
       <c r="R97" s="7" t="s">
         <v>497</v>
       </c>
-      <c r="Y97" s="21">
+      <c r="Y97" s="20">
         <v>9781681372563</v>
       </c>
       <c r="Z97" s="4"/>
@@ -11431,10 +11627,10 @@
         <f t="shared" si="8"/>
         <v>covers/inhuman-land.jpg</v>
       </c>
-      <c r="AY97" s="34" t="s">
+      <c r="AY97" s="33" t="s">
         <v>506</v>
       </c>
-      <c r="AZ97" s="25" t="s">
+      <c r="AZ97" s="24" t="s">
         <v>505</v>
       </c>
       <c r="BD97" t="s">
@@ -11447,7 +11643,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="98" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>468</v>
       </c>
@@ -11486,10 +11682,10 @@
         <f t="shared" si="8"/>
         <v>covers/mud-sweeter.jpg</v>
       </c>
-      <c r="AY98" s="35" t="s">
+      <c r="AY98" s="34" t="s">
         <v>472</v>
       </c>
-      <c r="AZ98" s="25" t="s">
+      <c r="AZ98" s="24" t="s">
         <v>471</v>
       </c>
       <c r="BD98" t="s">
@@ -11502,7 +11698,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="99" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>508</v>
       </c>
@@ -11541,10 +11737,10 @@
         <f t="shared" si="8"/>
         <v>covers/house-of-day.jpg</v>
       </c>
-      <c r="AY99" s="34" t="s">
+      <c r="AY99" s="33" t="s">
         <v>510</v>
       </c>
-      <c r="AZ99" s="25" t="s">
+      <c r="AZ99" s="24" t="s">
         <v>509</v>
       </c>
       <c r="BD99" t="s">
@@ -11557,7 +11753,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="100" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>511</v>
       </c>
@@ -11587,7 +11783,7 @@
       <c r="S100" s="3">
         <v>27.95</v>
       </c>
-      <c r="Y100" s="21">
+      <c r="Y100" s="20">
         <v>9781953943705</v>
       </c>
       <c r="Z100" s="4"/>
@@ -11596,10 +11792,10 @@
         <f t="shared" si="8"/>
         <v>covers/garden-memory.jpg</v>
       </c>
-      <c r="AY100" s="34" t="s">
+      <c r="AY100" s="33" t="s">
         <v>514</v>
       </c>
-      <c r="AZ100" s="25" t="s">
+      <c r="AZ100" s="24" t="s">
         <v>515</v>
       </c>
       <c r="BD100" t="s">
@@ -11612,7 +11808,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="101" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>518</v>
       </c>
@@ -11641,7 +11837,7 @@
       <c r="S101" s="3">
         <v>16</v>
       </c>
-      <c r="Y101" s="21">
+      <c r="Y101" s="20">
         <v>9781939931115</v>
       </c>
       <c r="Z101" s="4"/>
@@ -11653,10 +11849,10 @@
       <c r="AJ101">
         <v>2014</v>
       </c>
-      <c r="AY101" s="34" t="s">
+      <c r="AY101" s="33" t="s">
         <v>522</v>
       </c>
-      <c r="AZ101" s="25" t="s">
+      <c r="AZ101" s="24" t="s">
         <v>523</v>
       </c>
       <c r="BD101" t="s">
@@ -11669,7 +11865,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="102" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>524</v>
       </c>
@@ -11698,7 +11894,7 @@
       <c r="S102" s="3">
         <v>16</v>
       </c>
-      <c r="Y102" s="21">
+      <c r="Y102" s="20">
         <v>9781939931122</v>
       </c>
       <c r="Z102" s="4" t="s">
@@ -11721,10 +11917,10 @@
       <c r="AJ102">
         <v>2014</v>
       </c>
-      <c r="AY102" s="34" t="s">
+      <c r="AY102" s="33" t="s">
         <v>527</v>
       </c>
-      <c r="AZ102" s="25" t="s">
+      <c r="AZ102" s="24" t="s">
         <v>526</v>
       </c>
       <c r="BD102" t="s">
@@ -11737,7 +11933,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="103" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>533</v>
       </c>
@@ -11766,7 +11962,7 @@
       <c r="S103" s="3">
         <v>35</v>
       </c>
-      <c r="Y103" s="23">
+      <c r="Y103" s="22">
         <v>9780875806976</v>
       </c>
       <c r="Z103" s="4" t="s">
@@ -11786,10 +11982,10 @@
         <f t="shared" si="8"/>
         <v>covers/beautiful-twentysomethings.jpg</v>
       </c>
-      <c r="AY103" s="34" t="s">
+      <c r="AY103" s="33" t="s">
         <v>532</v>
       </c>
-      <c r="AZ103" s="25" t="s">
+      <c r="AZ103" s="24" t="s">
         <v>531</v>
       </c>
       <c r="BD103" t="s">
@@ -11802,7 +11998,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="104" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>534</v>
       </c>
@@ -11848,10 +12044,10 @@
         <f t="shared" si="8"/>
         <v>covers/laras-wars.jpg</v>
       </c>
-      <c r="AY104" s="34" t="s">
+      <c r="AY104" s="33" t="s">
         <v>539</v>
       </c>
-      <c r="AZ104" s="25" t="s">
+      <c r="AZ104" s="24" t="s">
         <v>538</v>
       </c>
       <c r="BD104" t="s">
@@ -11864,7 +12060,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="105" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>544</v>
       </c>
@@ -11893,7 +12089,7 @@
       <c r="S105" s="3">
         <v>18</v>
       </c>
-      <c r="Y105" s="21">
+      <c r="Y105" s="20">
         <v>9781644213759</v>
       </c>
       <c r="Z105" s="4" t="s">
@@ -11913,10 +12109,10 @@
         <f t="shared" ref="AI105:AI133" si="11">"covers/" &amp; A105 &amp; ".jpg"</f>
         <v>covers/little-beauty.jpg</v>
       </c>
-      <c r="AY105" s="34" t="s">
+      <c r="AY105" s="33" t="s">
         <v>543</v>
       </c>
-      <c r="AZ105" s="25" t="s">
+      <c r="AZ105" s="24" t="s">
         <v>542</v>
       </c>
       <c r="BD105" t="s">
@@ -11929,7 +12125,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="106" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>549</v>
       </c>
@@ -11958,7 +12154,7 @@
       <c r="S106" s="3">
         <v>17</v>
       </c>
-      <c r="Y106" s="21">
+      <c r="Y106" s="20">
         <v>9781681372587</v>
       </c>
       <c r="Z106" s="4" t="s">
@@ -11978,10 +12174,10 @@
         <f t="shared" si="11"/>
         <v>covers/lectures-proust.jpg</v>
       </c>
-      <c r="AY106" s="34" t="s">
+      <c r="AY106" s="33" t="s">
         <v>547</v>
       </c>
-      <c r="AZ106" s="25" t="s">
+      <c r="AZ106" s="24" t="s">
         <v>548</v>
       </c>
       <c r="BD106" t="s">
@@ -11994,7 +12190,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="107" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>552</v>
       </c>
@@ -12023,7 +12219,7 @@
       <c r="S107" s="3">
         <v>18</v>
       </c>
-      <c r="Y107" s="21">
+      <c r="Y107" s="20">
         <v>9781681374864</v>
       </c>
       <c r="Z107" s="4" t="s">
@@ -12043,10 +12239,10 @@
         <f t="shared" si="11"/>
         <v>covers/Starobielsk-essays.jpg</v>
       </c>
-      <c r="AY107" s="34" t="s">
+      <c r="AY107" s="33" t="s">
         <v>554</v>
       </c>
-      <c r="AZ107" s="25" t="s">
+      <c r="AZ107" s="24" t="s">
         <v>553</v>
       </c>
       <c r="BD107" t="s">
@@ -12059,7 +12255,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="108" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>558</v>
       </c>
@@ -12100,7 +12296,7 @@
       <c r="S108" s="3">
         <v>37</v>
       </c>
-      <c r="Y108" s="21">
+      <c r="Y108" s="20">
         <v>9780374536374</v>
       </c>
       <c r="Z108" s="4" t="s">
@@ -12120,10 +12316,10 @@
         <f t="shared" si="11"/>
         <v>covers/jedwabne-crime.jpg</v>
       </c>
-      <c r="AY108" s="34" t="s">
+      <c r="AY108" s="33" t="s">
         <v>555</v>
       </c>
-      <c r="AZ108" s="25" t="s">
+      <c r="AZ108" s="24" t="s">
         <v>556</v>
       </c>
       <c r="BD108" t="s">
@@ -12136,7 +12332,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="109" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>566</v>
       </c>
@@ -12165,7 +12361,7 @@
       <c r="S109" s="3">
         <v>15</v>
       </c>
-      <c r="Y109" s="21">
+      <c r="Y109" s="20">
         <v>9781681377308</v>
       </c>
       <c r="Z109" s="4" t="s">
@@ -12185,10 +12381,10 @@
         <f t="shared" si="11"/>
         <v>covers/ginczanka-firebird.jpg</v>
       </c>
-      <c r="AY109" s="34" t="s">
+      <c r="AY109" s="33" t="s">
         <v>565</v>
       </c>
-      <c r="AZ109" s="25" t="s">
+      <c r="AZ109" s="24" t="s">
         <v>564</v>
       </c>
       <c r="BD109" t="s">
@@ -12201,7 +12397,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="110" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>569</v>
       </c>
@@ -12230,7 +12426,7 @@
       <c r="S110" s="3">
         <v>15</v>
       </c>
-      <c r="Y110" s="24">
+      <c r="Y110" s="23">
         <v>9781681371603</v>
       </c>
       <c r="Z110" s="4" t="s">
@@ -12250,10 +12446,10 @@
         <f t="shared" si="11"/>
         <v>covers/life-grows.jpg</v>
       </c>
-      <c r="AY110" s="34" t="s">
+      <c r="AY110" s="33" t="s">
         <v>570</v>
       </c>
-      <c r="AZ110" s="25" t="s">
+      <c r="AZ110" s="24" t="s">
         <v>571</v>
       </c>
       <c r="BD110" t="s">
@@ -12266,7 +12462,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="111" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>572</v>
       </c>
@@ -12295,7 +12491,7 @@
       <c r="S111" s="3">
         <v>17</v>
       </c>
-      <c r="Y111" s="21">
+      <c r="Y111" s="20">
         <v>9781068740404</v>
       </c>
       <c r="Z111" s="4" t="s">
@@ -12314,7 +12510,7 @@
         <f t="shared" si="11"/>
         <v>covers/voracious.jpg</v>
       </c>
-      <c r="AY111" s="34" t="s">
+      <c r="AY111" s="33" t="s">
         <v>573</v>
       </c>
       <c r="BD111" t="s">
@@ -12327,7 +12523,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="112" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>577</v>
       </c>
@@ -12356,7 +12552,7 @@
       <c r="S112" s="3">
         <v>18</v>
       </c>
-      <c r="Y112" s="21">
+      <c r="Y112" s="20">
         <v>9781786074980</v>
       </c>
       <c r="Z112" s="4" t="s">
@@ -12376,10 +12572,10 @@
         <f t="shared" si="11"/>
         <v>covers/lala.jpg</v>
       </c>
-      <c r="AY112" s="34" t="s">
+      <c r="AY112" s="33" t="s">
         <v>582</v>
       </c>
-      <c r="AZ112" s="25" t="s">
+      <c r="AZ112" s="24" t="s">
         <v>580</v>
       </c>
       <c r="BD112" t="s">
@@ -12392,7 +12588,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="113" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>583</v>
       </c>
@@ -12421,7 +12617,7 @@
       <c r="S113" s="3">
         <v>24</v>
       </c>
-      <c r="Y113" s="21">
+      <c r="Y113" s="20">
         <v>9780143129745</v>
       </c>
       <c r="Z113" s="4" t="s">
@@ -12441,10 +12637,10 @@
         <f t="shared" si="11"/>
         <v>covers/dancing-bears.jpg</v>
       </c>
-      <c r="AY113" s="34" t="s">
+      <c r="AY113" s="33" t="s">
         <v>587</v>
       </c>
-      <c r="AZ113" s="25" t="s">
+      <c r="AZ113" s="24" t="s">
         <v>586</v>
       </c>
       <c r="BD113" t="s">
@@ -12457,7 +12653,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="114" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>590</v>
       </c>
@@ -12486,7 +12682,7 @@
       <c r="S114" s="3">
         <v>15</v>
       </c>
-      <c r="Y114" s="21">
+      <c r="Y114" s="20">
         <v>9781503935860</v>
       </c>
       <c r="Z114" s="4" t="s">
@@ -12506,10 +12702,10 @@
         <f t="shared" si="11"/>
         <v>covers/rage.jpg</v>
       </c>
-      <c r="AY114" s="34" t="s">
+      <c r="AY114" s="33" t="s">
         <v>592</v>
       </c>
-      <c r="AZ114" s="25" t="s">
+      <c r="AZ114" s="24" t="s">
         <v>593</v>
       </c>
       <c r="BD114" t="s">
@@ -12528,7 +12724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>594</v>
       </c>
@@ -12554,7 +12750,7 @@
       <c r="R115" s="7" t="s">
         <v>596</v>
       </c>
-      <c r="Y115" s="21">
+      <c r="Y115" s="20">
         <v>9781908524027</v>
       </c>
       <c r="Z115" s="4"/>
@@ -12563,10 +12759,10 @@
         <f t="shared" si="11"/>
         <v>covers/grain-truth.jpg</v>
       </c>
-      <c r="AY115" s="34" t="s">
+      <c r="AY115" s="33" t="s">
         <v>598</v>
       </c>
-      <c r="AZ115" s="25" t="s">
+      <c r="AZ115" s="24" t="s">
         <v>599</v>
       </c>
       <c r="BD115" t="s">
@@ -12585,7 +12781,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>601</v>
       </c>
@@ -12626,7 +12822,7 @@
       <c r="S116" s="3">
         <v>19</v>
       </c>
-      <c r="Y116" s="21">
+      <c r="Y116" s="20">
         <v>9780525541349</v>
       </c>
       <c r="Z116" s="4" t="s">
@@ -12645,10 +12841,10 @@
         <f t="shared" si="11"/>
         <v>covers/over-the-bones.jpg</v>
       </c>
-      <c r="AY116" s="34" t="s">
+      <c r="AY116" s="33" t="s">
         <v>603</v>
       </c>
-      <c r="AZ116" s="25" t="s">
+      <c r="AZ116" s="24" t="s">
         <v>643</v>
       </c>
       <c r="BD116" t="s">
@@ -12661,7 +12857,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="117" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>604</v>
       </c>
@@ -12702,7 +12898,7 @@
       <c r="S117" s="3">
         <v>12.5</v>
       </c>
-      <c r="Y117" s="21">
+      <c r="Y117" s="20">
         <v>9780593087503</v>
       </c>
       <c r="Z117" s="4" t="s">
@@ -12722,10 +12918,10 @@
         <f t="shared" si="11"/>
         <v>covers/jacobs-books.jpg</v>
       </c>
-      <c r="AY117" s="34" t="s">
+      <c r="AY117" s="33" t="s">
         <v>606</v>
       </c>
-      <c r="AZ117" s="25" t="s">
+      <c r="AZ117" s="24" t="s">
         <v>607</v>
       </c>
       <c r="BD117" t="s">
@@ -12738,7 +12934,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="118" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>608</v>
       </c>
@@ -12779,7 +12975,7 @@
       <c r="S118" s="3">
         <v>20</v>
       </c>
-      <c r="Y118" s="21">
+      <c r="Y118" s="20">
         <v>9780593712955</v>
       </c>
       <c r="Z118" s="4" t="s">
@@ -12799,10 +12995,10 @@
         <f t="shared" si="11"/>
         <v>covers/empusium.jpg</v>
       </c>
-      <c r="AY118" s="34" t="s">
+      <c r="AY118" s="33" t="s">
         <v>610</v>
       </c>
-      <c r="AZ118" s="25" t="s">
+      <c r="AZ118" s="24" t="s">
         <v>611</v>
       </c>
       <c r="BD118" t="s">
@@ -12815,7 +13011,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="119" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>613</v>
       </c>
@@ -12864,7 +13060,7 @@
         <f t="shared" si="11"/>
         <v>covers/mr-distinctive.jpg</v>
       </c>
-      <c r="AY119" s="34" t="s">
+      <c r="AY119" s="33" t="s">
         <v>614</v>
       </c>
       <c r="BD119" t="s">
@@ -12877,7 +13073,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="120" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>615</v>
       </c>
@@ -12926,10 +13122,10 @@
         <f t="shared" si="11"/>
         <v>covers/lost-soul.jpg</v>
       </c>
-      <c r="AY120" s="34" t="s">
+      <c r="AY120" s="33" t="s">
         <v>617</v>
       </c>
-      <c r="AZ120" s="25" t="s">
+      <c r="AZ120" s="24" t="s">
         <v>616</v>
       </c>
       <c r="BD120" t="s">
@@ -12942,7 +13138,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="121" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>621</v>
       </c>
@@ -12968,7 +13164,7 @@
       <c r="S121" s="3">
         <v>19.5</v>
       </c>
-      <c r="Y121" s="21">
+      <c r="Y121" s="20">
         <v>9781786079299</v>
       </c>
       <c r="Z121" s="4" t="s">
@@ -12988,7 +13184,7 @@
         <f t="shared" si="11"/>
         <v>covers/torn-curtain.jpg</v>
       </c>
-      <c r="AY121" s="34" t="s">
+      <c r="AY121" s="33" t="s">
         <v>623</v>
       </c>
       <c r="BD121" t="s">
@@ -13007,7 +13203,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>626</v>
       </c>
@@ -13037,7 +13233,7 @@
       <c r="S122" s="3">
         <v>24</v>
       </c>
-      <c r="Y122" s="21">
+      <c r="Y122" s="20">
         <v>9780988859296</v>
       </c>
       <c r="Z122" s="4" t="s">
@@ -13057,7 +13253,7 @@
         <f t="shared" si="11"/>
         <v>covers/on-niemen.jpg</v>
       </c>
-      <c r="AY122" s="34" t="s">
+      <c r="AY122" s="33" t="s">
         <v>631</v>
       </c>
       <c r="BD122" t="s">
@@ -13070,7 +13266,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="123" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>633</v>
       </c>
@@ -13121,10 +13317,10 @@
         <f t="shared" si="11"/>
         <v>covers/marta.jpg</v>
       </c>
-      <c r="AY123" s="34" t="s">
+      <c r="AY123" s="33" t="s">
         <v>636</v>
       </c>
-      <c r="AZ123" s="25" t="s">
+      <c r="AZ123" s="24" t="s">
         <v>632</v>
       </c>
       <c r="BD123" t="s">
@@ -13137,7 +13333,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="124" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>667</v>
       </c>
@@ -13184,13 +13380,13 @@
       <c r="AS124" t="s">
         <v>712</v>
       </c>
-      <c r="AT124" s="25" t="s">
+      <c r="AT124" s="24" t="s">
         <v>715</v>
       </c>
       <c r="AU124" t="s">
         <v>713</v>
       </c>
-      <c r="AY124" s="34" t="s">
+      <c r="AY124" s="33" t="s">
         <v>665</v>
       </c>
       <c r="BD124" t="s">
@@ -13203,7 +13399,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="125" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>672</v>
       </c>
@@ -13232,7 +13428,7 @@
       <c r="S125" s="3">
         <v>13.1</v>
       </c>
-      <c r="Y125" s="21">
+      <c r="Y125" s="20">
         <v>9781909232044</v>
       </c>
       <c r="Z125" s="4" t="s">
@@ -13251,10 +13447,10 @@
         <f t="shared" si="11"/>
         <v>covers/dark-domain.jpg</v>
       </c>
-      <c r="AY125" s="37" t="s">
+      <c r="AY125" s="36" t="s">
         <v>673</v>
       </c>
-      <c r="AZ125" s="39" t="s">
+      <c r="AZ125" s="38" t="s">
         <v>674</v>
       </c>
       <c r="BD125" t="s">
@@ -13267,7 +13463,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="126" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>680</v>
       </c>
@@ -13302,7 +13498,7 @@
         <f t="shared" si="11"/>
         <v>covers/mannequins-ball.jpg</v>
       </c>
-      <c r="AY126" s="25" t="s">
+      <c r="AY126" s="24" t="s">
         <v>681</v>
       </c>
       <c r="BD126" t="s">
@@ -13315,7 +13511,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="127" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>682</v>
       </c>
@@ -13344,7 +13540,7 @@
       <c r="S127" s="3">
         <v>24.95</v>
       </c>
-      <c r="Y127" s="21">
+      <c r="Y127" s="20">
         <v>9781586424480</v>
       </c>
       <c r="Z127" s="4"/>
@@ -13353,10 +13549,10 @@
         <f t="shared" si="11"/>
         <v>covers/conversations-executioner.jpg</v>
       </c>
-      <c r="AY127" s="34" t="s">
+      <c r="AY127" s="33" t="s">
         <v>683</v>
       </c>
-      <c r="AZ127" s="25" t="s">
+      <c r="AZ127" s="24" t="s">
         <v>687</v>
       </c>
       <c r="BD127" t="s">
@@ -13369,7 +13565,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="128" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>678</v>
       </c>
@@ -13398,7 +13594,7 @@
       <c r="U128" s="3">
         <v>10</v>
       </c>
-      <c r="Y128" s="21">
+      <c r="Y128" s="20">
         <v>9780940962705</v>
       </c>
       <c r="Z128" s="4"/>
@@ -13407,7 +13603,7 @@
         <f t="shared" si="11"/>
         <v>covers/polish-monsters.jpg</v>
       </c>
-      <c r="AY128" s="34" t="s">
+      <c r="AY128" s="33" t="s">
         <v>676</v>
       </c>
       <c r="BD128" t="s">
@@ -13420,7 +13616,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="129" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>716</v>
       </c>
@@ -13446,7 +13642,7 @@
       <c r="S129" s="3">
         <v>12</v>
       </c>
-      <c r="Y129" s="21">
+      <c r="Y129" s="20">
         <v>9780802134028</v>
       </c>
       <c r="Z129" s="4" t="s">
@@ -13466,10 +13662,10 @@
         <f t="shared" si="11"/>
         <v>covers/mass-arras.jpg</v>
       </c>
-      <c r="AY129" s="34" t="s">
+      <c r="AY129" s="33" t="s">
         <v>719</v>
       </c>
-      <c r="AZ129" s="25" t="s">
+      <c r="AZ129" s="24" t="s">
         <v>718</v>
       </c>
       <c r="BD129" t="s">
@@ -13482,7 +13678,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="130" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>720</v>
       </c>
@@ -13524,7 +13720,7 @@
       <c r="S130" s="3">
         <v>15</v>
       </c>
-      <c r="Y130" s="21">
+      <c r="Y130" s="20">
         <v>9781782274728</v>
       </c>
       <c r="Z130" s="4" t="s">
@@ -13544,10 +13740,10 @@
         <f t="shared" si="11"/>
         <v>covers/salt-earth.jpg</v>
       </c>
-      <c r="AY130" s="34" t="s">
+      <c r="AY130" s="33" t="s">
         <v>724</v>
       </c>
-      <c r="AZ130" s="25" t="s">
+      <c r="AZ130" s="24" t="s">
         <v>723</v>
       </c>
       <c r="BD130" t="s">
@@ -13560,7 +13756,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="131" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>726</v>
       </c>
@@ -13589,7 +13785,7 @@
       <c r="S131" s="3">
         <v>20</v>
       </c>
-      <c r="Y131" s="21">
+      <c r="Y131" s="20">
         <v>9780966615265</v>
       </c>
       <c r="Z131" s="4"/>
@@ -13598,10 +13794,10 @@
         <f t="shared" si="11"/>
         <v>covers/7-plays.jpg</v>
       </c>
-      <c r="AY131" s="34" t="s">
+      <c r="AY131" s="33" t="s">
         <v>729</v>
       </c>
-      <c r="AZ131" s="25" t="s">
+      <c r="AZ131" s="24" t="s">
         <v>730</v>
       </c>
       <c r="BD131" t="s">
@@ -13613,8 +13809,14 @@
       <c r="BG131" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="132" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BI131" t="s">
+        <v>848</v>
+      </c>
+      <c r="BJ131">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>731</v>
       </c>
@@ -13654,7 +13856,7 @@
       <c r="S132" s="3">
         <v>12</v>
       </c>
-      <c r="Y132" s="21">
+      <c r="Y132" s="20">
         <v>9780802134882</v>
       </c>
       <c r="Z132" s="4" t="str">
@@ -13675,10 +13877,10 @@
         <f t="shared" si="11"/>
         <v>covers/self-woman.jpg</v>
       </c>
-      <c r="AY132" s="34" t="s">
+      <c r="AY132" s="33" t="s">
         <v>733</v>
       </c>
-      <c r="AZ132" s="25" t="s">
+      <c r="AZ132" s="24" t="s">
         <v>734</v>
       </c>
       <c r="BD132" t="s">
@@ -13691,7 +13893,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="133" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>736</v>
       </c>
@@ -13731,7 +13933,7 @@
       <c r="S133" s="3">
         <v>37</v>
       </c>
-      <c r="Y133" s="21">
+      <c r="Y133" s="20">
         <v>9780415866354</v>
       </c>
       <c r="Z133" s="4" t="str">
@@ -13752,7 +13954,7 @@
         <f t="shared" si="11"/>
         <v>covers/green-goose.jpg</v>
       </c>
-      <c r="AY133" s="34" t="s">
+      <c r="AY133" s="33" t="s">
         <v>737</v>
       </c>
       <c r="BD133" t="s">
@@ -13765,7 +13967,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="134" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>741</v>
       </c>
@@ -13775,7 +13977,7 @@
       <c r="C134">
         <v>1210</v>
       </c>
-      <c r="D134" s="26" t="s">
+      <c r="D134" s="25" t="s">
         <v>739</v>
       </c>
       <c r="E134" t="s">
@@ -13796,16 +13998,16 @@
       <c r="S134" s="3">
         <v>18</v>
       </c>
-      <c r="Y134" s="21">
+      <c r="Y134" s="20">
         <v>9780802140661</v>
       </c>
       <c r="Z134" s="4"/>
       <c r="AA134" s="4"/>
       <c r="AI134" t="str">
-        <f t="shared" ref="AI134:AI193" si="13">"covers/" &amp; A134 &amp; ".jpg"</f>
+        <f t="shared" ref="AI134:AI194" si="13">"covers/" &amp; A134 &amp; ".jpg"</f>
         <v>covers/mrozek-reader.jpg</v>
       </c>
-      <c r="AY134" s="34" t="s">
+      <c r="AY134" s="33" t="s">
         <v>742</v>
       </c>
       <c r="BD134" t="s">
@@ -13818,7 +14020,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="135" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>746</v>
       </c>
@@ -13828,7 +14030,7 @@
       <c r="C135">
         <v>1205</v>
       </c>
-      <c r="D135" s="26" t="s">
+      <c r="D135" s="25" t="s">
         <v>743</v>
       </c>
       <c r="E135" t="s">
@@ -13848,7 +14050,7 @@
       <c r="S135" s="3">
         <v>35</v>
       </c>
-      <c r="Y135" s="21">
+      <c r="Y135" s="20">
         <v>9780810109940</v>
       </c>
       <c r="Z135" s="4"/>
@@ -13857,7 +14059,7 @@
         <f t="shared" si="13"/>
         <v>covers/witkacy-reader.jpg</v>
       </c>
-      <c r="AY135" s="34" t="s">
+      <c r="AY135" s="33" t="s">
         <v>745</v>
       </c>
       <c r="BD135" t="s">
@@ -13876,7 +14078,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>750</v>
       </c>
@@ -13916,7 +14118,7 @@
       <c r="S136" s="3">
         <v>30</v>
       </c>
-      <c r="Y136" s="21">
+      <c r="Y136" s="20">
         <v>9780810129603</v>
       </c>
       <c r="Z136" s="4"/>
@@ -13925,7 +14127,7 @@
         <f t="shared" si="13"/>
         <v>covers/borowski-letters.jpg</v>
       </c>
-      <c r="AY136" s="34" t="s">
+      <c r="AY136" s="33" t="s">
         <v>751</v>
       </c>
       <c r="BD136" t="s">
@@ -13938,7 +14140,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="137" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>755</v>
       </c>
@@ -13948,7 +14150,7 @@
       <c r="C137">
         <v>1207</v>
       </c>
-      <c r="D137" s="26" t="s">
+      <c r="D137" s="25" t="s">
         <v>752</v>
       </c>
       <c r="E137" t="s">
@@ -13966,7 +14168,7 @@
       <c r="S137" s="3">
         <v>22</v>
       </c>
-      <c r="Y137" s="21">
+      <c r="Y137" s="20">
         <v>9780810115194</v>
       </c>
       <c r="Z137" s="4"/>
@@ -13975,7 +14177,7 @@
         <f t="shared" si="13"/>
         <v>covers/ashes-diamonds.jpg</v>
       </c>
-      <c r="AY137" s="34" t="s">
+      <c r="AY137" s="33" t="s">
         <v>754</v>
       </c>
       <c r="BD137" t="s">
@@ -13988,7 +14190,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="138" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>757</v>
       </c>
@@ -14026,7 +14228,7 @@
       <c r="S138" s="3">
         <v>22</v>
       </c>
-      <c r="Y138" s="21">
+      <c r="Y138" s="20">
         <v>9780821417164</v>
       </c>
       <c r="Z138" s="4" t="str">
@@ -14047,10 +14249,10 @@
         <f t="shared" si="13"/>
         <v>covers/holy-week.jpg</v>
       </c>
-      <c r="AY138" s="34" t="s">
+      <c r="AY138" s="33" t="s">
         <v>760</v>
       </c>
-      <c r="AZ138" s="25" t="s">
+      <c r="AZ138" s="24" t="s">
         <v>759</v>
       </c>
       <c r="BD138" t="s">
@@ -14063,7 +14265,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="139" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>762</v>
       </c>
@@ -14089,7 +14291,7 @@
       <c r="S139" s="3">
         <v>15</v>
       </c>
-      <c r="Y139" s="21">
+      <c r="Y139" s="20">
         <v>9780936839837</v>
       </c>
       <c r="Z139" s="4" t="str">
@@ -14110,7 +14312,7 @@
         <f t="shared" si="13"/>
         <v>covers/witkacy-3-plays.jpg</v>
       </c>
-      <c r="AY139" s="34" t="s">
+      <c r="AY139" s="33" t="s">
         <v>764</v>
       </c>
       <c r="BD139" t="s">
@@ -14130,7 +14332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>766</v>
       </c>
@@ -14181,10 +14383,10 @@
         <f t="shared" si="13"/>
         <v>covers/here-in-our.jpg</v>
       </c>
-      <c r="AY140" s="34" t="s">
+      <c r="AY140" s="33" t="s">
         <v>769</v>
       </c>
-      <c r="AZ140" s="25" t="s">
+      <c r="AZ140" s="24" t="s">
         <v>770</v>
       </c>
       <c r="BD140" t="s">
@@ -14197,7 +14399,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="141" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>775</v>
       </c>
@@ -14238,7 +14440,7 @@
       <c r="S141" s="3">
         <v>14</v>
       </c>
-      <c r="Y141" s="21">
+      <c r="Y141" s="20">
         <v>9780374528591</v>
       </c>
       <c r="Z141" s="4"/>
@@ -14247,10 +14449,10 @@
         <f t="shared" si="13"/>
         <v>covers/to-begin-where.jpg</v>
       </c>
-      <c r="AY141" s="34" t="s">
+      <c r="AY141" s="33" t="s">
         <v>773</v>
       </c>
-      <c r="AZ141" s="25" t="s">
+      <c r="AZ141" s="24" t="s">
         <v>774</v>
       </c>
       <c r="BD141" t="s">
@@ -14263,7 +14465,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="142" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>776</v>
       </c>
@@ -14301,7 +14503,7 @@
       <c r="S142" s="3">
         <v>57</v>
       </c>
-      <c r="Y142" s="21">
+      <c r="Y142" s="20">
         <v>9781498556330</v>
       </c>
       <c r="Z142" s="4" t="str">
@@ -14322,10 +14524,10 @@
         <f t="shared" si="13"/>
         <v>covers/melchior-w.jpg</v>
       </c>
-      <c r="AY142" s="34" t="s">
+      <c r="AY142" s="33" t="s">
         <v>781</v>
       </c>
-      <c r="AZ142" s="25" t="s">
+      <c r="AZ142" s="24" t="s">
         <v>780</v>
       </c>
       <c r="BD142" t="s">
@@ -14344,7 +14546,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>784</v>
       </c>
@@ -14398,10 +14600,10 @@
         <f t="shared" si="13"/>
         <v>covers/monte-cassino.jpg</v>
       </c>
-      <c r="AY143" s="34" t="s">
+      <c r="AY143" s="33" t="s">
         <v>786</v>
       </c>
-      <c r="AZ143" s="25" t="s">
+      <c r="AZ143" s="24" t="s">
         <v>785</v>
       </c>
       <c r="BD143" t="s">
@@ -14420,7 +14622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>787</v>
       </c>
@@ -14470,10 +14672,10 @@
         <f t="shared" si="13"/>
         <v>covers/schulz-hijack.jpg</v>
       </c>
-      <c r="AY144" s="34" t="s">
+      <c r="AY144" s="33" t="s">
         <v>791</v>
       </c>
-      <c r="AZ144" s="25" t="s">
+      <c r="AZ144" s="24" t="s">
         <v>792</v>
       </c>
       <c r="BD144" t="s">
@@ -14492,7 +14694,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>793</v>
       </c>
@@ -14502,7 +14704,7 @@
       <c r="C145">
         <v>921</v>
       </c>
-      <c r="D145" s="26" t="s">
+      <c r="D145" s="25" t="s">
         <v>794</v>
       </c>
       <c r="E145" t="s">
@@ -14522,7 +14724,7 @@
       <c r="T145" s="3">
         <v>8</v>
       </c>
-      <c r="Y145" s="21">
+      <c r="Y145" s="20">
         <v>9781517543655</v>
       </c>
       <c r="Z145" s="4"/>
@@ -14531,7 +14733,7 @@
         <f t="shared" si="13"/>
         <v>covers/cinnamon.jpg</v>
       </c>
-      <c r="AY145" s="34" t="s">
+      <c r="AY145" s="33" t="s">
         <v>798</v>
       </c>
       <c r="BD145" t="s">
@@ -14550,7 +14752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>800</v>
       </c>
@@ -14581,7 +14783,7 @@
       <c r="T146" s="3">
         <v>12</v>
       </c>
-      <c r="Y146" s="21">
+      <c r="Y146" s="20">
         <v>9780140186246</v>
       </c>
       <c r="Z146" s="4"/>
@@ -14590,7 +14792,7 @@
         <f t="shared" si="13"/>
         <v>covers/to-the-gas.jpg</v>
       </c>
-      <c r="AY146" s="34" t="s">
+      <c r="AY146" s="33" t="s">
         <v>803</v>
       </c>
       <c r="BD146" t="s">
@@ -14603,7 +14805,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="147" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>807</v>
       </c>
@@ -14613,7 +14815,7 @@
       <c r="C147">
         <v>944</v>
       </c>
-      <c r="D147" s="26" t="s">
+      <c r="D147" s="25" t="s">
         <v>804</v>
       </c>
       <c r="E147" t="str">
@@ -14634,7 +14836,7 @@
       <c r="T147" s="3">
         <v>17</v>
       </c>
-      <c r="Y147" s="21">
+      <c r="Y147" s="20">
         <v>9780143105145</v>
       </c>
       <c r="Z147" s="4"/>
@@ -14643,7 +14845,7 @@
         <f t="shared" si="13"/>
         <v>covers/street-crocodiles.jpg</v>
       </c>
-      <c r="AY147" s="34" t="s">
+      <c r="AY147" s="33" t="s">
         <v>806</v>
       </c>
       <c r="BD147" t="s">
@@ -14655,8 +14857,14 @@
       <c r="BG147" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="148" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BI147" t="s">
+        <v>846</v>
+      </c>
+      <c r="BJ147">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="148" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>811</v>
       </c>
@@ -14687,7 +14895,7 @@
       <c r="T148" s="3">
         <v>11</v>
       </c>
-      <c r="Y148" s="21">
+      <c r="Y148" s="20">
         <v>9781782277897</v>
       </c>
       <c r="Z148" s="4" t="s">
@@ -14706,10 +14914,10 @@
         <f t="shared" si="13"/>
         <v>covers/nocturnal-apparitions.jpg</v>
       </c>
-      <c r="AY148" s="34" t="s">
+      <c r="AY148" s="33" t="s">
         <v>812</v>
       </c>
-      <c r="AZ148" s="25" t="s">
+      <c r="AZ148" s="24" t="s">
         <v>813</v>
       </c>
       <c r="BD148" t="s">
@@ -14721,8 +14929,14 @@
       <c r="BG148" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="149" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BI148" t="s">
+        <v>846</v>
+      </c>
+      <c r="BJ148">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>815</v>
       </c>
@@ -14732,7 +14946,7 @@
       <c r="C149">
         <v>988</v>
       </c>
-      <c r="D149" s="26" t="s">
+      <c r="D149" s="25" t="s">
         <v>814</v>
       </c>
       <c r="E149" t="str">
@@ -14753,7 +14967,7 @@
       <c r="T149" s="3">
         <v>13</v>
       </c>
-      <c r="Y149" s="21">
+      <c r="Y149" s="20">
         <v>9780692519554</v>
       </c>
       <c r="Z149" s="4"/>
@@ -14762,7 +14976,7 @@
         <f t="shared" si="13"/>
         <v>covers/vahazar.jpg</v>
       </c>
-      <c r="AY149" s="34" t="s">
+      <c r="AY149" s="33" t="s">
         <v>817</v>
       </c>
       <c r="BD149" t="s">
@@ -14774,8 +14988,14 @@
       <c r="BG149" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="150" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BI149" t="s">
+        <v>848</v>
+      </c>
+      <c r="BJ149">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="150" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>820</v>
       </c>
@@ -14805,7 +15025,7 @@
       <c r="T150" s="3">
         <v>12</v>
       </c>
-      <c r="Y150" s="21">
+      <c r="Y150" s="20">
         <v>9780979123672</v>
       </c>
       <c r="Z150" s="4" t="s">
@@ -14825,7 +15045,7 @@
         <f t="shared" si="13"/>
         <v>covers/women.jpg</v>
       </c>
-      <c r="AY150" s="34" t="s">
+      <c r="AY150" s="33" t="s">
         <v>823</v>
       </c>
       <c r="BD150" t="s">
@@ -14837,8 +15057,14 @@
       <c r="BG150" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="151" spans="1:62" x14ac:dyDescent="0.25">
+      <c r="BI150" t="s">
+        <v>845</v>
+      </c>
+      <c r="BJ150">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>825</v>
       </c>
@@ -14848,7 +15074,7 @@
       <c r="C151">
         <v>1001</v>
       </c>
-      <c r="D151" s="26" t="s">
+      <c r="D151" s="25" t="s">
         <v>824</v>
       </c>
       <c r="E151" t="s">
@@ -14868,7 +15094,7 @@
       <c r="T151" s="3">
         <v>28</v>
       </c>
-      <c r="Y151" s="21">
+      <c r="Y151" s="20">
         <v>9780875807409</v>
       </c>
       <c r="Z151" s="4" t="s">
@@ -14881,17 +15107,17 @@
       <c r="AB151" s="5">
         <v>17</v>
       </c>
-      <c r="AH151" s="27">
+      <c r="AH151" s="26">
         <v>9781609092016</v>
       </c>
       <c r="AI151" t="str">
         <f t="shared" si="13"/>
         <v>covers/boundary.jpg</v>
       </c>
-      <c r="AY151" s="34" t="s">
+      <c r="AY151" s="33" t="s">
         <v>827</v>
       </c>
-      <c r="AZ151" s="25" t="s">
+      <c r="AZ151" s="24" t="s">
         <v>828</v>
       </c>
       <c r="BD151" t="s">
@@ -14904,7 +15130,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="152" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>834</v>
       </c>
@@ -14934,7 +15160,7 @@
       <c r="T152" s="3">
         <v>12</v>
       </c>
-      <c r="Y152" s="21">
+      <c r="Y152" s="20">
         <v>9780875807102</v>
       </c>
       <c r="Z152" s="4"/>
@@ -14943,10 +15169,10 @@
         <f t="shared" si="13"/>
         <v>covers/romance-teresa.jpg</v>
       </c>
-      <c r="AY152" s="34" t="s">
+      <c r="AY152" s="33" t="s">
         <v>831</v>
       </c>
-      <c r="AZ152" s="25" t="s">
+      <c r="AZ152" s="24" t="s">
         <v>833</v>
       </c>
       <c r="BD152" t="s">
@@ -14965,7 +15191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>837</v>
       </c>
@@ -15007,7 +15233,7 @@
       <c r="T153" s="3">
         <v>15</v>
       </c>
-      <c r="Y153" s="21">
+      <c r="Y153" s="20">
         <v>9780810117433</v>
       </c>
       <c r="Z153" s="4"/>
@@ -15016,10 +15242,10 @@
         <f t="shared" si="13"/>
         <v>covers/medalions.jpg</v>
       </c>
-      <c r="AY153" s="34" t="s">
+      <c r="AY153" s="33" t="s">
         <v>843</v>
       </c>
-      <c r="AZ153" s="25" t="s">
+      <c r="AZ153" s="24" t="s">
         <v>844</v>
       </c>
       <c r="BD153" t="s">
@@ -15038,7 +15264,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>841</v>
       </c>
@@ -15065,7 +15291,7 @@
       <c r="T154" s="3">
         <v>23</v>
       </c>
-      <c r="Y154" s="21">
+      <c r="Y154" s="20">
         <v>9781910895320</v>
       </c>
       <c r="Z154" s="4"/>
@@ -15074,7 +15300,7 @@
         <f t="shared" si="13"/>
         <v>covers/corsets.jpg</v>
       </c>
-      <c r="AY154" s="34" t="s">
+      <c r="AY154" s="33" t="s">
         <v>842</v>
       </c>
       <c r="BD154" t="s">
@@ -15093,7 +15319,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="155" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>1075</v>
       </c>
@@ -15131,7 +15357,7 @@
         <f t="shared" si="13"/>
         <v>covers/phantoms-breslau.jpg</v>
       </c>
-      <c r="AY155" s="34" t="s">
+      <c r="AY155" s="33" t="s">
         <v>852</v>
       </c>
       <c r="BD155" t="s">
@@ -15144,7 +15370,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="156" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>855</v>
       </c>
@@ -15154,7 +15380,7 @@
       <c r="C156">
         <v>1012</v>
       </c>
-      <c r="D156" s="28" t="s">
+      <c r="D156" s="27" t="s">
         <v>854</v>
       </c>
       <c r="E156" t="s">
@@ -15182,10 +15408,10 @@
         <f t="shared" si="13"/>
         <v>covers/death-breslau.jpg</v>
       </c>
-      <c r="AY156" s="34" t="s">
+      <c r="AY156" s="33" t="s">
         <v>856</v>
       </c>
-      <c r="AZ156" s="25" t="s">
+      <c r="AZ156" s="24" t="s">
         <v>857</v>
       </c>
       <c r="BD156" t="s">
@@ -15198,7 +15424,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="157" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>858</v>
       </c>
@@ -15247,10 +15473,10 @@
         <f t="shared" si="13"/>
         <v>covers/end-breslau.jpg</v>
       </c>
-      <c r="AY157" s="34" t="s">
+      <c r="AY157" s="33" t="s">
         <v>861</v>
       </c>
-      <c r="AZ157" s="25" t="s">
+      <c r="AZ157" s="24" t="s">
         <v>862</v>
       </c>
       <c r="BD157" t="s">
@@ -15263,7 +15489,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="158" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>864</v>
       </c>
@@ -15292,7 +15518,7 @@
       <c r="S158" s="3">
         <v>17</v>
       </c>
-      <c r="Y158" s="21">
+      <c r="Y158" s="20">
         <v>9781848662926</v>
       </c>
       <c r="AH158" s="8">
@@ -15302,7 +15528,7 @@
         <f t="shared" si="13"/>
         <v>covers/minotaur.jpg</v>
       </c>
-      <c r="AY158" s="34" t="s">
+      <c r="AY158" s="33" t="s">
         <v>865</v>
       </c>
       <c r="BD158" t="s">
@@ -15315,7 +15541,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="159" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>866</v>
       </c>
@@ -15344,7 +15570,7 @@
       <c r="S159" s="3">
         <v>24</v>
       </c>
-      <c r="Y159" s="21">
+      <c r="Y159" s="20">
         <v>9780810142879</v>
       </c>
       <c r="Z159" s="4" t="s">
@@ -15364,10 +15590,10 @@
         <f t="shared" si="13"/>
         <v>covers/niko-dyzma.jpg</v>
       </c>
-      <c r="AY159" s="34" t="s">
+      <c r="AY159" s="33" t="s">
         <v>871</v>
       </c>
-      <c r="AZ159" s="25" t="s">
+      <c r="AZ159" s="24" t="s">
         <v>870</v>
       </c>
       <c r="BD159" t="s">
@@ -15380,7 +15606,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="160" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>872</v>
       </c>
@@ -15409,7 +15635,7 @@
       <c r="S160" s="3">
         <v>17</v>
       </c>
-      <c r="Y160" s="21">
+      <c r="Y160" s="20">
         <v>9781897231371</v>
       </c>
       <c r="Z160" s="4"/>
@@ -15418,10 +15644,10 @@
         <f t="shared" si="13"/>
         <v>covers/wrote-stone.jpg</v>
       </c>
-      <c r="AY160" s="34" t="s">
+      <c r="AY160" s="33" t="s">
         <v>876</v>
       </c>
-      <c r="AZ160" s="25" t="s">
+      <c r="AZ160" s="24" t="s">
         <v>875</v>
       </c>
       <c r="BD160" t="s">
@@ -15433,8 +15659,14 @@
       <c r="BG160" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="161" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BI160" t="s">
+        <v>1087</v>
+      </c>
+      <c r="BJ160">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>878</v>
       </c>
@@ -15478,7 +15710,7 @@
       <c r="S161" s="3">
         <v>20</v>
       </c>
-      <c r="Y161" s="21">
+      <c r="Y161" s="20">
         <v>9788088628019</v>
       </c>
       <c r="Z161" s="4" t="s">
@@ -15498,10 +15730,10 @@
         <f t="shared" si="13"/>
         <v>covers/phoebe-hicks.jpg</v>
       </c>
-      <c r="AY161" s="34" t="s">
+      <c r="AY161" s="33" t="s">
         <v>881</v>
       </c>
-      <c r="AZ161" s="25" t="s">
+      <c r="AZ161" s="24" t="s">
         <v>884</v>
       </c>
       <c r="BD161" t="s">
@@ -15514,7 +15746,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="162" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>885</v>
       </c>
@@ -15543,7 +15775,7 @@
       <c r="S162" s="3">
         <v>20</v>
       </c>
-      <c r="Y162" s="21">
+      <c r="Y162" s="20">
         <v>9780692037690</v>
       </c>
       <c r="AA162" s="4"/>
@@ -15551,7 +15783,7 @@
         <f t="shared" si="13"/>
         <v>covers/roman-spring.jpg</v>
       </c>
-      <c r="AY162" s="34" t="s">
+      <c r="AY162" s="33" t="s">
         <v>889</v>
       </c>
       <c r="BD162" t="s">
@@ -15564,7 +15796,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="163" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>890</v>
       </c>
@@ -15602,7 +15834,7 @@
       <c r="S163" s="3">
         <v>27</v>
       </c>
-      <c r="Y163" s="21">
+      <c r="Y163" s="20">
         <v>9781804840504</v>
       </c>
       <c r="Z163" s="4" t="s">
@@ -15622,10 +15854,10 @@
         <f t="shared" si="13"/>
         <v>covers/kochanowski-selected.jpg</v>
       </c>
-      <c r="AY163" s="34" t="s">
+      <c r="AY163" s="33" t="s">
         <v>895</v>
       </c>
-      <c r="AZ163" s="25" t="s">
+      <c r="AZ163" s="24" t="s">
         <v>896</v>
       </c>
       <c r="BD163" t="s">
@@ -15638,7 +15870,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="164" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>898</v>
       </c>
@@ -15667,7 +15899,7 @@
       <c r="S164" s="3">
         <v>21</v>
       </c>
-      <c r="Y164" s="21">
+      <c r="Y164" s="20">
         <v>9780691013800</v>
       </c>
       <c r="Z164" s="4" t="s">
@@ -15687,10 +15919,10 @@
         <f t="shared" si="13"/>
         <v>covers/sounds-feelings.jpg</v>
       </c>
-      <c r="AY164" s="34" t="s">
+      <c r="AY164" s="33" t="s">
         <v>903</v>
       </c>
-      <c r="AZ164" s="25" t="s">
+      <c r="AZ164" s="24" t="s">
         <v>902</v>
       </c>
       <c r="BD164" t="s">
@@ -15703,7 +15935,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="165" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>905</v>
       </c>
@@ -15732,7 +15964,7 @@
       <c r="S165" s="3">
         <v>20</v>
       </c>
-      <c r="Y165" s="21">
+      <c r="Y165" s="20">
         <v>9780875806846</v>
       </c>
       <c r="Z165" s="4" t="s">
@@ -15752,7 +15984,7 @@
         <f t="shared" si="13"/>
         <v>covers/the-heathen.jpg</v>
       </c>
-      <c r="AY165" s="34" t="s">
+      <c r="AY165" s="33" t="s">
         <v>907</v>
       </c>
       <c r="BD165" t="s">
@@ -15765,7 +15997,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="166" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>908</v>
       </c>
@@ -15794,7 +16026,7 @@
       <c r="S166" s="3">
         <v>18</v>
       </c>
-      <c r="Y166" s="21">
+      <c r="Y166" s="20">
         <v>9780875804507</v>
       </c>
       <c r="Z166" s="4" t="s">
@@ -15805,10 +16037,10 @@
         <f t="shared" si="13"/>
         <v>covers/malvina.jpg</v>
       </c>
-      <c r="AY166" s="34" t="s">
+      <c r="AY166" s="33" t="s">
         <v>911</v>
       </c>
-      <c r="AZ166" s="25" t="s">
+      <c r="AZ166" s="24" t="s">
         <v>912</v>
       </c>
       <c r="BD166" t="s">
@@ -15821,7 +16053,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="167" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>914</v>
       </c>
@@ -15850,7 +16082,7 @@
       <c r="S167" s="3">
         <v>15</v>
       </c>
-      <c r="Y167" s="21">
+      <c r="Y167" s="20">
         <v>9798363629457</v>
       </c>
       <c r="Z167" s="4" t="s">
@@ -15869,7 +16101,7 @@
         <f t="shared" si="13"/>
         <v>covers/bird-streets.jpg</v>
       </c>
-      <c r="AY167" s="29" t="s">
+      <c r="AY167" s="28" t="s">
         <v>919</v>
       </c>
       <c r="BD167" t="s">
@@ -15882,7 +16114,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="168" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>921</v>
       </c>
@@ -15923,7 +16155,7 @@
       <c r="S168" s="3">
         <v>44</v>
       </c>
-      <c r="Y168" s="21">
+      <c r="Y168" s="20">
         <v>9789057020025</v>
       </c>
       <c r="Z168" s="4" t="s">
@@ -15943,7 +16175,7 @@
         <f t="shared" si="13"/>
         <v>covers/country-house.jpg</v>
       </c>
-      <c r="AY168" s="30" t="s">
+      <c r="AY168" s="29" t="s">
         <v>923</v>
       </c>
       <c r="BD168" t="s">
@@ -15955,8 +16187,14 @@
       <c r="BG168" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="169" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BI168" t="s">
+        <v>848</v>
+      </c>
+      <c r="BJ168">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="169" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>925</v>
       </c>
@@ -15995,7 +16233,7 @@
         <f t="shared" si="13"/>
         <v>covers/locomotive.jpg</v>
       </c>
-      <c r="AY169" s="31" t="s">
+      <c r="AY169" s="30" t="s">
         <v>924</v>
       </c>
       <c r="BD169" t="s">
@@ -16008,7 +16246,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="170" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>932</v>
       </c>
@@ -16018,7 +16256,7 @@
       <c r="C170">
         <v>1005</v>
       </c>
-      <c r="D170" s="32" t="s">
+      <c r="D170" s="31" t="s">
         <v>931</v>
       </c>
       <c r="E170" t="s">
@@ -16033,7 +16271,7 @@
       <c r="J170" s="7">
         <v>110</v>
       </c>
-      <c r="P170" s="33">
+      <c r="P170" s="32">
         <v>9788375763454</v>
       </c>
       <c r="Q170" s="2"/>
@@ -16044,7 +16282,7 @@
         <f t="shared" si="13"/>
         <v>covers/zofia-stry.jpg</v>
       </c>
-      <c r="AY170" s="29" t="s">
+      <c r="AY170" s="28" t="s">
         <v>934</v>
       </c>
       <c r="BD170" t="s">
@@ -16057,7 +16295,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="171" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>935</v>
       </c>
@@ -16099,7 +16337,7 @@
       <c r="S171" s="3">
         <v>21</v>
       </c>
-      <c r="Y171" s="21">
+      <c r="Y171" s="20">
         <v>9781543240900</v>
       </c>
       <c r="Z171" s="4" t="s">
@@ -16119,7 +16357,7 @@
         <f t="shared" si="13"/>
         <v>covers/67-tales.jpg</v>
       </c>
-      <c r="AY171" s="34" t="s">
+      <c r="AY171" s="33" t="s">
         <v>939</v>
       </c>
       <c r="BD171" t="s">
@@ -16132,7 +16370,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="172" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>941</v>
       </c>
@@ -16178,10 +16416,10 @@
         <f t="shared" si="13"/>
         <v>covers/triumph-provocation.jpg</v>
       </c>
-      <c r="AY172" s="34" t="s">
+      <c r="AY172" s="33" t="s">
         <v>946</v>
       </c>
-      <c r="AZ172" s="25" t="s">
+      <c r="AZ172" s="24" t="s">
         <v>945</v>
       </c>
       <c r="BD172" t="s">
@@ -16194,7 +16432,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="173" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>947</v>
       </c>
@@ -16240,7 +16478,7 @@
       <c r="S173" s="2">
         <v>19</v>
       </c>
-      <c r="Y173" s="21">
+      <c r="Y173" s="20">
         <v>9788395612206</v>
       </c>
       <c r="Z173" s="4"/>
@@ -16249,7 +16487,7 @@
         <f t="shared" si="13"/>
         <v>covers/sindbad.jpg</v>
       </c>
-      <c r="AY173" s="34" t="s">
+      <c r="AY173" s="33" t="s">
         <v>952</v>
       </c>
       <c r="BD173" t="s">
@@ -16262,7 +16500,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="174" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>954</v>
       </c>
@@ -16293,7 +16531,7 @@
       <c r="S174" s="3">
         <v>20</v>
       </c>
-      <c r="Y174" s="21">
+      <c r="Y174" s="20">
         <v>9781546749554</v>
       </c>
       <c r="Z174" s="4"/>
@@ -16302,7 +16540,7 @@
         <f t="shared" si="13"/>
         <v>covers/beyond-beyond.jpg</v>
       </c>
-      <c r="AY174" s="34" t="s">
+      <c r="AY174" s="33" t="s">
         <v>956</v>
       </c>
       <c r="BD174" t="s">
@@ -16315,7 +16553,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="175" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>958</v>
       </c>
@@ -16346,7 +16584,7 @@
       <c r="S175" s="3">
         <v>29</v>
       </c>
-      <c r="Y175" s="21">
+      <c r="Y175" s="20">
         <v>9780692201398</v>
       </c>
       <c r="Z175" s="4"/>
@@ -16355,7 +16593,7 @@
         <f t="shared" si="13"/>
         <v>covers/marvellations.jpg</v>
       </c>
-      <c r="AY175" s="38" t="s">
+      <c r="AY175" s="37" t="s">
         <v>959</v>
       </c>
       <c r="BD175" t="s">
@@ -16368,7 +16606,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="176" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>961</v>
       </c>
@@ -16399,7 +16637,7 @@
       <c r="S176" s="3">
         <v>16</v>
       </c>
-      <c r="Y176" s="21">
+      <c r="Y176" s="20">
         <v>9781466220232</v>
       </c>
       <c r="Z176" s="4"/>
@@ -16408,7 +16646,7 @@
         <f t="shared" si="13"/>
         <v>covers/33-poems.jpg</v>
       </c>
-      <c r="AY176" s="34" t="s">
+      <c r="AY176" s="33" t="s">
         <v>962</v>
       </c>
       <c r="BD176" t="s">
@@ -16421,7 +16659,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="177" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>963</v>
       </c>
@@ -16448,7 +16686,7 @@
       <c r="S177" s="3">
         <v>25</v>
       </c>
-      <c r="Y177" s="21">
+      <c r="Y177" s="20">
         <v>9781595340337</v>
       </c>
       <c r="Z177" s="4"/>
@@ -16457,7 +16695,7 @@
         <f t="shared" si="13"/>
         <v>covers/on-writing.jpg</v>
       </c>
-      <c r="AY177" s="34" t="s">
+      <c r="AY177" s="33" t="s">
         <v>966</v>
       </c>
       <c r="BD177" t="s">
@@ -16470,7 +16708,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="178" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>968</v>
       </c>
@@ -16509,7 +16747,7 @@
       <c r="S178" s="3">
         <v>40</v>
       </c>
-      <c r="Y178" s="21">
+      <c r="Y178" s="20">
         <v>9781501387142</v>
       </c>
       <c r="Z178" s="4"/>
@@ -16518,10 +16756,10 @@
         <f t="shared" si="13"/>
         <v>covers/polish-lit-as-world.jpg</v>
       </c>
-      <c r="AY178" s="34" t="s">
+      <c r="AY178" s="33" t="s">
         <v>971</v>
       </c>
-      <c r="AZ178" s="25" t="s">
+      <c r="AZ178" s="24" t="s">
         <v>972</v>
       </c>
       <c r="BD178" t="s">
@@ -16534,7 +16772,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="179" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>976</v>
       </c>
@@ -16564,7 +16802,7 @@
       <c r="S179" s="3">
         <v>16</v>
       </c>
-      <c r="Y179" s="21">
+      <c r="Y179" s="20">
         <v>9781934414880</v>
       </c>
       <c r="Z179" s="4"/>
@@ -16573,7 +16811,7 @@
         <f t="shared" si="13"/>
         <v>covers/folding-star.jpg</v>
       </c>
-      <c r="AY179" s="34" t="s">
+      <c r="AY179" s="33" t="s">
         <v>977</v>
       </c>
       <c r="BD179" t="s">
@@ -16586,7 +16824,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="180" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>978</v>
       </c>
@@ -16616,7 +16854,7 @@
       <c r="S180" s="3">
         <v>16</v>
       </c>
-      <c r="Y180" s="21">
+      <c r="Y180" s="20">
         <v>9781938160349</v>
       </c>
       <c r="Z180" s="4"/>
@@ -16625,7 +16863,7 @@
         <f t="shared" si="13"/>
         <v>covers/world-shared.jpg</v>
       </c>
-      <c r="AY180" s="34" t="s">
+      <c r="AY180" s="33" t="s">
         <v>982</v>
       </c>
       <c r="BD180" t="s">
@@ -16638,7 +16876,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="181" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>983</v>
       </c>
@@ -16668,7 +16906,7 @@
       <c r="S181" s="3">
         <v>16</v>
       </c>
-      <c r="Y181" s="21">
+      <c r="Y181" s="20">
         <v>9781935744078</v>
       </c>
       <c r="Z181" s="4" t="s">
@@ -16685,10 +16923,10 @@
         <f t="shared" si="13"/>
         <v>covers/poems-norwid.jpg</v>
       </c>
-      <c r="AY181" s="34" t="s">
+      <c r="AY181" s="33" t="s">
         <v>985</v>
       </c>
-      <c r="AZ181" s="25" t="s">
+      <c r="AZ181" s="24" t="s">
         <v>986</v>
       </c>
       <c r="BD181" t="s">
@@ -16701,7 +16939,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="182" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>988</v>
       </c>
@@ -16749,10 +16987,10 @@
         <f t="shared" si="13"/>
         <v>covers/sound-modern.jpg</v>
       </c>
-      <c r="AY182" s="34" t="s">
+      <c r="AY182" s="33" t="s">
         <v>995</v>
       </c>
-      <c r="AZ182" s="25" t="s">
+      <c r="AZ182" s="24" t="s">
         <v>994</v>
       </c>
       <c r="BD182" t="s">
@@ -16765,7 +17003,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="183" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>996</v>
       </c>
@@ -16795,7 +17033,7 @@
       <c r="S183" s="3">
         <v>20</v>
       </c>
-      <c r="Y183" s="21">
+      <c r="Y183" s="20">
         <v>9780802145130</v>
       </c>
       <c r="Z183" s="4" t="str">
@@ -16816,10 +17054,10 @@
         <f t="shared" si="13"/>
         <v>covers/pornografia.jpg</v>
       </c>
-      <c r="AY183" s="34" t="s">
+      <c r="AY183" s="33" t="s">
         <v>999</v>
       </c>
-      <c r="AZ183" s="25" t="s">
+      <c r="AZ183" s="24" t="s">
         <v>1000</v>
       </c>
       <c r="BD183" t="s">
@@ -16832,7 +17070,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="184" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>1001</v>
       </c>
@@ -16862,7 +17100,7 @@
       <c r="S184" s="3">
         <v>17</v>
       </c>
-      <c r="Y184" s="21">
+      <c r="Y184" s="20">
         <v>9780300175301</v>
       </c>
       <c r="Z184" s="4" t="str">
@@ -16882,10 +17120,10 @@
         <f t="shared" si="13"/>
         <v>covers/transatlantic.jpg</v>
       </c>
-      <c r="AY184" s="34" t="s">
+      <c r="AY184" s="33" t="s">
         <v>1004</v>
       </c>
-      <c r="AZ184" s="25" t="s">
+      <c r="AZ184" s="24" t="s">
         <v>1003</v>
       </c>
       <c r="BD184" t="s">
@@ -16898,7 +17136,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="185" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>1005</v>
       </c>
@@ -16937,7 +17175,7 @@
       <c r="S185" s="3">
         <v>27</v>
       </c>
-      <c r="Y185" s="21">
+      <c r="Y185" s="20">
         <v>9781021190314</v>
       </c>
       <c r="Z185" s="4"/>
@@ -16946,7 +17184,7 @@
         <f t="shared" si="13"/>
         <v>covers/angels-dust.jpg</v>
       </c>
-      <c r="AY185" s="34" t="s">
+      <c r="AY185" s="33" t="s">
         <v>1008</v>
       </c>
       <c r="BD185" t="s">
@@ -16959,7 +17197,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="186" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>1010</v>
       </c>
@@ -16992,7 +17230,7 @@
       <c r="S186" s="3">
         <v>18</v>
       </c>
-      <c r="Y186" s="21">
+      <c r="Y186" s="20">
         <v>9788086264349</v>
       </c>
       <c r="Z186" s="4" t="str">
@@ -17013,10 +17251,10 @@
         <f t="shared" si="13"/>
         <v>covers/burn-paris.jpg</v>
       </c>
-      <c r="AY186" s="34" t="s">
+      <c r="AY186" s="33" t="s">
         <v>1015</v>
       </c>
-      <c r="AZ186" s="25" t="s">
+      <c r="AZ186" s="24" t="s">
         <v>1016</v>
       </c>
       <c r="BD186" t="s">
@@ -17029,7 +17267,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="187" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>1035</v>
       </c>
@@ -17059,7 +17297,7 @@
       <c r="S187" s="3">
         <v>13</v>
       </c>
-      <c r="Y187" s="21">
+      <c r="Y187" s="20">
         <v>9781939931214</v>
       </c>
       <c r="Z187" s="4" t="str">
@@ -17080,10 +17318,10 @@
         <f t="shared" si="13"/>
         <v>covers/killing-auntie.jpg</v>
       </c>
-      <c r="AY187" s="34" t="s">
+      <c r="AY187" s="33" t="s">
         <v>1040</v>
       </c>
-      <c r="AZ187" s="25" t="s">
+      <c r="AZ187" s="24" t="s">
         <v>1041</v>
       </c>
       <c r="BD187" t="s">
@@ -17096,7 +17334,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="188" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>1042</v>
       </c>
@@ -17132,13 +17370,13 @@
         <v>Paperback</v>
       </c>
       <c r="R188" s="2" t="str">
-        <f t="shared" ref="R188:R236" si="18">I188</f>
+        <f t="shared" ref="R188" si="18">I188</f>
         <v>Academic Studies Press</v>
       </c>
       <c r="S188" s="3">
         <v>23</v>
       </c>
-      <c r="Y188" s="21">
+      <c r="Y188" s="20">
         <v>9781644695654</v>
       </c>
       <c r="Z188" s="4" t="str">
@@ -17159,10 +17397,10 @@
         <f t="shared" si="13"/>
         <v>covers/palestine-3rd.jpg</v>
       </c>
-      <c r="AY188" s="34" t="s">
+      <c r="AY188" s="33" t="s">
         <v>1046</v>
       </c>
-      <c r="AZ188" s="25" t="s">
+      <c r="AZ188" s="24" t="s">
         <v>1047</v>
       </c>
       <c r="BD188" t="s">
@@ -17175,7 +17413,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="189" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>1049</v>
       </c>
@@ -17206,7 +17444,7 @@
       <c r="S189" s="3">
         <v>35</v>
       </c>
-      <c r="Y189" s="21">
+      <c r="Y189" s="20">
         <v>9780810111349</v>
       </c>
       <c r="Z189" s="4"/>
@@ -17215,14 +17453,23 @@
         <f t="shared" si="13"/>
         <v>covers/insatiability.jpg</v>
       </c>
-      <c r="AY189" s="34" t="s">
+      <c r="AY189" s="33" t="s">
         <v>1051</v>
       </c>
-      <c r="AZ189" s="25" t="s">
+      <c r="AZ189" s="24" t="s">
         <v>1052</v>
       </c>
-    </row>
-    <row r="190" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BD189" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE189" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG189" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="190" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>1054</v>
       </c>
@@ -17252,7 +17499,7 @@
       <c r="S190" s="3">
         <v>12</v>
       </c>
-      <c r="Y190" s="21">
+      <c r="Y190" s="20">
         <v>9780156881500</v>
       </c>
       <c r="Z190" s="4"/>
@@ -17261,11 +17508,20 @@
         <f t="shared" si="13"/>
         <v>covers/pirx.jpg</v>
       </c>
-      <c r="AY190" s="34" t="s">
+      <c r="AY190" s="33" t="s">
         <v>1056</v>
       </c>
-    </row>
-    <row r="191" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BD190" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE190" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG190" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="191" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>1061</v>
       </c>
@@ -17295,7 +17551,7 @@
       <c r="S191" s="3">
         <v>11</v>
       </c>
-      <c r="Y191" s="21">
+      <c r="Y191" s="20">
         <v>9780156165006</v>
       </c>
       <c r="Z191" s="4"/>
@@ -17304,11 +17560,20 @@
         <f t="shared" si="13"/>
         <v>covers/chain-chance.jpg</v>
       </c>
-      <c r="AY191" s="34" t="s">
+      <c r="AY191" s="33" t="s">
         <v>1063</v>
       </c>
-    </row>
-    <row r="192" spans="1:59" x14ac:dyDescent="0.25">
+      <c r="BD191" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE191" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG191" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="192" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>1058</v>
       </c>
@@ -17337,7 +17602,7 @@
       <c r="S192" s="3">
         <v>22</v>
       </c>
-      <c r="Y192" s="21">
+      <c r="Y192" s="20">
         <v>9780374519377</v>
       </c>
       <c r="Z192" s="4"/>
@@ -17346,19 +17611,31 @@
         <f t="shared" si="13"/>
         <v>covers/ulro.jpg</v>
       </c>
-      <c r="AY192" s="34" t="s">
+      <c r="AY192" s="33" t="s">
         <v>1059</v>
       </c>
-      <c r="AZ192" s="25" t="s">
+      <c r="AZ192" s="24" t="s">
         <v>1060</v>
       </c>
-    </row>
-    <row r="193" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="BD192" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE192" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG192" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="193" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>1068</v>
       </c>
       <c r="B193" t="s">
         <v>1071</v>
+      </c>
+      <c r="C193">
+        <v>703</v>
       </c>
       <c r="D193" s="15" t="s">
         <v>1065</v>
@@ -17383,7 +17660,7 @@
         <v>9798887196886</v>
       </c>
       <c r="Q193" s="2" t="str">
-        <f>Q191</f>
+        <f t="shared" ref="Q193:Q194" si="19">Q191</f>
         <v>Paperback</v>
       </c>
       <c r="R193" s="2" t="str">
@@ -17393,7 +17670,7 @@
       <c r="S193" s="3">
         <v>25</v>
       </c>
-      <c r="Y193" s="21">
+      <c r="Y193" s="20">
         <v>9798887196893</v>
       </c>
       <c r="Z193" s="4" t="str">
@@ -17414,409 +17691,335 @@
         <f t="shared" si="13"/>
         <v>covers/little-orphan-mary.jpg</v>
       </c>
-      <c r="AY193" s="34" t="s">
+      <c r="AY193" s="33" t="s">
         <v>1069</v>
       </c>
-    </row>
-    <row r="194" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="H194" s="6"/>
-      <c r="I194" s="10"/>
-      <c r="Q194" s="2"/>
+      <c r="BD193" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE193" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG193" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="194" spans="1:59" ht="85.5" x14ac:dyDescent="0.45">
+      <c r="A194" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B194" t="s">
+        <v>124</v>
+      </c>
+      <c r="C194">
+        <v>1670</v>
+      </c>
+      <c r="D194" s="15" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E194" t="s">
+        <v>127</v>
+      </c>
+      <c r="F194" t="s">
+        <v>156</v>
+      </c>
+      <c r="H194" s="6" t="str">
+        <f>H193</f>
+        <v>Hardcover</v>
+      </c>
+      <c r="I194" s="10" t="s">
+        <v>1090</v>
+      </c>
+      <c r="J194" s="7">
+        <v>42</v>
+      </c>
+      <c r="P194" s="10">
+        <v>9780393049398</v>
+      </c>
+      <c r="Q194" s="2" t="str">
+        <f t="shared" si="19"/>
+        <v>Paperback</v>
+      </c>
+      <c r="R194" s="49" t="str">
+        <f>I194</f>
+        <v xml:space="preserve">W. W. Norton </v>
+      </c>
+      <c r="S194" s="3">
+        <v>20</v>
+      </c>
+      <c r="Y194" s="20">
+        <v>9780393323856</v>
+      </c>
       <c r="Z194" s="4"/>
       <c r="AA194" s="4"/>
-    </row>
-    <row r="195" spans="1:51" x14ac:dyDescent="0.25">
+      <c r="AI194" t="str">
+        <f t="shared" si="13"/>
+        <v>covers/miracle-fair.jpg</v>
+      </c>
+      <c r="AY194" s="50" t="s">
+        <v>1091</v>
+      </c>
+      <c r="AZ194" s="51" t="s">
+        <v>1092</v>
+      </c>
+      <c r="BD194" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE194" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG194" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="195" spans="1:59" x14ac:dyDescent="0.45">
       <c r="H195" s="6"/>
-      <c r="R195" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+      <c r="R195" s="2"/>
       <c r="Z195" s="4"/>
       <c r="AA195" s="4"/>
     </row>
-    <row r="196" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:59" x14ac:dyDescent="0.45">
       <c r="H196" s="6"/>
-      <c r="R196" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+      <c r="R196" s="2"/>
       <c r="Z196" s="4"/>
       <c r="AA196" s="4"/>
     </row>
-    <row r="197" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:59" x14ac:dyDescent="0.45">
       <c r="H197" s="6"/>
-      <c r="R197" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+      <c r="R197" s="2"/>
       <c r="Z197" s="4"/>
       <c r="AA197" s="4"/>
     </row>
-    <row r="198" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:59" x14ac:dyDescent="0.45">
       <c r="H198" s="6"/>
-      <c r="R198" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+      <c r="R198" s="2"/>
       <c r="Z198" s="4"/>
       <c r="AA198" s="4"/>
     </row>
-    <row r="199" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:59" x14ac:dyDescent="0.45">
       <c r="H199" s="6"/>
-      <c r="R199" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+      <c r="R199" s="2"/>
       <c r="Z199" s="4"/>
       <c r="AA199" s="4"/>
     </row>
-    <row r="200" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:59" x14ac:dyDescent="0.45">
       <c r="H200" s="6"/>
-      <c r="R200" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+      <c r="R200" s="2"/>
       <c r="Z200" s="4"/>
       <c r="AA200" s="4"/>
     </row>
-    <row r="201" spans="1:51" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:59" x14ac:dyDescent="0.45">
       <c r="H201" s="6"/>
-      <c r="R201" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+      <c r="R201" s="2"/>
       <c r="Z201" s="4"/>
       <c r="AA201" s="4"/>
     </row>
-    <row r="202" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="R202" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="202" spans="1:59" x14ac:dyDescent="0.45">
+      <c r="R202" s="2"/>
       <c r="Z202" s="4"/>
       <c r="AA202" s="4"/>
     </row>
-    <row r="203" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="R203" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="203" spans="1:59" x14ac:dyDescent="0.45">
+      <c r="R203" s="2"/>
       <c r="Z203" s="4"/>
       <c r="AA203" s="4"/>
     </row>
-    <row r="204" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="R204" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="204" spans="1:59" x14ac:dyDescent="0.45">
+      <c r="R204" s="2"/>
       <c r="Z204" s="4"/>
       <c r="AA204" s="4"/>
     </row>
-    <row r="205" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="R205" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="205" spans="1:59" x14ac:dyDescent="0.45">
+      <c r="R205" s="2"/>
       <c r="Z205" s="4"/>
       <c r="AA205" s="4"/>
     </row>
-    <row r="206" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="R206" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="206" spans="1:59" x14ac:dyDescent="0.45">
+      <c r="R206" s="2"/>
       <c r="Z206" s="4"/>
       <c r="AA206" s="4"/>
     </row>
-    <row r="207" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="R207" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="207" spans="1:59" x14ac:dyDescent="0.45">
+      <c r="R207" s="2"/>
       <c r="Z207" s="4"/>
       <c r="AA207" s="4"/>
     </row>
-    <row r="208" spans="1:51" x14ac:dyDescent="0.25">
-      <c r="R208" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="208" spans="1:59" x14ac:dyDescent="0.45">
+      <c r="R208" s="2"/>
       <c r="Z208" s="4"/>
       <c r="AA208" s="4"/>
     </row>
-    <row r="209" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R209" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="209" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R209" s="2"/>
       <c r="Z209" s="4"/>
       <c r="AA209" s="4"/>
     </row>
-    <row r="210" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R210" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="210" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R210" s="2"/>
       <c r="Z210" s="4"/>
       <c r="AA210" s="4"/>
     </row>
-    <row r="211" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R211" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="211" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R211" s="2"/>
       <c r="Z211" s="4"/>
       <c r="AA211" s="4"/>
     </row>
-    <row r="212" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R212" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="212" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R212" s="2"/>
       <c r="Z212" s="4"/>
       <c r="AA212" s="4"/>
     </row>
-    <row r="213" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R213" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="213" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R213" s="2"/>
       <c r="Z213" s="4"/>
       <c r="AA213" s="4"/>
     </row>
-    <row r="214" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R214" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="214" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R214" s="2"/>
       <c r="Z214" s="4"/>
       <c r="AA214" s="4"/>
     </row>
-    <row r="215" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R215" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="215" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R215" s="2"/>
       <c r="Z215" s="4"/>
       <c r="AA215" s="4"/>
     </row>
-    <row r="216" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R216" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="216" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R216" s="2"/>
       <c r="Z216" s="4"/>
       <c r="AA216" s="4"/>
     </row>
-    <row r="217" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R217" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="217" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R217" s="2"/>
       <c r="Z217" s="4"/>
       <c r="AA217" s="4"/>
     </row>
-    <row r="218" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R218" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="218" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R218" s="2"/>
       <c r="Z218" s="4"/>
       <c r="AA218" s="4"/>
     </row>
-    <row r="219" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R219" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="219" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R219" s="2"/>
       <c r="Z219" s="4"/>
       <c r="AA219" s="4"/>
     </row>
-    <row r="220" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R220" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="220" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R220" s="2"/>
       <c r="Z220" s="4"/>
       <c r="AA220" s="4"/>
     </row>
-    <row r="221" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R221" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="221" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R221" s="2"/>
       <c r="Z221" s="4"/>
       <c r="AA221" s="4"/>
     </row>
-    <row r="222" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R222" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="222" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R222" s="2"/>
       <c r="Z222" s="4"/>
       <c r="AA222" s="4"/>
     </row>
-    <row r="223" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R223" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="223" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R223" s="2"/>
       <c r="Z223" s="4"/>
       <c r="AA223" s="4"/>
     </row>
-    <row r="224" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R224" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="224" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R224" s="2"/>
       <c r="Z224" s="4"/>
       <c r="AA224" s="4"/>
     </row>
-    <row r="225" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R225" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="225" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R225" s="2"/>
       <c r="Z225" s="4"/>
       <c r="AA225" s="4"/>
     </row>
-    <row r="226" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R226" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="226" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R226" s="2"/>
       <c r="Z226" s="4"/>
       <c r="AA226" s="4"/>
     </row>
-    <row r="227" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R227" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="227" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R227" s="2"/>
       <c r="Z227" s="4"/>
       <c r="AA227" s="4"/>
     </row>
-    <row r="228" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R228" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="228" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R228" s="2"/>
       <c r="Z228" s="4"/>
       <c r="AA228" s="4"/>
     </row>
-    <row r="229" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R229" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="229" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R229" s="2"/>
       <c r="Z229" s="4"/>
       <c r="AA229" s="4"/>
     </row>
-    <row r="230" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R230" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="230" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R230" s="2"/>
       <c r="Z230" s="4"/>
       <c r="AA230" s="4"/>
     </row>
-    <row r="231" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R231" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="231" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R231" s="2"/>
       <c r="Z231" s="4"/>
       <c r="AA231" s="4"/>
     </row>
-    <row r="232" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R232" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="232" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R232" s="2"/>
       <c r="Z232" s="4"/>
       <c r="AA232" s="4"/>
     </row>
-    <row r="233" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R233" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="233" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R233" s="2"/>
       <c r="Z233" s="4"/>
       <c r="AA233" s="4"/>
     </row>
-    <row r="234" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R234" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="234" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R234" s="2"/>
       <c r="Z234" s="4"/>
       <c r="AA234" s="4"/>
     </row>
-    <row r="235" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R235" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="235" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R235" s="2"/>
       <c r="Z235" s="4"/>
       <c r="AA235" s="4"/>
     </row>
-    <row r="236" spans="18:27" x14ac:dyDescent="0.25">
-      <c r="R236" s="2">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
+    <row r="236" spans="18:27" x14ac:dyDescent="0.45">
+      <c r="R236" s="2"/>
       <c r="Z236" s="4"/>
-      <c r="AA236" s="4" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="237" spans="18:27" x14ac:dyDescent="0.25">
+      <c r="AA236" s="4"/>
+    </row>
+    <row r="237" spans="18:27" x14ac:dyDescent="0.45">
       <c r="Z237" s="4"/>
-      <c r="AA237" s="4" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="238" spans="18:27" x14ac:dyDescent="0.25">
+      <c r="AA237" s="4"/>
+    </row>
+    <row r="238" spans="18:27" x14ac:dyDescent="0.45">
       <c r="Z238" s="4"/>
-      <c r="AA238" s="4" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="239" spans="18:27" x14ac:dyDescent="0.25">
+      <c r="AA238" s="4"/>
+    </row>
+    <row r="239" spans="18:27" x14ac:dyDescent="0.45">
       <c r="Z239" s="4"/>
-      <c r="AA239" s="4" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="240" spans="18:27" x14ac:dyDescent="0.25">
+      <c r="AA239" s="4"/>
+    </row>
+    <row r="240" spans="18:27" x14ac:dyDescent="0.45">
       <c r="Z240" s="4"/>
-      <c r="AA240" s="4" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="241" spans="26:27" x14ac:dyDescent="0.25">
+      <c r="AA240" s="4"/>
+    </row>
+    <row r="241" spans="26:27" x14ac:dyDescent="0.45">
       <c r="Z241" s="4"/>
-      <c r="AA241" s="4" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="242" spans="26:27" x14ac:dyDescent="0.25">
+      <c r="AA241" s="4"/>
+    </row>
+    <row r="242" spans="26:27" x14ac:dyDescent="0.45">
       <c r="Z242" s="4"/>
-      <c r="AA242" s="4" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="243" spans="26:27" x14ac:dyDescent="0.25">
+      <c r="AA242" s="4"/>
+    </row>
+    <row r="243" spans="26:27" x14ac:dyDescent="0.45">
       <c r="Z243" s="4"/>
-      <c r="AA243" s="4" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="244" spans="26:27" x14ac:dyDescent="0.25">
+      <c r="AA243" s="4"/>
+    </row>
+    <row r="244" spans="26:27" x14ac:dyDescent="0.45">
       <c r="Z244" s="4"/>
-      <c r="AA244" s="4" t="s">
-        <v>341</v>
-      </c>
+      <c r="AA244" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/the-polish-atheneum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3555" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5460FCC2-3C56-4E0B-AEE8-F2FE0A5260C6}"/>
+  <xr:revisionPtr revIDLastSave="3559" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14E546A4-A97F-41BF-AA05-922B5CA223B4}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4672,7 +4672,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -4732,16 +4732,13 @@
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -4764,10 +4761,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5088,33 +5081,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01CE5F32-AD1D-47CB-A8F1-52ACBFFA0BE8}">
   <dimension ref="A1:BJ244"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="29.1328125" customWidth="1"/>
-    <col min="2" max="2" width="50.86328125" customWidth="1"/>
-    <col min="3" max="3" width="13.73046875" customWidth="1"/>
+    <col min="1" max="1" width="29.140625" customWidth="1"/>
+    <col min="2" max="2" width="50.85546875" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
     <col min="4" max="4" width="46" style="15" customWidth="1"/>
     <col min="5" max="7" width="46" customWidth="1"/>
-    <col min="8" max="10" width="9.1328125" style="7"/>
+    <col min="8" max="10" width="9.140625" style="7"/>
     <col min="11" max="12" width="9" style="7"/>
-    <col min="13" max="15" width="9.1328125" style="7"/>
-    <col min="16" max="16" width="28.86328125" style="10" customWidth="1"/>
-    <col min="17" max="24" width="9.1328125" style="3"/>
+    <col min="13" max="15" width="9.140625" style="7"/>
+    <col min="16" max="16" width="28.85546875" style="10" customWidth="1"/>
+    <col min="17" max="24" width="9.140625" style="3"/>
     <col min="25" max="25" width="17" style="20" customWidth="1"/>
-    <col min="26" max="33" width="9.1328125" style="5"/>
+    <col min="26" max="33" width="9.140625" style="5"/>
     <col min="34" max="34" width="22" style="8" customWidth="1"/>
-    <col min="35" max="36" width="26.265625" customWidth="1"/>
+    <col min="35" max="36" width="26.28515625" customWidth="1"/>
     <col min="39" max="39" width="16" customWidth="1"/>
-    <col min="41" max="41" width="21.1328125" customWidth="1"/>
-    <col min="42" max="45" width="19.73046875" customWidth="1"/>
-    <col min="46" max="46" width="19.73046875" style="24" customWidth="1"/>
-    <col min="47" max="50" width="19.73046875" customWidth="1"/>
-    <col min="51" max="51" width="95.86328125" style="33" customWidth="1"/>
-    <col min="52" max="52" width="66.86328125" style="24" customWidth="1"/>
-    <col min="53" max="55" width="19.73046875" customWidth="1"/>
+    <col min="41" max="41" width="21.140625" customWidth="1"/>
+    <col min="42" max="45" width="19.7109375" customWidth="1"/>
+    <col min="46" max="46" width="19.7109375" style="24" customWidth="1"/>
+    <col min="47" max="50" width="19.7109375" customWidth="1"/>
+    <col min="51" max="51" width="95.85546875" style="33" customWidth="1"/>
+    <col min="52" max="52" width="66.85546875" style="24" customWidth="1"/>
+    <col min="53" max="55" width="19.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -5302,7 +5295,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -5388,7 +5381,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -5462,7 +5455,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -5543,7 +5536,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -5599,7 +5592,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -5666,7 +5659,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -5732,7 +5725,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -5802,7 +5795,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -5876,7 +5869,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -5946,7 +5939,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -6011,7 +6004,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>62</v>
       </c>
@@ -6080,7 +6073,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -6139,7 +6132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -6200,7 +6193,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>72</v>
       </c>
@@ -6208,7 +6201,7 @@
         <v>74</v>
       </c>
       <c r="C15">
-        <v>100</v>
+        <v>675</v>
       </c>
       <c r="D15" s="14" t="s">
         <v>69</v>
@@ -6265,7 +6258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>73</v>
       </c>
@@ -6330,7 +6323,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>123</v>
       </c>
@@ -6416,7 +6409,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>367</v>
       </c>
@@ -6477,7 +6470,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>122</v>
       </c>
@@ -6563,7 +6556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>84</v>
       </c>
@@ -6658,7 +6651,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>80</v>
       </c>
@@ -6753,7 +6746,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>1018</v>
       </c>
@@ -6848,7 +6841,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>1020</v>
       </c>
@@ -6943,7 +6936,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>1024</v>
       </c>
@@ -7038,7 +7031,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>1027</v>
       </c>
@@ -7133,7 +7126,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>1030</v>
       </c>
@@ -7228,7 +7221,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>1064</v>
       </c>
@@ -7326,7 +7319,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>87</v>
       </c>
@@ -7406,7 +7399,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>91</v>
       </c>
@@ -7462,7 +7455,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>121</v>
       </c>
@@ -7518,7 +7511,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>105</v>
       </c>
@@ -7611,7 +7604,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>1033</v>
       </c>
@@ -7702,7 +7695,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>96</v>
       </c>
@@ -7810,7 +7803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>97</v>
       </c>
@@ -7892,7 +7885,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>104</v>
       </c>
@@ -7956,7 +7949,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>103</v>
       </c>
@@ -8020,7 +8013,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>116</v>
       </c>
@@ -8098,7 +8091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>117</v>
       </c>
@@ -8176,7 +8169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>118</v>
       </c>
@@ -8244,7 +8237,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>150</v>
       </c>
@@ -8292,7 +8285,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>154</v>
       </c>
@@ -8351,7 +8344,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>155</v>
       </c>
@@ -8402,7 +8395,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>145</v>
       </c>
@@ -8453,7 +8446,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>146</v>
       </c>
@@ -8519,7 +8512,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>147</v>
       </c>
@@ -8582,7 +8575,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>148</v>
       </c>
@@ -8645,7 +8638,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>200</v>
       </c>
@@ -8691,7 +8684,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>149</v>
       </c>
@@ -8740,7 +8733,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>196</v>
       </c>
@@ -8803,7 +8796,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>188</v>
       </c>
@@ -8876,7 +8869,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>191</v>
       </c>
@@ -8949,7 +8942,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>190</v>
       </c>
@@ -9022,7 +9015,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>189</v>
       </c>
@@ -9095,7 +9088,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="54" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>209</v>
       </c>
@@ -9155,7 +9148,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>213</v>
       </c>
@@ -9255,7 +9248,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="56" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>218</v>
       </c>
@@ -9305,7 +9298,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="57" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>223</v>
       </c>
@@ -9356,7 +9349,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="58" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>228</v>
       </c>
@@ -9406,7 +9399,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="59" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>242</v>
       </c>
@@ -9464,96 +9457,96 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:62" s="39" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A60" s="39" t="s">
+    <row r="60" spans="1:62" s="24" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="24" t="s">
         <v>243</v>
       </c>
-      <c r="B60" s="39" t="s">
+      <c r="B60" s="24" t="s">
         <v>298</v>
       </c>
       <c r="C60">
         <v>603</v>
       </c>
-      <c r="D60" s="40" t="s">
+      <c r="D60" s="39" t="s">
         <v>244</v>
       </c>
-      <c r="E60" s="39" t="s">
+      <c r="E60" s="24" t="s">
         <v>245</v>
       </c>
-      <c r="F60" s="39" t="s">
+      <c r="F60" s="24" t="s">
         <v>246</v>
       </c>
-      <c r="H60" s="41"/>
-      <c r="I60" s="41"/>
-      <c r="J60" s="41"/>
-      <c r="K60" s="41"/>
-      <c r="L60" s="41"/>
-      <c r="M60" s="41"/>
-      <c r="N60" s="41"/>
-      <c r="O60" s="41"/>
-      <c r="P60" s="41"/>
-      <c r="Q60" s="42" t="s">
+      <c r="H60" s="40"/>
+      <c r="I60" s="40"/>
+      <c r="J60" s="40"/>
+      <c r="K60" s="40"/>
+      <c r="L60" s="40"/>
+      <c r="M60" s="40"/>
+      <c r="N60" s="40"/>
+      <c r="O60" s="40"/>
+      <c r="P60" s="40"/>
+      <c r="Q60" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="R60" s="41" t="s">
+      <c r="R60" s="40" t="s">
         <v>247</v>
       </c>
-      <c r="S60" s="43">
+      <c r="S60" s="42">
         <v>50</v>
       </c>
-      <c r="T60" s="43"/>
-      <c r="U60" s="43"/>
-      <c r="V60" s="43"/>
-      <c r="W60" s="43"/>
-      <c r="X60" s="43"/>
-      <c r="Y60" s="44">
+      <c r="T60" s="42"/>
+      <c r="U60" s="42"/>
+      <c r="V60" s="42"/>
+      <c r="W60" s="42"/>
+      <c r="X60" s="42"/>
+      <c r="Y60" s="43">
         <v>9780316498845</v>
       </c>
-      <c r="Z60" s="45"/>
-      <c r="AA60" s="45"/>
-      <c r="AB60" s="46"/>
-      <c r="AC60" s="46"/>
-      <c r="AD60" s="46"/>
-      <c r="AE60" s="46"/>
-      <c r="AF60" s="46"/>
-      <c r="AG60" s="46"/>
-      <c r="AH60" s="46"/>
-      <c r="AI60" s="39" t="str">
+      <c r="Z60" s="44"/>
+      <c r="AA60" s="44"/>
+      <c r="AB60" s="45"/>
+      <c r="AC60" s="45"/>
+      <c r="AD60" s="45"/>
+      <c r="AE60" s="45"/>
+      <c r="AF60" s="45"/>
+      <c r="AG60" s="45"/>
+      <c r="AH60" s="45"/>
+      <c r="AI60" s="24" t="str">
         <f t="shared" si="0"/>
         <v>covers/witcher-set.jpg</v>
       </c>
-      <c r="AP60" s="39" t="s">
+      <c r="AP60" s="24" t="s">
         <v>1077</v>
       </c>
-      <c r="AR60" s="39" t="s">
+      <c r="AR60" s="24" t="s">
         <v>1076</v>
       </c>
-      <c r="AS60" s="39" t="s">
+      <c r="AS60" s="24" t="s">
         <v>1079</v>
       </c>
-      <c r="AU60" s="39" t="s">
+      <c r="AU60" s="24" t="s">
         <v>1078</v>
       </c>
-      <c r="AV60" s="39" t="s">
+      <c r="AV60" s="24" t="s">
         <v>1081</v>
       </c>
-      <c r="AX60" s="47" t="s">
+      <c r="AX60" s="38" t="s">
         <v>1080</v>
       </c>
-      <c r="AY60" s="48" t="s">
+      <c r="AY60" s="35" t="s">
         <v>248</v>
       </c>
-      <c r="BD60" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="BE60" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="BG60" s="39" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="61" spans="1:62" x14ac:dyDescent="0.45">
+      <c r="BD60" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="BE60" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="BG60" s="24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="61" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>249</v>
       </c>
@@ -9590,7 +9583,7 @@
         <f t="shared" si="0"/>
         <v>covers/tower-fools.jpg</v>
       </c>
-      <c r="AP61" s="39" t="s">
+      <c r="AP61" s="24" t="s">
         <v>1083</v>
       </c>
       <c r="AR61" t="s">
@@ -9621,7 +9614,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>254</v>
       </c>
@@ -9658,7 +9651,7 @@
         <f t="shared" si="0"/>
         <v>covers/warrior-god.jpg</v>
       </c>
-      <c r="AP62" s="39" t="s">
+      <c r="AP62" s="24" t="s">
         <v>1083</v>
       </c>
       <c r="AR62" t="s">
@@ -9683,7 +9676,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>257</v>
       </c>
@@ -9720,7 +9713,7 @@
         <f t="shared" si="0"/>
         <v>covers/light-perpetua.jpg</v>
       </c>
-      <c r="AP63" s="39" t="s">
+      <c r="AP63" s="24" t="s">
         <v>1083</v>
       </c>
       <c r="AR63" t="s">
@@ -9745,7 +9738,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>260</v>
       </c>
@@ -9812,7 +9805,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="65" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>266</v>
       </c>
@@ -9861,7 +9854,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>272</v>
       </c>
@@ -9913,7 +9906,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>277</v>
       </c>
@@ -9965,7 +9958,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>279</v>
       </c>
@@ -10016,7 +10009,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>283</v>
       </c>
@@ -10064,7 +10057,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>287</v>
       </c>
@@ -10112,7 +10105,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>291</v>
       </c>
@@ -10120,7 +10113,7 @@
         <v>74</v>
       </c>
       <c r="C71">
-        <v>457</v>
+        <v>1502</v>
       </c>
       <c r="D71" s="15" t="s">
         <v>292</v>
@@ -10160,7 +10153,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>295</v>
       </c>
@@ -10209,7 +10202,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>301</v>
       </c>
@@ -10268,7 +10261,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>308</v>
       </c>
@@ -10344,7 +10337,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>315</v>
       </c>
@@ -10424,7 +10417,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>265</v>
       </c>
@@ -10485,7 +10478,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="77" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>337</v>
       </c>
@@ -10539,7 +10532,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="78" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>345</v>
       </c>
@@ -10593,7 +10586,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="79" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>349</v>
       </c>
@@ -10647,7 +10640,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="80" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>400</v>
       </c>
@@ -10698,7 +10691,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>410</v>
       </c>
@@ -10752,7 +10745,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>413</v>
       </c>
@@ -10806,7 +10799,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="83" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>418</v>
       </c>
@@ -10854,7 +10847,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="84" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>422</v>
       </c>
@@ -10918,7 +10911,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>429</v>
       </c>
@@ -10969,7 +10962,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="86" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>435</v>
       </c>
@@ -10977,7 +10970,7 @@
         <v>74</v>
       </c>
       <c r="C86">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="D86" s="15" t="s">
         <v>434</v>
@@ -11023,7 +11016,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>440</v>
       </c>
@@ -11031,7 +11024,7 @@
         <v>74</v>
       </c>
       <c r="C87">
-        <v>810</v>
+        <v>351</v>
       </c>
       <c r="D87" s="15" t="s">
         <v>438</v>
@@ -11077,7 +11070,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="1:62" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:62" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>445</v>
       </c>
@@ -11131,7 +11124,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="89" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>451</v>
       </c>
@@ -11185,7 +11178,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>458</v>
       </c>
@@ -11255,7 +11248,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>463</v>
       </c>
@@ -11320,7 +11313,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="92" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>473</v>
       </c>
@@ -11380,7 +11373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>480</v>
       </c>
@@ -11434,7 +11427,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="94" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>484</v>
       </c>
@@ -11485,7 +11478,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="95" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>491</v>
       </c>
@@ -11538,7 +11531,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="96" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>501</v>
       </c>
@@ -11592,7 +11585,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="97" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>503</v>
       </c>
@@ -11643,7 +11636,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="98" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>468</v>
       </c>
@@ -11698,7 +11691,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="99" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>508</v>
       </c>
@@ -11753,7 +11746,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="100" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>511</v>
       </c>
@@ -11808,7 +11801,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="101" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>518</v>
       </c>
@@ -11865,7 +11858,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="102" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>524</v>
       </c>
@@ -11933,7 +11926,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="103" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>533</v>
       </c>
@@ -11998,7 +11991,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="104" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>534</v>
       </c>
@@ -12060,7 +12053,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="105" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>544</v>
       </c>
@@ -12125,7 +12118,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="106" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>549</v>
       </c>
@@ -12190,7 +12183,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="107" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>552</v>
       </c>
@@ -12255,7 +12248,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="108" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>558</v>
       </c>
@@ -12332,7 +12325,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="109" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>566</v>
       </c>
@@ -12397,7 +12390,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="110" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>569</v>
       </c>
@@ -12462,7 +12455,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="111" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>572</v>
       </c>
@@ -12523,7 +12516,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="112" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>577</v>
       </c>
@@ -12588,7 +12581,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="113" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>583</v>
       </c>
@@ -12653,7 +12646,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="114" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>590</v>
       </c>
@@ -12724,7 +12717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>594</v>
       </c>
@@ -12781,7 +12774,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>601</v>
       </c>
@@ -12857,7 +12850,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="117" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>604</v>
       </c>
@@ -12934,7 +12927,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="118" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>608</v>
       </c>
@@ -13011,7 +13004,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="119" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>613</v>
       </c>
@@ -13073,7 +13066,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="120" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>615</v>
       </c>
@@ -13138,7 +13131,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="121" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>621</v>
       </c>
@@ -13203,7 +13196,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>626</v>
       </c>
@@ -13266,7 +13259,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="123" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>633</v>
       </c>
@@ -13333,7 +13326,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="124" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>667</v>
       </c>
@@ -13399,7 +13392,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="125" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>672</v>
       </c>
@@ -13463,7 +13456,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="126" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>680</v>
       </c>
@@ -13511,7 +13504,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="127" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>682</v>
       </c>
@@ -13565,7 +13558,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="128" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>678</v>
       </c>
@@ -13616,7 +13609,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="129" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>716</v>
       </c>
@@ -13678,7 +13671,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="130" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>720</v>
       </c>
@@ -13756,7 +13749,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="131" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>726</v>
       </c>
@@ -13816,7 +13809,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>731</v>
       </c>
@@ -13893,7 +13886,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="133" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>736</v>
       </c>
@@ -13967,7 +13960,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="134" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>741</v>
       </c>
@@ -14020,7 +14013,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="135" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>746</v>
       </c>
@@ -14078,7 +14071,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>750</v>
       </c>
@@ -14140,7 +14133,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="137" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>755</v>
       </c>
@@ -14190,7 +14183,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="138" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>757</v>
       </c>
@@ -14265,7 +14258,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="139" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>762</v>
       </c>
@@ -14332,7 +14325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>766</v>
       </c>
@@ -14399,7 +14392,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="141" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>775</v>
       </c>
@@ -14465,7 +14458,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="142" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>776</v>
       </c>
@@ -14546,7 +14539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>784</v>
       </c>
@@ -14622,7 +14615,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>787</v>
       </c>
@@ -14694,7 +14687,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>793</v>
       </c>
@@ -14752,7 +14745,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>800</v>
       </c>
@@ -14805,7 +14798,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="147" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>807</v>
       </c>
@@ -14864,7 +14857,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="148" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>811</v>
       </c>
@@ -14936,7 +14929,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>815</v>
       </c>
@@ -14995,7 +14988,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="150" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>820</v>
       </c>
@@ -15064,7 +15057,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>825</v>
       </c>
@@ -15130,7 +15123,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="152" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>834</v>
       </c>
@@ -15191,7 +15184,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>837</v>
       </c>
@@ -15264,7 +15257,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>841</v>
       </c>
@@ -15319,7 +15312,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="155" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>1075</v>
       </c>
@@ -15370,7 +15363,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="156" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>855</v>
       </c>
@@ -15424,7 +15417,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="157" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>858</v>
       </c>
@@ -15489,7 +15482,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="158" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>864</v>
       </c>
@@ -15541,7 +15534,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="159" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>866</v>
       </c>
@@ -15606,7 +15599,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="160" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>872</v>
       </c>
@@ -15666,7 +15659,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>878</v>
       </c>
@@ -15746,7 +15739,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="162" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>885</v>
       </c>
@@ -15796,7 +15789,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="163" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>890</v>
       </c>
@@ -15870,7 +15863,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="164" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>898</v>
       </c>
@@ -15935,7 +15928,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="165" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>905</v>
       </c>
@@ -15997,7 +15990,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="166" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>908</v>
       </c>
@@ -16053,7 +16046,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="167" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>914</v>
       </c>
@@ -16114,7 +16107,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="168" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>921</v>
       </c>
@@ -16194,7 +16187,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>925</v>
       </c>
@@ -16246,7 +16239,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="170" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>932</v>
       </c>
@@ -16295,7 +16288,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="171" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>935</v>
       </c>
@@ -16370,7 +16363,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="172" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>941</v>
       </c>
@@ -16432,7 +16425,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="173" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>947</v>
       </c>
@@ -16500,7 +16493,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="174" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>954</v>
       </c>
@@ -16553,7 +16546,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="175" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>958</v>
       </c>
@@ -16606,7 +16599,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="176" spans="1:62" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>961</v>
       </c>
@@ -16659,7 +16652,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="177" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>963</v>
       </c>
@@ -16708,7 +16701,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="178" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>968</v>
       </c>
@@ -16772,7 +16765,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="179" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>976</v>
       </c>
@@ -16824,7 +16817,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="180" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>978</v>
       </c>
@@ -16876,7 +16869,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="181" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>983</v>
       </c>
@@ -16939,7 +16932,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="182" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>988</v>
       </c>
@@ -17003,7 +16996,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="183" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>996</v>
       </c>
@@ -17070,7 +17063,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="184" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>1001</v>
       </c>
@@ -17136,7 +17129,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="185" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>1005</v>
       </c>
@@ -17197,7 +17190,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="186" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>1010</v>
       </c>
@@ -17267,7 +17260,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="187" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>1035</v>
       </c>
@@ -17334,7 +17327,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="188" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>1042</v>
       </c>
@@ -17413,7 +17406,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="189" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>1049</v>
       </c>
@@ -17469,7 +17462,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="190" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>1054</v>
       </c>
@@ -17521,7 +17514,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="191" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>1061</v>
       </c>
@@ -17573,7 +17566,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="192" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>1058</v>
       </c>
@@ -17627,7 +17620,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="193" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:59" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>1068</v>
       </c>
@@ -17704,7 +17697,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="194" spans="1:59" ht="85.5" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:59" ht="105" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>1088</v>
       </c>
@@ -17740,7 +17733,7 @@
         <f t="shared" si="19"/>
         <v>Paperback</v>
       </c>
-      <c r="R194" s="49" t="str">
+      <c r="R194" s="46" t="str">
         <f>I194</f>
         <v xml:space="preserve">W. W. Norton </v>
       </c>
@@ -17756,10 +17749,10 @@
         <f t="shared" si="13"/>
         <v>covers/miracle-fair.jpg</v>
       </c>
-      <c r="AY194" s="50" t="s">
+      <c r="AY194" s="47" t="s">
         <v>1091</v>
       </c>
-      <c r="AZ194" s="51" t="s">
+      <c r="AZ194" s="48" t="s">
         <v>1092</v>
       </c>
       <c r="BD194" t="s">
@@ -17772,252 +17765,252 @@
         <v>31</v>
       </c>
     </row>
-    <row r="195" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:59" x14ac:dyDescent="0.25">
       <c r="H195" s="6"/>
       <c r="R195" s="2"/>
       <c r="Z195" s="4"/>
       <c r="AA195" s="4"/>
     </row>
-    <row r="196" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:59" x14ac:dyDescent="0.25">
       <c r="H196" s="6"/>
       <c r="R196" s="2"/>
       <c r="Z196" s="4"/>
       <c r="AA196" s="4"/>
     </row>
-    <row r="197" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:59" x14ac:dyDescent="0.25">
       <c r="H197" s="6"/>
       <c r="R197" s="2"/>
       <c r="Z197" s="4"/>
       <c r="AA197" s="4"/>
     </row>
-    <row r="198" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:59" x14ac:dyDescent="0.25">
       <c r="H198" s="6"/>
       <c r="R198" s="2"/>
       <c r="Z198" s="4"/>
       <c r="AA198" s="4"/>
     </row>
-    <row r="199" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:59" x14ac:dyDescent="0.25">
       <c r="H199" s="6"/>
       <c r="R199" s="2"/>
       <c r="Z199" s="4"/>
       <c r="AA199" s="4"/>
     </row>
-    <row r="200" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:59" x14ac:dyDescent="0.25">
       <c r="H200" s="6"/>
       <c r="R200" s="2"/>
       <c r="Z200" s="4"/>
       <c r="AA200" s="4"/>
     </row>
-    <row r="201" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:59" x14ac:dyDescent="0.25">
       <c r="H201" s="6"/>
       <c r="R201" s="2"/>
       <c r="Z201" s="4"/>
       <c r="AA201" s="4"/>
     </row>
-    <row r="202" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:59" x14ac:dyDescent="0.25">
       <c r="R202" s="2"/>
       <c r="Z202" s="4"/>
       <c r="AA202" s="4"/>
     </row>
-    <row r="203" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:59" x14ac:dyDescent="0.25">
       <c r="R203" s="2"/>
       <c r="Z203" s="4"/>
       <c r="AA203" s="4"/>
     </row>
-    <row r="204" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:59" x14ac:dyDescent="0.25">
       <c r="R204" s="2"/>
       <c r="Z204" s="4"/>
       <c r="AA204" s="4"/>
     </row>
-    <row r="205" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:59" x14ac:dyDescent="0.25">
       <c r="R205" s="2"/>
       <c r="Z205" s="4"/>
       <c r="AA205" s="4"/>
     </row>
-    <row r="206" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:59" x14ac:dyDescent="0.25">
       <c r="R206" s="2"/>
       <c r="Z206" s="4"/>
       <c r="AA206" s="4"/>
     </row>
-    <row r="207" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:59" x14ac:dyDescent="0.25">
       <c r="R207" s="2"/>
       <c r="Z207" s="4"/>
       <c r="AA207" s="4"/>
     </row>
-    <row r="208" spans="1:59" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:59" x14ac:dyDescent="0.25">
       <c r="R208" s="2"/>
       <c r="Z208" s="4"/>
       <c r="AA208" s="4"/>
     </row>
-    <row r="209" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="209" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R209" s="2"/>
       <c r="Z209" s="4"/>
       <c r="AA209" s="4"/>
     </row>
-    <row r="210" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="210" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R210" s="2"/>
       <c r="Z210" s="4"/>
       <c r="AA210" s="4"/>
     </row>
-    <row r="211" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="211" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R211" s="2"/>
       <c r="Z211" s="4"/>
       <c r="AA211" s="4"/>
     </row>
-    <row r="212" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="212" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R212" s="2"/>
       <c r="Z212" s="4"/>
       <c r="AA212" s="4"/>
     </row>
-    <row r="213" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="213" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R213" s="2"/>
       <c r="Z213" s="4"/>
       <c r="AA213" s="4"/>
     </row>
-    <row r="214" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="214" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R214" s="2"/>
       <c r="Z214" s="4"/>
       <c r="AA214" s="4"/>
     </row>
-    <row r="215" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="215" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R215" s="2"/>
       <c r="Z215" s="4"/>
       <c r="AA215" s="4"/>
     </row>
-    <row r="216" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="216" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R216" s="2"/>
       <c r="Z216" s="4"/>
       <c r="AA216" s="4"/>
     </row>
-    <row r="217" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="217" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R217" s="2"/>
       <c r="Z217" s="4"/>
       <c r="AA217" s="4"/>
     </row>
-    <row r="218" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="218" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R218" s="2"/>
       <c r="Z218" s="4"/>
       <c r="AA218" s="4"/>
     </row>
-    <row r="219" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="219" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R219" s="2"/>
       <c r="Z219" s="4"/>
       <c r="AA219" s="4"/>
     </row>
-    <row r="220" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="220" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R220" s="2"/>
       <c r="Z220" s="4"/>
       <c r="AA220" s="4"/>
     </row>
-    <row r="221" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="221" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R221" s="2"/>
       <c r="Z221" s="4"/>
       <c r="AA221" s="4"/>
     </row>
-    <row r="222" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="222" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R222" s="2"/>
       <c r="Z222" s="4"/>
       <c r="AA222" s="4"/>
     </row>
-    <row r="223" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="223" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R223" s="2"/>
       <c r="Z223" s="4"/>
       <c r="AA223" s="4"/>
     </row>
-    <row r="224" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="224" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R224" s="2"/>
       <c r="Z224" s="4"/>
       <c r="AA224" s="4"/>
     </row>
-    <row r="225" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="225" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R225" s="2"/>
       <c r="Z225" s="4"/>
       <c r="AA225" s="4"/>
     </row>
-    <row r="226" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="226" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R226" s="2"/>
       <c r="Z226" s="4"/>
       <c r="AA226" s="4"/>
     </row>
-    <row r="227" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="227" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R227" s="2"/>
       <c r="Z227" s="4"/>
       <c r="AA227" s="4"/>
     </row>
-    <row r="228" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="228" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R228" s="2"/>
       <c r="Z228" s="4"/>
       <c r="AA228" s="4"/>
     </row>
-    <row r="229" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="229" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R229" s="2"/>
       <c r="Z229" s="4"/>
       <c r="AA229" s="4"/>
     </row>
-    <row r="230" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="230" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R230" s="2"/>
       <c r="Z230" s="4"/>
       <c r="AA230" s="4"/>
     </row>
-    <row r="231" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="231" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R231" s="2"/>
       <c r="Z231" s="4"/>
       <c r="AA231" s="4"/>
     </row>
-    <row r="232" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="232" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R232" s="2"/>
       <c r="Z232" s="4"/>
       <c r="AA232" s="4"/>
     </row>
-    <row r="233" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="233" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R233" s="2"/>
       <c r="Z233" s="4"/>
       <c r="AA233" s="4"/>
     </row>
-    <row r="234" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="234" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R234" s="2"/>
       <c r="Z234" s="4"/>
       <c r="AA234" s="4"/>
     </row>
-    <row r="235" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="235" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R235" s="2"/>
       <c r="Z235" s="4"/>
       <c r="AA235" s="4"/>
     </row>
-    <row r="236" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="236" spans="18:27" x14ac:dyDescent="0.25">
       <c r="R236" s="2"/>
       <c r="Z236" s="4"/>
       <c r="AA236" s="4"/>
     </row>
-    <row r="237" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="237" spans="18:27" x14ac:dyDescent="0.25">
       <c r="Z237" s="4"/>
       <c r="AA237" s="4"/>
     </row>
-    <row r="238" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="238" spans="18:27" x14ac:dyDescent="0.25">
       <c r="Z238" s="4"/>
       <c r="AA238" s="4"/>
     </row>
-    <row r="239" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="239" spans="18:27" x14ac:dyDescent="0.25">
       <c r="Z239" s="4"/>
       <c r="AA239" s="4"/>
     </row>
-    <row r="240" spans="18:27" x14ac:dyDescent="0.45">
+    <row r="240" spans="18:27" x14ac:dyDescent="0.25">
       <c r="Z240" s="4"/>
       <c r="AA240" s="4"/>
     </row>
-    <row r="241" spans="26:27" x14ac:dyDescent="0.45">
+    <row r="241" spans="26:27" x14ac:dyDescent="0.25">
       <c r="Z241" s="4"/>
       <c r="AA241" s="4"/>
     </row>
-    <row r="242" spans="26:27" x14ac:dyDescent="0.45">
+    <row r="242" spans="26:27" x14ac:dyDescent="0.25">
       <c r="Z242" s="4"/>
       <c r="AA242" s="4"/>
     </row>
-    <row r="243" spans="26:27" x14ac:dyDescent="0.45">
+    <row r="243" spans="26:27" x14ac:dyDescent="0.25">
       <c r="Z243" s="4"/>
       <c r="AA243" s="4"/>
     </row>
-    <row r="244" spans="26:27" x14ac:dyDescent="0.45">
+    <row r="244" spans="26:27" x14ac:dyDescent="0.25">
       <c r="Z244" s="4"/>
       <c r="AA244" s="4"/>
     </row>

--- a/catalog.xlsx
+++ b/catalog.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/abac970dd7fde214/ATHENEUM/the-polish-atheneum/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3559" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{14E546A4-A97F-41BF-AA05-922B5CA223B4}"/>
+  <xr:revisionPtr revIDLastSave="3563" documentId="8_{7A17575A-3159-426C-AEB6-2C4506AAA768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EE20892-E678-4D1B-8FF0-3829AB219E35}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{2B1B7759-F909-4AF6-A557-483382B14A56}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -4761,6 +4761,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5081,33 +5085,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{01CE5F32-AD1D-47CB-A8F1-52ACBFFA0BE8}">
   <dimension ref="A1:BJ244"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="29.140625" customWidth="1"/>
-    <col min="2" max="2" width="50.85546875" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="1" max="1" width="29.1328125" customWidth="1"/>
+    <col min="2" max="2" width="50.86328125" customWidth="1"/>
+    <col min="3" max="3" width="13.73046875" customWidth="1"/>
     <col min="4" max="4" width="46" style="15" customWidth="1"/>
     <col min="5" max="7" width="46" customWidth="1"/>
-    <col min="8" max="10" width="9.140625" style="7"/>
+    <col min="8" max="10" width="9.1328125" style="7"/>
     <col min="11" max="12" width="9" style="7"/>
-    <col min="13" max="15" width="9.140625" style="7"/>
-    <col min="16" max="16" width="28.85546875" style="10" customWidth="1"/>
-    <col min="17" max="24" width="9.140625" style="3"/>
+    <col min="13" max="15" width="9.1328125" style="7"/>
+    <col min="16" max="16" width="28.86328125" style="10" customWidth="1"/>
+    <col min="17" max="24" width="9.1328125" style="3"/>
     <col min="25" max="25" width="17" style="20" customWidth="1"/>
-    <col min="26" max="33" width="9.140625" style="5"/>
+    <col min="26" max="33" width="9.1328125" style="5"/>
     <col min="34" max="34" width="22" style="8" customWidth="1"/>
-    <col min="35" max="36" width="26.28515625" customWidth="1"/>
+    <col min="35" max="36" width="26.265625" customWidth="1"/>
     <col min="39" max="39" width="16" customWidth="1"/>
-    <col min="41" max="41" width="21.140625" customWidth="1"/>
-    <col min="42" max="45" width="19.7109375" customWidth="1"/>
-    <col min="46" max="46" width="19.7109375" style="24" customWidth="1"/>
-    <col min="47" max="50" width="19.7109375" customWidth="1"/>
-    <col min="51" max="51" width="95.85546875" style="33" customWidth="1"/>
-    <col min="52" max="52" width="66.85546875" style="24" customWidth="1"/>
-    <col min="53" max="55" width="19.7109375" customWidth="1"/>
+    <col min="41" max="41" width="21.1328125" customWidth="1"/>
+    <col min="42" max="45" width="19.73046875" customWidth="1"/>
+    <col min="46" max="46" width="19.73046875" style="24" customWidth="1"/>
+    <col min="47" max="50" width="19.73046875" customWidth="1"/>
+    <col min="51" max="51" width="95.86328125" style="33" customWidth="1"/>
+    <col min="52" max="52" width="66.86328125" style="24" customWidth="1"/>
+    <col min="53" max="55" width="19.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -5295,7 +5299,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -5381,7 +5385,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -5455,7 +5459,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -5536,7 +5540,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>76</v>
       </c>
@@ -5592,7 +5596,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -5659,7 +5663,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -5725,7 +5729,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>42</v>
       </c>
@@ -5795,7 +5799,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="9" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>48</v>
       </c>
@@ -5869,7 +5873,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -5939,7 +5943,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>57</v>
       </c>
@@ -6004,7 +6008,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>62</v>
       </c>
@@ -6073,7 +6077,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -6132,7 +6136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>68</v>
       </c>
@@ -6193,7 +6197,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="15" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>72</v>
       </c>
@@ -6258,7 +6262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>73</v>
       </c>
@@ -6323,7 +6327,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>123</v>
       </c>
@@ -6409,7 +6413,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>367</v>
       </c>
@@ -6470,7 +6474,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>122</v>
       </c>
@@ -6556,7 +6560,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>84</v>
       </c>
@@ -6651,7 +6655,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>80</v>
       </c>
@@ -6746,7 +6750,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>1018</v>
       </c>
@@ -6841,7 +6845,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>1020</v>
       </c>
@@ -6936,7 +6940,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>1024</v>
       </c>
@@ -7031,7 +7035,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="25" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>1027</v>
       </c>
@@ -7126,7 +7130,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>1030</v>
       </c>
@@ -7221,7 +7225,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>1064</v>
       </c>
@@ -7319,7 +7323,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>87</v>
       </c>
@@ -7399,7 +7403,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>91</v>
       </c>
@@ -7455,7 +7459,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>121</v>
       </c>
@@ -7511,7 +7515,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>105</v>
       </c>
@@ -7604,7 +7608,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>1033</v>
       </c>
@@ -7695,7 +7699,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>96</v>
       </c>
@@ -7803,7 +7807,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>97</v>
       </c>
@@ -7885,7 +7889,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>104</v>
       </c>
@@ -7949,7 +7953,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
         <v>103</v>
       </c>
@@ -8013,7 +8017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
         <v>116</v>
       </c>
@@ -8091,7 +8095,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
         <v>117</v>
       </c>
@@ -8169,7 +8173,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
         <v>118</v>
       </c>
@@ -8237,7 +8241,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
         <v>150</v>
       </c>
@@ -8285,7 +8289,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="41" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
         <v>154</v>
       </c>
@@ -8344,7 +8348,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="42" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
         <v>155</v>
       </c>
@@ -8395,7 +8399,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
         <v>145</v>
       </c>
@@ -8446,7 +8450,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
         <v>146</v>
       </c>
@@ -8512,7 +8516,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="45" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
         <v>147</v>
       </c>
@@ -8575,7 +8579,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="46" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
         <v>148</v>
       </c>
@@ -8638,7 +8642,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
         <v>200</v>
       </c>
@@ -8684,7 +8688,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
         <v>149</v>
       </c>
@@ -8733,7 +8737,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="49" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
         <v>196</v>
       </c>
@@ -8796,7 +8800,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="50" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
         <v>188</v>
       </c>
@@ -8869,7 +8873,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="51" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
         <v>191</v>
       </c>
@@ -8942,7 +8946,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="52" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
         <v>190</v>
       </c>
@@ -9015,7 +9019,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="53" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
         <v>189</v>
       </c>
@@ -9088,7 +9092,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="54" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
         <v>209</v>
       </c>
@@ -9148,7 +9152,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
         <v>213</v>
       </c>
@@ -9248,7 +9252,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="56" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
         <v>218</v>
       </c>
@@ -9298,7 +9302,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="57" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
         <v>223</v>
       </c>
@@ -9349,7 +9353,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="58" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
         <v>228</v>
       </c>
@@ -9399,7 +9403,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="59" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
         <v>242</v>
       </c>
@@ -9457,7 +9461,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="60" spans="1:62" s="24" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:62" s="24" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A60" s="24" t="s">
         <v>243</v>
       </c>
@@ -9546,7 +9550,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
         <v>249</v>
       </c>
@@ -9554,7 +9558,7 @@
         <v>298</v>
       </c>
       <c r="C61">
-        <v>850</v>
+        <v>575</v>
       </c>
       <c r="D61" s="15" t="s">
         <v>250</v>
@@ -9614,7 +9618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
         <v>254</v>
       </c>
@@ -9676,7 +9680,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
         <v>257</v>
       </c>
@@ -9738,7 +9742,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="64" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
         <v>260</v>
       </c>
@@ -9805,7 +9809,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="65" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
         <v>266</v>
       </c>
@@ -9854,7 +9858,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="66" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
         <v>272</v>
       </c>
@@ -9906,7 +9910,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
         <v>277</v>
       </c>
@@ -9958,7 +9962,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
         <v>279</v>
       </c>
@@ -10009,7 +10013,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
         <v>283</v>
       </c>
@@ -10057,7 +10061,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A70" t="s">
         <v>287</v>
       </c>
@@ -10105,7 +10109,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
         <v>291</v>
       </c>
@@ -10153,7 +10157,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A72" t="s">
         <v>295</v>
       </c>
@@ -10202,7 +10206,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A73" t="s">
         <v>301</v>
       </c>
@@ -10261,7 +10265,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A74" t="s">
         <v>308</v>
       </c>
@@ -10337,7 +10341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A75" t="s">
         <v>315</v>
       </c>
@@ -10417,7 +10421,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
         <v>265</v>
       </c>
@@ -10478,7 +10482,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="77" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A77" t="s">
         <v>337</v>
       </c>
@@ -10532,7 +10536,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="78" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A78" t="s">
         <v>345</v>
       </c>
@@ -10586,7 +10590,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="79" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A79" t="s">
         <v>349</v>
       </c>
@@ -10640,7 +10644,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="80" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
         <v>400</v>
       </c>
@@ -10691,7 +10695,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="81" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
         <v>410</v>
       </c>
@@ -10745,7 +10749,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="82" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A82" t="s">
         <v>413</v>
       </c>
@@ -10799,7 +10803,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="83" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A83" t="s">
         <v>418</v>
       </c>
@@ -10847,7 +10851,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="84" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A84" t="s">
         <v>422</v>
       </c>
@@ -10911,7 +10915,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="85" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A85" t="s">
         <v>429</v>
       </c>
@@ -10962,7 +10966,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="86" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A86" t="s">
         <v>435</v>
       </c>
@@ -11016,7 +11020,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="87" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A87" t="s">
         <v>440</v>
       </c>
@@ -11070,7 +11074,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="88" spans="1:62" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:62" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
         <v>445</v>
       </c>
@@ -11124,7 +11128,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="89" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
         <v>451</v>
       </c>
@@ -11178,7 +11182,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="90" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
         <v>458</v>
       </c>
@@ -11248,7 +11252,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
         <v>463</v>
       </c>
@@ -11313,7 +11317,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="92" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
         <v>473</v>
       </c>
@@ -11373,7 +11377,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A93" t="s">
         <v>480</v>
       </c>
@@ -11427,7 +11431,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="94" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
         <v>484</v>
       </c>
@@ -11478,7 +11482,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="95" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A95" t="s">
         <v>491</v>
       </c>
@@ -11531,7 +11535,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="96" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A96" t="s">
         <v>501</v>
       </c>
@@ -11585,7 +11589,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="97" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A97" t="s">
         <v>503</v>
       </c>
@@ -11636,7 +11640,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="98" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A98" t="s">
         <v>468</v>
       </c>
@@ -11691,7 +11695,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="99" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A99" t="s">
         <v>508</v>
       </c>
@@ -11746,7 +11750,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="100" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A100" t="s">
         <v>511</v>
       </c>
@@ -11801,7 +11805,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="101" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A101" t="s">
         <v>518</v>
       </c>
@@ -11858,7 +11862,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="102" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A102" t="s">
         <v>524</v>
       </c>
@@ -11926,7 +11930,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="103" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A103" t="s">
         <v>533</v>
       </c>
@@ -11991,7 +11995,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="104" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A104" t="s">
         <v>534</v>
       </c>
@@ -12053,7 +12057,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="105" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A105" t="s">
         <v>544</v>
       </c>
@@ -12118,7 +12122,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="106" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A106" t="s">
         <v>549</v>
       </c>
@@ -12183,7 +12187,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="107" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A107" t="s">
         <v>552</v>
       </c>
@@ -12248,7 +12252,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="108" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A108" t="s">
         <v>558</v>
       </c>
@@ -12325,7 +12329,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="109" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A109" t="s">
         <v>566</v>
       </c>
@@ -12390,7 +12394,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="110" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A110" t="s">
         <v>569</v>
       </c>
@@ -12455,7 +12459,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="111" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A111" t="s">
         <v>572</v>
       </c>
@@ -12516,7 +12520,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="112" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A112" t="s">
         <v>577</v>
       </c>
@@ -12581,7 +12585,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="113" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A113" t="s">
         <v>583</v>
       </c>
@@ -12646,7 +12650,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="114" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A114" t="s">
         <v>590</v>
       </c>
@@ -12717,7 +12721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A115" t="s">
         <v>594</v>
       </c>
@@ -12774,7 +12778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A116" t="s">
         <v>601</v>
       </c>
@@ -12850,7 +12854,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="117" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A117" t="s">
         <v>604</v>
       </c>
@@ -12927,7 +12931,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="118" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A118" t="s">
         <v>608</v>
       </c>
@@ -13004,7 +13008,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="119" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A119" t="s">
         <v>613</v>
       </c>
@@ -13066,7 +13070,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="120" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A120" t="s">
         <v>615</v>
       </c>
@@ -13131,7 +13135,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="121" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A121" t="s">
         <v>621</v>
       </c>
@@ -13196,7 +13200,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A122" t="s">
         <v>626</v>
       </c>
@@ -13259,7 +13263,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="123" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A123" t="s">
         <v>633</v>
       </c>
@@ -13326,7 +13330,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="124" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A124" t="s">
         <v>667</v>
       </c>
@@ -13392,7 +13396,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="125" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A125" t="s">
         <v>672</v>
       </c>
@@ -13456,7 +13460,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="126" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A126" t="s">
         <v>680</v>
       </c>
@@ -13504,7 +13508,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="127" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A127" t="s">
         <v>682</v>
       </c>
@@ -13558,7 +13562,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="128" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A128" t="s">
         <v>678</v>
       </c>
@@ -13609,7 +13613,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="129" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A129" t="s">
         <v>716</v>
       </c>
@@ -13671,7 +13675,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="130" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A130" t="s">
         <v>720</v>
       </c>
@@ -13749,7 +13753,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="131" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A131" t="s">
         <v>726</v>
       </c>
@@ -13809,7 +13813,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="132" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A132" t="s">
         <v>731</v>
       </c>
@@ -13886,7 +13890,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="133" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A133" t="s">
         <v>736</v>
       </c>
@@ -13960,7 +13964,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="134" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A134" t="s">
         <v>741</v>
       </c>
@@ -14013,7 +14017,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="135" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A135" t="s">
         <v>746</v>
       </c>
@@ -14071,7 +14075,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="136" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A136" t="s">
         <v>750</v>
       </c>
@@ -14133,7 +14137,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="137" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A137" t="s">
         <v>755</v>
       </c>
@@ -14183,7 +14187,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="138" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A138" t="s">
         <v>757</v>
       </c>
@@ -14258,7 +14262,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="139" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A139" t="s">
         <v>762</v>
       </c>
@@ -14325,7 +14329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A140" t="s">
         <v>766</v>
       </c>
@@ -14392,7 +14396,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="141" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A141" t="s">
         <v>775</v>
       </c>
@@ -14458,7 +14462,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="142" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A142" t="s">
         <v>776</v>
       </c>
@@ -14539,7 +14543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A143" t="s">
         <v>784</v>
       </c>
@@ -14615,7 +14619,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A144" t="s">
         <v>787</v>
       </c>
@@ -14687,7 +14691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A145" t="s">
         <v>793</v>
       </c>
@@ -14745,7 +14749,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A146" t="s">
         <v>800</v>
       </c>
@@ -14798,7 +14802,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="147" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A147" t="s">
         <v>807</v>
       </c>
@@ -14857,7 +14861,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="148" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A148" t="s">
         <v>811</v>
       </c>
@@ -14929,7 +14933,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="149" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A149" t="s">
         <v>815</v>
       </c>
@@ -14988,7 +14992,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="150" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A150" t="s">
         <v>820</v>
       </c>
@@ -15057,7 +15061,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="151" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A151" t="s">
         <v>825</v>
       </c>
@@ -15123,7 +15127,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="152" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A152" t="s">
         <v>834</v>
       </c>
@@ -15184,7 +15188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A153" t="s">
         <v>837</v>
       </c>
@@ -15257,7 +15261,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A154" t="s">
         <v>841</v>
       </c>
@@ -15312,7 +15316,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="155" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A155" t="s">
         <v>1075</v>
       </c>
@@ -15363,7 +15367,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="156" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A156" t="s">
         <v>855</v>
       </c>
@@ -15417,7 +15421,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="157" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A157" t="s">
         <v>858</v>
       </c>
@@ -15482,7 +15486,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="158" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A158" t="s">
         <v>864</v>
       </c>
@@ -15534,7 +15538,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="159" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A159" t="s">
         <v>866</v>
       </c>
@@ -15599,7 +15603,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="160" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A160" t="s">
         <v>872</v>
       </c>
@@ -15659,7 +15663,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A161" t="s">
         <v>878</v>
       </c>
@@ -15739,7 +15743,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="162" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A162" t="s">
         <v>885</v>
       </c>
@@ -15789,7 +15793,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="163" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A163" t="s">
         <v>890</v>
       </c>
@@ -15863,7 +15867,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="164" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A164" t="s">
         <v>898</v>
       </c>
@@ -15928,7 +15932,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="165" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A165" t="s">
         <v>905</v>
       </c>
@@ -15990,7 +15994,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="166" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A166" t="s">
         <v>908</v>
       </c>
@@ -16046,7 +16050,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="167" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A167" t="s">
         <v>914</v>
       </c>
@@ -16107,7 +16111,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="168" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A168" t="s">
         <v>921</v>
       </c>
@@ -16187,7 +16191,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="169" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A169" t="s">
         <v>925</v>
       </c>
@@ -16239,7 +16243,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="170" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A170" t="s">
         <v>932</v>
       </c>
@@ -16288,7 +16292,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="171" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A171" t="s">
         <v>935</v>
       </c>
@@ -16363,7 +16367,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="172" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A172" t="s">
         <v>941</v>
       </c>
@@ -16425,7 +16429,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="173" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A173" t="s">
         <v>947</v>
       </c>
@@ -16493,7 +16497,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="174" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A174" t="s">
         <v>954</v>
       </c>
@@ -16546,7 +16550,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="175" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A175" t="s">
         <v>958</v>
       </c>
@@ -16599,7 +16603,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="176" spans="1:62" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:62" x14ac:dyDescent="0.45">
       <c r="A176" t="s">
         <v>961</v>
       </c>
@@ -16652,7 +16656,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="177" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A177" t="s">
         <v>963</v>
       </c>
@@ -16701,7 +16705,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="178" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A178" t="s">
         <v>968</v>
       </c>
@@ -16765,7 +16769,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="179" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A179" t="s">
         <v>976</v>
       </c>
@@ -16817,7 +16821,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="180" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A180" t="s">
         <v>978</v>
       </c>
@@ -16869,7 +16873,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="181" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A181" t="s">
         <v>983</v>
       </c>
@@ -16932,7 +16936,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="182" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A182" t="s">
         <v>988</v>
       </c>
@@ -16996,7 +17000,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="183" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A183" t="s">
         <v>996</v>
       </c>
@@ -17063,7 +17067,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="184" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A184" t="s">
         <v>1001</v>
       </c>
@@ -17129,7 +17133,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="185" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A185" t="s">
         <v>1005</v>
       </c>
@@ -17190,7 +17194,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="186" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A186" t="s">
         <v>1010</v>
       </c>
@@ -17260,7 +17264,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="187" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A187" t="s">
         <v>1035</v>
       </c>
@@ -17327,7 +17331,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="188" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A188" t="s">
         <v>1042</v>
       </c>
@@ -17406,7 +17410,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="189" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A189" t="s">
         <v>1049</v>
       </c>
@@ -17462,7 +17466,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="190" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A190" t="s">
         <v>1054</v>
       </c>
@@ -17470,7 +17474,7 @@
         <v>298</v>
       </c>
       <c r="C190">
-        <v>575</v>
+        <v>1575</v>
       </c>
       <c r="D190" s="15" t="s">
         <v>1053</v>
@@ -17514,7 +17518,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="191" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A191" t="s">
         <v>1061</v>
       </c>
@@ -17566,7 +17570,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="192" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A192" t="s">
         <v>1058</v>
       </c>
@@ -17620,7 +17624,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="193" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:59" x14ac:dyDescent="0.45">
       <c r="A193" t="s">
         <v>1068</v>
       </c>
@@ -17697,7 +17701,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="194" spans="1:59" ht="105" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:59" ht="85.5" x14ac:dyDescent="0.45">
       <c r="A194" t="s">
         <v>1088</v>
       </c>
@@ -17765,252 +17769,252 @@
         <v>31</v>
       </c>
     </row>
-    <row r="195" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:59" x14ac:dyDescent="0.45">
       <c r="H195" s="6"/>
       <c r="R195" s="2"/>
       <c r="Z195" s="4"/>
       <c r="AA195" s="4"/>
     </row>
-    <row r="196" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:59" x14ac:dyDescent="0.45">
       <c r="H196" s="6"/>
       <c r="R196" s="2"/>
       <c r="Z196" s="4"/>
       <c r="AA196" s="4"/>
     </row>
-    <row r="197" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:59" x14ac:dyDescent="0.45">
       <c r="H197" s="6"/>
       <c r="R197" s="2"/>
       <c r="Z197" s="4"/>
       <c r="AA197" s="4"/>
     </row>
-    <row r="198" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:59" x14ac:dyDescent="0.45">
       <c r="H198" s="6"/>
       <c r="R198" s="2"/>
       <c r="Z198" s="4"/>
       <c r="AA198" s="4"/>
     </row>
-    <row r="199" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:59" x14ac:dyDescent="0.45">
       <c r="H199" s="6"/>
       <c r="R199" s="2"/>
       <c r="Z199" s="4"/>
       <c r="AA199" s="4"/>
     </row>
-    <row r="200" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:59" x14ac:dyDescent="0.45">
       <c r="H200" s="6"/>
       <c r="R200" s="2"/>
       <c r="Z200" s="4"/>
       <c r="AA200" s="4"/>
     </row>
-    <row r="201" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:59" x14ac:dyDescent="0.45">
       <c r="H201" s="6"/>
       <c r="R201" s="2"/>
       <c r="Z201" s="4"/>
       <c r="AA201" s="4"/>
     </row>
-    <row r="202" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:59" x14ac:dyDescent="0.45">
       <c r="R202" s="2"/>
       <c r="Z202" s="4"/>
       <c r="AA202" s="4"/>
     </row>
-    <row r="203" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:59" x14ac:dyDescent="0.45">
       <c r="R203" s="2"/>
       <c r="Z203" s="4"/>
       <c r="AA203" s="4"/>
     </row>
-    <row r="204" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:59" x14ac:dyDescent="0.45">
       <c r="R204" s="2"/>
       <c r="Z204" s="4"/>
       <c r="AA204" s="4"/>
     </row>
-    <row r="205" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:59" x14ac:dyDescent="0.45">
       <c r="R205" s="2"/>
       <c r="Z205" s="4"/>
       <c r="AA205" s="4"/>
     </row>
-    <row r="206" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:59" x14ac:dyDescent="0.45">
       <c r="R206" s="2"/>
       <c r="Z206" s="4"/>
       <c r="AA206" s="4"/>
     </row>
-    <row r="207" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:59" x14ac:dyDescent="0.45">
       <c r="R207" s="2"/>
       <c r="Z207" s="4"/>
       <c r="AA207" s="4"/>
     </row>
-    <row r="208" spans="1:59" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:59" x14ac:dyDescent="0.45">
       <c r="R208" s="2"/>
       <c r="Z208" s="4"/>
       <c r="AA208" s="4"/>
     </row>
-    <row r="209" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="209" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R209" s="2"/>
       <c r="Z209" s="4"/>
       <c r="AA209" s="4"/>
     </row>
-    <row r="210" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="210" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R210" s="2"/>
       <c r="Z210" s="4"/>
       <c r="AA210" s="4"/>
     </row>
-    <row r="211" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="211" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R211" s="2"/>
       <c r="Z211" s="4"/>
       <c r="AA211" s="4"/>
     </row>
-    <row r="212" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="212" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R212" s="2"/>
       <c r="Z212" s="4"/>
       <c r="AA212" s="4"/>
     </row>
-    <row r="213" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="213" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R213" s="2"/>
       <c r="Z213" s="4"/>
       <c r="AA213" s="4"/>
     </row>
-    <row r="214" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="214" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R214" s="2"/>
       <c r="Z214" s="4"/>
       <c r="AA214" s="4"/>
     </row>
-    <row r="215" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="215" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R215" s="2"/>
       <c r="Z215" s="4"/>
       <c r="AA215" s="4"/>
     </row>
-    <row r="216" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="216" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R216" s="2"/>
       <c r="Z216" s="4"/>
       <c r="AA216" s="4"/>
     </row>
-    <row r="217" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="217" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R217" s="2"/>
       <c r="Z217" s="4"/>
       <c r="AA217" s="4"/>
     </row>
-    <row r="218" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="218" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R218" s="2"/>
       <c r="Z218" s="4"/>
       <c r="AA218" s="4"/>
     </row>
-    <row r="219" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="219" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R219" s="2"/>
       <c r="Z219" s="4"/>
       <c r="AA219" s="4"/>
     </row>
-    <row r="220" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="220" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R220" s="2"/>
       <c r="Z220" s="4"/>
       <c r="AA220" s="4"/>
     </row>
-    <row r="221" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="221" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R221" s="2"/>
       <c r="Z221" s="4"/>
       <c r="AA221" s="4"/>
     </row>
-    <row r="222" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="222" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R222" s="2"/>
       <c r="Z222" s="4"/>
       <c r="AA222" s="4"/>
     </row>
-    <row r="223" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="223" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R223" s="2"/>
       <c r="Z223" s="4"/>
       <c r="AA223" s="4"/>
     </row>
-    <row r="224" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="224" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R224" s="2"/>
       <c r="Z224" s="4"/>
       <c r="AA224" s="4"/>
     </row>
-    <row r="225" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="225" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R225" s="2"/>
       <c r="Z225" s="4"/>
       <c r="AA225" s="4"/>
     </row>
-    <row r="226" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="226" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R226" s="2"/>
       <c r="Z226" s="4"/>
       <c r="AA226" s="4"/>
     </row>
-    <row r="227" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="227" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R227" s="2"/>
       <c r="Z227" s="4"/>
       <c r="AA227" s="4"/>
     </row>
-    <row r="228" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="228" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R228" s="2"/>
       <c r="Z228" s="4"/>
       <c r="AA228" s="4"/>
     </row>
-    <row r="229" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="229" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R229" s="2"/>
       <c r="Z229" s="4"/>
       <c r="AA229" s="4"/>
     </row>
-    <row r="230" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="230" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R230" s="2"/>
       <c r="Z230" s="4"/>
       <c r="AA230" s="4"/>
     </row>
-    <row r="231" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="231" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R231" s="2"/>
       <c r="Z231" s="4"/>
       <c r="AA231" s="4"/>
     </row>
-    <row r="232" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="232" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R232" s="2"/>
       <c r="Z232" s="4"/>
       <c r="AA232" s="4"/>
     </row>
-    <row r="233" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="233" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R233" s="2"/>
       <c r="Z233" s="4"/>
       <c r="AA233" s="4"/>
     </row>
-    <row r="234" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="234" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R234" s="2"/>
       <c r="Z234" s="4"/>
       <c r="AA234" s="4"/>
     </row>
-    <row r="235" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="235" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R235" s="2"/>
       <c r="Z235" s="4"/>
       <c r="AA235" s="4"/>
     </row>
-    <row r="236" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="236" spans="18:27" x14ac:dyDescent="0.45">
       <c r="R236" s="2"/>
       <c r="Z236" s="4"/>
       <c r="AA236" s="4"/>
     </row>
-    <row r="237" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="237" spans="18:27" x14ac:dyDescent="0.45">
       <c r="Z237" s="4"/>
       <c r="AA237" s="4"/>
     </row>
-    <row r="238" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="238" spans="18:27" x14ac:dyDescent="0.45">
       <c r="Z238" s="4"/>
       <c r="AA238" s="4"/>
     </row>
-    <row r="239" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="239" spans="18:27" x14ac:dyDescent="0.45">
       <c r="Z239" s="4"/>
       <c r="AA239" s="4"/>
     </row>
-    <row r="240" spans="18:27" x14ac:dyDescent="0.25">
+    <row r="240" spans="18:27" x14ac:dyDescent="0.45">
       <c r="Z240" s="4"/>
       <c r="AA240" s="4"/>
     </row>
-    <row r="241" spans="26:27" x14ac:dyDescent="0.25">
+    <row r="241" spans="26:27" x14ac:dyDescent="0.45">
       <c r="Z241" s="4"/>
       <c r="AA241" s="4"/>
     </row>
-    <row r="242" spans="26:27" x14ac:dyDescent="0.25">
+    <row r="242" spans="26:27" x14ac:dyDescent="0.45">
       <c r="Z242" s="4"/>
       <c r="AA242" s="4"/>
     </row>
-    <row r="243" spans="26:27" x14ac:dyDescent="0.25">
+    <row r="243" spans="26:27" x14ac:dyDescent="0.45">
       <c r="Z243" s="4"/>
       <c r="AA243" s="4"/>
     </row>
-    <row r="244" spans="26:27" x14ac:dyDescent="0.25">
+    <row r="244" spans="26:27" x14ac:dyDescent="0.45">
       <c r="Z244" s="4"/>
       <c r="AA244" s="4"/>
     </row>
